--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-25.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-25.xlsx
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-23 01:49:35</t>
+          <t>2026-03-23 03:55:01</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-23 01:49:35</t>
+          <t>2026-03-23 03:55:01</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-23 01:49:35</t>
+          <t>2026-03-23 03:55:01</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-23 01:49:35</t>
+          <t>2026-03-23 03:55:01</t>
         </is>
       </c>
     </row>
@@ -1539,7 +1539,7 @@
         <v>4.2</v>
       </c>
       <c r="H6" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="I6" t="n">
         <v>2.24</v>
@@ -1548,7 +1548,7 @@
         <v>3.5</v>
       </c>
       <c r="K6" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-23 01:49:35</t>
+          <t>2026-03-23 03:55:01</t>
         </is>
       </c>
     </row>
@@ -1727,22 +1727,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="G7" t="n">
         <v>3.5</v>
       </c>
       <c r="H7" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="I7" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="J7" t="n">
         <v>3.4</v>
       </c>
       <c r="K7" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-23 01:49:35</t>
+          <t>2026-03-23 03:55:01</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
         <v>3.35</v>
       </c>
       <c r="K8" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-23 01:49:35</t>
+          <t>2026-03-23 03:55:01</t>
         </is>
       </c>
     </row>
@@ -2115,7 +2115,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="G9" t="n">
         <v>3.5</v>
@@ -2148,7 +2148,7 @@
         <v>1.51</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.48</v>
+        <v>2.42</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-23 01:49:35</t>
+          <t>2026-03-23 03:55:01</t>
         </is>
       </c>
     </row>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-23 01:49:35</t>
+          <t>2026-03-23 03:55:01</t>
         </is>
       </c>
     </row>
@@ -2503,19 +2503,19 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4.4</v>
+        <v>6.6</v>
       </c>
       <c r="G11" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H11" t="n">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="I11" t="n">
         <v>1.76</v>
       </c>
       <c r="J11" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="K11" t="n">
         <v>4.3</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-23 01:49:35</t>
+          <t>2026-03-23 03:55:01</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-25.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-25.xlsx
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-23 03:55:01</t>
+          <t>2026-03-23 06:00:41</t>
         </is>
       </c>
     </row>
@@ -951,16 +951,16 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="G3" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="H3" t="n">
         <v>4.1</v>
       </c>
       <c r="I3" t="n">
-        <v>5.4</v>
+        <v>4.7</v>
       </c>
       <c r="J3" t="n">
         <v>3.65</v>
@@ -984,7 +984,7 @@
         <v>2.04</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.67</v>
+        <v>1.79</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-23 03:55:01</t>
+          <t>2026-03-23 06:00:41</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-23 03:55:01</t>
+          <t>2026-03-23 06:00:41</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-23 03:55:01</t>
+          <t>2026-03-23 06:00:41</t>
         </is>
       </c>
     </row>
@@ -1533,22 +1533,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="G6" t="n">
         <v>4.2</v>
       </c>
       <c r="H6" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="I6" t="n">
         <v>2.24</v>
       </c>
       <c r="J6" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K6" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1566,7 +1566,7 @@
         <v>2</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-23 03:55:01</t>
+          <t>2026-03-23 06:00:41</t>
         </is>
       </c>
     </row>
@@ -1736,10 +1736,10 @@
         <v>2.24</v>
       </c>
       <c r="I7" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="J7" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="K7" t="n">
         <v>3.7</v>
@@ -1760,7 +1760,7 @@
         <v>2.1</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-23 03:55:01</t>
+          <t>2026-03-23 06:00:41</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
         <v>2.3</v>
       </c>
       <c r="I8" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="J8" t="n">
         <v>3.35</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-23 03:55:01</t>
+          <t>2026-03-23 06:00:41</t>
         </is>
       </c>
     </row>
@@ -2118,16 +2118,16 @@
         <v>2.86</v>
       </c>
       <c r="G9" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="H9" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="I9" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="J9" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="K9" t="n">
         <v>3.3</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-23 03:55:01</t>
+          <t>2026-03-23 06:00:41</t>
         </is>
       </c>
     </row>
@@ -2309,22 +2309,22 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="G10" t="n">
         <v>2.7</v>
       </c>
       <c r="H10" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="I10" t="n">
         <v>4.2</v>
       </c>
       <c r="J10" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="K10" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-23 03:55:01</t>
+          <t>2026-03-23 06:00:41</t>
         </is>
       </c>
     </row>
@@ -2506,19 +2506,19 @@
         <v>6.6</v>
       </c>
       <c r="G11" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="H11" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="I11" t="n">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="J11" t="n">
         <v>3.6</v>
       </c>
       <c r="K11" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -2536,7 +2536,7 @@
         <v>1.68</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-23 03:55:01</t>
+          <t>2026-03-23 06:00:41</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-25.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-25.xlsx
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-23 06:00:41</t>
+          <t>2026-03-23 08:06:12</t>
         </is>
       </c>
     </row>
@@ -951,10 +951,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="G3" t="n">
-        <v>2.04</v>
+        <v>1.99</v>
       </c>
       <c r="H3" t="n">
         <v>4.1</v>
@@ -963,10 +963,10 @@
         <v>4.7</v>
       </c>
       <c r="J3" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K3" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-23 06:00:41</t>
+          <t>2026-03-23 08:06:12</t>
         </is>
       </c>
     </row>
@@ -1175,10 +1175,10 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-23 06:00:41</t>
+          <t>2026-03-23 08:06:12</t>
         </is>
       </c>
     </row>
@@ -1339,16 +1339,16 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="G5" t="n">
         <v>4.5</v>
       </c>
       <c r="H5" t="n">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="I5" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="J5" t="n">
         <v>3.3</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-23 06:00:41</t>
+          <t>2026-03-23 08:06:12</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q6" t="n">
         <v>1.79</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-23 06:00:41</t>
+          <t>2026-03-23 08:06:12</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-23 06:00:41</t>
+          <t>2026-03-23 08:06:12</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-23 06:00:41</t>
+          <t>2026-03-23 08:06:12</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-23 06:00:41</t>
+          <t>2026-03-23 08:06:12</t>
         </is>
       </c>
     </row>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="G10" t="n">
         <v>2.7</v>
@@ -2321,7 +2321,7 @@
         <v>4.2</v>
       </c>
       <c r="J10" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="K10" t="n">
         <v>2.9</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-23 06:00:41</t>
+          <t>2026-03-23 08:06:12</t>
         </is>
       </c>
     </row>
@@ -2509,13 +2509,13 @@
         <v>8</v>
       </c>
       <c r="H11" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="I11" t="n">
         <v>1.72</v>
       </c>
       <c r="J11" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K11" t="n">
         <v>4.2</v>
@@ -2536,7 +2536,7 @@
         <v>1.68</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-23 06:00:41</t>
+          <t>2026-03-23 08:06:12</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-25.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH11"/>
+  <dimension ref="A1:BH12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -733,7 +733,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Turkish 2 Lig</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -743,36 +743,36 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Albion FC</t>
+          <t>Ankaragucu</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Wanderers (Uru)</t>
+          <t>Ankaraspor</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.58</v>
+        <v>1.01</v>
       </c>
       <c r="G2" t="n">
-        <v>3.1</v>
+        <v>1000</v>
       </c>
       <c r="H2" t="n">
-        <v>3.1</v>
+        <v>1.01</v>
       </c>
       <c r="I2" t="n">
-        <v>3.85</v>
+        <v>1000</v>
       </c>
       <c r="J2" t="n">
-        <v>2.64</v>
+        <v>1.02</v>
       </c>
       <c r="K2" t="n">
-        <v>3.25</v>
+        <v>1000</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -787,10 +787,10 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>1.5</v>
+        <v>1.24</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.44</v>
+        <v>1.01</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -920,14 +920,14 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-23 08:06:12</t>
+          <t>2026-03-23 10:13:21</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>English National League</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -937,36 +937,36 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>16:45:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Wealdstone</t>
+          <t>Albion FC</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Yeovil</t>
+          <t>Wanderers (Uru)</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.88</v>
+        <v>2.58</v>
       </c>
       <c r="G3" t="n">
-        <v>1.99</v>
+        <v>3.1</v>
       </c>
       <c r="H3" t="n">
-        <v>4.1</v>
+        <v>3.05</v>
       </c>
       <c r="I3" t="n">
-        <v>4.7</v>
+        <v>3.85</v>
       </c>
       <c r="J3" t="n">
-        <v>3.7</v>
+        <v>2.66</v>
       </c>
       <c r="K3" t="n">
-        <v>3.9</v>
+        <v>3.25</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -981,10 +981,10 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>2.04</v>
+        <v>1.5</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.79</v>
+        <v>2.44</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-23 08:06:12</t>
+          <t>2026-03-23 10:13:21</t>
         </is>
       </c>
     </row>
@@ -1136,31 +1136,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Southend</t>
+          <t>Wealdstone</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Woking</t>
+          <t>Yeovil</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.62</v>
+        <v>1.88</v>
       </c>
       <c r="G4" t="n">
-        <v>1.78</v>
+        <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>5.3</v>
+        <v>4.1</v>
       </c>
       <c r="I4" t="n">
-        <v>6.2</v>
+        <v>4.7</v>
       </c>
       <c r="J4" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="K4" t="n">
-        <v>4.6</v>
+        <v>3.9</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -1175,10 +1175,10 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-23 08:06:12</t>
+          <t>2026-03-23 10:13:21</t>
         </is>
       </c>
     </row>
@@ -1330,31 +1330,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Tamworth FC</t>
+          <t>Southend</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Forest Green</t>
+          <t>Woking</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3.45</v>
+        <v>1.62</v>
       </c>
       <c r="G5" t="n">
-        <v>4.5</v>
+        <v>1.78</v>
       </c>
       <c r="H5" t="n">
-        <v>1.98</v>
+        <v>5.3</v>
       </c>
       <c r="I5" t="n">
-        <v>2.4</v>
+        <v>6.2</v>
       </c>
       <c r="J5" t="n">
-        <v>3.3</v>
+        <v>3.85</v>
       </c>
       <c r="K5" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -1369,10 +1369,10 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>2.26</v>
+        <v>2.02</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-23 08:06:12</t>
+          <t>2026-03-23 10:13:21</t>
         </is>
       </c>
     </row>
@@ -1524,31 +1524,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Scunthorpe</t>
+          <t>Tamworth FC</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>Forest Green</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="G6" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="H6" t="n">
-        <v>2.06</v>
+        <v>1.99</v>
       </c>
       <c r="I6" t="n">
-        <v>2.24</v>
+        <v>2.14</v>
       </c>
       <c r="J6" t="n">
-        <v>3.55</v>
+        <v>3.85</v>
       </c>
       <c r="K6" t="n">
-        <v>3.65</v>
+        <v>4.4</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1563,10 +1563,10 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>2.02</v>
+        <v>2.26</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-23 08:06:12</t>
+          <t>2026-03-23 10:13:21</t>
         </is>
       </c>
     </row>
@@ -1718,31 +1718,31 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Truro City</t>
+          <t>Scunthorpe</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Solihull Moors</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="G7" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="H7" t="n">
-        <v>2.24</v>
+        <v>2.1</v>
       </c>
       <c r="I7" t="n">
-        <v>2.42</v>
+        <v>2.26</v>
       </c>
       <c r="J7" t="n">
         <v>3.55</v>
       </c>
       <c r="K7" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -1757,10 +1757,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-23 08:06:12</t>
+          <t>2026-03-23 10:13:21</t>
         </is>
       </c>
     </row>
@@ -1912,31 +1912,31 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Morecambe</t>
+          <t>Truro City</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hartlepool</t>
+          <t>Solihull Moors</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.86</v>
+        <v>3.05</v>
       </c>
       <c r="G8" t="n">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="H8" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="I8" t="n">
-        <v>2.8</v>
+        <v>2.48</v>
       </c>
       <c r="J8" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="K8" t="n">
-        <v>4.3</v>
+        <v>3.7</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -1951,10 +1951,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.32</v>
+        <v>2.08</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -2084,14 +2084,14 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-23 08:06:12</t>
+          <t>2026-03-23 10:13:21</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>English National League</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2101,36 +2101,36 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>16:45:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Cerro</t>
+          <t>Morecambe</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Juventud De Las Piedras</t>
+          <t>Hartlepool</t>
         </is>
       </c>
       <c r="F9" t="n">
         <v>2.86</v>
       </c>
       <c r="G9" t="n">
-        <v>3.25</v>
+        <v>3.65</v>
       </c>
       <c r="H9" t="n">
-        <v>2.72</v>
+        <v>2.3</v>
       </c>
       <c r="I9" t="n">
-        <v>3.25</v>
+        <v>2.78</v>
       </c>
       <c r="J9" t="n">
-        <v>2.88</v>
+        <v>3.35</v>
       </c>
       <c r="K9" t="n">
-        <v>3.3</v>
+        <v>4.3</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -2145,10 +2145,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.51</v>
+        <v>2.3</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.42</v>
+        <v>1.53</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -2278,14 +2278,14 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-23 08:06:12</t>
+          <t>2026-03-23 10:13:21</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2295,36 +2295,36 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Deportivo Riestra</t>
+          <t>Cerro</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>San Lorenzo</t>
+          <t>Juventud De Las Piedras</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.5</v>
+        <v>2.86</v>
       </c>
       <c r="G10" t="n">
-        <v>2.7</v>
+        <v>3.25</v>
       </c>
       <c r="H10" t="n">
-        <v>3.7</v>
+        <v>2.72</v>
       </c>
       <c r="I10" t="n">
-        <v>4.2</v>
+        <v>3.25</v>
       </c>
       <c r="J10" t="n">
-        <v>2.68</v>
+        <v>2.88</v>
       </c>
       <c r="K10" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -2339,10 +2339,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1.31</v>
+        <v>1.51</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.85</v>
+        <v>2.42</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -2472,201 +2472,395 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-23 08:06:12</t>
+          <t>2026-03-23 10:13:21</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>Argentinian Primera Division</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Deportivo Riestra</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>San Lorenzo</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="H11" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="I11" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>2026-03-23 10:13:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>Uruguayan Primera Division</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>2026-03-25</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>20:30:00</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>Boston River</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>Penarol</t>
         </is>
       </c>
-      <c r="F11" t="n">
+      <c r="F12" t="n">
         <v>6.6</v>
       </c>
-      <c r="G11" t="n">
+      <c r="G12" t="n">
         <v>8</v>
       </c>
-      <c r="H11" t="n">
+      <c r="H12" t="n">
         <v>1.6</v>
       </c>
-      <c r="I11" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="J11" t="n">
+      <c r="I12" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="J12" t="n">
         <v>3.65</v>
       </c>
-      <c r="K11" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
+      <c r="K12" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
         <v>1.68</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="Q12" t="n">
         <v>2.18</v>
       </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>0</v>
-      </c>
-      <c r="T11" t="n">
-        <v>0</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" t="n">
-        <v>0</v>
-      </c>
-      <c r="W11" t="n">
-        <v>0</v>
-      </c>
-      <c r="X11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH11" t="inlineStr">
-        <is>
-          <t>2026-03-23 08:06:12</t>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>2026-03-23 10:13:21</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-25.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-25.xlsx
@@ -757,170 +757,170 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="G2" t="n">
         <v>1000</v>
       </c>
       <c r="H2" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="I2" t="n">
         <v>1000</v>
       </c>
       <c r="J2" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K2" t="n">
         <v>1000</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P2" t="n">
         <v>1.24</v>
       </c>
       <c r="Q2" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S2" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="T2" t="n">
         <v>1.01</v>
       </c>
-      <c r="R2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0</v>
-      </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-23 10:13:21</t>
+          <t>2026-03-23 12:20:33</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-23 10:13:21</t>
+          <t>2026-03-23 12:20:33</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-23 10:13:21</t>
+          <t>2026-03-23 12:20:33</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-23 10:13:21</t>
+          <t>2026-03-23 12:20:33</t>
         </is>
       </c>
     </row>
@@ -1548,7 +1548,7 @@
         <v>3.85</v>
       </c>
       <c r="K6" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-23 10:13:21</t>
+          <t>2026-03-23 12:20:33</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-23 10:13:21</t>
+          <t>2026-03-23 12:20:33</t>
         </is>
       </c>
     </row>
@@ -1921,16 +1921,16 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="G8" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="H8" t="n">
-        <v>2.26</v>
+        <v>2.34</v>
       </c>
       <c r="I8" t="n">
-        <v>2.48</v>
+        <v>2.54</v>
       </c>
       <c r="J8" t="n">
         <v>3.55</v>
@@ -1951,10 +1951,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-23 10:13:21</t>
+          <t>2026-03-23 12:20:33</t>
         </is>
       </c>
     </row>
@@ -2115,7 +2115,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="G9" t="n">
         <v>3.65</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-23 10:13:21</t>
+          <t>2026-03-23 12:20:33</t>
         </is>
       </c>
     </row>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-23 10:13:21</t>
+          <t>2026-03-23 12:20:33</t>
         </is>
       </c>
     </row>
@@ -2506,16 +2506,16 @@
         <v>2.5</v>
       </c>
       <c r="G11" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="H11" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="I11" t="n">
         <v>4.2</v>
       </c>
       <c r="J11" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="K11" t="n">
         <v>2.9</v>
@@ -2533,10 +2533,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-23 10:13:21</t>
+          <t>2026-03-23 12:20:33</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
         <v>1.6</v>
       </c>
       <c r="I12" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="J12" t="n">
         <v>3.65</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-23 10:13:21</t>
+          <t>2026-03-23 12:20:33</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-25.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-25.xlsx
@@ -763,7 +763,7 @@
         <v>1000</v>
       </c>
       <c r="H2" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="I2" t="n">
         <v>1000</v>
@@ -781,7 +781,7 @@
         <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O2" t="n">
         <v>1.01</v>
@@ -790,13 +790,13 @@
         <v>1.24</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.02</v>
+        <v>1.28</v>
       </c>
       <c r="R2" t="n">
         <v>1.18</v>
       </c>
       <c r="S2" t="n">
-        <v>1.02</v>
+        <v>1.28</v>
       </c>
       <c r="T2" t="n">
         <v>1.01</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-23 12:20:33</t>
+          <t>2026-03-23 14:28:14</t>
         </is>
       </c>
     </row>
@@ -969,16 +969,16 @@
         <v>3.25</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P3" t="n">
         <v>1.5</v>
@@ -987,134 +987,134 @@
         <v>2.44</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-23 12:20:33</t>
+          <t>2026-03-23 14:28:14</t>
         </is>
       </c>
     </row>
@@ -1151,7 +1151,7 @@
         <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="I4" t="n">
         <v>4.7</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-23 12:20:33</t>
+          <t>2026-03-23 14:28:14</t>
         </is>
       </c>
     </row>
@@ -1339,7 +1339,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="G5" t="n">
         <v>1.78</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-23 12:20:33</t>
+          <t>2026-03-23 14:28:14</t>
         </is>
       </c>
     </row>
@@ -1545,7 +1545,7 @@
         <v>2.14</v>
       </c>
       <c r="J6" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="K6" t="n">
         <v>4.3</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-23 12:20:33</t>
+          <t>2026-03-23 14:28:14</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-23 12:20:33</t>
+          <t>2026-03-23 14:28:14</t>
         </is>
       </c>
     </row>
@@ -1921,16 +1921,16 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="G8" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="H8" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="I8" t="n">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="J8" t="n">
         <v>3.55</v>
@@ -1951,10 +1951,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-23 12:20:33</t>
+          <t>2026-03-23 14:28:14</t>
         </is>
       </c>
     </row>
@@ -2121,7 +2121,7 @@
         <v>3.65</v>
       </c>
       <c r="H9" t="n">
-        <v>2.3</v>
+        <v>2.04</v>
       </c>
       <c r="I9" t="n">
         <v>2.78</v>
@@ -2145,10 +2145,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-23 12:20:33</t>
+          <t>2026-03-23 14:28:14</t>
         </is>
       </c>
     </row>
@@ -2315,7 +2315,7 @@
         <v>3.25</v>
       </c>
       <c r="H10" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="I10" t="n">
         <v>3.25</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-23 12:20:33</t>
+          <t>2026-03-23 14:28:14</t>
         </is>
       </c>
     </row>
@@ -2506,16 +2506,16 @@
         <v>2.5</v>
       </c>
       <c r="G11" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="H11" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="I11" t="n">
         <v>4.2</v>
       </c>
       <c r="J11" t="n">
-        <v>2.68</v>
+        <v>2.78</v>
       </c>
       <c r="K11" t="n">
         <v>2.9</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-23 12:20:33</t>
+          <t>2026-03-23 14:28:14</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
         <v>1.6</v>
       </c>
       <c r="I12" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="J12" t="n">
         <v>3.65</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-23 12:20:33</t>
+          <t>2026-03-23 14:28:14</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-25.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-25.xlsx
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-23 14:28:14</t>
+          <t>2026-03-23 16:35:25</t>
         </is>
       </c>
     </row>
@@ -972,40 +972,40 @@
         <v>1.01</v>
       </c>
       <c r="M3" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="N3" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="O3" t="n">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="P3" t="n">
         <v>1.5</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="R3" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="S3" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="T3" t="n">
-        <v>1.01</v>
+        <v>1.78</v>
       </c>
       <c r="U3" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="V3" t="n">
         <v>1.35</v>
       </c>
       <c r="W3" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="X3" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="Y3" t="n">
         <v>12.5</v>
@@ -1059,7 +1059,7 @@
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>5.6</v>
+        <v>1.03</v>
       </c>
       <c r="AQ3" t="n">
         <v>5.9</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-23 14:28:14</t>
+          <t>2026-03-23 16:35:25</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
         <v>2.04</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-23 14:28:14</t>
+          <t>2026-03-23 16:35:25</t>
         </is>
       </c>
     </row>
@@ -1342,13 +1342,13 @@
         <v>1.63</v>
       </c>
       <c r="G5" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="H5" t="n">
         <v>5.3</v>
       </c>
       <c r="I5" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="J5" t="n">
         <v>3.85</v>
@@ -1369,10 +1369,10 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-23 14:28:14</t>
+          <t>2026-03-23 16:35:25</t>
         </is>
       </c>
     </row>
@@ -1539,13 +1539,13 @@
         <v>4</v>
       </c>
       <c r="H6" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="I6" t="n">
         <v>2.14</v>
       </c>
       <c r="J6" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K6" t="n">
         <v>4.3</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-23 14:28:14</t>
+          <t>2026-03-23 16:35:25</t>
         </is>
       </c>
     </row>
@@ -1733,7 +1733,7 @@
         <v>4.1</v>
       </c>
       <c r="H7" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="I7" t="n">
         <v>2.26</v>
@@ -1742,7 +1742,7 @@
         <v>3.55</v>
       </c>
       <c r="K7" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-23 14:28:14</t>
+          <t>2026-03-23 16:35:25</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-23 14:28:14</t>
+          <t>2026-03-23 16:35:25</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="Q9" t="n">
         <v>1.57</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-23 14:28:14</t>
+          <t>2026-03-23 16:35:25</t>
         </is>
       </c>
     </row>
@@ -2315,7 +2315,7 @@
         <v>3.25</v>
       </c>
       <c r="H10" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="I10" t="n">
         <v>3.25</v>
@@ -2342,7 +2342,7 @@
         <v>1.51</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-23 14:28:14</t>
+          <t>2026-03-23 16:35:25</t>
         </is>
       </c>
     </row>
@@ -2515,7 +2515,7 @@
         <v>4.2</v>
       </c>
       <c r="J11" t="n">
-        <v>2.78</v>
+        <v>2.72</v>
       </c>
       <c r="K11" t="n">
         <v>2.9</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-23 14:28:14</t>
+          <t>2026-03-23 16:35:25</t>
         </is>
       </c>
     </row>
@@ -2703,16 +2703,16 @@
         <v>8</v>
       </c>
       <c r="H12" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="I12" t="n">
         <v>1.71</v>
       </c>
       <c r="J12" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="K12" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-23 14:28:14</t>
+          <t>2026-03-23 16:35:25</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-25.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-25.xlsx
@@ -757,7 +757,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="G2" t="n">
         <v>1000</v>
@@ -784,7 +784,7 @@
         <v>1.25</v>
       </c>
       <c r="O2" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P2" t="n">
         <v>1.24</v>
@@ -796,13 +796,13 @@
         <v>1.18</v>
       </c>
       <c r="S2" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="T2" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U2" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V2" t="n">
         <v>1.01</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-23 16:35:25</t>
+          <t>2026-03-23 18:41:59</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
         <v>1000</v>
       </c>
       <c r="Y3" t="n">
-        <v>12.5</v>
+        <v>970</v>
       </c>
       <c r="Z3" t="n">
         <v>29</v>
@@ -1017,7 +1017,7 @@
         <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>11</v>
+        <v>970</v>
       </c>
       <c r="AC3" t="n">
         <v>9.6</v>
@@ -1032,7 +1032,7 @@
         <v>23</v>
       </c>
       <c r="AG3" t="n">
-        <v>18.5</v>
+        <v>970</v>
       </c>
       <c r="AH3" t="n">
         <v>32</v>
@@ -1059,16 +1059,16 @@
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.03</v>
+        <v>1.98</v>
       </c>
       <c r="AQ3" t="n">
         <v>5.9</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.03</v>
+        <v>1.86</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.03</v>
+        <v>1.98</v>
       </c>
       <c r="AT3" t="n">
         <v>5.3</v>
@@ -1080,41 +1080,41 @@
         <v>9.6</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.03</v>
+        <v>1.98</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.03</v>
+        <v>1.82</v>
       </c>
       <c r="AY3" t="n">
         <v>8.4</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.03</v>
+        <v>1.87</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.03</v>
+        <v>1.98</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.03</v>
+        <v>1.98</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.03</v>
+        <v>1.98</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.03</v>
+        <v>1.98</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.03</v>
+        <v>1.98</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.01</v>
+        <v>1.98</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.01</v>
+        <v>1.98</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-23 16:35:25</t>
+          <t>2026-03-23 18:41:59</t>
         </is>
       </c>
     </row>
@@ -1163,152 +1163,152 @@
         <v>3.9</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="P4" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AO4" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AP4" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AU4" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AV4" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AW4" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AX4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AY4" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BA4" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG4" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-23 16:35:25</t>
+          <t>2026-03-23 18:41:59</t>
         </is>
       </c>
     </row>
@@ -1357,152 +1357,152 @@
         <v>4.6</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="P5" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="Q5" t="n">
         <v>1.78</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AO5" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AU5" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AW5" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AX5" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY5" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BA5" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="BF5" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BG5" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-23 16:35:25</t>
+          <t>2026-03-23 18:41:59</t>
         </is>
       </c>
     </row>
@@ -1551,16 +1551,16 @@
         <v>4.3</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="P6" t="n">
         <v>2.26</v>
@@ -1569,134 +1569,134 @@
         <v>1.67</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AO6" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AP6" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AS6" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AU6" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AV6" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW6" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AX6" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AY6" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="BC6" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="BD6" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BE6" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="BF6" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BG6" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-23 16:35:25</t>
+          <t>2026-03-23 18:41:59</t>
         </is>
       </c>
     </row>
@@ -1730,10 +1730,10 @@
         <v>3.5</v>
       </c>
       <c r="G7" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="H7" t="n">
-        <v>2.06</v>
+        <v>2.14</v>
       </c>
       <c r="I7" t="n">
         <v>2.26</v>
@@ -1745,16 +1745,16 @@
         <v>3.75</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="P7" t="n">
         <v>2.02</v>
@@ -1763,134 +1763,134 @@
         <v>1.8</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AO7" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AP7" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AS7" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AT7" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AU7" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AV7" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AW7" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AX7" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AY7" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BA7" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="BD7" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BF7" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="BG7" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-23 16:35:25</t>
+          <t>2026-03-23 18:41:59</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1921,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="G8" t="n">
         <v>3.3</v>
@@ -1930,7 +1930,7 @@
         <v>2.36</v>
       </c>
       <c r="I8" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="J8" t="n">
         <v>3.55</v>
@@ -1939,152 +1939,152 @@
         <v>3.7</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="P8" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.86</v>
+        <v>1.77</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AS8" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AT8" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU8" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AV8" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AW8" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AX8" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AY8" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="BD8" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="BF8" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="BG8" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-23 16:35:25</t>
+          <t>2026-03-23 18:41:59</t>
         </is>
       </c>
     </row>
@@ -2118,167 +2118,167 @@
         <v>2.88</v>
       </c>
       <c r="G9" t="n">
-        <v>3.65</v>
+        <v>3.25</v>
       </c>
       <c r="H9" t="n">
-        <v>2.04</v>
+        <v>2.28</v>
       </c>
       <c r="I9" t="n">
-        <v>2.78</v>
+        <v>2.68</v>
       </c>
       <c r="J9" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="K9" t="n">
         <v>4.3</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="P9" t="n">
         <v>2.24</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AL9" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AN9" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AO9" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AP9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AS9" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AT9" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AU9" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AV9" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW9" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AX9" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AY9" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="BA9" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="BB9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BC9" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BD9" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="BE9" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="BF9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BG9" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-23 16:35:25</t>
+          <t>2026-03-23 18:41:59</t>
         </is>
       </c>
     </row>
@@ -2309,170 +2309,170 @@
         </is>
       </c>
       <c r="F10" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J10" t="n">
         <v>2.86</v>
-      </c>
-      <c r="G10" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="H10" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="I10" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="J10" t="n">
-        <v>2.88</v>
       </c>
       <c r="K10" t="n">
         <v>3.3</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="P10" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.44</v>
+        <v>2.58</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AL10" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN10" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AO10" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AP10" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-23 16:35:25</t>
+          <t>2026-03-23 18:41:59</t>
         </is>
       </c>
     </row>
@@ -2515,10 +2515,10 @@
         <v>4.2</v>
       </c>
       <c r="J11" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="K11" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-23 16:35:25</t>
+          <t>2026-03-23 18:41:59</t>
         </is>
       </c>
     </row>
@@ -2727,7 +2727,7 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="Q12" t="n">
         <v>2.18</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-23 16:35:25</t>
+          <t>2026-03-23 18:41:59</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-25.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH12"/>
+  <dimension ref="A1:BH15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -781,7 +781,7 @@
         <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="O2" t="n">
         <v>1.02</v>
@@ -796,7 +796,7 @@
         <v>1.18</v>
       </c>
       <c r="S2" t="n">
-        <v>1.27</v>
+        <v>1.05</v>
       </c>
       <c r="T2" t="n">
         <v>1.11</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-23 18:41:59</t>
+          <t>2026-03-23 20:48:35</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-23 18:41:59</t>
+          <t>2026-03-23 20:48:35</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="G4" t="n">
         <v>2</v>
@@ -1157,13 +1157,13 @@
         <v>4.7</v>
       </c>
       <c r="J4" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="K4" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="L4" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="M4" t="n">
         <v>1.05</v>
@@ -1271,10 +1271,10 @@
         <v>6.6</v>
       </c>
       <c r="AV4" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AW4" t="n">
-        <v>6.6</v>
+        <v>38</v>
       </c>
       <c r="AX4" t="n">
         <v>9</v>
@@ -1289,7 +1289,7 @@
         <v>6.6</v>
       </c>
       <c r="BB4" t="n">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="BC4" t="n">
         <v>14</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-23 18:41:59</t>
+          <t>2026-03-23 20:48:35</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
         <v>5.3</v>
       </c>
       <c r="I5" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="J5" t="n">
         <v>3.85</v>
@@ -1357,7 +1357,7 @@
         <v>4.6</v>
       </c>
       <c r="L5" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="M5" t="n">
         <v>1.05</v>
@@ -1369,10 +1369,10 @@
         <v>1.26</v>
       </c>
       <c r="P5" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="R5" t="n">
         <v>1.4</v>
@@ -1387,7 +1387,7 @@
         <v>2</v>
       </c>
       <c r="V5" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="W5" t="n">
         <v>2.28</v>
@@ -1441,7 +1441,7 @@
         <v>120</v>
       </c>
       <c r="AN5" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AO5" t="n">
         <v>100</v>
@@ -1453,7 +1453,7 @@
         <v>15.5</v>
       </c>
       <c r="AR5" t="n">
-        <v>7.2</v>
+        <v>34</v>
       </c>
       <c r="AS5" t="n">
         <v>8</v>
@@ -1468,7 +1468,7 @@
         <v>17</v>
       </c>
       <c r="AW5" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AX5" t="n">
         <v>8.199999999999999</v>
@@ -1489,20 +1489,20 @@
         <v>13</v>
       </c>
       <c r="BD5" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BE5" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BF5" t="n">
         <v>7.4</v>
       </c>
       <c r="BG5" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-23 18:41:59</t>
+          <t>2026-03-23 20:48:35</t>
         </is>
       </c>
     </row>
@@ -1536,13 +1536,13 @@
         <v>3.5</v>
       </c>
       <c r="G6" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="H6" t="n">
         <v>1.98</v>
       </c>
       <c r="I6" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="J6" t="n">
         <v>3.85</v>
@@ -1584,7 +1584,7 @@
         <v>1.87</v>
       </c>
       <c r="W6" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="X6" t="n">
         <v>25</v>
@@ -1635,10 +1635,10 @@
         <v>85</v>
       </c>
       <c r="AN6" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AO6" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AP6" t="n">
         <v>15</v>
@@ -1665,7 +1665,7 @@
         <v>16.5</v>
       </c>
       <c r="AX6" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AY6" t="n">
         <v>13</v>
@@ -1674,29 +1674,29 @@
         <v>13.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BB6" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BD6" t="n">
         <v>6.6</v>
       </c>
-      <c r="BC6" t="n">
+      <c r="BE6" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BF6" t="n">
         <v>6.2</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>6</v>
       </c>
       <c r="BG6" t="n">
         <v>8.4</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-23 18:41:59</t>
+          <t>2026-03-23 20:48:35</t>
         </is>
       </c>
     </row>
@@ -1778,7 +1778,7 @@
         <v>1.79</v>
       </c>
       <c r="W7" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="X7" t="n">
         <v>17.5</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-23 18:41:59</t>
+          <t>2026-03-23 20:48:35</t>
         </is>
       </c>
     </row>
@@ -1954,7 +1954,7 @@
         <v>1.98</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="R8" t="n">
         <v>1.34</v>
@@ -1963,13 +1963,13 @@
         <v>2.78</v>
       </c>
       <c r="T8" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="U8" t="n">
         <v>2.06</v>
       </c>
       <c r="V8" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="W8" t="n">
         <v>1.44</v>
@@ -2038,7 +2038,7 @@
         <v>10.5</v>
       </c>
       <c r="AS8" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="AT8" t="n">
         <v>8.800000000000001</v>
@@ -2050,7 +2050,7 @@
         <v>8.4</v>
       </c>
       <c r="AW8" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="AX8" t="n">
         <v>14.5</v>
@@ -2062,29 +2062,29 @@
         <v>10.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="BB8" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="BC8" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="BD8" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="BE8" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="BF8" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-23 18:41:59</t>
+          <t>2026-03-23 20:48:35</t>
         </is>
       </c>
     </row>
@@ -2121,7 +2121,7 @@
         <v>3.25</v>
       </c>
       <c r="H9" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="I9" t="n">
         <v>2.68</v>
@@ -2145,7 +2145,7 @@
         <v>1.23</v>
       </c>
       <c r="P9" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="Q9" t="n">
         <v>1.58</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-23 18:41:59</t>
+          <t>2026-03-23 20:48:35</t>
         </is>
       </c>
     </row>
@@ -2318,16 +2318,16 @@
         <v>2.56</v>
       </c>
       <c r="I10" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="J10" t="n">
         <v>2.86</v>
       </c>
       <c r="K10" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="L10" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="M10" t="n">
         <v>1.12</v>
@@ -2357,7 +2357,7 @@
         <v>1.78</v>
       </c>
       <c r="V10" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="W10" t="n">
         <v>1.4</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-23 18:41:59</t>
+          <t>2026-03-23 20:48:35</t>
         </is>
       </c>
     </row>
@@ -2503,364 +2503,946 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="G11" t="n">
-        <v>2.68</v>
+        <v>2.76</v>
       </c>
       <c r="H11" t="n">
         <v>3.65</v>
       </c>
       <c r="I11" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="J11" t="n">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="K11" t="n">
         <v>2.92</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="P11" t="n">
         <v>1.31</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AL11" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>550</v>
       </c>
       <c r="AN11" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AO11" t="n">
-        <v>0</v>
+        <v>220</v>
       </c>
       <c r="AP11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AR11" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS11" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AT11" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AU11" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AV11" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AW11" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AX11" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AY11" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="BA11" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="BB11" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BD11" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BE11" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="BF11" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BG11" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-23 18:41:59</t>
+          <t>2026-03-23 20:48:35</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>Colombian Primera B</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Real Soacha Cundinamarca FC</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Atletico FC Cali</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K12" t="n">
+        <v>950</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N12" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="W12" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="X12" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>24</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>25</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>2026-03-23 20:48:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>US United Soccer League</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Lexington SC</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Brooklyn FC</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="H13" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="I13" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K13" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N13" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="W13" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="X13" t="n">
+        <v>970</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>25</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>70</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>32</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>140</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>29</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>130</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>970</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>13</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>2026-03-23 20:48:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>US United Soccer League</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>20:30:00</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Sporting Club Jacksonville</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Miami FC</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="G14" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="I14" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J14" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N14" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="X14" t="n">
+        <v>970</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>970</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>38</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>28</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>27</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>970</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>40</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>65</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>44</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>38</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>22</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>2026-03-23 20:48:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>Uruguayan Primera Division</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>2026-03-25</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>20:30:00</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>Boston River</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>Penarol</t>
         </is>
       </c>
-      <c r="F12" t="n">
+      <c r="F15" t="n">
         <v>6.6</v>
       </c>
-      <c r="G12" t="n">
+      <c r="G15" t="n">
         <v>8</v>
       </c>
-      <c r="H12" t="n">
+      <c r="H15" t="n">
         <v>1.59</v>
       </c>
-      <c r="I12" t="n">
+      <c r="I15" t="n">
         <v>1.71</v>
       </c>
-      <c r="J12" t="n">
+      <c r="J15" t="n">
         <v>3.6</v>
       </c>
-      <c r="K12" t="n">
+      <c r="K15" t="n">
         <v>4.2</v>
       </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
+      <c r="L15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N15" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="P15" t="n">
         <v>1.69</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="Q15" t="n">
         <v>2.18</v>
       </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" t="n">
-        <v>0</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" t="n">
-        <v>0</v>
-      </c>
-      <c r="W12" t="n">
-        <v>0</v>
-      </c>
-      <c r="X12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH12" t="inlineStr">
-        <is>
-          <t>2026-03-23 18:41:59</t>
+      <c r="R15" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="V15" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>2026-03-23 20:48:35</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-25.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH15"/>
+  <dimension ref="A1:BH17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -769,7 +769,7 @@
         <v>1000</v>
       </c>
       <c r="J2" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="K2" t="n">
         <v>1000</v>
@@ -920,14 +920,14 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-23 20:48:35</t>
+          <t>2026-03-23 22:54:23</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Algerian Ligue 1</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -937,105 +937,105 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:45:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Albion FC</t>
+          <t>Belouizdad</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Wanderers (Uru)</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.58</v>
+        <v>2.36</v>
       </c>
       <c r="G3" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="H3" t="n">
-        <v>3.05</v>
+        <v>2.92</v>
       </c>
       <c r="I3" t="n">
-        <v>3.85</v>
+        <v>4.4</v>
       </c>
       <c r="J3" t="n">
-        <v>2.66</v>
+        <v>2.52</v>
       </c>
       <c r="K3" t="n">
-        <v>3.25</v>
+        <v>4.3</v>
       </c>
       <c r="L3" t="n">
         <v>1.01</v>
       </c>
       <c r="M3" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>2.5</v>
+        <v>1.27</v>
       </c>
       <c r="O3" t="n">
-        <v>1.58</v>
+        <v>1.01</v>
       </c>
       <c r="P3" t="n">
-        <v>1.5</v>
+        <v>1.27</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.46</v>
+        <v>2.8</v>
       </c>
       <c r="R3" t="n">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="S3" t="n">
-        <v>4.6</v>
+        <v>2.8</v>
       </c>
       <c r="T3" t="n">
-        <v>1.78</v>
+        <v>1.01</v>
       </c>
       <c r="U3" t="n">
-        <v>1.55</v>
+        <v>1.01</v>
       </c>
       <c r="V3" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="W3" t="n">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="X3" t="n">
         <v>1000</v>
       </c>
       <c r="Y3" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Z3" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AA3" t="n">
         <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AC3" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="AD3" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AE3" t="n">
         <v>1000</v>
       </c>
       <c r="AF3" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AG3" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AH3" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AI3" t="n">
         <v>1000</v>
@@ -1059,69 +1059,69 @@
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.98</v>
+        <v>1.03</v>
       </c>
       <c r="AQ3" t="n">
-        <v>5.9</v>
+        <v>1.03</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.86</v>
+        <v>1.03</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.98</v>
+        <v>1.03</v>
       </c>
       <c r="AT3" t="n">
-        <v>5.3</v>
+        <v>1.03</v>
       </c>
       <c r="AU3" t="n">
-        <v>4.7</v>
+        <v>1.03</v>
       </c>
       <c r="AV3" t="n">
-        <v>9.6</v>
+        <v>1.03</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.98</v>
+        <v>1.03</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.82</v>
+        <v>1.03</v>
       </c>
       <c r="AY3" t="n">
-        <v>8.4</v>
+        <v>1.03</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.87</v>
+        <v>1.03</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.98</v>
+        <v>1.03</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.98</v>
+        <v>1.03</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.98</v>
+        <v>1.03</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.98</v>
+        <v>1.03</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.98</v>
+        <v>1.03</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.98</v>
+        <v>1.01</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.98</v>
+        <v>1.01</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-23 20:48:35</t>
+          <t>2026-03-23 22:54:23</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>English National League</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1131,191 +1131,191 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>16:45:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Wealdstone</t>
+          <t>Albion FC</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Yeovil</t>
+          <t>Wanderers (Uru)</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.86</v>
+        <v>2.58</v>
       </c>
       <c r="G4" t="n">
-        <v>2</v>
+        <v>2.94</v>
       </c>
       <c r="H4" t="n">
-        <v>4.2</v>
+        <v>3.05</v>
       </c>
       <c r="I4" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="J4" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="K4" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="X4" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>22</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>17</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="BC4" t="n">
         <v>4.7</v>
       </c>
-      <c r="J4" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="K4" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="L4" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N4" t="n">
-        <v>4</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="P4" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S4" t="n">
-        <v>3</v>
-      </c>
-      <c r="T4" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="U4" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="W4" t="n">
-        <v>2</v>
-      </c>
-      <c r="X4" t="n">
-        <v>21</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>34</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>120</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>9</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>22</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>65</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>15</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>60</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>26</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>20</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>34</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>110</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>60</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>12</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>7</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>16</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>38</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>9</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>13</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>14</v>
-      </c>
       <c r="BD4" t="n">
-        <v>6.2</v>
+        <v>2.7</v>
       </c>
       <c r="BE4" t="n">
-        <v>7</v>
+        <v>2.48</v>
       </c>
       <c r="BF4" t="n">
-        <v>8.800000000000001</v>
+        <v>2.66</v>
       </c>
       <c r="BG4" t="n">
-        <v>36</v>
+        <v>2.7</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-23 20:48:35</t>
+          <t>2026-03-23 22:54:23</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>English National League</t>
+          <t>Algerian Ligue 1</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1325,184 +1325,184 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>16:45:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Southend</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Woking</t>
+          <t>Kabylie</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.63</v>
+        <v>1.35</v>
       </c>
       <c r="G5" t="n">
-        <v>1.77</v>
+        <v>2.48</v>
       </c>
       <c r="H5" t="n">
-        <v>5.3</v>
+        <v>3.9</v>
       </c>
       <c r="I5" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="J5" t="n">
-        <v>3.85</v>
+        <v>2.9</v>
       </c>
       <c r="K5" t="n">
-        <v>4.6</v>
+        <v>950</v>
       </c>
       <c r="L5" t="n">
-        <v>1.35</v>
+        <v>1.01</v>
       </c>
       <c r="M5" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>3.95</v>
+        <v>1.38</v>
       </c>
       <c r="O5" t="n">
-        <v>1.26</v>
+        <v>1.01</v>
       </c>
       <c r="P5" t="n">
-        <v>2.04</v>
+        <v>1.38</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.76</v>
+        <v>2.38</v>
       </c>
       <c r="R5" t="n">
-        <v>1.4</v>
+        <v>1.08</v>
       </c>
       <c r="S5" t="n">
-        <v>2.98</v>
+        <v>2.38</v>
       </c>
       <c r="T5" t="n">
-        <v>1.79</v>
+        <v>1.01</v>
       </c>
       <c r="U5" t="n">
-        <v>2</v>
+        <v>1.01</v>
       </c>
       <c r="V5" t="n">
         <v>1.2</v>
       </c>
       <c r="W5" t="n">
-        <v>2.28</v>
+        <v>1.67</v>
       </c>
       <c r="X5" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="Y5" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="Z5" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AA5" t="n">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="AC5" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AD5" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AE5" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AF5" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AG5" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AH5" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AI5" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AK5" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AL5" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AM5" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AO5" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>13</v>
+        <v>1.03</v>
       </c>
       <c r="AQ5" t="n">
-        <v>15.5</v>
+        <v>1.03</v>
       </c>
       <c r="AR5" t="n">
-        <v>34</v>
+        <v>1.03</v>
       </c>
       <c r="AS5" t="n">
-        <v>8</v>
+        <v>1.03</v>
       </c>
       <c r="AT5" t="n">
-        <v>7</v>
+        <v>1.03</v>
       </c>
       <c r="AU5" t="n">
-        <v>7.4</v>
+        <v>1.03</v>
       </c>
       <c r="AV5" t="n">
-        <v>17</v>
+        <v>1.03</v>
       </c>
       <c r="AW5" t="n">
-        <v>7.8</v>
+        <v>1.03</v>
       </c>
       <c r="AX5" t="n">
-        <v>8.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AY5" t="n">
-        <v>7.8</v>
+        <v>1.03</v>
       </c>
       <c r="AZ5" t="n">
-        <v>15</v>
+        <v>1.03</v>
       </c>
       <c r="BA5" t="n">
-        <v>7.6</v>
+        <v>1.03</v>
       </c>
       <c r="BB5" t="n">
-        <v>13</v>
+        <v>1.03</v>
       </c>
       <c r="BC5" t="n">
-        <v>13</v>
+        <v>1.03</v>
       </c>
       <c r="BD5" t="n">
-        <v>7</v>
+        <v>1.03</v>
       </c>
       <c r="BE5" t="n">
-        <v>8</v>
+        <v>1.03</v>
       </c>
       <c r="BF5" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BG5" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-23 20:48:35</t>
+          <t>2026-03-23 22:54:23</t>
         </is>
       </c>
     </row>
@@ -1524,179 +1524,179 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Tamworth FC</t>
+          <t>Wealdstone</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Forest Green</t>
+          <t>Yeovil</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.5</v>
+        <v>1.86</v>
       </c>
       <c r="G6" t="n">
-        <v>3.95</v>
+        <v>2</v>
       </c>
       <c r="H6" t="n">
-        <v>1.98</v>
+        <v>4.2</v>
       </c>
       <c r="I6" t="n">
-        <v>2.16</v>
+        <v>4.8</v>
       </c>
       <c r="J6" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="K6" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N6" t="n">
+        <v>4</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="W6" t="n">
+        <v>2</v>
+      </c>
+      <c r="X6" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>42</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>120</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>19</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>27</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>55</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>12</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AR6" t="n">
         <v>4.3</v>
       </c>
-      <c r="L6" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="N6" t="n">
+      <c r="AS6" t="n">
         <v>4.6</v>
       </c>
-      <c r="O6" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="P6" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S6" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="T6" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="U6" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X6" t="n">
-        <v>25</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="Z6" t="n">
+      <c r="AT6" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BB6" t="n">
         <v>15.5</v>
       </c>
-      <c r="AA6" t="n">
-        <v>26</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>21</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>32</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>17</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>32</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>80</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>42</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>50</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>85</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>34</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>15</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>10</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>20</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>6</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>13</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>6</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>6.8</v>
-      </c>
       <c r="BC6" t="n">
-        <v>6.4</v>
+        <v>14</v>
       </c>
       <c r="BD6" t="n">
-        <v>6.6</v>
+        <v>4.2</v>
       </c>
       <c r="BE6" t="n">
-        <v>6.8</v>
+        <v>4.6</v>
       </c>
       <c r="BF6" t="n">
-        <v>6.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG6" t="n">
-        <v>8.4</v>
+        <v>4.4</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-23 20:48:35</t>
+          <t>2026-03-23 22:54:23</t>
         </is>
       </c>
     </row>
@@ -1718,179 +1718,179 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Scunthorpe</t>
+          <t>Southend</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>Woking</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.5</v>
+        <v>1.68</v>
       </c>
       <c r="G7" t="n">
-        <v>4</v>
+        <v>1.76</v>
       </c>
       <c r="H7" t="n">
-        <v>2.14</v>
+        <v>5.4</v>
       </c>
       <c r="I7" t="n">
-        <v>2.26</v>
+        <v>6.6</v>
       </c>
       <c r="J7" t="n">
-        <v>3.55</v>
+        <v>3.95</v>
       </c>
       <c r="K7" t="n">
-        <v>3.75</v>
+        <v>4.5</v>
       </c>
       <c r="L7" t="n">
         <v>1.32</v>
       </c>
       <c r="M7" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N7" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="O7" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="P7" t="n">
         <v>2.02</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="R7" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S7" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="T7" t="n">
-        <v>1.68</v>
+        <v>1.79</v>
       </c>
       <c r="U7" t="n">
-        <v>2.16</v>
+        <v>2</v>
       </c>
       <c r="V7" t="n">
-        <v>1.79</v>
+        <v>1.2</v>
       </c>
       <c r="W7" t="n">
-        <v>1.35</v>
+        <v>2.3</v>
       </c>
       <c r="X7" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>22</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>50</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>170</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>24</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>80</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>18</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>100</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ7" t="n">
         <v>17.5</v>
       </c>
-      <c r="Y7" t="n">
-        <v>11</v>
-      </c>
-      <c r="Z7" t="n">
+      <c r="AR7" t="n">
+        <v>34</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>8</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>17</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>55</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AZ7" t="n">
         <v>15</v>
       </c>
-      <c r="AA7" t="n">
-        <v>28</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>16</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>9</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>23</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>29</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>36</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>85</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>44</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>50</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>90</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>42</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>15</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>20</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>21</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>12</v>
-      </c>
-      <c r="AZ7" t="n">
+      <c r="BA7" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BB7" t="n">
         <v>13</v>
       </c>
-      <c r="BA7" t="n">
+      <c r="BC7" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD7" t="n">
         <v>7</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>7.4</v>
       </c>
       <c r="BE7" t="n">
         <v>8</v>
       </c>
       <c r="BF7" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BG7" t="n">
-        <v>11</v>
+        <v>7.8</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-23 20:48:35</t>
+          <t>2026-03-23 22:54:23</t>
         </is>
       </c>
     </row>
@@ -1912,179 +1912,179 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Truro City</t>
+          <t>Tamworth FC</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Solihull Moors</t>
+          <t>Forest Green</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.94</v>
+        <v>3.5</v>
       </c>
       <c r="G8" t="n">
-        <v>3.3</v>
+        <v>3.95</v>
       </c>
       <c r="H8" t="n">
-        <v>2.36</v>
+        <v>1.99</v>
       </c>
       <c r="I8" t="n">
-        <v>2.62</v>
+        <v>2.14</v>
       </c>
       <c r="J8" t="n">
-        <v>3.55</v>
+        <v>3.85</v>
       </c>
       <c r="K8" t="n">
-        <v>3.7</v>
+        <v>4.4</v>
       </c>
       <c r="L8" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="M8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N8" t="n">
-        <v>3.05</v>
+        <v>4.6</v>
       </c>
       <c r="O8" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="P8" t="n">
-        <v>1.98</v>
+        <v>2.26</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="R8" t="n">
-        <v>1.34</v>
+        <v>1.5</v>
       </c>
       <c r="S8" t="n">
-        <v>2.78</v>
+        <v>2.66</v>
       </c>
       <c r="T8" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="U8" t="n">
-        <v>2.06</v>
+        <v>2.32</v>
       </c>
       <c r="V8" t="n">
-        <v>1.61</v>
+        <v>1.87</v>
       </c>
       <c r="W8" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="X8" t="n">
-        <v>19.5</v>
+        <v>25</v>
       </c>
       <c r="Y8" t="n">
-        <v>970</v>
+        <v>12.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="AA8" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AB8" t="n">
-        <v>970</v>
+        <v>18.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>15.5</v>
+        <v>13</v>
       </c>
       <c r="AE8" t="n">
+        <v>21</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>30</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>32</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>42</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>75</v>
+      </c>
+      <c r="AN8" t="n">
         <v>34</v>
       </c>
-      <c r="AF8" t="n">
-        <v>29</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>1000</v>
-      </c>
       <c r="AO8" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AP8" t="n">
-        <v>10.5</v>
+        <v>15</v>
       </c>
       <c r="AQ8" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR8" t="n">
         <v>10.5</v>
       </c>
       <c r="AS8" t="n">
-        <v>2.26</v>
+        <v>18</v>
       </c>
       <c r="AT8" t="n">
-        <v>8.800000000000001</v>
+        <v>12.5</v>
       </c>
       <c r="AU8" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>8</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>21</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>21</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>48</v>
+      </c>
+      <c r="BF8" t="n">
         <v>5.6</v>
       </c>
-      <c r="AV8" t="n">
+      <c r="BG8" t="n">
         <v>8.4</v>
       </c>
-      <c r="AW8" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>2.26</v>
-      </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-23 20:48:35</t>
+          <t>2026-03-23 22:54:23</t>
         </is>
       </c>
     </row>
@@ -2106,186 +2106,186 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Morecambe</t>
+          <t>Scunthorpe</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hartlepool</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.88</v>
+        <v>3.45</v>
       </c>
       <c r="G9" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="H9" t="n">
-        <v>2.32</v>
+        <v>2.14</v>
       </c>
       <c r="I9" t="n">
-        <v>2.68</v>
+        <v>2.26</v>
       </c>
       <c r="J9" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="K9" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="L9" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="M9" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N9" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="O9" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="P9" t="n">
-        <v>2.26</v>
+        <v>1.99</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.58</v>
+        <v>1.81</v>
       </c>
       <c r="R9" t="n">
-        <v>1.47</v>
+        <v>1.39</v>
       </c>
       <c r="S9" t="n">
-        <v>2.68</v>
+        <v>3</v>
       </c>
       <c r="T9" t="n">
-        <v>1.59</v>
+        <v>1.69</v>
       </c>
       <c r="U9" t="n">
-        <v>2.36</v>
+        <v>2.16</v>
       </c>
       <c r="V9" t="n">
-        <v>1.6</v>
+        <v>1.79</v>
       </c>
       <c r="W9" t="n">
-        <v>1.44</v>
+        <v>1.34</v>
       </c>
       <c r="X9" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="Y9" t="n">
-        <v>970</v>
+        <v>11</v>
       </c>
       <c r="Z9" t="n">
-        <v>970</v>
+        <v>15</v>
       </c>
       <c r="AA9" t="n">
+        <v>28</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>16</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>23</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>29</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>18</v>
+      </c>
+      <c r="AI9" t="n">
         <v>36</v>
       </c>
-      <c r="AB9" t="n">
-        <v>970</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>970</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>970</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>26</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>23</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>970</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>34</v>
-      </c>
       <c r="AJ9" t="n">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="AK9" t="n">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="AL9" t="n">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="AM9" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AN9" t="n">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="AO9" t="n">
-        <v>970</v>
+        <v>15</v>
       </c>
       <c r="AP9" t="n">
-        <v>6</v>
+        <v>12.5</v>
       </c>
       <c r="AQ9" t="n">
-        <v>9.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR9" t="n">
-        <v>5.7</v>
+        <v>10.5</v>
       </c>
       <c r="AS9" t="n">
-        <v>2.22</v>
+        <v>20</v>
       </c>
       <c r="AT9" t="n">
+        <v>13</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>21</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>50</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BG9" t="n">
         <v>11</v>
       </c>
-      <c r="AU9" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>16</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>7</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>6</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>5.4</v>
-      </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-23 20:48:35</t>
+          <t>2026-03-23 22:54:23</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>English National League</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2295,191 +2295,191 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>16:45:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Cerro</t>
+          <t>Truro City</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Juventud De Las Piedras</t>
+          <t>Solihull Moors</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.1</v>
+        <v>2.94</v>
       </c>
       <c r="G10" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="H10" t="n">
-        <v>2.56</v>
+        <v>2.36</v>
       </c>
       <c r="I10" t="n">
-        <v>2.88</v>
+        <v>2.62</v>
       </c>
       <c r="J10" t="n">
-        <v>2.86</v>
+        <v>3.55</v>
       </c>
       <c r="K10" t="n">
-        <v>3.25</v>
+        <v>3.7</v>
       </c>
       <c r="L10" t="n">
-        <v>1.51</v>
+        <v>1.32</v>
       </c>
       <c r="M10" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="N10" t="n">
-        <v>2.5</v>
+        <v>3.6</v>
       </c>
       <c r="O10" t="n">
-        <v>1.53</v>
+        <v>1.28</v>
       </c>
       <c r="P10" t="n">
-        <v>1.52</v>
+        <v>1.98</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.58</v>
+        <v>1.83</v>
       </c>
       <c r="R10" t="n">
-        <v>1.18</v>
+        <v>1.38</v>
       </c>
       <c r="S10" t="n">
-        <v>5.1</v>
+        <v>3.05</v>
       </c>
       <c r="T10" t="n">
-        <v>2.06</v>
+        <v>1.67</v>
       </c>
       <c r="U10" t="n">
-        <v>1.78</v>
+        <v>2.22</v>
       </c>
       <c r="V10" t="n">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="W10" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="X10" t="n">
-        <v>9.6</v>
+        <v>970</v>
       </c>
       <c r="Y10" t="n">
         <v>970</v>
       </c>
       <c r="Z10" t="n">
-        <v>970</v>
+        <v>17</v>
       </c>
       <c r="AA10" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AB10" t="n">
         <v>970</v>
       </c>
       <c r="AC10" t="n">
-        <v>970</v>
+        <v>9.4</v>
       </c>
       <c r="AD10" t="n">
         <v>970</v>
       </c>
       <c r="AE10" t="n">
-        <v>46</v>
+        <v>27</v>
       </c>
       <c r="AF10" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AG10" t="n">
         <v>970</v>
       </c>
       <c r="AH10" t="n">
-        <v>24</v>
+        <v>17.5</v>
       </c>
       <c r="AI10" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AJ10" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AK10" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AL10" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AM10" t="n">
         <v>1000</v>
       </c>
       <c r="AN10" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AO10" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>6.8</v>
+        <v>5.2</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.01</v>
+        <v>2.88</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.01</v>
+        <v>2.42</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.01</v>
+        <v>2.18</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.01</v>
+        <v>2.42</v>
       </c>
       <c r="BD10" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.01</v>
+        <v>2.2</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="BG10" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-23 20:48:35</t>
+          <t>2026-03-23 22:54:23</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>English National League</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2489,191 +2489,191 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>16:45:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Deportivo Riestra</t>
+          <t>Morecambe</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>San Lorenzo</t>
+          <t>Hartlepool</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.54</v>
+        <v>2.9</v>
       </c>
       <c r="G11" t="n">
-        <v>2.76</v>
+        <v>3.1</v>
       </c>
       <c r="H11" t="n">
-        <v>3.65</v>
+        <v>2.32</v>
       </c>
       <c r="I11" t="n">
-        <v>4.1</v>
+        <v>2.56</v>
       </c>
       <c r="J11" t="n">
-        <v>2.66</v>
+        <v>3.75</v>
       </c>
       <c r="K11" t="n">
-        <v>2.92</v>
+        <v>4.3</v>
       </c>
       <c r="L11" t="n">
-        <v>1.82</v>
+        <v>1.32</v>
       </c>
       <c r="M11" t="n">
-        <v>1.21</v>
+        <v>1.05</v>
       </c>
       <c r="N11" t="n">
-        <v>1.96</v>
+        <v>3.9</v>
       </c>
       <c r="O11" t="n">
-        <v>1.91</v>
+        <v>1.23</v>
       </c>
       <c r="P11" t="n">
-        <v>1.31</v>
+        <v>2.26</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.8</v>
+        <v>1.58</v>
       </c>
       <c r="R11" t="n">
-        <v>1.1</v>
+        <v>1.47</v>
       </c>
       <c r="S11" t="n">
-        <v>9.199999999999999</v>
+        <v>2.68</v>
       </c>
       <c r="T11" t="n">
-        <v>2.74</v>
+        <v>1.59</v>
       </c>
       <c r="U11" t="n">
-        <v>1.41</v>
+        <v>2.36</v>
       </c>
       <c r="V11" t="n">
-        <v>1.33</v>
+        <v>1.64</v>
       </c>
       <c r="W11" t="n">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="X11" t="n">
-        <v>5.7</v>
+        <v>25</v>
       </c>
       <c r="Y11" t="n">
-        <v>8</v>
+        <v>970</v>
       </c>
       <c r="Z11" t="n">
+        <v>970</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>36</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE11" t="n">
         <v>25</v>
       </c>
-      <c r="AA11" t="n">
-        <v>130</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>21</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>120</v>
-      </c>
       <c r="AF11" t="n">
-        <v>14.5</v>
+        <v>23</v>
       </c>
       <c r="AG11" t="n">
-        <v>16</v>
+        <v>970</v>
       </c>
       <c r="AH11" t="n">
+        <v>970</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>34</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>55</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL11" t="n">
         <v>38</v>
       </c>
-      <c r="AI11" t="n">
-        <v>200</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>50</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>60</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>160</v>
-      </c>
       <c r="AM11" t="n">
-        <v>550</v>
+        <v>85</v>
       </c>
       <c r="AN11" t="n">
-        <v>80</v>
+        <v>22</v>
       </c>
       <c r="AO11" t="n">
-        <v>220</v>
+        <v>970</v>
       </c>
       <c r="AP11" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="AQ11" t="n">
-        <v>7</v>
+        <v>4.6</v>
       </c>
       <c r="AR11" t="n">
-        <v>8.199999999999999</v>
+        <v>3.3</v>
       </c>
       <c r="AS11" t="n">
-        <v>11</v>
+        <v>5.8</v>
       </c>
       <c r="AT11" t="n">
-        <v>5.5</v>
+        <v>10.5</v>
       </c>
       <c r="AU11" t="n">
         <v>6.8</v>
       </c>
       <c r="AV11" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW11" t="n">
-        <v>65</v>
+        <v>2.08</v>
       </c>
       <c r="AX11" t="n">
-        <v>12.5</v>
+        <v>2.14</v>
       </c>
       <c r="AY11" t="n">
-        <v>13.5</v>
+        <v>4.6</v>
       </c>
       <c r="AZ11" t="n">
-        <v>30</v>
+        <v>4.9</v>
       </c>
       <c r="BA11" t="n">
-        <v>11.5</v>
+        <v>1.6</v>
       </c>
       <c r="BB11" t="n">
-        <v>9.800000000000001</v>
+        <v>2.76</v>
       </c>
       <c r="BC11" t="n">
-        <v>10</v>
+        <v>1.59</v>
       </c>
       <c r="BD11" t="n">
-        <v>11</v>
+        <v>5.8</v>
       </c>
       <c r="BE11" t="n">
-        <v>11.5</v>
+        <v>1.64</v>
       </c>
       <c r="BF11" t="n">
-        <v>10.5</v>
+        <v>5.2</v>
       </c>
       <c r="BG11" t="n">
-        <v>11.5</v>
+        <v>4.8</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-23 20:48:35</t>
+          <t>2026-03-23 22:54:23</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Colombian Primera B</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2683,174 +2683,174 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Real Soacha Cundinamarca FC</t>
+          <t>Cerro</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Atletico FC Cali</t>
+          <t>Juventud De Las Piedras</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.66</v>
+        <v>3.1</v>
       </c>
       <c r="G12" t="n">
-        <v>1.81</v>
+        <v>3.5</v>
       </c>
       <c r="H12" t="n">
-        <v>1.09</v>
+        <v>2.6</v>
       </c>
       <c r="I12" t="n">
-        <v>1000</v>
+        <v>2.96</v>
       </c>
       <c r="J12" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="K12" t="n">
         <v>3.25</v>
       </c>
-      <c r="K12" t="n">
-        <v>950</v>
-      </c>
       <c r="L12" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="N12" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X12" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>970</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>55</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>48</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>75</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>60</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>90</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>80</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>55</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS12" t="n">
         <v>1.01</v>
       </c>
-      <c r="M12" t="n">
+      <c r="AT12" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW12" t="n">
         <v>1.01</v>
       </c>
-      <c r="N12" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="O12" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="P12" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="S12" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T12" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="W12" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="X12" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>24</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>12</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>13</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>25</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>1.03</v>
-      </c>
       <c r="AX12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY12" t="n">
         <v>1.03</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF12" t="n">
         <v>1.01</v>
@@ -2860,14 +2860,14 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-23 20:48:35</t>
+          <t>2026-03-23 22:54:23</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>US United Soccer League</t>
+          <t>Argentinian Primera Division</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2877,191 +2877,191 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Lexington SC</t>
+          <t>Deportivo Riestra</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>San Lorenzo</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.57</v>
+        <v>2.52</v>
       </c>
       <c r="G13" t="n">
-        <v>1.75</v>
+        <v>2.76</v>
       </c>
       <c r="H13" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="I13" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J13" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="N13" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="S13" t="n">
+        <v>8</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="X13" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>30</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>130</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>25</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>120</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>38</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>200</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>50</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>60</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>160</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>550</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>80</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>230</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>7</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AT13" t="n">
         <v>5.4</v>
-      </c>
-      <c r="I13" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="J13" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="K13" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="M13" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N13" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="O13" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="P13" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S13" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="W13" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="X13" t="n">
-        <v>970</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>25</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>70</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>9</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>32</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>140</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>29</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>130</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>970</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>23</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>50</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>13</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>10</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>4</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>5.7</v>
       </c>
       <c r="AU13" t="n">
         <v>6.8</v>
       </c>
       <c r="AV13" t="n">
-        <v>3.8</v>
+        <v>5.1</v>
       </c>
       <c r="AW13" t="n">
-        <v>4.2</v>
+        <v>6.2</v>
       </c>
       <c r="AX13" t="n">
-        <v>6.8</v>
+        <v>12.5</v>
       </c>
       <c r="AY13" t="n">
-        <v>7.4</v>
+        <v>13.5</v>
       </c>
       <c r="AZ13" t="n">
-        <v>3.75</v>
+        <v>5.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>4.2</v>
+        <v>6.2</v>
       </c>
       <c r="BB13" t="n">
-        <v>11.5</v>
+        <v>5.7</v>
       </c>
       <c r="BC13" t="n">
-        <v>3.65</v>
+        <v>5.8</v>
       </c>
       <c r="BD13" t="n">
-        <v>4</v>
+        <v>6.2</v>
       </c>
       <c r="BE13" t="n">
-        <v>4.2</v>
+        <v>6.4</v>
       </c>
       <c r="BF13" t="n">
-        <v>7.8</v>
+        <v>6</v>
       </c>
       <c r="BG13" t="n">
-        <v>4.2</v>
+        <v>6.2</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-23 20:48:35</t>
+          <t>2026-03-23 22:54:23</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>US United Soccer League</t>
+          <t>Colombian Primera B</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3071,378 +3071,766 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Sporting Club Jacksonville</t>
+          <t>Real Soacha Cundinamarca FC</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Miami FC</t>
+          <t>Atletico FC Cali</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.1</v>
+        <v>1.43</v>
       </c>
       <c r="G14" t="n">
-        <v>3.25</v>
+        <v>1.77</v>
       </c>
       <c r="H14" t="n">
-        <v>2.36</v>
+        <v>6.2</v>
       </c>
       <c r="I14" t="n">
-        <v>2.5</v>
+        <v>1000</v>
       </c>
       <c r="J14" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="K14" t="n">
-        <v>4.1</v>
+        <v>7.2</v>
       </c>
       <c r="L14" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="M14" t="n">
         <v>1.06</v>
       </c>
       <c r="N14" t="n">
-        <v>3.55</v>
+        <v>2.58</v>
       </c>
       <c r="O14" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="P14" t="n">
-        <v>1.94</v>
+        <v>1.71</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="R14" t="n">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="S14" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="T14" t="n">
-        <v>1.72</v>
+        <v>1.9</v>
       </c>
       <c r="U14" t="n">
-        <v>2.14</v>
+        <v>1.11</v>
       </c>
       <c r="V14" t="n">
-        <v>1.68</v>
+        <v>1.01</v>
       </c>
       <c r="W14" t="n">
-        <v>1.45</v>
+        <v>2.28</v>
       </c>
       <c r="X14" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Y14" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Z14" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AA14" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AB14" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AC14" t="n">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AD14" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AE14" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AF14" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AG14" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AH14" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AI14" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AJ14" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AK14" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AL14" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AM14" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AN14" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AO14" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>4.2</v>
+        <v>1.03</v>
       </c>
       <c r="AQ14" t="n">
-        <v>7.6</v>
+        <v>1.03</v>
       </c>
       <c r="AR14" t="n">
-        <v>4.2</v>
+        <v>1.03</v>
       </c>
       <c r="AS14" t="n">
-        <v>4.9</v>
+        <v>1.03</v>
       </c>
       <c r="AT14" t="n">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AU14" t="n">
-        <v>6.6</v>
+        <v>1.03</v>
       </c>
       <c r="AV14" t="n">
-        <v>8.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AW14" t="n">
-        <v>4.7</v>
+        <v>1.03</v>
       </c>
       <c r="AX14" t="n">
-        <v>4.6</v>
+        <v>1.03</v>
       </c>
       <c r="AY14" t="n">
-        <v>4.2</v>
+        <v>1.03</v>
       </c>
       <c r="AZ14" t="n">
-        <v>4.3</v>
+        <v>1.03</v>
       </c>
       <c r="BA14" t="n">
-        <v>4.9</v>
+        <v>1.03</v>
       </c>
       <c r="BB14" t="n">
-        <v>5.1</v>
+        <v>1.03</v>
       </c>
       <c r="BC14" t="n">
-        <v>4.9</v>
+        <v>1.03</v>
       </c>
       <c r="BD14" t="n">
-        <v>5.1</v>
+        <v>1.03</v>
       </c>
       <c r="BE14" t="n">
-        <v>5.3</v>
+        <v>1.03</v>
       </c>
       <c r="BF14" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BG14" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-23 20:48:35</t>
+          <t>2026-03-23 22:54:23</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>US United Soccer League</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Lexington SC</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Brooklyn FC</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="H15" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="I15" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="J15" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="K15" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N15" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="W15" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="X15" t="n">
+        <v>970</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>25</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>70</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>32</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>140</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>29</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>130</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>970</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>13</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>2026-03-23 22:54:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>US United Soccer League</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>20:30:00</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Sporting Club Jacksonville</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Miami FC</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="G16" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H16" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J16" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K16" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N16" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X16" t="n">
+        <v>970</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>970</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>38</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>28</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>27</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>970</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>40</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>65</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>44</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>38</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>22</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>2026-03-23 22:54:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>Uruguayan Primera Division</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>2026-03-25</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>20:30:00</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>Boston River</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>Penarol</t>
         </is>
       </c>
-      <c r="F15" t="n">
+      <c r="F17" t="n">
         <v>6.6</v>
       </c>
-      <c r="G15" t="n">
+      <c r="G17" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K17" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N17" t="n">
+        <v>3</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S17" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="V17" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X17" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>17</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>20</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>24</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>65</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>34</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>28</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>300</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>160</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>160</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>230</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>270</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>14</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV17" t="n">
         <v>8</v>
       </c>
-      <c r="H15" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="I15" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="J15" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="K15" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="L15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N15" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="O15" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="P15" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S15" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="V15" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH15" t="inlineStr">
-        <is>
-          <t>2026-03-23 20:48:35</t>
+      <c r="AW17" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>36</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>170</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>10</v>
+      </c>
+      <c r="BH17" t="inlineStr">
+        <is>
+          <t>2026-03-23 22:54:23</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-25.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH17"/>
+  <dimension ref="A1:BH18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -865,52 +865,52 @@
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF2" t="n">
         <v>1.01</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-23 22:54:23</t>
+          <t>2026-03-24 01:00:06</t>
         </is>
       </c>
     </row>
@@ -951,22 +951,22 @@
         </is>
       </c>
       <c r="F3" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="G3" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="I3" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J3" t="n">
         <v>2.36</v>
       </c>
-      <c r="G3" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="H3" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="I3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="J3" t="n">
-        <v>2.52</v>
-      </c>
       <c r="K3" t="n">
-        <v>4.3</v>
+        <v>950</v>
       </c>
       <c r="L3" t="n">
         <v>1.01</v>
@@ -975,34 +975,34 @@
         <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>1.27</v>
+        <v>1.87</v>
       </c>
       <c r="O3" t="n">
-        <v>1.01</v>
+        <v>1.7</v>
       </c>
       <c r="P3" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="R3" t="n">
         <v>1.08</v>
       </c>
       <c r="S3" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="T3" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U3" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V3" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="W3" t="n">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="X3" t="n">
         <v>1000</v>
@@ -1059,52 +1059,52 @@
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF3" t="n">
         <v>1.01</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-23 22:54:23</t>
+          <t>2026-03-24 01:00:06</t>
         </is>
       </c>
     </row>
@@ -1217,7 +1217,7 @@
         <v>970</v>
       </c>
       <c r="AD4" t="n">
-        <v>15.5</v>
+        <v>950</v>
       </c>
       <c r="AE4" t="n">
         <v>1000</v>
@@ -1229,7 +1229,7 @@
         <v>970</v>
       </c>
       <c r="AH4" t="n">
-        <v>24</v>
+        <v>950</v>
       </c>
       <c r="AI4" t="n">
         <v>1000</v>
@@ -1259,7 +1259,7 @@
         <v>7</v>
       </c>
       <c r="AR4" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AS4" t="n">
         <v>2.7</v>
@@ -1274,7 +1274,7 @@
         <v>5.3</v>
       </c>
       <c r="AW4" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="AX4" t="n">
         <v>5.5</v>
@@ -1286,7 +1286,7 @@
         <v>6</v>
       </c>
       <c r="BA4" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="BB4" t="n">
         <v>2.66</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-23 22:54:23</t>
+          <t>2026-03-24 01:00:06</t>
         </is>
       </c>
     </row>
@@ -1339,58 +1339,58 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.35</v>
+        <v>1.76</v>
       </c>
       <c r="G5" t="n">
-        <v>2.48</v>
+        <v>2.28</v>
       </c>
       <c r="H5" t="n">
         <v>3.9</v>
       </c>
       <c r="I5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J5" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="K5" t="n">
-        <v>950</v>
+        <v>5.6</v>
       </c>
       <c r="L5" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="M5" t="n">
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>1.38</v>
+        <v>2.22</v>
       </c>
       <c r="O5" t="n">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="P5" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.38</v>
+        <v>2.14</v>
       </c>
       <c r="R5" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="S5" t="n">
-        <v>2.38</v>
+        <v>2.8</v>
       </c>
       <c r="T5" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U5" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V5" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="W5" t="n">
-        <v>1.67</v>
+        <v>1.78</v>
       </c>
       <c r="X5" t="n">
         <v>1000</v>
@@ -1447,52 +1447,52 @@
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF5" t="n">
         <v>1.01</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-23 22:54:23</t>
+          <t>2026-03-24 01:00:06</t>
         </is>
       </c>
     </row>
@@ -1524,179 +1524,179 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Wealdstone</t>
+          <t>Morecambe</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Yeovil</t>
+          <t>Hartlepool</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.86</v>
+        <v>2.9</v>
       </c>
       <c r="G6" t="n">
-        <v>2</v>
+        <v>3.1</v>
       </c>
       <c r="H6" t="n">
-        <v>4.2</v>
+        <v>2.32</v>
       </c>
       <c r="I6" t="n">
-        <v>4.8</v>
+        <v>2.56</v>
       </c>
       <c r="J6" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K6" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L6" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="M6" t="n">
         <v>1.05</v>
       </c>
       <c r="N6" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="O6" t="n">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="P6" t="n">
-        <v>2.02</v>
+        <v>2.2</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.83</v>
+        <v>1.59</v>
       </c>
       <c r="R6" t="n">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="S6" t="n">
-        <v>3</v>
+        <v>2.68</v>
       </c>
       <c r="T6" t="n">
-        <v>1.74</v>
+        <v>1.6</v>
       </c>
       <c r="U6" t="n">
-        <v>2.14</v>
+        <v>2.36</v>
       </c>
       <c r="V6" t="n">
-        <v>1.26</v>
+        <v>1.64</v>
       </c>
       <c r="W6" t="n">
-        <v>2</v>
+        <v>1.47</v>
       </c>
       <c r="X6" t="n">
-        <v>21</v>
+        <v>950</v>
       </c>
       <c r="Y6" t="n">
-        <v>20</v>
+        <v>970</v>
       </c>
       <c r="Z6" t="n">
-        <v>42</v>
+        <v>970</v>
       </c>
       <c r="AA6" t="n">
-        <v>120</v>
+        <v>36</v>
       </c>
       <c r="AB6" t="n">
-        <v>12</v>
+        <v>970</v>
       </c>
       <c r="AC6" t="n">
-        <v>10.5</v>
+        <v>970</v>
       </c>
       <c r="AD6" t="n">
-        <v>19</v>
+        <v>970</v>
       </c>
       <c r="AE6" t="n">
-        <v>65</v>
+        <v>25</v>
       </c>
       <c r="AF6" t="n">
-        <v>14.5</v>
+        <v>23</v>
       </c>
       <c r="AG6" t="n">
-        <v>12.5</v>
+        <v>970</v>
       </c>
       <c r="AH6" t="n">
-        <v>22</v>
+        <v>970</v>
       </c>
       <c r="AI6" t="n">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="AJ6" t="n">
-        <v>27</v>
+        <v>55</v>
       </c>
       <c r="AK6" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="AL6" t="n">
         <v>38</v>
       </c>
       <c r="AM6" t="n">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="AN6" t="n">
-        <v>14.5</v>
+        <v>22</v>
       </c>
       <c r="AO6" t="n">
-        <v>55</v>
+        <v>970</v>
       </c>
       <c r="AP6" t="n">
-        <v>12</v>
+        <v>5.5</v>
       </c>
       <c r="AQ6" t="n">
-        <v>12.5</v>
+        <v>4.7</v>
       </c>
       <c r="AR6" t="n">
-        <v>4.3</v>
+        <v>2.92</v>
       </c>
       <c r="AS6" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AT6" t="n">
-        <v>7.2</v>
+        <v>10.5</v>
       </c>
       <c r="AU6" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV6" t="n">
-        <v>13.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW6" t="n">
-        <v>4.4</v>
+        <v>2.08</v>
       </c>
       <c r="AX6" t="n">
-        <v>9</v>
+        <v>1.92</v>
       </c>
       <c r="AY6" t="n">
-        <v>7.8</v>
+        <v>4.7</v>
       </c>
       <c r="AZ6" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="BA6" t="n">
-        <v>4.4</v>
+        <v>1.61</v>
       </c>
       <c r="BB6" t="n">
-        <v>15.5</v>
+        <v>2.78</v>
       </c>
       <c r="BC6" t="n">
-        <v>14</v>
+        <v>1.6</v>
       </c>
       <c r="BD6" t="n">
-        <v>4.2</v>
+        <v>6</v>
       </c>
       <c r="BE6" t="n">
-        <v>4.6</v>
+        <v>1.66</v>
       </c>
       <c r="BF6" t="n">
-        <v>8.800000000000001</v>
+        <v>5.3</v>
       </c>
       <c r="BG6" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-23 22:54:23</t>
+          <t>2026-03-24 01:00:06</t>
         </is>
       </c>
     </row>
@@ -1718,179 +1718,179 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Southend</t>
+          <t>Scunthorpe</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Woking</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.68</v>
+        <v>3.45</v>
       </c>
       <c r="G7" t="n">
-        <v>1.76</v>
+        <v>4</v>
       </c>
       <c r="H7" t="n">
-        <v>5.4</v>
+        <v>2.14</v>
       </c>
       <c r="I7" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="J7" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K7" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N7" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="X7" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>28</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>16</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>23</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>29</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>18</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>36</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>75</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>46</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>90</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>42</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>15</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>20</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>13</v>
+      </c>
+      <c r="AU7" t="n">
         <v>6.6</v>
       </c>
-      <c r="J7" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="K7" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N7" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="P7" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="U7" t="n">
-        <v>2</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="W7" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="X7" t="n">
-        <v>20</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>22</v>
-      </c>
-      <c r="Z7" t="n">
+      <c r="AV7" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>21</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB7" t="n">
         <v>50</v>
       </c>
-      <c r="AA7" t="n">
-        <v>170</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>24</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>80</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>11</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>80</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>18</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>36</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>120</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>100</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>13</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>34</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>8</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>17</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>55</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>15</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>13</v>
-      </c>
       <c r="BC7" t="n">
-        <v>13</v>
+        <v>7.2</v>
       </c>
       <c r="BD7" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BE7" t="n">
         <v>8</v>
       </c>
       <c r="BF7" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BG7" t="n">
-        <v>7.8</v>
+        <v>11</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-23 22:54:23</t>
+          <t>2026-03-24 01:00:06</t>
         </is>
       </c>
     </row>
@@ -1912,179 +1912,179 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Tamworth FC</t>
+          <t>Truro City</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Forest Green</t>
+          <t>Solihull Moors</t>
         </is>
       </c>
       <c r="F8" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="G8" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="J8" t="n">
         <v>3.5</v>
       </c>
-      <c r="G8" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="H8" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="I8" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="J8" t="n">
-        <v>3.85</v>
-      </c>
       <c r="K8" t="n">
-        <v>4.4</v>
+        <v>3.7</v>
       </c>
       <c r="L8" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="M8" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="N8" t="n">
-        <v>4.6</v>
+        <v>3.55</v>
       </c>
       <c r="O8" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="P8" t="n">
-        <v>2.26</v>
+        <v>1.88</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.67</v>
+        <v>1.9</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5</v>
+        <v>1.37</v>
       </c>
       <c r="S8" t="n">
-        <v>2.66</v>
+        <v>3.1</v>
       </c>
       <c r="T8" t="n">
-        <v>1.61</v>
+        <v>1.68</v>
       </c>
       <c r="U8" t="n">
-        <v>2.32</v>
+        <v>2.2</v>
       </c>
       <c r="V8" t="n">
-        <v>1.87</v>
+        <v>1.62</v>
       </c>
       <c r="W8" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="X8" t="n">
-        <v>25</v>
+        <v>970</v>
       </c>
       <c r="Y8" t="n">
-        <v>12.5</v>
+        <v>970</v>
       </c>
       <c r="Z8" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AA8" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>18.5</v>
+        <v>970</v>
       </c>
       <c r="AC8" t="n">
-        <v>11.5</v>
+        <v>8</v>
       </c>
       <c r="AD8" t="n">
-        <v>13</v>
+        <v>970</v>
       </c>
       <c r="AE8" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="AF8" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="AG8" t="n">
-        <v>16.5</v>
+        <v>970</v>
       </c>
       <c r="AH8" t="n">
-        <v>17</v>
+        <v>950</v>
       </c>
       <c r="AI8" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AJ8" t="n">
         <v>1000</v>
       </c>
       <c r="AK8" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AL8" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AM8" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AO8" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>15</v>
+        <v>5.5</v>
       </c>
       <c r="AQ8" t="n">
-        <v>8.800000000000001</v>
+        <v>4.7</v>
       </c>
       <c r="AR8" t="n">
-        <v>10.5</v>
+        <v>5.3</v>
       </c>
       <c r="AS8" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="AT8" t="n">
-        <v>12.5</v>
+        <v>5.1</v>
       </c>
       <c r="AU8" t="n">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="AV8" t="n">
-        <v>8</v>
+        <v>5.1</v>
       </c>
       <c r="AW8" t="n">
-        <v>14.5</v>
+        <v>3.2</v>
       </c>
       <c r="AX8" t="n">
-        <v>21</v>
+        <v>5.8</v>
       </c>
       <c r="AY8" t="n">
-        <v>11.5</v>
+        <v>5.3</v>
       </c>
       <c r="AZ8" t="n">
-        <v>13.5</v>
+        <v>5.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="BB8" t="n">
-        <v>6</v>
+        <v>3.05</v>
       </c>
       <c r="BC8" t="n">
+        <v>3</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BG8" t="n">
         <v>5.8</v>
       </c>
-      <c r="BD8" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>48</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>8.4</v>
-      </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-23 22:54:23</t>
+          <t>2026-03-24 01:00:06</t>
         </is>
       </c>
     </row>
@@ -2106,179 +2106,179 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Scunthorpe</t>
+          <t>Southend</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>Woking</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.45</v>
+        <v>1.67</v>
       </c>
       <c r="G9" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="H9" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="I9" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N9" t="n">
         <v>4</v>
       </c>
-      <c r="H9" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="I9" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="J9" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="K9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N9" t="n">
-        <v>3.85</v>
-      </c>
       <c r="O9" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="P9" t="n">
-        <v>1.99</v>
+        <v>2.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="R9" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="S9" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="T9" t="n">
-        <v>1.69</v>
+        <v>1.78</v>
       </c>
       <c r="U9" t="n">
-        <v>2.16</v>
+        <v>2.02</v>
       </c>
       <c r="V9" t="n">
-        <v>1.79</v>
+        <v>1.2</v>
       </c>
       <c r="W9" t="n">
-        <v>1.34</v>
+        <v>2.3</v>
       </c>
       <c r="X9" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Y9" t="n">
+        <v>22</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>50</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>170</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>24</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>80</v>
+      </c>
+      <c r="AF9" t="n">
         <v>11</v>
       </c>
-      <c r="Z9" t="n">
+      <c r="AG9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>18</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>100</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>34</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>8</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>17</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>55</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AZ9" t="n">
         <v>15</v>
       </c>
-      <c r="AA9" t="n">
-        <v>28</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>16</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>9</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>23</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>29</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>18</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>36</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>75</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>46</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>50</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>90</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>42</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>15</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>20</v>
-      </c>
-      <c r="AT9" t="n">
+      <c r="BA9" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BB9" t="n">
         <v>13</v>
       </c>
-      <c r="AU9" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>21</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>12</v>
-      </c>
-      <c r="AZ9" t="n">
+      <c r="BC9" t="n">
         <v>13</v>
       </c>
-      <c r="BA9" t="n">
+      <c r="BD9" t="n">
         <v>7</v>
       </c>
-      <c r="BB9" t="n">
-        <v>50</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BD9" t="n">
+      <c r="BE9" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF9" t="n">
         <v>7.4</v>
       </c>
-      <c r="BE9" t="n">
+      <c r="BG9" t="n">
         <v>7.8</v>
       </c>
-      <c r="BF9" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>11</v>
-      </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-23 22:54:23</t>
+          <t>2026-03-24 01:00:06</t>
         </is>
       </c>
     </row>
@@ -2300,179 +2300,179 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Truro City</t>
+          <t>Wealdstone</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Solihull Moors</t>
+          <t>Yeovil</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.94</v>
+        <v>1.86</v>
       </c>
       <c r="G10" t="n">
-        <v>3.3</v>
+        <v>2</v>
       </c>
       <c r="H10" t="n">
-        <v>2.36</v>
+        <v>4.2</v>
       </c>
       <c r="I10" t="n">
-        <v>2.62</v>
+        <v>4.8</v>
       </c>
       <c r="J10" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="K10" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="L10" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="M10" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N10" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="O10" t="n">
         <v>1.28</v>
       </c>
       <c r="P10" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="Q10" t="n">
         <v>1.83</v>
       </c>
       <c r="R10" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="S10" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="T10" t="n">
-        <v>1.67</v>
+        <v>1.74</v>
       </c>
       <c r="U10" t="n">
-        <v>2.22</v>
+        <v>2.14</v>
       </c>
       <c r="V10" t="n">
-        <v>1.61</v>
+        <v>1.26</v>
       </c>
       <c r="W10" t="n">
-        <v>1.44</v>
+        <v>2</v>
       </c>
       <c r="X10" t="n">
-        <v>970</v>
+        <v>21</v>
       </c>
       <c r="Y10" t="n">
-        <v>970</v>
+        <v>20</v>
       </c>
       <c r="Z10" t="n">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="AA10" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AB10" t="n">
-        <v>970</v>
+        <v>12</v>
       </c>
       <c r="AC10" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AD10" t="n">
-        <v>970</v>
+        <v>19</v>
       </c>
       <c r="AE10" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ10" t="n">
         <v>27</v>
       </c>
-      <c r="AF10" t="n">
-        <v>25</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>1000</v>
-      </c>
       <c r="AK10" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AL10" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AM10" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN10" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AO10" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AP10" t="n">
-        <v>5.2</v>
+        <v>12</v>
       </c>
       <c r="AQ10" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AS10" t="n">
         <v>4.6</v>
       </c>
-      <c r="AR10" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>2.88</v>
-      </c>
       <c r="AT10" t="n">
-        <v>4.8</v>
+        <v>7.2</v>
       </c>
       <c r="AU10" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AV10" t="n">
-        <v>9.4</v>
+        <v>13.5</v>
       </c>
       <c r="AW10" t="n">
-        <v>5.7</v>
+        <v>4.4</v>
       </c>
       <c r="AX10" t="n">
-        <v>5.6</v>
+        <v>9</v>
       </c>
       <c r="AY10" t="n">
-        <v>4.9</v>
+        <v>7.8</v>
       </c>
       <c r="AZ10" t="n">
-        <v>5.2</v>
+        <v>13</v>
       </c>
       <c r="BA10" t="n">
-        <v>2.42</v>
+        <v>4.4</v>
       </c>
       <c r="BB10" t="n">
-        <v>2.18</v>
+        <v>15.5</v>
       </c>
       <c r="BC10" t="n">
-        <v>2.42</v>
+        <v>14</v>
       </c>
       <c r="BD10" t="n">
-        <v>6.4</v>
+        <v>4.2</v>
       </c>
       <c r="BE10" t="n">
-        <v>2.2</v>
+        <v>4.6</v>
       </c>
       <c r="BF10" t="n">
-        <v>3.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG10" t="n">
-        <v>5.3</v>
+        <v>4.4</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-23 22:54:23</t>
+          <t>2026-03-24 01:00:06</t>
         </is>
       </c>
     </row>
@@ -2494,179 +2494,179 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Morecambe</t>
+          <t>Tamworth FC</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hartlepool</t>
+          <t>Forest Green</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="G11" t="n">
-        <v>3.1</v>
+        <v>3.95</v>
       </c>
       <c r="H11" t="n">
-        <v>2.32</v>
+        <v>2</v>
       </c>
       <c r="I11" t="n">
-        <v>2.56</v>
+        <v>2.14</v>
       </c>
       <c r="J11" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="K11" t="n">
         <v>4.3</v>
       </c>
       <c r="L11" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="M11" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N11" t="n">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="O11" t="n">
         <v>1.23</v>
       </c>
       <c r="P11" t="n">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.58</v>
+        <v>1.7</v>
       </c>
       <c r="R11" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="S11" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="T11" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="U11" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="V11" t="n">
-        <v>1.64</v>
+        <v>1.87</v>
       </c>
       <c r="W11" t="n">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="X11" t="n">
         <v>25</v>
       </c>
       <c r="Y11" t="n">
-        <v>970</v>
+        <v>12.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>970</v>
+        <v>17.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="AB11" t="n">
-        <v>970</v>
+        <v>18.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>970</v>
+        <v>13</v>
       </c>
       <c r="AE11" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AF11" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="AG11" t="n">
-        <v>970</v>
+        <v>16.5</v>
       </c>
       <c r="AH11" t="n">
-        <v>970</v>
+        <v>17</v>
       </c>
       <c r="AI11" t="n">
+        <v>32</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>42</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>75</v>
+      </c>
+      <c r="AN11" t="n">
         <v>34</v>
       </c>
-      <c r="AJ11" t="n">
-        <v>55</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>32</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>38</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>85</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>22</v>
-      </c>
       <c r="AO11" t="n">
-        <v>970</v>
+        <v>12</v>
       </c>
       <c r="AP11" t="n">
-        <v>5.4</v>
+        <v>15</v>
       </c>
       <c r="AQ11" t="n">
-        <v>4.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR11" t="n">
-        <v>3.3</v>
+        <v>10.5</v>
       </c>
       <c r="AS11" t="n">
+        <v>18</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>8</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>21</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>21</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BC11" t="n">
         <v>5.8</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>1.59</v>
       </c>
       <c r="BD11" t="n">
         <v>5.8</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.64</v>
+        <v>48</v>
       </c>
       <c r="BF11" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="BG11" t="n">
-        <v>4.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-23 22:54:23</t>
+          <t>2026-03-24 01:00:06</t>
         </is>
       </c>
     </row>
@@ -2700,13 +2700,13 @@
         <v>3.1</v>
       </c>
       <c r="G12" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="H12" t="n">
         <v>2.6</v>
       </c>
       <c r="I12" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="J12" t="n">
         <v>2.82</v>
@@ -2715,28 +2715,28 @@
         <v>3.25</v>
       </c>
       <c r="L12" t="n">
-        <v>1.58</v>
+        <v>1.52</v>
       </c>
       <c r="M12" t="n">
         <v>1.12</v>
       </c>
       <c r="N12" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="O12" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="P12" t="n">
         <v>1.5</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="R12" t="n">
         <v>1.18</v>
       </c>
       <c r="S12" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="T12" t="n">
         <v>2.06</v>
@@ -2748,10 +2748,10 @@
         <v>1.51</v>
       </c>
       <c r="W12" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="X12" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="Y12" t="n">
         <v>970</v>
@@ -2781,7 +2781,7 @@
         <v>970</v>
       </c>
       <c r="AH12" t="n">
-        <v>24</v>
+        <v>950</v>
       </c>
       <c r="AI12" t="n">
         <v>80</v>
@@ -2811,10 +2811,10 @@
         <v>6.4</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="AS12" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AT12" t="n">
         <v>7</v>
@@ -2826,41 +2826,41 @@
         <v>10</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BA12" t="n">
-        <v>1.01</v>
+        <v>1.79</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="BD12" t="n">
-        <v>1.01</v>
+        <v>1.79</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.01</v>
+        <v>1.61</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.01</v>
+        <v>1.79</v>
       </c>
       <c r="BG12" t="n">
-        <v>1.01</v>
+        <v>1.99</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-23 22:54:23</t>
+          <t>2026-03-24 01:00:06</t>
         </is>
       </c>
     </row>
@@ -2891,19 +2891,19 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="G13" t="n">
         <v>2.76</v>
       </c>
       <c r="H13" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="I13" t="n">
         <v>4.1</v>
       </c>
       <c r="J13" t="n">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="K13" t="n">
         <v>2.92</v>
@@ -2915,22 +2915,22 @@
         <v>1.21</v>
       </c>
       <c r="N13" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="O13" t="n">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="P13" t="n">
         <v>1.31</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="R13" t="n">
         <v>1.1</v>
       </c>
       <c r="S13" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="T13" t="n">
         <v>2.74</v>
@@ -2948,7 +2948,7 @@
         <v>6.6</v>
       </c>
       <c r="Y13" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z13" t="n">
         <v>30</v>
@@ -2960,10 +2960,10 @@
         <v>6.2</v>
       </c>
       <c r="AC13" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD13" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AE13" t="n">
         <v>120</v>
@@ -2972,10 +2972,10 @@
         <v>17.5</v>
       </c>
       <c r="AG13" t="n">
-        <v>16</v>
+        <v>950</v>
       </c>
       <c r="AH13" t="n">
-        <v>38</v>
+        <v>950</v>
       </c>
       <c r="AI13" t="n">
         <v>200</v>
@@ -2987,7 +2987,7 @@
         <v>60</v>
       </c>
       <c r="AL13" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AM13" t="n">
         <v>550</v>
@@ -2996,7 +2996,7 @@
         <v>80</v>
       </c>
       <c r="AO13" t="n">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="AP13" t="n">
         <v>5</v>
@@ -3005,10 +3005,10 @@
         <v>7</v>
       </c>
       <c r="AR13" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="AS13" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="AT13" t="n">
         <v>5.4</v>
@@ -3017,10 +3017,10 @@
         <v>6.8</v>
       </c>
       <c r="AV13" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="AW13" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="AX13" t="n">
         <v>12.5</v>
@@ -3029,32 +3029,32 @@
         <v>13.5</v>
       </c>
       <c r="AZ13" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="BA13" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BB13" t="n">
         <v>6.2</v>
       </c>
-      <c r="BB13" t="n">
-        <v>5.7</v>
-      </c>
       <c r="BC13" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="BD13" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BE13" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BF13" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BG13" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-23 22:54:23</t>
+          <t>2026-03-24 01:00:06</t>
         </is>
       </c>
     </row>
@@ -3094,7 +3094,7 @@
         <v>6.2</v>
       </c>
       <c r="I14" t="n">
-        <v>1000</v>
+        <v>870</v>
       </c>
       <c r="J14" t="n">
         <v>3.5</v>
@@ -3109,13 +3109,13 @@
         <v>1.06</v>
       </c>
       <c r="N14" t="n">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="O14" t="n">
         <v>1.35</v>
       </c>
       <c r="P14" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="Q14" t="n">
         <v>2</v>
@@ -3133,7 +3133,7 @@
         <v>1.11</v>
       </c>
       <c r="V14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W14" t="n">
         <v>2.28</v>
@@ -3193,52 +3193,52 @@
         <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF14" t="n">
         <v>1.01</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-23 22:54:23</t>
+          <t>2026-03-24 01:00:06</t>
         </is>
       </c>
     </row>
@@ -3312,22 +3312,22 @@
         <v>1.84</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="R15" t="n">
         <v>1.32</v>
       </c>
       <c r="S15" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="T15" t="n">
-        <v>1.76</v>
+        <v>1.96</v>
       </c>
       <c r="U15" t="n">
         <v>1.77</v>
       </c>
       <c r="V15" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="W15" t="n">
         <v>2.36</v>
@@ -3336,7 +3336,7 @@
         <v>970</v>
       </c>
       <c r="Y15" t="n">
-        <v>25</v>
+        <v>950</v>
       </c>
       <c r="Z15" t="n">
         <v>70</v>
@@ -3351,7 +3351,7 @@
         <v>11.5</v>
       </c>
       <c r="AD15" t="n">
-        <v>32</v>
+        <v>950</v>
       </c>
       <c r="AE15" t="n">
         <v>140</v>
@@ -3363,7 +3363,7 @@
         <v>12</v>
       </c>
       <c r="AH15" t="n">
-        <v>29</v>
+        <v>950</v>
       </c>
       <c r="AI15" t="n">
         <v>130</v>
@@ -3442,14 +3442,14 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-23 22:54:23</t>
+          <t>2026-03-24 01:00:06</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>US United Soccer League</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3464,186 +3464,186 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Sporting Club Jacksonville</t>
+          <t>Boston River</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Miami FC</t>
+          <t>Penarol</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>3.1</v>
+        <v>6.6</v>
       </c>
       <c r="G16" t="n">
-        <v>3.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H16" t="n">
-        <v>2.2</v>
+        <v>1.59</v>
       </c>
       <c r="I16" t="n">
-        <v>2.5</v>
+        <v>1.71</v>
       </c>
       <c r="J16" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K16" t="n">
         <v>4.2</v>
       </c>
       <c r="L16" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="M16" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="N16" t="n">
-        <v>3.55</v>
+        <v>3</v>
       </c>
       <c r="O16" t="n">
-        <v>1.32</v>
+        <v>1.41</v>
       </c>
       <c r="P16" t="n">
-        <v>1.94</v>
+        <v>1.69</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.86</v>
+        <v>2.18</v>
       </c>
       <c r="R16" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="S16" t="n">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="T16" t="n">
-        <v>1.72</v>
+        <v>2.14</v>
       </c>
       <c r="U16" t="n">
-        <v>2.14</v>
+        <v>1.71</v>
       </c>
       <c r="V16" t="n">
-        <v>1.68</v>
+        <v>2.4</v>
       </c>
       <c r="W16" t="n">
-        <v>1.4</v>
+        <v>1.14</v>
       </c>
       <c r="X16" t="n">
-        <v>970</v>
+        <v>13.5</v>
       </c>
       <c r="Y16" t="n">
-        <v>970</v>
+        <v>7</v>
       </c>
       <c r="Z16" t="n">
-        <v>970</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AA16" t="n">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="AB16" t="n">
-        <v>970</v>
+        <v>20</v>
       </c>
       <c r="AC16" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AD16" t="n">
-        <v>970</v>
+        <v>11</v>
       </c>
       <c r="AE16" t="n">
+        <v>24</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>65</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>34</v>
+      </c>
+      <c r="AH16" t="n">
         <v>28</v>
       </c>
-      <c r="AF16" t="n">
-        <v>27</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>970</v>
-      </c>
       <c r="AI16" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="AJ16" t="n">
-        <v>65</v>
+        <v>300</v>
       </c>
       <c r="AK16" t="n">
-        <v>44</v>
+        <v>160</v>
       </c>
       <c r="AL16" t="n">
-        <v>60</v>
+        <v>160</v>
       </c>
       <c r="AM16" t="n">
-        <v>110</v>
+        <v>230</v>
       </c>
       <c r="AN16" t="n">
-        <v>38</v>
+        <v>270</v>
       </c>
       <c r="AO16" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="AP16" t="n">
-        <v>4.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ16" t="n">
-        <v>7.6</v>
+        <v>5.2</v>
       </c>
       <c r="AR16" t="n">
-        <v>4.2</v>
+        <v>6.8</v>
       </c>
       <c r="AS16" t="n">
-        <v>4.9</v>
+        <v>12.5</v>
       </c>
       <c r="AT16" t="n">
-        <v>10.5</v>
+        <v>14.5</v>
       </c>
       <c r="AU16" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV16" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AW16" t="n">
-        <v>4.7</v>
+        <v>15.5</v>
       </c>
       <c r="AX16" t="n">
-        <v>4.6</v>
+        <v>6.8</v>
       </c>
       <c r="AY16" t="n">
-        <v>4.2</v>
+        <v>6.2</v>
       </c>
       <c r="AZ16" t="n">
-        <v>4.3</v>
+        <v>20</v>
       </c>
       <c r="BA16" t="n">
-        <v>4.9</v>
+        <v>36</v>
       </c>
       <c r="BB16" t="n">
-        <v>5.1</v>
+        <v>7.4</v>
       </c>
       <c r="BC16" t="n">
-        <v>4.9</v>
+        <v>7.2</v>
       </c>
       <c r="BD16" t="n">
-        <v>5.1</v>
+        <v>7.2</v>
       </c>
       <c r="BE16" t="n">
-        <v>5.3</v>
+        <v>7.4</v>
       </c>
       <c r="BF16" t="n">
-        <v>4.9</v>
+        <v>7.4</v>
       </c>
       <c r="BG16" t="n">
-        <v>4.4</v>
+        <v>10</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-23 22:54:23</t>
+          <t>2026-03-24 01:00:06</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>US United Soccer League</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3658,179 +3658,373 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Boston River</t>
+          <t>Sporting Club Jacksonville</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Penarol</t>
+          <t>Miami FC</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>6.6</v>
+        <v>3.1</v>
       </c>
       <c r="G17" t="n">
-        <v>8.199999999999999</v>
+        <v>3.5</v>
       </c>
       <c r="H17" t="n">
-        <v>1.59</v>
+        <v>2.2</v>
       </c>
       <c r="I17" t="n">
-        <v>1.71</v>
+        <v>2.5</v>
       </c>
       <c r="J17" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="K17" t="n">
         <v>4.2</v>
       </c>
       <c r="L17" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="M17" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="N17" t="n">
-        <v>3</v>
+        <v>3.55</v>
       </c>
       <c r="O17" t="n">
-        <v>1.41</v>
+        <v>1.32</v>
       </c>
       <c r="P17" t="n">
-        <v>1.69</v>
+        <v>1.94</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.18</v>
+        <v>1.86</v>
       </c>
       <c r="R17" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="S17" t="n">
-        <v>4.1</v>
+        <v>3.3</v>
       </c>
       <c r="T17" t="n">
-        <v>2.12</v>
+        <v>1.72</v>
       </c>
       <c r="U17" t="n">
-        <v>1.71</v>
+        <v>2.14</v>
       </c>
       <c r="V17" t="n">
-        <v>2.4</v>
+        <v>1.68</v>
       </c>
       <c r="W17" t="n">
-        <v>1.14</v>
+        <v>1.4</v>
       </c>
       <c r="X17" t="n">
-        <v>13.5</v>
+        <v>970</v>
       </c>
       <c r="Y17" t="n">
-        <v>7</v>
+        <v>970</v>
       </c>
       <c r="Z17" t="n">
-        <v>9.199999999999999</v>
+        <v>970</v>
       </c>
       <c r="AA17" t="n">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="AB17" t="n">
-        <v>20</v>
+        <v>970</v>
       </c>
       <c r="AC17" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AD17" t="n">
-        <v>11</v>
+        <v>970</v>
       </c>
       <c r="AE17" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="AF17" t="n">
+        <v>27</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>970</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AJ17" t="n">
         <v>65</v>
       </c>
-      <c r="AG17" t="n">
-        <v>34</v>
-      </c>
-      <c r="AH17" t="n">
+      <c r="AK17" t="n">
+        <v>44</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>38</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>22</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>5</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BH17" t="inlineStr">
+        <is>
+          <t>2026-03-24 01:00:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Colombian Primera A</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>22:00:00</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>America de Cali S.A</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Llaneros FC</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="H18" t="n">
+        <v>7</v>
+      </c>
+      <c r="I18" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K18" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N18" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S18" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="W18" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="X18" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>75</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH18" t="n">
         <v>28</v>
       </c>
-      <c r="AI17" t="n">
-        <v>55</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>300</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>160</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>160</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>230</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>270</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>14</v>
-      </c>
-      <c r="AP17" t="n">
+      <c r="AI18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>21</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>9</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>10</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD18" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AQ17" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>8</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>20</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>36</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>170</v>
-      </c>
-      <c r="BG17" t="n">
+      <c r="BE18" t="n">
         <v>10</v>
       </c>
-      <c r="BH17" t="inlineStr">
-        <is>
-          <t>2026-03-23 22:54:23</t>
+      <c r="BF18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>10</v>
+      </c>
+      <c r="BH18" t="inlineStr">
+        <is>
+          <t>2026-03-24 01:00:06</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-25.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-25.xlsx
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-24 01:00:06</t>
+          <t>2026-03-24 03:05:41</t>
         </is>
       </c>
     </row>
@@ -951,28 +951,28 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.58</v>
+        <v>2.82</v>
       </c>
       <c r="G3" t="n">
         <v>3.65</v>
       </c>
       <c r="H3" t="n">
-        <v>2.22</v>
+        <v>2.62</v>
       </c>
       <c r="I3" t="n">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="J3" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="K3" t="n">
-        <v>950</v>
+        <v>3.05</v>
       </c>
       <c r="L3" t="n">
         <v>1.01</v>
       </c>
       <c r="M3" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="N3" t="n">
         <v>1.87</v>
@@ -981,7 +981,7 @@
         <v>1.7</v>
       </c>
       <c r="P3" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="Q3" t="n">
         <v>2.88</v>
@@ -993,13 +993,13 @@
         <v>2.88</v>
       </c>
       <c r="T3" t="n">
-        <v>1.11</v>
+        <v>2.1</v>
       </c>
       <c r="U3" t="n">
-        <v>1.11</v>
+        <v>1.61</v>
       </c>
       <c r="V3" t="n">
-        <v>1.32</v>
+        <v>1.41</v>
       </c>
       <c r="W3" t="n">
         <v>1.37</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-24 01:00:06</t>
+          <t>2026-03-24 03:05:41</t>
         </is>
       </c>
     </row>
@@ -1151,7 +1151,7 @@
         <v>2.94</v>
       </c>
       <c r="H4" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="I4" t="n">
         <v>3.55</v>
@@ -1160,16 +1160,16 @@
         <v>2.84</v>
       </c>
       <c r="K4" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="L4" t="n">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="M4" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="N4" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="O4" t="n">
         <v>1.58</v>
@@ -1187,7 +1187,7 @@
         <v>5</v>
       </c>
       <c r="T4" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="U4" t="n">
         <v>1.76</v>
@@ -1196,10 +1196,10 @@
         <v>1.39</v>
       </c>
       <c r="W4" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="X4" t="n">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y4" t="n">
         <v>970</v>
@@ -1217,13 +1217,13 @@
         <v>970</v>
       </c>
       <c r="AD4" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AE4" t="n">
         <v>1000</v>
       </c>
       <c r="AF4" t="n">
-        <v>17</v>
+        <v>970</v>
       </c>
       <c r="AG4" t="n">
         <v>970</v>
@@ -1259,56 +1259,56 @@
         <v>7</v>
       </c>
       <c r="AR4" t="n">
-        <v>4.2</v>
+        <v>2.54</v>
       </c>
       <c r="AS4" t="n">
-        <v>2.7</v>
+        <v>5.2</v>
       </c>
       <c r="AT4" t="n">
         <v>6.2</v>
       </c>
       <c r="AU4" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AV4" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="AW4" t="n">
-        <v>2.68</v>
+        <v>7.6</v>
       </c>
       <c r="AX4" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="AY4" t="n">
         <v>10</v>
       </c>
       <c r="AZ4" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BA4" t="n">
-        <v>2.72</v>
+        <v>2.5</v>
       </c>
       <c r="BB4" t="n">
-        <v>2.66</v>
+        <v>7.6</v>
       </c>
       <c r="BC4" t="n">
-        <v>4.7</v>
+        <v>7.2</v>
       </c>
       <c r="BD4" t="n">
-        <v>2.7</v>
+        <v>5.1</v>
       </c>
       <c r="BE4" t="n">
-        <v>2.48</v>
+        <v>1.55</v>
       </c>
       <c r="BF4" t="n">
-        <v>2.66</v>
+        <v>2.74</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.7</v>
+        <v>2.78</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-24 01:00:06</t>
+          <t>2026-03-24 03:05:41</t>
         </is>
       </c>
     </row>
@@ -1339,58 +1339,58 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.76</v>
+        <v>1.89</v>
       </c>
       <c r="G5" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="H5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I5" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="J5" t="n">
+        <v>3</v>
+      </c>
+      <c r="K5" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N5" t="n">
         <v>2.28</v>
       </c>
-      <c r="H5" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="I5" t="n">
-        <v>7</v>
-      </c>
-      <c r="J5" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="K5" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="L5" t="n">
+      <c r="O5" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="P5" t="n">
         <v>1.5</v>
       </c>
-      <c r="M5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N5" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="P5" t="n">
-        <v>1.39</v>
-      </c>
       <c r="Q5" t="n">
-        <v>2.14</v>
+        <v>2.36</v>
       </c>
       <c r="R5" t="n">
-        <v>1.09</v>
+        <v>1.18</v>
       </c>
       <c r="S5" t="n">
-        <v>2.8</v>
+        <v>3.45</v>
       </c>
       <c r="T5" t="n">
-        <v>1.11</v>
+        <v>2.2</v>
       </c>
       <c r="U5" t="n">
-        <v>1.11</v>
+        <v>1.66</v>
       </c>
       <c r="V5" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="W5" t="n">
-        <v>1.78</v>
+        <v>1.89</v>
       </c>
       <c r="X5" t="n">
         <v>1000</v>
@@ -1447,62 +1447,62 @@
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.01</v>
+        <v>2.44</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.01</v>
+        <v>2.6</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.01</v>
+        <v>2.86</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.01</v>
+        <v>2.92</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-24 01:00:06</t>
+          <t>2026-03-24 03:05:41</t>
         </is>
       </c>
     </row>
@@ -1536,46 +1536,46 @@
         <v>2.9</v>
       </c>
       <c r="G6" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="H6" t="n">
         <v>2.32</v>
       </c>
       <c r="I6" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="J6" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="K6" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L6" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="M6" t="n">
         <v>1.05</v>
       </c>
       <c r="N6" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="O6" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P6" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="Q6" t="n">
         <v>1.59</v>
       </c>
       <c r="R6" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="S6" t="n">
         <v>2.68</v>
       </c>
       <c r="T6" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="U6" t="n">
         <v>2.36</v>
@@ -1584,7 +1584,7 @@
         <v>1.64</v>
       </c>
       <c r="W6" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="X6" t="n">
         <v>950</v>
@@ -1632,25 +1632,25 @@
         <v>38</v>
       </c>
       <c r="AM6" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AN6" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AO6" t="n">
         <v>970</v>
       </c>
       <c r="AP6" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="AQ6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AS6" t="n">
         <v>4.7</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>4.8</v>
       </c>
       <c r="AT6" t="n">
         <v>10.5</v>
@@ -1662,41 +1662,41 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AW6" t="n">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.92</v>
+        <v>2.02</v>
       </c>
       <c r="AY6" t="n">
         <v>4.7</v>
       </c>
       <c r="AZ6" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BG6" t="n">
         <v>5</v>
       </c>
-      <c r="BA6" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>6</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>4.9</v>
-      </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-24 01:00:06</t>
+          <t>2026-03-24 03:05:41</t>
         </is>
       </c>
     </row>
@@ -1736,43 +1736,43 @@
         <v>2.14</v>
       </c>
       <c r="I7" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="J7" t="n">
         <v>3.55</v>
       </c>
       <c r="K7" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L7" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="M7" t="n">
         <v>1.06</v>
       </c>
       <c r="N7" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="O7" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="P7" t="n">
-        <v>1.98</v>
+        <v>1.92</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.84</v>
+        <v>1.88</v>
       </c>
       <c r="R7" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="S7" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="T7" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="U7" t="n">
-        <v>2.16</v>
+        <v>2.08</v>
       </c>
       <c r="V7" t="n">
         <v>1.79</v>
@@ -1781,7 +1781,7 @@
         <v>1.34</v>
       </c>
       <c r="X7" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="Y7" t="n">
         <v>11</v>
@@ -1802,7 +1802,7 @@
         <v>11.5</v>
       </c>
       <c r="AE7" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AF7" t="n">
         <v>29</v>
@@ -1814,7 +1814,7 @@
         <v>18</v>
       </c>
       <c r="AI7" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="AJ7" t="n">
         <v>75</v>
@@ -1823,74 +1823,74 @@
         <v>46</v>
       </c>
       <c r="AL7" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AM7" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AO7" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="AP7" t="n">
-        <v>12.5</v>
+        <v>4.1</v>
       </c>
       <c r="AQ7" t="n">
-        <v>8.199999999999999</v>
+        <v>4.2</v>
       </c>
       <c r="AR7" t="n">
-        <v>10.5</v>
+        <v>4.7</v>
       </c>
       <c r="AS7" t="n">
-        <v>20</v>
+        <v>5.6</v>
       </c>
       <c r="AT7" t="n">
-        <v>13</v>
+        <v>4.9</v>
       </c>
       <c r="AU7" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BB7" t="n">
         <v>6.6</v>
       </c>
-      <c r="AV7" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>21</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>12</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>13</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>7</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>50</v>
-      </c>
       <c r="BC7" t="n">
-        <v>7.2</v>
+        <v>6.2</v>
       </c>
       <c r="BD7" t="n">
-        <v>7.4</v>
+        <v>6.2</v>
       </c>
       <c r="BE7" t="n">
-        <v>8</v>
+        <v>5.3</v>
       </c>
       <c r="BF7" t="n">
-        <v>7.2</v>
+        <v>6.2</v>
       </c>
       <c r="BG7" t="n">
-        <v>11</v>
+        <v>4.7</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-24 01:00:06</t>
+          <t>2026-03-24 03:05:41</t>
         </is>
       </c>
     </row>
@@ -1924,10 +1924,10 @@
         <v>2.98</v>
       </c>
       <c r="G8" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="H8" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="I8" t="n">
         <v>2.62</v>
@@ -1939,7 +1939,7 @@
         <v>3.7</v>
       </c>
       <c r="L8" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="M8" t="n">
         <v>1.06</v>
@@ -1948,7 +1948,7 @@
         <v>3.55</v>
       </c>
       <c r="O8" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="P8" t="n">
         <v>1.88</v>
@@ -1957,16 +1957,16 @@
         <v>1.9</v>
       </c>
       <c r="R8" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="S8" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="T8" t="n">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="U8" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="V8" t="n">
         <v>1.62</v>
@@ -1981,7 +1981,7 @@
         <v>970</v>
       </c>
       <c r="Z8" t="n">
-        <v>16</v>
+        <v>970</v>
       </c>
       <c r="AA8" t="n">
         <v>1000</v>
@@ -2029,7 +2029,7 @@
         <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="AQ8" t="n">
         <v>4.7</v>
@@ -2038,19 +2038,19 @@
         <v>5.3</v>
       </c>
       <c r="AS8" t="n">
-        <v>3</v>
+        <v>4.1</v>
       </c>
       <c r="AT8" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="AU8" t="n">
         <v>6.2</v>
       </c>
       <c r="AV8" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="AW8" t="n">
-        <v>3.2</v>
+        <v>3.95</v>
       </c>
       <c r="AX8" t="n">
         <v>5.8</v>
@@ -2062,29 +2062,29 @@
         <v>5.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>3</v>
+        <v>2.08</v>
       </c>
       <c r="BB8" t="n">
-        <v>3.05</v>
+        <v>4.2</v>
       </c>
       <c r="BC8" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="BD8" t="n">
         <v>6.8</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="BF8" t="n">
-        <v>3.2</v>
+        <v>4.5</v>
       </c>
       <c r="BG8" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-24 01:00:06</t>
+          <t>2026-03-24 03:05:41</t>
         </is>
       </c>
     </row>
@@ -2118,10 +2118,10 @@
         <v>1.67</v>
       </c>
       <c r="G9" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="H9" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="I9" t="n">
         <v>6.6</v>
@@ -2148,7 +2148,7 @@
         <v>2.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="R9" t="n">
         <v>1.41</v>
@@ -2220,7 +2220,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AO9" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AP9" t="n">
         <v>13</v>
@@ -2229,16 +2229,16 @@
         <v>17.5</v>
       </c>
       <c r="AR9" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AS9" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT9" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AU9" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV9" t="n">
         <v>17</v>
@@ -2247,25 +2247,25 @@
         <v>55</v>
       </c>
       <c r="AX9" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AY9" t="n">
         <v>7.8</v>
       </c>
       <c r="AZ9" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>7.8</v>
+        <v>55</v>
       </c>
       <c r="BB9" t="n">
         <v>13</v>
       </c>
       <c r="BC9" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="BD9" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="BE9" t="n">
         <v>8</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-24 01:00:06</t>
+          <t>2026-03-24 03:05:41</t>
         </is>
       </c>
     </row>
@@ -2312,10 +2312,10 @@
         <v>1.86</v>
       </c>
       <c r="G10" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="H10" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="I10" t="n">
         <v>4.8</v>
@@ -2330,10 +2330,10 @@
         <v>1.36</v>
       </c>
       <c r="M10" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N10" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="O10" t="n">
         <v>1.28</v>
@@ -2348,31 +2348,31 @@
         <v>1.41</v>
       </c>
       <c r="S10" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="T10" t="n">
         <v>1.74</v>
       </c>
       <c r="U10" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="V10" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="W10" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="X10" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Y10" t="n">
         <v>20</v>
       </c>
       <c r="Z10" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AA10" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AB10" t="n">
         <v>12</v>
@@ -2387,7 +2387,7 @@
         <v>65</v>
       </c>
       <c r="AF10" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AG10" t="n">
         <v>12.5</v>
@@ -2399,10 +2399,10 @@
         <v>60</v>
       </c>
       <c r="AJ10" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AK10" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AL10" t="n">
         <v>38</v>
@@ -2420,7 +2420,7 @@
         <v>12</v>
       </c>
       <c r="AQ10" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="AR10" t="n">
         <v>4.3</v>
@@ -2429,50 +2429,50 @@
         <v>4.6</v>
       </c>
       <c r="AT10" t="n">
-        <v>7.2</v>
+        <v>8.6</v>
       </c>
       <c r="AU10" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="AV10" t="n">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="AW10" t="n">
-        <v>4.4</v>
+        <v>44</v>
       </c>
       <c r="AX10" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY10" t="n">
         <v>9</v>
       </c>
-      <c r="AY10" t="n">
-        <v>7.8</v>
-      </c>
       <c r="AZ10" t="n">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="BA10" t="n">
         <v>4.4</v>
       </c>
       <c r="BB10" t="n">
-        <v>15.5</v>
+        <v>19</v>
       </c>
       <c r="BC10" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="BD10" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BE10" t="n">
         <v>4.6</v>
       </c>
       <c r="BF10" t="n">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BG10" t="n">
         <v>4.4</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-24 01:00:06</t>
+          <t>2026-03-24 03:05:41</t>
         </is>
       </c>
     </row>
@@ -2503,16 +2503,16 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="G11" t="n">
         <v>3.95</v>
       </c>
       <c r="H11" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="I11" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="J11" t="n">
         <v>3.85</v>
@@ -2524,7 +2524,7 @@
         <v>1.27</v>
       </c>
       <c r="M11" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N11" t="n">
         <v>4.5</v>
@@ -2536,19 +2536,19 @@
         <v>2.2</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="S11" t="n">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="T11" t="n">
         <v>1.62</v>
       </c>
       <c r="U11" t="n">
-        <v>2.32</v>
+        <v>2.26</v>
       </c>
       <c r="V11" t="n">
         <v>1.87</v>
@@ -2557,7 +2557,7 @@
         <v>1.36</v>
       </c>
       <c r="X11" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Y11" t="n">
         <v>12.5</v>
@@ -2572,7 +2572,7 @@
         <v>18.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD11" t="n">
         <v>13</v>
@@ -2602,7 +2602,7 @@
         <v>44</v>
       </c>
       <c r="AM11" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AN11" t="n">
         <v>34</v>
@@ -2611,62 +2611,62 @@
         <v>12</v>
       </c>
       <c r="AP11" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AQ11" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AR11" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AS11" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AT11" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AU11" t="n">
         <v>7</v>
       </c>
       <c r="AV11" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AW11" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AX11" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AY11" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AZ11" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BB11" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BC11" t="n">
-        <v>5.8</v>
+        <v>29</v>
       </c>
       <c r="BD11" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BE11" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BF11" t="n">
-        <v>5.6</v>
+        <v>23</v>
       </c>
       <c r="BG11" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-24 01:00:06</t>
+          <t>2026-03-24 03:05:41</t>
         </is>
       </c>
     </row>
@@ -2703,10 +2703,10 @@
         <v>3.55</v>
       </c>
       <c r="H12" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="I12" t="n">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="J12" t="n">
         <v>2.82</v>
@@ -2739,13 +2739,13 @@
         <v>5.3</v>
       </c>
       <c r="T12" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="U12" t="n">
         <v>1.76</v>
       </c>
       <c r="V12" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="W12" t="n">
         <v>1.39</v>
@@ -2814,19 +2814,19 @@
         <v>5.6</v>
       </c>
       <c r="AS12" t="n">
-        <v>7</v>
+        <v>1.99</v>
       </c>
       <c r="AT12" t="n">
         <v>7</v>
       </c>
       <c r="AU12" t="n">
-        <v>5.5</v>
+        <v>3.8</v>
       </c>
       <c r="AV12" t="n">
         <v>10</v>
       </c>
       <c r="AW12" t="n">
-        <v>7</v>
+        <v>3.8</v>
       </c>
       <c r="AX12" t="n">
         <v>6</v>
@@ -2841,7 +2841,7 @@
         <v>1.79</v>
       </c>
       <c r="BB12" t="n">
-        <v>3.95</v>
+        <v>1.78</v>
       </c>
       <c r="BC12" t="n">
         <v>2</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-24 01:00:06</t>
+          <t>2026-03-24 03:05:41</t>
         </is>
       </c>
     </row>
@@ -2891,19 +2891,19 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="G13" t="n">
-        <v>2.76</v>
+        <v>2.82</v>
       </c>
       <c r="H13" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="I13" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="J13" t="n">
-        <v>2.72</v>
+        <v>2.64</v>
       </c>
       <c r="K13" t="n">
         <v>2.92</v>
@@ -2915,7 +2915,7 @@
         <v>1.21</v>
       </c>
       <c r="N13" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="O13" t="n">
         <v>1.89</v>
@@ -2933,7 +2933,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="U13" t="n">
         <v>1.5</v>
@@ -2942,7 +2942,7 @@
         <v>1.33</v>
       </c>
       <c r="W13" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="X13" t="n">
         <v>6.6</v>
@@ -2966,22 +2966,22 @@
         <v>24</v>
       </c>
       <c r="AE13" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AF13" t="n">
         <v>17.5</v>
       </c>
       <c r="AG13" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AH13" t="n">
         <v>950</v>
       </c>
       <c r="AI13" t="n">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AJ13" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AK13" t="n">
         <v>60</v>
@@ -2990,7 +2990,7 @@
         <v>150</v>
       </c>
       <c r="AM13" t="n">
-        <v>550</v>
+        <v>540</v>
       </c>
       <c r="AN13" t="n">
         <v>80</v>
@@ -3005,22 +3005,22 @@
         <v>7</v>
       </c>
       <c r="AR13" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="AS13" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AT13" t="n">
         <v>5.4</v>
       </c>
       <c r="AU13" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AV13" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="AW13" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AX13" t="n">
         <v>12.5</v>
@@ -3029,32 +3029,32 @@
         <v>13.5</v>
       </c>
       <c r="AZ13" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BA13" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BB13" t="n">
         <v>6.2</v>
       </c>
       <c r="BC13" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BF13" t="n">
         <v>6.4</v>
       </c>
-      <c r="BD13" t="n">
+      <c r="BG13" t="n">
         <v>6.8</v>
       </c>
-      <c r="BE13" t="n">
-        <v>7</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>7</v>
-      </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-24 01:00:06</t>
+          <t>2026-03-24 03:05:41</t>
         </is>
       </c>
     </row>
@@ -3085,58 +3085,58 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.43</v>
+        <v>1.52</v>
       </c>
       <c r="G14" t="n">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="H14" t="n">
-        <v>6.2</v>
+        <v>5.1</v>
       </c>
       <c r="I14" t="n">
-        <v>870</v>
+        <v>13.5</v>
       </c>
       <c r="J14" t="n">
         <v>3.5</v>
       </c>
       <c r="K14" t="n">
-        <v>7.2</v>
+        <v>5.4</v>
       </c>
       <c r="L14" t="n">
-        <v>1.33</v>
+        <v>1.01</v>
       </c>
       <c r="M14" t="n">
         <v>1.06</v>
       </c>
       <c r="N14" t="n">
-        <v>2.54</v>
+        <v>2.4</v>
       </c>
       <c r="O14" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="P14" t="n">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="Q14" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="R14" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="S14" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="T14" t="n">
-        <v>1.9</v>
+        <v>1.11</v>
       </c>
       <c r="U14" t="n">
         <v>1.11</v>
       </c>
       <c r="V14" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="W14" t="n">
-        <v>2.28</v>
+        <v>2.16</v>
       </c>
       <c r="X14" t="n">
         <v>1000</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-24 01:00:06</t>
+          <t>2026-03-24 03:05:41</t>
         </is>
       </c>
     </row>
@@ -3279,13 +3279,13 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="G15" t="n">
         <v>1.73</v>
       </c>
       <c r="H15" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="I15" t="n">
         <v>8.6</v>
@@ -3294,7 +3294,7 @@
         <v>3.85</v>
       </c>
       <c r="K15" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L15" t="n">
         <v>1.34</v>
@@ -3303,25 +3303,25 @@
         <v>1.07</v>
       </c>
       <c r="N15" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="O15" t="n">
         <v>1.32</v>
       </c>
       <c r="P15" t="n">
-        <v>1.84</v>
+        <v>1.89</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="R15" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S15" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="T15" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="U15" t="n">
         <v>1.77</v>
@@ -3345,7 +3345,7 @@
         <v>1000</v>
       </c>
       <c r="AB15" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AC15" t="n">
         <v>11.5</v>
@@ -3354,7 +3354,7 @@
         <v>950</v>
       </c>
       <c r="AE15" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AF15" t="n">
         <v>11.5</v>
@@ -3366,31 +3366,31 @@
         <v>950</v>
       </c>
       <c r="AI15" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AJ15" t="n">
         <v>970</v>
       </c>
       <c r="AK15" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL15" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AM15" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AN15" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AO15" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AP15" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AQ15" t="n">
-        <v>3.7</v>
+        <v>14.5</v>
       </c>
       <c r="AR15" t="n">
         <v>4</v>
@@ -3399,19 +3399,19 @@
         <v>4.2</v>
       </c>
       <c r="AT15" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AU15" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV15" t="n">
         <v>3.8</v>
       </c>
       <c r="AW15" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AX15" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AY15" t="n">
         <v>7.4</v>
@@ -3420,29 +3420,29 @@
         <v>3.75</v>
       </c>
       <c r="BA15" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BB15" t="n">
         <v>11.5</v>
       </c>
       <c r="BC15" t="n">
-        <v>3.65</v>
+        <v>13</v>
       </c>
       <c r="BD15" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BE15" t="n">
         <v>4.2</v>
       </c>
       <c r="BF15" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BG15" t="n">
         <v>4.2</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-24 01:00:06</t>
+          <t>2026-03-24 03:05:41</t>
         </is>
       </c>
     </row>
@@ -3473,10 +3473,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="G16" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="H16" t="n">
         <v>1.59</v>
@@ -3491,34 +3491,34 @@
         <v>4.2</v>
       </c>
       <c r="L16" t="n">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="M16" t="n">
         <v>1.09</v>
       </c>
       <c r="N16" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="O16" t="n">
         <v>1.41</v>
       </c>
       <c r="P16" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="R16" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="S16" t="n">
         <v>4.1</v>
       </c>
       <c r="T16" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="U16" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="V16" t="n">
         <v>2.4</v>
@@ -3527,13 +3527,13 @@
         <v>1.14</v>
       </c>
       <c r="X16" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Y16" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="Z16" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AA16" t="n">
         <v>17</v>
@@ -3554,13 +3554,13 @@
         <v>65</v>
       </c>
       <c r="AG16" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AH16" t="n">
         <v>28</v>
       </c>
       <c r="AI16" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AJ16" t="n">
         <v>300</v>
@@ -3575,7 +3575,7 @@
         <v>230</v>
       </c>
       <c r="AN16" t="n">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="AO16" t="n">
         <v>14</v>
@@ -3584,7 +3584,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AQ16" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AR16" t="n">
         <v>6.8</v>
@@ -3605,10 +3605,10 @@
         <v>15.5</v>
       </c>
       <c r="AX16" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="AY16" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AZ16" t="n">
         <v>20</v>
@@ -3617,26 +3617,26 @@
         <v>36</v>
       </c>
       <c r="BB16" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="BC16" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD16" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE16" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF16" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="BG16" t="n">
         <v>10</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-24 01:00:06</t>
+          <t>2026-03-24 03:05:41</t>
         </is>
       </c>
     </row>
@@ -3667,40 +3667,40 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
       <c r="G17" t="n">
-        <v>3.5</v>
+        <v>2.92</v>
       </c>
       <c r="H17" t="n">
-        <v>2.2</v>
+        <v>2.72</v>
       </c>
       <c r="I17" t="n">
-        <v>2.5</v>
+        <v>2.98</v>
       </c>
       <c r="J17" t="n">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="K17" t="n">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="L17" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="M17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N17" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="O17" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="P17" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="R17" t="n">
         <v>1.36</v>
@@ -3709,16 +3709,16 @@
         <v>3.3</v>
       </c>
       <c r="T17" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="U17" t="n">
         <v>2.14</v>
       </c>
       <c r="V17" t="n">
-        <v>1.68</v>
+        <v>1.5</v>
       </c>
       <c r="W17" t="n">
-        <v>1.4</v>
+        <v>1.54</v>
       </c>
       <c r="X17" t="n">
         <v>970</v>
@@ -3730,22 +3730,22 @@
         <v>970</v>
       </c>
       <c r="AA17" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="AB17" t="n">
-        <v>970</v>
+        <v>13</v>
       </c>
       <c r="AC17" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AD17" t="n">
         <v>970</v>
       </c>
       <c r="AE17" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="AF17" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="AG17" t="n">
         <v>970</v>
@@ -3754,83 +3754,83 @@
         <v>970</v>
       </c>
       <c r="AI17" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="AJ17" t="n">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="AK17" t="n">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="AL17" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AM17" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AN17" t="n">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="AO17" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="AP17" t="n">
-        <v>4.3</v>
+        <v>11.5</v>
       </c>
       <c r="AQ17" t="n">
-        <v>7.6</v>
+        <v>9.6</v>
       </c>
       <c r="AR17" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="AS17" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW17" t="n">
         <v>5</v>
       </c>
-      <c r="AT17" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>4.8</v>
-      </c>
       <c r="AX17" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="AY17" t="n">
-        <v>4.3</v>
+        <v>9.6</v>
       </c>
       <c r="AZ17" t="n">
-        <v>4.4</v>
+        <v>12.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BB17" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="BC17" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BD17" t="n">
         <v>5.1</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>5.2</v>
       </c>
       <c r="BE17" t="n">
         <v>5.4</v>
       </c>
       <c r="BF17" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="BG17" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-24 01:00:06</t>
+          <t>2026-03-24 03:05:41</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="G18" t="n">
         <v>1.67</v>
@@ -3876,43 +3876,43 @@
         <v>3.7</v>
       </c>
       <c r="K18" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L18" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="M18" t="n">
         <v>1.09</v>
       </c>
       <c r="N18" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="O18" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="P18" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="R18" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S18" t="n">
         <v>4.1</v>
       </c>
       <c r="T18" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="U18" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="V18" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="W18" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="X18" t="n">
         <v>12</v>
@@ -3921,7 +3921,7 @@
         <v>20</v>
       </c>
       <c r="Z18" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AA18" t="n">
         <v>1000</v>
@@ -3930,34 +3930,34 @@
         <v>6.8</v>
       </c>
       <c r="AC18" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AD18" t="n">
-        <v>30</v>
+        <v>950</v>
       </c>
       <c r="AE18" t="n">
         <v>1000</v>
       </c>
       <c r="AF18" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AG18" t="n">
         <v>10.5</v>
       </c>
       <c r="AH18" t="n">
-        <v>28</v>
+        <v>950</v>
       </c>
       <c r="AI18" t="n">
         <v>1000</v>
       </c>
       <c r="AJ18" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AK18" t="n">
         <v>21</v>
       </c>
       <c r="AL18" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AM18" t="n">
         <v>1000</v>
@@ -3975,7 +3975,7 @@
         <v>6.8</v>
       </c>
       <c r="AR18" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS18" t="n">
         <v>10</v>
@@ -3993,7 +3993,7 @@
         <v>10</v>
       </c>
       <c r="AX18" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AY18" t="n">
         <v>9.199999999999999</v>
@@ -4002,10 +4002,10 @@
         <v>7.6</v>
       </c>
       <c r="BA18" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BB18" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BC18" t="n">
         <v>7</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-24 01:00:06</t>
+          <t>2026-03-24 03:05:41</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-25.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-25.xlsx
@@ -757,7 +757,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="G2" t="n">
         <v>1000</v>
@@ -781,13 +781,13 @@
         <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>1.1</v>
+        <v>1.28</v>
       </c>
       <c r="O2" t="n">
         <v>1.02</v>
       </c>
       <c r="P2" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="Q2" t="n">
         <v>1.28</v>
@@ -805,10 +805,10 @@
         <v>1.11</v>
       </c>
       <c r="V2" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W2" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X2" t="n">
         <v>1000</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-24 03:05:41</t>
+          <t>2026-03-24 05:11:15</t>
         </is>
       </c>
     </row>
@@ -951,91 +951,91 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="G3" t="n">
-        <v>3.65</v>
+        <v>3.2</v>
       </c>
       <c r="H3" t="n">
-        <v>2.62</v>
+        <v>2.98</v>
       </c>
       <c r="I3" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="J3" t="n">
-        <v>2.42</v>
+        <v>2.64</v>
       </c>
       <c r="K3" t="n">
         <v>3.05</v>
       </c>
       <c r="L3" t="n">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="M3" t="n">
         <v>1.14</v>
       </c>
       <c r="N3" t="n">
-        <v>1.87</v>
+        <v>2.16</v>
       </c>
       <c r="O3" t="n">
         <v>1.7</v>
       </c>
       <c r="P3" t="n">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="R3" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="S3" t="n">
-        <v>2.88</v>
+        <v>7</v>
       </c>
       <c r="T3" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="U3" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="V3" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W3" t="n">
-        <v>1.37</v>
+        <v>1.46</v>
       </c>
       <c r="X3" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="Y3" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="Z3" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AA3" t="n">
         <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AC3" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AD3" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AE3" t="n">
         <v>1000</v>
       </c>
       <c r="AF3" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AG3" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AH3" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AI3" t="n">
         <v>1000</v>
@@ -1044,7 +1044,7 @@
         <v>1000</v>
       </c>
       <c r="AK3" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AL3" t="n">
         <v>1000</v>
@@ -1059,62 +1059,62 @@
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-24 03:05:41</t>
+          <t>2026-03-24 05:11:15</t>
         </is>
       </c>
     </row>
@@ -1148,7 +1148,7 @@
         <v>2.58</v>
       </c>
       <c r="G4" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="H4" t="n">
         <v>3.1</v>
@@ -1214,7 +1214,7 @@
         <v>970</v>
       </c>
       <c r="AC4" t="n">
-        <v>970</v>
+        <v>7.4</v>
       </c>
       <c r="AD4" t="n">
         <v>970</v>
@@ -1259,10 +1259,10 @@
         <v>7</v>
       </c>
       <c r="AR4" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="AS4" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AT4" t="n">
         <v>6.2</v>
@@ -1271,13 +1271,13 @@
         <v>5.6</v>
       </c>
       <c r="AV4" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AW4" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AX4" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AY4" t="n">
         <v>10</v>
@@ -1286,29 +1286,29 @@
         <v>6.4</v>
       </c>
       <c r="BA4" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="BB4" t="n">
         <v>7.6</v>
       </c>
       <c r="BC4" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BD4" t="n">
-        <v>5.1</v>
+        <v>4</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.55</v>
+        <v>2.18</v>
       </c>
       <c r="BF4" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-24 03:05:41</t>
+          <t>2026-03-24 05:11:15</t>
         </is>
       </c>
     </row>
@@ -1360,19 +1360,19 @@
         <v>1.48</v>
       </c>
       <c r="M5" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="N5" t="n">
-        <v>2.28</v>
+        <v>2.46</v>
       </c>
       <c r="O5" t="n">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="P5" t="n">
         <v>1.5</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.36</v>
+        <v>2.6</v>
       </c>
       <c r="R5" t="n">
         <v>1.18</v>
@@ -1384,16 +1384,16 @@
         <v>2.2</v>
       </c>
       <c r="U5" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="V5" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="W5" t="n">
         <v>1.89</v>
       </c>
       <c r="X5" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Y5" t="n">
         <v>1000</v>
@@ -1447,62 +1447,62 @@
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>3.85</v>
+        <v>4.4</v>
       </c>
       <c r="AQ5" t="n">
-        <v>3</v>
+        <v>4.9</v>
       </c>
       <c r="AR5" t="n">
-        <v>3.5</v>
+        <v>6.4</v>
       </c>
       <c r="AS5" t="n">
-        <v>3.8</v>
+        <v>1.49</v>
       </c>
       <c r="AT5" t="n">
-        <v>2.44</v>
+        <v>3.55</v>
       </c>
       <c r="AU5" t="n">
-        <v>2.6</v>
+        <v>3.9</v>
       </c>
       <c r="AV5" t="n">
-        <v>3.25</v>
+        <v>2.12</v>
       </c>
       <c r="AW5" t="n">
-        <v>3.8</v>
+        <v>2.28</v>
       </c>
       <c r="AX5" t="n">
-        <v>2.86</v>
+        <v>4.5</v>
       </c>
       <c r="AY5" t="n">
-        <v>2.92</v>
+        <v>4.7</v>
       </c>
       <c r="AZ5" t="n">
-        <v>3.4</v>
+        <v>1.8</v>
       </c>
       <c r="BA5" t="n">
-        <v>3.8</v>
+        <v>1.49</v>
       </c>
       <c r="BB5" t="n">
-        <v>3.3</v>
+        <v>2.14</v>
       </c>
       <c r="BC5" t="n">
-        <v>3.4</v>
+        <v>1.7</v>
       </c>
       <c r="BD5" t="n">
-        <v>3.8</v>
+        <v>2.26</v>
       </c>
       <c r="BE5" t="n">
-        <v>3.8</v>
+        <v>1.5</v>
       </c>
       <c r="BF5" t="n">
-        <v>3.3</v>
+        <v>1.69</v>
       </c>
       <c r="BG5" t="n">
-        <v>3.8</v>
+        <v>1.49</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-24 03:05:41</t>
+          <t>2026-03-24 05:11:15</t>
         </is>
       </c>
     </row>
@@ -1533,16 +1533,16 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="G6" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="H6" t="n">
-        <v>2.32</v>
+        <v>2.24</v>
       </c>
       <c r="I6" t="n">
-        <v>2.54</v>
+        <v>2.46</v>
       </c>
       <c r="J6" t="n">
         <v>3.7</v>
@@ -1551,7 +1551,7 @@
         <v>4.2</v>
       </c>
       <c r="L6" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="M6" t="n">
         <v>1.05</v>
@@ -1578,13 +1578,13 @@
         <v>1.62</v>
       </c>
       <c r="U6" t="n">
-        <v>2.36</v>
+        <v>2.18</v>
       </c>
       <c r="V6" t="n">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="W6" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="X6" t="n">
         <v>950</v>
@@ -1626,7 +1626,7 @@
         <v>55</v>
       </c>
       <c r="AK6" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AL6" t="n">
         <v>38</v>
@@ -1641,16 +1641,16 @@
         <v>970</v>
       </c>
       <c r="AP6" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AQ6" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AR6" t="n">
-        <v>3.2</v>
+        <v>5</v>
       </c>
       <c r="AS6" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AT6" t="n">
         <v>10.5</v>
@@ -1662,41 +1662,41 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.93</v>
+        <v>2.02</v>
       </c>
       <c r="AX6" t="n">
-        <v>2.02</v>
+        <v>2.14</v>
       </c>
       <c r="AY6" t="n">
-        <v>4.7</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ6" t="n">
         <v>11.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="BB6" t="n">
-        <v>2.44</v>
+        <v>6.2</v>
       </c>
       <c r="BC6" t="n">
         <v>1.68</v>
       </c>
       <c r="BD6" t="n">
-        <v>5.9</v>
+        <v>1.77</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.74</v>
+        <v>6.4</v>
       </c>
       <c r="BF6" t="n">
-        <v>5.5</v>
+        <v>3.05</v>
       </c>
       <c r="BG6" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-24 03:05:41</t>
+          <t>2026-03-24 05:11:15</t>
         </is>
       </c>
     </row>
@@ -1727,7 +1727,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="G7" t="n">
         <v>4</v>
@@ -1742,7 +1742,7 @@
         <v>3.55</v>
       </c>
       <c r="K7" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L7" t="n">
         <v>1.37</v>
@@ -1754,13 +1754,13 @@
         <v>3.7</v>
       </c>
       <c r="O7" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="P7" t="n">
         <v>1.92</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="R7" t="n">
         <v>1.36</v>
@@ -1769,10 +1769,10 @@
         <v>3.2</v>
       </c>
       <c r="T7" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="U7" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="V7" t="n">
         <v>1.79</v>
@@ -1781,7 +1781,7 @@
         <v>1.34</v>
       </c>
       <c r="X7" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="Y7" t="n">
         <v>11</v>
@@ -1793,7 +1793,7 @@
         <v>28</v>
       </c>
       <c r="AB7" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AC7" t="n">
         <v>9</v>
@@ -1802,7 +1802,7 @@
         <v>11.5</v>
       </c>
       <c r="AE7" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AF7" t="n">
         <v>29</v>
@@ -1814,7 +1814,7 @@
         <v>18</v>
       </c>
       <c r="AI7" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AJ7" t="n">
         <v>75</v>
@@ -1826,71 +1826,71 @@
         <v>55</v>
       </c>
       <c r="AM7" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN7" t="n">
         <v>44</v>
       </c>
       <c r="AO7" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>12</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AW7" t="n">
         <v>19</v>
       </c>
-      <c r="AP7" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>5.3</v>
-      </c>
       <c r="AX7" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="AY7" t="n">
-        <v>4.9</v>
+        <v>13</v>
       </c>
       <c r="AZ7" t="n">
-        <v>5</v>
+        <v>14.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="BB7" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BC7" t="n">
-        <v>6.2</v>
+        <v>36</v>
       </c>
       <c r="BD7" t="n">
-        <v>6.2</v>
+        <v>42</v>
       </c>
       <c r="BE7" t="n">
-        <v>5.3</v>
+        <v>7.6</v>
       </c>
       <c r="BF7" t="n">
-        <v>6.2</v>
+        <v>34</v>
       </c>
       <c r="BG7" t="n">
-        <v>4.7</v>
+        <v>13</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-24 03:05:41</t>
+          <t>2026-03-24 05:11:15</t>
         </is>
       </c>
     </row>
@@ -1921,25 +1921,25 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="G8" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="H8" t="n">
         <v>2.38</v>
       </c>
       <c r="I8" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="J8" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K8" t="n">
         <v>3.7</v>
       </c>
       <c r="L8" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="M8" t="n">
         <v>1.06</v>
@@ -1948,7 +1948,7 @@
         <v>3.55</v>
       </c>
       <c r="O8" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="P8" t="n">
         <v>1.88</v>
@@ -1960,7 +1960,7 @@
         <v>1.36</v>
       </c>
       <c r="S8" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="T8" t="n">
         <v>1.73</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-24 03:05:41</t>
+          <t>2026-03-24 05:11:15</t>
         </is>
       </c>
     </row>
@@ -2118,13 +2118,13 @@
         <v>1.67</v>
       </c>
       <c r="G9" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="H9" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="I9" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="J9" t="n">
         <v>3.9</v>
@@ -2148,16 +2148,16 @@
         <v>2.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="R9" t="n">
         <v>1.41</v>
       </c>
       <c r="S9" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="T9" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="U9" t="n">
         <v>2.02</v>
@@ -2223,62 +2223,62 @@
         <v>90</v>
       </c>
       <c r="AP9" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="AQ9" t="n">
-        <v>17.5</v>
+        <v>6.2</v>
       </c>
       <c r="AR9" t="n">
-        <v>36</v>
+        <v>7.2</v>
       </c>
       <c r="AS9" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AT9" t="n">
-        <v>7.4</v>
+        <v>4.5</v>
       </c>
       <c r="AU9" t="n">
-        <v>8.199999999999999</v>
+        <v>4.6</v>
       </c>
       <c r="AV9" t="n">
-        <v>17</v>
+        <v>6.2</v>
       </c>
       <c r="AW9" t="n">
-        <v>55</v>
+        <v>7.8</v>
       </c>
       <c r="AX9" t="n">
-        <v>9</v>
+        <v>4.8</v>
       </c>
       <c r="AY9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA9" t="n">
         <v>7.8</v>
       </c>
-      <c r="AZ9" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>55</v>
-      </c>
       <c r="BB9" t="n">
-        <v>13</v>
+        <v>5.8</v>
       </c>
       <c r="BC9" t="n">
-        <v>14.5</v>
+        <v>5.9</v>
       </c>
       <c r="BD9" t="n">
-        <v>25</v>
+        <v>6.8</v>
       </c>
       <c r="BE9" t="n">
         <v>8</v>
       </c>
       <c r="BF9" t="n">
-        <v>7.4</v>
+        <v>4.6</v>
       </c>
       <c r="BG9" t="n">
         <v>7.8</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-24 03:05:41</t>
+          <t>2026-03-24 05:11:15</t>
         </is>
       </c>
     </row>
@@ -2312,7 +2312,7 @@
         <v>1.86</v>
       </c>
       <c r="G10" t="n">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="H10" t="n">
         <v>4.1</v>
@@ -2324,16 +2324,16 @@
         <v>3.7</v>
       </c>
       <c r="K10" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L10" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="M10" t="n">
         <v>1.06</v>
       </c>
       <c r="N10" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="O10" t="n">
         <v>1.28</v>
@@ -2351,16 +2351,16 @@
         <v>3.05</v>
       </c>
       <c r="T10" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="U10" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="V10" t="n">
         <v>1.27</v>
       </c>
       <c r="W10" t="n">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="X10" t="n">
         <v>20</v>
@@ -2384,7 +2384,7 @@
         <v>19</v>
       </c>
       <c r="AE10" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AF10" t="n">
         <v>15</v>
@@ -2393,7 +2393,7 @@
         <v>12.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI10" t="n">
         <v>60</v>
@@ -2405,7 +2405,7 @@
         <v>24</v>
       </c>
       <c r="AL10" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AM10" t="n">
         <v>110</v>
@@ -2417,40 +2417,40 @@
         <v>55</v>
       </c>
       <c r="AP10" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="AQ10" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AR10" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AS10" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AT10" t="n">
-        <v>8.6</v>
+        <v>3.5</v>
       </c>
       <c r="AU10" t="n">
-        <v>7.6</v>
+        <v>3.4</v>
       </c>
       <c r="AV10" t="n">
         <v>16</v>
       </c>
       <c r="AW10" t="n">
-        <v>44</v>
+        <v>4.6</v>
       </c>
       <c r="AX10" t="n">
-        <v>10.5</v>
+        <v>3.75</v>
       </c>
       <c r="AY10" t="n">
-        <v>9</v>
+        <v>3.55</v>
       </c>
       <c r="AZ10" t="n">
-        <v>15.5</v>
+        <v>13</v>
       </c>
       <c r="BA10" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BB10" t="n">
         <v>19</v>
@@ -2459,20 +2459,20 @@
         <v>17</v>
       </c>
       <c r="BD10" t="n">
-        <v>4.3</v>
+        <v>24</v>
       </c>
       <c r="BE10" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BF10" t="n">
-        <v>10.5</v>
+        <v>3.7</v>
       </c>
       <c r="BG10" t="n">
-        <v>4.4</v>
+        <v>40</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-24 03:05:41</t>
+          <t>2026-03-24 05:11:15</t>
         </is>
       </c>
     </row>
@@ -2509,7 +2509,7 @@
         <v>3.95</v>
       </c>
       <c r="H11" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="I11" t="n">
         <v>2.16</v>
@@ -2545,13 +2545,13 @@
         <v>2.7</v>
       </c>
       <c r="T11" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="U11" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="V11" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="W11" t="n">
         <v>1.36</v>
@@ -2602,7 +2602,7 @@
         <v>44</v>
       </c>
       <c r="AM11" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AN11" t="n">
         <v>34</v>
@@ -2614,10 +2614,10 @@
         <v>14.5</v>
       </c>
       <c r="AQ11" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AR11" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AS11" t="n">
         <v>21</v>
@@ -2626,13 +2626,13 @@
         <v>14</v>
       </c>
       <c r="AU11" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AV11" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="AW11" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AX11" t="n">
         <v>20</v>
@@ -2641,10 +2641,10 @@
         <v>13.5</v>
       </c>
       <c r="AZ11" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="BA11" t="n">
-        <v>22</v>
+        <v>5.7</v>
       </c>
       <c r="BB11" t="n">
         <v>6.4</v>
@@ -2656,17 +2656,17 @@
         <v>6</v>
       </c>
       <c r="BE11" t="n">
-        <v>50</v>
+        <v>6.4</v>
       </c>
       <c r="BF11" t="n">
-        <v>23</v>
+        <v>5.8</v>
       </c>
       <c r="BG11" t="n">
         <v>10</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-24 03:05:41</t>
+          <t>2026-03-24 05:11:15</t>
         </is>
       </c>
     </row>
@@ -2703,16 +2703,16 @@
         <v>3.55</v>
       </c>
       <c r="H12" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="I12" t="n">
         <v>2.9</v>
       </c>
       <c r="J12" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="K12" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="L12" t="n">
         <v>1.52</v>
@@ -2721,7 +2721,7 @@
         <v>1.12</v>
       </c>
       <c r="N12" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="O12" t="n">
         <v>1.54</v>
@@ -2730,7 +2730,7 @@
         <v>1.5</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="R12" t="n">
         <v>1.18</v>
@@ -2817,7 +2817,7 @@
         <v>1.99</v>
       </c>
       <c r="AT12" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AU12" t="n">
         <v>3.8</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-24 03:05:41</t>
+          <t>2026-03-24 05:11:15</t>
         </is>
       </c>
     </row>
@@ -2891,170 +2891,170 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.56</v>
+        <v>2.46</v>
       </c>
       <c r="G13" t="n">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="H13" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="I13" t="n">
-        <v>3.95</v>
+        <v>4.8</v>
       </c>
       <c r="J13" t="n">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="K13" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="L13" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="M13" t="n">
-        <v>1.21</v>
+        <v>1.01</v>
       </c>
       <c r="N13" t="n">
-        <v>1.95</v>
+        <v>1.77</v>
       </c>
       <c r="O13" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="P13" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="R13" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="S13" t="n">
-        <v>9.199999999999999</v>
+        <v>3.7</v>
       </c>
       <c r="T13" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="X13" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>160</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>29</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>140</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>19</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>50</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>260</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>60</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>65</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>160</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>610</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>110</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>310</v>
+      </c>
+      <c r="AP13" t="n">
         <v>2.72</v>
       </c>
-      <c r="U13" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="X13" t="n">
+      <c r="AQ13" t="n">
         <v>6.6</v>
       </c>
-      <c r="Y13" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>30</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>130</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>24</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>110</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>950</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>190</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>55</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>60</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>150</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>540</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>80</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>220</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>5</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>7</v>
-      </c>
       <c r="AR13" t="n">
-        <v>5.6</v>
+        <v>4.3</v>
       </c>
       <c r="AS13" t="n">
-        <v>6.6</v>
+        <v>4.8</v>
       </c>
       <c r="AT13" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="AU13" t="n">
-        <v>6.6</v>
+        <v>2.98</v>
       </c>
       <c r="AV13" t="n">
-        <v>5.4</v>
+        <v>16.5</v>
       </c>
       <c r="AW13" t="n">
-        <v>6.6</v>
+        <v>4.8</v>
       </c>
       <c r="AX13" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AY13" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AZ13" t="n">
-        <v>5.9</v>
+        <v>4.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>6.6</v>
+        <v>4.9</v>
       </c>
       <c r="BB13" t="n">
-        <v>6.2</v>
+        <v>4.6</v>
       </c>
       <c r="BC13" t="n">
-        <v>6.2</v>
+        <v>4.6</v>
       </c>
       <c r="BD13" t="n">
-        <v>6.6</v>
+        <v>4.8</v>
       </c>
       <c r="BE13" t="n">
-        <v>6.8</v>
+        <v>4.9</v>
       </c>
       <c r="BF13" t="n">
-        <v>6.4</v>
+        <v>4.7</v>
       </c>
       <c r="BG13" t="n">
-        <v>6.8</v>
+        <v>4.9</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-24 03:05:41</t>
+          <t>2026-03-24 05:11:15</t>
         </is>
       </c>
     </row>
@@ -3091,164 +3091,164 @@
         <v>1.81</v>
       </c>
       <c r="H14" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="I14" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="J14" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N14" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="W14" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AU14" t="n">
         <v>3.5</v>
       </c>
-      <c r="K14" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="L14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M14" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N14" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="O14" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="P14" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="S14" t="n">
-        <v>3</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W14" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>1.01</v>
-      </c>
       <c r="AV14" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.01</v>
+        <v>2.42</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>1.01</v>
+        <v>2.42</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BD14" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.01</v>
+        <v>2.2</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BG14" t="n">
-        <v>1.01</v>
+        <v>2.2</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-24 03:05:41</t>
+          <t>2026-03-24 05:11:15</t>
         </is>
       </c>
     </row>
@@ -3282,10 +3282,10 @@
         <v>1.56</v>
       </c>
       <c r="G15" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="H15" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="I15" t="n">
         <v>8.6</v>
@@ -3297,7 +3297,7 @@
         <v>4.6</v>
       </c>
       <c r="L15" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="M15" t="n">
         <v>1.07</v>
@@ -3309,7 +3309,7 @@
         <v>1.32</v>
       </c>
       <c r="P15" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="Q15" t="n">
         <v>1.85</v>
@@ -3330,7 +3330,7 @@
         <v>1.14</v>
       </c>
       <c r="W15" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="X15" t="n">
         <v>970</v>
@@ -3378,7 +3378,7 @@
         <v>48</v>
       </c>
       <c r="AM15" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AN15" t="n">
         <v>12.5</v>
@@ -3390,25 +3390,25 @@
         <v>10.5</v>
       </c>
       <c r="AQ15" t="n">
-        <v>14.5</v>
+        <v>3.7</v>
       </c>
       <c r="AR15" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AS15" t="n">
         <v>4.2</v>
       </c>
       <c r="AT15" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AU15" t="n">
         <v>7</v>
       </c>
       <c r="AV15" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="AW15" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AX15" t="n">
         <v>7</v>
@@ -3420,7 +3420,7 @@
         <v>3.75</v>
       </c>
       <c r="BA15" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BB15" t="n">
         <v>11.5</v>
@@ -3429,7 +3429,7 @@
         <v>13</v>
       </c>
       <c r="BD15" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BE15" t="n">
         <v>4.2</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-24 03:05:41</t>
+          <t>2026-03-24 05:11:15</t>
         </is>
       </c>
     </row>
@@ -3479,7 +3479,7 @@
         <v>8</v>
       </c>
       <c r="H16" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="I16" t="n">
         <v>1.71</v>
@@ -3488,7 +3488,7 @@
         <v>3.6</v>
       </c>
       <c r="K16" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="L16" t="n">
         <v>1.46</v>
@@ -3497,7 +3497,7 @@
         <v>1.09</v>
       </c>
       <c r="N16" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="O16" t="n">
         <v>1.41</v>
@@ -3515,10 +3515,10 @@
         <v>4.1</v>
       </c>
       <c r="T16" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="U16" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="V16" t="n">
         <v>2.4</v>
@@ -3584,25 +3584,25 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AQ16" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="AR16" t="n">
         <v>6.8</v>
       </c>
       <c r="AS16" t="n">
-        <v>12.5</v>
+        <v>5.7</v>
       </c>
       <c r="AT16" t="n">
         <v>14.5</v>
       </c>
       <c r="AU16" t="n">
-        <v>6.8</v>
+        <v>4.4</v>
       </c>
       <c r="AV16" t="n">
         <v>8</v>
       </c>
       <c r="AW16" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AX16" t="n">
         <v>7.6</v>
@@ -3614,7 +3614,7 @@
         <v>20</v>
       </c>
       <c r="BA16" t="n">
-        <v>36</v>
+        <v>7.4</v>
       </c>
       <c r="BB16" t="n">
         <v>8.4</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-24 03:05:41</t>
+          <t>2026-03-24 05:11:15</t>
         </is>
       </c>
     </row>
@@ -3670,13 +3670,13 @@
         <v>2.6</v>
       </c>
       <c r="G17" t="n">
-        <v>2.92</v>
+        <v>2.78</v>
       </c>
       <c r="H17" t="n">
         <v>2.72</v>
       </c>
       <c r="I17" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="J17" t="n">
         <v>3.35</v>
@@ -3718,7 +3718,7 @@
         <v>1.5</v>
       </c>
       <c r="W17" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="X17" t="n">
         <v>970</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-24 03:05:41</t>
+          <t>2026-03-24 05:11:15</t>
         </is>
       </c>
     </row>
@@ -3864,31 +3864,31 @@
         <v>1.58</v>
       </c>
       <c r="G18" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="H18" t="n">
         <v>7</v>
       </c>
       <c r="I18" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="J18" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="K18" t="n">
         <v>4.1</v>
       </c>
       <c r="L18" t="n">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="M18" t="n">
         <v>1.09</v>
       </c>
       <c r="N18" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="O18" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="P18" t="n">
         <v>1.72</v>
@@ -3912,7 +3912,7 @@
         <v>1.14</v>
       </c>
       <c r="W18" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="X18" t="n">
         <v>12</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-24 03:05:41</t>
+          <t>2026-03-24 05:11:15</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-25.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH18"/>
+  <dimension ref="A1:BH19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,13 +757,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="G2" t="n">
         <v>1000</v>
       </c>
       <c r="H2" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="I2" t="n">
         <v>1000</v>
@@ -781,13 +781,13 @@
         <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="O2" t="n">
         <v>1.02</v>
       </c>
       <c r="P2" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="Q2" t="n">
         <v>1.28</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-24 05:11:15</t>
+          <t>2026-03-24 07:16:59</t>
         </is>
       </c>
     </row>
@@ -951,13 +951,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="G3" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="H3" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="I3" t="n">
         <v>3.45</v>
@@ -972,31 +972,31 @@
         <v>1.58</v>
       </c>
       <c r="M3" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="N3" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="O3" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="P3" t="n">
         <v>1.38</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.1</v>
+        <v>2.96</v>
       </c>
       <c r="R3" t="n">
         <v>1.13</v>
       </c>
       <c r="S3" t="n">
-        <v>7</v>
+        <v>3.45</v>
       </c>
       <c r="T3" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="U3" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="V3" t="n">
         <v>1.4</v>
@@ -1008,34 +1008,34 @@
         <v>8</v>
       </c>
       <c r="Y3" t="n">
-        <v>9.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z3" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AA3" t="n">
         <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>9</v>
+        <v>7.8</v>
       </c>
       <c r="AC3" t="n">
-        <v>8.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD3" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>75</v>
+      </c>
+      <c r="AF3" t="n">
         <v>19</v>
       </c>
-      <c r="AE3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>21</v>
-      </c>
       <c r="AG3" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AH3" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AI3" t="n">
         <v>1000</v>
@@ -1044,7 +1044,7 @@
         <v>1000</v>
       </c>
       <c r="AK3" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AL3" t="n">
         <v>1000</v>
@@ -1059,62 +1059,62 @@
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AY3" t="n">
         <v>5.1</v>
       </c>
-      <c r="AQ3" t="n">
+      <c r="AZ3" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BC3" t="n">
         <v>6.6</v>
       </c>
-      <c r="AR3" t="n">
-        <v>14</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>13</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>20</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>4.3</v>
-      </c>
       <c r="BD3" t="n">
-        <v>4.5</v>
+        <v>7.2</v>
       </c>
       <c r="BE3" t="n">
-        <v>4.6</v>
+        <v>7.4</v>
       </c>
       <c r="BF3" t="n">
-        <v>4.4</v>
+        <v>7</v>
       </c>
       <c r="BG3" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-24 05:11:15</t>
+          <t>2026-03-24 07:16:59</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="G4" t="n">
         <v>2.92</v>
@@ -1169,7 +1169,7 @@
         <v>1.13</v>
       </c>
       <c r="N4" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="O4" t="n">
         <v>1.58</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-24 05:11:15</t>
+          <t>2026-03-24 07:16:59</t>
         </is>
       </c>
     </row>
@@ -1363,7 +1363,7 @@
         <v>1.12</v>
       </c>
       <c r="N5" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="O5" t="n">
         <v>1.53</v>
@@ -1372,7 +1372,7 @@
         <v>1.5</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="R5" t="n">
         <v>1.18</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-24 05:11:15</t>
+          <t>2026-03-24 07:16:59</t>
         </is>
       </c>
     </row>
@@ -1533,16 +1533,16 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="G6" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="H6" t="n">
         <v>2.24</v>
       </c>
       <c r="I6" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="J6" t="n">
         <v>3.7</v>
@@ -1563,13 +1563,13 @@
         <v>1.24</v>
       </c>
       <c r="P6" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.59</v>
+        <v>1.63</v>
       </c>
       <c r="R6" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="S6" t="n">
         <v>2.68</v>
@@ -1581,10 +1581,10 @@
         <v>2.18</v>
       </c>
       <c r="V6" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="W6" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="X6" t="n">
         <v>950</v>
@@ -1653,7 +1653,7 @@
         <v>4.8</v>
       </c>
       <c r="AT6" t="n">
-        <v>10.5</v>
+        <v>5</v>
       </c>
       <c r="AU6" t="n">
         <v>6.8</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-24 05:11:15</t>
+          <t>2026-03-24 07:16:59</t>
         </is>
       </c>
     </row>
@@ -1727,22 +1727,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="G7" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="H7" t="n">
         <v>2.14</v>
       </c>
       <c r="I7" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="J7" t="n">
         <v>3.55</v>
       </c>
       <c r="K7" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L7" t="n">
         <v>1.37</v>
@@ -1751,31 +1751,31 @@
         <v>1.06</v>
       </c>
       <c r="N7" t="n">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="O7" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="P7" t="n">
-        <v>1.92</v>
+        <v>2.02</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.89</v>
+        <v>1.79</v>
       </c>
       <c r="R7" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="S7" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="T7" t="n">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="U7" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="V7" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="W7" t="n">
         <v>1.34</v>
@@ -1790,107 +1790,107 @@
         <v>15</v>
       </c>
       <c r="AA7" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AB7" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AC7" t="n">
         <v>9</v>
       </c>
       <c r="AD7" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AE7" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AF7" t="n">
         <v>29</v>
       </c>
       <c r="AG7" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AH7" t="n">
         <v>18</v>
       </c>
       <c r="AI7" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AJ7" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AK7" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AL7" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AM7" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="AN7" t="n">
         <v>44</v>
       </c>
       <c r="AO7" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AP7" t="n">
         <v>11.5</v>
       </c>
       <c r="AQ7" t="n">
-        <v>8.4</v>
+        <v>4.9</v>
       </c>
       <c r="AR7" t="n">
-        <v>11.5</v>
+        <v>5.6</v>
       </c>
       <c r="AS7" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AT7" t="n">
-        <v>12</v>
+        <v>5.9</v>
       </c>
       <c r="AU7" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AV7" t="n">
-        <v>9.4</v>
+        <v>4.9</v>
       </c>
       <c r="AW7" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AX7" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AY7" t="n">
-        <v>13</v>
+        <v>5.7</v>
       </c>
       <c r="AZ7" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BA7" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BB7" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BC7" t="n">
         <v>7.4</v>
       </c>
-      <c r="BC7" t="n">
+      <c r="BD7" t="n">
         <v>36</v>
       </c>
-      <c r="BD7" t="n">
-        <v>42</v>
-      </c>
       <c r="BE7" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BF7" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BG7" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-24 05:11:15</t>
+          <t>2026-03-24 07:16:59</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
         <v>3</v>
       </c>
       <c r="G8" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="H8" t="n">
         <v>2.38</v>
@@ -1933,13 +1933,13 @@
         <v>2.6</v>
       </c>
       <c r="J8" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="K8" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L8" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="M8" t="n">
         <v>1.06</v>
@@ -1951,7 +1951,7 @@
         <v>1.3</v>
       </c>
       <c r="P8" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="Q8" t="n">
         <v>1.9</v>
@@ -1963,16 +1963,16 @@
         <v>3.25</v>
       </c>
       <c r="T8" t="n">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="U8" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="V8" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="W8" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="X8" t="n">
         <v>970</v>
@@ -2029,19 +2029,19 @@
         <v>1000</v>
       </c>
       <c r="AP8" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AR8" t="n">
         <v>5.4</v>
       </c>
-      <c r="AQ8" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>5.3</v>
-      </c>
       <c r="AS8" t="n">
-        <v>4.1</v>
+        <v>3.15</v>
       </c>
       <c r="AT8" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AU8" t="n">
         <v>6.2</v>
@@ -2050,41 +2050,41 @@
         <v>5</v>
       </c>
       <c r="AW8" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AX8" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AY8" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AZ8" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BA8" t="n">
-        <v>2.08</v>
+        <v>1.82</v>
       </c>
       <c r="BB8" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BC8" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="BD8" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BE8" t="n">
         <v>1.53</v>
       </c>
       <c r="BF8" t="n">
-        <v>4.5</v>
+        <v>3.45</v>
       </c>
       <c r="BG8" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-24 05:11:15</t>
+          <t>2026-03-24 07:16:59</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2118,7 @@
         <v>1.67</v>
       </c>
       <c r="G9" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="H9" t="n">
         <v>5.4</v>
@@ -2139,7 +2139,7 @@
         <v>1.05</v>
       </c>
       <c r="N9" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="O9" t="n">
         <v>1.26</v>
@@ -2154,22 +2154,22 @@
         <v>1.41</v>
       </c>
       <c r="S9" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="T9" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="U9" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="V9" t="n">
         <v>1.2</v>
       </c>
       <c r="W9" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="X9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Y9" t="n">
         <v>22</v>
@@ -2202,7 +2202,7 @@
         <v>21</v>
       </c>
       <c r="AI9" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AJ9" t="n">
         <v>18</v>
@@ -2211,7 +2211,7 @@
         <v>18.5</v>
       </c>
       <c r="AL9" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AM9" t="n">
         <v>120</v>
@@ -2229,19 +2229,19 @@
         <v>6.2</v>
       </c>
       <c r="AR9" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AS9" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT9" t="n">
-        <v>4.5</v>
+        <v>7.8</v>
       </c>
       <c r="AU9" t="n">
         <v>4.6</v>
       </c>
       <c r="AV9" t="n">
-        <v>6.2</v>
+        <v>18.5</v>
       </c>
       <c r="AW9" t="n">
         <v>7.8</v>
@@ -2253,10 +2253,10 @@
         <v>4.7</v>
       </c>
       <c r="AZ9" t="n">
-        <v>6</v>
+        <v>16.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BB9" t="n">
         <v>5.8</v>
@@ -2265,7 +2265,7 @@
         <v>5.9</v>
       </c>
       <c r="BD9" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BE9" t="n">
         <v>8</v>
@@ -2274,11 +2274,11 @@
         <v>4.6</v>
       </c>
       <c r="BG9" t="n">
-        <v>7.8</v>
+        <v>60</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-24 05:11:15</t>
+          <t>2026-03-24 07:16:59</t>
         </is>
       </c>
     </row>
@@ -2309,61 +2309,61 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="G10" t="n">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="H10" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="I10" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="J10" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="K10" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="L10" t="n">
-        <v>1.3</v>
+        <v>1.41</v>
       </c>
       <c r="M10" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N10" t="n">
-        <v>4</v>
+        <v>3.55</v>
       </c>
       <c r="O10" t="n">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="P10" t="n">
-        <v>2.02</v>
+        <v>1.88</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="R10" t="n">
-        <v>1.41</v>
+        <v>1.34</v>
       </c>
       <c r="S10" t="n">
-        <v>3.05</v>
+        <v>3.55</v>
       </c>
       <c r="T10" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="U10" t="n">
-        <v>2.14</v>
+        <v>2.04</v>
       </c>
       <c r="V10" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="W10" t="n">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="X10" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="Y10" t="n">
         <v>20</v>
@@ -2375,16 +2375,16 @@
         <v>110</v>
       </c>
       <c r="AB10" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD10" t="n">
         <v>19</v>
       </c>
       <c r="AE10" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AF10" t="n">
         <v>15</v>
@@ -2396,7 +2396,7 @@
         <v>21</v>
       </c>
       <c r="AI10" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AJ10" t="n">
         <v>26</v>
@@ -2405,7 +2405,7 @@
         <v>24</v>
       </c>
       <c r="AL10" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AM10" t="n">
         <v>110</v>
@@ -2414,43 +2414,43 @@
         <v>14.5</v>
       </c>
       <c r="AO10" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="AP10" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="AQ10" t="n">
         <v>12.5</v>
       </c>
       <c r="AR10" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="AS10" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="AT10" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AU10" t="n">
         <v>3.5</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>3.4</v>
       </c>
       <c r="AV10" t="n">
         <v>16</v>
       </c>
       <c r="AW10" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="AX10" t="n">
-        <v>3.75</v>
+        <v>10.5</v>
       </c>
       <c r="AY10" t="n">
-        <v>3.55</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ10" t="n">
         <v>13</v>
       </c>
       <c r="BA10" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="BB10" t="n">
         <v>19</v>
@@ -2462,17 +2462,17 @@
         <v>24</v>
       </c>
       <c r="BE10" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="BF10" t="n">
-        <v>3.7</v>
+        <v>12.5</v>
       </c>
       <c r="BG10" t="n">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-24 05:11:15</t>
+          <t>2026-03-24 07:16:59</t>
         </is>
       </c>
     </row>
@@ -2503,13 +2503,13 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="G11" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="H11" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="I11" t="n">
         <v>2.16</v>
@@ -2551,10 +2551,10 @@
         <v>2.3</v>
       </c>
       <c r="V11" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="W11" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="X11" t="n">
         <v>24</v>
@@ -2572,7 +2572,7 @@
         <v>18.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD11" t="n">
         <v>13</v>
@@ -2614,10 +2614,10 @@
         <v>14.5</v>
       </c>
       <c r="AQ11" t="n">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR11" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AS11" t="n">
         <v>21</v>
@@ -2635,7 +2635,7 @@
         <v>14.5</v>
       </c>
       <c r="AX11" t="n">
-        <v>20</v>
+        <v>5.8</v>
       </c>
       <c r="AY11" t="n">
         <v>13.5</v>
@@ -2644,29 +2644,29 @@
         <v>14</v>
       </c>
       <c r="BA11" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BB11" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BC11" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="BD11" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BF11" t="n">
         <v>6</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>5.8</v>
       </c>
       <c r="BG11" t="n">
         <v>10</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-24 05:11:15</t>
+          <t>2026-03-24 07:16:59</t>
         </is>
       </c>
     </row>
@@ -2703,16 +2703,16 @@
         <v>3.55</v>
       </c>
       <c r="H12" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="I12" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="J12" t="n">
         <v>2.84</v>
       </c>
       <c r="K12" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="L12" t="n">
         <v>1.52</v>
@@ -2721,7 +2721,7 @@
         <v>1.12</v>
       </c>
       <c r="N12" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="O12" t="n">
         <v>1.54</v>
@@ -2745,7 +2745,7 @@
         <v>1.76</v>
       </c>
       <c r="V12" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="W12" t="n">
         <v>1.39</v>
@@ -2811,40 +2811,40 @@
         <v>6.4</v>
       </c>
       <c r="AR12" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AS12" t="n">
-        <v>1.99</v>
+        <v>1.77</v>
       </c>
       <c r="AT12" t="n">
         <v>7.2</v>
       </c>
       <c r="AU12" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="AV12" t="n">
         <v>10</v>
       </c>
       <c r="AW12" t="n">
-        <v>3.8</v>
+        <v>2.72</v>
       </c>
       <c r="AX12" t="n">
-        <v>6</v>
+        <v>15.5</v>
       </c>
       <c r="AY12" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AZ12" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="BA12" t="n">
         <v>1.79</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.78</v>
+        <v>7.6</v>
       </c>
       <c r="BC12" t="n">
-        <v>2</v>
+        <v>7.4</v>
       </c>
       <c r="BD12" t="n">
         <v>1.79</v>
@@ -2853,14 +2853,14 @@
         <v>1.61</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.79</v>
+        <v>2.8</v>
       </c>
       <c r="BG12" t="n">
-        <v>1.99</v>
+        <v>1.77</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-24 05:11:15</t>
+          <t>2026-03-24 07:16:59</t>
         </is>
       </c>
     </row>
@@ -2891,85 +2891,85 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="G13" t="n">
-        <v>2.88</v>
+        <v>2.66</v>
       </c>
       <c r="H13" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="I13" t="n">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="J13" t="n">
-        <v>2.6</v>
+        <v>2.74</v>
       </c>
       <c r="K13" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="L13" t="n">
         <v>1.79</v>
       </c>
       <c r="M13" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="N13" t="n">
-        <v>1.77</v>
+        <v>1.97</v>
       </c>
       <c r="O13" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="P13" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="R13" t="n">
         <v>1.08</v>
       </c>
       <c r="S13" t="n">
-        <v>3.7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>2.42</v>
+        <v>2.84</v>
       </c>
       <c r="U13" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="V13" t="n">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="W13" t="n">
-        <v>1.54</v>
+        <v>1.6</v>
       </c>
       <c r="X13" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="Y13" t="n">
-        <v>11</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z13" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AA13" t="n">
-        <v>160</v>
+        <v>130</v>
       </c>
       <c r="AB13" t="n">
-        <v>7.4</v>
+        <v>6.2</v>
       </c>
       <c r="AC13" t="n">
         <v>7.4</v>
       </c>
       <c r="AD13" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AE13" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AF13" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AG13" t="n">
         <v>19</v>
@@ -2978,10 +2978,10 @@
         <v>50</v>
       </c>
       <c r="AI13" t="n">
-        <v>260</v>
+        <v>230</v>
       </c>
       <c r="AJ13" t="n">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="AK13" t="n">
         <v>65</v>
@@ -2993,34 +2993,34 @@
         <v>610</v>
       </c>
       <c r="AN13" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="AO13" t="n">
-        <v>310</v>
+        <v>250</v>
       </c>
       <c r="AP13" t="n">
-        <v>2.72</v>
+        <v>4.9</v>
       </c>
       <c r="AQ13" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>38</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AU13" t="n">
         <v>6.6</v>
       </c>
-      <c r="AR13" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>2.98</v>
-      </c>
       <c r="AV13" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AW13" t="n">
-        <v>4.8</v>
+        <v>38</v>
       </c>
       <c r="AX13" t="n">
         <v>10.5</v>
@@ -3029,32 +3029,32 @@
         <v>13</v>
       </c>
       <c r="AZ13" t="n">
-        <v>4.5</v>
+        <v>30</v>
       </c>
       <c r="BA13" t="n">
-        <v>4.9</v>
+        <v>48</v>
       </c>
       <c r="BB13" t="n">
-        <v>4.6</v>
+        <v>23</v>
       </c>
       <c r="BC13" t="n">
-        <v>4.6</v>
+        <v>28</v>
       </c>
       <c r="BD13" t="n">
-        <v>4.8</v>
+        <v>44</v>
       </c>
       <c r="BE13" t="n">
-        <v>4.9</v>
+        <v>55</v>
       </c>
       <c r="BF13" t="n">
-        <v>4.7</v>
+        <v>32</v>
       </c>
       <c r="BG13" t="n">
-        <v>4.9</v>
+        <v>46</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-24 05:11:15</t>
+          <t>2026-03-24 07:16:59</t>
         </is>
       </c>
     </row>
@@ -3071,72 +3071,72 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Real Soacha Cundinamarca FC</t>
+          <t>Barranquilla</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Atletico FC Cali</t>
+          <t>Leones FC</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.52</v>
+        <v>1.04</v>
       </c>
       <c r="G14" t="n">
-        <v>1.81</v>
+        <v>1000</v>
       </c>
       <c r="H14" t="n">
-        <v>5.7</v>
+        <v>1.04</v>
       </c>
       <c r="I14" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="J14" t="n">
-        <v>3.2</v>
+        <v>1.02</v>
       </c>
       <c r="K14" t="n">
-        <v>4.9</v>
+        <v>1000</v>
       </c>
       <c r="L14" t="n">
-        <v>1.42</v>
+        <v>1.01</v>
       </c>
       <c r="M14" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="N14" t="n">
-        <v>2.74</v>
+        <v>1.25</v>
       </c>
       <c r="O14" t="n">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="P14" t="n">
-        <v>1.54</v>
+        <v>1.24</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.02</v>
+        <v>1.3</v>
       </c>
       <c r="R14" t="n">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="S14" t="n">
-        <v>1.05</v>
+        <v>1.3</v>
       </c>
       <c r="T14" t="n">
-        <v>2.16</v>
+        <v>1.01</v>
       </c>
       <c r="U14" t="n">
-        <v>1.69</v>
+        <v>1.01</v>
       </c>
       <c r="V14" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="W14" t="n">
-        <v>2.24</v>
+        <v>1.01</v>
       </c>
       <c r="X14" t="n">
         <v>1000</v>
@@ -3193,69 +3193,69 @@
         <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>3.75</v>
+        <v>1.03</v>
       </c>
       <c r="AQ14" t="n">
-        <v>4.2</v>
+        <v>1.03</v>
       </c>
       <c r="AR14" t="n">
-        <v>4.9</v>
+        <v>1.03</v>
       </c>
       <c r="AS14" t="n">
-        <v>2.2</v>
+        <v>1.03</v>
       </c>
       <c r="AT14" t="n">
-        <v>3.05</v>
+        <v>1.03</v>
       </c>
       <c r="AU14" t="n">
-        <v>3.5</v>
+        <v>1.03</v>
       </c>
       <c r="AV14" t="n">
-        <v>4.6</v>
+        <v>1.03</v>
       </c>
       <c r="AW14" t="n">
-        <v>2.42</v>
+        <v>1.03</v>
       </c>
       <c r="AX14" t="n">
-        <v>3.45</v>
+        <v>1.03</v>
       </c>
       <c r="AY14" t="n">
-        <v>3.65</v>
+        <v>1.03</v>
       </c>
       <c r="AZ14" t="n">
-        <v>4.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA14" t="n">
-        <v>2.42</v>
+        <v>1.03</v>
       </c>
       <c r="BB14" t="n">
-        <v>4.1</v>
+        <v>1.03</v>
       </c>
       <c r="BC14" t="n">
-        <v>4.3</v>
+        <v>1.03</v>
       </c>
       <c r="BD14" t="n">
-        <v>4.8</v>
+        <v>1.03</v>
       </c>
       <c r="BE14" t="n">
-        <v>2.2</v>
+        <v>1.03</v>
       </c>
       <c r="BF14" t="n">
-        <v>3.95</v>
+        <v>1.01</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.2</v>
+        <v>1.01</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-24 05:11:15</t>
+          <t>2026-03-24 07:16:59</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>US United Soccer League</t>
+          <t>Colombian Primera B</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3270,186 +3270,186 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Lexington SC</t>
+          <t>Real Soacha Cundinamarca FC</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Atletico FC Cali</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="G15" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="H15" t="n">
         <v>6</v>
       </c>
       <c r="I15" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J15" t="n">
-        <v>3.85</v>
+        <v>3.25</v>
       </c>
       <c r="K15" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N15" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="W15" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AV15" t="n">
         <v>4.6</v>
       </c>
-      <c r="L15" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="M15" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N15" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="O15" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="P15" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S15" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="W15" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="X15" t="n">
-        <v>970</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>950</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>70</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>950</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>130</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>950</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>120</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>970</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>22</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>48</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>170</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>180</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AR15" t="n">
+      <c r="AW15" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="BB15" t="n">
         <v>4.1</v>
       </c>
-      <c r="AS15" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>7</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>11.5</v>
-      </c>
       <c r="BC15" t="n">
-        <v>13</v>
+        <v>4.3</v>
       </c>
       <c r="BD15" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="BE15" t="n">
-        <v>4.2</v>
+        <v>2.2</v>
       </c>
       <c r="BF15" t="n">
-        <v>7.6</v>
+        <v>3.95</v>
       </c>
       <c r="BG15" t="n">
-        <v>4.2</v>
+        <v>2.2</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-24 05:11:15</t>
+          <t>2026-03-24 07:16:59</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>US United Soccer League</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3459,191 +3459,191 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Boston River</t>
+          <t>Lexington SC</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Penarol</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>6.8</v>
+        <v>1.56</v>
       </c>
       <c r="G16" t="n">
-        <v>8</v>
+        <v>1.75</v>
       </c>
       <c r="H16" t="n">
-        <v>1.6</v>
+        <v>6</v>
       </c>
       <c r="I16" t="n">
-        <v>1.71</v>
+        <v>8.6</v>
       </c>
       <c r="J16" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="K16" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N16" t="n">
         <v>3.6</v>
       </c>
-      <c r="K16" t="n">
+      <c r="O16" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="W16" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="X16" t="n">
+        <v>970</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>950</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>70</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>950</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>130</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>950</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>120</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>970</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>22</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>170</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>180</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD16" t="n">
         <v>4</v>
       </c>
-      <c r="L16" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="M16" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="N16" t="n">
-        <v>3</v>
-      </c>
-      <c r="O16" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="P16" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="S16" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="V16" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X16" t="n">
-        <v>13</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>9</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>17</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>20</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>11</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>24</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>65</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>30</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>28</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>50</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>300</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>160</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>160</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>230</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>260</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>14</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>8</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>17</v>
-      </c>
-      <c r="AX16" t="n">
+      <c r="BE16" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BF16" t="n">
         <v>7.6</v>
       </c>
-      <c r="AY16" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>20</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>8.4</v>
-      </c>
       <c r="BG16" t="n">
-        <v>10</v>
+        <v>4.2</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-24 05:11:15</t>
+          <t>2026-03-24 07:16:59</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>US United Soccer League</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3658,186 +3658,186 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Sporting Club Jacksonville</t>
+          <t>Boston River</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Miami FC</t>
+          <t>Penarol</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.6</v>
+        <v>6.8</v>
       </c>
       <c r="G17" t="n">
-        <v>2.78</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H17" t="n">
-        <v>2.72</v>
+        <v>1.6</v>
       </c>
       <c r="I17" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K17" t="n">
+        <v>4</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N17" t="n">
         <v>3</v>
       </c>
-      <c r="J17" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="K17" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="L17" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="M17" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N17" t="n">
-        <v>3.7</v>
-      </c>
       <c r="O17" t="n">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="P17" t="n">
-        <v>1.91</v>
+        <v>1.7</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.91</v>
+        <v>2.18</v>
       </c>
       <c r="R17" t="n">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="S17" t="n">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="T17" t="n">
-        <v>1.7</v>
+        <v>2.12</v>
       </c>
       <c r="U17" t="n">
-        <v>2.14</v>
+        <v>1.72</v>
       </c>
       <c r="V17" t="n">
-        <v>1.5</v>
+        <v>2.52</v>
       </c>
       <c r="W17" t="n">
-        <v>1.56</v>
+        <v>1.14</v>
       </c>
       <c r="X17" t="n">
-        <v>970</v>
+        <v>13</v>
       </c>
       <c r="Y17" t="n">
-        <v>970</v>
+        <v>6.8</v>
       </c>
       <c r="Z17" t="n">
-        <v>970</v>
+        <v>9</v>
       </c>
       <c r="AA17" t="n">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="AB17" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="AC17" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD17" t="n">
-        <v>970</v>
+        <v>11</v>
       </c>
       <c r="AE17" t="n">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="AF17" t="n">
-        <v>21</v>
+        <v>65</v>
       </c>
       <c r="AG17" t="n">
-        <v>970</v>
+        <v>30</v>
       </c>
       <c r="AH17" t="n">
-        <v>970</v>
+        <v>28</v>
       </c>
       <c r="AI17" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AJ17" t="n">
-        <v>48</v>
+        <v>300</v>
       </c>
       <c r="AK17" t="n">
-        <v>34</v>
+        <v>160</v>
       </c>
       <c r="AL17" t="n">
-        <v>46</v>
+        <v>160</v>
       </c>
       <c r="AM17" t="n">
-        <v>100</v>
+        <v>230</v>
       </c>
       <c r="AN17" t="n">
-        <v>28</v>
+        <v>260</v>
       </c>
       <c r="AO17" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="AP17" t="n">
-        <v>11.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ17" t="n">
-        <v>9.6</v>
+        <v>5.6</v>
       </c>
       <c r="AR17" t="n">
-        <v>4.6</v>
+        <v>6.8</v>
       </c>
       <c r="AS17" t="n">
-        <v>5.1</v>
+        <v>13.5</v>
       </c>
       <c r="AT17" t="n">
-        <v>9.199999999999999</v>
+        <v>14.5</v>
       </c>
       <c r="AU17" t="n">
-        <v>6.2</v>
+        <v>4.5</v>
       </c>
       <c r="AV17" t="n">
+        <v>8</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>17</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BG17" t="n">
         <v>10</v>
       </c>
-      <c r="AW17" t="n">
-        <v>5</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BG17" t="n">
-        <v>4.8</v>
-      </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-24 05:11:15</t>
+          <t>2026-03-24 07:16:59</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>US United Soccer League</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3847,184 +3847,378 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>22:00:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>America de Cali S.A</t>
+          <t>Sporting Club Jacksonville</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Llaneros FC</t>
+          <t>Miami FC</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.58</v>
+        <v>2.6</v>
       </c>
       <c r="G18" t="n">
-        <v>1.65</v>
+        <v>2.82</v>
       </c>
       <c r="H18" t="n">
-        <v>7</v>
+        <v>2.72</v>
       </c>
       <c r="I18" t="n">
-        <v>8</v>
+        <v>3.05</v>
       </c>
       <c r="J18" t="n">
-        <v>4</v>
+        <v>3.35</v>
       </c>
       <c r="K18" t="n">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="L18" t="n">
-        <v>1.46</v>
+        <v>1.35</v>
       </c>
       <c r="M18" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="N18" t="n">
-        <v>3.05</v>
+        <v>3.7</v>
       </c>
       <c r="O18" t="n">
-        <v>1.41</v>
+        <v>1.31</v>
       </c>
       <c r="P18" t="n">
-        <v>1.72</v>
+        <v>1.91</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.22</v>
+        <v>1.91</v>
       </c>
       <c r="R18" t="n">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="S18" t="n">
-        <v>4.1</v>
+        <v>3.3</v>
       </c>
       <c r="T18" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="U18" t="n">
-        <v>1.73</v>
+        <v>2.14</v>
       </c>
       <c r="V18" t="n">
-        <v>1.14</v>
+        <v>1.5</v>
       </c>
       <c r="W18" t="n">
-        <v>2.54</v>
+        <v>1.54</v>
       </c>
       <c r="X18" t="n">
-        <v>12</v>
+        <v>970</v>
       </c>
       <c r="Y18" t="n">
-        <v>20</v>
+        <v>970</v>
       </c>
       <c r="Z18" t="n">
-        <v>65</v>
+        <v>970</v>
       </c>
       <c r="AA18" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AB18" t="n">
-        <v>6.8</v>
+        <v>13</v>
       </c>
       <c r="AC18" t="n">
         <v>9</v>
       </c>
       <c r="AD18" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>36</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>970</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>48</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>48</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>28</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>28</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BH18" t="inlineStr">
+        <is>
+          <t>2026-03-24 07:16:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Colombian Primera A</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>22:00:00</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>America de Cali S.A</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Llaneros FC</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="H19" t="n">
+        <v>7</v>
+      </c>
+      <c r="I19" t="n">
+        <v>8</v>
+      </c>
+      <c r="J19" t="n">
+        <v>4</v>
+      </c>
+      <c r="K19" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N19" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S19" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="W19" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="X19" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>65</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD19" t="n">
         <v>950</v>
       </c>
-      <c r="AE18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AG18" t="n">
+      <c r="AE19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AG19" t="n">
         <v>10.5</v>
       </c>
-      <c r="AH18" t="n">
+      <c r="AH19" t="n">
         <v>950</v>
       </c>
-      <c r="AI18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>16</v>
-      </c>
-      <c r="AK18" t="n">
+      <c r="AI19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>970</v>
+      </c>
+      <c r="AK19" t="n">
         <v>21</v>
       </c>
-      <c r="AL18" t="n">
+      <c r="AL19" t="n">
         <v>50</v>
       </c>
-      <c r="AM18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN18" t="n">
+      <c r="AM19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN19" t="n">
         <v>14.5</v>
       </c>
-      <c r="AO18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP18" t="n">
+      <c r="AO19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP19" t="n">
         <v>10</v>
       </c>
-      <c r="AQ18" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AR18" t="n">
+      <c r="AQ19" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AY19" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AS18" t="n">
-        <v>10</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>10</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>10</v>
-      </c>
-      <c r="BB18" t="n">
+      <c r="AZ19" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BB19" t="n">
         <v>6.4</v>
       </c>
-      <c r="BC18" t="n">
-        <v>7</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>10</v>
-      </c>
-      <c r="BF18" t="n">
+      <c r="BC19" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>42</v>
+      </c>
+      <c r="BE19" t="n">
         <v>10.5</v>
       </c>
-      <c r="BG18" t="n">
-        <v>10</v>
-      </c>
-      <c r="BH18" t="inlineStr">
-        <is>
-          <t>2026-03-24 05:11:15</t>
+      <c r="BF19" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>2026-03-24 07:16:59</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-25.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH19"/>
+  <dimension ref="A1:BH21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -743,36 +743,36 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Ankaragucu</t>
+          <t>Menemen Belediyespor</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Ankaraspor</t>
+          <t>Mardin Buyuksehir Belediye</t>
         </is>
       </c>
       <c r="F2" t="n">
         <v>1.05</v>
       </c>
       <c r="G2" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="H2" t="n">
         <v>1.05</v>
       </c>
       <c r="I2" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="J2" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="K2" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L2" t="n">
         <v>1.01</v>
@@ -781,28 +781,28 @@
         <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>1.33</v>
+        <v>1.08</v>
       </c>
       <c r="O2" t="n">
         <v>1.02</v>
       </c>
       <c r="P2" t="n">
-        <v>1.32</v>
+        <v>1.07</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.28</v>
+        <v>1.02</v>
       </c>
       <c r="R2" t="n">
-        <v>1.18</v>
+        <v>1.07</v>
       </c>
       <c r="S2" t="n">
-        <v>1.05</v>
+        <v>1.31</v>
       </c>
       <c r="T2" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="U2" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="V2" t="n">
         <v>1.02</v>
@@ -865,52 +865,52 @@
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF2" t="n">
         <v>1.01</v>
@@ -920,14 +920,14 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-24 07:16:59</t>
+          <t>2026-03-24 09:23:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Algerian Ligue 1</t>
+          <t>Turkish 2 Lig</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -937,102 +937,102 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>13:45:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Belouizdad</t>
+          <t>Altinordu</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Kastamonuspor</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.8</v>
+        <v>1.09</v>
       </c>
       <c r="G3" t="n">
-        <v>3.25</v>
+        <v>150</v>
       </c>
       <c r="H3" t="n">
-        <v>2.96</v>
+        <v>1.05</v>
       </c>
       <c r="I3" t="n">
-        <v>3.45</v>
+        <v>210</v>
       </c>
       <c r="J3" t="n">
-        <v>2.64</v>
+        <v>1.09</v>
       </c>
       <c r="K3" t="n">
-        <v>3.05</v>
+        <v>950</v>
       </c>
       <c r="L3" t="n">
-        <v>1.58</v>
+        <v>1.01</v>
       </c>
       <c r="M3" t="n">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>2.12</v>
+        <v>1.15</v>
       </c>
       <c r="O3" t="n">
-        <v>1.69</v>
+        <v>1.02</v>
       </c>
       <c r="P3" t="n">
-        <v>1.38</v>
+        <v>1.15</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.96</v>
+        <v>1.01</v>
       </c>
       <c r="R3" t="n">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="S3" t="n">
-        <v>3.45</v>
+        <v>1.02</v>
       </c>
       <c r="T3" t="n">
-        <v>2.28</v>
+        <v>1.01</v>
       </c>
       <c r="U3" t="n">
-        <v>1.6</v>
+        <v>1.01</v>
       </c>
       <c r="V3" t="n">
-        <v>1.4</v>
+        <v>1.02</v>
       </c>
       <c r="W3" t="n">
-        <v>1.46</v>
+        <v>1.02</v>
       </c>
       <c r="X3" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="Y3" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="Z3" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AA3" t="n">
         <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="AC3" t="n">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="AD3" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AE3" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AF3" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AG3" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AH3" t="n">
         <v>1000</v>
@@ -1059,69 +1059,69 @@
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>3.9</v>
+        <v>1.03</v>
       </c>
       <c r="AQ3" t="n">
-        <v>3.95</v>
+        <v>1.03</v>
       </c>
       <c r="AR3" t="n">
-        <v>5.5</v>
+        <v>1.03</v>
       </c>
       <c r="AS3" t="n">
-        <v>6.8</v>
+        <v>1.03</v>
       </c>
       <c r="AT3" t="n">
-        <v>3.85</v>
+        <v>1.03</v>
       </c>
       <c r="AU3" t="n">
-        <v>3.7</v>
+        <v>1.03</v>
       </c>
       <c r="AV3" t="n">
-        <v>5.2</v>
+        <v>1.03</v>
       </c>
       <c r="AW3" t="n">
-        <v>6.8</v>
+        <v>1.03</v>
       </c>
       <c r="AX3" t="n">
-        <v>5.4</v>
+        <v>1.03</v>
       </c>
       <c r="AY3" t="n">
-        <v>5.1</v>
+        <v>1.03</v>
       </c>
       <c r="AZ3" t="n">
-        <v>6</v>
+        <v>1.03</v>
       </c>
       <c r="BA3" t="n">
-        <v>7.2</v>
+        <v>1.03</v>
       </c>
       <c r="BB3" t="n">
-        <v>6.8</v>
+        <v>1.03</v>
       </c>
       <c r="BC3" t="n">
-        <v>6.6</v>
+        <v>1.03</v>
       </c>
       <c r="BD3" t="n">
-        <v>7.2</v>
+        <v>1.03</v>
       </c>
       <c r="BE3" t="n">
-        <v>7.4</v>
+        <v>1.03</v>
       </c>
       <c r="BF3" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BG3" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-24 07:16:59</t>
+          <t>2026-03-24 09:23:00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Turkish 2 Lig</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1131,105 +1131,105 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Albion FC</t>
+          <t>Ankaragucu</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Wanderers (Uru)</t>
+          <t>Ankaraspor</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.6</v>
+        <v>1.05</v>
       </c>
       <c r="G4" t="n">
-        <v>2.92</v>
+        <v>60</v>
       </c>
       <c r="H4" t="n">
-        <v>3.1</v>
+        <v>1.09</v>
       </c>
       <c r="I4" t="n">
-        <v>3.55</v>
+        <v>1000</v>
       </c>
       <c r="J4" t="n">
-        <v>2.84</v>
+        <v>1.1</v>
       </c>
       <c r="K4" t="n">
-        <v>3.2</v>
+        <v>950</v>
       </c>
       <c r="L4" t="n">
-        <v>1.52</v>
+        <v>1.01</v>
       </c>
       <c r="M4" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="N4" t="n">
-        <v>2.46</v>
+        <v>1.1</v>
       </c>
       <c r="O4" t="n">
-        <v>1.58</v>
+        <v>1.06</v>
       </c>
       <c r="P4" t="n">
-        <v>1.5</v>
+        <v>1.24</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.62</v>
+        <v>1.27</v>
       </c>
       <c r="R4" t="n">
         <v>1.18</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>1.26</v>
       </c>
       <c r="T4" t="n">
-        <v>2.12</v>
+        <v>1.11</v>
       </c>
       <c r="U4" t="n">
-        <v>1.76</v>
+        <v>1.11</v>
       </c>
       <c r="V4" t="n">
-        <v>1.39</v>
+        <v>1.02</v>
       </c>
       <c r="W4" t="n">
-        <v>1.52</v>
+        <v>1.02</v>
       </c>
       <c r="X4" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="Y4" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Z4" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AA4" t="n">
         <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AC4" t="n">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="AD4" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AE4" t="n">
         <v>1000</v>
       </c>
       <c r="AF4" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AG4" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AH4" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AI4" t="n">
         <v>1000</v>
@@ -1253,62 +1253,62 @@
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AQ4" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AR4" t="n">
-        <v>2.56</v>
+        <v>1.01</v>
       </c>
       <c r="AS4" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="AT4" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AU4" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="AV4" t="n">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="AW4" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AX4" t="n">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="AY4" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AZ4" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BA4" t="n">
-        <v>2.52</v>
+        <v>1.01</v>
       </c>
       <c r="BB4" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BC4" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BD4" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BE4" t="n">
-        <v>2.18</v>
+        <v>1.01</v>
       </c>
       <c r="BF4" t="n">
-        <v>2.76</v>
+        <v>1.01</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.8</v>
+        <v>1.01</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-24 07:16:59</t>
+          <t>2026-03-24 09:23:00</t>
         </is>
       </c>
     </row>
@@ -1325,191 +1325,191 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>13:45:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Belouizdad</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.89</v>
+        <v>2.8</v>
       </c>
       <c r="G5" t="n">
-        <v>2.12</v>
+        <v>3.2</v>
       </c>
       <c r="H5" t="n">
-        <v>4.2</v>
+        <v>2.96</v>
       </c>
       <c r="I5" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="J5" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="K5" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="N5" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="S5" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="X5" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>20</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>75</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>19</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>14</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BC5" t="n">
         <v>6.6</v>
       </c>
-      <c r="J5" t="n">
-        <v>3</v>
-      </c>
-      <c r="K5" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="N5" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="P5" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S5" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="X5" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>1.7</v>
-      </c>
       <c r="BD5" t="n">
-        <v>2.26</v>
+        <v>7.2</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.5</v>
+        <v>7.4</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.69</v>
+        <v>7</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.49</v>
+        <v>7</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-24 07:16:59</t>
+          <t>2026-03-24 09:23:00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>English National League</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1519,84 +1519,84 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>16:45:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Morecambe</t>
+          <t>Albion FC</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Hartlepool</t>
+          <t>Wanderers (Uru)</t>
         </is>
       </c>
       <c r="F6" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="G6" t="n">
         <v>2.98</v>
       </c>
-      <c r="G6" t="n">
-        <v>3.35</v>
-      </c>
       <c r="H6" t="n">
-        <v>2.24</v>
+        <v>3.1</v>
       </c>
       <c r="I6" t="n">
-        <v>2.44</v>
+        <v>3.6</v>
       </c>
       <c r="J6" t="n">
-        <v>3.7</v>
+        <v>2.66</v>
       </c>
       <c r="K6" t="n">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="L6" t="n">
-        <v>1.28</v>
+        <v>1.51</v>
       </c>
       <c r="M6" t="n">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="N6" t="n">
-        <v>4</v>
+        <v>2.46</v>
       </c>
       <c r="O6" t="n">
-        <v>1.24</v>
+        <v>1.58</v>
       </c>
       <c r="P6" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.63</v>
+        <v>2.5</v>
       </c>
       <c r="R6" t="n">
-        <v>1.46</v>
+        <v>1.18</v>
       </c>
       <c r="S6" t="n">
-        <v>2.68</v>
+        <v>5</v>
       </c>
       <c r="T6" t="n">
-        <v>1.62</v>
+        <v>2.08</v>
       </c>
       <c r="U6" t="n">
-        <v>2.18</v>
+        <v>1.75</v>
       </c>
       <c r="V6" t="n">
-        <v>1.7</v>
+        <v>1.38</v>
       </c>
       <c r="W6" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="X6" t="n">
-        <v>950</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y6" t="n">
         <v>970</v>
       </c>
       <c r="Z6" t="n">
-        <v>970</v>
+        <v>22</v>
       </c>
       <c r="AA6" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AB6" t="n">
         <v>970</v>
@@ -1608,102 +1608,102 @@
         <v>970</v>
       </c>
       <c r="AE6" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AF6" t="n">
-        <v>23</v>
+        <v>970</v>
       </c>
       <c r="AG6" t="n">
         <v>970</v>
       </c>
       <c r="AH6" t="n">
-        <v>970</v>
+        <v>950</v>
       </c>
       <c r="AI6" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AJ6" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AK6" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AL6" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AM6" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AO6" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="AQ6" t="n">
-        <v>4.6</v>
+        <v>7.2</v>
       </c>
       <c r="AR6" t="n">
-        <v>5</v>
+        <v>2.56</v>
       </c>
       <c r="AS6" t="n">
-        <v>4.8</v>
+        <v>8</v>
       </c>
       <c r="AT6" t="n">
-        <v>5</v>
+        <v>6.2</v>
       </c>
       <c r="AU6" t="n">
-        <v>6.8</v>
+        <v>5.6</v>
       </c>
       <c r="AV6" t="n">
-        <v>8.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>2.02</v>
+        <v>7.8</v>
       </c>
       <c r="AX6" t="n">
-        <v>2.14</v>
+        <v>5.9</v>
       </c>
       <c r="AY6" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ6" t="n">
-        <v>11.5</v>
+        <v>6.4</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.76</v>
+        <v>2.1</v>
       </c>
       <c r="BB6" t="n">
-        <v>6.2</v>
+        <v>2.06</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.68</v>
+        <v>7.4</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.77</v>
+        <v>2.1</v>
       </c>
       <c r="BE6" t="n">
-        <v>6.4</v>
+        <v>1.96</v>
       </c>
       <c r="BF6" t="n">
-        <v>3.05</v>
+        <v>2.06</v>
       </c>
       <c r="BG6" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-24 07:16:59</t>
+          <t>2026-03-24 09:23:00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>English National League</t>
+          <t>Algerian Ligue 1</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1713,184 +1713,184 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>16:45:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Scunthorpe</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>Kabylie</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.45</v>
+        <v>1.91</v>
       </c>
       <c r="G7" t="n">
-        <v>3.95</v>
+        <v>2.08</v>
       </c>
       <c r="H7" t="n">
-        <v>2.14</v>
+        <v>4.7</v>
       </c>
       <c r="I7" t="n">
-        <v>2.26</v>
+        <v>6</v>
       </c>
       <c r="J7" t="n">
-        <v>3.55</v>
+        <v>3</v>
       </c>
       <c r="K7" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="L7" t="n">
-        <v>1.37</v>
+        <v>1.48</v>
       </c>
       <c r="M7" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="N7" t="n">
-        <v>3.95</v>
+        <v>2.44</v>
       </c>
       <c r="O7" t="n">
-        <v>1.28</v>
+        <v>1.53</v>
       </c>
       <c r="P7" t="n">
-        <v>2.02</v>
+        <v>1.5</v>
       </c>
       <c r="Q7" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S7" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="X7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BA7" t="n">
         <v>1.79</v>
       </c>
-      <c r="R7" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="S7" t="n">
-        <v>3</v>
-      </c>
-      <c r="T7" t="n">
+      <c r="BB7" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>7</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>6</v>
+      </c>
+      <c r="BG7" t="n">
         <v>1.68</v>
       </c>
-      <c r="U7" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="X7" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>11</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>15</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>27</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>18</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>9</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>11</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>23</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>29</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>16</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>18</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>36</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>70</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>44</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>50</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>90</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>44</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>14</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>36</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>8</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>32</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>12.5</v>
-      </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-24 07:16:59</t>
+          <t>2026-03-24 09:23:00</t>
         </is>
       </c>
     </row>
@@ -1912,179 +1912,179 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Truro City</t>
+          <t>Morecambe</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Solihull Moors</t>
+          <t>Hartlepool</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="G8" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="H8" t="n">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="I8" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="J8" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="K8" t="n">
-        <v>3.65</v>
+        <v>4.2</v>
       </c>
       <c r="L8" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="M8" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N8" t="n">
-        <v>3.55</v>
+        <v>4.5</v>
       </c>
       <c r="O8" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="P8" t="n">
-        <v>1.89</v>
+        <v>2.18</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.9</v>
+        <v>1.72</v>
       </c>
       <c r="R8" t="n">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="S8" t="n">
-        <v>3.25</v>
+        <v>2.74</v>
       </c>
       <c r="T8" t="n">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="U8" t="n">
-        <v>2.16</v>
+        <v>2.28</v>
       </c>
       <c r="V8" t="n">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="W8" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="X8" t="n">
-        <v>970</v>
+        <v>950</v>
       </c>
       <c r="Y8" t="n">
-        <v>970</v>
+        <v>14.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>970</v>
+        <v>19.5</v>
       </c>
       <c r="AA8" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AB8" t="n">
         <v>970</v>
       </c>
       <c r="AC8" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AD8" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>28</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>29</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>950</v>
+      </c>
+      <c r="AH8" t="n">
         <v>970</v>
       </c>
-      <c r="AE8" t="n">
-        <v>29</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>22</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>950</v>
-      </c>
       <c r="AI8" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AK8" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AL8" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AM8" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AN8" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AO8" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AP8" t="n">
-        <v>5.6</v>
+        <v>4</v>
       </c>
       <c r="AQ8" t="n">
-        <v>4.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR8" t="n">
-        <v>5.4</v>
+        <v>11.5</v>
       </c>
       <c r="AS8" t="n">
-        <v>3.15</v>
+        <v>21</v>
       </c>
       <c r="AT8" t="n">
-        <v>5.2</v>
+        <v>12.5</v>
       </c>
       <c r="AU8" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="AV8" t="n">
-        <v>5</v>
+        <v>8.4</v>
       </c>
       <c r="AW8" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="AX8" t="n">
-        <v>6</v>
+        <v>16.5</v>
       </c>
       <c r="AY8" t="n">
-        <v>5.4</v>
+        <v>10</v>
       </c>
       <c r="AZ8" t="n">
-        <v>5.7</v>
+        <v>12</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.82</v>
+        <v>23</v>
       </c>
       <c r="BB8" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BC8" t="n">
         <v>4.3</v>
       </c>
-      <c r="BC8" t="n">
-        <v>2.2</v>
-      </c>
       <c r="BD8" t="n">
-        <v>7</v>
+        <v>4.4</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.53</v>
+        <v>4.6</v>
       </c>
       <c r="BF8" t="n">
-        <v>3.45</v>
+        <v>18.5</v>
       </c>
       <c r="BG8" t="n">
-        <v>5.9</v>
+        <v>10.5</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-24 07:16:59</t>
+          <t>2026-03-24 09:23:00</t>
         </is>
       </c>
     </row>
@@ -2106,179 +2106,179 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Southend</t>
+          <t>Truro City</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Woking</t>
+          <t>Solihull Moors</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.67</v>
+        <v>2.84</v>
       </c>
       <c r="G9" t="n">
-        <v>1.75</v>
+        <v>3.25</v>
       </c>
       <c r="H9" t="n">
-        <v>5.4</v>
+        <v>2.44</v>
       </c>
       <c r="I9" t="n">
-        <v>6.4</v>
+        <v>2.74</v>
       </c>
       <c r="J9" t="n">
-        <v>3.9</v>
+        <v>3.55</v>
       </c>
       <c r="K9" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="L9" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="M9" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N9" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="O9" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="P9" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.75</v>
+        <v>1.93</v>
       </c>
       <c r="R9" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="S9" t="n">
-        <v>2.94</v>
+        <v>3.25</v>
       </c>
       <c r="T9" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="U9" t="n">
-        <v>2.04</v>
+        <v>2.14</v>
       </c>
       <c r="V9" t="n">
-        <v>1.2</v>
+        <v>1.64</v>
       </c>
       <c r="W9" t="n">
-        <v>2.32</v>
+        <v>1.47</v>
       </c>
       <c r="X9" t="n">
-        <v>21</v>
+        <v>970</v>
       </c>
       <c r="Y9" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>970</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>28</v>
+      </c>
+      <c r="AF9" t="n">
         <v>22</v>
       </c>
-      <c r="Z9" t="n">
-        <v>50</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>170</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>24</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>80</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>11</v>
-      </c>
       <c r="AG9" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>950</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AY9" t="n">
         <v>10.5</v>
       </c>
-      <c r="AH9" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>75</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>18</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>34</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>120</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>90</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>6</v>
-      </c>
-      <c r="AQ9" t="n">
+      <c r="AZ9" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>26</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BG9" t="n">
         <v>6.2</v>
       </c>
-      <c r="AR9" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>7</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>8</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>60</v>
-      </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-24 07:16:59</t>
+          <t>2026-03-24 09:23:00</t>
         </is>
       </c>
     </row>
@@ -2300,179 +2300,179 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Wealdstone</t>
+          <t>Scunthorpe</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Yeovil</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.9</v>
+        <v>3.5</v>
       </c>
       <c r="G10" t="n">
-        <v>2.02</v>
+        <v>4</v>
       </c>
       <c r="H10" t="n">
-        <v>4.3</v>
+        <v>2.14</v>
       </c>
       <c r="I10" t="n">
-        <v>4.9</v>
+        <v>2.26</v>
       </c>
       <c r="J10" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K10" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="L10" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N10" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="R10" t="n">
         <v>1.41</v>
       </c>
-      <c r="M10" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N10" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="O10" t="n">
+      <c r="S10" t="n">
+        <v>3</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="W10" t="n">
         <v>1.34</v>
       </c>
-      <c r="P10" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="U10" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.98</v>
-      </c>
       <c r="X10" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="Y10" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="Z10" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>27</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>18</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>23</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>29</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>36</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>70</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>44</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>85</v>
+      </c>
+      <c r="AN10" t="n">
         <v>40</v>
       </c>
-      <c r="AA10" t="n">
-        <v>110</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>19</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>60</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>15</v>
-      </c>
-      <c r="AG10" t="n">
+      <c r="AO10" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AR10" t="n">
         <v>12.5</v>
       </c>
-      <c r="AH10" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>65</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>26</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>24</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>38</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>110</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>70</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>12</v>
-      </c>
-      <c r="AQ10" t="n">
+      <c r="AS10" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>13</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>22</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>32</v>
+      </c>
+      <c r="BG10" t="n">
         <v>12.5</v>
       </c>
-      <c r="AR10" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>16</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>5</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>13</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>5</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>19</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>17</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>24</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>5</v>
-      </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-24 07:16:59</t>
+          <t>2026-03-24 09:23:00</t>
         </is>
       </c>
     </row>
@@ -2494,186 +2494,186 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Tamworth FC</t>
+          <t>Southend</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Forest Green</t>
+          <t>Woking</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3.5</v>
+        <v>1.67</v>
       </c>
       <c r="G11" t="n">
-        <v>4</v>
+        <v>1.75</v>
       </c>
       <c r="H11" t="n">
-        <v>1.99</v>
+        <v>5.4</v>
       </c>
       <c r="I11" t="n">
-        <v>2.16</v>
+        <v>6.6</v>
       </c>
       <c r="J11" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K11" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="L11" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="M11" t="n">
         <v>1.05</v>
       </c>
       <c r="N11" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="O11" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="P11" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="R11" t="n">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="S11" t="n">
-        <v>2.7</v>
+        <v>2.96</v>
       </c>
       <c r="T11" t="n">
-        <v>1.64</v>
+        <v>1.79</v>
       </c>
       <c r="U11" t="n">
-        <v>2.3</v>
+        <v>2.02</v>
       </c>
       <c r="V11" t="n">
-        <v>1.87</v>
+        <v>1.2</v>
       </c>
       <c r="W11" t="n">
-        <v>1.34</v>
+        <v>2.32</v>
       </c>
       <c r="X11" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="Y11" t="n">
-        <v>12.5</v>
+        <v>25</v>
       </c>
       <c r="Z11" t="n">
-        <v>17.5</v>
+        <v>55</v>
       </c>
       <c r="AA11" t="n">
-        <v>26</v>
+        <v>170</v>
       </c>
       <c r="AB11" t="n">
-        <v>18.5</v>
+        <v>10</v>
       </c>
       <c r="AC11" t="n">
         <v>10.5</v>
       </c>
       <c r="AD11" t="n">
+        <v>26</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>90</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>18</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>100</v>
+      </c>
+      <c r="AP11" t="n">
         <v>13</v>
       </c>
-      <c r="AE11" t="n">
-        <v>21</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>30</v>
-      </c>
-      <c r="AG11" t="n">
+      <c r="AQ11" t="n">
         <v>16.5</v>
       </c>
-      <c r="AH11" t="n">
-        <v>17</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>32</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>42</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>44</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>75</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>34</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>12</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>9.800000000000001</v>
-      </c>
       <c r="AR11" t="n">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="AS11" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="AT11" t="n">
-        <v>14</v>
+        <v>7.8</v>
       </c>
       <c r="AU11" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="AV11" t="n">
-        <v>9.4</v>
+        <v>18.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>14.5</v>
+        <v>55</v>
       </c>
       <c r="AX11" t="n">
-        <v>5.8</v>
+        <v>9</v>
       </c>
       <c r="AY11" t="n">
-        <v>13.5</v>
+        <v>7.8</v>
       </c>
       <c r="AZ11" t="n">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="BA11" t="n">
         <v>5.9</v>
       </c>
       <c r="BB11" t="n">
-        <v>6.6</v>
+        <v>14</v>
       </c>
       <c r="BC11" t="n">
-        <v>32</v>
+        <v>14.5</v>
       </c>
       <c r="BD11" t="n">
-        <v>6.2</v>
+        <v>5.5</v>
       </c>
       <c r="BE11" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="BF11" t="n">
+        <v>8</v>
+      </c>
+      <c r="BG11" t="n">
         <v>6</v>
       </c>
-      <c r="BG11" t="n">
-        <v>10</v>
-      </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-24 07:16:59</t>
+          <t>2026-03-24 09:23:00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>English National League</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2683,191 +2683,191 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>16:45:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Cerro</t>
+          <t>Wealdstone</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Juventud De Las Piedras</t>
+          <t>Yeovil</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3.1</v>
+        <v>1.9</v>
       </c>
       <c r="G12" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="H12" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I12" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K12" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N12" t="n">
         <v>3.55</v>
       </c>
-      <c r="H12" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="I12" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="J12" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="K12" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="M12" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="N12" t="n">
-        <v>2.48</v>
-      </c>
       <c r="O12" t="n">
-        <v>1.54</v>
+        <v>1.34</v>
       </c>
       <c r="P12" t="n">
-        <v>1.5</v>
+        <v>1.86</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.62</v>
+        <v>1.99</v>
       </c>
       <c r="R12" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="S12" t="n">
-        <v>5.3</v>
+        <v>3.55</v>
       </c>
       <c r="T12" t="n">
-        <v>2.08</v>
+        <v>1.84</v>
       </c>
       <c r="U12" t="n">
-        <v>1.76</v>
+        <v>2.02</v>
       </c>
       <c r="V12" t="n">
-        <v>1.53</v>
+        <v>1.27</v>
       </c>
       <c r="W12" t="n">
-        <v>1.39</v>
+        <v>1.98</v>
       </c>
       <c r="X12" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>40</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>110</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC12" t="n">
         <v>9.4</v>
       </c>
-      <c r="Y12" t="n">
-        <v>970</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>970</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>55</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>970</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>970</v>
-      </c>
       <c r="AD12" t="n">
-        <v>970</v>
+        <v>19</v>
       </c>
       <c r="AE12" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="AF12" t="n">
-        <v>22</v>
+        <v>14.5</v>
       </c>
       <c r="AG12" t="n">
-        <v>970</v>
+        <v>12.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>950</v>
+        <v>21</v>
       </c>
       <c r="AI12" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="AJ12" t="n">
-        <v>75</v>
+        <v>27</v>
       </c>
       <c r="AK12" t="n">
-        <v>60</v>
+        <v>24</v>
       </c>
       <c r="AL12" t="n">
-        <v>90</v>
+        <v>38</v>
       </c>
       <c r="AM12" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN12" t="n">
-        <v>80</v>
+        <v>15</v>
       </c>
       <c r="AO12" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="AP12" t="n">
-        <v>6.4</v>
+        <v>10</v>
       </c>
       <c r="AQ12" t="n">
-        <v>6.4</v>
+        <v>12.5</v>
       </c>
       <c r="AR12" t="n">
-        <v>5.7</v>
+        <v>5</v>
       </c>
       <c r="AS12" t="n">
-        <v>1.77</v>
+        <v>5.5</v>
       </c>
       <c r="AT12" t="n">
         <v>7.2</v>
       </c>
       <c r="AU12" t="n">
-        <v>3.85</v>
+        <v>7.2</v>
       </c>
       <c r="AV12" t="n">
+        <v>16</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>50</v>
+      </c>
+      <c r="AX12" t="n">
         <v>10</v>
       </c>
-      <c r="AW12" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>15.5</v>
-      </c>
       <c r="AY12" t="n">
-        <v>5.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ12" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>1.79</v>
+        <v>5.3</v>
       </c>
       <c r="BB12" t="n">
-        <v>7.6</v>
+        <v>20</v>
       </c>
       <c r="BC12" t="n">
-        <v>7.4</v>
+        <v>18.5</v>
       </c>
       <c r="BD12" t="n">
-        <v>1.79</v>
+        <v>5</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.61</v>
+        <v>5.5</v>
       </c>
       <c r="BF12" t="n">
-        <v>2.8</v>
+        <v>12.5</v>
       </c>
       <c r="BG12" t="n">
-        <v>1.77</v>
+        <v>55</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-24 07:16:59</t>
+          <t>2026-03-24 09:23:00</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>English National League</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2877,191 +2877,191 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>16:45:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Deportivo Riestra</t>
+          <t>Tamworth FC</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>San Lorenzo</t>
+          <t>Forest Green</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.48</v>
+        <v>3.55</v>
       </c>
       <c r="G13" t="n">
-        <v>2.66</v>
+        <v>4</v>
       </c>
       <c r="H13" t="n">
-        <v>3.8</v>
+        <v>2</v>
       </c>
       <c r="I13" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="K13" t="n">
         <v>4.3</v>
       </c>
-      <c r="J13" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="K13" t="n">
-        <v>2.8</v>
-      </c>
       <c r="L13" t="n">
-        <v>1.79</v>
+        <v>1.27</v>
       </c>
       <c r="M13" t="n">
-        <v>1.21</v>
+        <v>1.05</v>
       </c>
       <c r="N13" t="n">
-        <v>1.97</v>
+        <v>4.5</v>
       </c>
       <c r="O13" t="n">
-        <v>1.89</v>
+        <v>1.23</v>
       </c>
       <c r="P13" t="n">
-        <v>1.28</v>
+        <v>2.2</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.85</v>
+        <v>1.7</v>
       </c>
       <c r="R13" t="n">
-        <v>1.08</v>
+        <v>1.49</v>
       </c>
       <c r="S13" t="n">
-        <v>8.800000000000001</v>
+        <v>2.7</v>
       </c>
       <c r="T13" t="n">
-        <v>2.84</v>
+        <v>1.64</v>
       </c>
       <c r="U13" t="n">
-        <v>1.45</v>
+        <v>2.32</v>
       </c>
       <c r="V13" t="n">
-        <v>1.31</v>
+        <v>1.87</v>
       </c>
       <c r="W13" t="n">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="X13" t="n">
-        <v>5.5</v>
+        <v>25</v>
       </c>
       <c r="Y13" t="n">
-        <v>8.800000000000001</v>
+        <v>14.5</v>
       </c>
       <c r="Z13" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="AA13" t="n">
-        <v>130</v>
+        <v>30</v>
       </c>
       <c r="AB13" t="n">
-        <v>6.2</v>
+        <v>21</v>
       </c>
       <c r="AC13" t="n">
-        <v>7.4</v>
+        <v>10.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="AE13" t="n">
-        <v>130</v>
+        <v>24</v>
       </c>
       <c r="AF13" t="n">
+        <v>34</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>36</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>85</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>48</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>75</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>38</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>14</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>18</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>17</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY13" t="n">
         <v>13.5</v>
       </c>
-      <c r="AG13" t="n">
-        <v>19</v>
-      </c>
-      <c r="AH13" t="n">
+      <c r="AZ13" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>32</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BE13" t="n">
         <v>50</v>
       </c>
-      <c r="AI13" t="n">
-        <v>230</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>46</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>65</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>160</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>610</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>90</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>250</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>38</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>17</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>38</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>13</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>30</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>48</v>
-      </c>
-      <c r="BB13" t="n">
+      <c r="BF13" t="n">
         <v>23</v>
       </c>
-      <c r="BC13" t="n">
-        <v>28</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>44</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>55</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>32</v>
-      </c>
       <c r="BG13" t="n">
-        <v>46</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-24 07:16:59</t>
+          <t>2026-03-24 09:23:00</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Colombian Primera B</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3071,191 +3071,191 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Barranquilla</t>
+          <t>Cerro</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Leones FC</t>
+          <t>Juventud De Las Piedras</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.04</v>
+        <v>3.15</v>
       </c>
       <c r="G14" t="n">
-        <v>1000</v>
+        <v>3.55</v>
       </c>
       <c r="H14" t="n">
-        <v>1.04</v>
+        <v>2.56</v>
       </c>
       <c r="I14" t="n">
-        <v>1000</v>
+        <v>2.88</v>
       </c>
       <c r="J14" t="n">
-        <v>1.02</v>
+        <v>2.86</v>
       </c>
       <c r="K14" t="n">
-        <v>1000</v>
+        <v>3.25</v>
       </c>
       <c r="L14" t="n">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="M14" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="N14" t="n">
-        <v>1.25</v>
+        <v>2.5</v>
       </c>
       <c r="O14" t="n">
-        <v>1.3</v>
+        <v>1.54</v>
       </c>
       <c r="P14" t="n">
-        <v>1.24</v>
+        <v>1.5</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.3</v>
+        <v>2.62</v>
       </c>
       <c r="R14" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="S14" t="n">
-        <v>1.3</v>
+        <v>5.3</v>
       </c>
       <c r="T14" t="n">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="U14" t="n">
-        <v>1.01</v>
+        <v>1.75</v>
       </c>
       <c r="V14" t="n">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="W14" t="n">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="X14" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="Y14" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z14" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AA14" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AB14" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC14" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD14" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE14" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AF14" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AG14" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH14" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI14" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AK14" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AL14" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AM14" t="n">
         <v>1000</v>
       </c>
       <c r="AN14" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AO14" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.03</v>
+        <v>5.7</v>
       </c>
       <c r="AS14" t="n">
-        <v>1.03</v>
+        <v>1.78</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="AV14" t="n">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.03</v>
+        <v>2.76</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.03</v>
+        <v>15.5</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.03</v>
+        <v>17</v>
       </c>
       <c r="BA14" t="n">
-        <v>1.03</v>
+        <v>1.8</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.03</v>
+        <v>2.82</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="BD14" t="n">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.03</v>
+        <v>1.61</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.01</v>
+        <v>2.82</v>
       </c>
       <c r="BG14" t="n">
-        <v>1.01</v>
+        <v>1.78</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-24 07:16:59</t>
+          <t>2026-03-24 09:23:00</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Colombian Primera B</t>
+          <t>Argentinian Primera Division</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3265,191 +3265,191 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Real Soacha Cundinamarca FC</t>
+          <t>Deportivo Riestra</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Atletico FC Cali</t>
+          <t>San Lorenzo</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.58</v>
+        <v>2.52</v>
       </c>
       <c r="G15" t="n">
-        <v>1.72</v>
+        <v>2.62</v>
       </c>
       <c r="H15" t="n">
-        <v>6</v>
+        <v>3.85</v>
       </c>
       <c r="I15" t="n">
-        <v>9.199999999999999</v>
+        <v>4.2</v>
       </c>
       <c r="J15" t="n">
-        <v>3.25</v>
+        <v>2.74</v>
       </c>
       <c r="K15" t="n">
-        <v>4.7</v>
+        <v>2.8</v>
       </c>
       <c r="L15" t="n">
-        <v>1.42</v>
+        <v>1.8</v>
       </c>
       <c r="M15" t="n">
-        <v>1.09</v>
+        <v>1.21</v>
       </c>
       <c r="N15" t="n">
-        <v>2.72</v>
+        <v>1.98</v>
       </c>
       <c r="O15" t="n">
-        <v>1.41</v>
+        <v>1.9</v>
       </c>
       <c r="P15" t="n">
-        <v>1.66</v>
+        <v>1.29</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.1</v>
+        <v>3</v>
       </c>
       <c r="R15" t="n">
-        <v>1.24</v>
+        <v>1.08</v>
       </c>
       <c r="S15" t="n">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="T15" t="n">
-        <v>2.16</v>
+        <v>2.8</v>
       </c>
       <c r="U15" t="n">
-        <v>1.69</v>
+        <v>1.45</v>
       </c>
       <c r="V15" t="n">
-        <v>1.12</v>
+        <v>1.32</v>
       </c>
       <c r="W15" t="n">
-        <v>2.28</v>
+        <v>1.61</v>
       </c>
       <c r="X15" t="n">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="Y15" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="Z15" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AA15" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AB15" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="AC15" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="AD15" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AE15" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AF15" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AG15" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AH15" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AI15" t="n">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AK15" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AL15" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AM15" t="n">
-        <v>1000</v>
+        <v>590</v>
       </c>
       <c r="AN15" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AO15" t="n">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="AP15" t="n">
-        <v>3.75</v>
+        <v>4.9</v>
       </c>
       <c r="AQ15" t="n">
-        <v>4.2</v>
+        <v>7</v>
       </c>
       <c r="AR15" t="n">
-        <v>4.9</v>
+        <v>16.5</v>
       </c>
       <c r="AS15" t="n">
-        <v>2.2</v>
+        <v>38</v>
       </c>
       <c r="AT15" t="n">
-        <v>3.05</v>
+        <v>5.6</v>
       </c>
       <c r="AU15" t="n">
-        <v>3.5</v>
+        <v>6.6</v>
       </c>
       <c r="AV15" t="n">
-        <v>4.6</v>
+        <v>19</v>
       </c>
       <c r="AW15" t="n">
-        <v>2.42</v>
+        <v>38</v>
       </c>
       <c r="AX15" t="n">
-        <v>3.45</v>
+        <v>10.5</v>
       </c>
       <c r="AY15" t="n">
-        <v>3.65</v>
+        <v>14.5</v>
       </c>
       <c r="AZ15" t="n">
-        <v>4.5</v>
+        <v>25</v>
       </c>
       <c r="BA15" t="n">
-        <v>2.42</v>
+        <v>48</v>
       </c>
       <c r="BB15" t="n">
-        <v>4.1</v>
+        <v>23</v>
       </c>
       <c r="BC15" t="n">
-        <v>4.3</v>
+        <v>28</v>
       </c>
       <c r="BD15" t="n">
-        <v>4.8</v>
+        <v>44</v>
       </c>
       <c r="BE15" t="n">
-        <v>2.2</v>
+        <v>55</v>
       </c>
       <c r="BF15" t="n">
-        <v>3.95</v>
+        <v>32</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.2</v>
+        <v>46</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-24 07:16:59</t>
+          <t>2026-03-24 09:23:00</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>US United Soccer League</t>
+          <t>Colombian Primera B</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3459,191 +3459,191 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Lexington SC</t>
+          <t>Barranquilla</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Leones FC</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.56</v>
+        <v>1.04</v>
       </c>
       <c r="G16" t="n">
-        <v>1.75</v>
+        <v>1000</v>
       </c>
       <c r="H16" t="n">
-        <v>6</v>
+        <v>1.04</v>
       </c>
       <c r="I16" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="J16" t="n">
-        <v>3.85</v>
+        <v>1.03</v>
       </c>
       <c r="K16" t="n">
-        <v>4.6</v>
+        <v>1000</v>
       </c>
       <c r="L16" t="n">
-        <v>1.33</v>
+        <v>1.01</v>
       </c>
       <c r="M16" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="N16" t="n">
-        <v>3.6</v>
+        <v>1.25</v>
       </c>
       <c r="O16" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="P16" t="n">
-        <v>1.88</v>
+        <v>1.24</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.85</v>
+        <v>1.29</v>
       </c>
       <c r="R16" t="n">
-        <v>1.34</v>
+        <v>1.13</v>
       </c>
       <c r="S16" t="n">
-        <v>3.35</v>
+        <v>1.29</v>
       </c>
       <c r="T16" t="n">
-        <v>1.94</v>
+        <v>1.11</v>
       </c>
       <c r="U16" t="n">
-        <v>1.77</v>
+        <v>1.11</v>
       </c>
       <c r="V16" t="n">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="W16" t="n">
-        <v>2.34</v>
+        <v>1.01</v>
       </c>
       <c r="X16" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Y16" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="Z16" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AA16" t="n">
         <v>1000</v>
       </c>
       <c r="AB16" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="AC16" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AD16" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AE16" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AF16" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AG16" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AH16" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AI16" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AJ16" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AK16" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AL16" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AM16" t="n">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AN16" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AO16" t="n">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AP16" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ16" t="n">
-        <v>3.7</v>
+        <v>1.01</v>
       </c>
       <c r="AR16" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="AS16" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="AT16" t="n">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="AU16" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AV16" t="n">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="AW16" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="AX16" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AY16" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AZ16" t="n">
-        <v>3.75</v>
+        <v>1.01</v>
       </c>
       <c r="BA16" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BB16" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC16" t="n">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="BD16" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BE16" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BF16" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BG16" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-24 07:16:59</t>
+          <t>2026-03-24 09:23:00</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Colombian Primera B</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3653,184 +3653,184 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Boston River</t>
+          <t>Real Soacha Cundinamarca FC</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Penarol</t>
+          <t>Atletico FC Cali</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>6.8</v>
+        <v>1.57</v>
       </c>
       <c r="G17" t="n">
-        <v>8.199999999999999</v>
+        <v>1.7</v>
       </c>
       <c r="H17" t="n">
-        <v>1.6</v>
+        <v>6.2</v>
       </c>
       <c r="I17" t="n">
-        <v>1.64</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J17" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="K17" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="L17" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="M17" t="n">
         <v>1.09</v>
       </c>
       <c r="N17" t="n">
-        <v>3</v>
+        <v>2.78</v>
       </c>
       <c r="O17" t="n">
         <v>1.4</v>
       </c>
       <c r="P17" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="Q17" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="W17" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AW17" t="n">
         <v>2.18</v>
       </c>
-      <c r="R17" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="S17" t="n">
+      <c r="AX17" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BB17" t="n">
         <v>4.1</v>
       </c>
-      <c r="T17" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="V17" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X17" t="n">
-        <v>13</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>9</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>17</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>20</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>11</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>23</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>65</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>30</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>28</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>50</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>300</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>160</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>160</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>230</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>260</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>14</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>8</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>17</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>20</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>8.4</v>
-      </c>
       <c r="BC17" t="n">
-        <v>8.199999999999999</v>
+        <v>4.4</v>
       </c>
       <c r="BD17" t="n">
-        <v>8.199999999999999</v>
+        <v>4.9</v>
       </c>
       <c r="BE17" t="n">
-        <v>8.4</v>
+        <v>2.18</v>
       </c>
       <c r="BF17" t="n">
-        <v>8.4</v>
+        <v>4</v>
       </c>
       <c r="BG17" t="n">
-        <v>10</v>
+        <v>2.02</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-24 07:16:59</t>
+          <t>2026-03-24 09:23:00</t>
         </is>
       </c>
     </row>
@@ -3847,191 +3847,191 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Sporting Club Jacksonville</t>
+          <t>Lexington SC</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Miami FC</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.6</v>
+        <v>1.57</v>
       </c>
       <c r="G18" t="n">
-        <v>2.82</v>
+        <v>1.71</v>
       </c>
       <c r="H18" t="n">
-        <v>2.72</v>
+        <v>6</v>
       </c>
       <c r="I18" t="n">
-        <v>3.05</v>
+        <v>8.6</v>
       </c>
       <c r="J18" t="n">
-        <v>3.35</v>
+        <v>3.9</v>
       </c>
       <c r="K18" t="n">
-        <v>3.75</v>
+        <v>4.6</v>
       </c>
       <c r="L18" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="M18" t="n">
         <v>1.07</v>
       </c>
       <c r="N18" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="O18" t="n">
         <v>1.31</v>
       </c>
       <c r="P18" t="n">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="R18" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="S18" t="n">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="T18" t="n">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="U18" t="n">
-        <v>2.14</v>
+        <v>1.86</v>
       </c>
       <c r="V18" t="n">
-        <v>1.5</v>
+        <v>1.14</v>
       </c>
       <c r="W18" t="n">
-        <v>1.54</v>
+        <v>2.4</v>
       </c>
       <c r="X18" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>950</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>70</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>950</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>130</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>950</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>120</v>
+      </c>
+      <c r="AJ18" t="n">
         <v>970</v>
       </c>
-      <c r="Y18" t="n">
-        <v>970</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>970</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>46</v>
-      </c>
-      <c r="AB18" t="n">
+      <c r="AK18" t="n">
+        <v>22</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>180</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>180</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BC18" t="n">
         <v>13</v>
       </c>
-      <c r="AC18" t="n">
-        <v>9</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>970</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>36</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>21</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>970</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>48</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>48</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>34</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>46</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>100</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>28</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>28</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>5</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>4.9</v>
-      </c>
       <c r="BD18" t="n">
-        <v>5.1</v>
+        <v>4</v>
       </c>
       <c r="BE18" t="n">
-        <v>5.4</v>
+        <v>4.2</v>
       </c>
       <c r="BF18" t="n">
-        <v>4.8</v>
+        <v>7.6</v>
       </c>
       <c r="BG18" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-24 07:16:59</t>
+          <t>2026-03-24 09:23:00</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4041,36 +4041,36 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>22:00:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>America de Cali S.A</t>
+          <t>Boston River</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Llaneros FC</t>
+          <t>Penarol</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.58</v>
+        <v>6.8</v>
       </c>
       <c r="G19" t="n">
-        <v>1.65</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H19" t="n">
-        <v>7</v>
+        <v>1.6</v>
       </c>
       <c r="I19" t="n">
-        <v>8</v>
+        <v>1.64</v>
       </c>
       <c r="J19" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K19" t="n">
         <v>4</v>
-      </c>
-      <c r="K19" t="n">
-        <v>4.1</v>
       </c>
       <c r="L19" t="n">
         <v>1.46</v>
@@ -4079,146 +4079,534 @@
         <v>1.09</v>
       </c>
       <c r="N19" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="O19" t="n">
         <v>1.41</v>
       </c>
       <c r="P19" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="V19" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X19" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>17</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>20</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>22</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>65</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>30</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>28</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>50</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>300</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>160</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>160</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>230</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>260</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>16</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>17</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>22</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>36</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>10</v>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>2026-03-24 09:23:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>US United Soccer League</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>20:30:00</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Sporting Club Jacksonville</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Miami FC</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="G20" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="H20" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="J20" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K20" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N20" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="X20" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>970</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>48</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>36</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>970</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>50</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>50</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>36</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>32</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>30</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>9</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>20</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>19</v>
+      </c>
+      <c r="BH20" t="inlineStr">
+        <is>
+          <t>2026-03-24 09:23:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Colombian Primera A</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>22:00:00</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>America de Cali S.A</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Llaneros FC</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="H21" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="I21" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="J21" t="n">
+        <v>4</v>
+      </c>
+      <c r="K21" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N21" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="P21" t="n">
         <v>1.72</v>
       </c>
-      <c r="Q19" t="n">
+      <c r="Q21" t="n">
         <v>2.22</v>
       </c>
-      <c r="R19" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="S19" t="n">
+      <c r="R21" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S21" t="n">
         <v>4.1</v>
       </c>
-      <c r="T19" t="n">
+      <c r="T21" t="n">
         <v>2.2</v>
       </c>
-      <c r="U19" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="V19" t="n">
+      <c r="U21" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="V21" t="n">
         <v>1.14</v>
       </c>
-      <c r="W19" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="X19" t="n">
+      <c r="W21" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="X21" t="n">
         <v>12</v>
       </c>
-      <c r="Y19" t="n">
-        <v>20</v>
-      </c>
-      <c r="Z19" t="n">
+      <c r="Y21" t="n">
+        <v>950</v>
+      </c>
+      <c r="Z21" t="n">
         <v>65</v>
       </c>
-      <c r="AA19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AC19" t="n">
+      <c r="AA21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AC21" t="n">
         <v>9</v>
       </c>
-      <c r="AD19" t="n">
+      <c r="AD21" t="n">
         <v>950</v>
       </c>
-      <c r="AE19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF19" t="n">
+      <c r="AE21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF21" t="n">
         <v>8.6</v>
       </c>
-      <c r="AG19" t="n">
+      <c r="AG21" t="n">
         <v>10.5</v>
       </c>
-      <c r="AH19" t="n">
+      <c r="AH21" t="n">
         <v>950</v>
       </c>
-      <c r="AI19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ19" t="n">
+      <c r="AI21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ21" t="n">
         <v>970</v>
       </c>
-      <c r="AK19" t="n">
+      <c r="AK21" t="n">
         <v>21</v>
       </c>
-      <c r="AL19" t="n">
+      <c r="AL21" t="n">
         <v>50</v>
       </c>
-      <c r="AM19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP19" t="n">
+      <c r="AM21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>15</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP21" t="n">
         <v>10</v>
       </c>
-      <c r="AQ19" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AR19" t="n">
+      <c r="AQ21" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>10</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>25</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>23</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>11</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BD21" t="n">
         <v>9.6</v>
       </c>
-      <c r="AS19" t="n">
+      <c r="BE21" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BF21" t="n">
         <v>10.5</v>
       </c>
-      <c r="AT19" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>8</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>42</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BG19" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BH19" t="inlineStr">
-        <is>
-          <t>2026-03-24 07:16:59</t>
+      <c r="BG21" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BH21" t="inlineStr">
+        <is>
+          <t>2026-03-24 09:23:00</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-25.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH21"/>
+  <dimension ref="A1:BH23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,22 +757,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.05</v>
+        <v>3.65</v>
       </c>
       <c r="G2" t="n">
-        <v>500</v>
+        <v>44</v>
       </c>
       <c r="H2" t="n">
-        <v>1.05</v>
+        <v>1.85</v>
       </c>
       <c r="I2" t="n">
-        <v>500</v>
+        <v>2.14</v>
       </c>
       <c r="J2" t="n">
-        <v>1.06</v>
+        <v>3</v>
       </c>
       <c r="K2" t="n">
-        <v>950</v>
+        <v>5.1</v>
       </c>
       <c r="L2" t="n">
         <v>1.01</v>
@@ -781,34 +781,34 @@
         <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>1.08</v>
+        <v>2.84</v>
       </c>
       <c r="O2" t="n">
-        <v>1.02</v>
+        <v>1.39</v>
       </c>
       <c r="P2" t="n">
-        <v>1.07</v>
+        <v>1.69</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.02</v>
+        <v>2.02</v>
       </c>
       <c r="R2" t="n">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="S2" t="n">
-        <v>1.31</v>
+        <v>2.02</v>
       </c>
       <c r="T2" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U2" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V2" t="n">
-        <v>1.02</v>
+        <v>1.87</v>
       </c>
       <c r="W2" t="n">
-        <v>1.02</v>
+        <v>1.25</v>
       </c>
       <c r="X2" t="n">
         <v>1000</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-24 09:23:00</t>
+          <t>2026-03-24 11:28:59</t>
         </is>
       </c>
     </row>
@@ -951,170 +951,170 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.09</v>
+        <v>2.44</v>
       </c>
       <c r="G3" t="n">
-        <v>150</v>
+        <v>2.78</v>
       </c>
       <c r="H3" t="n">
-        <v>1.05</v>
+        <v>2.82</v>
       </c>
       <c r="I3" t="n">
-        <v>210</v>
+        <v>3.25</v>
       </c>
       <c r="J3" t="n">
-        <v>1.09</v>
+        <v>3.25</v>
       </c>
       <c r="K3" t="n">
-        <v>950</v>
+        <v>3.75</v>
       </c>
       <c r="L3" t="n">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="M3" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N3" t="n">
-        <v>1.15</v>
+        <v>3.45</v>
       </c>
       <c r="O3" t="n">
-        <v>1.02</v>
+        <v>1.32</v>
       </c>
       <c r="P3" t="n">
-        <v>1.15</v>
+        <v>1.85</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.01</v>
+        <v>1.96</v>
       </c>
       <c r="R3" t="n">
-        <v>1.07</v>
+        <v>1.33</v>
       </c>
       <c r="S3" t="n">
-        <v>1.02</v>
+        <v>3.45</v>
       </c>
       <c r="T3" t="n">
-        <v>1.01</v>
+        <v>1.74</v>
       </c>
       <c r="U3" t="n">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="V3" t="n">
-        <v>1.02</v>
+        <v>1.44</v>
       </c>
       <c r="W3" t="n">
-        <v>1.02</v>
+        <v>1.56</v>
       </c>
       <c r="X3" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AA3" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AB3" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AC3" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AD3" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AE3" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AF3" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AG3" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI3" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AK3" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AL3" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM3" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AN3" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AO3" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.03</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.03</v>
+        <v>15</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.03</v>
+        <v>5.9</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.03</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.03</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.03</v>
+        <v>21</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-24 09:23:00</t>
+          <t>2026-03-24 11:28:59</t>
         </is>
       </c>
     </row>
@@ -1145,10 +1145,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="G4" t="n">
-        <v>60</v>
+        <v>600</v>
       </c>
       <c r="H4" t="n">
         <v>1.09</v>
@@ -1178,13 +1178,13 @@
         <v>1.24</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="R4" t="n">
         <v>1.18</v>
       </c>
       <c r="S4" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="T4" t="n">
         <v>1.11</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-24 09:23:00</t>
+          <t>2026-03-24 11:28:59</t>
         </is>
       </c>
     </row>
@@ -1357,7 +1357,7 @@
         <v>3.05</v>
       </c>
       <c r="L5" t="n">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="M5" t="n">
         <v>1.14</v>
@@ -1381,10 +1381,10 @@
         <v>6.2</v>
       </c>
       <c r="T5" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="U5" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="V5" t="n">
         <v>1.4</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-24 09:23:00</t>
+          <t>2026-03-24 11:28:59</t>
         </is>
       </c>
     </row>
@@ -1536,13 +1536,13 @@
         <v>2.56</v>
       </c>
       <c r="G6" t="n">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="H6" t="n">
         <v>3.1</v>
       </c>
       <c r="I6" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="J6" t="n">
         <v>2.66</v>
@@ -1557,16 +1557,16 @@
         <v>1.13</v>
       </c>
       <c r="N6" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="O6" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="P6" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="R6" t="n">
         <v>1.18</v>
@@ -1581,10 +1581,10 @@
         <v>1.75</v>
       </c>
       <c r="V6" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="W6" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="X6" t="n">
         <v>8.800000000000001</v>
@@ -1599,7 +1599,7 @@
         <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>970</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC6" t="n">
         <v>970</v>
@@ -1647,56 +1647,56 @@
         <v>7.2</v>
       </c>
       <c r="AR6" t="n">
-        <v>2.56</v>
+        <v>3.05</v>
       </c>
       <c r="AS6" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT6" t="n">
         <v>6.2</v>
       </c>
       <c r="AU6" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AV6" t="n">
         <v>11.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AX6" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AY6" t="n">
         <v>10</v>
       </c>
       <c r="AZ6" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BA6" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="BB6" t="n">
-        <v>2.06</v>
+        <v>3.35</v>
       </c>
       <c r="BC6" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BD6" t="n">
-        <v>2.1</v>
+        <v>3.4</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="BF6" t="n">
-        <v>2.06</v>
+        <v>3.35</v>
       </c>
       <c r="BG6" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-24 09:23:00</t>
+          <t>2026-03-24 11:28:59</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-24 09:23:00</t>
+          <t>2026-03-24 11:28:59</t>
         </is>
       </c>
     </row>
@@ -1921,16 +1921,16 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="G8" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="H8" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="I8" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="J8" t="n">
         <v>3.7</v>
@@ -1951,13 +1951,13 @@
         <v>1.23</v>
       </c>
       <c r="P8" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="Q8" t="n">
         <v>1.72</v>
       </c>
       <c r="R8" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="S8" t="n">
         <v>2.74</v>
@@ -1966,10 +1966,10 @@
         <v>1.6</v>
       </c>
       <c r="U8" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="V8" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="W8" t="n">
         <v>1.41</v>
@@ -1978,10 +1978,10 @@
         <v>950</v>
       </c>
       <c r="Y8" t="n">
-        <v>14.5</v>
+        <v>970</v>
       </c>
       <c r="Z8" t="n">
-        <v>19.5</v>
+        <v>970</v>
       </c>
       <c r="AA8" t="n">
         <v>38</v>
@@ -1993,13 +1993,13 @@
         <v>11</v>
       </c>
       <c r="AD8" t="n">
-        <v>14</v>
+        <v>970</v>
       </c>
       <c r="AE8" t="n">
         <v>28</v>
       </c>
       <c r="AF8" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AG8" t="n">
         <v>950</v>
@@ -2008,16 +2008,16 @@
         <v>970</v>
       </c>
       <c r="AI8" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AJ8" t="n">
         <v>65</v>
       </c>
       <c r="AK8" t="n">
+        <v>36</v>
+      </c>
+      <c r="AL8" t="n">
         <v>42</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>48</v>
       </c>
       <c r="AM8" t="n">
         <v>90</v>
@@ -2026,10 +2026,10 @@
         <v>32</v>
       </c>
       <c r="AO8" t="n">
-        <v>17</v>
+        <v>970</v>
       </c>
       <c r="AP8" t="n">
-        <v>4</v>
+        <v>4.9</v>
       </c>
       <c r="AQ8" t="n">
         <v>8.800000000000001</v>
@@ -2053,10 +2053,10 @@
         <v>17</v>
       </c>
       <c r="AX8" t="n">
-        <v>16.5</v>
+        <v>5</v>
       </c>
       <c r="AY8" t="n">
-        <v>10</v>
+        <v>4.3</v>
       </c>
       <c r="AZ8" t="n">
         <v>12</v>
@@ -2065,26 +2065,26 @@
         <v>23</v>
       </c>
       <c r="BB8" t="n">
-        <v>4.5</v>
+        <v>5.6</v>
       </c>
       <c r="BC8" t="n">
-        <v>4.3</v>
+        <v>5.3</v>
       </c>
       <c r="BD8" t="n">
-        <v>4.4</v>
+        <v>5.4</v>
       </c>
       <c r="BE8" t="n">
-        <v>4.6</v>
+        <v>5.8</v>
       </c>
       <c r="BF8" t="n">
-        <v>18.5</v>
+        <v>5.2</v>
       </c>
       <c r="BG8" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-24 09:23:00</t>
+          <t>2026-03-24 11:28:59</t>
         </is>
       </c>
     </row>
@@ -2106,179 +2106,179 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Truro City</t>
+          <t>Scunthorpe</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Solihull Moors</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.84</v>
+        <v>3.5</v>
       </c>
       <c r="G9" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="H9" t="n">
-        <v>2.44</v>
+        <v>2.14</v>
       </c>
       <c r="I9" t="n">
-        <v>2.74</v>
+        <v>2.24</v>
       </c>
       <c r="J9" t="n">
         <v>3.55</v>
       </c>
       <c r="K9" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="L9" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="M9" t="n">
         <v>1.06</v>
       </c>
       <c r="N9" t="n">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="O9" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="P9" t="n">
-        <v>1.9</v>
+        <v>2.04</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.93</v>
+        <v>1.78</v>
       </c>
       <c r="R9" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="S9" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="T9" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="U9" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="V9" t="n">
-        <v>1.64</v>
+        <v>1.8</v>
       </c>
       <c r="W9" t="n">
-        <v>1.47</v>
+        <v>1.35</v>
       </c>
       <c r="X9" t="n">
-        <v>970</v>
+        <v>17.5</v>
       </c>
       <c r="Y9" t="n">
-        <v>970</v>
+        <v>11</v>
       </c>
       <c r="Z9" t="n">
-        <v>970</v>
+        <v>15</v>
       </c>
       <c r="AA9" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AB9" t="n">
-        <v>970</v>
+        <v>18</v>
       </c>
       <c r="AC9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AD9" t="n">
-        <v>970</v>
+        <v>11</v>
       </c>
       <c r="AE9" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="AF9" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="AG9" t="n">
-        <v>970</v>
+        <v>16</v>
       </c>
       <c r="AH9" t="n">
-        <v>950</v>
+        <v>17.5</v>
       </c>
       <c r="AI9" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AK9" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AL9" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AM9" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AN9" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AO9" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AP9" t="n">
-        <v>5.7</v>
+        <v>11.5</v>
       </c>
       <c r="AQ9" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AR9" t="n">
-        <v>5.6</v>
+        <v>12.5</v>
       </c>
       <c r="AS9" t="n">
-        <v>3.45</v>
+        <v>6.8</v>
       </c>
       <c r="AT9" t="n">
-        <v>5.2</v>
+        <v>13</v>
       </c>
       <c r="AU9" t="n">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV9" t="n">
-        <v>5.2</v>
+        <v>9</v>
       </c>
       <c r="AW9" t="n">
-        <v>4.6</v>
+        <v>18.5</v>
       </c>
       <c r="AX9" t="n">
-        <v>6.2</v>
+        <v>22</v>
       </c>
       <c r="AY9" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AZ9" t="n">
-        <v>5.8</v>
+        <v>14</v>
       </c>
       <c r="BA9" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BB9" t="n">
-        <v>5.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC9" t="n">
-        <v>26</v>
+        <v>7.6</v>
       </c>
       <c r="BD9" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BE9" t="n">
-        <v>3.35</v>
+        <v>8.4</v>
       </c>
       <c r="BF9" t="n">
-        <v>3.35</v>
+        <v>32</v>
       </c>
       <c r="BG9" t="n">
-        <v>6.2</v>
+        <v>12.5</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-24 09:23:00</t>
+          <t>2026-03-24 11:28:59</t>
         </is>
       </c>
     </row>
@@ -2300,179 +2300,179 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Scunthorpe</t>
+          <t>Truro City</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>Solihull Moors</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.5</v>
+        <v>2.64</v>
       </c>
       <c r="G10" t="n">
-        <v>4</v>
+        <v>2.86</v>
       </c>
       <c r="H10" t="n">
-        <v>2.14</v>
+        <v>2.56</v>
       </c>
       <c r="I10" t="n">
-        <v>2.26</v>
+        <v>2.82</v>
       </c>
       <c r="J10" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="K10" t="n">
         <v>4.1</v>
       </c>
       <c r="L10" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="M10" t="n">
         <v>1.06</v>
       </c>
       <c r="N10" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="O10" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="P10" t="n">
-        <v>2.04</v>
+        <v>1.94</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.78</v>
+        <v>1.89</v>
       </c>
       <c r="R10" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="S10" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="T10" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="U10" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="V10" t="n">
-        <v>1.8</v>
+        <v>1.54</v>
       </c>
       <c r="W10" t="n">
-        <v>1.34</v>
+        <v>1.54</v>
       </c>
       <c r="X10" t="n">
-        <v>17.5</v>
+        <v>970</v>
       </c>
       <c r="Y10" t="n">
-        <v>11</v>
+        <v>970</v>
       </c>
       <c r="Z10" t="n">
-        <v>15</v>
+        <v>970</v>
       </c>
       <c r="AA10" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AB10" t="n">
-        <v>18</v>
+        <v>970</v>
       </c>
       <c r="AC10" t="n">
-        <v>9</v>
+        <v>970</v>
       </c>
       <c r="AD10" t="n">
-        <v>11</v>
+        <v>970</v>
       </c>
       <c r="AE10" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="AF10" t="n">
-        <v>29</v>
+        <v>19.5</v>
       </c>
       <c r="AG10" t="n">
-        <v>16</v>
+        <v>970</v>
       </c>
       <c r="AH10" t="n">
-        <v>17.5</v>
+        <v>950</v>
       </c>
       <c r="AI10" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AJ10" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AK10" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AL10" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AM10" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AN10" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AO10" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>11.5</v>
+        <v>6</v>
       </c>
       <c r="AQ10" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AR10" t="n">
-        <v>12.5</v>
+        <v>5.9</v>
       </c>
       <c r="AS10" t="n">
-        <v>6.8</v>
+        <v>5.3</v>
       </c>
       <c r="AT10" t="n">
-        <v>13</v>
+        <v>5.1</v>
       </c>
       <c r="AU10" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BD10" t="n">
         <v>7.4</v>
       </c>
-      <c r="AV10" t="n">
-        <v>9</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>22</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>14</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>7.8</v>
-      </c>
       <c r="BE10" t="n">
-        <v>8.4</v>
+        <v>5.7</v>
       </c>
       <c r="BF10" t="n">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="BG10" t="n">
-        <v>12.5</v>
+        <v>4.8</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-24 09:23:00</t>
+          <t>2026-03-24 11:28:59</t>
         </is>
       </c>
     </row>
@@ -2569,7 +2569,7 @@
         <v>170</v>
       </c>
       <c r="AB11" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AC11" t="n">
         <v>10.5</v>
@@ -2581,22 +2581,22 @@
         <v>90</v>
       </c>
       <c r="AF11" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AG11" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH11" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AI11" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AJ11" t="n">
         <v>19.5</v>
       </c>
       <c r="AK11" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="AL11" t="n">
         <v>38</v>
@@ -2629,31 +2629,31 @@
         <v>7.6</v>
       </c>
       <c r="AV11" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AW11" t="n">
         <v>55</v>
       </c>
       <c r="AX11" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="AY11" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AZ11" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BB11" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BC11" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BD11" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BE11" t="n">
         <v>6</v>
@@ -2662,11 +2662,11 @@
         <v>8</v>
       </c>
       <c r="BG11" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-24 09:23:00</t>
+          <t>2026-03-24 11:28:59</t>
         </is>
       </c>
     </row>
@@ -2709,10 +2709,10 @@
         <v>4.9</v>
       </c>
       <c r="J12" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K12" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L12" t="n">
         <v>1.42</v>
@@ -2748,7 +2748,7 @@
         <v>1.27</v>
       </c>
       <c r="W12" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="X12" t="n">
         <v>17</v>
@@ -2826,7 +2826,7 @@
         <v>16</v>
       </c>
       <c r="AW12" t="n">
-        <v>50</v>
+        <v>5.3</v>
       </c>
       <c r="AX12" t="n">
         <v>10</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-24 09:23:00</t>
+          <t>2026-03-24 11:28:59</t>
         </is>
       </c>
     </row>
@@ -3054,14 +3054,14 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-24 09:23:00</t>
+          <t>2026-03-24 11:28:59</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Colombian Primera B</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3076,186 +3076,186 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Cerro</t>
+          <t>Envigado</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Juventud De Las Piedras</t>
+          <t>Bogota</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.15</v>
+        <v>1.46</v>
       </c>
       <c r="G14" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="H14" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="I14" t="n">
+        <v>12</v>
+      </c>
+      <c r="J14" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K14" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N14" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S14" t="n">
         <v>3.55</v>
       </c>
-      <c r="H14" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="I14" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="J14" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="K14" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="L14" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="M14" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="N14" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="O14" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="P14" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S14" t="n">
-        <v>5.3</v>
-      </c>
       <c r="T14" t="n">
-        <v>2.08</v>
+        <v>2.26</v>
       </c>
       <c r="U14" t="n">
-        <v>1.75</v>
+        <v>1.64</v>
       </c>
       <c r="V14" t="n">
-        <v>1.53</v>
+        <v>1.1</v>
       </c>
       <c r="W14" t="n">
-        <v>1.39</v>
+        <v>2.68</v>
       </c>
       <c r="X14" t="n">
-        <v>9.4</v>
+        <v>14.5</v>
       </c>
       <c r="Y14" t="n">
-        <v>970</v>
+        <v>26</v>
       </c>
       <c r="Z14" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AA14" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AB14" t="n">
-        <v>970</v>
+        <v>7.6</v>
       </c>
       <c r="AC14" t="n">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>970</v>
+        <v>40</v>
       </c>
       <c r="AE14" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AF14" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>36</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>15</v>
+      </c>
+      <c r="AK14" t="n">
         <v>22</v>
       </c>
-      <c r="AG14" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>950</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>80</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>75</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>60</v>
-      </c>
       <c r="AL14" t="n">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="AM14" t="n">
         <v>1000</v>
       </c>
       <c r="AN14" t="n">
-        <v>80</v>
+        <v>11.5</v>
       </c>
       <c r="AO14" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>6.4</v>
+        <v>1.03</v>
       </c>
       <c r="AQ14" t="n">
-        <v>4.2</v>
+        <v>1.03</v>
       </c>
       <c r="AR14" t="n">
-        <v>5.7</v>
+        <v>1.03</v>
       </c>
       <c r="AS14" t="n">
-        <v>1.78</v>
+        <v>1.03</v>
       </c>
       <c r="AT14" t="n">
-        <v>7.2</v>
+        <v>1.03</v>
       </c>
       <c r="AU14" t="n">
-        <v>6.2</v>
+        <v>7.6</v>
       </c>
       <c r="AV14" t="n">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AW14" t="n">
-        <v>2.76</v>
+        <v>1.03</v>
       </c>
       <c r="AX14" t="n">
-        <v>15.5</v>
+        <v>1.03</v>
       </c>
       <c r="AY14" t="n">
-        <v>11.5</v>
+        <v>8.4</v>
       </c>
       <c r="AZ14" t="n">
-        <v>17</v>
+        <v>1.03</v>
       </c>
       <c r="BA14" t="n">
-        <v>1.8</v>
+        <v>1.03</v>
       </c>
       <c r="BB14" t="n">
-        <v>2.82</v>
+        <v>1.03</v>
       </c>
       <c r="BC14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF14" t="n">
         <v>7.6</v>
       </c>
-      <c r="BD14" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>2.82</v>
-      </c>
       <c r="BG14" t="n">
-        <v>1.78</v>
+        <v>1.01</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-24 09:23:00</t>
+          <t>2026-03-24 11:28:59</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3265,191 +3265,191 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Deportivo Riestra</t>
+          <t>Cerro</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>San Lorenzo</t>
+          <t>Juventud De Las Piedras</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.52</v>
+        <v>3.15</v>
       </c>
       <c r="G15" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="K15" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q15" t="n">
         <v>2.62</v>
       </c>
-      <c r="H15" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="I15" t="n">
+      <c r="R15" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X15" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>970</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>55</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>48</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>950</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>75</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>60</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>90</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>80</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>55</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AQ15" t="n">
         <v>4.2</v>
       </c>
-      <c r="J15" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="K15" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="L15" t="n">
+      <c r="AR15" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA15" t="n">
         <v>1.8</v>
       </c>
-      <c r="M15" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="N15" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="O15" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="P15" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>3</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="S15" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="W15" t="n">
+      <c r="BB15" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BE15" t="n">
         <v>1.61</v>
       </c>
-      <c r="X15" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>26</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>130</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>24</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>130</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>17</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>48</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>230</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>44</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>65</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>160</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>590</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>90</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>250</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>7</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>38</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>19</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>38</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>25</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>48</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>23</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>28</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>44</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>55</v>
-      </c>
       <c r="BF15" t="n">
-        <v>32</v>
+        <v>2.82</v>
       </c>
       <c r="BG15" t="n">
-        <v>46</v>
+        <v>1.78</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-24 09:23:00</t>
+          <t>2026-03-24 11:28:59</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Colombian Primera B</t>
+          <t>Argentinian Primera Division</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3464,179 +3464,179 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Barranquilla</t>
+          <t>Deportivo Riestra</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Leones FC</t>
+          <t>San Lorenzo</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.04</v>
+        <v>2.62</v>
       </c>
       <c r="G16" t="n">
-        <v>1000</v>
+        <v>2.72</v>
       </c>
       <c r="H16" t="n">
-        <v>1.04</v>
+        <v>3.75</v>
       </c>
       <c r="I16" t="n">
-        <v>1000</v>
+        <v>4</v>
       </c>
       <c r="J16" t="n">
-        <v>1.03</v>
+        <v>2.72</v>
       </c>
       <c r="K16" t="n">
-        <v>1000</v>
+        <v>2.76</v>
       </c>
       <c r="L16" t="n">
         <v>1.01</v>
       </c>
       <c r="M16" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="N16" t="n">
-        <v>1.25</v>
+        <v>1.97</v>
       </c>
       <c r="O16" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="P16" t="n">
         <v>1.29</v>
       </c>
-      <c r="P16" t="n">
-        <v>1.24</v>
-      </c>
       <c r="Q16" t="n">
-        <v>1.29</v>
+        <v>3.85</v>
       </c>
       <c r="R16" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="S16" t="n">
-        <v>1.29</v>
+        <v>4</v>
       </c>
       <c r="T16" t="n">
-        <v>1.11</v>
+        <v>2.8</v>
       </c>
       <c r="U16" t="n">
-        <v>1.11</v>
+        <v>1.45</v>
       </c>
       <c r="V16" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="W16" t="n">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="X16" t="n">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="Y16" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="Z16" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AA16" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AB16" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="AC16" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="AD16" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AE16" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AF16" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AG16" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AH16" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AI16" t="n">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AK16" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AL16" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AM16" t="n">
-        <v>1000</v>
+        <v>590</v>
       </c>
       <c r="AN16" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AO16" t="n">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="AS16" t="n">
-        <v>1.01</v>
+        <v>38</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AV16" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.01</v>
+        <v>38</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.01</v>
+        <v>25</v>
       </c>
       <c r="BA16" t="n">
-        <v>1.01</v>
+        <v>46</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.01</v>
+        <v>24</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.01</v>
+        <v>28</v>
       </c>
       <c r="BD16" t="n">
-        <v>1.01</v>
+        <v>44</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.01</v>
+        <v>55</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="BG16" t="n">
-        <v>1.01</v>
+        <v>46</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-24 09:23:00</t>
+          <t>2026-03-24 11:28:59</t>
         </is>
       </c>
     </row>
@@ -3653,191 +3653,191 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Real Soacha Cundinamarca FC</t>
+          <t>Barranquilla</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Atletico FC Cali</t>
+          <t>Leones FC</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.57</v>
+        <v>1.82</v>
       </c>
       <c r="G17" t="n">
-        <v>1.7</v>
+        <v>2.14</v>
       </c>
       <c r="H17" t="n">
-        <v>6.2</v>
+        <v>3.7</v>
       </c>
       <c r="I17" t="n">
-        <v>9.199999999999999</v>
+        <v>5.6</v>
       </c>
       <c r="J17" t="n">
-        <v>3.4</v>
+        <v>3.05</v>
       </c>
       <c r="K17" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="L17" t="n">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="M17" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="N17" t="n">
-        <v>2.78</v>
+        <v>3</v>
       </c>
       <c r="O17" t="n">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="P17" t="n">
-        <v>1.67</v>
+        <v>1.78</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="R17" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="S17" t="n">
-        <v>3.9</v>
+        <v>3.1</v>
       </c>
       <c r="T17" t="n">
-        <v>2.16</v>
+        <v>1.77</v>
       </c>
       <c r="U17" t="n">
-        <v>1.68</v>
+        <v>1.92</v>
       </c>
       <c r="V17" t="n">
-        <v>1.12</v>
+        <v>1.21</v>
       </c>
       <c r="W17" t="n">
-        <v>2.42</v>
+        <v>1.87</v>
       </c>
       <c r="X17" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="Y17" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="Z17" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AA17" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AB17" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AC17" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AD17" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AE17" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AF17" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AG17" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH17" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI17" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AK17" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AL17" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AM17" t="n">
         <v>1000</v>
       </c>
       <c r="AN17" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AO17" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AP17" t="n">
-        <v>3.8</v>
+        <v>3.45</v>
       </c>
       <c r="AQ17" t="n">
-        <v>4.3</v>
+        <v>3.55</v>
       </c>
       <c r="AR17" t="n">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="AS17" t="n">
-        <v>2.02</v>
+        <v>4.2</v>
       </c>
       <c r="AT17" t="n">
         <v>3.1</v>
       </c>
       <c r="AU17" t="n">
-        <v>3.55</v>
+        <v>3.05</v>
       </c>
       <c r="AV17" t="n">
-        <v>4.6</v>
+        <v>3.65</v>
       </c>
       <c r="AW17" t="n">
-        <v>2.18</v>
+        <v>4.1</v>
       </c>
       <c r="AX17" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="AY17" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AZ17" t="n">
         <v>3.7</v>
       </c>
-      <c r="AZ17" t="n">
-        <v>4.6</v>
-      </c>
       <c r="BA17" t="n">
-        <v>2.18</v>
+        <v>4.1</v>
       </c>
       <c r="BB17" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BG17" t="n">
         <v>4.1</v>
       </c>
-      <c r="BC17" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>4</v>
-      </c>
-      <c r="BG17" t="n">
-        <v>2.02</v>
-      </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-24 09:23:00</t>
+          <t>2026-03-24 11:28:59</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>US United Soccer League</t>
+          <t>Paraguayan Primera Division</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3847,191 +3847,191 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>19:30:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Lexington SC</t>
+          <t>Guarani (Par)</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Club 2 de Mayo</t>
         </is>
       </c>
       <c r="F18" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="G18" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="I18" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K18" t="n">
+        <v>950</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N18" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="P18" t="n">
         <v>1.57</v>
       </c>
-      <c r="G18" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="H18" t="n">
-        <v>6</v>
-      </c>
-      <c r="I18" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="J18" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="K18" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="L18" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="M18" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N18" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="O18" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="P18" t="n">
-        <v>1.87</v>
-      </c>
       <c r="Q18" t="n">
-        <v>1.94</v>
+        <v>2.02</v>
       </c>
       <c r="R18" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="S18" t="n">
-        <v>3.05</v>
+        <v>3.55</v>
       </c>
       <c r="T18" t="n">
-        <v>1.95</v>
+        <v>1.11</v>
       </c>
       <c r="U18" t="n">
-        <v>1.86</v>
+        <v>1.11</v>
       </c>
       <c r="V18" t="n">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="W18" t="n">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="X18" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="Y18" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="Z18" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AA18" t="n">
         <v>1000</v>
       </c>
       <c r="AB18" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="AC18" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AD18" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AE18" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AF18" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AG18" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AH18" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AI18" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AJ18" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AK18" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AL18" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AM18" t="n">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AN18" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AO18" t="n">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AP18" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ18" t="n">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR18" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="AS18" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="AT18" t="n">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="AU18" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AV18" t="n">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW18" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="AX18" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AY18" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AZ18" t="n">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA18" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BB18" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC18" t="n">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="BD18" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BE18" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BF18" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BG18" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-24 09:23:00</t>
+          <t>2026-03-24 11:28:59</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Colombian Primera B</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4041,54 +4041,54 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Boston River</t>
+          <t>Real Soacha Cundinamarca FC</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Penarol</t>
+          <t>Atletico FC Cali</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>6.8</v>
+        <v>1.55</v>
       </c>
       <c r="G19" t="n">
-        <v>8.199999999999999</v>
+        <v>1.67</v>
       </c>
       <c r="H19" t="n">
-        <v>1.6</v>
+        <v>6.4</v>
       </c>
       <c r="I19" t="n">
-        <v>1.64</v>
+        <v>9.6</v>
       </c>
       <c r="J19" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="K19" t="n">
-        <v>4</v>
+        <v>4.9</v>
       </c>
       <c r="L19" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="M19" t="n">
         <v>1.09</v>
       </c>
       <c r="N19" t="n">
-        <v>3</v>
+        <v>2.78</v>
       </c>
       <c r="O19" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="P19" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="R19" t="n">
         <v>1.25</v>
@@ -4097,128 +4097,128 @@
         <v>3.9</v>
       </c>
       <c r="T19" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="U19" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="V19" t="n">
-        <v>2.52</v>
+        <v>1.12</v>
       </c>
       <c r="W19" t="n">
-        <v>1.14</v>
+        <v>2.48</v>
       </c>
       <c r="X19" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="Y19" t="n">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="Z19" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="AA19" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AB19" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AC19" t="n">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AD19" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AE19" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AF19" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AG19" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AH19" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AI19" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AJ19" t="n">
-        <v>300</v>
+        <v>1000</v>
       </c>
       <c r="AK19" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AL19" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AM19" t="n">
-        <v>230</v>
+        <v>1000</v>
       </c>
       <c r="AN19" t="n">
-        <v>260</v>
+        <v>1000</v>
       </c>
       <c r="AO19" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AP19" t="n">
-        <v>8.800000000000001</v>
+        <v>3.95</v>
       </c>
       <c r="AQ19" t="n">
-        <v>5.6</v>
+        <v>4.5</v>
       </c>
       <c r="AR19" t="n">
-        <v>7.4</v>
+        <v>3</v>
       </c>
       <c r="AS19" t="n">
-        <v>13.5</v>
+        <v>1.58</v>
       </c>
       <c r="AT19" t="n">
-        <v>16</v>
+        <v>3.2</v>
       </c>
       <c r="AU19" t="n">
-        <v>6.8</v>
+        <v>3.7</v>
       </c>
       <c r="AV19" t="n">
-        <v>8.800000000000001</v>
+        <v>4.9</v>
       </c>
       <c r="AW19" t="n">
-        <v>17</v>
+        <v>1.58</v>
       </c>
       <c r="AX19" t="n">
-        <v>8</v>
+        <v>3.55</v>
       </c>
       <c r="AY19" t="n">
-        <v>22</v>
+        <v>3.85</v>
       </c>
       <c r="AZ19" t="n">
-        <v>20</v>
+        <v>4.8</v>
       </c>
       <c r="BA19" t="n">
-        <v>36</v>
+        <v>1.58</v>
       </c>
       <c r="BB19" t="n">
-        <v>8.800000000000001</v>
+        <v>4.3</v>
       </c>
       <c r="BC19" t="n">
-        <v>8.6</v>
+        <v>4.5</v>
       </c>
       <c r="BD19" t="n">
-        <v>8.6</v>
+        <v>3.85</v>
       </c>
       <c r="BE19" t="n">
-        <v>8.800000000000001</v>
+        <v>1.58</v>
       </c>
       <c r="BF19" t="n">
-        <v>8.800000000000001</v>
+        <v>4.1</v>
       </c>
       <c r="BG19" t="n">
-        <v>10</v>
+        <v>1.59</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-24 09:23:00</t>
+          <t>2026-03-24 11:28:59</t>
         </is>
       </c>
     </row>
@@ -4235,191 +4235,191 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Sporting Club Jacksonville</t>
+          <t>Lexington SC</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Miami FC</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.64</v>
+        <v>1.57</v>
       </c>
       <c r="G20" t="n">
-        <v>2.88</v>
+        <v>1.71</v>
       </c>
       <c r="H20" t="n">
-        <v>2.66</v>
+        <v>6</v>
       </c>
       <c r="I20" t="n">
-        <v>2.94</v>
+        <v>8.6</v>
       </c>
       <c r="J20" t="n">
-        <v>3.35</v>
+        <v>3.9</v>
       </c>
       <c r="K20" t="n">
-        <v>3.8</v>
+        <v>4.6</v>
       </c>
       <c r="L20" t="n">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="M20" t="n">
         <v>1.07</v>
       </c>
       <c r="N20" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="O20" t="n">
         <v>1.31</v>
       </c>
       <c r="P20" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.89</v>
+        <v>1.94</v>
       </c>
       <c r="R20" t="n">
         <v>1.34</v>
       </c>
       <c r="S20" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="T20" t="n">
-        <v>1.73</v>
+        <v>1.95</v>
       </c>
       <c r="U20" t="n">
-        <v>2.12</v>
+        <v>1.84</v>
       </c>
       <c r="V20" t="n">
-        <v>1.51</v>
+        <v>1.14</v>
       </c>
       <c r="W20" t="n">
-        <v>1.55</v>
+        <v>2.4</v>
       </c>
       <c r="X20" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="Y20" t="n">
-        <v>13.5</v>
+        <v>950</v>
       </c>
       <c r="Z20" t="n">
+        <v>70</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>950</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>130</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>950</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>120</v>
+      </c>
+      <c r="AJ20" t="n">
         <v>970</v>
       </c>
-      <c r="AA20" t="n">
-        <v>48</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>970</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>36</v>
-      </c>
-      <c r="AF20" t="n">
+      <c r="AK20" t="n">
         <v>22</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>970</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>50</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>50</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>36</v>
       </c>
       <c r="AL20" t="n">
         <v>48</v>
       </c>
       <c r="AM20" t="n">
-        <v>110</v>
+        <v>180</v>
       </c>
       <c r="AN20" t="n">
-        <v>32</v>
+        <v>12.5</v>
       </c>
       <c r="AO20" t="n">
-        <v>30</v>
+        <v>180</v>
       </c>
       <c r="AP20" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AQ20" t="n">
-        <v>9</v>
+        <v>14.5</v>
       </c>
       <c r="AR20" t="n">
-        <v>14.5</v>
+        <v>4.1</v>
       </c>
       <c r="AS20" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="AT20" t="n">
-        <v>8.800000000000001</v>
+        <v>5.8</v>
       </c>
       <c r="AU20" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AV20" t="n">
-        <v>9.800000000000001</v>
+        <v>18.5</v>
       </c>
       <c r="AW20" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="AX20" t="n">
-        <v>14.5</v>
+        <v>7</v>
       </c>
       <c r="AY20" t="n">
-        <v>9.6</v>
+        <v>7.4</v>
       </c>
       <c r="AZ20" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BC20" t="n">
         <v>13</v>
       </c>
-      <c r="BA20" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>4.4</v>
-      </c>
       <c r="BD20" t="n">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="BE20" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="BF20" t="n">
-        <v>20</v>
+        <v>7.6</v>
       </c>
       <c r="BG20" t="n">
-        <v>19</v>
+        <v>4.2</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-24 09:23:00</t>
+          <t>2026-03-24 11:28:59</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4429,184 +4429,572 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>22:00:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>America de Cali S.A</t>
+          <t>Boston River</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Llaneros FC</t>
+          <t>Penarol</t>
         </is>
       </c>
       <c r="F21" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="G21" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H21" t="n">
         <v>1.6</v>
       </c>
-      <c r="G21" t="n">
+      <c r="I21" t="n">
         <v>1.64</v>
       </c>
-      <c r="H21" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="I21" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="J21" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K21" t="n">
         <v>4</v>
       </c>
-      <c r="K21" t="n">
-        <v>4.1</v>
-      </c>
       <c r="L21" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="M21" t="n">
         <v>1.09</v>
       </c>
       <c r="N21" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="O21" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="P21" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="R21" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="S21" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="T21" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="U21" t="n">
         <v>1.72</v>
       </c>
       <c r="V21" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="W21" t="n">
         <v>1.14</v>
       </c>
-      <c r="W21" t="n">
+      <c r="X21" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>17</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>20</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>22</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>65</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>30</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>28</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>50</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>300</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>160</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>160</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>230</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>260</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>16</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>17</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>22</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>36</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>10</v>
+      </c>
+      <c r="BH21" t="inlineStr">
+        <is>
+          <t>2026-03-24 11:28:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>US United Soccer League</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>20:30:00</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Sporting Club Jacksonville</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Miami FC</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="G22" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="I22" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="J22" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K22" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N22" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S22" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="X22" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>970</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>48</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>36</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>970</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>50</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>50</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>36</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>32</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>30</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>9</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>20</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>19</v>
+      </c>
+      <c r="BH22" t="inlineStr">
+        <is>
+          <t>2026-03-24 11:28:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Colombian Primera A</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>22:00:00</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>America de Cali S.A</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Llaneros FC</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="G23" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="H23" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="I23" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="J23" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K23" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N23" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S23" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="W23" t="n">
         <v>2.56</v>
       </c>
-      <c r="X21" t="n">
+      <c r="X23" t="n">
         <v>12</v>
       </c>
-      <c r="Y21" t="n">
+      <c r="Y23" t="n">
         <v>950</v>
       </c>
-      <c r="Z21" t="n">
+      <c r="Z23" t="n">
         <v>65</v>
       </c>
-      <c r="AA21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB21" t="n">
+      <c r="AA23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB23" t="n">
         <v>6.6</v>
       </c>
-      <c r="AC21" t="n">
+      <c r="AC23" t="n">
         <v>9</v>
       </c>
-      <c r="AD21" t="n">
+      <c r="AD23" t="n">
         <v>950</v>
       </c>
-      <c r="AE21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF21" t="n">
+      <c r="AE23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF23" t="n">
         <v>8.6</v>
       </c>
-      <c r="AG21" t="n">
+      <c r="AG23" t="n">
         <v>10.5</v>
       </c>
-      <c r="AH21" t="n">
+      <c r="AH23" t="n">
         <v>950</v>
       </c>
-      <c r="AI21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ21" t="n">
+      <c r="AI23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ23" t="n">
         <v>970</v>
       </c>
-      <c r="AK21" t="n">
+      <c r="AK23" t="n">
         <v>21</v>
       </c>
-      <c r="AL21" t="n">
+      <c r="AL23" t="n">
         <v>50</v>
       </c>
-      <c r="AM21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN21" t="n">
+      <c r="AM23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN23" t="n">
         <v>15</v>
       </c>
-      <c r="AO21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP21" t="n">
+      <c r="AO23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP23" t="n">
         <v>10</v>
       </c>
-      <c r="AQ21" t="n">
+      <c r="AQ23" t="n">
         <v>7.4</v>
       </c>
-      <c r="AR21" t="n">
+      <c r="AR23" t="n">
         <v>10</v>
       </c>
-      <c r="AS21" t="n">
+      <c r="AS23" t="n">
         <v>11.5</v>
       </c>
-      <c r="AT21" t="n">
+      <c r="AT23" t="n">
         <v>5.9</v>
       </c>
-      <c r="AU21" t="n">
+      <c r="AU23" t="n">
         <v>7.8</v>
       </c>
-      <c r="AV21" t="n">
+      <c r="AV23" t="n">
         <v>25</v>
       </c>
-      <c r="AW21" t="n">
+      <c r="AW23" t="n">
         <v>11</v>
       </c>
-      <c r="AX21" t="n">
+      <c r="AX23" t="n">
         <v>7.6</v>
       </c>
-      <c r="AY21" t="n">
+      <c r="AY23" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AZ21" t="n">
+      <c r="AZ23" t="n">
         <v>23</v>
       </c>
-      <c r="BA21" t="n">
+      <c r="BA23" t="n">
         <v>11</v>
       </c>
-      <c r="BB21" t="n">
+      <c r="BB23" t="n">
         <v>6.6</v>
       </c>
-      <c r="BC21" t="n">
+      <c r="BC23" t="n">
         <v>7.6</v>
       </c>
-      <c r="BD21" t="n">
+      <c r="BD23" t="n">
         <v>9.6</v>
       </c>
-      <c r="BE21" t="n">
+      <c r="BE23" t="n">
         <v>11.5</v>
       </c>
-      <c r="BF21" t="n">
+      <c r="BF23" t="n">
         <v>10.5</v>
       </c>
-      <c r="BG21" t="n">
+      <c r="BG23" t="n">
         <v>11.5</v>
       </c>
-      <c r="BH21" t="inlineStr">
-        <is>
-          <t>2026-03-24 09:23:00</t>
+      <c r="BH23" t="inlineStr">
+        <is>
+          <t>2026-03-24 11:28:59</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-25.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH23"/>
+  <dimension ref="A1:BH27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,58 +757,58 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3.65</v>
+        <v>1.03</v>
       </c>
       <c r="G2" t="n">
-        <v>44</v>
+        <v>990</v>
       </c>
       <c r="H2" t="n">
-        <v>1.85</v>
+        <v>1.01</v>
       </c>
       <c r="I2" t="n">
-        <v>2.14</v>
+        <v>990</v>
       </c>
       <c r="J2" t="n">
-        <v>3</v>
+        <v>1.04</v>
       </c>
       <c r="K2" t="n">
-        <v>5.1</v>
+        <v>950</v>
       </c>
       <c r="L2" t="n">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="M2" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N2" t="n">
-        <v>2.84</v>
+        <v>1.26</v>
       </c>
       <c r="O2" t="n">
-        <v>1.39</v>
+        <v>1.07</v>
       </c>
       <c r="P2" t="n">
-        <v>1.69</v>
+        <v>1.25</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.02</v>
+        <v>1.06</v>
       </c>
       <c r="R2" t="n">
         <v>1.18</v>
       </c>
       <c r="S2" t="n">
-        <v>2.02</v>
+        <v>1.36</v>
       </c>
       <c r="T2" t="n">
         <v>1.11</v>
       </c>
       <c r="U2" t="n">
-        <v>1.11</v>
+        <v>1.66</v>
       </c>
       <c r="V2" t="n">
-        <v>1.87</v>
+        <v>1.01</v>
       </c>
       <c r="W2" t="n">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="X2" t="n">
         <v>1000</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-24 11:28:59</t>
+          <t>2026-03-24 13:35:31</t>
         </is>
       </c>
     </row>
@@ -942,179 +942,179 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Altinordu</t>
+          <t>Beyoglu Yeni Carsi</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Kastamonuspor</t>
+          <t>Muglaspor</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.44</v>
+        <v>5</v>
       </c>
       <c r="G3" t="n">
-        <v>2.78</v>
+        <v>7.8</v>
       </c>
       <c r="H3" t="n">
-        <v>2.82</v>
+        <v>1.7</v>
       </c>
       <c r="I3" t="n">
-        <v>3.25</v>
+        <v>1.86</v>
       </c>
       <c r="J3" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="K3" t="n">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="L3" t="n">
-        <v>1.41</v>
+        <v>1.49</v>
       </c>
       <c r="M3" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N3" t="n">
-        <v>3.45</v>
+        <v>2.72</v>
       </c>
       <c r="O3" t="n">
-        <v>1.32</v>
+        <v>1.44</v>
       </c>
       <c r="P3" t="n">
-        <v>1.85</v>
+        <v>1.62</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.96</v>
+        <v>2.3</v>
       </c>
       <c r="R3" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="S3" t="n">
-        <v>3.45</v>
+        <v>4</v>
       </c>
       <c r="T3" t="n">
-        <v>1.74</v>
+        <v>2.12</v>
       </c>
       <c r="U3" t="n">
-        <v>2.1</v>
+        <v>1.72</v>
       </c>
       <c r="V3" t="n">
-        <v>1.44</v>
+        <v>2.16</v>
       </c>
       <c r="W3" t="n">
-        <v>1.56</v>
+        <v>1.16</v>
       </c>
       <c r="X3" t="n">
-        <v>16.5</v>
+        <v>12.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>14.5</v>
+        <v>7.8</v>
       </c>
       <c r="Z3" t="n">
-        <v>25</v>
+        <v>11.5</v>
       </c>
       <c r="AA3" t="n">
+        <v>23</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>28</v>
+      </c>
+      <c r="AF3" t="n">
         <v>60</v>
       </c>
-      <c r="AB3" t="n">
-        <v>13</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>16</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>44</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>21</v>
-      </c>
       <c r="AG3" t="n">
-        <v>14.5</v>
+        <v>30</v>
       </c>
       <c r="AH3" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="AI3" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AJ3" t="n">
-        <v>46</v>
+        <v>250</v>
       </c>
       <c r="AK3" t="n">
-        <v>36</v>
+        <v>140</v>
       </c>
       <c r="AL3" t="n">
-        <v>55</v>
+        <v>150</v>
       </c>
       <c r="AM3" t="n">
-        <v>120</v>
+        <v>240</v>
       </c>
       <c r="AN3" t="n">
-        <v>30</v>
+        <v>230</v>
       </c>
       <c r="AO3" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="AP3" t="n">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AQ3" t="n">
-        <v>8.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AR3" t="n">
-        <v>15</v>
+        <v>1.03</v>
       </c>
       <c r="AS3" t="n">
-        <v>4.1</v>
+        <v>1.03</v>
       </c>
       <c r="AT3" t="n">
-        <v>7.8</v>
+        <v>1.03</v>
       </c>
       <c r="AU3" t="n">
-        <v>5.9</v>
+        <v>1.03</v>
       </c>
       <c r="AV3" t="n">
-        <v>9.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AW3" t="n">
-        <v>4</v>
+        <v>1.03</v>
       </c>
       <c r="AX3" t="n">
-        <v>12.5</v>
+        <v>1.03</v>
       </c>
       <c r="AY3" t="n">
-        <v>8.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AZ3" t="n">
-        <v>12.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA3" t="n">
-        <v>4.1</v>
+        <v>1.03</v>
       </c>
       <c r="BB3" t="n">
-        <v>4</v>
+        <v>1.03</v>
       </c>
       <c r="BC3" t="n">
-        <v>21</v>
+        <v>1.03</v>
       </c>
       <c r="BD3" t="n">
-        <v>4</v>
+        <v>1.03</v>
       </c>
       <c r="BE3" t="n">
-        <v>4.2</v>
+        <v>1.03</v>
       </c>
       <c r="BF3" t="n">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG3" t="n">
-        <v>3.95</v>
+        <v>1.01</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-24 11:28:59</t>
+          <t>2026-03-24 13:35:31</t>
         </is>
       </c>
     </row>
@@ -1131,60 +1131,60 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Ankaragucu</t>
+          <t>Altinordu</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ankaraspor</t>
+          <t>Kastamonuspor</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.09</v>
+        <v>2.26</v>
       </c>
       <c r="G4" t="n">
-        <v>600</v>
+        <v>2.86</v>
       </c>
       <c r="H4" t="n">
-        <v>1.09</v>
+        <v>2.78</v>
       </c>
       <c r="I4" t="n">
-        <v>1000</v>
+        <v>3.85</v>
       </c>
       <c r="J4" t="n">
-        <v>1.1</v>
+        <v>2.92</v>
       </c>
       <c r="K4" t="n">
-        <v>950</v>
+        <v>3.75</v>
       </c>
       <c r="L4" t="n">
         <v>1.01</v>
       </c>
       <c r="M4" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N4" t="n">
-        <v>1.1</v>
+        <v>3.45</v>
       </c>
       <c r="O4" t="n">
-        <v>1.06</v>
+        <v>1.32</v>
       </c>
       <c r="P4" t="n">
-        <v>1.24</v>
+        <v>1.85</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.29</v>
+        <v>1.96</v>
       </c>
       <c r="R4" t="n">
-        <v>1.18</v>
+        <v>1.32</v>
       </c>
       <c r="S4" t="n">
-        <v>1.28</v>
+        <v>3.45</v>
       </c>
       <c r="T4" t="n">
         <v>1.11</v>
@@ -1193,129 +1193,129 @@
         <v>1.11</v>
       </c>
       <c r="V4" t="n">
-        <v>1.02</v>
+        <v>1.36</v>
       </c>
       <c r="W4" t="n">
-        <v>1.02</v>
+        <v>1.55</v>
       </c>
       <c r="X4" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AA4" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AB4" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AC4" t="n">
         <v>1000</v>
       </c>
       <c r="AD4" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AE4" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AF4" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AG4" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI4" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AK4" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AL4" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM4" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AN4" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AO4" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.01</v>
+        <v>2.52</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.01</v>
+        <v>2.46</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.01</v>
+        <v>2.66</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.01</v>
+        <v>2.84</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.01</v>
+        <v>2.42</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.01</v>
+        <v>2.96</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.01</v>
+        <v>2.52</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.01</v>
+        <v>2.78</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.01</v>
+        <v>2.6</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.01</v>
+        <v>2.46</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.01</v>
+        <v>2.6</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.01</v>
+        <v>2.84</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.01</v>
+        <v>2.8</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.01</v>
+        <v>2.74</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.01</v>
+        <v>2.82</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.01</v>
+        <v>2.9</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.01</v>
+        <v>2.7</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.01</v>
+        <v>2.76</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-24 11:28:59</t>
+          <t>2026-03-24 13:35:31</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Algerian Ligue 1</t>
+          <t>Turkish 2 Lig</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1325,102 +1325,102 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>13:45:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Belouizdad</t>
+          <t>Karacabey Belediyespor AS</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Karaman Belediyespor</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.8</v>
+        <v>1.11</v>
       </c>
       <c r="G5" t="n">
-        <v>3.2</v>
+        <v>1.29</v>
       </c>
       <c r="H5" t="n">
-        <v>2.96</v>
+        <v>13.5</v>
       </c>
       <c r="I5" t="n">
-        <v>3.45</v>
+        <v>1000</v>
       </c>
       <c r="J5" t="n">
-        <v>2.64</v>
+        <v>6.4</v>
       </c>
       <c r="K5" t="n">
-        <v>3.05</v>
+        <v>40</v>
       </c>
       <c r="L5" t="n">
-        <v>1.67</v>
+        <v>1.01</v>
       </c>
       <c r="M5" t="n">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>2.16</v>
+        <v>2.4</v>
       </c>
       <c r="O5" t="n">
-        <v>1.69</v>
+        <v>1.15</v>
       </c>
       <c r="P5" t="n">
-        <v>1.38</v>
+        <v>2.4</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.1</v>
+        <v>1.35</v>
       </c>
       <c r="R5" t="n">
-        <v>1.13</v>
+        <v>1.57</v>
       </c>
       <c r="S5" t="n">
-        <v>6.2</v>
+        <v>1.94</v>
       </c>
       <c r="T5" t="n">
-        <v>2.3</v>
+        <v>1.01</v>
       </c>
       <c r="U5" t="n">
-        <v>1.62</v>
+        <v>1.01</v>
       </c>
       <c r="V5" t="n">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="W5" t="n">
-        <v>1.45</v>
+        <v>4.4</v>
       </c>
       <c r="X5" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="Y5" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="Z5" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AA5" t="n">
         <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="AC5" t="n">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="AD5" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AE5" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AF5" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AG5" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AH5" t="n">
         <v>1000</v>
@@ -1447,69 +1447,69 @@
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>5.1</v>
+        <v>1.03</v>
       </c>
       <c r="AQ5" t="n">
-        <v>5.9</v>
+        <v>1.03</v>
       </c>
       <c r="AR5" t="n">
-        <v>14</v>
+        <v>1.03</v>
       </c>
       <c r="AS5" t="n">
-        <v>6.8</v>
+        <v>1.03</v>
       </c>
       <c r="AT5" t="n">
-        <v>3.85</v>
+        <v>1.03</v>
       </c>
       <c r="AU5" t="n">
-        <v>5.2</v>
+        <v>1.03</v>
       </c>
       <c r="AV5" t="n">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="AW5" t="n">
-        <v>6.8</v>
+        <v>1.03</v>
       </c>
       <c r="AX5" t="n">
-        <v>13</v>
+        <v>1.03</v>
       </c>
       <c r="AY5" t="n">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="AZ5" t="n">
-        <v>20</v>
+        <v>1.03</v>
       </c>
       <c r="BA5" t="n">
-        <v>7.2</v>
+        <v>1.03</v>
       </c>
       <c r="BB5" t="n">
-        <v>6.8</v>
+        <v>1.03</v>
       </c>
       <c r="BC5" t="n">
-        <v>6.6</v>
+        <v>1.03</v>
       </c>
       <c r="BD5" t="n">
-        <v>7.2</v>
+        <v>1.03</v>
       </c>
       <c r="BE5" t="n">
-        <v>7.4</v>
+        <v>1.03</v>
       </c>
       <c r="BF5" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BG5" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-24 11:28:59</t>
+          <t>2026-03-24 13:35:31</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Turkish 2 Lig</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1519,191 +1519,191 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Albion FC</t>
+          <t>Batman Petrolspor</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Wanderers (Uru)</t>
+          <t>Sanliurfaspor</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.56</v>
+        <v>1.48</v>
       </c>
       <c r="G6" t="n">
-        <v>2.94</v>
+        <v>1.67</v>
       </c>
       <c r="H6" t="n">
-        <v>3.1</v>
+        <v>5.5</v>
       </c>
       <c r="I6" t="n">
-        <v>3.55</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J6" t="n">
-        <v>2.66</v>
+        <v>3.75</v>
       </c>
       <c r="K6" t="n">
-        <v>3.2</v>
+        <v>5.1</v>
       </c>
       <c r="L6" t="n">
-        <v>1.51</v>
+        <v>1.33</v>
       </c>
       <c r="M6" t="n">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="N6" t="n">
-        <v>2.5</v>
+        <v>3.95</v>
       </c>
       <c r="O6" t="n">
-        <v>1.57</v>
+        <v>1.25</v>
       </c>
       <c r="P6" t="n">
-        <v>1.51</v>
+        <v>2.02</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.54</v>
+        <v>1.73</v>
       </c>
       <c r="R6" t="n">
-        <v>1.18</v>
+        <v>1.41</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>2.88</v>
       </c>
       <c r="T6" t="n">
-        <v>2.08</v>
+        <v>1.84</v>
       </c>
       <c r="U6" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="V6" t="n">
-        <v>1.39</v>
+        <v>1.12</v>
       </c>
       <c r="W6" t="n">
-        <v>1.51</v>
+        <v>2.42</v>
       </c>
       <c r="X6" t="n">
-        <v>8.800000000000001</v>
+        <v>22</v>
       </c>
       <c r="Y6" t="n">
-        <v>970</v>
+        <v>29</v>
       </c>
       <c r="Z6" t="n">
-        <v>22</v>
+        <v>75</v>
       </c>
       <c r="AA6" t="n">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="AB6" t="n">
-        <v>8.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>970</v>
+        <v>12.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>970</v>
+        <v>32</v>
       </c>
       <c r="AE6" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AF6" t="n">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="AG6" t="n">
-        <v>970</v>
+        <v>12</v>
       </c>
       <c r="AH6" t="n">
-        <v>950</v>
+        <v>28</v>
       </c>
       <c r="AI6" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AK6" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AL6" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AM6" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AN6" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AO6" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AP6" t="n">
-        <v>6.4</v>
+        <v>1.03</v>
       </c>
       <c r="AQ6" t="n">
-        <v>7.2</v>
+        <v>1.03</v>
       </c>
       <c r="AR6" t="n">
-        <v>3.05</v>
+        <v>1.03</v>
       </c>
       <c r="AS6" t="n">
-        <v>8.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AT6" t="n">
-        <v>6.2</v>
+        <v>1.03</v>
       </c>
       <c r="AU6" t="n">
-        <v>5.7</v>
+        <v>1.03</v>
       </c>
       <c r="AV6" t="n">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="AW6" t="n">
-        <v>8</v>
+        <v>1.03</v>
       </c>
       <c r="AX6" t="n">
-        <v>6</v>
+        <v>1.03</v>
       </c>
       <c r="AY6" t="n">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AZ6" t="n">
-        <v>6.6</v>
+        <v>1.03</v>
       </c>
       <c r="BA6" t="n">
-        <v>2.14</v>
+        <v>1.03</v>
       </c>
       <c r="BB6" t="n">
-        <v>3.35</v>
+        <v>1.03</v>
       </c>
       <c r="BC6" t="n">
-        <v>7.6</v>
+        <v>1.03</v>
       </c>
       <c r="BD6" t="n">
-        <v>3.4</v>
+        <v>1.03</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.92</v>
+        <v>1.03</v>
       </c>
       <c r="BF6" t="n">
-        <v>3.35</v>
+        <v>1.01</v>
       </c>
       <c r="BG6" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-24 11:28:59</t>
+          <t>2026-03-24 13:35:31</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Algerian Ligue 1</t>
+          <t>Turkish 2 Lig</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1713,191 +1713,191 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Ankaragucu</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Kabylie</t>
+          <t>Ankaraspor</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="G7" t="n">
-        <v>2.08</v>
+        <v>2.24</v>
       </c>
       <c r="H7" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="I7" t="n">
         <v>4.7</v>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K7" t="n">
+        <v>4</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N7" t="n">
+        <v>3</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>950</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AU7" t="n">
         <v>6</v>
       </c>
-      <c r="J7" t="n">
-        <v>3</v>
-      </c>
-      <c r="K7" t="n">
+      <c r="AV7" t="n">
         <v>3.5</v>
       </c>
-      <c r="L7" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="N7" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="P7" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S7" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="X7" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AQ7" t="n">
+      <c r="AW7" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AX7" t="n">
         <v>9.4</v>
       </c>
-      <c r="AR7" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AX7" t="n">
+      <c r="AY7" t="n">
         <v>7.8</v>
       </c>
-      <c r="AY7" t="n">
-        <v>8.4</v>
-      </c>
       <c r="AZ7" t="n">
-        <v>1.8</v>
+        <v>3.6</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.79</v>
+        <v>4</v>
       </c>
       <c r="BB7" t="n">
-        <v>5.9</v>
+        <v>3.75</v>
       </c>
       <c r="BC7" t="n">
-        <v>6</v>
+        <v>3.65</v>
       </c>
       <c r="BD7" t="n">
-        <v>7</v>
+        <v>3.9</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.5</v>
+        <v>4.1</v>
       </c>
       <c r="BF7" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="BG7" t="n">
-        <v>1.68</v>
+        <v>4</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-24 11:28:59</t>
+          <t>2026-03-24 13:35:31</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>English National League</t>
+          <t>Algerian Ligue 1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1907,191 +1907,191 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>16:45:00</t>
+          <t>13:45:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Morecambe</t>
+          <t>Belouizdad</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hartlepool</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3.15</v>
+        <v>2.8</v>
       </c>
       <c r="G8" t="n">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="H8" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="I8" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="K8" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="N8" t="n">
         <v>2.16</v>
       </c>
-      <c r="I8" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="J8" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="K8" t="n">
+      <c r="O8" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="S8" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="X8" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>34</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>75</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>70</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>14</v>
+      </c>
+      <c r="AS8" t="n">
         <v>4.2</v>
       </c>
-      <c r="L8" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N8" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="P8" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="T8" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="U8" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="X8" t="n">
-        <v>950</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>970</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>970</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>38</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>970</v>
-      </c>
-      <c r="AC8" t="n">
+      <c r="AT8" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY8" t="n">
         <v>11</v>
       </c>
-      <c r="AD8" t="n">
-        <v>970</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>28</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>26</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>950</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>970</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>34</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>65</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>36</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>42</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>90</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>32</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>970</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>21</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>17</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>5</v>
-      </c>
-      <c r="AY8" t="n">
+      <c r="AZ8" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA8" t="n">
         <v>4.3</v>
       </c>
-      <c r="AZ8" t="n">
-        <v>12</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>23</v>
-      </c>
       <c r="BB8" t="n">
-        <v>5.6</v>
+        <v>4.2</v>
       </c>
       <c r="BC8" t="n">
-        <v>5.3</v>
+        <v>4.1</v>
       </c>
       <c r="BD8" t="n">
-        <v>5.4</v>
+        <v>4.2</v>
       </c>
       <c r="BE8" t="n">
-        <v>5.8</v>
+        <v>4.3</v>
       </c>
       <c r="BF8" t="n">
-        <v>5.2</v>
+        <v>4.2</v>
       </c>
       <c r="BG8" t="n">
-        <v>11</v>
+        <v>4.2</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-24 11:28:59</t>
+          <t>2026-03-24 13:35:31</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>English National League</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2101,191 +2101,191 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>16:45:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Scunthorpe</t>
+          <t>Albion FC</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>Wanderers (Uru)</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.5</v>
+        <v>2.64</v>
       </c>
       <c r="G9" t="n">
-        <v>4</v>
+        <v>2.86</v>
       </c>
       <c r="H9" t="n">
-        <v>2.14</v>
+        <v>3.25</v>
       </c>
       <c r="I9" t="n">
-        <v>2.24</v>
+        <v>3.55</v>
       </c>
       <c r="J9" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="K9" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="X9" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>22</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>950</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>7</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW9" t="n">
         <v>3.55</v>
       </c>
-      <c r="K9" t="n">
-        <v>4</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N9" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="P9" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S9" t="n">
-        <v>3</v>
-      </c>
-      <c r="T9" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="U9" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="X9" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>11</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>15</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>27</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>18</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>9</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>11</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>23</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>29</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>16</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>36</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>70</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>44</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>50</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>85</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>40</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AS9" t="n">
+      <c r="AX9" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>7</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BF9" t="n">
         <v>6.8</v>
       </c>
-      <c r="AT9" t="n">
-        <v>13</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>9</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>22</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>14</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>32</v>
-      </c>
       <c r="BG9" t="n">
-        <v>12.5</v>
+        <v>7</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-24 11:28:59</t>
+          <t>2026-03-24 13:35:31</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>English National League</t>
+          <t>Algerian Ligue 1</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2295,105 +2295,105 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>16:45:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Truro City</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Solihull Moors</t>
+          <t>Kabylie</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.64</v>
+        <v>1.91</v>
       </c>
       <c r="G10" t="n">
-        <v>2.86</v>
+        <v>2.1</v>
       </c>
       <c r="H10" t="n">
-        <v>2.56</v>
+        <v>4.8</v>
       </c>
       <c r="I10" t="n">
-        <v>2.82</v>
+        <v>5.7</v>
       </c>
       <c r="J10" t="n">
-        <v>3.65</v>
+        <v>3</v>
       </c>
       <c r="K10" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="L10" t="n">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="M10" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="N10" t="n">
-        <v>3.9</v>
+        <v>2.5</v>
       </c>
       <c r="O10" t="n">
-        <v>1.3</v>
+        <v>1.53</v>
       </c>
       <c r="P10" t="n">
-        <v>1.94</v>
+        <v>1.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.89</v>
+        <v>2.4</v>
       </c>
       <c r="R10" t="n">
-        <v>1.37</v>
+        <v>1.18</v>
       </c>
       <c r="S10" t="n">
-        <v>3.25</v>
+        <v>4.8</v>
       </c>
       <c r="T10" t="n">
-        <v>1.7</v>
+        <v>2.18</v>
       </c>
       <c r="U10" t="n">
-        <v>2.16</v>
+        <v>1.66</v>
       </c>
       <c r="V10" t="n">
-        <v>1.54</v>
+        <v>1.21</v>
       </c>
       <c r="W10" t="n">
-        <v>1.54</v>
+        <v>1.9</v>
       </c>
       <c r="X10" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Y10" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Z10" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AA10" t="n">
         <v>1000</v>
       </c>
       <c r="AB10" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AC10" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AD10" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AE10" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AF10" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AG10" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AH10" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AI10" t="n">
         <v>1000</v>
@@ -2417,62 +2417,62 @@
         <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AQ10" t="n">
         <v>9.4</v>
       </c>
       <c r="AR10" t="n">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="AS10" t="n">
-        <v>5.3</v>
+        <v>1.59</v>
       </c>
       <c r="AT10" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="AU10" t="n">
-        <v>7.2</v>
+        <v>5.7</v>
       </c>
       <c r="AV10" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="AW10" t="n">
-        <v>5</v>
+        <v>1.58</v>
       </c>
       <c r="AX10" t="n">
-        <v>6</v>
+        <v>7.8</v>
       </c>
       <c r="AY10" t="n">
-        <v>10.5</v>
+        <v>8.4</v>
       </c>
       <c r="AZ10" t="n">
-        <v>13.5</v>
+        <v>6.2</v>
       </c>
       <c r="BA10" t="n">
-        <v>7.2</v>
+        <v>1.65</v>
       </c>
       <c r="BB10" t="n">
-        <v>3.4</v>
+        <v>6.4</v>
       </c>
       <c r="BC10" t="n">
-        <v>5.1</v>
+        <v>6.6</v>
       </c>
       <c r="BD10" t="n">
-        <v>7.4</v>
+        <v>2.38</v>
       </c>
       <c r="BE10" t="n">
-        <v>5.7</v>
+        <v>1.59</v>
       </c>
       <c r="BF10" t="n">
-        <v>5</v>
+        <v>6.2</v>
       </c>
       <c r="BG10" t="n">
-        <v>4.8</v>
+        <v>1.59</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-24 11:28:59</t>
+          <t>2026-03-24 13:35:31</t>
         </is>
       </c>
     </row>
@@ -2494,179 +2494,179 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Southend</t>
+          <t>Morecambe</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Woking</t>
+          <t>Hartlepool</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.67</v>
+        <v>3.25</v>
       </c>
       <c r="G11" t="n">
-        <v>1.75</v>
+        <v>3.75</v>
       </c>
       <c r="H11" t="n">
-        <v>5.4</v>
+        <v>2.22</v>
       </c>
       <c r="I11" t="n">
-        <v>6.6</v>
+        <v>2.4</v>
       </c>
       <c r="J11" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="K11" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="L11" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="M11" t="n">
         <v>1.05</v>
       </c>
       <c r="N11" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="O11" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="P11" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="R11" t="n">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="S11" t="n">
-        <v>2.96</v>
+        <v>2.74</v>
       </c>
       <c r="T11" t="n">
-        <v>1.79</v>
+        <v>1.63</v>
       </c>
       <c r="U11" t="n">
-        <v>2.02</v>
+        <v>2.32</v>
       </c>
       <c r="V11" t="n">
-        <v>1.2</v>
+        <v>1.71</v>
       </c>
       <c r="W11" t="n">
-        <v>2.32</v>
+        <v>1.37</v>
       </c>
       <c r="X11" t="n">
-        <v>20</v>
+        <v>950</v>
       </c>
       <c r="Y11" t="n">
-        <v>25</v>
+        <v>970</v>
       </c>
       <c r="Z11" t="n">
-        <v>55</v>
+        <v>970</v>
       </c>
       <c r="AA11" t="n">
-        <v>170</v>
+        <v>30</v>
       </c>
       <c r="AB11" t="n">
-        <v>9.6</v>
+        <v>970</v>
       </c>
       <c r="AC11" t="n">
-        <v>10.5</v>
+        <v>970</v>
       </c>
       <c r="AD11" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>23</v>
+      </c>
+      <c r="AF11" t="n">
         <v>26</v>
       </c>
-      <c r="AE11" t="n">
-        <v>90</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>12</v>
-      </c>
       <c r="AG11" t="n">
-        <v>10.5</v>
+        <v>970</v>
       </c>
       <c r="AH11" t="n">
-        <v>22</v>
+        <v>970</v>
       </c>
       <c r="AI11" t="n">
+        <v>34</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>60</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>36</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>42</v>
+      </c>
+      <c r="AM11" t="n">
         <v>85</v>
       </c>
-      <c r="AJ11" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>38</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>120</v>
-      </c>
       <c r="AN11" t="n">
-        <v>10.5</v>
+        <v>28</v>
       </c>
       <c r="AO11" t="n">
-        <v>100</v>
+        <v>970</v>
       </c>
       <c r="AP11" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AQ11" t="n">
-        <v>16.5</v>
+        <v>5</v>
       </c>
       <c r="AR11" t="n">
-        <v>38</v>
+        <v>5.5</v>
       </c>
       <c r="AS11" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AW11" t="n">
         <v>6</v>
       </c>
-      <c r="AT11" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>17</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>55</v>
-      </c>
       <c r="AX11" t="n">
-        <v>8.4</v>
+        <v>6.2</v>
       </c>
       <c r="AY11" t="n">
-        <v>8.4</v>
+        <v>5.4</v>
       </c>
       <c r="AZ11" t="n">
-        <v>15.5</v>
+        <v>5.6</v>
       </c>
       <c r="BA11" t="n">
-        <v>5.8</v>
+        <v>3.5</v>
       </c>
       <c r="BB11" t="n">
-        <v>13</v>
+        <v>7.4</v>
       </c>
       <c r="BC11" t="n">
-        <v>13.5</v>
+        <v>2.46</v>
       </c>
       <c r="BD11" t="n">
-        <v>5.4</v>
+        <v>3.6</v>
       </c>
       <c r="BE11" t="n">
-        <v>6</v>
+        <v>3.05</v>
       </c>
       <c r="BF11" t="n">
-        <v>8</v>
+        <v>6.4</v>
       </c>
       <c r="BG11" t="n">
-        <v>5.9</v>
+        <v>5.3</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-24 11:28:59</t>
+          <t>2026-03-24 13:35:31</t>
         </is>
       </c>
     </row>
@@ -2688,179 +2688,179 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Wealdstone</t>
+          <t>Truro City</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Yeovil</t>
+          <t>Solihull Moors</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.9</v>
+        <v>2.78</v>
       </c>
       <c r="G12" t="n">
-        <v>2.02</v>
+        <v>2.84</v>
       </c>
       <c r="H12" t="n">
-        <v>4.3</v>
+        <v>2.58</v>
       </c>
       <c r="I12" t="n">
-        <v>4.9</v>
+        <v>2.76</v>
       </c>
       <c r="J12" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="K12" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="L12" t="n">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="M12" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N12" t="n">
-        <v>3.55</v>
+        <v>3.85</v>
       </c>
       <c r="O12" t="n">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="P12" t="n">
-        <v>1.86</v>
+        <v>1.95</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.99</v>
+        <v>1.88</v>
       </c>
       <c r="R12" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="S12" t="n">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="T12" t="n">
-        <v>1.84</v>
+        <v>1.7</v>
       </c>
       <c r="U12" t="n">
-        <v>2.02</v>
+        <v>2.12</v>
       </c>
       <c r="V12" t="n">
-        <v>1.27</v>
+        <v>1.59</v>
       </c>
       <c r="W12" t="n">
-        <v>2</v>
+        <v>1.54</v>
       </c>
       <c r="X12" t="n">
+        <v>970</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>970</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>30</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>950</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>13</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>21</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>30</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BG12" t="n">
         <v>17</v>
       </c>
-      <c r="Y12" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>40</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>110</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>19</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>60</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>65</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>27</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>24</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>38</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>140</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>15</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>70</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>10</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>5</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>16</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>10</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>20</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>5</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>55</v>
-      </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-24 11:28:59</t>
+          <t>2026-03-24 13:35:31</t>
         </is>
       </c>
     </row>
@@ -2882,186 +2882,186 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Tamworth FC</t>
+          <t>Scunthorpe</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Forest Green</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="F13" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="G13" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="I13" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="J13" t="n">
         <v>3.55</v>
       </c>
-      <c r="G13" t="n">
-        <v>4</v>
-      </c>
-      <c r="H13" t="n">
-        <v>2</v>
-      </c>
-      <c r="I13" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="J13" t="n">
-        <v>3.85</v>
-      </c>
       <c r="K13" t="n">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="L13" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N13" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="O13" t="n">
         <v>1.27</v>
       </c>
-      <c r="M13" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N13" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O13" t="n">
-        <v>1.23</v>
-      </c>
       <c r="P13" t="n">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="R13" t="n">
-        <v>1.49</v>
+        <v>1.41</v>
       </c>
       <c r="S13" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="T13" t="n">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="U13" t="n">
-        <v>2.32</v>
+        <v>2.18</v>
       </c>
       <c r="V13" t="n">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="W13" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="X13" t="n">
-        <v>25</v>
+        <v>19.5</v>
       </c>
       <c r="Y13" t="n">
-        <v>14.5</v>
+        <v>11.5</v>
       </c>
       <c r="Z13" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AA13" t="n">
+        <v>27</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>18</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>23</v>
+      </c>
+      <c r="AF13" t="n">
         <v>30</v>
       </c>
-      <c r="AB13" t="n">
-        <v>21</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>13</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>24</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>34</v>
-      </c>
       <c r="AG13" t="n">
-        <v>19.5</v>
+        <v>16</v>
       </c>
       <c r="AH13" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="AI13" t="n">
         <v>36</v>
       </c>
       <c r="AJ13" t="n">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="AK13" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AL13" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AM13" t="n">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="AN13" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AO13" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AP13" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AQ13" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR13" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AS13" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW13" t="n">
         <v>18</v>
       </c>
-      <c r="AT13" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>17</v>
-      </c>
       <c r="AX13" t="n">
-        <v>4</v>
+        <v>6.6</v>
       </c>
       <c r="AY13" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="AZ13" t="n">
         <v>14</v>
       </c>
       <c r="BA13" t="n">
-        <v>4.1</v>
+        <v>6.8</v>
       </c>
       <c r="BB13" t="n">
-        <v>4.3</v>
+        <v>50</v>
       </c>
       <c r="BC13" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BD13" t="n">
-        <v>4.2</v>
+        <v>7.2</v>
       </c>
       <c r="BE13" t="n">
-        <v>50</v>
+        <v>7.6</v>
       </c>
       <c r="BF13" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="BG13" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-24 11:28:59</t>
+          <t>2026-03-24 13:35:31</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Colombian Primera B</t>
+          <t>English National League</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3071,191 +3071,191 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>16:45:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Envigado</t>
+          <t>Southend</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Bogota</t>
+          <t>Woking</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.46</v>
+        <v>1.68</v>
       </c>
       <c r="G14" t="n">
-        <v>1.59</v>
+        <v>1.73</v>
       </c>
       <c r="H14" t="n">
-        <v>7.2</v>
+        <v>5.4</v>
       </c>
       <c r="I14" t="n">
-        <v>12</v>
+        <v>6.6</v>
       </c>
       <c r="J14" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="K14" t="n">
-        <v>5.7</v>
+        <v>4.5</v>
       </c>
       <c r="L14" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="M14" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="N14" t="n">
+        <v>4</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S14" t="n">
         <v>2.96</v>
       </c>
-      <c r="O14" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="P14" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>2</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S14" t="n">
-        <v>3.55</v>
-      </c>
       <c r="T14" t="n">
-        <v>2.26</v>
+        <v>1.79</v>
       </c>
       <c r="U14" t="n">
-        <v>1.64</v>
+        <v>2.02</v>
       </c>
       <c r="V14" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="W14" t="n">
-        <v>2.68</v>
+        <v>2.36</v>
       </c>
       <c r="X14" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>950</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>50</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>170</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>24</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>80</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>85</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>18</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>100</v>
+      </c>
+      <c r="AP14" t="n">
         <v>14.5</v>
       </c>
-      <c r="Y14" t="n">
-        <v>26</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>40</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF14" t="n">
+      <c r="AQ14" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AS14" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="AG14" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>36</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>15</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>22</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>65</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>1.03</v>
-      </c>
       <c r="AT14" t="n">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AU14" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV14" t="n">
-        <v>1.03</v>
+        <v>18.5</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.03</v>
+        <v>55</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.03</v>
+        <v>9</v>
       </c>
       <c r="AY14" t="n">
         <v>8.4</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.03</v>
+        <v>16.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>1.03</v>
+        <v>55</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.03</v>
+        <v>14</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="BD14" t="n">
-        <v>1.03</v>
+        <v>25</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF14" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BG14" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-24 11:28:59</t>
+          <t>2026-03-24 13:35:31</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>English National League</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3265,191 +3265,191 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>16:45:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Cerro</t>
+          <t>Wealdstone</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Juventud De Las Piedras</t>
+          <t>Yeovil</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.15</v>
+        <v>1.91</v>
       </c>
       <c r="G15" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="H15" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I15" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J15" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K15" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N15" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S15" t="n">
         <v>3.55</v>
       </c>
-      <c r="H15" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="I15" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="J15" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="K15" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="L15" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="M15" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="N15" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="O15" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="P15" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S15" t="n">
-        <v>5.3</v>
-      </c>
       <c r="T15" t="n">
-        <v>2.08</v>
+        <v>1.83</v>
       </c>
       <c r="U15" t="n">
-        <v>1.75</v>
+        <v>2.02</v>
       </c>
       <c r="V15" t="n">
-        <v>1.53</v>
+        <v>1.26</v>
       </c>
       <c r="W15" t="n">
-        <v>1.4</v>
+        <v>1.98</v>
       </c>
       <c r="X15" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>34</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>130</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>19</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>24</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>22</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>15</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>70</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>24</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>50</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>48</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>8</v>
+      </c>
+      <c r="BE15" t="n">
         <v>9.4</v>
       </c>
-      <c r="Y15" t="n">
-        <v>970</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>970</v>
-      </c>
-      <c r="AA15" t="n">
+      <c r="BF15" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BG15" t="n">
         <v>55</v>
       </c>
-      <c r="AB15" t="n">
-        <v>970</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>970</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>970</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>48</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>22</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>950</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>80</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>75</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>60</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>90</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>80</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>55</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>17</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="BG15" t="n">
-        <v>1.78</v>
-      </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-24 11:28:59</t>
+          <t>2026-03-24 13:35:31</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>English National League</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3459,184 +3459,184 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>16:45:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Deportivo Riestra</t>
+          <t>Tamworth FC</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>San Lorenzo</t>
+          <t>Forest Green</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.62</v>
+        <v>3.55</v>
       </c>
       <c r="G16" t="n">
-        <v>2.72</v>
+        <v>3.95</v>
       </c>
       <c r="H16" t="n">
+        <v>2</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="J16" t="n">
         <v>3.75</v>
       </c>
-      <c r="I16" t="n">
-        <v>4</v>
-      </c>
-      <c r="J16" t="n">
-        <v>2.72</v>
-      </c>
       <c r="K16" t="n">
-        <v>2.76</v>
+        <v>4.3</v>
       </c>
       <c r="L16" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="M16" t="n">
-        <v>1.21</v>
+        <v>1.05</v>
       </c>
       <c r="N16" t="n">
-        <v>1.97</v>
+        <v>4.5</v>
       </c>
       <c r="O16" t="n">
-        <v>1.88</v>
+        <v>1.23</v>
       </c>
       <c r="P16" t="n">
-        <v>1.29</v>
+        <v>2.2</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.85</v>
+        <v>1.7</v>
       </c>
       <c r="R16" t="n">
-        <v>1.08</v>
+        <v>1.49</v>
       </c>
       <c r="S16" t="n">
-        <v>4</v>
+        <v>2.7</v>
       </c>
       <c r="T16" t="n">
-        <v>2.8</v>
+        <v>1.64</v>
       </c>
       <c r="U16" t="n">
-        <v>1.45</v>
+        <v>2.32</v>
       </c>
       <c r="V16" t="n">
-        <v>1.33</v>
+        <v>1.87</v>
       </c>
       <c r="W16" t="n">
-        <v>1.58</v>
+        <v>1.34</v>
       </c>
       <c r="X16" t="n">
-        <v>5.6</v>
+        <v>24</v>
       </c>
       <c r="Y16" t="n">
-        <v>8.4</v>
+        <v>12.5</v>
       </c>
       <c r="Z16" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA16" t="n">
         <v>26</v>
       </c>
-      <c r="AA16" t="n">
-        <v>120</v>
-      </c>
       <c r="AB16" t="n">
-        <v>6.4</v>
+        <v>18</v>
       </c>
       <c r="AC16" t="n">
-        <v>7.6</v>
+        <v>9.6</v>
       </c>
       <c r="AD16" t="n">
-        <v>24</v>
+        <v>11.5</v>
       </c>
       <c r="AE16" t="n">
-        <v>120</v>
+        <v>21</v>
       </c>
       <c r="AF16" t="n">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="AG16" t="n">
         <v>17</v>
       </c>
       <c r="AH16" t="n">
-        <v>48</v>
+        <v>17.5</v>
       </c>
       <c r="AI16" t="n">
-        <v>230</v>
+        <v>32</v>
       </c>
       <c r="AJ16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>42</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>75</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>34</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>12</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>12</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>21</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>17</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>32</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BE16" t="n">
         <v>50</v>
       </c>
-      <c r="AK16" t="n">
-        <v>65</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>160</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>590</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>90</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>240</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>16</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>38</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>16</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>38</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>13</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>25</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>46</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>24</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>28</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>44</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>55</v>
-      </c>
       <c r="BF16" t="n">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="BG16" t="n">
-        <v>46</v>
+        <v>8.4</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-24 11:28:59</t>
+          <t>2026-03-24 13:35:31</t>
         </is>
       </c>
     </row>
@@ -3653,191 +3653,191 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Barranquilla</t>
+          <t>Envigado</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Leones FC</t>
+          <t>Bogota</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.82</v>
+        <v>1.44</v>
       </c>
       <c r="G17" t="n">
-        <v>2.14</v>
+        <v>1.55</v>
       </c>
       <c r="H17" t="n">
-        <v>3.7</v>
+        <v>7.4</v>
       </c>
       <c r="I17" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="J17" t="n">
+        <v>4</v>
+      </c>
+      <c r="K17" t="n">
         <v>5.6</v>
       </c>
-      <c r="J17" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="K17" t="n">
-        <v>4.2</v>
-      </c>
       <c r="L17" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="M17" t="n">
         <v>1.07</v>
       </c>
       <c r="N17" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="O17" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="P17" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.83</v>
+        <v>2.06</v>
       </c>
       <c r="R17" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="S17" t="n">
-        <v>3.1</v>
+        <v>3.55</v>
       </c>
       <c r="T17" t="n">
-        <v>1.77</v>
+        <v>2.26</v>
       </c>
       <c r="U17" t="n">
-        <v>1.92</v>
+        <v>1.63</v>
       </c>
       <c r="V17" t="n">
-        <v>1.21</v>
+        <v>1.1</v>
       </c>
       <c r="W17" t="n">
-        <v>1.87</v>
+        <v>2.8</v>
       </c>
       <c r="X17" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="Y17" t="n">
-        <v>18.5</v>
+        <v>27</v>
       </c>
       <c r="Z17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD17" t="n">
         <v>42</v>
       </c>
-      <c r="AA17" t="n">
-        <v>130</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>22</v>
-      </c>
       <c r="AE17" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AF17" t="n">
-        <v>14.5</v>
+        <v>8</v>
       </c>
       <c r="AG17" t="n">
         <v>12.5</v>
       </c>
       <c r="AH17" t="n">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="AI17" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AJ17" t="n">
-        <v>28</v>
+        <v>14.5</v>
       </c>
       <c r="AK17" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AL17" t="n">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="AM17" t="n">
         <v>1000</v>
       </c>
       <c r="AN17" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="AO17" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AP17" t="n">
-        <v>3.45</v>
+        <v>1.03</v>
       </c>
       <c r="AQ17" t="n">
-        <v>3.55</v>
+        <v>1.03</v>
       </c>
       <c r="AR17" t="n">
-        <v>3.95</v>
+        <v>1.03</v>
       </c>
       <c r="AS17" t="n">
-        <v>4.2</v>
+        <v>1.03</v>
       </c>
       <c r="AT17" t="n">
-        <v>3.1</v>
+        <v>1.03</v>
       </c>
       <c r="AU17" t="n">
-        <v>3.05</v>
+        <v>1.03</v>
       </c>
       <c r="AV17" t="n">
-        <v>3.65</v>
+        <v>1.03</v>
       </c>
       <c r="AW17" t="n">
-        <v>4.1</v>
+        <v>1.03</v>
       </c>
       <c r="AX17" t="n">
-        <v>3.35</v>
+        <v>1.03</v>
       </c>
       <c r="AY17" t="n">
-        <v>3.25</v>
+        <v>1.03</v>
       </c>
       <c r="AZ17" t="n">
-        <v>3.7</v>
+        <v>1.03</v>
       </c>
       <c r="BA17" t="n">
-        <v>4.1</v>
+        <v>1.03</v>
       </c>
       <c r="BB17" t="n">
-        <v>3.8</v>
+        <v>1.03</v>
       </c>
       <c r="BC17" t="n">
-        <v>3.75</v>
+        <v>1.03</v>
       </c>
       <c r="BD17" t="n">
-        <v>4</v>
+        <v>1.03</v>
       </c>
       <c r="BE17" t="n">
-        <v>4.2</v>
+        <v>1.03</v>
       </c>
       <c r="BF17" t="n">
-        <v>3.5</v>
+        <v>7.4</v>
       </c>
       <c r="BG17" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-24 11:28:59</t>
+          <t>2026-03-24 13:35:31</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Paraguayan Primera Division</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3847,191 +3847,191 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>19:30:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Guarani (Par)</t>
+          <t>Cerro</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Club 2 de Mayo</t>
+          <t>Juventud De Las Piedras</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.68</v>
+        <v>3.25</v>
       </c>
       <c r="G18" t="n">
-        <v>2.12</v>
+        <v>3.55</v>
       </c>
       <c r="H18" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="K18" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="N18" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="T18" t="n">
         <v>2.08</v>
       </c>
-      <c r="I18" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="J18" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="K18" t="n">
+      <c r="U18" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="X18" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>970</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>46</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>42</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH18" t="n">
         <v>950</v>
       </c>
-      <c r="L18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N18" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="O18" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="P18" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="S18" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="T18" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1000</v>
-      </c>
       <c r="AI18" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AK18" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AL18" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AM18" t="n">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AN18" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AO18" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AS18" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AT18" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AU18" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AV18" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AW18" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AY18" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AZ18" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BA18" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.01</v>
+        <v>2.84</v>
       </c>
       <c r="BD18" t="n">
-        <v>1.01</v>
+        <v>2.88</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.01</v>
+        <v>2.62</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BG18" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-24 11:28:59</t>
+          <t>2026-03-24 13:35:31</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Colombian Primera B</t>
+          <t>Argentinian Primera Division</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4041,191 +4041,191 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Real Soacha Cundinamarca FC</t>
+          <t>Deportivo Riestra</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Atletico FC Cali</t>
+          <t>San Lorenzo</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.55</v>
+        <v>2.62</v>
       </c>
       <c r="G19" t="n">
-        <v>1.67</v>
+        <v>2.66</v>
       </c>
       <c r="H19" t="n">
-        <v>6.4</v>
+        <v>3.85</v>
       </c>
       <c r="I19" t="n">
-        <v>9.6</v>
+        <v>4</v>
       </c>
       <c r="J19" t="n">
-        <v>3.4</v>
+        <v>2.72</v>
       </c>
       <c r="K19" t="n">
-        <v>4.9</v>
+        <v>2.76</v>
       </c>
       <c r="L19" t="n">
-        <v>1.42</v>
+        <v>1.01</v>
       </c>
       <c r="M19" t="n">
-        <v>1.09</v>
+        <v>1.21</v>
       </c>
       <c r="N19" t="n">
-        <v>2.78</v>
+        <v>1.97</v>
       </c>
       <c r="O19" t="n">
-        <v>1.4</v>
+        <v>1.87</v>
       </c>
       <c r="P19" t="n">
-        <v>1.67</v>
+        <v>1.27</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.1</v>
+        <v>3.85</v>
       </c>
       <c r="R19" t="n">
-        <v>1.25</v>
+        <v>1.08</v>
       </c>
       <c r="S19" t="n">
         <v>3.9</v>
       </c>
       <c r="T19" t="n">
-        <v>2.2</v>
+        <v>2.78</v>
       </c>
       <c r="U19" t="n">
-        <v>1.66</v>
+        <v>1.45</v>
       </c>
       <c r="V19" t="n">
-        <v>1.12</v>
+        <v>1.33</v>
       </c>
       <c r="W19" t="n">
-        <v>2.48</v>
+        <v>1.6</v>
       </c>
       <c r="X19" t="n">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="Y19" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="Z19" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AA19" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AB19" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="AC19" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="AD19" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AE19" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AF19" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AG19" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AH19" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AI19" t="n">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AK19" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AL19" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AM19" t="n">
-        <v>1000</v>
+        <v>570</v>
       </c>
       <c r="AN19" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AO19" t="n">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AP19" t="n">
-        <v>3.95</v>
+        <v>4.8</v>
       </c>
       <c r="AQ19" t="n">
-        <v>4.5</v>
+        <v>7.2</v>
       </c>
       <c r="AR19" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="AS19" t="n">
-        <v>1.58</v>
+        <v>38</v>
       </c>
       <c r="AT19" t="n">
-        <v>3.2</v>
+        <v>5.7</v>
       </c>
       <c r="AU19" t="n">
-        <v>3.7</v>
+        <v>6.6</v>
       </c>
       <c r="AV19" t="n">
-        <v>4.9</v>
+        <v>18</v>
       </c>
       <c r="AW19" t="n">
-        <v>1.58</v>
+        <v>38</v>
       </c>
       <c r="AX19" t="n">
-        <v>3.55</v>
+        <v>11.5</v>
       </c>
       <c r="AY19" t="n">
-        <v>3.85</v>
+        <v>15</v>
       </c>
       <c r="AZ19" t="n">
-        <v>4.8</v>
+        <v>25</v>
       </c>
       <c r="BA19" t="n">
-        <v>1.58</v>
+        <v>46</v>
       </c>
       <c r="BB19" t="n">
-        <v>4.3</v>
+        <v>24</v>
       </c>
       <c r="BC19" t="n">
-        <v>4.5</v>
+        <v>28</v>
       </c>
       <c r="BD19" t="n">
-        <v>3.85</v>
+        <v>44</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.58</v>
+        <v>55</v>
       </c>
       <c r="BF19" t="n">
-        <v>4.1</v>
+        <v>32</v>
       </c>
       <c r="BG19" t="n">
-        <v>1.59</v>
+        <v>46</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-24 11:28:59</t>
+          <t>2026-03-24 13:35:31</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>US United Soccer League</t>
+          <t>Colombian Primera B</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4235,168 +4235,168 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Lexington SC</t>
+          <t>Barranquilla</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Leones FC</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.57</v>
+        <v>1.94</v>
       </c>
       <c r="G20" t="n">
-        <v>1.71</v>
+        <v>2.14</v>
       </c>
       <c r="H20" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I20" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J20" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K20" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N20" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="X20" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>40</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>130</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>80</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>90</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>30</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>29</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>23</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>100</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AT20" t="n">
         <v>6</v>
       </c>
-      <c r="I20" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="J20" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="K20" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="L20" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="M20" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N20" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="O20" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="P20" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="S20" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T20" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="W20" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="X20" t="n">
+      <c r="AU20" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>13</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>18</v>
+      </c>
+      <c r="BC20" t="n">
         <v>17.5</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>950</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>70</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>950</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>130</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>950</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>120</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>970</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>22</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>48</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>180</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>180</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>7</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>13</v>
       </c>
       <c r="BD20" t="n">
         <v>4</v>
@@ -4405,21 +4405,21 @@
         <v>4.2</v>
       </c>
       <c r="BF20" t="n">
-        <v>7.6</v>
+        <v>13.5</v>
       </c>
       <c r="BG20" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-24 11:28:59</t>
+          <t>2026-03-24 13:35:31</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Paraguayan Primera Division</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4429,191 +4429,191 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>19:30:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Boston River</t>
+          <t>Guarani (Par)</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Penarol</t>
+          <t>Club 2 de Mayo</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>6.8</v>
+        <v>1.91</v>
       </c>
       <c r="G21" t="n">
-        <v>8.199999999999999</v>
+        <v>2</v>
       </c>
       <c r="H21" t="n">
-        <v>1.6</v>
+        <v>4</v>
       </c>
       <c r="I21" t="n">
-        <v>1.64</v>
+        <v>4.9</v>
       </c>
       <c r="J21" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="K21" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="L21" t="n">
-        <v>1.46</v>
+        <v>1.01</v>
       </c>
       <c r="M21" t="n">
         <v>1.09</v>
       </c>
       <c r="N21" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="O21" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="P21" t="n">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.2</v>
+        <v>2.04</v>
       </c>
       <c r="R21" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="S21" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="T21" t="n">
-        <v>2.14</v>
+        <v>1.11</v>
       </c>
       <c r="U21" t="n">
-        <v>1.72</v>
+        <v>1.11</v>
       </c>
       <c r="V21" t="n">
-        <v>2.52</v>
+        <v>1.26</v>
       </c>
       <c r="W21" t="n">
-        <v>1.14</v>
+        <v>1.94</v>
       </c>
       <c r="X21" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="Y21" t="n">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="Z21" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="AA21" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AB21" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AC21" t="n">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AD21" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AE21" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AF21" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AG21" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AH21" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AI21" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AJ21" t="n">
-        <v>300</v>
+        <v>1000</v>
       </c>
       <c r="AK21" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AL21" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AM21" t="n">
-        <v>230</v>
+        <v>1000</v>
       </c>
       <c r="AN21" t="n">
-        <v>260</v>
+        <v>1000</v>
       </c>
       <c r="AO21" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AP21" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AQ21" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="AR21" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AS21" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="AT21" t="n">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="AU21" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="AV21" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AW21" t="n">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="AX21" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="AY21" t="n">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="AZ21" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BA21" t="n">
-        <v>36</v>
+        <v>1.01</v>
       </c>
       <c r="BB21" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BC21" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="BD21" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="BE21" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BF21" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BG21" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-24 11:28:59</t>
+          <t>2026-03-24 13:35:31</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>US United Soccer League</t>
+          <t>Colombian Primera B</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4623,378 +4623,1154 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Sporting Club Jacksonville</t>
+          <t>Real Soacha Cundinamarca FC</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Miami FC</t>
+          <t>Atletico FC Cali</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.64</v>
+        <v>1.54</v>
       </c>
       <c r="G22" t="n">
-        <v>2.86</v>
+        <v>1.67</v>
       </c>
       <c r="H22" t="n">
-        <v>2.66</v>
+        <v>6.4</v>
       </c>
       <c r="I22" t="n">
-        <v>2.92</v>
+        <v>9.6</v>
       </c>
       <c r="J22" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="K22" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N22" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S22" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="W22" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AT22" t="n">
         <v>3.7</v>
       </c>
-      <c r="L22" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="M22" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N22" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="O22" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="P22" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="S22" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="T22" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="U22" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="X22" t="n">
-        <v>17</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>970</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>48</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>970</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>36</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>22</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>970</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>50</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>50</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>36</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>48</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>110</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>32</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>30</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>11</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>9</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>8.800000000000001</v>
-      </c>
       <c r="AU22" t="n">
-        <v>6.2</v>
+        <v>4.4</v>
       </c>
       <c r="AV22" t="n">
-        <v>9.800000000000001</v>
+        <v>1.2</v>
       </c>
       <c r="AW22" t="n">
-        <v>4.4</v>
+        <v>1.24</v>
       </c>
       <c r="AX22" t="n">
-        <v>14.5</v>
+        <v>4.1</v>
       </c>
       <c r="AY22" t="n">
-        <v>9.6</v>
+        <v>4.7</v>
       </c>
       <c r="AZ22" t="n">
-        <v>13</v>
+        <v>1.2</v>
       </c>
       <c r="BA22" t="n">
-        <v>4.6</v>
+        <v>1.24</v>
       </c>
       <c r="BB22" t="n">
-        <v>4.6</v>
+        <v>1.76</v>
       </c>
       <c r="BC22" t="n">
-        <v>4.4</v>
+        <v>1.43</v>
       </c>
       <c r="BD22" t="n">
-        <v>4.6</v>
+        <v>1.22</v>
       </c>
       <c r="BE22" t="n">
-        <v>4.8</v>
+        <v>1.24</v>
       </c>
       <c r="BF22" t="n">
-        <v>20</v>
+        <v>2.06</v>
       </c>
       <c r="BG22" t="n">
-        <v>19</v>
+        <v>1.24</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-24 11:28:59</t>
+          <t>2026-03-24 13:35:31</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>US USL League One</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Greenville Triumph SC</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>New York Cosmos</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="G23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="K23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N23" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S23" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH23" t="inlineStr">
+        <is>
+          <t>2026-03-24 13:35:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>US United Soccer League</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Lexington SC</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Brooklyn FC</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="H24" t="n">
+        <v>6</v>
+      </c>
+      <c r="I24" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="J24" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="K24" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N24" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="P24" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S24" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="W24" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="X24" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>25</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>65</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>240</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>950</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>130</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>28</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>120</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>22</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>170</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>13</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>170</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>18</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BG24" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BH24" t="inlineStr">
+        <is>
+          <t>2026-03-24 13:35:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Uruguayan Primera Division</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>20:30:00</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Boston River</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Penarol</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="G25" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="J25" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K25" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L25" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="M25" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N25" t="n">
+        <v>3</v>
+      </c>
+      <c r="O25" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="P25" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S25" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="V25" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X25" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>17</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>20</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>22</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>65</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>32</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>32</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>310</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>170</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>160</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>240</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>280</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>14</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>16</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>17</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>22</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>36</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BG25" t="n">
+        <v>11</v>
+      </c>
+      <c r="BH25" t="inlineStr">
+        <is>
+          <t>2026-03-24 13:35:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>US United Soccer League</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>20:30:00</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Sporting Club Jacksonville</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Miami FC</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="G26" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="H26" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="I26" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="J26" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K26" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="M26" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N26" t="n">
+        <v>4</v>
+      </c>
+      <c r="O26" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="P26" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S26" t="n">
+        <v>3</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="X26" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>22</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>46</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>34</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>44</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>48</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>90</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>26</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>25</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>21</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>5</v>
+      </c>
+      <c r="BF26" t="n">
+        <v>17</v>
+      </c>
+      <c r="BG26" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BH26" t="inlineStr">
+        <is>
+          <t>2026-03-24 13:35:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
           <t>Colombian Primera A</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>2026-03-25</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>22:00:00</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>America de Cali S.A</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>Llaneros FC</t>
         </is>
       </c>
-      <c r="F23" t="n">
+      <c r="F27" t="n">
         <v>1.6</v>
       </c>
-      <c r="G23" t="n">
+      <c r="G27" t="n">
         <v>1.64</v>
       </c>
-      <c r="H23" t="n">
+      <c r="H27" t="n">
         <v>7.2</v>
       </c>
-      <c r="I23" t="n">
+      <c r="I27" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="J23" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="K23" t="n">
+      <c r="J27" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K27" t="n">
         <v>4.1</v>
       </c>
-      <c r="L23" t="n">
+      <c r="L27" t="n">
         <v>1.47</v>
       </c>
-      <c r="M23" t="n">
+      <c r="M27" t="n">
         <v>1.09</v>
       </c>
-      <c r="N23" t="n">
+      <c r="N27" t="n">
         <v>3.1</v>
       </c>
-      <c r="O23" t="n">
+      <c r="O27" t="n">
         <v>1.42</v>
       </c>
-      <c r="P23" t="n">
+      <c r="P27" t="n">
         <v>1.72</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="Q27" t="n">
         <v>2.22</v>
       </c>
-      <c r="R23" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S23" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="T23" t="n">
+      <c r="R27" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S27" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T27" t="n">
         <v>2.2</v>
       </c>
-      <c r="U23" t="n">
+      <c r="U27" t="n">
         <v>1.72</v>
       </c>
-      <c r="V23" t="n">
+      <c r="V27" t="n">
         <v>1.14</v>
       </c>
-      <c r="W23" t="n">
+      <c r="W27" t="n">
         <v>2.56</v>
       </c>
-      <c r="X23" t="n">
-        <v>12</v>
-      </c>
-      <c r="Y23" t="n">
+      <c r="X27" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Y27" t="n">
         <v>950</v>
       </c>
-      <c r="Z23" t="n">
+      <c r="Z27" t="n">
         <v>65</v>
       </c>
-      <c r="AA23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB23" t="n">
+      <c r="AA27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>950</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>950</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>970</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>21</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ27" t="n">
         <v>6.6</v>
       </c>
-      <c r="AC23" t="n">
-        <v>9</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>950</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF23" t="n">
+      <c r="AR27" t="n">
         <v>8.6</v>
       </c>
-      <c r="AG23" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>950</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>970</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>21</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>50</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>15</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>10</v>
-      </c>
-      <c r="AQ23" t="n">
+      <c r="AS27" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV27" t="n">
         <v>7.4</v>
       </c>
-      <c r="AR23" t="n">
-        <v>10</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>25</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>11</v>
-      </c>
-      <c r="AX23" t="n">
+      <c r="AW27" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AX27" t="n">
         <v>7.6</v>
       </c>
-      <c r="AY23" t="n">
+      <c r="AY27" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AZ23" t="n">
-        <v>23</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>11</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BC23" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BD23" t="n">
+      <c r="AZ27" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BE27" t="n">
         <v>9.6</v>
       </c>
-      <c r="BE23" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BF23" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BG23" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BH23" t="inlineStr">
-        <is>
-          <t>2026-03-24 11:28:59</t>
+      <c r="BF27" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BG27" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BH27" t="inlineStr">
+        <is>
+          <t>2026-03-24 13:35:31</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-25.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-25.xlsx
@@ -757,58 +757,58 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.03</v>
+        <v>3.65</v>
       </c>
       <c r="G2" t="n">
-        <v>990</v>
+        <v>5.4</v>
       </c>
       <c r="H2" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="J2" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K2" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="L2" t="n">
         <v>1.01</v>
       </c>
-      <c r="I2" t="n">
-        <v>990</v>
-      </c>
-      <c r="J2" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="K2" t="n">
-        <v>950</v>
-      </c>
-      <c r="L2" t="n">
-        <v>1.41</v>
-      </c>
       <c r="M2" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N2" t="n">
-        <v>1.26</v>
+        <v>2.7</v>
       </c>
       <c r="O2" t="n">
-        <v>1.07</v>
+        <v>1.38</v>
       </c>
       <c r="P2" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="R2" t="n">
         <v>1.25</v>
       </c>
-      <c r="Q2" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.18</v>
-      </c>
       <c r="S2" t="n">
-        <v>1.36</v>
+        <v>3.45</v>
       </c>
       <c r="T2" t="n">
-        <v>1.11</v>
+        <v>1.91</v>
       </c>
       <c r="U2" t="n">
-        <v>1.66</v>
+        <v>1.87</v>
       </c>
       <c r="V2" t="n">
-        <v>1.01</v>
+        <v>1.78</v>
       </c>
       <c r="W2" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="X2" t="n">
         <v>1000</v>
@@ -916,11 +916,11 @@
         <v>1.01</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-24 13:35:31</t>
+          <t>2026-03-24 15:41:44</t>
         </is>
       </c>
     </row>
@@ -963,7 +963,7 @@
         <v>1.86</v>
       </c>
       <c r="J3" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="K3" t="n">
         <v>3.95</v>
@@ -975,10 +975,10 @@
         <v>1.08</v>
       </c>
       <c r="N3" t="n">
-        <v>2.72</v>
+        <v>2.82</v>
       </c>
       <c r="O3" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="P3" t="n">
         <v>1.62</v>
@@ -1017,7 +1017,7 @@
         <v>23</v>
       </c>
       <c r="AB3" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AC3" t="n">
         <v>10</v>
@@ -1041,7 +1041,7 @@
         <v>65</v>
       </c>
       <c r="AJ3" t="n">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="AK3" t="n">
         <v>140</v>
@@ -1059,37 +1059,37 @@
         <v>20</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.03</v>
+        <v>14</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.03</v>
+        <v>16.5</v>
       </c>
       <c r="AX3" t="n">
         <v>1.03</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.03</v>
+        <v>18</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.03</v>
+        <v>18.5</v>
       </c>
       <c r="BA3" t="n">
         <v>1.03</v>
@@ -1107,14 +1107,14 @@
         <v>1.03</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.01</v>
+        <v>130</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-24 13:35:31</t>
+          <t>2026-03-24 15:41:44</t>
         </is>
       </c>
     </row>
@@ -1145,40 +1145,40 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.26</v>
+        <v>2.62</v>
       </c>
       <c r="G4" t="n">
-        <v>2.86</v>
+        <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>2.78</v>
+        <v>2.62</v>
       </c>
       <c r="I4" t="n">
-        <v>3.85</v>
+        <v>3</v>
       </c>
       <c r="J4" t="n">
-        <v>2.92</v>
+        <v>3.25</v>
       </c>
       <c r="K4" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="L4" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="M4" t="n">
         <v>1.07</v>
       </c>
       <c r="N4" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="O4" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="P4" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="R4" t="n">
         <v>1.32</v>
@@ -1187,40 +1187,40 @@
         <v>3.45</v>
       </c>
       <c r="T4" t="n">
-        <v>1.11</v>
+        <v>1.76</v>
       </c>
       <c r="U4" t="n">
-        <v>1.11</v>
+        <v>2.1</v>
       </c>
       <c r="V4" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="W4" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="X4" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Y4" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AA4" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AB4" t="n">
         <v>13</v>
       </c>
       <c r="AC4" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD4" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AE4" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AF4" t="n">
         <v>21</v>
@@ -1232,7 +1232,7 @@
         <v>21</v>
       </c>
       <c r="AI4" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AJ4" t="n">
         <v>46</v>
@@ -1250,65 +1250,65 @@
         <v>30</v>
       </c>
       <c r="AO4" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AP4" t="n">
-        <v>2.52</v>
+        <v>10</v>
       </c>
       <c r="AQ4" t="n">
-        <v>2.46</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR4" t="n">
-        <v>2.66</v>
+        <v>15</v>
       </c>
       <c r="AS4" t="n">
-        <v>2.84</v>
+        <v>4.7</v>
       </c>
       <c r="AT4" t="n">
-        <v>2.42</v>
+        <v>8</v>
       </c>
       <c r="AU4" t="n">
-        <v>2.96</v>
+        <v>5.9</v>
       </c>
       <c r="AV4" t="n">
-        <v>2.52</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW4" t="n">
-        <v>2.78</v>
+        <v>4.5</v>
       </c>
       <c r="AX4" t="n">
-        <v>2.6</v>
+        <v>12.5</v>
       </c>
       <c r="AY4" t="n">
-        <v>2.46</v>
+        <v>9.4</v>
       </c>
       <c r="AZ4" t="n">
-        <v>2.6</v>
+        <v>12.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>2.84</v>
+        <v>4.7</v>
       </c>
       <c r="BB4" t="n">
-        <v>2.8</v>
+        <v>4.6</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.74</v>
+        <v>21</v>
       </c>
       <c r="BD4" t="n">
-        <v>2.82</v>
+        <v>4.7</v>
       </c>
       <c r="BE4" t="n">
-        <v>2.9</v>
+        <v>4.9</v>
       </c>
       <c r="BF4" t="n">
-        <v>2.7</v>
+        <v>17.5</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.76</v>
+        <v>4.5</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-24 13:35:31</t>
+          <t>2026-03-24 15:41:44</t>
         </is>
       </c>
     </row>
@@ -1342,7 +1342,7 @@
         <v>1.11</v>
       </c>
       <c r="G5" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="H5" t="n">
         <v>13.5</v>
@@ -1360,7 +1360,7 @@
         <v>1.01</v>
       </c>
       <c r="M5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N5" t="n">
         <v>2.4</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-24 13:35:31</t>
+          <t>2026-03-24 15:41:44</t>
         </is>
       </c>
     </row>
@@ -1533,13 +1533,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="G6" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="H6" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="I6" t="n">
         <v>9.199999999999999</v>
@@ -1578,13 +1578,13 @@
         <v>1.84</v>
       </c>
       <c r="U6" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="V6" t="n">
         <v>1.12</v>
       </c>
       <c r="W6" t="n">
-        <v>2.42</v>
+        <v>2.52</v>
       </c>
       <c r="X6" t="n">
         <v>22</v>
@@ -1641,10 +1641,10 @@
         <v>160</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.03</v>
+        <v>13</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.03</v>
+        <v>17</v>
       </c>
       <c r="AR6" t="n">
         <v>1.03</v>
@@ -1653,34 +1653,34 @@
         <v>1.03</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.03</v>
+        <v>19</v>
       </c>
       <c r="AW6" t="n">
         <v>1.03</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.03</v>
+        <v>16</v>
       </c>
       <c r="BA6" t="n">
         <v>1.03</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="BD6" t="n">
         <v>1.03</v>
@@ -1689,14 +1689,14 @@
         <v>1.03</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.01</v>
+        <v>85</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-24 13:35:31</t>
+          <t>2026-03-24 15:41:44</t>
         </is>
       </c>
     </row>
@@ -1733,7 +1733,7 @@
         <v>2.24</v>
       </c>
       <c r="H7" t="n">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="I7" t="n">
         <v>4.7</v>
@@ -1745,7 +1745,7 @@
         <v>4</v>
       </c>
       <c r="L7" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="M7" t="n">
         <v>1.07</v>
@@ -1760,7 +1760,7 @@
         <v>1.79</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.84</v>
+        <v>1.96</v>
       </c>
       <c r="R7" t="n">
         <v>1.3</v>
@@ -1853,7 +1853,7 @@
         <v>6</v>
       </c>
       <c r="AV7" t="n">
-        <v>3.5</v>
+        <v>12</v>
       </c>
       <c r="AW7" t="n">
         <v>3.95</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-24 13:35:31</t>
+          <t>2026-03-24 15:41:44</t>
         </is>
       </c>
     </row>
@@ -1924,19 +1924,19 @@
         <v>2.8</v>
       </c>
       <c r="G8" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="H8" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="I8" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="J8" t="n">
         <v>2.64</v>
       </c>
       <c r="K8" t="n">
-        <v>3.05</v>
+        <v>2.96</v>
       </c>
       <c r="L8" t="n">
         <v>1.67</v>
@@ -1966,7 +1966,7 @@
         <v>2.28</v>
       </c>
       <c r="U8" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="V8" t="n">
         <v>1.4</v>
@@ -1975,7 +1975,7 @@
         <v>1.45</v>
       </c>
       <c r="X8" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="Y8" t="n">
         <v>9.4</v>
@@ -1990,7 +1990,7 @@
         <v>9</v>
       </c>
       <c r="AC8" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD8" t="n">
         <v>19.5</v>
@@ -2029,19 +2029,19 @@
         <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="AQ8" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AR8" t="n">
         <v>14</v>
       </c>
       <c r="AS8" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AT8" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AU8" t="n">
         <v>5.2</v>
@@ -2050,7 +2050,7 @@
         <v>11.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AX8" t="n">
         <v>13</v>
@@ -2062,29 +2062,29 @@
         <v>20</v>
       </c>
       <c r="BA8" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BB8" t="n">
         <v>4.3</v>
       </c>
-      <c r="BB8" t="n">
+      <c r="BC8" t="n">
         <v>4.2</v>
       </c>
-      <c r="BC8" t="n">
-        <v>4.1</v>
-      </c>
       <c r="BD8" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BE8" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BF8" t="n">
         <v>4.3</v>
       </c>
-      <c r="BF8" t="n">
-        <v>4.2</v>
-      </c>
       <c r="BG8" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-24 13:35:31</t>
+          <t>2026-03-24 15:41:44</t>
         </is>
       </c>
     </row>
@@ -2115,22 +2115,22 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.64</v>
+        <v>2.56</v>
       </c>
       <c r="G9" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="H9" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="I9" t="n">
         <v>3.55</v>
       </c>
       <c r="J9" t="n">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="K9" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="L9" t="n">
         <v>1.51</v>
@@ -2139,28 +2139,28 @@
         <v>1.13</v>
       </c>
       <c r="N9" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="O9" t="n">
         <v>1.57</v>
       </c>
       <c r="P9" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.6</v>
+        <v>2.68</v>
       </c>
       <c r="R9" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="S9" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="T9" t="n">
         <v>2.12</v>
       </c>
       <c r="U9" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="V9" t="n">
         <v>1.39</v>
@@ -2181,13 +2181,13 @@
         <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>9.199999999999999</v>
+        <v>970</v>
       </c>
       <c r="AC9" t="n">
         <v>970</v>
       </c>
       <c r="AD9" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AE9" t="n">
         <v>1000</v>
@@ -2229,10 +2229,10 @@
         <v>7.2</v>
       </c>
       <c r="AR9" t="n">
-        <v>5.7</v>
+        <v>16</v>
       </c>
       <c r="AS9" t="n">
-        <v>7</v>
+        <v>8.6</v>
       </c>
       <c r="AT9" t="n">
         <v>6.2</v>
@@ -2244,7 +2244,7 @@
         <v>11.5</v>
       </c>
       <c r="AW9" t="n">
-        <v>3.55</v>
+        <v>2.66</v>
       </c>
       <c r="AX9" t="n">
         <v>12</v>
@@ -2253,32 +2253,32 @@
         <v>10</v>
       </c>
       <c r="AZ9" t="n">
-        <v>5.9</v>
+        <v>7</v>
       </c>
       <c r="BA9" t="n">
-        <v>7.2</v>
+        <v>2.72</v>
       </c>
       <c r="BB9" t="n">
-        <v>6.6</v>
+        <v>8</v>
       </c>
       <c r="BC9" t="n">
-        <v>6.6</v>
+        <v>8</v>
       </c>
       <c r="BD9" t="n">
-        <v>7</v>
+        <v>3.25</v>
       </c>
       <c r="BE9" t="n">
-        <v>2.56</v>
+        <v>2.76</v>
       </c>
       <c r="BF9" t="n">
-        <v>6.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG9" t="n">
-        <v>7</v>
+        <v>2.7</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-24 13:35:31</t>
+          <t>2026-03-24 15:41:44</t>
         </is>
       </c>
     </row>
@@ -2309,19 +2309,19 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="G10" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="H10" t="n">
         <v>4.8</v>
       </c>
       <c r="I10" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="J10" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K10" t="n">
         <v>3.5</v>
@@ -2357,7 +2357,7 @@
         <v>1.66</v>
       </c>
       <c r="V10" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="W10" t="n">
         <v>1.9</v>
@@ -2438,7 +2438,7 @@
         <v>6</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="AX10" t="n">
         <v>7.8</v>
@@ -2447,7 +2447,7 @@
         <v>8.4</v>
       </c>
       <c r="AZ10" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BA10" t="n">
         <v>1.65</v>
@@ -2459,20 +2459,20 @@
         <v>6.6</v>
       </c>
       <c r="BD10" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="BF10" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BG10" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-24 13:35:31</t>
+          <t>2026-03-24 15:41:44</t>
         </is>
       </c>
     </row>
@@ -2506,13 +2506,13 @@
         <v>3.25</v>
       </c>
       <c r="G11" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="H11" t="n">
         <v>2.22</v>
       </c>
       <c r="I11" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="J11" t="n">
         <v>3.4</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-24 13:35:31</t>
+          <t>2026-03-24 15:41:44</t>
         </is>
       </c>
     </row>
@@ -2700,22 +2700,22 @@
         <v>2.78</v>
       </c>
       <c r="G12" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="H12" t="n">
         <v>2.58</v>
       </c>
       <c r="I12" t="n">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="J12" t="n">
         <v>3.6</v>
       </c>
       <c r="K12" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L12" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="M12" t="n">
         <v>1.06</v>
@@ -2730,7 +2730,7 @@
         <v>1.95</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="R12" t="n">
         <v>1.37</v>
@@ -2745,7 +2745,7 @@
         <v>2.12</v>
       </c>
       <c r="V12" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="W12" t="n">
         <v>1.54</v>
@@ -2775,7 +2775,7 @@
         <v>30</v>
       </c>
       <c r="AF12" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AG12" t="n">
         <v>970</v>
@@ -2808,19 +2808,19 @@
         <v>12.5</v>
       </c>
       <c r="AQ12" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="AR12" t="n">
         <v>13</v>
       </c>
       <c r="AS12" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AT12" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AU12" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AV12" t="n">
         <v>10</v>
@@ -2829,10 +2829,10 @@
         <v>21</v>
       </c>
       <c r="AX12" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="AY12" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="AZ12" t="n">
         <v>14</v>
@@ -2841,16 +2841,16 @@
         <v>30</v>
       </c>
       <c r="BB12" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BC12" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BD12" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="BE12" t="n">
-        <v>3.35</v>
+        <v>1.81</v>
       </c>
       <c r="BF12" t="n">
         <v>18.5</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-24 13:35:31</t>
+          <t>2026-03-24 15:41:44</t>
         </is>
       </c>
     </row>
@@ -2894,19 +2894,19 @@
         <v>3.65</v>
       </c>
       <c r="G13" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="H13" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="I13" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="J13" t="n">
         <v>3.55</v>
       </c>
       <c r="K13" t="n">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="L13" t="n">
         <v>1.33</v>
@@ -2924,7 +2924,7 @@
         <v>2.06</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="R13" t="n">
         <v>1.41</v>
@@ -2933,19 +2933,19 @@
         <v>3</v>
       </c>
       <c r="T13" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="U13" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="V13" t="n">
         <v>1.81</v>
       </c>
       <c r="W13" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="X13" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="Y13" t="n">
         <v>11.5</v>
@@ -2957,7 +2957,7 @@
         <v>27</v>
       </c>
       <c r="AB13" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AC13" t="n">
         <v>9</v>
@@ -2984,7 +2984,7 @@
         <v>70</v>
       </c>
       <c r="AK13" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AL13" t="n">
         <v>50</v>
@@ -3023,7 +3023,7 @@
         <v>18</v>
       </c>
       <c r="AX13" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AY13" t="n">
         <v>11.5</v>
@@ -3032,7 +3032,7 @@
         <v>14</v>
       </c>
       <c r="BA13" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BB13" t="n">
         <v>50</v>
@@ -3041,20 +3041,20 @@
         <v>34</v>
       </c>
       <c r="BD13" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BF13" t="n">
         <v>7.2</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>7</v>
       </c>
       <c r="BG13" t="n">
         <v>11</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-24 13:35:31</t>
+          <t>2026-03-24 15:41:44</t>
         </is>
       </c>
     </row>
@@ -3088,7 +3088,7 @@
         <v>1.68</v>
       </c>
       <c r="G14" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="H14" t="n">
         <v>5.4</v>
@@ -3097,7 +3097,7 @@
         <v>6.6</v>
       </c>
       <c r="J14" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="K14" t="n">
         <v>4.5</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-24 13:35:31</t>
+          <t>2026-03-24 15:41:44</t>
         </is>
       </c>
     </row>
@@ -3282,10 +3282,10 @@
         <v>1.91</v>
       </c>
       <c r="G15" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="H15" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="I15" t="n">
         <v>4.8</v>
@@ -3321,7 +3321,7 @@
         <v>3.55</v>
       </c>
       <c r="T15" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="U15" t="n">
         <v>2.02</v>
@@ -3330,7 +3330,7 @@
         <v>1.26</v>
       </c>
       <c r="W15" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="X15" t="n">
         <v>17</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-24 13:35:31</t>
+          <t>2026-03-24 15:41:44</t>
         </is>
       </c>
     </row>
@@ -3473,55 +3473,55 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="G16" t="n">
         <v>3.95</v>
       </c>
       <c r="H16" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="I16" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="J16" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="K16" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L16" t="n">
         <v>1.27</v>
       </c>
       <c r="M16" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N16" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="O16" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="P16" t="n">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="R16" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="S16" t="n">
         <v>2.7</v>
       </c>
       <c r="T16" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="U16" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="V16" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="W16" t="n">
         <v>1.34</v>
@@ -3530,7 +3530,7 @@
         <v>24</v>
       </c>
       <c r="Y16" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="Z16" t="n">
         <v>15</v>
@@ -3539,7 +3539,7 @@
         <v>26</v>
       </c>
       <c r="AB16" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AC16" t="n">
         <v>9.6</v>
@@ -3569,13 +3569,13 @@
         <v>42</v>
       </c>
       <c r="AL16" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AM16" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AN16" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AO16" t="n">
         <v>12</v>
@@ -3593,7 +3593,7 @@
         <v>21</v>
       </c>
       <c r="AT16" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AU16" t="n">
         <v>7.8</v>
@@ -3605,7 +3605,7 @@
         <v>17</v>
       </c>
       <c r="AX16" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="AY16" t="n">
         <v>11.5</v>
@@ -3614,29 +3614,29 @@
         <v>12</v>
       </c>
       <c r="BA16" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="BB16" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="BC16" t="n">
         <v>32</v>
       </c>
       <c r="BD16" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="BE16" t="n">
         <v>50</v>
       </c>
       <c r="BF16" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="BG16" t="n">
         <v>8.4</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-24 13:35:31</t>
+          <t>2026-03-24 15:41:44</t>
         </is>
       </c>
     </row>
@@ -3682,7 +3682,7 @@
         <v>4</v>
       </c>
       <c r="K17" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="L17" t="n">
         <v>1.42</v>
@@ -3700,7 +3700,7 @@
         <v>1.75</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.06</v>
+        <v>1.98</v>
       </c>
       <c r="R17" t="n">
         <v>1.28</v>
@@ -3739,7 +3739,7 @@
         <v>11</v>
       </c>
       <c r="AD17" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AE17" t="n">
         <v>1000</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-24 13:35:31</t>
+          <t>2026-03-24 15:41:44</t>
         </is>
       </c>
     </row>
@@ -3867,7 +3867,7 @@
         <v>3.55</v>
       </c>
       <c r="H18" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="I18" t="n">
         <v>2.86</v>
@@ -3876,7 +3876,7 @@
         <v>2.86</v>
       </c>
       <c r="K18" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="L18" t="n">
         <v>1.58</v>
@@ -3906,13 +3906,13 @@
         <v>2.08</v>
       </c>
       <c r="U18" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="V18" t="n">
         <v>1.53</v>
       </c>
       <c r="W18" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="X18" t="n">
         <v>9.6</v>
@@ -3930,7 +3930,7 @@
         <v>970</v>
       </c>
       <c r="AC18" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD18" t="n">
         <v>970</v>
@@ -3951,7 +3951,7 @@
         <v>80</v>
       </c>
       <c r="AJ18" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AK18" t="n">
         <v>60</v>
@@ -3978,7 +3978,7 @@
         <v>12.5</v>
       </c>
       <c r="AS18" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AT18" t="n">
         <v>7.2</v>
@@ -3990,41 +3990,41 @@
         <v>10</v>
       </c>
       <c r="AW18" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AX18" t="n">
-        <v>6.4</v>
+        <v>16</v>
       </c>
       <c r="AY18" t="n">
         <v>11.5</v>
       </c>
       <c r="AZ18" t="n">
-        <v>6.4</v>
+        <v>17.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BB18" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC18" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="BD18" t="n">
-        <v>2.88</v>
+        <v>2.62</v>
       </c>
       <c r="BE18" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="BF18" t="n">
-        <v>8</v>
+        <v>2.9</v>
       </c>
       <c r="BG18" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-24 13:35:31</t>
+          <t>2026-03-24 15:41:44</t>
         </is>
       </c>
     </row>
@@ -4058,19 +4058,19 @@
         <v>2.62</v>
       </c>
       <c r="G19" t="n">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="H19" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="I19" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="J19" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="K19" t="n">
-        <v>2.76</v>
+        <v>2.82</v>
       </c>
       <c r="L19" t="n">
         <v>1.01</v>
@@ -4079,10 +4079,10 @@
         <v>1.21</v>
       </c>
       <c r="N19" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="O19" t="n">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="P19" t="n">
         <v>1.27</v>
@@ -4103,10 +4103,10 @@
         <v>1.45</v>
       </c>
       <c r="V19" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W19" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="X19" t="n">
         <v>5.5</v>
@@ -4145,7 +4145,7 @@
         <v>210</v>
       </c>
       <c r="AJ19" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AK19" t="n">
         <v>65</v>
@@ -4181,7 +4181,7 @@
         <v>6.6</v>
       </c>
       <c r="AV19" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AW19" t="n">
         <v>38</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-24 13:35:31</t>
+          <t>2026-03-24 15:41:44</t>
         </is>
       </c>
     </row>
@@ -4249,64 +4249,64 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="G20" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="H20" t="n">
         <v>4.1</v>
       </c>
       <c r="I20" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="J20" t="n">
-        <v>3.25</v>
+        <v>2.92</v>
       </c>
       <c r="K20" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L20" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="M20" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N20" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="O20" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="P20" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.12</v>
+        <v>2.02</v>
       </c>
       <c r="R20" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="S20" t="n">
-        <v>3.55</v>
+        <v>4.1</v>
       </c>
       <c r="T20" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="U20" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="V20" t="n">
         <v>1.23</v>
       </c>
       <c r="W20" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="X20" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="Y20" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="Z20" t="n">
         <v>40</v>
@@ -4315,10 +4315,10 @@
         <v>130</v>
       </c>
       <c r="AB20" t="n">
-        <v>9.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC20" t="n">
-        <v>9.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD20" t="n">
         <v>22</v>
@@ -4333,86 +4333,86 @@
         <v>13</v>
       </c>
       <c r="AH20" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AI20" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AJ20" t="n">
+        <v>32</v>
+      </c>
+      <c r="AK20" t="n">
         <v>30</v>
       </c>
-      <c r="AK20" t="n">
-        <v>29</v>
-      </c>
       <c r="AL20" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AM20" t="n">
         <v>1000</v>
       </c>
       <c r="AN20" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AO20" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AP20" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ20" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR20" t="n">
-        <v>3.95</v>
+        <v>4.5</v>
       </c>
       <c r="AS20" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="AT20" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="AU20" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="AV20" t="n">
         <v>13</v>
       </c>
       <c r="AW20" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="AX20" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AY20" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AZ20" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BA20" t="n">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="BB20" t="n">
         <v>18</v>
       </c>
       <c r="BC20" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BD20" t="n">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="BE20" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="BF20" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BG20" t="n">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-24 13:35:31</t>
+          <t>2026-03-24 15:41:44</t>
         </is>
       </c>
     </row>
@@ -4443,22 +4443,22 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="G21" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="H21" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="I21" t="n">
         <v>4.9</v>
       </c>
       <c r="J21" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K21" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="L21" t="n">
         <v>1.01</v>
@@ -4467,16 +4467,16 @@
         <v>1.09</v>
       </c>
       <c r="N21" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="O21" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="P21" t="n">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="R21" t="n">
         <v>1.26</v>
@@ -4485,16 +4485,16 @@
         <v>4.2</v>
       </c>
       <c r="T21" t="n">
-        <v>1.11</v>
+        <v>1.98</v>
       </c>
       <c r="U21" t="n">
-        <v>1.11</v>
+        <v>1.86</v>
       </c>
       <c r="V21" t="n">
         <v>1.26</v>
       </c>
       <c r="W21" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="X21" t="n">
         <v>1000</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-24 13:35:31</t>
+          <t>2026-03-24 15:41:44</t>
         </is>
       </c>
     </row>
@@ -4655,7 +4655,7 @@
         <v>4.8</v>
       </c>
       <c r="L22" t="n">
-        <v>1.46</v>
+        <v>1.01</v>
       </c>
       <c r="M22" t="n">
         <v>1.09</v>
@@ -4751,10 +4751,10 @@
         <v>1.43</v>
       </c>
       <c r="AR22" t="n">
-        <v>1.23</v>
+        <v>1.49</v>
       </c>
       <c r="AS22" t="n">
-        <v>1.24</v>
+        <v>1.52</v>
       </c>
       <c r="AT22" t="n">
         <v>3.7</v>
@@ -4763,22 +4763,22 @@
         <v>4.4</v>
       </c>
       <c r="AV22" t="n">
-        <v>1.2</v>
+        <v>1.46</v>
       </c>
       <c r="AW22" t="n">
-        <v>1.24</v>
+        <v>1.51</v>
       </c>
       <c r="AX22" t="n">
         <v>4.1</v>
       </c>
       <c r="AY22" t="n">
-        <v>4.7</v>
+        <v>8</v>
       </c>
       <c r="AZ22" t="n">
-        <v>1.2</v>
+        <v>1.46</v>
       </c>
       <c r="BA22" t="n">
-        <v>1.24</v>
+        <v>1.51</v>
       </c>
       <c r="BB22" t="n">
         <v>1.76</v>
@@ -4787,20 +4787,20 @@
         <v>1.43</v>
       </c>
       <c r="BD22" t="n">
-        <v>1.22</v>
+        <v>1.49</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.24</v>
+        <v>1.51</v>
       </c>
       <c r="BF22" t="n">
-        <v>2.06</v>
+        <v>9.6</v>
       </c>
       <c r="BG22" t="n">
-        <v>1.24</v>
+        <v>1.52</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-24 13:35:31</t>
+          <t>2026-03-24 15:41:44</t>
         </is>
       </c>
     </row>
@@ -4846,7 +4846,7 @@
         <v>1.02</v>
       </c>
       <c r="K23" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L23" t="n">
         <v>1.01</v>
@@ -4855,7 +4855,7 @@
         <v>1.01</v>
       </c>
       <c r="N23" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O23" t="n">
         <v>1.23</v>
@@ -4870,7 +4870,7 @@
         <v>1.18</v>
       </c>
       <c r="S23" t="n">
-        <v>1.23</v>
+        <v>1.66</v>
       </c>
       <c r="T23" t="n">
         <v>1.01</v>
@@ -4939,52 +4939,52 @@
         <v>1000</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS23" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT23" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU23" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV23" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW23" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX23" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY23" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ23" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA23" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC23" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD23" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF23" t="n">
         <v>1.01</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-24 13:35:31</t>
+          <t>2026-03-24 15:41:44</t>
         </is>
       </c>
     </row>
@@ -5025,7 +5025,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="G24" t="n">
         <v>1.69</v>
@@ -5034,13 +5034,13 @@
         <v>6</v>
       </c>
       <c r="I24" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="J24" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K24" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L24" t="n">
         <v>1.39</v>
@@ -5055,25 +5055,25 @@
         <v>1.31</v>
       </c>
       <c r="P24" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="R24" t="n">
         <v>1.33</v>
       </c>
       <c r="S24" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="T24" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="U24" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="V24" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="W24" t="n">
         <v>2.44</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-24 13:35:31</t>
+          <t>2026-03-24 15:41:44</t>
         </is>
       </c>
     </row>
@@ -5225,7 +5225,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="H25" t="n">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="I25" t="n">
         <v>1.65</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-24 13:35:31</t>
+          <t>2026-03-24 15:41:44</t>
         </is>
       </c>
     </row>
@@ -5416,19 +5416,19 @@
         <v>2.72</v>
       </c>
       <c r="G26" t="n">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="H26" t="n">
         <v>2.6</v>
       </c>
       <c r="I26" t="n">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="J26" t="n">
         <v>3.5</v>
       </c>
       <c r="K26" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L26" t="n">
         <v>1.32</v>
@@ -5461,10 +5461,10 @@
         <v>2.22</v>
       </c>
       <c r="V26" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="W26" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="X26" t="n">
         <v>19</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-24 13:35:31</t>
+          <t>2026-03-24 15:41:44</t>
         </is>
       </c>
     </row>
@@ -5610,7 +5610,7 @@
         <v>1.6</v>
       </c>
       <c r="G27" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="H27" t="n">
         <v>7.2</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-24 13:35:31</t>
+          <t>2026-03-24 15:41:44</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-25.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH27"/>
+  <dimension ref="A1:BH29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -865,62 +865,62 @@
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.03</v>
+        <v>3.7</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.03</v>
+        <v>3.3</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.03</v>
+        <v>3.7</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.03</v>
+        <v>3.3</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.03</v>
+        <v>3.6</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.03</v>
+        <v>3.75</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.03</v>
+        <v>3.75</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BG2" t="n">
-        <v>14</v>
+        <v>4.1</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-24 15:41:44</t>
+          <t>2026-03-24 17:47:56</t>
         </is>
       </c>
     </row>
@@ -969,7 +969,7 @@
         <v>3.95</v>
       </c>
       <c r="L3" t="n">
-        <v>1.49</v>
+        <v>1.42</v>
       </c>
       <c r="M3" t="n">
         <v>1.08</v>
@@ -1083,7 +1083,7 @@
         <v>16.5</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY3" t="n">
         <v>18</v>
@@ -1092,29 +1092,29 @@
         <v>18.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF3" t="n">
-        <v>130</v>
+        <v>1.01</v>
       </c>
       <c r="BG3" t="n">
         <v>12</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-24 15:41:44</t>
+          <t>2026-03-24 17:47:56</t>
         </is>
       </c>
     </row>
@@ -1145,43 +1145,43 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="G4" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="H4" t="n">
-        <v>2.62</v>
+        <v>2.98</v>
       </c>
       <c r="I4" t="n">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="J4" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K4" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="L4" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="M4" t="n">
         <v>1.07</v>
       </c>
       <c r="N4" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="O4" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="P4" t="n">
-        <v>1.81</v>
+        <v>1.87</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="R4" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S4" t="n">
         <v>3.45</v>
@@ -1193,10 +1193,10 @@
         <v>2.1</v>
       </c>
       <c r="V4" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="W4" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="X4" t="n">
         <v>16</v>
@@ -1208,10 +1208,10 @@
         <v>23</v>
       </c>
       <c r="AA4" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="AB4" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AC4" t="n">
         <v>8.199999999999999</v>
@@ -1223,10 +1223,10 @@
         <v>40</v>
       </c>
       <c r="AF4" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AG4" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AH4" t="n">
         <v>21</v>
@@ -1235,46 +1235,46 @@
         <v>55</v>
       </c>
       <c r="AJ4" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AK4" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AL4" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AM4" t="n">
         <v>120</v>
       </c>
       <c r="AN4" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AO4" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="AP4" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AQ4" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AR4" t="n">
         <v>15</v>
       </c>
       <c r="AS4" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="AT4" t="n">
         <v>8</v>
       </c>
       <c r="AU4" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AV4" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AW4" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AX4" t="n">
         <v>12.5</v>
@@ -1286,29 +1286,29 @@
         <v>12.5</v>
       </c>
       <c r="BA4" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BB4" t="n">
         <v>4.7</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>4.6</v>
       </c>
       <c r="BC4" t="n">
         <v>21</v>
       </c>
       <c r="BD4" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BE4" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BF4" t="n">
         <v>17.5</v>
       </c>
       <c r="BG4" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-24 15:41:44</t>
+          <t>2026-03-24 17:47:56</t>
         </is>
       </c>
     </row>
@@ -1339,22 +1339,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="G5" t="n">
-        <v>1.3</v>
+        <v>1.41</v>
       </c>
       <c r="H5" t="n">
-        <v>13.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I5" t="n">
         <v>1000</v>
       </c>
       <c r="J5" t="n">
-        <v>6.4</v>
+        <v>4.9</v>
       </c>
       <c r="K5" t="n">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="L5" t="n">
         <v>1.01</v>
@@ -1363,34 +1363,34 @@
         <v>1.02</v>
       </c>
       <c r="N5" t="n">
-        <v>2.4</v>
+        <v>2.02</v>
       </c>
       <c r="O5" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="P5" t="n">
-        <v>2.4</v>
+        <v>2.02</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.35</v>
+        <v>1.56</v>
       </c>
       <c r="R5" t="n">
-        <v>1.57</v>
+        <v>1.39</v>
       </c>
       <c r="S5" t="n">
-        <v>1.94</v>
+        <v>2.36</v>
       </c>
       <c r="T5" t="n">
         <v>1.01</v>
       </c>
       <c r="U5" t="n">
-        <v>1.01</v>
+        <v>1.66</v>
       </c>
       <c r="V5" t="n">
         <v>1.01</v>
       </c>
       <c r="W5" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="X5" t="n">
         <v>1000</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-24 15:41:44</t>
+          <t>2026-03-24 17:47:56</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
         <v>1.49</v>
       </c>
       <c r="G6" t="n">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="H6" t="n">
         <v>5.7</v>
@@ -1545,7 +1545,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="J6" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="K6" t="n">
         <v>5.1</v>
@@ -1584,7 +1584,7 @@
         <v>1.12</v>
       </c>
       <c r="W6" t="n">
-        <v>2.52</v>
+        <v>2.4</v>
       </c>
       <c r="X6" t="n">
         <v>22</v>
@@ -1647,10 +1647,10 @@
         <v>17</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AT6" t="n">
         <v>6.4</v>
@@ -1662,7 +1662,7 @@
         <v>19</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AX6" t="n">
         <v>7</v>
@@ -1674,7 +1674,7 @@
         <v>16</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BB6" t="n">
         <v>10.5</v>
@@ -1683,27 +1683,27 @@
         <v>12</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BF6" t="n">
         <v>6</v>
       </c>
       <c r="BG6" t="n">
-        <v>85</v>
+        <v>4.2</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-24 15:41:44</t>
+          <t>2026-03-24 17:47:56</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Turkish 2 Lig</t>
+          <t>Italian Serie D</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1713,72 +1713,72 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>10:30:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Ankaragucu</t>
+          <t>Lentigione Calcio</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ankaraspor</t>
+          <t>Pistoiese</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.92</v>
+        <v>1.01</v>
       </c>
       <c r="G7" t="n">
-        <v>2.24</v>
+        <v>1000</v>
       </c>
       <c r="H7" t="n">
-        <v>3.65</v>
+        <v>1.01</v>
       </c>
       <c r="I7" t="n">
-        <v>4.7</v>
+        <v>1000</v>
       </c>
       <c r="J7" t="n">
-        <v>3.25</v>
+        <v>1.02</v>
       </c>
       <c r="K7" t="n">
-        <v>4</v>
+        <v>1000</v>
       </c>
       <c r="L7" t="n">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="M7" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>3</v>
+        <v>1.24</v>
       </c>
       <c r="O7" t="n">
-        <v>1.33</v>
+        <v>1.01</v>
       </c>
       <c r="P7" t="n">
-        <v>1.79</v>
+        <v>1.24</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.96</v>
+        <v>1.01</v>
       </c>
       <c r="R7" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="S7" t="n">
-        <v>3.15</v>
+        <v>1.02</v>
       </c>
       <c r="T7" t="n">
-        <v>1.78</v>
+        <v>1.01</v>
       </c>
       <c r="U7" t="n">
-        <v>1.97</v>
+        <v>1.01</v>
       </c>
       <c r="V7" t="n">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="W7" t="n">
-        <v>1.8</v>
+        <v>1.01</v>
       </c>
       <c r="X7" t="n">
         <v>1000</v>
@@ -1793,10 +1793,10 @@
         <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AC7" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AD7" t="n">
         <v>1000</v>
@@ -1808,7 +1808,7 @@
         <v>1000</v>
       </c>
       <c r="AG7" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AH7" t="n">
         <v>1000</v>
@@ -1835,69 +1835,69 @@
         <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AQ7" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR7" t="n">
-        <v>3.8</v>
+        <v>1.01</v>
       </c>
       <c r="AS7" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="AT7" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AU7" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AV7" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AW7" t="n">
-        <v>3.95</v>
+        <v>1.01</v>
       </c>
       <c r="AX7" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AY7" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AZ7" t="n">
-        <v>3.6</v>
+        <v>1.01</v>
       </c>
       <c r="BA7" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BB7" t="n">
-        <v>3.75</v>
+        <v>1.01</v>
       </c>
       <c r="BC7" t="n">
-        <v>3.65</v>
+        <v>1.01</v>
       </c>
       <c r="BD7" t="n">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="BE7" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BF7" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BG7" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-24 15:41:44</t>
+          <t>2026-03-24 17:47:56</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Algerian Ligue 1</t>
+          <t>Italian Serie D</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1907,114 +1907,114 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>13:45:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Belouizdad</t>
+          <t>Ghivizzano Borgo A Mozz</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Vivi Altotevere Sansepo</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.8</v>
+        <v>1.01</v>
       </c>
       <c r="G8" t="n">
-        <v>3.25</v>
+        <v>1000</v>
       </c>
       <c r="H8" t="n">
-        <v>3</v>
+        <v>1.01</v>
       </c>
       <c r="I8" t="n">
-        <v>3.5</v>
+        <v>1000</v>
       </c>
       <c r="J8" t="n">
-        <v>2.64</v>
+        <v>1.02</v>
       </c>
       <c r="K8" t="n">
-        <v>2.96</v>
+        <v>1000</v>
       </c>
       <c r="L8" t="n">
-        <v>1.67</v>
+        <v>1.01</v>
       </c>
       <c r="M8" t="n">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>2.16</v>
+        <v>1.24</v>
       </c>
       <c r="O8" t="n">
-        <v>1.69</v>
+        <v>1.01</v>
       </c>
       <c r="P8" t="n">
-        <v>1.38</v>
+        <v>1.24</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.1</v>
+        <v>1.01</v>
       </c>
       <c r="R8" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="S8" t="n">
-        <v>6.2</v>
+        <v>1.02</v>
       </c>
       <c r="T8" t="n">
-        <v>2.28</v>
+        <v>1.01</v>
       </c>
       <c r="U8" t="n">
-        <v>1.62</v>
+        <v>1.01</v>
       </c>
       <c r="V8" t="n">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="W8" t="n">
-        <v>1.45</v>
+        <v>1.01</v>
       </c>
       <c r="X8" t="n">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="Y8" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="Z8" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AA8" t="n">
         <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="AC8" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AD8" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AE8" t="n">
         <v>1000</v>
       </c>
       <c r="AF8" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AG8" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AH8" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AI8" t="n">
         <v>1000</v>
       </c>
       <c r="AJ8" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AK8" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AL8" t="n">
         <v>1000</v>
@@ -2029,69 +2029,69 @@
         <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="AQ8" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AR8" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="AS8" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="AT8" t="n">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="AU8" t="n">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="AV8" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW8" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="AX8" t="n">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="AY8" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AZ8" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BA8" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BB8" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BC8" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BD8" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BE8" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BF8" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BG8" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-24 15:41:44</t>
+          <t>2026-03-24 17:47:56</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Turkish 2 Lig</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2101,105 +2101,105 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Albion FC</t>
+          <t>Ankaragucu</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Wanderers (Uru)</t>
+          <t>Ankaraspor</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.56</v>
+        <v>1.94</v>
       </c>
       <c r="G9" t="n">
-        <v>2.84</v>
+        <v>2.24</v>
       </c>
       <c r="H9" t="n">
-        <v>3.1</v>
+        <v>3.85</v>
       </c>
       <c r="I9" t="n">
-        <v>3.55</v>
+        <v>4.8</v>
       </c>
       <c r="J9" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="K9" t="n">
-        <v>3.25</v>
+        <v>3.85</v>
       </c>
       <c r="L9" t="n">
-        <v>1.51</v>
+        <v>1.37</v>
       </c>
       <c r="M9" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="N9" t="n">
-        <v>2.5</v>
+        <v>3.05</v>
       </c>
       <c r="O9" t="n">
-        <v>1.57</v>
+        <v>1.37</v>
       </c>
       <c r="P9" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.68</v>
+        <v>2.08</v>
       </c>
       <c r="R9" t="n">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="S9" t="n">
-        <v>5.5</v>
+        <v>3.85</v>
       </c>
       <c r="T9" t="n">
-        <v>2.12</v>
+        <v>1.86</v>
       </c>
       <c r="U9" t="n">
-        <v>1.74</v>
+        <v>1.92</v>
       </c>
       <c r="V9" t="n">
-        <v>1.39</v>
+        <v>1.26</v>
       </c>
       <c r="W9" t="n">
-        <v>1.54</v>
+        <v>1.8</v>
       </c>
       <c r="X9" t="n">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="Y9" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Z9" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AA9" t="n">
         <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>970</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC9" t="n">
-        <v>970</v>
+        <v>9.4</v>
       </c>
       <c r="AD9" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AE9" t="n">
         <v>1000</v>
       </c>
       <c r="AF9" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AG9" t="n">
-        <v>970</v>
+        <v>950</v>
       </c>
       <c r="AH9" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AI9" t="n">
         <v>1000</v>
@@ -2223,62 +2223,62 @@
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>6.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ9" t="n">
-        <v>7.2</v>
+        <v>10.5</v>
       </c>
       <c r="AR9" t="n">
-        <v>16</v>
+        <v>4.2</v>
       </c>
       <c r="AS9" t="n">
-        <v>8.6</v>
+        <v>4.5</v>
       </c>
       <c r="AT9" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AU9" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AV9" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AW9" t="n">
-        <v>2.66</v>
+        <v>4.4</v>
       </c>
       <c r="AX9" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BF9" t="n">
         <v>12</v>
       </c>
-      <c r="AY9" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>7</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>8</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>8</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="BG9" t="n">
-        <v>2.7</v>
+        <v>4.5</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-24 15:41:44</t>
+          <t>2026-03-24 17:47:56</t>
         </is>
       </c>
     </row>
@@ -2295,114 +2295,114 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>13:45:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Belouizdad</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.9</v>
+        <v>2.8</v>
       </c>
       <c r="G10" t="n">
-        <v>2.08</v>
+        <v>3.2</v>
       </c>
       <c r="H10" t="n">
-        <v>4.8</v>
+        <v>3</v>
       </c>
       <c r="I10" t="n">
-        <v>5.8</v>
+        <v>3.5</v>
       </c>
       <c r="J10" t="n">
-        <v>3.05</v>
+        <v>2.64</v>
       </c>
       <c r="K10" t="n">
-        <v>3.5</v>
+        <v>2.96</v>
       </c>
       <c r="L10" t="n">
-        <v>1.48</v>
+        <v>1.67</v>
       </c>
       <c r="M10" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="N10" t="n">
-        <v>2.5</v>
+        <v>2.16</v>
       </c>
       <c r="O10" t="n">
-        <v>1.53</v>
+        <v>1.69</v>
       </c>
       <c r="P10" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
       <c r="R10" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="S10" t="n">
-        <v>4.8</v>
+        <v>6.2</v>
       </c>
       <c r="T10" t="n">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="U10" t="n">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="V10" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="W10" t="n">
-        <v>1.9</v>
+        <v>1.45</v>
       </c>
       <c r="X10" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="Y10" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="Z10" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AA10" t="n">
         <v>1000</v>
       </c>
       <c r="AB10" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AC10" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD10" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AE10" t="n">
         <v>1000</v>
       </c>
       <c r="AF10" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AG10" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AI10" t="n">
         <v>1000</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AK10" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AL10" t="n">
         <v>1000</v>
@@ -2417,69 +2417,69 @@
         <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>6.4</v>
+        <v>5.7</v>
       </c>
       <c r="AQ10" t="n">
-        <v>9.4</v>
+        <v>6</v>
       </c>
       <c r="AR10" t="n">
-        <v>6.8</v>
+        <v>14</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.59</v>
+        <v>4.3</v>
       </c>
       <c r="AT10" t="n">
-        <v>4.8</v>
+        <v>5.7</v>
       </c>
       <c r="AU10" t="n">
-        <v>5.7</v>
+        <v>5.2</v>
       </c>
       <c r="AV10" t="n">
-        <v>6</v>
+        <v>11.5</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.59</v>
+        <v>4.3</v>
       </c>
       <c r="AX10" t="n">
-        <v>7.8</v>
+        <v>13</v>
       </c>
       <c r="AY10" t="n">
-        <v>8.4</v>
+        <v>11</v>
       </c>
       <c r="AZ10" t="n">
-        <v>6.4</v>
+        <v>20</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.65</v>
+        <v>4.4</v>
       </c>
       <c r="BB10" t="n">
-        <v>6.4</v>
+        <v>4.3</v>
       </c>
       <c r="BC10" t="n">
-        <v>6.6</v>
+        <v>4.2</v>
       </c>
       <c r="BD10" t="n">
-        <v>2.4</v>
+        <v>4.4</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.6</v>
+        <v>4.5</v>
       </c>
       <c r="BF10" t="n">
-        <v>6.4</v>
+        <v>4.3</v>
       </c>
       <c r="BG10" t="n">
-        <v>1.6</v>
+        <v>4.3</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-24 15:41:44</t>
+          <t>2026-03-24 17:47:56</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>English National League</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2489,84 +2489,84 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>16:45:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Morecambe</t>
+          <t>Albion FC</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hartlepool</t>
+          <t>Wanderers (Uru)</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3.25</v>
+        <v>2.56</v>
       </c>
       <c r="G11" t="n">
-        <v>3.7</v>
+        <v>2.84</v>
       </c>
       <c r="H11" t="n">
-        <v>2.22</v>
+        <v>3.1</v>
       </c>
       <c r="I11" t="n">
-        <v>2.42</v>
+        <v>3.55</v>
       </c>
       <c r="J11" t="n">
-        <v>3.4</v>
+        <v>2.88</v>
       </c>
       <c r="K11" t="n">
-        <v>4.1</v>
+        <v>3.2</v>
       </c>
       <c r="L11" t="n">
-        <v>1.28</v>
+        <v>1.52</v>
       </c>
       <c r="M11" t="n">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="N11" t="n">
-        <v>4.5</v>
+        <v>2.48</v>
       </c>
       <c r="O11" t="n">
-        <v>1.23</v>
+        <v>1.57</v>
       </c>
       <c r="P11" t="n">
-        <v>2.18</v>
+        <v>1.5</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.71</v>
+        <v>2.68</v>
       </c>
       <c r="R11" t="n">
-        <v>1.47</v>
+        <v>1.18</v>
       </c>
       <c r="S11" t="n">
-        <v>2.74</v>
+        <v>5.5</v>
       </c>
       <c r="T11" t="n">
-        <v>1.63</v>
+        <v>2.12</v>
       </c>
       <c r="U11" t="n">
-        <v>2.32</v>
+        <v>1.74</v>
       </c>
       <c r="V11" t="n">
-        <v>1.71</v>
+        <v>1.39</v>
       </c>
       <c r="W11" t="n">
-        <v>1.37</v>
+        <v>1.54</v>
       </c>
       <c r="X11" t="n">
-        <v>950</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y11" t="n">
         <v>970</v>
       </c>
       <c r="Z11" t="n">
-        <v>970</v>
+        <v>22</v>
       </c>
       <c r="AA11" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AB11" t="n">
         <v>970</v>
@@ -2575,105 +2575,105 @@
         <v>970</v>
       </c>
       <c r="AD11" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF11" t="n">
         <v>970</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>23</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>26</v>
       </c>
       <c r="AG11" t="n">
         <v>970</v>
       </c>
       <c r="AH11" t="n">
-        <v>970</v>
+        <v>950</v>
       </c>
       <c r="AI11" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AJ11" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AK11" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AL11" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AM11" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AN11" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AO11" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>14</v>
+        <v>6.4</v>
       </c>
       <c r="AQ11" t="n">
-        <v>5</v>
+        <v>7.2</v>
       </c>
       <c r="AR11" t="n">
-        <v>5.5</v>
+        <v>16</v>
       </c>
       <c r="AS11" t="n">
-        <v>3.45</v>
+        <v>8.6</v>
       </c>
       <c r="AT11" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AU11" t="n">
         <v>5.7</v>
       </c>
-      <c r="AU11" t="n">
-        <v>4.5</v>
-      </c>
       <c r="AV11" t="n">
-        <v>4.9</v>
+        <v>11.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>6</v>
+        <v>2.66</v>
       </c>
       <c r="AX11" t="n">
-        <v>6.2</v>
+        <v>12</v>
       </c>
       <c r="AY11" t="n">
-        <v>5.4</v>
+        <v>10</v>
       </c>
       <c r="AZ11" t="n">
-        <v>5.6</v>
+        <v>7</v>
       </c>
       <c r="BA11" t="n">
-        <v>3.5</v>
+        <v>2.72</v>
       </c>
       <c r="BB11" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BC11" t="n">
-        <v>2.46</v>
+        <v>8</v>
       </c>
       <c r="BD11" t="n">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="BE11" t="n">
-        <v>3.05</v>
+        <v>2.76</v>
       </c>
       <c r="BF11" t="n">
-        <v>6.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG11" t="n">
-        <v>5.3</v>
+        <v>2.7</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-24 15:41:44</t>
+          <t>2026-03-24 17:47:56</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>English National League</t>
+          <t>Algerian Ligue 1</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2683,105 +2683,105 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>16:45:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Truro City</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Solihull Moors</t>
+          <t>Kabylie</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.78</v>
+        <v>1.89</v>
       </c>
       <c r="G12" t="n">
-        <v>2.86</v>
+        <v>2.08</v>
       </c>
       <c r="H12" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="I12" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="K12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="N12" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q12" t="n">
         <v>2.58</v>
       </c>
-      <c r="I12" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="J12" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="K12" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="M12" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N12" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="O12" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="P12" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1.87</v>
-      </c>
       <c r="R12" t="n">
-        <v>1.37</v>
+        <v>1.18</v>
       </c>
       <c r="S12" t="n">
-        <v>3.2</v>
+        <v>4.8</v>
       </c>
       <c r="T12" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="U12" t="n">
-        <v>2.12</v>
+        <v>1.67</v>
       </c>
       <c r="V12" t="n">
-        <v>1.58</v>
+        <v>1.21</v>
       </c>
       <c r="W12" t="n">
-        <v>1.54</v>
+        <v>1.92</v>
       </c>
       <c r="X12" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Y12" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Z12" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AA12" t="n">
         <v>1000</v>
       </c>
       <c r="AB12" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AC12" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AD12" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AE12" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AF12" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AG12" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AH12" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AI12" t="n">
         <v>1000</v>
@@ -2805,62 +2805,62 @@
         <v>1000</v>
       </c>
       <c r="AP12" t="n">
-        <v>12.5</v>
+        <v>6.4</v>
       </c>
       <c r="AQ12" t="n">
-        <v>5</v>
+        <v>9.4</v>
       </c>
       <c r="AR12" t="n">
-        <v>13</v>
+        <v>6.8</v>
       </c>
       <c r="AS12" t="n">
-        <v>7</v>
+        <v>1.76</v>
       </c>
       <c r="AT12" t="n">
-        <v>8.800000000000001</v>
+        <v>4.8</v>
       </c>
       <c r="AU12" t="n">
-        <v>4.3</v>
+        <v>5.8</v>
       </c>
       <c r="AV12" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AW12" t="n">
-        <v>21</v>
+        <v>2.44</v>
       </c>
       <c r="AX12" t="n">
-        <v>5.8</v>
+        <v>7.8</v>
       </c>
       <c r="AY12" t="n">
-        <v>5.1</v>
+        <v>8.4</v>
       </c>
       <c r="AZ12" t="n">
-        <v>14</v>
+        <v>6.4</v>
       </c>
       <c r="BA12" t="n">
-        <v>30</v>
+        <v>2.24</v>
       </c>
       <c r="BB12" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="BC12" t="n">
-        <v>6.6</v>
+        <v>20</v>
       </c>
       <c r="BD12" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.81</v>
+        <v>1.6</v>
       </c>
       <c r="BF12" t="n">
-        <v>18.5</v>
+        <v>6.4</v>
       </c>
       <c r="BG12" t="n">
-        <v>17</v>
+        <v>1.6</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-24 15:41:44</t>
+          <t>2026-03-24 17:47:56</t>
         </is>
       </c>
     </row>
@@ -2882,179 +2882,179 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Scunthorpe</t>
+          <t>Morecambe</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>Hartlepool</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3.65</v>
+        <v>3.15</v>
       </c>
       <c r="G13" t="n">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="H13" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="I13" t="n">
-        <v>2.22</v>
+        <v>2.4</v>
       </c>
       <c r="J13" t="n">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="K13" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="L13" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="M13" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N13" t="n">
-        <v>3.95</v>
+        <v>4.5</v>
       </c>
       <c r="O13" t="n">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="P13" t="n">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.82</v>
+        <v>1.72</v>
       </c>
       <c r="R13" t="n">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="S13" t="n">
-        <v>3</v>
+        <v>2.74</v>
       </c>
       <c r="T13" t="n">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="U13" t="n">
-        <v>2.2</v>
+        <v>2.32</v>
       </c>
       <c r="V13" t="n">
-        <v>1.81</v>
+        <v>1.71</v>
       </c>
       <c r="W13" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="X13" t="n">
-        <v>19</v>
+        <v>950</v>
       </c>
       <c r="Y13" t="n">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="Z13" t="n">
-        <v>15.5</v>
+        <v>970</v>
       </c>
       <c r="AA13" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AB13" t="n">
-        <v>17.5</v>
+        <v>970</v>
       </c>
       <c r="AC13" t="n">
-        <v>9</v>
+        <v>970</v>
       </c>
       <c r="AD13" t="n">
-        <v>11</v>
+        <v>970</v>
       </c>
       <c r="AE13" t="n">
         <v>23</v>
       </c>
       <c r="AF13" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="AG13" t="n">
-        <v>16</v>
+        <v>970</v>
       </c>
       <c r="AH13" t="n">
-        <v>17.5</v>
+        <v>970</v>
       </c>
       <c r="AI13" t="n">
+        <v>34</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>60</v>
+      </c>
+      <c r="AK13" t="n">
         <v>36</v>
       </c>
-      <c r="AJ13" t="n">
-        <v>70</v>
-      </c>
-      <c r="AK13" t="n">
+      <c r="AL13" t="n">
         <v>42</v>
       </c>
-      <c r="AL13" t="n">
-        <v>50</v>
-      </c>
       <c r="AM13" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AN13" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="AO13" t="n">
-        <v>15</v>
+        <v>970</v>
       </c>
       <c r="AP13" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AQ13" t="n">
-        <v>9.199999999999999</v>
+        <v>5</v>
       </c>
       <c r="AR13" t="n">
-        <v>12.5</v>
+        <v>5.5</v>
       </c>
       <c r="AS13" t="n">
-        <v>19.5</v>
+        <v>3.45</v>
       </c>
       <c r="AT13" t="n">
-        <v>11.5</v>
+        <v>5.7</v>
       </c>
       <c r="AU13" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BB13" t="n">
         <v>7.4</v>
       </c>
-      <c r="AV13" t="n">
-        <v>9</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>18</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>14</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>7</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>50</v>
-      </c>
       <c r="BC13" t="n">
-        <v>34</v>
+        <v>2.46</v>
       </c>
       <c r="BD13" t="n">
-        <v>7.4</v>
+        <v>3.6</v>
       </c>
       <c r="BE13" t="n">
-        <v>7.8</v>
+        <v>3.05</v>
       </c>
       <c r="BF13" t="n">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="BG13" t="n">
-        <v>11</v>
+        <v>5.3</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-24 15:41:44</t>
+          <t>2026-03-24 17:47:56</t>
         </is>
       </c>
     </row>
@@ -3076,179 +3076,179 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Southend</t>
+          <t>Truro City</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Woking</t>
+          <t>Solihull Moors</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.68</v>
+        <v>2.78</v>
       </c>
       <c r="G14" t="n">
-        <v>1.74</v>
+        <v>2.86</v>
       </c>
       <c r="H14" t="n">
-        <v>5.4</v>
+        <v>2.64</v>
       </c>
       <c r="I14" t="n">
-        <v>6.6</v>
+        <v>2.8</v>
       </c>
       <c r="J14" t="n">
-        <v>3.95</v>
+        <v>3.5</v>
       </c>
       <c r="K14" t="n">
-        <v>4.5</v>
+        <v>3.65</v>
       </c>
       <c r="L14" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="M14" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N14" t="n">
         <v>4</v>
       </c>
       <c r="O14" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="P14" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.75</v>
+        <v>1.84</v>
       </c>
       <c r="R14" t="n">
         <v>1.41</v>
       </c>
       <c r="S14" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="T14" t="n">
-        <v>1.79</v>
+        <v>1.65</v>
       </c>
       <c r="U14" t="n">
-        <v>2.02</v>
+        <v>2.28</v>
       </c>
       <c r="V14" t="n">
-        <v>1.2</v>
+        <v>1.55</v>
       </c>
       <c r="W14" t="n">
-        <v>2.36</v>
+        <v>1.53</v>
       </c>
       <c r="X14" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>42</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>29</v>
+      </c>
+      <c r="AF14" t="n">
         <v>20</v>
       </c>
-      <c r="Y14" t="n">
+      <c r="AG14" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH14" t="n">
         <v>950</v>
       </c>
-      <c r="Z14" t="n">
-        <v>50</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>170</v>
-      </c>
-      <c r="AB14" t="n">
+      <c r="AI14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>46</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>42</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>26</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>16</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>17</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BB14" t="n">
         <v>9.6</v>
       </c>
-      <c r="AC14" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>24</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>80</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>85</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>18</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>36</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>120</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>100</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>55</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>9</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>55</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>14</v>
-      </c>
       <c r="BC14" t="n">
-        <v>14.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BD14" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="BE14" t="n">
-        <v>8.199999999999999</v>
+        <v>6.8</v>
       </c>
       <c r="BF14" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="BG14" t="n">
         <v>7.8</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-24 15:41:44</t>
+          <t>2026-03-24 17:47:56</t>
         </is>
       </c>
     </row>
@@ -3270,179 +3270,179 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Wealdstone</t>
+          <t>Scunthorpe</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Yeovil</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.91</v>
+        <v>3.5</v>
       </c>
       <c r="G15" t="n">
-        <v>2</v>
+        <v>3.95</v>
       </c>
       <c r="H15" t="n">
-        <v>4.4</v>
+        <v>2.06</v>
       </c>
       <c r="I15" t="n">
-        <v>4.8</v>
+        <v>2.2</v>
       </c>
       <c r="J15" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="K15" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="L15" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="M15" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N15" t="n">
-        <v>3.5</v>
+        <v>3.95</v>
       </c>
       <c r="O15" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="W15" t="n">
         <v>1.33</v>
       </c>
-      <c r="P15" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>2</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S15" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="U15" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="W15" t="n">
-        <v>2</v>
-      </c>
       <c r="X15" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="Y15" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="Z15" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>27</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>23</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>29</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AI15" t="n">
         <v>34</v>
       </c>
-      <c r="AA15" t="n">
-        <v>130</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>19</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>60</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>12</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH15" t="n">
+      <c r="AJ15" t="n">
+        <v>70</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>42</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>85</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>15</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AS15" t="n">
         <v>19.5</v>
       </c>
-      <c r="AI15" t="n">
-        <v>65</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>24</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>22</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>38</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>140</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>15</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>70</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>10</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>24</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>9.6</v>
-      </c>
       <c r="AT15" t="n">
+        <v>13</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>18</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA15" t="n">
         <v>7.6</v>
       </c>
-      <c r="AU15" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AW15" t="n">
+      <c r="BB15" t="n">
         <v>50</v>
       </c>
-      <c r="AX15" t="n">
-        <v>10</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>48</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>16.5</v>
-      </c>
       <c r="BC15" t="n">
-        <v>15.5</v>
+        <v>34</v>
       </c>
       <c r="BD15" t="n">
         <v>8</v>
       </c>
       <c r="BE15" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="BF15" t="n">
-        <v>12.5</v>
+        <v>7.8</v>
       </c>
       <c r="BG15" t="n">
-        <v>55</v>
+        <v>11</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-24 15:41:44</t>
+          <t>2026-03-24 17:47:56</t>
         </is>
       </c>
     </row>
@@ -3476,10 +3476,10 @@
         <v>3.5</v>
       </c>
       <c r="G16" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="H16" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="I16" t="n">
         <v>2.18</v>
@@ -3506,25 +3506,25 @@
         <v>2.28</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="R16" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="S16" t="n">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="T16" t="n">
         <v>1.6</v>
       </c>
       <c r="U16" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="V16" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="W16" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="X16" t="n">
         <v>24</v>
@@ -3539,10 +3539,10 @@
         <v>26</v>
       </c>
       <c r="AB16" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AC16" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD16" t="n">
         <v>11.5</v>
@@ -3551,13 +3551,13 @@
         <v>21</v>
       </c>
       <c r="AF16" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AG16" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AH16" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AI16" t="n">
         <v>32</v>
@@ -3566,7 +3566,7 @@
         <v>1000</v>
       </c>
       <c r="AK16" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AL16" t="n">
         <v>44</v>
@@ -3584,7 +3584,7 @@
         <v>14.5</v>
       </c>
       <c r="AQ16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AR16" t="n">
         <v>12</v>
@@ -3593,7 +3593,7 @@
         <v>21</v>
       </c>
       <c r="AT16" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AU16" t="n">
         <v>7.8</v>
@@ -3605,45 +3605,45 @@
         <v>17</v>
       </c>
       <c r="AX16" t="n">
-        <v>6.4</v>
+        <v>19</v>
       </c>
       <c r="AY16" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ16" t="n">
         <v>11.5</v>
       </c>
-      <c r="AZ16" t="n">
-        <v>12</v>
-      </c>
       <c r="BA16" t="n">
-        <v>6.4</v>
+        <v>21</v>
       </c>
       <c r="BB16" t="n">
-        <v>7.2</v>
+        <v>44</v>
       </c>
       <c r="BC16" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BD16" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="BE16" t="n">
         <v>50</v>
       </c>
       <c r="BF16" t="n">
-        <v>6.4</v>
+        <v>21</v>
       </c>
       <c r="BG16" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-24 15:41:44</t>
+          <t>2026-03-24 17:47:56</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Colombian Primera B</t>
+          <t>English National League</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3653,191 +3653,191 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>16:45:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Envigado</t>
+          <t>Southend</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Bogota</t>
+          <t>Woking</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.44</v>
+        <v>1.68</v>
       </c>
       <c r="G17" t="n">
-        <v>1.55</v>
+        <v>1.74</v>
       </c>
       <c r="H17" t="n">
-        <v>7.4</v>
+        <v>5.4</v>
       </c>
       <c r="I17" t="n">
+        <v>6</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K17" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N17" t="n">
+        <v>4</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="W17" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="X17" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>950</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>50</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>170</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>24</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>80</v>
+      </c>
+      <c r="AF17" t="n">
         <v>11.5</v>
       </c>
-      <c r="J17" t="n">
-        <v>4</v>
-      </c>
-      <c r="K17" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="L17" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="M17" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N17" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="O17" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="P17" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S17" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="W17" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="X17" t="n">
-        <v>15</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>27</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>7</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>11</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>40</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF17" t="n">
+      <c r="AG17" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>85</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>18</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>100</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>36</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>55</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>55</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>14</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>25</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF17" t="n">
         <v>8</v>
       </c>
-      <c r="AG17" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>38</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>22</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>65</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>11</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>7.4</v>
-      </c>
       <c r="BG17" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-24 15:41:44</t>
+          <t>2026-03-24 17:47:56</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>English National League</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3847,191 +3847,191 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>16:45:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Cerro</t>
+          <t>Wealdstone</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Juventud De Las Piedras</t>
+          <t>Yeovil</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>3.25</v>
+        <v>1.92</v>
       </c>
       <c r="G18" t="n">
+        <v>2</v>
+      </c>
+      <c r="H18" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I18" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K18" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N18" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S18" t="n">
         <v>3.55</v>
       </c>
-      <c r="H18" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="I18" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="J18" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="K18" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="L18" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="M18" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="N18" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="O18" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="P18" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S18" t="n">
-        <v>5.3</v>
-      </c>
       <c r="T18" t="n">
-        <v>2.08</v>
+        <v>1.84</v>
       </c>
       <c r="U18" t="n">
-        <v>1.76</v>
+        <v>2.02</v>
       </c>
       <c r="V18" t="n">
-        <v>1.53</v>
+        <v>1.27</v>
       </c>
       <c r="W18" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="X18" t="n">
-        <v>9.6</v>
+        <v>16.5</v>
       </c>
       <c r="Y18" t="n">
-        <v>970</v>
+        <v>15.5</v>
       </c>
       <c r="Z18" t="n">
-        <v>970</v>
+        <v>34</v>
       </c>
       <c r="AA18" t="n">
-        <v>46</v>
+        <v>130</v>
       </c>
       <c r="AB18" t="n">
-        <v>970</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC18" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>19</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>24</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>22</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>15</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>70</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>12</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>24</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>10</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AU18" t="n">
         <v>7.2</v>
       </c>
-      <c r="AD18" t="n">
-        <v>970</v>
-      </c>
-      <c r="AE18" t="n">
+      <c r="AV18" t="n">
+        <v>16</v>
+      </c>
+      <c r="AW18" t="n">
         <v>42</v>
       </c>
-      <c r="AF18" t="n">
-        <v>22</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>950</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>80</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>70</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>60</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>90</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>220</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>70</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>48</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AR18" t="n">
+      <c r="AX18" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>20</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>27</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BF18" t="n">
         <v>12.5</v>
       </c>
-      <c r="AS18" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>4</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>16</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>2.9</v>
-      </c>
       <c r="BG18" t="n">
-        <v>7.8</v>
+        <v>50</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-24 15:41:44</t>
+          <t>2026-03-24 17:47:56</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Colombian Primera B</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4041,191 +4041,191 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Deportivo Riestra</t>
+          <t>Envigado</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>San Lorenzo</t>
+          <t>Bogota</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.62</v>
+        <v>1.43</v>
       </c>
       <c r="G19" t="n">
-        <v>2.7</v>
+        <v>1.52</v>
       </c>
       <c r="H19" t="n">
-        <v>3.75</v>
+        <v>9</v>
       </c>
       <c r="I19" t="n">
-        <v>3.95</v>
+        <v>12</v>
       </c>
       <c r="J19" t="n">
-        <v>2.74</v>
+        <v>4.1</v>
       </c>
       <c r="K19" t="n">
-        <v>2.82</v>
+        <v>4.9</v>
       </c>
       <c r="L19" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="M19" t="n">
-        <v>1.21</v>
+        <v>1.08</v>
       </c>
       <c r="N19" t="n">
-        <v>2</v>
+        <v>3.1</v>
       </c>
       <c r="O19" t="n">
-        <v>1.91</v>
+        <v>1.37</v>
       </c>
       <c r="P19" t="n">
-        <v>1.27</v>
+        <v>1.76</v>
       </c>
       <c r="Q19" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="W19" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="X19" t="n">
+        <v>970</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>26</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>42</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>38</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>970</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>22</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>970</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>3</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AX19" t="n">
         <v>3.85</v>
       </c>
-      <c r="R19" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="S19" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="X19" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>26</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>110</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>24</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>110</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>14</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>17</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>48</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>210</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>48</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>65</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>160</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>570</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>85</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>220</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>16</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>38</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>16</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>38</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>11.5</v>
-      </c>
       <c r="AY19" t="n">
-        <v>15</v>
+        <v>1.71</v>
       </c>
       <c r="AZ19" t="n">
-        <v>25</v>
+        <v>1.44</v>
       </c>
       <c r="BA19" t="n">
-        <v>46</v>
+        <v>1.48</v>
       </c>
       <c r="BB19" t="n">
-        <v>24</v>
+        <v>4.7</v>
       </c>
       <c r="BC19" t="n">
-        <v>28</v>
+        <v>5.6</v>
       </c>
       <c r="BD19" t="n">
-        <v>44</v>
+        <v>1.46</v>
       </c>
       <c r="BE19" t="n">
-        <v>55</v>
+        <v>1.49</v>
       </c>
       <c r="BF19" t="n">
-        <v>32</v>
+        <v>2.8</v>
       </c>
       <c r="BG19" t="n">
-        <v>46</v>
+        <v>1.49</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-24 15:41:44</t>
+          <t>2026-03-24 17:47:56</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Colombian Primera B</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4235,191 +4235,191 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Barranquilla</t>
+          <t>Cerro</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Leones FC</t>
+          <t>Juventud De Las Piedras</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.95</v>
+        <v>2.94</v>
       </c>
       <c r="G20" t="n">
-        <v>2.16</v>
+        <v>3.3</v>
       </c>
       <c r="H20" t="n">
-        <v>4.1</v>
+        <v>2.72</v>
       </c>
       <c r="I20" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="J20" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="K20" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="N20" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S20" t="n">
         <v>5.3</v>
       </c>
-      <c r="J20" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="K20" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="L20" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="M20" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="N20" t="n">
-        <v>3</v>
-      </c>
-      <c r="O20" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="P20" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S20" t="n">
-        <v>4.1</v>
-      </c>
       <c r="T20" t="n">
-        <v>1.92</v>
+        <v>2.1</v>
       </c>
       <c r="U20" t="n">
-        <v>1.88</v>
+        <v>1.76</v>
       </c>
       <c r="V20" t="n">
-        <v>1.23</v>
+        <v>1.51</v>
       </c>
       <c r="W20" t="n">
-        <v>1.86</v>
+        <v>1.43</v>
       </c>
       <c r="X20" t="n">
-        <v>13.5</v>
+        <v>9.6</v>
       </c>
       <c r="Y20" t="n">
-        <v>16.5</v>
+        <v>8.4</v>
       </c>
       <c r="Z20" t="n">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="AA20" t="n">
-        <v>130</v>
+        <v>60</v>
       </c>
       <c r="AB20" t="n">
-        <v>8.199999999999999</v>
+        <v>970</v>
       </c>
       <c r="AC20" t="n">
-        <v>8.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="AD20" t="n">
-        <v>22</v>
+        <v>970</v>
       </c>
       <c r="AE20" t="n">
+        <v>44</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>20</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>950</v>
+      </c>
+      <c r="AI20" t="n">
         <v>80</v>
       </c>
-      <c r="AF20" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>26</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>95</v>
-      </c>
       <c r="AJ20" t="n">
-        <v>32</v>
+        <v>65</v>
       </c>
       <c r="AK20" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="AL20" t="n">
+        <v>90</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>220</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>70</v>
+      </c>
+      <c r="AO20" t="n">
         <v>60</v>
       </c>
-      <c r="AM20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>24</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>110</v>
-      </c>
       <c r="AP20" t="n">
-        <v>8.199999999999999</v>
+        <v>6.6</v>
       </c>
       <c r="AQ20" t="n">
-        <v>9.800000000000001</v>
+        <v>7.2</v>
       </c>
       <c r="AR20" t="n">
-        <v>4.5</v>
+        <v>5.9</v>
       </c>
       <c r="AS20" t="n">
-        <v>4.9</v>
+        <v>7.4</v>
       </c>
       <c r="AT20" t="n">
-        <v>5.8</v>
+        <v>7.2</v>
       </c>
       <c r="AU20" t="n">
-        <v>5.8</v>
+        <v>3.9</v>
       </c>
       <c r="AV20" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AW20" t="n">
-        <v>4.7</v>
+        <v>7.2</v>
       </c>
       <c r="AX20" t="n">
-        <v>8.800000000000001</v>
+        <v>16</v>
       </c>
       <c r="AY20" t="n">
-        <v>8</v>
+        <v>11.5</v>
       </c>
       <c r="AZ20" t="n">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="BA20" t="n">
-        <v>4.8</v>
+        <v>7.8</v>
       </c>
       <c r="BB20" t="n">
-        <v>18</v>
+        <v>7.6</v>
       </c>
       <c r="BC20" t="n">
-        <v>18</v>
+        <v>7.4</v>
       </c>
       <c r="BD20" t="n">
-        <v>4.7</v>
+        <v>6</v>
       </c>
       <c r="BE20" t="n">
-        <v>4.9</v>
+        <v>6.2</v>
       </c>
       <c r="BF20" t="n">
-        <v>14.5</v>
+        <v>46</v>
       </c>
       <c r="BG20" t="n">
-        <v>4.8</v>
+        <v>7.4</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-24 15:41:44</t>
+          <t>2026-03-24 17:47:56</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Paraguayan Primera Division</t>
+          <t>Argentinian Primera Division</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4429,184 +4429,184 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>19:30:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Guarani (Par)</t>
+          <t>Deportivo Riestra</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Club 2 de Mayo</t>
+          <t>San Lorenzo</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.92</v>
+        <v>2.62</v>
       </c>
       <c r="G21" t="n">
-        <v>2.06</v>
+        <v>2.7</v>
       </c>
       <c r="H21" t="n">
-        <v>4.4</v>
+        <v>3.75</v>
       </c>
       <c r="I21" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="N21" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="X21" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>26</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>110</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>24</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>110</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>48</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>210</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>48</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>65</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>160</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>570</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>85</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>220</v>
+      </c>
+      <c r="AP21" t="n">
         <v>4.9</v>
       </c>
-      <c r="J21" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="K21" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="L21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M21" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="N21" t="n">
-        <v>3</v>
-      </c>
-      <c r="O21" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="P21" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="S21" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="T21" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>1.01</v>
-      </c>
       <c r="AQ21" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="AS21" t="n">
-        <v>1.01</v>
+        <v>38</v>
       </c>
       <c r="AT21" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="AU21" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AV21" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.01</v>
+        <v>38</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="AZ21" t="n">
-        <v>1.01</v>
+        <v>24</v>
       </c>
       <c r="BA21" t="n">
-        <v>1.01</v>
+        <v>46</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.01</v>
+        <v>23</v>
       </c>
       <c r="BC21" t="n">
-        <v>1.01</v>
+        <v>28</v>
       </c>
       <c r="BD21" t="n">
-        <v>1.01</v>
+        <v>44</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.01</v>
+        <v>55</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="BG21" t="n">
-        <v>1.01</v>
+        <v>46</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-24 15:41:44</t>
+          <t>2026-03-24 17:47:56</t>
         </is>
       </c>
     </row>
@@ -4623,191 +4623,191 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Real Soacha Cundinamarca FC</t>
+          <t>Barranquilla</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Atletico FC Cali</t>
+          <t>Leones FC</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.54</v>
+        <v>1.95</v>
       </c>
       <c r="G22" t="n">
-        <v>1.67</v>
+        <v>2.16</v>
       </c>
       <c r="H22" t="n">
-        <v>6.4</v>
+        <v>4.1</v>
       </c>
       <c r="I22" t="n">
-        <v>9.6</v>
+        <v>5.1</v>
       </c>
       <c r="J22" t="n">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="K22" t="n">
-        <v>4.8</v>
+        <v>3.7</v>
       </c>
       <c r="L22" t="n">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="M22" t="n">
         <v>1.09</v>
       </c>
       <c r="N22" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="O22" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="P22" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.12</v>
+        <v>2.02</v>
       </c>
       <c r="R22" t="n">
         <v>1.25</v>
       </c>
       <c r="S22" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="T22" t="n">
-        <v>2.2</v>
+        <v>1.93</v>
       </c>
       <c r="U22" t="n">
-        <v>1.67</v>
+        <v>1.88</v>
       </c>
       <c r="V22" t="n">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="W22" t="n">
-        <v>2.48</v>
+        <v>1.86</v>
       </c>
       <c r="X22" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="Y22" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="Z22" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AA22" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AB22" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC22" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD22" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AE22" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AF22" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AG22" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH22" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AI22" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AK22" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AL22" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM22" t="n">
         <v>1000</v>
       </c>
       <c r="AN22" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AO22" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AP22" t="n">
-        <v>2.16</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.43</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR22" t="n">
-        <v>1.49</v>
+        <v>4.5</v>
       </c>
       <c r="AS22" t="n">
-        <v>1.52</v>
+        <v>4.8</v>
       </c>
       <c r="AT22" t="n">
-        <v>3.7</v>
+        <v>5.8</v>
       </c>
       <c r="AU22" t="n">
-        <v>4.4</v>
+        <v>5.8</v>
       </c>
       <c r="AV22" t="n">
-        <v>1.46</v>
+        <v>13</v>
       </c>
       <c r="AW22" t="n">
-        <v>1.51</v>
+        <v>4.7</v>
       </c>
       <c r="AX22" t="n">
-        <v>4.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY22" t="n">
         <v>8</v>
       </c>
       <c r="AZ22" t="n">
-        <v>1.46</v>
+        <v>15</v>
       </c>
       <c r="BA22" t="n">
-        <v>1.51</v>
+        <v>4.7</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.76</v>
+        <v>18</v>
       </c>
       <c r="BC22" t="n">
-        <v>1.43</v>
+        <v>18</v>
       </c>
       <c r="BD22" t="n">
-        <v>1.49</v>
+        <v>4.6</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.51</v>
+        <v>4.9</v>
       </c>
       <c r="BF22" t="n">
-        <v>9.6</v>
+        <v>14.5</v>
       </c>
       <c r="BG22" t="n">
-        <v>1.52</v>
+        <v>4.8</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-24 15:41:44</t>
+          <t>2026-03-24 17:47:56</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>US USL League One</t>
+          <t>Paraguayan Primera Division</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4817,72 +4817,72 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>19:30:00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Greenville Triumph SC</t>
+          <t>Guarani (Par)</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>New York Cosmos</t>
+          <t>Club 2 de Mayo</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.01</v>
+        <v>1.92</v>
       </c>
       <c r="G23" t="n">
-        <v>1000</v>
+        <v>2.06</v>
       </c>
       <c r="H23" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="I23" t="n">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="J23" t="n">
-        <v>1.02</v>
+        <v>3.45</v>
       </c>
       <c r="K23" t="n">
-        <v>950</v>
+        <v>3.85</v>
       </c>
       <c r="L23" t="n">
         <v>1.01</v>
       </c>
       <c r="M23" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N23" t="n">
-        <v>1.25</v>
+        <v>3</v>
       </c>
       <c r="O23" t="n">
-        <v>1.23</v>
+        <v>1.41</v>
       </c>
       <c r="P23" t="n">
-        <v>1.24</v>
+        <v>1.7</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.23</v>
+        <v>2.14</v>
       </c>
       <c r="R23" t="n">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="S23" t="n">
-        <v>1.66</v>
+        <v>4.2</v>
       </c>
       <c r="T23" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="U23" t="n">
-        <v>1.01</v>
+        <v>1.86</v>
       </c>
       <c r="V23" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="W23" t="n">
-        <v>1.01</v>
+        <v>1.95</v>
       </c>
       <c r="X23" t="n">
         <v>1000</v>
@@ -4939,52 +4939,52 @@
         <v>1000</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS23" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT23" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU23" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV23" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW23" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX23" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY23" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ23" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA23" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC23" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD23" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF23" t="n">
         <v>1.01</v>
@@ -4994,14 +4994,14 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-24 15:41:44</t>
+          <t>2026-03-24 17:47:56</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>US United Soccer League</t>
+          <t>Colombian Primera B</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5016,186 +5016,186 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Lexington SC</t>
+          <t>Real Soacha Cundinamarca FC</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Atletico FC Cali</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.6</v>
+        <v>1.54</v>
       </c>
       <c r="G24" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="H24" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="I24" t="n">
-        <v>7.4</v>
+        <v>9.6</v>
       </c>
       <c r="J24" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K24" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N24" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="P24" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S24" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="W24" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AT24" t="n">
         <v>3.7</v>
       </c>
-      <c r="K24" t="n">
+      <c r="AU24" t="n">
         <v>4.4</v>
       </c>
-      <c r="L24" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="M24" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N24" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="O24" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="P24" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S24" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="T24" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="W24" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="X24" t="n">
-        <v>18</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>25</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>65</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>240</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>950</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>130</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>28</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>120</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>22</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>48</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>170</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>13</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>170</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>4</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>6.8</v>
-      </c>
       <c r="AV24" t="n">
-        <v>18</v>
+        <v>1.46</v>
       </c>
       <c r="AW24" t="n">
-        <v>4.2</v>
+        <v>1.51</v>
       </c>
       <c r="AX24" t="n">
-        <v>7</v>
+        <v>4.1</v>
       </c>
       <c r="AY24" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AZ24" t="n">
-        <v>16.5</v>
+        <v>1.46</v>
       </c>
       <c r="BA24" t="n">
-        <v>4.1</v>
+        <v>1.51</v>
       </c>
       <c r="BB24" t="n">
-        <v>11.5</v>
+        <v>1.76</v>
       </c>
       <c r="BC24" t="n">
-        <v>13</v>
+        <v>1.43</v>
       </c>
       <c r="BD24" t="n">
-        <v>4</v>
+        <v>1.49</v>
       </c>
       <c r="BE24" t="n">
-        <v>4.2</v>
+        <v>1.51</v>
       </c>
       <c r="BF24" t="n">
-        <v>7.8</v>
+        <v>9.6</v>
       </c>
       <c r="BG24" t="n">
-        <v>4.2</v>
+        <v>1.52</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-24 15:41:44</t>
+          <t>2026-03-24 17:47:56</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>US USL League One</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5205,184 +5205,184 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Boston River</t>
+          <t>Greenville Triumph SC</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Penarol</t>
+          <t>New York Cosmos</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="G25" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="H25" t="n">
-        <v>1.61</v>
+        <v>1.01</v>
       </c>
       <c r="I25" t="n">
-        <v>1.65</v>
+        <v>1000</v>
       </c>
       <c r="J25" t="n">
-        <v>3.7</v>
+        <v>1.03</v>
       </c>
       <c r="K25" t="n">
-        <v>4.1</v>
+        <v>950</v>
       </c>
       <c r="L25" t="n">
-        <v>1.46</v>
+        <v>1.01</v>
       </c>
       <c r="M25" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="N25" t="n">
-        <v>3</v>
+        <v>1.25</v>
       </c>
       <c r="O25" t="n">
-        <v>1.41</v>
+        <v>1.23</v>
       </c>
       <c r="P25" t="n">
-        <v>1.68</v>
+        <v>1.24</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.2</v>
+        <v>1.23</v>
       </c>
       <c r="R25" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="S25" t="n">
-        <v>4.2</v>
+        <v>1.66</v>
       </c>
       <c r="T25" t="n">
-        <v>2.12</v>
+        <v>1.01</v>
       </c>
       <c r="U25" t="n">
-        <v>1.72</v>
+        <v>1.01</v>
       </c>
       <c r="V25" t="n">
-        <v>2.52</v>
+        <v>1.01</v>
       </c>
       <c r="W25" t="n">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="X25" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="Y25" t="n">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="Z25" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AA25" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AB25" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AC25" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AD25" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AE25" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AF25" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AG25" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AH25" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AI25" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AJ25" t="n">
-        <v>310</v>
+        <v>1000</v>
       </c>
       <c r="AK25" t="n">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AL25" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AM25" t="n">
-        <v>240</v>
+        <v>1000</v>
       </c>
       <c r="AN25" t="n">
-        <v>280</v>
+        <v>1000</v>
       </c>
       <c r="AO25" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AP25" t="n">
-        <v>8.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AQ25" t="n">
-        <v>5.6</v>
+        <v>1.03</v>
       </c>
       <c r="AR25" t="n">
-        <v>7.4</v>
+        <v>1.03</v>
       </c>
       <c r="AS25" t="n">
-        <v>12.5</v>
+        <v>1.03</v>
       </c>
       <c r="AT25" t="n">
-        <v>16</v>
+        <v>1.03</v>
       </c>
       <c r="AU25" t="n">
-        <v>7.6</v>
+        <v>1.03</v>
       </c>
       <c r="AV25" t="n">
-        <v>8.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AW25" t="n">
-        <v>17</v>
+        <v>1.03</v>
       </c>
       <c r="AX25" t="n">
-        <v>6.2</v>
+        <v>1.03</v>
       </c>
       <c r="AY25" t="n">
-        <v>22</v>
+        <v>1.03</v>
       </c>
       <c r="AZ25" t="n">
-        <v>20</v>
+        <v>1.03</v>
       </c>
       <c r="BA25" t="n">
-        <v>36</v>
+        <v>1.03</v>
       </c>
       <c r="BB25" t="n">
-        <v>6.8</v>
+        <v>1.03</v>
       </c>
       <c r="BC25" t="n">
-        <v>6.6</v>
+        <v>1.03</v>
       </c>
       <c r="BD25" t="n">
-        <v>6.6</v>
+        <v>1.03</v>
       </c>
       <c r="BE25" t="n">
-        <v>6.6</v>
+        <v>1.03</v>
       </c>
       <c r="BF25" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BG25" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-24 15:41:44</t>
+          <t>2026-03-24 17:47:56</t>
         </is>
       </c>
     </row>
@@ -5399,378 +5399,766 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Sporting Club Jacksonville</t>
+          <t>Lexington SC</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Miami FC</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.72</v>
+        <v>1.6</v>
       </c>
       <c r="G26" t="n">
-        <v>2.9</v>
+        <v>1.69</v>
       </c>
       <c r="H26" t="n">
-        <v>2.6</v>
+        <v>6</v>
       </c>
       <c r="I26" t="n">
-        <v>2.78</v>
+        <v>7.4</v>
       </c>
       <c r="J26" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="K26" t="n">
-        <v>3.95</v>
+        <v>4.4</v>
       </c>
       <c r="L26" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="M26" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N26" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="O26" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="P26" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S26" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="W26" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="X26" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>25</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>65</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>240</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>950</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>130</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>28</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>120</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>22</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>170</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>13</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>170</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AR26" t="n">
         <v>4</v>
       </c>
-      <c r="O26" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="P26" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S26" t="n">
-        <v>3</v>
-      </c>
-      <c r="T26" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="U26" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="V26" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="X26" t="n">
-        <v>19</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>22</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>46</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>34</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>22</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>19</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>44</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>48</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>34</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>44</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>90</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>26</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>25</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>14.5</v>
-      </c>
       <c r="AS26" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="AT26" t="n">
-        <v>9.6</v>
+        <v>5.9</v>
       </c>
       <c r="AU26" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV26" t="n">
-        <v>9.800000000000001</v>
+        <v>18</v>
       </c>
       <c r="AW26" t="n">
-        <v>21</v>
+        <v>4.2</v>
       </c>
       <c r="AX26" t="n">
-        <v>14.5</v>
+        <v>7</v>
       </c>
       <c r="AY26" t="n">
-        <v>9.4</v>
+        <v>7.4</v>
       </c>
       <c r="AZ26" t="n">
-        <v>12.5</v>
+        <v>16.5</v>
       </c>
       <c r="BA26" t="n">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="BB26" t="n">
-        <v>4.8</v>
+        <v>11.5</v>
       </c>
       <c r="BC26" t="n">
-        <v>4.6</v>
+        <v>13</v>
       </c>
       <c r="BD26" t="n">
-        <v>4.7</v>
+        <v>4</v>
       </c>
       <c r="BE26" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="BF26" t="n">
-        <v>17</v>
+        <v>7.8</v>
       </c>
       <c r="BG26" t="n">
-        <v>16.5</v>
+        <v>4.2</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-24 15:41:44</t>
+          <t>2026-03-24 17:47:56</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>US United Soccer League</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>20:30:00</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Sporting Club Jacksonville</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Miami FC</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="G27" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="H27" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="I27" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="J27" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K27" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="L27" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N27" t="n">
+        <v>4</v>
+      </c>
+      <c r="O27" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="P27" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S27" t="n">
+        <v>3</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="U27" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="X27" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>42</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>30</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>40</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>48</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>90</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>26</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>23</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>21</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>6</v>
+      </c>
+      <c r="BF27" t="n">
+        <v>17</v>
+      </c>
+      <c r="BG27" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BH27" t="inlineStr">
+        <is>
+          <t>2026-03-24 17:47:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Uruguayan Primera Division</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>20:30:00</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Boston River</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Penarol</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="G28" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J28" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="K28" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="L28" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="M28" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N28" t="n">
+        <v>3</v>
+      </c>
+      <c r="O28" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="P28" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S28" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="V28" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X28" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>17</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>20</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>22</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>65</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>30</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>32</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>310</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>160</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>160</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>230</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>280</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>14</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>16</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>17</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>22</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>36</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>7</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BF28" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BG28" t="n">
+        <v>11</v>
+      </c>
+      <c r="BH28" t="inlineStr">
+        <is>
+          <t>2026-03-24 17:47:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>Colombian Primera A</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>2026-03-25</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>22:00:00</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>America de Cali S.A</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>Llaneros FC</t>
         </is>
       </c>
-      <c r="F27" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="G27" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="H27" t="n">
+      <c r="F29" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="G29" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="H29" t="n">
         <v>7.2</v>
       </c>
-      <c r="I27" t="n">
+      <c r="I29" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="J27" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="K27" t="n">
+      <c r="J29" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="K29" t="n">
         <v>4.1</v>
       </c>
-      <c r="L27" t="n">
+      <c r="L29" t="n">
         <v>1.47</v>
       </c>
-      <c r="M27" t="n">
+      <c r="M29" t="n">
         <v>1.09</v>
       </c>
-      <c r="N27" t="n">
+      <c r="N29" t="n">
         <v>3.1</v>
       </c>
-      <c r="O27" t="n">
+      <c r="O29" t="n">
         <v>1.42</v>
       </c>
-      <c r="P27" t="n">
+      <c r="P29" t="n">
         <v>1.72</v>
       </c>
-      <c r="Q27" t="n">
+      <c r="Q29" t="n">
         <v>2.22</v>
       </c>
-      <c r="R27" t="n">
+      <c r="R29" t="n">
         <v>1.27</v>
       </c>
-      <c r="S27" t="n">
+      <c r="S29" t="n">
         <v>4.2</v>
       </c>
-      <c r="T27" t="n">
+      <c r="T29" t="n">
         <v>2.2</v>
       </c>
-      <c r="U27" t="n">
+      <c r="U29" t="n">
         <v>1.72</v>
       </c>
-      <c r="V27" t="n">
+      <c r="V29" t="n">
         <v>1.14</v>
       </c>
-      <c r="W27" t="n">
+      <c r="W29" t="n">
         <v>2.56</v>
       </c>
-      <c r="X27" t="n">
+      <c r="X29" t="n">
         <v>11.5</v>
       </c>
-      <c r="Y27" t="n">
+      <c r="Y29" t="n">
         <v>950</v>
       </c>
-      <c r="Z27" t="n">
+      <c r="Z29" t="n">
         <v>65</v>
       </c>
-      <c r="AA27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB27" t="n">
+      <c r="AA29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB29" t="n">
         <v>7.4</v>
       </c>
-      <c r="AC27" t="n">
+      <c r="AC29" t="n">
         <v>10</v>
       </c>
-      <c r="AD27" t="n">
+      <c r="AD29" t="n">
         <v>950</v>
       </c>
-      <c r="AE27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF27" t="n">
+      <c r="AE29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF29" t="n">
         <v>8.6</v>
       </c>
-      <c r="AG27" t="n">
+      <c r="AG29" t="n">
         <v>10.5</v>
       </c>
-      <c r="AH27" t="n">
+      <c r="AH29" t="n">
         <v>950</v>
       </c>
-      <c r="AI27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ27" t="n">
+      <c r="AI29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ29" t="n">
         <v>970</v>
       </c>
-      <c r="AK27" t="n">
+      <c r="AK29" t="n">
         <v>21</v>
       </c>
-      <c r="AL27" t="n">
+      <c r="AL29" t="n">
         <v>55</v>
       </c>
-      <c r="AM27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN27" t="n">
+      <c r="AM29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN29" t="n">
         <v>12.5</v>
       </c>
-      <c r="AO27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP27" t="n">
-        <v>10</v>
-      </c>
-      <c r="AQ27" t="n">
+      <c r="AO29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ29" t="n">
         <v>6.6</v>
       </c>
-      <c r="AR27" t="n">
+      <c r="AR29" t="n">
         <v>8.6</v>
       </c>
-      <c r="AS27" t="n">
+      <c r="AS29" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="AT27" t="n">
+      <c r="AT29" t="n">
         <v>5.9</v>
       </c>
-      <c r="AU27" t="n">
+      <c r="AU29" t="n">
         <v>8</v>
       </c>
-      <c r="AV27" t="n">
+      <c r="AV29" t="n">
         <v>7.4</v>
       </c>
-      <c r="AW27" t="n">
+      <c r="AW29" t="n">
         <v>9.4</v>
       </c>
-      <c r="AX27" t="n">
+      <c r="AX29" t="n">
         <v>7.6</v>
       </c>
-      <c r="AY27" t="n">
+      <c r="AY29" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AZ27" t="n">
+      <c r="AZ29" t="n">
         <v>7.4</v>
       </c>
-      <c r="BA27" t="n">
+      <c r="BA29" t="n">
         <v>9.4</v>
       </c>
-      <c r="BB27" t="n">
+      <c r="BB29" t="n">
         <v>13.5</v>
       </c>
-      <c r="BC27" t="n">
+      <c r="BC29" t="n">
         <v>17.5</v>
       </c>
-      <c r="BD27" t="n">
+      <c r="BD29" t="n">
         <v>8.4</v>
       </c>
-      <c r="BE27" t="n">
+      <c r="BE29" t="n">
         <v>9.6</v>
       </c>
-      <c r="BF27" t="n">
+      <c r="BF29" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="BG27" t="n">
+      <c r="BG29" t="n">
         <v>9.6</v>
       </c>
-      <c r="BH27" t="inlineStr">
-        <is>
-          <t>2026-03-24 15:41:44</t>
+      <c r="BH29" t="inlineStr">
+        <is>
+          <t>2026-03-24 17:47:56</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-25.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-25.xlsx
@@ -757,22 +757,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="G2" t="n">
         <v>5.4</v>
       </c>
       <c r="H2" t="n">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="I2" t="n">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="J2" t="n">
         <v>3.35</v>
       </c>
       <c r="K2" t="n">
-        <v>5.3</v>
+        <v>4.5</v>
       </c>
       <c r="L2" t="n">
         <v>1.01</v>
@@ -805,7 +805,7 @@
         <v>1.87</v>
       </c>
       <c r="V2" t="n">
-        <v>1.78</v>
+        <v>1.82</v>
       </c>
       <c r="W2" t="n">
         <v>1.23</v>
@@ -826,7 +826,7 @@
         <v>1000</v>
       </c>
       <c r="AC2" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AD2" t="n">
         <v>1000</v>
@@ -865,62 +865,62 @@
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="AQ2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AZ2" t="n">
         <v>3.3</v>
       </c>
-      <c r="AR2" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AU2" t="n">
+      <c r="BA2" t="n">
         <v>3.3</v>
       </c>
-      <c r="AV2" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>4.6</v>
-      </c>
       <c r="BB2" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="BC2" t="n">
-        <v>4.8</v>
+        <v>3.35</v>
       </c>
       <c r="BD2" t="n">
-        <v>4.8</v>
+        <v>3.35</v>
       </c>
       <c r="BE2" t="n">
-        <v>3.75</v>
+        <v>3.45</v>
       </c>
       <c r="BF2" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="BG2" t="n">
-        <v>4.1</v>
+        <v>3</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-24 17:47:56</t>
+          <t>2026-03-24 19:53:23</t>
         </is>
       </c>
     </row>
@@ -951,13 +951,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="G3" t="n">
         <v>7.8</v>
       </c>
       <c r="H3" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="I3" t="n">
         <v>1.86</v>
@@ -1062,7 +1062,7 @@
         <v>7.6</v>
       </c>
       <c r="AQ3" t="n">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
       <c r="AR3" t="n">
         <v>7</v>
@@ -1074,7 +1074,7 @@
         <v>11.5</v>
       </c>
       <c r="AU3" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AV3" t="n">
         <v>7.8</v>
@@ -1083,7 +1083,7 @@
         <v>16.5</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AY3" t="n">
         <v>18</v>
@@ -1092,29 +1092,29 @@
         <v>18.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BG3" t="n">
         <v>12</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-24 17:47:56</t>
+          <t>2026-03-24 19:53:23</t>
         </is>
       </c>
     </row>
@@ -1145,22 +1145,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.5</v>
+        <v>2.32</v>
       </c>
       <c r="G4" t="n">
         <v>2.6</v>
       </c>
       <c r="H4" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="I4" t="n">
         <v>3.35</v>
       </c>
       <c r="J4" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="K4" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L4" t="n">
         <v>1.41</v>
@@ -1187,13 +1187,13 @@
         <v>3.45</v>
       </c>
       <c r="T4" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="U4" t="n">
         <v>2.1</v>
       </c>
       <c r="V4" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="W4" t="n">
         <v>1.62</v>
@@ -1289,13 +1289,13 @@
         <v>4.9</v>
       </c>
       <c r="BB4" t="n">
-        <v>4.7</v>
+        <v>6.4</v>
       </c>
       <c r="BC4" t="n">
         <v>21</v>
       </c>
       <c r="BD4" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BE4" t="n">
         <v>5.1</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-24 17:47:56</t>
+          <t>2026-03-24 19:53:23</t>
         </is>
       </c>
     </row>
@@ -1366,13 +1366,13 @@
         <v>2.02</v>
       </c>
       <c r="O5" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="P5" t="n">
         <v>2.02</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="R5" t="n">
         <v>1.39</v>
@@ -1447,62 +1447,62 @@
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="BF5" t="n">
         <v>1.01</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-24 17:47:56</t>
+          <t>2026-03-24 19:53:23</t>
         </is>
       </c>
     </row>
@@ -1533,22 +1533,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="G6" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="H6" t="n">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="I6" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="K6" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="L6" t="n">
         <v>1.33</v>
@@ -1557,7 +1557,7 @@
         <v>1.05</v>
       </c>
       <c r="N6" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="O6" t="n">
         <v>1.25</v>
@@ -1572,131 +1572,131 @@
         <v>1.41</v>
       </c>
       <c r="S6" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="T6" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="U6" t="n">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="V6" t="n">
         <v>1.12</v>
       </c>
       <c r="W6" t="n">
-        <v>2.4</v>
+        <v>2.66</v>
       </c>
       <c r="X6" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="Z6" t="n">
-        <v>75</v>
+        <v>270</v>
       </c>
       <c r="AA6" t="n">
-        <v>250</v>
+        <v>290</v>
       </c>
       <c r="AB6" t="n">
         <v>10.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AD6" t="n">
         <v>32</v>
       </c>
       <c r="AE6" t="n">
-        <v>130</v>
+        <v>480</v>
       </c>
       <c r="AF6" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AG6" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AI6" t="n">
-        <v>110</v>
+        <v>390</v>
       </c>
       <c r="AJ6" t="n">
+        <v>15</v>
+      </c>
+      <c r="AK6" t="n">
         <v>17.5</v>
       </c>
-      <c r="AK6" t="n">
+      <c r="AL6" t="n">
+        <v>150</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>390</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>200</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AQ6" t="n">
         <v>20</v>
       </c>
-      <c r="AL6" t="n">
-        <v>44</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>150</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>160</v>
-      </c>
-      <c r="AP6" t="n">
+      <c r="AR6" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>11</v>
+      </c>
+      <c r="BC6" t="n">
         <v>13</v>
       </c>
-      <c r="AQ6" t="n">
-        <v>17</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>19</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>7</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>16</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>12</v>
-      </c>
       <c r="BD6" t="n">
-        <v>4</v>
+        <v>19.5</v>
       </c>
       <c r="BE6" t="n">
-        <v>4.2</v>
+        <v>5.4</v>
       </c>
       <c r="BF6" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BG6" t="n">
-        <v>4.2</v>
+        <v>5.5</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-24 17:47:56</t>
+          <t>2026-03-24 19:53:23</t>
         </is>
       </c>
     </row>
@@ -1727,22 +1727,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="G7" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="H7" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="I7" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="J7" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="K7" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L7" t="n">
         <v>1.01</v>
@@ -1775,10 +1775,10 @@
         <v>1.01</v>
       </c>
       <c r="V7" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W7" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X7" t="n">
         <v>1000</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-24 17:47:56</t>
+          <t>2026-03-24 19:53:23</t>
         </is>
       </c>
     </row>
@@ -1921,22 +1921,22 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="G8" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="H8" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="I8" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="J8" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="K8" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L8" t="n">
         <v>1.01</v>
@@ -1954,13 +1954,13 @@
         <v>1.24</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R8" t="n">
         <v>1.18</v>
       </c>
       <c r="S8" t="n">
-        <v>1.02</v>
+        <v>1.37</v>
       </c>
       <c r="T8" t="n">
         <v>1.01</v>
@@ -1969,10 +1969,10 @@
         <v>1.01</v>
       </c>
       <c r="V8" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W8" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X8" t="n">
         <v>1000</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-24 17:47:56</t>
+          <t>2026-03-24 19:53:23</t>
         </is>
       </c>
     </row>
@@ -2115,61 +2115,61 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.94</v>
+        <v>2.08</v>
       </c>
       <c r="G9" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="H9" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="I9" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J9" t="n">
         <v>3</v>
       </c>
       <c r="K9" t="n">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="L9" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="M9" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="N9" t="n">
-        <v>3.05</v>
+        <v>2.82</v>
       </c>
       <c r="O9" t="n">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="P9" t="n">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="R9" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="S9" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="T9" t="n">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="U9" t="n">
-        <v>1.92</v>
+        <v>1.84</v>
       </c>
       <c r="V9" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="W9" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="X9" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="Y9" t="n">
         <v>1000</v>
@@ -2181,10 +2181,10 @@
         <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC9" t="n">
-        <v>9.4</v>
+        <v>14</v>
       </c>
       <c r="AD9" t="n">
         <v>1000</v>
@@ -2223,16 +2223,16 @@
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>9.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="AQ9" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AR9" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AS9" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="AT9" t="n">
         <v>6.6</v>
@@ -2244,41 +2244,41 @@
         <v>12</v>
       </c>
       <c r="AW9" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BF9" t="n">
         <v>4.4</v>
       </c>
-      <c r="AX9" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>8</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>4</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>12</v>
-      </c>
       <c r="BG9" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-24 17:47:56</t>
+          <t>2026-03-24 19:53:23</t>
         </is>
       </c>
     </row>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="G10" t="n">
         <v>3.2</v>
@@ -2321,7 +2321,7 @@
         <v>3.5</v>
       </c>
       <c r="J10" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="K10" t="n">
         <v>2.96</v>
@@ -2351,10 +2351,10 @@
         <v>6.2</v>
       </c>
       <c r="T10" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="U10" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="V10" t="n">
         <v>1.4</v>
@@ -2363,7 +2363,7 @@
         <v>1.45</v>
       </c>
       <c r="X10" t="n">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="Y10" t="n">
         <v>9.4</v>
@@ -2420,25 +2420,25 @@
         <v>5.7</v>
       </c>
       <c r="AQ10" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="AR10" t="n">
         <v>14</v>
       </c>
       <c r="AS10" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="AT10" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="AU10" t="n">
-        <v>5.2</v>
+        <v>5.9</v>
       </c>
       <c r="AV10" t="n">
         <v>11.5</v>
       </c>
       <c r="AW10" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="AX10" t="n">
         <v>13</v>
@@ -2450,29 +2450,29 @@
         <v>20</v>
       </c>
       <c r="BA10" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="BB10" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BC10" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BD10" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="BE10" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="BF10" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BG10" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-24 17:47:56</t>
+          <t>2026-03-24 19:53:23</t>
         </is>
       </c>
     </row>
@@ -2503,19 +2503,19 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="G11" t="n">
         <v>2.84</v>
       </c>
       <c r="H11" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="I11" t="n">
         <v>3.55</v>
       </c>
       <c r="J11" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="K11" t="n">
         <v>3.2</v>
@@ -2527,7 +2527,7 @@
         <v>1.13</v>
       </c>
       <c r="N11" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="O11" t="n">
         <v>1.57</v>
@@ -2548,7 +2548,7 @@
         <v>2.12</v>
       </c>
       <c r="U11" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="V11" t="n">
         <v>1.39</v>
@@ -2557,22 +2557,22 @@
         <v>1.54</v>
       </c>
       <c r="X11" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Y11" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="Y11" t="n">
-        <v>970</v>
-      </c>
       <c r="Z11" t="n">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="AA11" t="n">
         <v>1000</v>
       </c>
       <c r="AB11" t="n">
-        <v>970</v>
+        <v>8</v>
       </c>
       <c r="AC11" t="n">
-        <v>970</v>
+        <v>7.2</v>
       </c>
       <c r="AD11" t="n">
         <v>18</v>
@@ -2584,7 +2584,7 @@
         <v>970</v>
       </c>
       <c r="AG11" t="n">
-        <v>970</v>
+        <v>32</v>
       </c>
       <c r="AH11" t="n">
         <v>950</v>
@@ -2620,7 +2620,7 @@
         <v>16</v>
       </c>
       <c r="AS11" t="n">
-        <v>8.6</v>
+        <v>10.5</v>
       </c>
       <c r="AT11" t="n">
         <v>6.2</v>
@@ -2632,7 +2632,7 @@
         <v>11.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>2.66</v>
+        <v>5.5</v>
       </c>
       <c r="AX11" t="n">
         <v>12</v>
@@ -2641,32 +2641,32 @@
         <v>10</v>
       </c>
       <c r="AZ11" t="n">
-        <v>7</v>
+        <v>17.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>2.72</v>
+        <v>5.7</v>
       </c>
       <c r="BB11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BC11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BD11" t="n">
-        <v>3.25</v>
+        <v>7.6</v>
       </c>
       <c r="BE11" t="n">
-        <v>2.76</v>
+        <v>5.9</v>
       </c>
       <c r="BF11" t="n">
-        <v>8.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.7</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-24 17:47:56</t>
+          <t>2026-03-24 19:53:23</t>
         </is>
       </c>
     </row>
@@ -2697,7 +2697,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="G12" t="n">
         <v>2.08</v>
@@ -2730,7 +2730,7 @@
         <v>1.5</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="R12" t="n">
         <v>1.18</v>
@@ -2751,7 +2751,7 @@
         <v>1.92</v>
       </c>
       <c r="X12" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="Y12" t="n">
         <v>1000</v>
@@ -2766,7 +2766,7 @@
         <v>1000</v>
       </c>
       <c r="AC12" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AD12" t="n">
         <v>1000</v>
@@ -2814,7 +2814,7 @@
         <v>6.8</v>
       </c>
       <c r="AS12" t="n">
-        <v>1.76</v>
+        <v>1.88</v>
       </c>
       <c r="AT12" t="n">
         <v>4.8</v>
@@ -2823,7 +2823,7 @@
         <v>5.8</v>
       </c>
       <c r="AV12" t="n">
-        <v>6</v>
+        <v>16.5</v>
       </c>
       <c r="AW12" t="n">
         <v>2.44</v>
@@ -2835,7 +2835,7 @@
         <v>8.4</v>
       </c>
       <c r="AZ12" t="n">
-        <v>6.4</v>
+        <v>19.5</v>
       </c>
       <c r="BA12" t="n">
         <v>2.24</v>
@@ -2850,17 +2850,17 @@
         <v>7.4</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.6</v>
+        <v>2.46</v>
       </c>
       <c r="BF12" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BG12" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-24 17:47:56</t>
+          <t>2026-03-24 19:53:23</t>
         </is>
       </c>
     </row>
@@ -2894,19 +2894,19 @@
         <v>3.15</v>
       </c>
       <c r="G13" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="H13" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="I13" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="J13" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="K13" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="L13" t="n">
         <v>1.28</v>
@@ -2939,10 +2939,10 @@
         <v>2.32</v>
       </c>
       <c r="V13" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="W13" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="X13" t="n">
         <v>950</v>
@@ -2960,7 +2960,7 @@
         <v>970</v>
       </c>
       <c r="AC13" t="n">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="AD13" t="n">
         <v>970</v>
@@ -2990,7 +2990,7 @@
         <v>42</v>
       </c>
       <c r="AM13" t="n">
-        <v>85</v>
+        <v>200</v>
       </c>
       <c r="AN13" t="n">
         <v>28</v>
@@ -3002,59 +3002,59 @@
         <v>14</v>
       </c>
       <c r="AQ13" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AR13" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AS13" t="n">
-        <v>3.45</v>
+        <v>21</v>
       </c>
       <c r="AT13" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AU13" t="n">
         <v>4.5</v>
       </c>
       <c r="AV13" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AW13" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="AX13" t="n">
-        <v>6.2</v>
+        <v>17.5</v>
       </c>
       <c r="AY13" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>24</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>28</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>19</v>
+      </c>
+      <c r="BG13" t="n">
         <v>5.4</v>
       </c>
-      <c r="AZ13" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>5.3</v>
-      </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-24 17:47:56</t>
+          <t>2026-03-24 19:53:23</t>
         </is>
       </c>
     </row>
@@ -3085,25 +3085,25 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.78</v>
+        <v>2.68</v>
       </c>
       <c r="G14" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="H14" t="n">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="I14" t="n">
         <v>2.8</v>
       </c>
       <c r="J14" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="K14" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="L14" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="M14" t="n">
         <v>1.06</v>
@@ -3112,22 +3112,22 @@
         <v>4</v>
       </c>
       <c r="O14" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="P14" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="R14" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="S14" t="n">
         <v>3</v>
       </c>
       <c r="T14" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="U14" t="n">
         <v>2.28</v>
@@ -3142,19 +3142,19 @@
         <v>16</v>
       </c>
       <c r="Y14" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="Z14" t="n">
-        <v>18.5</v>
+        <v>38</v>
       </c>
       <c r="AA14" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AB14" t="n">
-        <v>13.5</v>
+        <v>970</v>
       </c>
       <c r="AC14" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD14" t="n">
         <v>13</v>
@@ -3169,7 +3169,7 @@
         <v>13.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>950</v>
+        <v>25</v>
       </c>
       <c r="AI14" t="n">
         <v>1000</v>
@@ -3178,19 +3178,19 @@
         <v>46</v>
       </c>
       <c r="AK14" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AL14" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AM14" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AN14" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AO14" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AP14" t="n">
         <v>12.5</v>
@@ -3205,50 +3205,50 @@
         <v>9.4</v>
       </c>
       <c r="AT14" t="n">
-        <v>6.4</v>
+        <v>11.5</v>
       </c>
       <c r="AU14" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AV14" t="n">
         <v>11</v>
       </c>
       <c r="AW14" t="n">
-        <v>8.6</v>
+        <v>13</v>
       </c>
       <c r="AX14" t="n">
         <v>17</v>
       </c>
       <c r="AY14" t="n">
-        <v>6.4</v>
+        <v>11</v>
       </c>
       <c r="AZ14" t="n">
         <v>13</v>
       </c>
       <c r="BA14" t="n">
-        <v>9.199999999999999</v>
+        <v>18</v>
       </c>
       <c r="BB14" t="n">
         <v>9.6</v>
       </c>
       <c r="BC14" t="n">
-        <v>8.800000000000001</v>
+        <v>14.5</v>
       </c>
       <c r="BD14" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="BE14" t="n">
-        <v>6.8</v>
+        <v>10</v>
       </c>
       <c r="BF14" t="n">
-        <v>20</v>
+        <v>6.4</v>
       </c>
       <c r="BG14" t="n">
-        <v>7.8</v>
+        <v>17.5</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-24 17:47:56</t>
+          <t>2026-03-24 19:53:23</t>
         </is>
       </c>
     </row>
@@ -3279,22 +3279,22 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="G15" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="H15" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="I15" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="J15" t="n">
         <v>3.6</v>
       </c>
       <c r="K15" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L15" t="n">
         <v>1.33</v>
@@ -3306,49 +3306,49 @@
         <v>3.95</v>
       </c>
       <c r="O15" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="P15" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="R15" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="S15" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="T15" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="U15" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="V15" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="W15" t="n">
         <v>1.33</v>
       </c>
       <c r="X15" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="Y15" t="n">
         <v>11</v>
       </c>
       <c r="Z15" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AA15" t="n">
         <v>27</v>
       </c>
       <c r="AB15" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AC15" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD15" t="n">
         <v>11</v>
@@ -3357,7 +3357,7 @@
         <v>23</v>
       </c>
       <c r="AF15" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AG15" t="n">
         <v>15.5</v>
@@ -3372,13 +3372,13 @@
         <v>70</v>
       </c>
       <c r="AK15" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="AL15" t="n">
         <v>50</v>
       </c>
       <c r="AM15" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AN15" t="n">
         <v>40</v>
@@ -3411,7 +3411,7 @@
         <v>18</v>
       </c>
       <c r="AX15" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AY15" t="n">
         <v>11.5</v>
@@ -3420,29 +3420,29 @@
         <v>14</v>
       </c>
       <c r="BA15" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB15" t="n">
         <v>50</v>
       </c>
       <c r="BC15" t="n">
-        <v>34</v>
+        <v>8.6</v>
       </c>
       <c r="BD15" t="n">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="BE15" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="BF15" t="n">
-        <v>7.8</v>
+        <v>30</v>
       </c>
       <c r="BG15" t="n">
         <v>11</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-24 17:47:56</t>
+          <t>2026-03-24 19:53:23</t>
         </is>
       </c>
     </row>
@@ -3479,16 +3479,16 @@
         <v>3.85</v>
       </c>
       <c r="H16" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="I16" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="J16" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="K16" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="L16" t="n">
         <v>1.27</v>
@@ -3518,13 +3518,13 @@
         <v>1.6</v>
       </c>
       <c r="U16" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="V16" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="W16" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="X16" t="n">
         <v>24</v>
@@ -3533,7 +3533,7 @@
         <v>14</v>
       </c>
       <c r="Z16" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AA16" t="n">
         <v>26</v>
@@ -3542,7 +3542,7 @@
         <v>19</v>
       </c>
       <c r="AC16" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AD16" t="n">
         <v>11.5</v>
@@ -3557,7 +3557,7 @@
         <v>16</v>
       </c>
       <c r="AH16" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AI16" t="n">
         <v>32</v>
@@ -3584,7 +3584,7 @@
         <v>14.5</v>
       </c>
       <c r="AQ16" t="n">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="AR16" t="n">
         <v>12</v>
@@ -3596,7 +3596,7 @@
         <v>15.5</v>
       </c>
       <c r="AU16" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="AV16" t="n">
         <v>9.4</v>
@@ -3620,10 +3620,10 @@
         <v>44</v>
       </c>
       <c r="BC16" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BD16" t="n">
         <v>30</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>7.8</v>
       </c>
       <c r="BE16" t="n">
         <v>50</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-24 17:47:56</t>
+          <t>2026-03-24 19:53:23</t>
         </is>
       </c>
     </row>
@@ -3667,22 +3667,22 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="G17" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="H17" t="n">
         <v>5.4</v>
       </c>
       <c r="I17" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="J17" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="K17" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="L17" t="n">
         <v>1.32</v>
@@ -3691,43 +3691,43 @@
         <v>1.05</v>
       </c>
       <c r="N17" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="O17" t="n">
         <v>1.26</v>
       </c>
       <c r="P17" t="n">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="R17" t="n">
         <v>1.41</v>
       </c>
       <c r="S17" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="T17" t="n">
         <v>1.79</v>
       </c>
       <c r="U17" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="V17" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="W17" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="X17" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="Y17" t="n">
-        <v>950</v>
+        <v>40</v>
       </c>
       <c r="Z17" t="n">
-        <v>50</v>
+        <v>220</v>
       </c>
       <c r="AA17" t="n">
         <v>170</v>
@@ -3739,10 +3739,10 @@
         <v>10</v>
       </c>
       <c r="AD17" t="n">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="AE17" t="n">
-        <v>80</v>
+        <v>400</v>
       </c>
       <c r="AF17" t="n">
         <v>11.5</v>
@@ -3754,7 +3754,7 @@
         <v>21</v>
       </c>
       <c r="AI17" t="n">
-        <v>85</v>
+        <v>320</v>
       </c>
       <c r="AJ17" t="n">
         <v>17.5</v>
@@ -3766,13 +3766,13 @@
         <v>36</v>
       </c>
       <c r="AM17" t="n">
-        <v>120</v>
+        <v>390</v>
       </c>
       <c r="AN17" t="n">
         <v>9.6</v>
       </c>
       <c r="AO17" t="n">
-        <v>100</v>
+        <v>310</v>
       </c>
       <c r="AP17" t="n">
         <v>14.5</v>
@@ -3784,7 +3784,7 @@
         <v>36</v>
       </c>
       <c r="AS17" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AT17" t="n">
         <v>7.8</v>
@@ -3820,17 +3820,17 @@
         <v>25</v>
       </c>
       <c r="BE17" t="n">
-        <v>8.199999999999999</v>
+        <v>36</v>
       </c>
       <c r="BF17" t="n">
         <v>8</v>
       </c>
       <c r="BG17" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-24 17:47:56</t>
+          <t>2026-03-24 19:53:23</t>
         </is>
       </c>
     </row>
@@ -3873,10 +3873,10 @@
         <v>4.8</v>
       </c>
       <c r="J18" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K18" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="L18" t="n">
         <v>1.42</v>
@@ -3885,19 +3885,19 @@
         <v>1.07</v>
       </c>
       <c r="N18" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="O18" t="n">
         <v>1.34</v>
       </c>
       <c r="P18" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="R18" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="S18" t="n">
         <v>3.55</v>
@@ -3906,7 +3906,7 @@
         <v>1.84</v>
       </c>
       <c r="U18" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="V18" t="n">
         <v>1.27</v>
@@ -3924,16 +3924,16 @@
         <v>34</v>
       </c>
       <c r="AA18" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AB18" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AC18" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AD18" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AE18" t="n">
         <v>60</v>
@@ -3942,7 +3942,7 @@
         <v>12</v>
       </c>
       <c r="AG18" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH18" t="n">
         <v>19</v>
@@ -3951,7 +3951,7 @@
         <v>65</v>
       </c>
       <c r="AJ18" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AK18" t="n">
         <v>22</v>
@@ -3966,7 +3966,7 @@
         <v>15</v>
       </c>
       <c r="AO18" t="n">
-        <v>70</v>
+        <v>260</v>
       </c>
       <c r="AP18" t="n">
         <v>12</v>
@@ -3978,7 +3978,7 @@
         <v>24</v>
       </c>
       <c r="AS18" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AT18" t="n">
         <v>7.6</v>
@@ -3990,7 +3990,7 @@
         <v>16</v>
       </c>
       <c r="AW18" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="AX18" t="n">
         <v>10</v>
@@ -4002,7 +4002,7 @@
         <v>14</v>
       </c>
       <c r="BA18" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BB18" t="n">
         <v>20</v>
@@ -4014,17 +4014,17 @@
         <v>27</v>
       </c>
       <c r="BE18" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF18" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BG18" t="n">
-        <v>50</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-24 17:47:56</t>
+          <t>2026-03-24 19:53:23</t>
         </is>
       </c>
     </row>
@@ -4055,7 +4055,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="G19" t="n">
         <v>1.52</v>
@@ -4073,34 +4073,34 @@
         <v>4.9</v>
       </c>
       <c r="L19" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="M19" t="n">
         <v>1.08</v>
       </c>
       <c r="N19" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="O19" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="P19" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="R19" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S19" t="n">
         <v>3.6</v>
       </c>
       <c r="T19" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="U19" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="V19" t="n">
         <v>1.09</v>
@@ -4139,7 +4139,7 @@
         <v>970</v>
       </c>
       <c r="AH19" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AI19" t="n">
         <v>1000</v>
@@ -4148,77 +4148,77 @@
         <v>970</v>
       </c>
       <c r="AK19" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL19" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AM19" t="n">
         <v>1000</v>
       </c>
       <c r="AN19" t="n">
-        <v>970</v>
+        <v>44</v>
       </c>
       <c r="AO19" t="n">
         <v>1000</v>
       </c>
       <c r="AP19" t="n">
-        <v>3</v>
+        <v>5.2</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.85</v>
+        <v>4.2</v>
       </c>
       <c r="AR19" t="n">
-        <v>1.47</v>
+        <v>4.2</v>
       </c>
       <c r="AS19" t="n">
-        <v>1.49</v>
+        <v>4.2</v>
       </c>
       <c r="AT19" t="n">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="AU19" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="AV19" t="n">
-        <v>1.9</v>
+        <v>4.2</v>
       </c>
       <c r="AW19" t="n">
-        <v>1.48</v>
+        <v>4.2</v>
       </c>
       <c r="AX19" t="n">
-        <v>3.85</v>
+        <v>6.4</v>
       </c>
       <c r="AY19" t="n">
-        <v>1.71</v>
+        <v>4.1</v>
       </c>
       <c r="AZ19" t="n">
-        <v>1.44</v>
+        <v>2.98</v>
       </c>
       <c r="BA19" t="n">
-        <v>1.48</v>
+        <v>4.2</v>
       </c>
       <c r="BB19" t="n">
-        <v>4.7</v>
+        <v>5.8</v>
       </c>
       <c r="BC19" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BD19" t="n">
-        <v>1.46</v>
+        <v>3.1</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.49</v>
+        <v>3.2</v>
       </c>
       <c r="BF19" t="n">
-        <v>2.8</v>
+        <v>7</v>
       </c>
       <c r="BG19" t="n">
-        <v>1.49</v>
+        <v>4.2</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-24 17:47:56</t>
+          <t>2026-03-24 19:53:23</t>
         </is>
       </c>
     </row>
@@ -4249,7 +4249,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="G20" t="n">
         <v>3.3</v>
@@ -4258,7 +4258,7 @@
         <v>2.72</v>
       </c>
       <c r="I20" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="J20" t="n">
         <v>2.86</v>
@@ -4297,13 +4297,13 @@
         <v>1.76</v>
       </c>
       <c r="V20" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="W20" t="n">
         <v>1.43</v>
       </c>
       <c r="X20" t="n">
-        <v>9.6</v>
+        <v>8.6</v>
       </c>
       <c r="Y20" t="n">
         <v>8.4</v>
@@ -4363,22 +4363,22 @@
         <v>7.2</v>
       </c>
       <c r="AR20" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="AS20" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT20" t="n">
         <v>7.2</v>
       </c>
       <c r="AU20" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="AV20" t="n">
         <v>10</v>
       </c>
       <c r="AW20" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="AX20" t="n">
         <v>16</v>
@@ -4390,29 +4390,29 @@
         <v>17.5</v>
       </c>
       <c r="BA20" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BB20" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BC20" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BD20" t="n">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="BE20" t="n">
-        <v>6.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF20" t="n">
         <v>46</v>
       </c>
       <c r="BG20" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-24 17:47:56</t>
+          <t>2026-03-24 19:53:23</t>
         </is>
       </c>
     </row>
@@ -4446,19 +4446,19 @@
         <v>2.62</v>
       </c>
       <c r="G21" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="H21" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="I21" t="n">
         <v>3.95</v>
       </c>
       <c r="J21" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="K21" t="n">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="L21" t="n">
         <v>1.01</v>
@@ -4470,37 +4470,37 @@
         <v>1.98</v>
       </c>
       <c r="O21" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="P21" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.8</v>
+        <v>2.86</v>
       </c>
       <c r="R21" t="n">
         <v>1.08</v>
       </c>
       <c r="S21" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="T21" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="U21" t="n">
         <v>1.46</v>
       </c>
       <c r="V21" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W21" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="X21" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="Y21" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z21" t="n">
         <v>26</v>
@@ -4527,49 +4527,49 @@
         <v>17</v>
       </c>
       <c r="AH21" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AI21" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AJ21" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AK21" t="n">
         <v>65</v>
       </c>
       <c r="AL21" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AM21" t="n">
-        <v>570</v>
+        <v>540</v>
       </c>
       <c r="AN21" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AO21" t="n">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AP21" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AQ21" t="n">
         <v>7.2</v>
       </c>
       <c r="AR21" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AS21" t="n">
         <v>38</v>
       </c>
       <c r="AT21" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="AU21" t="n">
         <v>6.6</v>
       </c>
       <c r="AV21" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AW21" t="n">
         <v>38</v>
@@ -4587,7 +4587,7 @@
         <v>46</v>
       </c>
       <c r="BB21" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BC21" t="n">
         <v>28</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-24 17:47:56</t>
+          <t>2026-03-24 19:53:23</t>
         </is>
       </c>
     </row>
@@ -4637,25 +4637,25 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="G22" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="H22" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="I22" t="n">
         <v>5.1</v>
       </c>
       <c r="J22" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K22" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="L22" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="M22" t="n">
         <v>1.09</v>
@@ -4667,28 +4667,28 @@
         <v>1.41</v>
       </c>
       <c r="P22" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.02</v>
+        <v>2.16</v>
       </c>
       <c r="R22" t="n">
         <v>1.25</v>
       </c>
       <c r="S22" t="n">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="T22" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="U22" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="V22" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="W22" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="X22" t="n">
         <v>13.5</v>
@@ -4697,13 +4697,13 @@
         <v>16.5</v>
       </c>
       <c r="Z22" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AA22" t="n">
         <v>130</v>
       </c>
       <c r="AB22" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AC22" t="n">
         <v>8.199999999999999</v>
@@ -4715,7 +4715,7 @@
         <v>80</v>
       </c>
       <c r="AF22" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AG22" t="n">
         <v>13</v>
@@ -4724,83 +4724,83 @@
         <v>26</v>
       </c>
       <c r="AI22" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AJ22" t="n">
         <v>32</v>
       </c>
       <c r="AK22" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AL22" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AM22" t="n">
         <v>1000</v>
       </c>
       <c r="AN22" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AO22" t="n">
         <v>110</v>
       </c>
       <c r="AP22" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AQ22" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AR22" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="AS22" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="AT22" t="n">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="AU22" t="n">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="AV22" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AW22" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="AX22" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AY22" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AZ22" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BA22" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="BB22" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BC22" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BD22" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="BE22" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="BF22" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BG22" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-24 17:47:56</t>
+          <t>2026-03-24 19:53:23</t>
         </is>
       </c>
     </row>
@@ -4831,10 +4831,10 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="G23" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H23" t="n">
         <v>4.4</v>
@@ -4843,10 +4843,10 @@
         <v>4.9</v>
       </c>
       <c r="J23" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="K23" t="n">
-        <v>3.85</v>
+        <v>3.65</v>
       </c>
       <c r="L23" t="n">
         <v>1.01</v>
@@ -4855,16 +4855,16 @@
         <v>1.09</v>
       </c>
       <c r="N23" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="O23" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="P23" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="R23" t="n">
         <v>1.26</v>
@@ -4876,13 +4876,13 @@
         <v>2</v>
       </c>
       <c r="U23" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="V23" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="W23" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="X23" t="n">
         <v>1000</v>
@@ -4939,62 +4939,62 @@
         <v>1000</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AS23" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AT23" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AU23" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AV23" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AW23" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AX23" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AY23" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AZ23" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="BA23" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="BC23" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="BD23" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BG23" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-24 17:47:56</t>
+          <t>2026-03-24 19:53:23</t>
         </is>
       </c>
     </row>
@@ -5133,16 +5133,16 @@
         <v>1000</v>
       </c>
       <c r="AP24" t="n">
-        <v>2.16</v>
+        <v>2.26</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.43</v>
+        <v>4.2</v>
       </c>
       <c r="AR24" t="n">
-        <v>1.49</v>
+        <v>4.2</v>
       </c>
       <c r="AS24" t="n">
-        <v>1.52</v>
+        <v>4.2</v>
       </c>
       <c r="AT24" t="n">
         <v>3.7</v>
@@ -5151,10 +5151,10 @@
         <v>4.4</v>
       </c>
       <c r="AV24" t="n">
-        <v>1.46</v>
+        <v>4.2</v>
       </c>
       <c r="AW24" t="n">
-        <v>1.51</v>
+        <v>4.2</v>
       </c>
       <c r="AX24" t="n">
         <v>4.1</v>
@@ -5163,32 +5163,32 @@
         <v>8</v>
       </c>
       <c r="AZ24" t="n">
-        <v>1.46</v>
+        <v>1.58</v>
       </c>
       <c r="BA24" t="n">
-        <v>1.51</v>
+        <v>4.2</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.76</v>
+        <v>1.95</v>
       </c>
       <c r="BC24" t="n">
-        <v>1.43</v>
+        <v>1.55</v>
       </c>
       <c r="BD24" t="n">
-        <v>1.49</v>
+        <v>1.62</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.51</v>
+        <v>1.65</v>
       </c>
       <c r="BF24" t="n">
         <v>9.6</v>
       </c>
       <c r="BG24" t="n">
-        <v>1.52</v>
+        <v>4.2</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-24 17:47:56</t>
+          <t>2026-03-24 19:53:23</t>
         </is>
       </c>
     </row>
@@ -5219,19 +5219,19 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="G25" t="n">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="H25" t="n">
-        <v>1.01</v>
+        <v>2.9</v>
       </c>
       <c r="I25" t="n">
         <v>1000</v>
       </c>
       <c r="J25" t="n">
-        <v>1.03</v>
+        <v>2.44</v>
       </c>
       <c r="K25" t="n">
         <v>950</v>
@@ -5267,10 +5267,10 @@
         <v>1.01</v>
       </c>
       <c r="V25" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="W25" t="n">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="X25" t="n">
         <v>1000</v>
@@ -5327,62 +5327,62 @@
         <v>1000</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.03</v>
+        <v>1.78</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.03</v>
+        <v>1.84</v>
       </c>
       <c r="AR25" t="n">
-        <v>1.03</v>
+        <v>1.9</v>
       </c>
       <c r="AS25" t="n">
-        <v>1.03</v>
+        <v>1.91</v>
       </c>
       <c r="AT25" t="n">
-        <v>1.03</v>
+        <v>1.7</v>
       </c>
       <c r="AU25" t="n">
-        <v>1.03</v>
+        <v>1.69</v>
       </c>
       <c r="AV25" t="n">
-        <v>1.03</v>
+        <v>1.84</v>
       </c>
       <c r="AW25" t="n">
-        <v>1.03</v>
+        <v>1.9</v>
       </c>
       <c r="AX25" t="n">
-        <v>1.03</v>
+        <v>1.74</v>
       </c>
       <c r="AY25" t="n">
-        <v>1.03</v>
+        <v>1.71</v>
       </c>
       <c r="AZ25" t="n">
-        <v>1.03</v>
+        <v>1.83</v>
       </c>
       <c r="BA25" t="n">
-        <v>1.03</v>
+        <v>1.9</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.03</v>
+        <v>1.82</v>
       </c>
       <c r="BC25" t="n">
-        <v>1.03</v>
+        <v>1.8</v>
       </c>
       <c r="BD25" t="n">
-        <v>1.03</v>
+        <v>1.88</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.03</v>
+        <v>1.9</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.01</v>
+        <v>2.64</v>
       </c>
       <c r="BG25" t="n">
-        <v>1.01</v>
+        <v>1.91</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-24 17:47:56</t>
+          <t>2026-03-24 19:53:23</t>
         </is>
       </c>
     </row>
@@ -5413,70 +5413,70 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="G26" t="n">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="H26" t="n">
         <v>6</v>
       </c>
       <c r="I26" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="J26" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="K26" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="L26" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="M26" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="N26" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="O26" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="P26" t="n">
-        <v>1.9</v>
+        <v>2.14</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.95</v>
+        <v>1.71</v>
       </c>
       <c r="R26" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="S26" t="n">
-        <v>3.35</v>
+        <v>2.96</v>
       </c>
       <c r="T26" t="n">
-        <v>1.94</v>
+        <v>1.83</v>
       </c>
       <c r="U26" t="n">
-        <v>1.88</v>
+        <v>2.02</v>
       </c>
       <c r="V26" t="n">
         <v>1.16</v>
       </c>
       <c r="W26" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="X26" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="Y26" t="n">
-        <v>25</v>
+        <v>950</v>
       </c>
       <c r="Z26" t="n">
-        <v>65</v>
+        <v>220</v>
       </c>
       <c r="AA26" t="n">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="AB26" t="n">
         <v>9.4</v>
@@ -5485,67 +5485,67 @@
         <v>11.5</v>
       </c>
       <c r="AD26" t="n">
-        <v>950</v>
+        <v>24</v>
       </c>
       <c r="AE26" t="n">
-        <v>130</v>
+        <v>400</v>
       </c>
       <c r="AF26" t="n">
         <v>11.5</v>
       </c>
       <c r="AG26" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AH26" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="AI26" t="n">
-        <v>120</v>
+        <v>390</v>
       </c>
       <c r="AJ26" t="n">
+        <v>17</v>
+      </c>
+      <c r="AK26" t="n">
         <v>19.5</v>
       </c>
-      <c r="AK26" t="n">
-        <v>22</v>
-      </c>
       <c r="AL26" t="n">
-        <v>48</v>
+        <v>150</v>
       </c>
       <c r="AM26" t="n">
-        <v>170</v>
+        <v>390</v>
       </c>
       <c r="AN26" t="n">
+        <v>9</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>160</v>
+      </c>
+      <c r="AP26" t="n">
         <v>13</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>170</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>10.5</v>
       </c>
       <c r="AQ26" t="n">
         <v>14.5</v>
       </c>
       <c r="AR26" t="n">
-        <v>4</v>
+        <v>6.2</v>
       </c>
       <c r="AS26" t="n">
-        <v>4.2</v>
+        <v>6.6</v>
       </c>
       <c r="AT26" t="n">
-        <v>5.9</v>
+        <v>8</v>
       </c>
       <c r="AU26" t="n">
-        <v>6.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV26" t="n">
         <v>18</v>
       </c>
       <c r="AW26" t="n">
-        <v>4.2</v>
+        <v>6.4</v>
       </c>
       <c r="AX26" t="n">
-        <v>7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY26" t="n">
         <v>7.4</v>
@@ -5554,7 +5554,7 @@
         <v>16.5</v>
       </c>
       <c r="BA26" t="n">
-        <v>4.1</v>
+        <v>6.4</v>
       </c>
       <c r="BB26" t="n">
         <v>11.5</v>
@@ -5563,20 +5563,20 @@
         <v>13</v>
       </c>
       <c r="BD26" t="n">
-        <v>4</v>
+        <v>19.5</v>
       </c>
       <c r="BE26" t="n">
-        <v>4.2</v>
+        <v>6.4</v>
       </c>
       <c r="BF26" t="n">
-        <v>7.8</v>
+        <v>6.4</v>
       </c>
       <c r="BG26" t="n">
-        <v>4.2</v>
+        <v>6.4</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-24 17:47:56</t>
+          <t>2026-03-24 19:53:23</t>
         </is>
       </c>
     </row>
@@ -5607,142 +5607,142 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.84</v>
+        <v>2.62</v>
       </c>
       <c r="G27" t="n">
-        <v>3.05</v>
+        <v>2.68</v>
       </c>
       <c r="H27" t="n">
-        <v>2.54</v>
+        <v>2.78</v>
       </c>
       <c r="I27" t="n">
-        <v>2.66</v>
+        <v>2.88</v>
       </c>
       <c r="J27" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="K27" t="n">
         <v>3.85</v>
       </c>
       <c r="L27" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="M27" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N27" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="O27" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="P27" t="n">
-        <v>2.04</v>
+        <v>2.16</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.82</v>
+        <v>1.73</v>
       </c>
       <c r="R27" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="S27" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="T27" t="n">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="U27" t="n">
-        <v>2.22</v>
+        <v>2.32</v>
       </c>
       <c r="V27" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="W27" t="n">
-        <v>1.49</v>
+        <v>1.59</v>
       </c>
       <c r="X27" t="n">
         <v>19</v>
       </c>
       <c r="Y27" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="Z27" t="n">
-        <v>19.5</v>
+        <v>27</v>
       </c>
       <c r="AA27" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="AB27" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AC27" t="n">
         <v>9.6</v>
       </c>
       <c r="AD27" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AE27" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="AF27" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AG27" t="n">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="AH27" t="n">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="AI27" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="AJ27" t="n">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="AK27" t="n">
+        <v>26</v>
+      </c>
+      <c r="AL27" t="n">
         <v>34</v>
       </c>
-      <c r="AL27" t="n">
-        <v>44</v>
-      </c>
       <c r="AM27" t="n">
-        <v>90</v>
+        <v>200</v>
       </c>
       <c r="AN27" t="n">
-        <v>26</v>
+        <v>19.5</v>
       </c>
       <c r="AO27" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="AP27" t="n">
         <v>12.5</v>
       </c>
       <c r="AQ27" t="n">
-        <v>9.800000000000001</v>
+        <v>13</v>
       </c>
       <c r="AR27" t="n">
-        <v>14.5</v>
+        <v>19.5</v>
       </c>
       <c r="AS27" t="n">
         <v>5.6</v>
       </c>
       <c r="AT27" t="n">
-        <v>10.5</v>
+        <v>8</v>
       </c>
       <c r="AU27" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="AV27" t="n">
-        <v>9.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="AW27" t="n">
         <v>21</v>
       </c>
       <c r="AX27" t="n">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="AY27" t="n">
-        <v>10.5</v>
+        <v>8</v>
       </c>
       <c r="AZ27" t="n">
         <v>12.5</v>
@@ -5751,26 +5751,26 @@
         <v>5.6</v>
       </c>
       <c r="BB27" t="n">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="BC27" t="n">
-        <v>5.4</v>
+        <v>18.5</v>
       </c>
       <c r="BD27" t="n">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="BE27" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="BF27" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="BG27" t="n">
-        <v>16.5</v>
+        <v>21</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-24 17:47:56</t>
+          <t>2026-03-24 19:53:23</t>
         </is>
       </c>
     </row>
@@ -5804,19 +5804,19 @@
         <v>6.8</v>
       </c>
       <c r="G28" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="H28" t="n">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="I28" t="n">
         <v>1.7</v>
       </c>
       <c r="J28" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K28" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="L28" t="n">
         <v>1.46</v>
@@ -5825,16 +5825,16 @@
         <v>1.09</v>
       </c>
       <c r="N28" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="O28" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="P28" t="n">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="R28" t="n">
         <v>1.25</v>
@@ -5843,34 +5843,34 @@
         <v>4.2</v>
       </c>
       <c r="T28" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="U28" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="V28" t="n">
         <v>2.42</v>
       </c>
       <c r="W28" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="X28" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="Y28" t="n">
         <v>6.8</v>
       </c>
       <c r="Z28" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AA28" t="n">
         <v>17</v>
       </c>
       <c r="AB28" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AC28" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="AD28" t="n">
         <v>11</v>
@@ -5885,16 +5885,16 @@
         <v>30</v>
       </c>
       <c r="AH28" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AI28" t="n">
         <v>55</v>
       </c>
       <c r="AJ28" t="n">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="AK28" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AL28" t="n">
         <v>160</v>
@@ -5909,62 +5909,62 @@
         <v>14</v>
       </c>
       <c r="AP28" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ28" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="AR28" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AS28" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AT28" t="n">
         <v>16</v>
       </c>
       <c r="AU28" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV28" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AW28" t="n">
         <v>17</v>
       </c>
       <c r="AX28" t="n">
-        <v>6.6</v>
+        <v>26</v>
       </c>
       <c r="AY28" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AZ28" t="n">
         <v>22</v>
       </c>
-      <c r="AZ28" t="n">
-        <v>20</v>
-      </c>
       <c r="BA28" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="BB28" t="n">
-        <v>7.2</v>
+        <v>10</v>
       </c>
       <c r="BC28" t="n">
-        <v>7</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BD28" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="BE28" t="n">
-        <v>7.2</v>
+        <v>10</v>
       </c>
       <c r="BF28" t="n">
-        <v>7.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG28" t="n">
         <v>11</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-24 17:47:56</t>
+          <t>2026-03-24 19:53:23</t>
         </is>
       </c>
     </row>
@@ -5998,7 +5998,7 @@
         <v>1.61</v>
       </c>
       <c r="G29" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="H29" t="n">
         <v>7.2</v>
@@ -6046,13 +6046,13 @@
         <v>1.14</v>
       </c>
       <c r="W29" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="X29" t="n">
         <v>11.5</v>
       </c>
       <c r="Y29" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="Z29" t="n">
         <v>65</v>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-24 17:47:56</t>
+          <t>2026-03-24 19:53:23</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-25.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-25.xlsx
@@ -760,64 +760,64 @@
         <v>3.75</v>
       </c>
       <c r="G2" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="H2" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="I2" t="n">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="J2" t="n">
         <v>3.35</v>
       </c>
       <c r="K2" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="L2" t="n">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="M2" t="n">
         <v>1.08</v>
       </c>
       <c r="N2" t="n">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="O2" t="n">
         <v>1.38</v>
       </c>
       <c r="P2" t="n">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="R2" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="S2" t="n">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="T2" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="U2" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="V2" t="n">
-        <v>1.82</v>
+        <v>1.86</v>
       </c>
       <c r="W2" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="X2" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Y2" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="Z2" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AA2" t="n">
         <v>1000</v>
@@ -829,7 +829,7 @@
         <v>42</v>
       </c>
       <c r="AD2" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AE2" t="n">
         <v>1000</v>
@@ -862,65 +862,65 @@
         <v>1000</v>
       </c>
       <c r="AO2" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AP2" t="n">
-        <v>3.3</v>
+        <v>6.2</v>
       </c>
       <c r="AQ2" t="n">
-        <v>3.5</v>
+        <v>4.9</v>
       </c>
       <c r="AR2" t="n">
-        <v>3.35</v>
+        <v>5.8</v>
       </c>
       <c r="AS2" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="AT2" t="n">
-        <v>3.1</v>
+        <v>5.5</v>
       </c>
       <c r="AU2" t="n">
-        <v>3.4</v>
+        <v>4.9</v>
       </c>
       <c r="AV2" t="n">
-        <v>2.96</v>
+        <v>5.1</v>
       </c>
       <c r="AW2" t="n">
         <v>3.1</v>
       </c>
       <c r="AX2" t="n">
-        <v>3.2</v>
+        <v>2.4</v>
       </c>
       <c r="AY2" t="n">
-        <v>3</v>
+        <v>3.65</v>
       </c>
       <c r="AZ2" t="n">
-        <v>3.3</v>
+        <v>2.84</v>
       </c>
       <c r="BA2" t="n">
-        <v>3.3</v>
+        <v>1.9</v>
       </c>
       <c r="BB2" t="n">
-        <v>3.4</v>
+        <v>1.95</v>
       </c>
       <c r="BC2" t="n">
-        <v>3.35</v>
+        <v>1.91</v>
       </c>
       <c r="BD2" t="n">
-        <v>3.35</v>
+        <v>1.92</v>
       </c>
       <c r="BE2" t="n">
-        <v>3.45</v>
+        <v>1.96</v>
       </c>
       <c r="BF2" t="n">
-        <v>3.4</v>
+        <v>2.46</v>
       </c>
       <c r="BG2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-24 19:53:23</t>
+          <t>2026-03-24 21:58:49</t>
         </is>
       </c>
     </row>
@@ -996,7 +996,7 @@
         <v>2.12</v>
       </c>
       <c r="U3" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="V3" t="n">
         <v>2.16</v>
@@ -1005,7 +1005,7 @@
         <v>1.16</v>
       </c>
       <c r="X3" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="Y3" t="n">
         <v>7.8</v>
@@ -1017,7 +1017,7 @@
         <v>23</v>
       </c>
       <c r="AB3" t="n">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="AC3" t="n">
         <v>10</v>
@@ -1029,7 +1029,7 @@
         <v>28</v>
       </c>
       <c r="AF3" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="AG3" t="n">
         <v>30</v>
@@ -1041,16 +1041,16 @@
         <v>65</v>
       </c>
       <c r="AJ3" t="n">
-        <v>240</v>
+        <v>900</v>
       </c>
       <c r="AK3" t="n">
-        <v>140</v>
+        <v>480</v>
       </c>
       <c r="AL3" t="n">
-        <v>150</v>
+        <v>450</v>
       </c>
       <c r="AM3" t="n">
-        <v>240</v>
+        <v>580</v>
       </c>
       <c r="AN3" t="n">
         <v>230</v>
@@ -1083,7 +1083,7 @@
         <v>16.5</v>
       </c>
       <c r="AX3" t="n">
-        <v>4.2</v>
+        <v>5.1</v>
       </c>
       <c r="AY3" t="n">
         <v>18</v>
@@ -1092,29 +1092,29 @@
         <v>18.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="BB3" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="BC3" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="BD3" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="BE3" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="BF3" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="BG3" t="n">
         <v>12</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-24 19:53:23</t>
+          <t>2026-03-24 21:58:49</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="G4" t="n">
         <v>2.6</v>
@@ -1163,7 +1163,7 @@
         <v>3.7</v>
       </c>
       <c r="L4" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="M4" t="n">
         <v>1.07</v>
@@ -1193,7 +1193,7 @@
         <v>2.1</v>
       </c>
       <c r="V4" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="W4" t="n">
         <v>1.62</v>
@@ -1208,7 +1208,7 @@
         <v>23</v>
       </c>
       <c r="AA4" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AB4" t="n">
         <v>12.5</v>
@@ -1241,16 +1241,16 @@
         <v>34</v>
       </c>
       <c r="AL4" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AM4" t="n">
-        <v>120</v>
+        <v>440</v>
       </c>
       <c r="AN4" t="n">
         <v>28</v>
       </c>
       <c r="AO4" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AP4" t="n">
         <v>10.5</v>
@@ -1262,19 +1262,19 @@
         <v>15</v>
       </c>
       <c r="AS4" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AT4" t="n">
         <v>8</v>
       </c>
       <c r="AU4" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="AV4" t="n">
         <v>10</v>
       </c>
       <c r="AW4" t="n">
-        <v>4.7</v>
+        <v>14.5</v>
       </c>
       <c r="AX4" t="n">
         <v>12.5</v>
@@ -1286,29 +1286,29 @@
         <v>12.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BB4" t="n">
-        <v>6.4</v>
+        <v>16</v>
       </c>
       <c r="BC4" t="n">
         <v>21</v>
       </c>
       <c r="BD4" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BE4" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BF4" t="n">
         <v>17.5</v>
       </c>
       <c r="BG4" t="n">
-        <v>4.8</v>
+        <v>6.2</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-24 19:53:23</t>
+          <t>2026-03-24 21:58:49</t>
         </is>
       </c>
     </row>
@@ -1342,7 +1342,7 @@
         <v>1.18</v>
       </c>
       <c r="G5" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="H5" t="n">
         <v>9.199999999999999</v>
@@ -1351,7 +1351,7 @@
         <v>1000</v>
       </c>
       <c r="J5" t="n">
-        <v>4.9</v>
+        <v>6.2</v>
       </c>
       <c r="K5" t="n">
         <v>21</v>
@@ -1360,19 +1360,19 @@
         <v>1.01</v>
       </c>
       <c r="M5" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N5" t="n">
-        <v>2.02</v>
+        <v>4.6</v>
       </c>
       <c r="O5" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="P5" t="n">
-        <v>2.02</v>
+        <v>2.26</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.52</v>
+        <v>1.65</v>
       </c>
       <c r="R5" t="n">
         <v>1.39</v>
@@ -1390,7 +1390,7 @@
         <v>1.01</v>
       </c>
       <c r="W5" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="X5" t="n">
         <v>1000</v>
@@ -1441,7 +1441,7 @@
         <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AO5" t="n">
         <v>1000</v>
@@ -1498,11 +1498,11 @@
         <v>1.01</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.09</v>
+        <v>4.2</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-24 19:53:23</t>
+          <t>2026-03-24 21:58:49</t>
         </is>
       </c>
     </row>
@@ -1599,7 +1599,7 @@
         <v>290</v>
       </c>
       <c r="AB6" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC6" t="n">
         <v>11.5</v>
@@ -1611,10 +1611,10 @@
         <v>480</v>
       </c>
       <c r="AF6" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG6" t="n">
         <v>11</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>12.5</v>
       </c>
       <c r="AH6" t="n">
         <v>26</v>
@@ -1629,7 +1629,7 @@
         <v>17.5</v>
       </c>
       <c r="AL6" t="n">
-        <v>150</v>
+        <v>85</v>
       </c>
       <c r="AM6" t="n">
         <v>390</v>
@@ -1647,10 +1647,10 @@
         <v>20</v>
       </c>
       <c r="AR6" t="n">
-        <v>5.2</v>
+        <v>6.4</v>
       </c>
       <c r="AS6" t="n">
-        <v>5.5</v>
+        <v>6.8</v>
       </c>
       <c r="AT6" t="n">
         <v>7.2</v>
@@ -1662,7 +1662,7 @@
         <v>14</v>
       </c>
       <c r="AW6" t="n">
-        <v>5.4</v>
+        <v>6.6</v>
       </c>
       <c r="AX6" t="n">
         <v>7.6</v>
@@ -1674,7 +1674,7 @@
         <v>19</v>
       </c>
       <c r="BA6" t="n">
-        <v>5.4</v>
+        <v>6.4</v>
       </c>
       <c r="BB6" t="n">
         <v>11</v>
@@ -1686,17 +1686,17 @@
         <v>19.5</v>
       </c>
       <c r="BE6" t="n">
-        <v>5.4</v>
+        <v>6.6</v>
       </c>
       <c r="BF6" t="n">
         <v>6.2</v>
       </c>
       <c r="BG6" t="n">
-        <v>5.5</v>
+        <v>6.6</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-24 19:53:23</t>
+          <t>2026-03-24 21:58:49</t>
         </is>
       </c>
     </row>
@@ -1727,22 +1727,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.1</v>
+        <v>1.98</v>
       </c>
       <c r="G7" t="n">
-        <v>500</v>
+        <v>10.5</v>
       </c>
       <c r="H7" t="n">
-        <v>1.05</v>
+        <v>1.99</v>
       </c>
       <c r="I7" t="n">
-        <v>500</v>
+        <v>44</v>
       </c>
       <c r="J7" t="n">
-        <v>1.06</v>
+        <v>2.64</v>
       </c>
       <c r="K7" t="n">
-        <v>950</v>
+        <v>7.6</v>
       </c>
       <c r="L7" t="n">
         <v>1.01</v>
@@ -1775,10 +1775,10 @@
         <v>1.01</v>
       </c>
       <c r="V7" t="n">
-        <v>1.02</v>
+        <v>1.33</v>
       </c>
       <c r="W7" t="n">
-        <v>1.02</v>
+        <v>1.36</v>
       </c>
       <c r="X7" t="n">
         <v>1000</v>
@@ -1796,7 +1796,7 @@
         <v>1000</v>
       </c>
       <c r="AC7" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AD7" t="n">
         <v>1000</v>
@@ -1835,62 +1835,62 @@
         <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BG7" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-24 19:53:23</t>
+          <t>2026-03-24 21:58:49</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-24 19:53:23</t>
+          <t>2026-03-24 21:58:49</t>
         </is>
       </c>
     </row>
@@ -2115,7 +2115,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="G9" t="n">
         <v>2.26</v>
@@ -2130,7 +2130,7 @@
         <v>3</v>
       </c>
       <c r="K9" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L9" t="n">
         <v>1.4</v>
@@ -2169,7 +2169,7 @@
         <v>1.79</v>
       </c>
       <c r="X9" t="n">
-        <v>90</v>
+        <v>21</v>
       </c>
       <c r="Y9" t="n">
         <v>1000</v>
@@ -2196,7 +2196,7 @@
         <v>1000</v>
       </c>
       <c r="AG9" t="n">
-        <v>950</v>
+        <v>36</v>
       </c>
       <c r="AH9" t="n">
         <v>1000</v>
@@ -2229,10 +2229,10 @@
         <v>9.4</v>
       </c>
       <c r="AR9" t="n">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="AS9" t="n">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="AT9" t="n">
         <v>6.6</v>
@@ -2244,7 +2244,7 @@
         <v>12</v>
       </c>
       <c r="AW9" t="n">
-        <v>4.9</v>
+        <v>5.7</v>
       </c>
       <c r="AX9" t="n">
         <v>10.5</v>
@@ -2253,32 +2253,32 @@
         <v>8.4</v>
       </c>
       <c r="AZ9" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="BA9" t="n">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="BB9" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="BC9" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="BD9" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="BE9" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BF9" t="n">
         <v>5.1</v>
       </c>
-      <c r="BF9" t="n">
-        <v>4.4</v>
-      </c>
       <c r="BG9" t="n">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-24 19:53:23</t>
+          <t>2026-03-24 21:58:49</t>
         </is>
       </c>
     </row>
@@ -2309,13 +2309,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="G10" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="H10" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="I10" t="n">
         <v>3.5</v>
@@ -2324,7 +2324,7 @@
         <v>2.62</v>
       </c>
       <c r="K10" t="n">
-        <v>2.96</v>
+        <v>2.9</v>
       </c>
       <c r="L10" t="n">
         <v>1.67</v>
@@ -2360,7 +2360,7 @@
         <v>1.4</v>
       </c>
       <c r="W10" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="X10" t="n">
         <v>7</v>
@@ -2372,7 +2372,7 @@
         <v>24</v>
       </c>
       <c r="AA10" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AB10" t="n">
         <v>9</v>
@@ -2384,7 +2384,7 @@
         <v>19.5</v>
       </c>
       <c r="AE10" t="n">
-        <v>1000</v>
+        <v>440</v>
       </c>
       <c r="AF10" t="n">
         <v>22</v>
@@ -2399,10 +2399,10 @@
         <v>1000</v>
       </c>
       <c r="AJ10" t="n">
-        <v>75</v>
+        <v>400</v>
       </c>
       <c r="AK10" t="n">
-        <v>70</v>
+        <v>290</v>
       </c>
       <c r="AL10" t="n">
         <v>1000</v>
@@ -2426,7 +2426,7 @@
         <v>14</v>
       </c>
       <c r="AS10" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="AT10" t="n">
         <v>6.4</v>
@@ -2438,7 +2438,7 @@
         <v>11.5</v>
       </c>
       <c r="AW10" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AX10" t="n">
         <v>13</v>
@@ -2450,29 +2450,29 @@
         <v>20</v>
       </c>
       <c r="BA10" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BB10" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BC10" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="BD10" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BE10" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BF10" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="BG10" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-24 19:53:23</t>
+          <t>2026-03-24 21:58:49</t>
         </is>
       </c>
     </row>
@@ -2503,22 +2503,22 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="G11" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="H11" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="I11" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="J11" t="n">
         <v>3</v>
       </c>
       <c r="K11" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="L11" t="n">
         <v>1.52</v>
@@ -2527,7 +2527,7 @@
         <v>1.13</v>
       </c>
       <c r="N11" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="O11" t="n">
         <v>1.57</v>
@@ -2548,43 +2548,43 @@
         <v>2.12</v>
       </c>
       <c r="U11" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="V11" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W11" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="X11" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="Y11" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="Z11" t="n">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="AA11" t="n">
         <v>1000</v>
       </c>
       <c r="AB11" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC11" t="n">
         <v>7.2</v>
       </c>
       <c r="AD11" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AE11" t="n">
-        <v>1000</v>
+        <v>290</v>
       </c>
       <c r="AF11" t="n">
         <v>970</v>
       </c>
       <c r="AG11" t="n">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="AH11" t="n">
         <v>950</v>
@@ -2593,7 +2593,7 @@
         <v>1000</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK11" t="n">
         <v>1000</v>
@@ -2611,62 +2611,62 @@
         <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AQ11" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AR11" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="AS11" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT11" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU11" t="n">
         <v>6.2</v>
       </c>
-      <c r="AU11" t="n">
-        <v>5.7</v>
-      </c>
       <c r="AV11" t="n">
+        <v>13</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AY11" t="n">
         <v>11.5</v>
       </c>
-      <c r="AW11" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>12</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>10</v>
-      </c>
       <c r="AZ11" t="n">
-        <v>17.5</v>
+        <v>8.6</v>
       </c>
       <c r="BA11" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BB11" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BC11" t="n">
         <v>10</v>
       </c>
       <c r="BD11" t="n">
-        <v>7.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BE11" t="n">
-        <v>5.9</v>
+        <v>11</v>
       </c>
       <c r="BF11" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG11" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-24 19:53:23</t>
+          <t>2026-03-24 21:58:49</t>
         </is>
       </c>
     </row>
@@ -2703,7 +2703,7 @@
         <v>2.08</v>
       </c>
       <c r="H12" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="I12" t="n">
         <v>5.8</v>
@@ -2742,7 +2742,7 @@
         <v>2.2</v>
       </c>
       <c r="U12" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="V12" t="n">
         <v>1.21</v>
@@ -2751,7 +2751,7 @@
         <v>1.92</v>
       </c>
       <c r="X12" t="n">
-        <v>90</v>
+        <v>16</v>
       </c>
       <c r="Y12" t="n">
         <v>1000</v>
@@ -2763,7 +2763,7 @@
         <v>1000</v>
       </c>
       <c r="AB12" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AC12" t="n">
         <v>14</v>
@@ -2775,10 +2775,10 @@
         <v>1000</v>
       </c>
       <c r="AF12" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AG12" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AH12" t="n">
         <v>1000</v>
@@ -2787,10 +2787,10 @@
         <v>1000</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AK12" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AL12" t="n">
         <v>1000</v>
@@ -2811,22 +2811,22 @@
         <v>9.4</v>
       </c>
       <c r="AR12" t="n">
-        <v>6.8</v>
+        <v>14.5</v>
       </c>
       <c r="AS12" t="n">
-        <v>1.88</v>
+        <v>5</v>
       </c>
       <c r="AT12" t="n">
         <v>4.8</v>
       </c>
       <c r="AU12" t="n">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="AV12" t="n">
-        <v>16.5</v>
+        <v>6.4</v>
       </c>
       <c r="AW12" t="n">
-        <v>2.44</v>
+        <v>8.6</v>
       </c>
       <c r="AX12" t="n">
         <v>7.8</v>
@@ -2838,29 +2838,29 @@
         <v>19.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>2.24</v>
+        <v>3.2</v>
       </c>
       <c r="BB12" t="n">
-        <v>6.4</v>
+        <v>10.5</v>
       </c>
       <c r="BC12" t="n">
         <v>20</v>
       </c>
       <c r="BD12" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BE12" t="n">
-        <v>2.46</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF12" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BG12" t="n">
-        <v>1.8</v>
+        <v>2.84</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-24 19:53:23</t>
+          <t>2026-03-24 21:58:49</t>
         </is>
       </c>
     </row>
@@ -2894,19 +2894,19 @@
         <v>3.15</v>
       </c>
       <c r="G13" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="H13" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="I13" t="n">
         <v>2.38</v>
       </c>
       <c r="J13" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="K13" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L13" t="n">
         <v>1.28</v>
@@ -2915,7 +2915,7 @@
         <v>1.05</v>
       </c>
       <c r="N13" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="O13" t="n">
         <v>1.23</v>
@@ -2933,19 +2933,19 @@
         <v>2.74</v>
       </c>
       <c r="T13" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="U13" t="n">
         <v>2.32</v>
       </c>
       <c r="V13" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="W13" t="n">
         <v>1.4</v>
       </c>
       <c r="X13" t="n">
-        <v>950</v>
+        <v>38</v>
       </c>
       <c r="Y13" t="n">
         <v>970</v>
@@ -2954,73 +2954,73 @@
         <v>970</v>
       </c>
       <c r="AA13" t="n">
-        <v>30</v>
+        <v>900</v>
       </c>
       <c r="AB13" t="n">
         <v>970</v>
       </c>
       <c r="AC13" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AD13" t="n">
-        <v>970</v>
+        <v>20</v>
       </c>
       <c r="AE13" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="AF13" t="n">
-        <v>26</v>
+        <v>65</v>
       </c>
       <c r="AG13" t="n">
         <v>970</v>
       </c>
       <c r="AH13" t="n">
-        <v>970</v>
+        <v>26</v>
       </c>
       <c r="AI13" t="n">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="AJ13" t="n">
-        <v>60</v>
+        <v>900</v>
       </c>
       <c r="AK13" t="n">
-        <v>36</v>
+        <v>80</v>
       </c>
       <c r="AL13" t="n">
-        <v>42</v>
+        <v>95</v>
       </c>
       <c r="AM13" t="n">
-        <v>200</v>
+        <v>580</v>
       </c>
       <c r="AN13" t="n">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="AO13" t="n">
-        <v>970</v>
+        <v>55</v>
       </c>
       <c r="AP13" t="n">
         <v>14</v>
       </c>
       <c r="AQ13" t="n">
-        <v>5.1</v>
+        <v>7</v>
       </c>
       <c r="AR13" t="n">
-        <v>5.7</v>
+        <v>13</v>
       </c>
       <c r="AS13" t="n">
         <v>21</v>
       </c>
       <c r="AT13" t="n">
-        <v>5.8</v>
+        <v>8.4</v>
       </c>
       <c r="AU13" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="AV13" t="n">
-        <v>5</v>
+        <v>6.2</v>
       </c>
       <c r="AW13" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AX13" t="n">
         <v>17.5</v>
@@ -3029,13 +3029,13 @@
         <v>10.5</v>
       </c>
       <c r="AZ13" t="n">
-        <v>12</v>
+        <v>8.4</v>
       </c>
       <c r="BA13" t="n">
-        <v>4.5</v>
+        <v>7.2</v>
       </c>
       <c r="BB13" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC13" t="n">
         <v>24</v>
@@ -3044,17 +3044,17 @@
         <v>28</v>
       </c>
       <c r="BE13" t="n">
-        <v>4.8</v>
+        <v>7.2</v>
       </c>
       <c r="BF13" t="n">
         <v>19</v>
       </c>
       <c r="BG13" t="n">
-        <v>5.4</v>
+        <v>11.5</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-24 19:53:23</t>
+          <t>2026-03-24 21:58:49</t>
         </is>
       </c>
     </row>
@@ -3085,13 +3085,13 @@
         </is>
       </c>
       <c r="F14" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="H14" t="n">
         <v>2.68</v>
-      </c>
-      <c r="G14" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="H14" t="n">
-        <v>2.58</v>
       </c>
       <c r="I14" t="n">
         <v>2.8</v>
@@ -3100,7 +3100,7 @@
         <v>3.6</v>
       </c>
       <c r="K14" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L14" t="n">
         <v>1.37</v>
@@ -3118,7 +3118,7 @@
         <v>2.06</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="R14" t="n">
         <v>1.42</v>
@@ -3136,19 +3136,19 @@
         <v>1.55</v>
       </c>
       <c r="W14" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="X14" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Y14" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Z14" t="n">
-        <v>38</v>
+        <v>970</v>
       </c>
       <c r="AA14" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AB14" t="n">
         <v>970</v>
@@ -3157,10 +3157,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AD14" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AE14" t="n">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="AF14" t="n">
         <v>20</v>
@@ -3172,7 +3172,7 @@
         <v>25</v>
       </c>
       <c r="AI14" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AJ14" t="n">
         <v>46</v>
@@ -3181,34 +3181,34 @@
         <v>30</v>
       </c>
       <c r="AL14" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AM14" t="n">
         <v>200</v>
       </c>
       <c r="AN14" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AO14" t="n">
         <v>23</v>
       </c>
       <c r="AP14" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AQ14" t="n">
         <v>11</v>
       </c>
       <c r="AR14" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="AS14" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AT14" t="n">
         <v>11.5</v>
       </c>
       <c r="AU14" t="n">
-        <v>7</v>
+        <v>5.3</v>
       </c>
       <c r="AV14" t="n">
         <v>11</v>
@@ -3220,16 +3220,16 @@
         <v>17</v>
       </c>
       <c r="AY14" t="n">
+        <v>7</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BB14" t="n">
         <v>11</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>13</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>18</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>9.6</v>
       </c>
       <c r="BC14" t="n">
         <v>14.5</v>
@@ -3238,17 +3238,17 @@
         <v>20</v>
       </c>
       <c r="BE14" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="BF14" t="n">
-        <v>6.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG14" t="n">
         <v>17.5</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-24 19:53:23</t>
+          <t>2026-03-24 21:58:49</t>
         </is>
       </c>
     </row>
@@ -3279,13 +3279,13 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="G15" t="n">
         <v>4</v>
       </c>
       <c r="H15" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="I15" t="n">
         <v>2.18</v>
@@ -3294,7 +3294,7 @@
         <v>3.6</v>
       </c>
       <c r="K15" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L15" t="n">
         <v>1.33</v>
@@ -3303,31 +3303,31 @@
         <v>1.06</v>
       </c>
       <c r="N15" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="O15" t="n">
         <v>1.28</v>
       </c>
       <c r="P15" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="Q15" t="n">
         <v>1.82</v>
       </c>
       <c r="R15" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S15" t="n">
         <v>3.1</v>
       </c>
       <c r="T15" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="U15" t="n">
         <v>2.18</v>
       </c>
       <c r="V15" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="W15" t="n">
         <v>1.33</v>
@@ -3369,10 +3369,10 @@
         <v>34</v>
       </c>
       <c r="AJ15" t="n">
-        <v>70</v>
+        <v>900</v>
       </c>
       <c r="AK15" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="AL15" t="n">
         <v>50</v>
@@ -3411,7 +3411,7 @@
         <v>18</v>
       </c>
       <c r="AX15" t="n">
-        <v>7.8</v>
+        <v>13</v>
       </c>
       <c r="AY15" t="n">
         <v>11.5</v>
@@ -3420,19 +3420,19 @@
         <v>14</v>
       </c>
       <c r="BA15" t="n">
-        <v>8.199999999999999</v>
+        <v>16</v>
       </c>
       <c r="BB15" t="n">
         <v>50</v>
       </c>
       <c r="BC15" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BD15" t="n">
         <v>36</v>
       </c>
       <c r="BE15" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BF15" t="n">
         <v>30</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-24 19:53:23</t>
+          <t>2026-03-24 21:58:49</t>
         </is>
       </c>
     </row>
@@ -3476,19 +3476,19 @@
         <v>3.5</v>
       </c>
       <c r="G16" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="H16" t="n">
         <v>2.1</v>
       </c>
       <c r="I16" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="J16" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="K16" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L16" t="n">
         <v>1.27</v>
@@ -3506,7 +3506,7 @@
         <v>2.28</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="R16" t="n">
         <v>1.51</v>
@@ -3518,19 +3518,19 @@
         <v>1.6</v>
       </c>
       <c r="U16" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="V16" t="n">
         <v>1.83</v>
       </c>
       <c r="W16" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="X16" t="n">
         <v>24</v>
       </c>
       <c r="Y16" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Z16" t="n">
         <v>16.5</v>
@@ -3563,7 +3563,7 @@
         <v>32</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AK16" t="n">
         <v>40</v>
@@ -3572,7 +3572,7 @@
         <v>44</v>
       </c>
       <c r="AM16" t="n">
-        <v>1000</v>
+        <v>320</v>
       </c>
       <c r="AN16" t="n">
         <v>32</v>
@@ -3593,7 +3593,7 @@
         <v>21</v>
       </c>
       <c r="AT16" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AU16" t="n">
         <v>7.2</v>
@@ -3620,7 +3620,7 @@
         <v>44</v>
       </c>
       <c r="BC16" t="n">
-        <v>7.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BD16" t="n">
         <v>30</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-24 19:53:23</t>
+          <t>2026-03-24 21:58:49</t>
         </is>
       </c>
     </row>
@@ -3667,22 +3667,22 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="G17" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="H17" t="n">
         <v>5.4</v>
       </c>
       <c r="I17" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="J17" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K17" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="L17" t="n">
         <v>1.32</v>
@@ -3697,7 +3697,7 @@
         <v>1.26</v>
       </c>
       <c r="P17" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="Q17" t="n">
         <v>1.78</v>
@@ -3706,19 +3706,19 @@
         <v>1.41</v>
       </c>
       <c r="S17" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="T17" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="U17" t="n">
         <v>2.04</v>
       </c>
       <c r="V17" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="W17" t="n">
-        <v>2.32</v>
+        <v>2.42</v>
       </c>
       <c r="X17" t="n">
         <v>18</v>
@@ -3730,7 +3730,7 @@
         <v>220</v>
       </c>
       <c r="AA17" t="n">
-        <v>170</v>
+        <v>900</v>
       </c>
       <c r="AB17" t="n">
         <v>9.6</v>
@@ -3739,7 +3739,7 @@
         <v>10</v>
       </c>
       <c r="AD17" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AE17" t="n">
         <v>400</v>
@@ -3766,7 +3766,7 @@
         <v>36</v>
       </c>
       <c r="AM17" t="n">
-        <v>390</v>
+        <v>580</v>
       </c>
       <c r="AN17" t="n">
         <v>9.6</v>
@@ -3787,7 +3787,7 @@
         <v>9</v>
       </c>
       <c r="AT17" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AU17" t="n">
         <v>8.199999999999999</v>
@@ -3826,11 +3826,11 @@
         <v>8</v>
       </c>
       <c r="BG17" t="n">
-        <v>8.6</v>
+        <v>65</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-24 19:53:23</t>
+          <t>2026-03-24 21:58:49</t>
         </is>
       </c>
     </row>
@@ -3864,7 +3864,7 @@
         <v>1.92</v>
       </c>
       <c r="G18" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="H18" t="n">
         <v>4.3</v>
@@ -3873,13 +3873,13 @@
         <v>4.8</v>
       </c>
       <c r="J18" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K18" t="n">
         <v>3.85</v>
       </c>
       <c r="L18" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="M18" t="n">
         <v>1.07</v>
@@ -3894,7 +3894,7 @@
         <v>1.88</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="R18" t="n">
         <v>1.34</v>
@@ -3912,7 +3912,7 @@
         <v>1.27</v>
       </c>
       <c r="W18" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="X18" t="n">
         <v>16.5</v>
@@ -3936,7 +3936,7 @@
         <v>18.5</v>
       </c>
       <c r="AE18" t="n">
-        <v>60</v>
+        <v>320</v>
       </c>
       <c r="AF18" t="n">
         <v>12</v>
@@ -3948,7 +3948,7 @@
         <v>19</v>
       </c>
       <c r="AI18" t="n">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="AJ18" t="n">
         <v>23</v>
@@ -3957,7 +3957,7 @@
         <v>22</v>
       </c>
       <c r="AL18" t="n">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="AM18" t="n">
         <v>130</v>
@@ -3978,7 +3978,7 @@
         <v>24</v>
       </c>
       <c r="AS18" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT18" t="n">
         <v>7.6</v>
@@ -4002,7 +4002,7 @@
         <v>14</v>
       </c>
       <c r="BA18" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB18" t="n">
         <v>20</v>
@@ -4014,7 +4014,7 @@
         <v>27</v>
       </c>
       <c r="BE18" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BF18" t="n">
         <v>13</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-24 19:53:23</t>
+          <t>2026-03-24 21:58:49</t>
         </is>
       </c>
     </row>
@@ -4055,7 +4055,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="G19" t="n">
         <v>1.52</v>
@@ -4067,7 +4067,7 @@
         <v>12</v>
       </c>
       <c r="J19" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K19" t="n">
         <v>4.9</v>
@@ -4076,43 +4076,43 @@
         <v>1.41</v>
       </c>
       <c r="M19" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N19" t="n">
         <v>3.3</v>
       </c>
       <c r="O19" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="P19" t="n">
         <v>1.79</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="R19" t="n">
         <v>1.29</v>
       </c>
       <c r="S19" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="T19" t="n">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="U19" t="n">
         <v>1.64</v>
       </c>
       <c r="V19" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="W19" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="X19" t="n">
         <v>970</v>
       </c>
       <c r="Y19" t="n">
-        <v>26</v>
+        <v>70</v>
       </c>
       <c r="Z19" t="n">
         <v>1000</v>
@@ -4124,49 +4124,49 @@
         <v>970</v>
       </c>
       <c r="AC19" t="n">
-        <v>970</v>
+        <v>42</v>
       </c>
       <c r="AD19" t="n">
-        <v>42</v>
+        <v>180</v>
       </c>
       <c r="AE19" t="n">
         <v>1000</v>
       </c>
       <c r="AF19" t="n">
-        <v>970</v>
+        <v>40</v>
       </c>
       <c r="AG19" t="n">
-        <v>970</v>
+        <v>25</v>
       </c>
       <c r="AH19" t="n">
-        <v>34</v>
+        <v>150</v>
       </c>
       <c r="AI19" t="n">
         <v>1000</v>
       </c>
       <c r="AJ19" t="n">
-        <v>970</v>
+        <v>900</v>
       </c>
       <c r="AK19" t="n">
-        <v>21</v>
+        <v>70</v>
       </c>
       <c r="AL19" t="n">
-        <v>60</v>
+        <v>370</v>
       </c>
       <c r="AM19" t="n">
         <v>1000</v>
       </c>
       <c r="AN19" t="n">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="AO19" t="n">
         <v>1000</v>
       </c>
       <c r="AP19" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="AQ19" t="n">
-        <v>4.2</v>
+        <v>6.8</v>
       </c>
       <c r="AR19" t="n">
         <v>4.2</v>
@@ -4175,13 +4175,13 @@
         <v>4.2</v>
       </c>
       <c r="AT19" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="AU19" t="n">
-        <v>4.7</v>
+        <v>6.2</v>
       </c>
       <c r="AV19" t="n">
-        <v>4.2</v>
+        <v>7.4</v>
       </c>
       <c r="AW19" t="n">
         <v>4.2</v>
@@ -4190,25 +4190,25 @@
         <v>6.4</v>
       </c>
       <c r="AY19" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="AZ19" t="n">
-        <v>2.98</v>
+        <v>7.2</v>
       </c>
       <c r="BA19" t="n">
         <v>4.2</v>
       </c>
       <c r="BB19" t="n">
-        <v>5.8</v>
+        <v>9.6</v>
       </c>
       <c r="BC19" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BD19" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="BE19" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="BF19" t="n">
         <v>7</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-24 19:53:23</t>
+          <t>2026-03-24 21:58:49</t>
         </is>
       </c>
     </row>
@@ -4249,22 +4249,22 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.98</v>
+        <v>3.15</v>
       </c>
       <c r="G20" t="n">
         <v>3.3</v>
       </c>
       <c r="H20" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="I20" t="n">
-        <v>3</v>
+        <v>2.86</v>
       </c>
       <c r="J20" t="n">
-        <v>2.86</v>
+        <v>2.96</v>
       </c>
       <c r="K20" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="L20" t="n">
         <v>1.58</v>
@@ -4273,31 +4273,31 @@
         <v>1.13</v>
       </c>
       <c r="N20" t="n">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="O20" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="P20" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="R20" t="n">
         <v>1.18</v>
       </c>
       <c r="S20" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="T20" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="U20" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="V20" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="W20" t="n">
         <v>1.43</v>
@@ -4309,110 +4309,110 @@
         <v>8.4</v>
       </c>
       <c r="Z20" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AA20" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AB20" t="n">
-        <v>970</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC20" t="n">
         <v>7.2</v>
       </c>
       <c r="AD20" t="n">
-        <v>970</v>
+        <v>17</v>
       </c>
       <c r="AE20" t="n">
-        <v>44</v>
+        <v>90</v>
       </c>
       <c r="AF20" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AG20" t="n">
-        <v>970</v>
+        <v>19</v>
       </c>
       <c r="AH20" t="n">
-        <v>950</v>
+        <v>36</v>
       </c>
       <c r="AI20" t="n">
-        <v>80</v>
+        <v>170</v>
       </c>
       <c r="AJ20" t="n">
+        <v>900</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>110</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>200</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>210</v>
+      </c>
+      <c r="AN20" t="n">
         <v>65</v>
       </c>
-      <c r="AK20" t="n">
-        <v>50</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>90</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>220</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>70</v>
-      </c>
       <c r="AO20" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AP20" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AQ20" t="n">
         <v>7.2</v>
       </c>
       <c r="AR20" t="n">
-        <v>6.4</v>
+        <v>11.5</v>
       </c>
       <c r="AS20" t="n">
-        <v>8.199999999999999</v>
+        <v>24</v>
       </c>
       <c r="AT20" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AU20" t="n">
-        <v>4.1</v>
+        <v>6.2</v>
       </c>
       <c r="AV20" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AW20" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="AX20" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AY20" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AZ20" t="n">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="BA20" t="n">
-        <v>8.6</v>
+        <v>34</v>
       </c>
       <c r="BB20" t="n">
-        <v>8.4</v>
+        <v>42</v>
       </c>
       <c r="BC20" t="n">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="BD20" t="n">
-        <v>4.5</v>
+        <v>55</v>
       </c>
       <c r="BE20" t="n">
-        <v>9.199999999999999</v>
+        <v>70</v>
       </c>
       <c r="BF20" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="BG20" t="n">
-        <v>8.199999999999999</v>
+        <v>25</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-24 19:53:23</t>
+          <t>2026-03-24 21:58:49</t>
         </is>
       </c>
     </row>
@@ -4458,7 +4458,7 @@
         <v>2.72</v>
       </c>
       <c r="K21" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="L21" t="n">
         <v>1.01</v>
@@ -4467,7 +4467,7 @@
         <v>1.2</v>
       </c>
       <c r="N21" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="O21" t="n">
         <v>1.9</v>
@@ -4476,7 +4476,7 @@
         <v>1.27</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.86</v>
+        <v>3.5</v>
       </c>
       <c r="R21" t="n">
         <v>1.08</v>
@@ -4497,7 +4497,7 @@
         <v>1.57</v>
       </c>
       <c r="X21" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="Y21" t="n">
         <v>8.199999999999999</v>
@@ -4533,7 +4533,7 @@
         <v>200</v>
       </c>
       <c r="AJ21" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AK21" t="n">
         <v>65</v>
@@ -4545,13 +4545,13 @@
         <v>540</v>
       </c>
       <c r="AN21" t="n">
-        <v>90</v>
+        <v>210</v>
       </c>
       <c r="AO21" t="n">
         <v>210</v>
       </c>
       <c r="AP21" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="AQ21" t="n">
         <v>7.2</v>
@@ -4569,7 +4569,7 @@
         <v>6.6</v>
       </c>
       <c r="AV21" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AW21" t="n">
         <v>38</v>
@@ -4578,7 +4578,7 @@
         <v>11.5</v>
       </c>
       <c r="AY21" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AZ21" t="n">
         <v>24</v>
@@ -4596,7 +4596,7 @@
         <v>44</v>
       </c>
       <c r="BE21" t="n">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="BF21" t="n">
         <v>32</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-24 19:53:23</t>
+          <t>2026-03-24 21:58:49</t>
         </is>
       </c>
     </row>
@@ -4640,10 +4640,10 @@
         <v>1.91</v>
       </c>
       <c r="G22" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="H22" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="I22" t="n">
         <v>5.1</v>
@@ -4697,7 +4697,7 @@
         <v>16.5</v>
       </c>
       <c r="Z22" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AA22" t="n">
         <v>130</v>
@@ -4733,7 +4733,7 @@
         <v>29</v>
       </c>
       <c r="AL22" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AM22" t="n">
         <v>1000</v>
@@ -4751,10 +4751,10 @@
         <v>10</v>
       </c>
       <c r="AR22" t="n">
-        <v>4.9</v>
+        <v>13</v>
       </c>
       <c r="AS22" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AT22" t="n">
         <v>6.6</v>
@@ -4766,7 +4766,7 @@
         <v>13.5</v>
       </c>
       <c r="AW22" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AX22" t="n">
         <v>8.6</v>
@@ -4778,7 +4778,7 @@
         <v>15.5</v>
       </c>
       <c r="BA22" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BB22" t="n">
         <v>17.5</v>
@@ -4787,20 +4787,20 @@
         <v>20</v>
       </c>
       <c r="BD22" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BE22" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BF22" t="n">
         <v>13.5</v>
       </c>
       <c r="BG22" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-24 19:53:23</t>
+          <t>2026-03-24 21:58:49</t>
         </is>
       </c>
     </row>
@@ -4882,7 +4882,7 @@
         <v>1.25</v>
       </c>
       <c r="W23" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="X23" t="n">
         <v>1000</v>
@@ -4942,59 +4942,59 @@
         <v>5.8</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.1</v>
+        <v>1.32</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.1</v>
+        <v>1.32</v>
       </c>
       <c r="AS23" t="n">
-        <v>1.1</v>
+        <v>1.33</v>
       </c>
       <c r="AT23" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AU23" t="n">
-        <v>1.1</v>
+        <v>1.34</v>
       </c>
       <c r="AV23" t="n">
-        <v>1.1</v>
+        <v>1.32</v>
       </c>
       <c r="AW23" t="n">
-        <v>1.1</v>
+        <v>1.33</v>
       </c>
       <c r="AX23" t="n">
-        <v>1.1</v>
+        <v>1.29</v>
       </c>
       <c r="AY23" t="n">
-        <v>1.1</v>
+        <v>1.29</v>
       </c>
       <c r="AZ23" t="n">
-        <v>1.1</v>
+        <v>1.31</v>
       </c>
       <c r="BA23" t="n">
-        <v>1.1</v>
+        <v>1.33</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.1</v>
+        <v>1.33</v>
       </c>
       <c r="BC23" t="n">
-        <v>1.1</v>
+        <v>1.31</v>
       </c>
       <c r="BD23" t="n">
-        <v>1.1</v>
+        <v>1.33</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.1</v>
+        <v>1.34</v>
       </c>
       <c r="BF23" t="n">
         <v>4.4</v>
       </c>
       <c r="BG23" t="n">
-        <v>1.09</v>
+        <v>1.55</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-24 19:53:23</t>
+          <t>2026-03-24 21:58:49</t>
         </is>
       </c>
     </row>
@@ -5025,22 +5025,22 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="G24" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="H24" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="I24" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="J24" t="n">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="K24" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="L24" t="n">
         <v>1.01</v>
@@ -5049,16 +5049,16 @@
         <v>1.09</v>
       </c>
       <c r="N24" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="O24" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="P24" t="n">
         <v>1.67</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="R24" t="n">
         <v>1.25</v>
@@ -5076,7 +5076,7 @@
         <v>1.13</v>
       </c>
       <c r="W24" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="X24" t="n">
         <v>1000</v>
@@ -5091,10 +5091,10 @@
         <v>1000</v>
       </c>
       <c r="AB24" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AC24" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AD24" t="n">
         <v>1000</v>
@@ -5103,7 +5103,7 @@
         <v>1000</v>
       </c>
       <c r="AF24" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AG24" t="n">
         <v>1000</v>
@@ -5115,7 +5115,7 @@
         <v>1000</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK24" t="n">
         <v>1000</v>
@@ -5127,13 +5127,13 @@
         <v>1000</v>
       </c>
       <c r="AN24" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AO24" t="n">
         <v>1000</v>
       </c>
       <c r="AP24" t="n">
-        <v>2.26</v>
+        <v>4</v>
       </c>
       <c r="AQ24" t="n">
         <v>4.2</v>
@@ -5145,10 +5145,10 @@
         <v>4.2</v>
       </c>
       <c r="AT24" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="AU24" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="AV24" t="n">
         <v>4.2</v>
@@ -5157,28 +5157,28 @@
         <v>4.2</v>
       </c>
       <c r="AX24" t="n">
-        <v>4.1</v>
+        <v>6.8</v>
       </c>
       <c r="AY24" t="n">
         <v>8</v>
       </c>
       <c r="AZ24" t="n">
-        <v>1.58</v>
+        <v>2.56</v>
       </c>
       <c r="BA24" t="n">
         <v>4.2</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.95</v>
+        <v>3.85</v>
       </c>
       <c r="BC24" t="n">
-        <v>1.55</v>
+        <v>2.48</v>
       </c>
       <c r="BD24" t="n">
-        <v>1.62</v>
+        <v>2.3</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.65</v>
+        <v>2.2</v>
       </c>
       <c r="BF24" t="n">
         <v>9.6</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-24 19:53:23</t>
+          <t>2026-03-24 21:58:49</t>
         </is>
       </c>
     </row>
@@ -5222,16 +5222,16 @@
         <v>1.4</v>
       </c>
       <c r="G25" t="n">
-        <v>4.1</v>
+        <v>2.44</v>
       </c>
       <c r="H25" t="n">
-        <v>2.9</v>
+        <v>3.35</v>
       </c>
       <c r="I25" t="n">
         <v>1000</v>
       </c>
       <c r="J25" t="n">
-        <v>2.44</v>
+        <v>3.4</v>
       </c>
       <c r="K25" t="n">
         <v>950</v>
@@ -5270,7 +5270,7 @@
         <v>1.13</v>
       </c>
       <c r="W25" t="n">
-        <v>1.48</v>
+        <v>1.69</v>
       </c>
       <c r="X25" t="n">
         <v>1000</v>
@@ -5327,62 +5327,62 @@
         <v>1000</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.78</v>
+        <v>1.22</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.84</v>
+        <v>1.21</v>
       </c>
       <c r="AR25" t="n">
-        <v>1.9</v>
+        <v>1.23</v>
       </c>
       <c r="AS25" t="n">
-        <v>1.91</v>
+        <v>1.24</v>
       </c>
       <c r="AT25" t="n">
-        <v>1.7</v>
+        <v>1.19</v>
       </c>
       <c r="AU25" t="n">
-        <v>1.69</v>
+        <v>1.21</v>
       </c>
       <c r="AV25" t="n">
-        <v>1.84</v>
+        <v>1.21</v>
       </c>
       <c r="AW25" t="n">
-        <v>1.9</v>
+        <v>1.24</v>
       </c>
       <c r="AX25" t="n">
-        <v>1.74</v>
+        <v>1.24</v>
       </c>
       <c r="AY25" t="n">
-        <v>1.71</v>
+        <v>1.2</v>
       </c>
       <c r="AZ25" t="n">
-        <v>1.83</v>
+        <v>1.24</v>
       </c>
       <c r="BA25" t="n">
-        <v>1.9</v>
+        <v>1.24</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.82</v>
+        <v>1.24</v>
       </c>
       <c r="BC25" t="n">
-        <v>1.8</v>
+        <v>1.22</v>
       </c>
       <c r="BD25" t="n">
-        <v>1.88</v>
+        <v>1.24</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.9</v>
+        <v>1.24</v>
       </c>
       <c r="BF25" t="n">
-        <v>2.64</v>
+        <v>1.21</v>
       </c>
       <c r="BG25" t="n">
-        <v>1.91</v>
+        <v>1.55</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-24 19:53:23</t>
+          <t>2026-03-24 21:58:49</t>
         </is>
       </c>
     </row>
@@ -5413,79 +5413,79 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.56</v>
+        <v>1.64</v>
       </c>
       <c r="G26" t="n">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="H26" t="n">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="I26" t="n">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="J26" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="K26" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="L26" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="M26" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N26" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="O26" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="P26" t="n">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.71</v>
+        <v>1.81</v>
       </c>
       <c r="R26" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="S26" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="T26" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="U26" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="V26" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="W26" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="X26" t="n">
-        <v>22</v>
+        <v>17.5</v>
       </c>
       <c r="Y26" t="n">
-        <v>950</v>
+        <v>40</v>
       </c>
       <c r="Z26" t="n">
         <v>220</v>
       </c>
       <c r="AA26" t="n">
-        <v>200</v>
+        <v>900</v>
       </c>
       <c r="AB26" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AC26" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AD26" t="n">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="AE26" t="n">
         <v>400</v>
@@ -5497,86 +5497,86 @@
         <v>11</v>
       </c>
       <c r="AH26" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI26" t="n">
         <v>390</v>
       </c>
       <c r="AJ26" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AK26" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="AL26" t="n">
         <v>150</v>
       </c>
       <c r="AM26" t="n">
-        <v>390</v>
+        <v>580</v>
       </c>
       <c r="AN26" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="AO26" t="n">
         <v>160</v>
       </c>
       <c r="AP26" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AQ26" t="n">
-        <v>14.5</v>
+        <v>17.5</v>
       </c>
       <c r="AR26" t="n">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="AS26" t="n">
-        <v>6.6</v>
+        <v>8</v>
       </c>
       <c r="AT26" t="n">
         <v>8</v>
       </c>
       <c r="AU26" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AV26" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AW26" t="n">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="AX26" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AY26" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AZ26" t="n">
         <v>16.5</v>
       </c>
       <c r="BA26" t="n">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="BB26" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BC26" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="BD26" t="n">
         <v>19.5</v>
       </c>
       <c r="BE26" t="n">
-        <v>6.4</v>
+        <v>8</v>
       </c>
       <c r="BF26" t="n">
-        <v>6.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG26" t="n">
-        <v>6.4</v>
+        <v>8</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-24 19:53:23</t>
+          <t>2026-03-24 21:58:49</t>
         </is>
       </c>
     </row>
@@ -5607,79 +5607,79 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.62</v>
+        <v>2.52</v>
       </c>
       <c r="G27" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="H27" t="n">
-        <v>2.78</v>
+        <v>2.84</v>
       </c>
       <c r="I27" t="n">
-        <v>2.88</v>
+        <v>3.05</v>
       </c>
       <c r="J27" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="K27" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L27" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="M27" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N27" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="O27" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="P27" t="n">
-        <v>2.16</v>
+        <v>2.08</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="R27" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="S27" t="n">
-        <v>2.96</v>
+        <v>3.15</v>
       </c>
       <c r="T27" t="n">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="U27" t="n">
-        <v>2.32</v>
+        <v>2.26</v>
       </c>
       <c r="V27" t="n">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="W27" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="X27" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="Y27" t="n">
-        <v>18</v>
+        <v>14.5</v>
       </c>
       <c r="Z27" t="n">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="AA27" t="n">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="AB27" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AC27" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD27" t="n">
-        <v>17</v>
+        <v>13.5</v>
       </c>
       <c r="AE27" t="n">
         <v>38</v>
@@ -5691,52 +5691,52 @@
         <v>12</v>
       </c>
       <c r="AH27" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AI27" t="n">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="AJ27" t="n">
         <v>38</v>
       </c>
       <c r="AK27" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AL27" t="n">
-        <v>34</v>
+        <v>95</v>
       </c>
       <c r="AM27" t="n">
-        <v>200</v>
+        <v>580</v>
       </c>
       <c r="AN27" t="n">
         <v>19.5</v>
       </c>
       <c r="AO27" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="AP27" t="n">
         <v>12.5</v>
       </c>
       <c r="AQ27" t="n">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="AR27" t="n">
-        <v>19.5</v>
+        <v>16.5</v>
       </c>
       <c r="AS27" t="n">
-        <v>5.6</v>
+        <v>7.2</v>
       </c>
       <c r="AT27" t="n">
         <v>8</v>
       </c>
       <c r="AU27" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AV27" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AW27" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="AX27" t="n">
         <v>12</v>
@@ -5748,29 +5748,29 @@
         <v>12.5</v>
       </c>
       <c r="BA27" t="n">
-        <v>5.6</v>
+        <v>7.2</v>
       </c>
       <c r="BB27" t="n">
-        <v>5.4</v>
+        <v>18</v>
       </c>
       <c r="BC27" t="n">
         <v>18.5</v>
       </c>
       <c r="BD27" t="n">
-        <v>5.3</v>
+        <v>18</v>
       </c>
       <c r="BE27" t="n">
-        <v>5.8</v>
+        <v>7.4</v>
       </c>
       <c r="BF27" t="n">
         <v>14</v>
       </c>
       <c r="BG27" t="n">
-        <v>21</v>
+        <v>6.6</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-24 19:53:23</t>
+          <t>2026-03-24 21:58:49</t>
         </is>
       </c>
     </row>
@@ -5807,7 +5807,7 @@
         <v>7.6</v>
       </c>
       <c r="H28" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="I28" t="n">
         <v>1.7</v>
@@ -5816,10 +5816,10 @@
         <v>3.7</v>
       </c>
       <c r="K28" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L28" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="M28" t="n">
         <v>1.09</v>
@@ -5834,7 +5834,7 @@
         <v>1.71</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="R28" t="n">
         <v>1.25</v>
@@ -5843,10 +5843,10 @@
         <v>4.2</v>
       </c>
       <c r="T28" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="U28" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="V28" t="n">
         <v>2.42</v>
@@ -5861,16 +5861,16 @@
         <v>6.8</v>
       </c>
       <c r="Z28" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AA28" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AB28" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AC28" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD28" t="n">
         <v>11</v>
@@ -5891,22 +5891,22 @@
         <v>55</v>
       </c>
       <c r="AJ28" t="n">
-        <v>300</v>
+        <v>900</v>
       </c>
       <c r="AK28" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AL28" t="n">
-        <v>160</v>
+        <v>450</v>
       </c>
       <c r="AM28" t="n">
-        <v>230</v>
+        <v>700</v>
       </c>
       <c r="AN28" t="n">
-        <v>280</v>
+        <v>700</v>
       </c>
       <c r="AO28" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AP28" t="n">
         <v>9.800000000000001</v>
@@ -5939,32 +5939,32 @@
         <v>18.5</v>
       </c>
       <c r="AZ28" t="n">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="BA28" t="n">
         <v>40</v>
       </c>
       <c r="BB28" t="n">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="BC28" t="n">
-        <v>9.800000000000001</v>
+        <v>40</v>
       </c>
       <c r="BD28" t="n">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="BE28" t="n">
-        <v>10</v>
+        <v>70</v>
       </c>
       <c r="BF28" t="n">
-        <v>9.800000000000001</v>
+        <v>46</v>
       </c>
       <c r="BG28" t="n">
         <v>11</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-24 19:53:23</t>
+          <t>2026-03-24 21:58:49</t>
         </is>
       </c>
     </row>
@@ -5998,13 +5998,13 @@
         <v>1.61</v>
       </c>
       <c r="G29" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="H29" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="I29" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="J29" t="n">
         <v>3.85</v>
@@ -6019,16 +6019,16 @@
         <v>1.09</v>
       </c>
       <c r="N29" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="O29" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="P29" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="R29" t="n">
         <v>1.27</v>
@@ -6040,13 +6040,13 @@
         <v>2.2</v>
       </c>
       <c r="U29" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="V29" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="W29" t="n">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="X29" t="n">
         <v>11.5</v>
@@ -6061,13 +6061,13 @@
         <v>1000</v>
       </c>
       <c r="AB29" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AC29" t="n">
         <v>10</v>
       </c>
       <c r="AD29" t="n">
-        <v>950</v>
+        <v>28</v>
       </c>
       <c r="AE29" t="n">
         <v>1000</v>
@@ -6106,13 +6106,13 @@
         <v>10.5</v>
       </c>
       <c r="AQ29" t="n">
-        <v>6.6</v>
+        <v>17</v>
       </c>
       <c r="AR29" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS29" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT29" t="n">
         <v>5.9</v>
@@ -6121,10 +6121,10 @@
         <v>8</v>
       </c>
       <c r="AV29" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AW29" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX29" t="n">
         <v>7.6</v>
@@ -6133,10 +6133,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ29" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="BA29" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB29" t="n">
         <v>13.5</v>
@@ -6145,20 +6145,20 @@
         <v>17.5</v>
       </c>
       <c r="BD29" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BE29" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="BF29" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BG29" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-24 19:53:23</t>
+          <t>2026-03-24 21:58:49</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-25.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-25.xlsx
@@ -757,10 +757,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="G2" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="H2" t="n">
         <v>1.94</v>
@@ -775,46 +775,46 @@
         <v>4.3</v>
       </c>
       <c r="L2" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="M2" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N2" t="n">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="O2" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="P2" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="Q2" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="R2" t="n">
         <v>1.27</v>
       </c>
       <c r="S2" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="T2" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="U2" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="V2" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="W2" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="X2" t="n">
         <v>22</v>
       </c>
       <c r="Y2" t="n">
-        <v>27</v>
+        <v>15.5</v>
       </c>
       <c r="Z2" t="n">
         <v>40</v>
@@ -862,10 +862,10 @@
         <v>1000</v>
       </c>
       <c r="AO2" t="n">
-        <v>85</v>
+        <v>55</v>
       </c>
       <c r="AP2" t="n">
-        <v>6.2</v>
+        <v>5.5</v>
       </c>
       <c r="AQ2" t="n">
         <v>4.9</v>
@@ -874,53 +874,53 @@
         <v>5.8</v>
       </c>
       <c r="AS2" t="n">
-        <v>3.15</v>
+        <v>7</v>
       </c>
       <c r="AT2" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AU2" t="n">
         <v>4.9</v>
       </c>
       <c r="AV2" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AW2" t="n">
-        <v>3.1</v>
+        <v>7</v>
       </c>
       <c r="AX2" t="n">
-        <v>2.4</v>
+        <v>2.56</v>
       </c>
       <c r="AY2" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="AZ2" t="n">
-        <v>2.84</v>
+        <v>9.6</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.9</v>
+        <v>4.4</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.95</v>
+        <v>2.28</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.91</v>
+        <v>2.22</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.92</v>
+        <v>2.24</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.96</v>
+        <v>3.55</v>
       </c>
       <c r="BF2" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="BG2" t="n">
         <v>4</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-24 21:58:49</t>
+          <t>2026-03-25 00:04:12</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="G3" t="n">
         <v>7.8</v>
@@ -966,10 +966,10 @@
         <v>3.35</v>
       </c>
       <c r="K3" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L3" t="n">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="M3" t="n">
         <v>1.08</v>
@@ -1092,7 +1092,7 @@
         <v>18.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="BB3" t="n">
         <v>4.9</v>
@@ -1104,7 +1104,7 @@
         <v>4.8</v>
       </c>
       <c r="BE3" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BF3" t="n">
         <v>4.9</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-24 21:58:49</t>
+          <t>2026-03-25 00:04:12</t>
         </is>
       </c>
     </row>
@@ -1151,19 +1151,19 @@
         <v>2.6</v>
       </c>
       <c r="H4" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="I4" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="J4" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="K4" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L4" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="M4" t="n">
         <v>1.07</v>
@@ -1193,7 +1193,7 @@
         <v>2.1</v>
       </c>
       <c r="V4" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="W4" t="n">
         <v>1.62</v>
@@ -1262,7 +1262,7 @@
         <v>15</v>
       </c>
       <c r="AS4" t="n">
-        <v>5.2</v>
+        <v>16</v>
       </c>
       <c r="AT4" t="n">
         <v>8</v>
@@ -1286,7 +1286,7 @@
         <v>12.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>5.1</v>
+        <v>17.5</v>
       </c>
       <c r="BB4" t="n">
         <v>16</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-24 21:58:49</t>
+          <t>2026-03-25 00:04:12</t>
         </is>
       </c>
     </row>
@@ -1342,58 +1342,58 @@
         <v>1.18</v>
       </c>
       <c r="G5" t="n">
-        <v>1.37</v>
+        <v>1.22</v>
       </c>
       <c r="H5" t="n">
-        <v>9.199999999999999</v>
+        <v>20</v>
       </c>
       <c r="I5" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="J5" t="n">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="K5" t="n">
-        <v>21</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="L5" t="n">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="M5" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N5" t="n">
-        <v>4.6</v>
+        <v>5.6</v>
       </c>
       <c r="O5" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="P5" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="S5" t="n">
         <v>2.26</v>
       </c>
-      <c r="Q5" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2.36</v>
-      </c>
       <c r="T5" t="n">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="U5" t="n">
         <v>1.66</v>
       </c>
       <c r="V5" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="W5" t="n">
-        <v>3.7</v>
+        <v>5.5</v>
       </c>
       <c r="X5" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="Y5" t="n">
         <v>1000</v>
@@ -1405,10 +1405,10 @@
         <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AD5" t="n">
         <v>1000</v>
@@ -1417,10 +1417,10 @@
         <v>1000</v>
       </c>
       <c r="AF5" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AG5" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AH5" t="n">
         <v>1000</v>
@@ -1429,10 +1429,10 @@
         <v>1000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AK5" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AL5" t="n">
         <v>1000</v>
@@ -1441,68 +1441,68 @@
         <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>29</v>
+        <v>3.75</v>
       </c>
       <c r="AO5" t="n">
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.09</v>
+        <v>20</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.09</v>
+        <v>6.6</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.09</v>
+        <v>7.2</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.09</v>
+        <v>7.4</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.09</v>
+        <v>8.4</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.09</v>
+        <v>14</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.09</v>
+        <v>6.8</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.09</v>
+        <v>7.2</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.09</v>
+        <v>6.8</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.09</v>
+        <v>10</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.09</v>
+        <v>6.4</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.09</v>
+        <v>7.2</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.09</v>
+        <v>7</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.09</v>
+        <v>11.5</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.09</v>
+        <v>6.6</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.09</v>
+        <v>7.2</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="BG5" t="n">
-        <v>4.2</v>
+        <v>7.4</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-24 21:58:49</t>
+          <t>2026-03-25 00:04:12</t>
         </is>
       </c>
     </row>
@@ -1536,13 +1536,13 @@
         <v>1.46</v>
       </c>
       <c r="G6" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="H6" t="n">
         <v>6.8</v>
       </c>
       <c r="I6" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="J6" t="n">
         <v>4.2</v>
@@ -1557,46 +1557,46 @@
         <v>1.05</v>
       </c>
       <c r="N6" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="O6" t="n">
         <v>1.25</v>
       </c>
       <c r="P6" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="R6" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="S6" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="T6" t="n">
         <v>1.87</v>
       </c>
       <c r="U6" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="V6" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="W6" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="X6" t="n">
         <v>19.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="Z6" t="n">
         <v>270</v>
       </c>
       <c r="AA6" t="n">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="AB6" t="n">
         <v>9.199999999999999</v>
@@ -1605,28 +1605,28 @@
         <v>11.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="AE6" t="n">
         <v>480</v>
       </c>
       <c r="AF6" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG6" t="n">
         <v>11</v>
       </c>
       <c r="AH6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI6" t="n">
         <v>390</v>
       </c>
       <c r="AJ6" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AK6" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AL6" t="n">
         <v>85</v>
@@ -1635,34 +1635,34 @@
         <v>390</v>
       </c>
       <c r="AN6" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AO6" t="n">
         <v>200</v>
       </c>
       <c r="AP6" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AQ6" t="n">
         <v>20</v>
       </c>
       <c r="AR6" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="AS6" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="AT6" t="n">
         <v>7.2</v>
       </c>
       <c r="AU6" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV6" t="n">
         <v>14</v>
       </c>
       <c r="AW6" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="AX6" t="n">
         <v>7.6</v>
@@ -1671,10 +1671,10 @@
         <v>8.4</v>
       </c>
       <c r="AZ6" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="BB6" t="n">
         <v>11</v>
@@ -1686,17 +1686,17 @@
         <v>19.5</v>
       </c>
       <c r="BE6" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="BF6" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BG6" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-24 21:58:49</t>
+          <t>2026-03-25 00:04:12</t>
         </is>
       </c>
     </row>
@@ -1727,170 +1727,170 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.98</v>
+        <v>2.68</v>
       </c>
       <c r="G7" t="n">
-        <v>10.5</v>
+        <v>3.35</v>
       </c>
       <c r="H7" t="n">
-        <v>1.99</v>
+        <v>2.68</v>
       </c>
       <c r="I7" t="n">
-        <v>44</v>
+        <v>3.35</v>
       </c>
       <c r="J7" t="n">
-        <v>2.64</v>
+        <v>2.84</v>
       </c>
       <c r="K7" t="n">
-        <v>7.6</v>
+        <v>3.4</v>
       </c>
       <c r="L7" t="n">
-        <v>1.01</v>
+        <v>1.49</v>
       </c>
       <c r="M7" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="N7" t="n">
-        <v>1.24</v>
+        <v>2.24</v>
       </c>
       <c r="O7" t="n">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="P7" t="n">
-        <v>1.24</v>
+        <v>1.46</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.01</v>
+        <v>2.14</v>
       </c>
       <c r="R7" t="n">
         <v>1.18</v>
       </c>
       <c r="S7" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="T7" t="n">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="U7" t="n">
-        <v>1.01</v>
+        <v>1.7</v>
       </c>
       <c r="V7" t="n">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="W7" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="X7" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="Y7" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="Z7" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AA7" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AB7" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AC7" t="n">
-        <v>500</v>
+        <v>7.6</v>
       </c>
       <c r="AD7" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AE7" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF7" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AG7" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AI7" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AK7" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AL7" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AM7" t="n">
         <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AO7" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AP7" t="n">
         <v>4.2</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.23</v>
+        <v>3.9</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.24</v>
+        <v>5</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.26</v>
+        <v>6</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.23</v>
+        <v>3.9</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.22</v>
+        <v>3.65</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.23</v>
+        <v>4.6</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.25</v>
+        <v>5.9</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.26</v>
+        <v>5</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.23</v>
+        <v>4.6</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.26</v>
+        <v>5.2</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.25</v>
+        <v>6.2</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.25</v>
+        <v>6</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.25</v>
+        <v>5.9</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.25</v>
+        <v>6.2</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.26</v>
+        <v>6.4</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.55</v>
+        <v>6</v>
       </c>
       <c r="BG7" t="n">
-        <v>1.55</v>
+        <v>6</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-24 21:58:49</t>
+          <t>2026-03-25 00:04:12</t>
         </is>
       </c>
     </row>
@@ -1921,64 +1921,64 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.1</v>
+        <v>1.53</v>
       </c>
       <c r="G8" t="n">
-        <v>500</v>
+        <v>1.68</v>
       </c>
       <c r="H8" t="n">
-        <v>1.05</v>
+        <v>6</v>
       </c>
       <c r="I8" t="n">
-        <v>500</v>
+        <v>8.6</v>
       </c>
       <c r="J8" t="n">
-        <v>1.06</v>
+        <v>3.45</v>
       </c>
       <c r="K8" t="n">
-        <v>950</v>
+        <v>4.5</v>
       </c>
       <c r="L8" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="M8" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N8" t="n">
-        <v>1.24</v>
+        <v>2.84</v>
       </c>
       <c r="O8" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="P8" t="n">
-        <v>1.24</v>
+        <v>1.73</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.02</v>
+        <v>1.94</v>
       </c>
       <c r="R8" t="n">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="S8" t="n">
-        <v>1.37</v>
+        <v>3.4</v>
       </c>
       <c r="T8" t="n">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="U8" t="n">
-        <v>1.01</v>
+        <v>1.71</v>
       </c>
       <c r="V8" t="n">
-        <v>1.02</v>
+        <v>1.13</v>
       </c>
       <c r="W8" t="n">
-        <v>1.02</v>
+        <v>2.46</v>
       </c>
       <c r="X8" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="Y8" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Z8" t="n">
         <v>1000</v>
@@ -1987,104 +1987,104 @@
         <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="AC8" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD8" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AE8" t="n">
         <v>1000</v>
       </c>
       <c r="AF8" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AG8" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AH8" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AI8" t="n">
         <v>1000</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AK8" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AL8" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM8" t="n">
         <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AO8" t="n">
         <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AS8" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BD8" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BG8" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-24 21:58:49</t>
+          <t>2026-03-25 00:04:12</t>
         </is>
       </c>
     </row>
@@ -2133,7 +2133,7 @@
         <v>3.65</v>
       </c>
       <c r="L9" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="M9" t="n">
         <v>1.1</v>
@@ -2229,10 +2229,10 @@
         <v>9.4</v>
       </c>
       <c r="AR9" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AS9" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AT9" t="n">
         <v>6.6</v>
@@ -2244,7 +2244,7 @@
         <v>12</v>
       </c>
       <c r="AW9" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="AX9" t="n">
         <v>10.5</v>
@@ -2253,32 +2253,32 @@
         <v>8.4</v>
       </c>
       <c r="AZ9" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BA9" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BB9" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BC9" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BD9" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BE9" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BF9" t="n">
         <v>5.1</v>
       </c>
       <c r="BG9" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-24 21:58:49</t>
+          <t>2026-03-25 00:04:12</t>
         </is>
       </c>
     </row>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="G10" t="n">
         <v>3.15</v>
@@ -2324,7 +2324,7 @@
         <v>2.62</v>
       </c>
       <c r="K10" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="L10" t="n">
         <v>1.67</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-24 21:58:49</t>
+          <t>2026-03-25 00:04:12</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
         <v>3.15</v>
       </c>
       <c r="L11" t="n">
-        <v>1.52</v>
+        <v>1.59</v>
       </c>
       <c r="M11" t="n">
         <v>1.13</v>
@@ -2557,7 +2557,7 @@
         <v>1.56</v>
       </c>
       <c r="X11" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y11" t="n">
         <v>9.199999999999999</v>
@@ -2569,13 +2569,13 @@
         <v>1000</v>
       </c>
       <c r="AB11" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AC11" t="n">
         <v>7.2</v>
       </c>
       <c r="AD11" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="AE11" t="n">
         <v>290</v>
@@ -2620,7 +2620,7 @@
         <v>9</v>
       </c>
       <c r="AS11" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AT11" t="n">
         <v>6.8</v>
@@ -2629,10 +2629,10 @@
         <v>6.2</v>
       </c>
       <c r="AV11" t="n">
-        <v>13</v>
+        <v>8.4</v>
       </c>
       <c r="AW11" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AX11" t="n">
         <v>7.6</v>
@@ -2641,32 +2641,32 @@
         <v>11.5</v>
       </c>
       <c r="AZ11" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BA11" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BB11" t="n">
+        <v>9</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BD11" t="n">
         <v>9.6</v>
       </c>
-      <c r="BC11" t="n">
-        <v>10</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>9.800000000000001</v>
-      </c>
       <c r="BE11" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BF11" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BG11" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-24 21:58:49</t>
+          <t>2026-03-25 00:04:12</t>
         </is>
       </c>
     </row>
@@ -2700,7 +2700,7 @@
         <v>1.9</v>
       </c>
       <c r="G12" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="H12" t="n">
         <v>4.8</v>
@@ -2748,7 +2748,7 @@
         <v>1.21</v>
       </c>
       <c r="W12" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="X12" t="n">
         <v>16</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-24 21:58:49</t>
+          <t>2026-03-25 00:04:12</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2894,7 @@
         <v>3.15</v>
       </c>
       <c r="G13" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="H13" t="n">
         <v>2.26</v>
@@ -2906,7 +2906,7 @@
         <v>3.55</v>
       </c>
       <c r="K13" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L13" t="n">
         <v>1.28</v>
@@ -2984,16 +2984,16 @@
         <v>900</v>
       </c>
       <c r="AK13" t="n">
-        <v>80</v>
+        <v>500</v>
       </c>
       <c r="AL13" t="n">
-        <v>95</v>
+        <v>500</v>
       </c>
       <c r="AM13" t="n">
         <v>580</v>
       </c>
       <c r="AN13" t="n">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="AO13" t="n">
         <v>55</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-24 21:58:49</t>
+          <t>2026-03-25 00:04:12</t>
         </is>
       </c>
     </row>
@@ -3091,19 +3091,19 @@
         <v>2.84</v>
       </c>
       <c r="H14" t="n">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="I14" t="n">
         <v>2.8</v>
       </c>
       <c r="J14" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="K14" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L14" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="M14" t="n">
         <v>1.06</v>
@@ -3136,16 +3136,16 @@
         <v>1.55</v>
       </c>
       <c r="W14" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="X14" t="n">
-        <v>15</v>
+        <v>970</v>
       </c>
       <c r="Y14" t="n">
         <v>13</v>
       </c>
       <c r="Z14" t="n">
-        <v>970</v>
+        <v>38</v>
       </c>
       <c r="AA14" t="n">
         <v>130</v>
@@ -3181,13 +3181,13 @@
         <v>30</v>
       </c>
       <c r="AL14" t="n">
-        <v>85</v>
+        <v>150</v>
       </c>
       <c r="AM14" t="n">
         <v>200</v>
       </c>
       <c r="AN14" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AO14" t="n">
         <v>23</v>
@@ -3202,7 +3202,7 @@
         <v>9</v>
       </c>
       <c r="AS14" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AT14" t="n">
         <v>11.5</v>
@@ -3220,16 +3220,16 @@
         <v>17</v>
       </c>
       <c r="AY14" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AZ14" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="BA14" t="n">
         <v>10.5</v>
       </c>
       <c r="BB14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BC14" t="n">
         <v>14.5</v>
@@ -3238,17 +3238,17 @@
         <v>20</v>
       </c>
       <c r="BE14" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF14" t="n">
-        <v>8.800000000000001</v>
+        <v>6.8</v>
       </c>
       <c r="BG14" t="n">
         <v>17.5</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-24 21:58:49</t>
+          <t>2026-03-25 00:04:12</t>
         </is>
       </c>
     </row>
@@ -3288,7 +3288,7 @@
         <v>2.08</v>
       </c>
       <c r="I15" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="J15" t="n">
         <v>3.6</v>
@@ -3309,7 +3309,7 @@
         <v>1.28</v>
       </c>
       <c r="P15" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="Q15" t="n">
         <v>1.82</v>
@@ -3324,10 +3324,10 @@
         <v>1.7</v>
       </c>
       <c r="U15" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="V15" t="n">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="W15" t="n">
         <v>1.33</v>
@@ -3354,7 +3354,7 @@
         <v>11</v>
       </c>
       <c r="AE15" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AF15" t="n">
         <v>28</v>
@@ -3375,10 +3375,10 @@
         <v>100</v>
       </c>
       <c r="AL15" t="n">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="AM15" t="n">
-        <v>90</v>
+        <v>580</v>
       </c>
       <c r="AN15" t="n">
         <v>40</v>
@@ -3399,7 +3399,7 @@
         <v>19.5</v>
       </c>
       <c r="AT15" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AU15" t="n">
         <v>7.4</v>
@@ -3426,7 +3426,7 @@
         <v>50</v>
       </c>
       <c r="BC15" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BD15" t="n">
         <v>36</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-24 21:58:49</t>
+          <t>2026-03-25 00:04:12</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
         <v>3.7</v>
       </c>
       <c r="K16" t="n">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="L16" t="n">
         <v>1.27</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-24 21:58:49</t>
+          <t>2026-03-25 00:04:12</t>
         </is>
       </c>
     </row>
@@ -3667,22 +3667,22 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="G17" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="H17" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="I17" t="n">
         <v>6</v>
       </c>
       <c r="J17" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K17" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="L17" t="n">
         <v>1.32</v>
@@ -3697,7 +3697,7 @@
         <v>1.26</v>
       </c>
       <c r="P17" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="Q17" t="n">
         <v>1.78</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-24 21:58:49</t>
+          <t>2026-03-25 00:04:12</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="G18" t="n">
         <v>2.02</v>
@@ -3876,10 +3876,10 @@
         <v>3.6</v>
       </c>
       <c r="K18" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="L18" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="M18" t="n">
         <v>1.07</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-24 21:58:49</t>
+          <t>2026-03-25 00:04:12</t>
         </is>
       </c>
     </row>
@@ -4151,7 +4151,7 @@
         <v>70</v>
       </c>
       <c r="AL19" t="n">
-        <v>370</v>
+        <v>500</v>
       </c>
       <c r="AM19" t="n">
         <v>1000</v>
@@ -4166,7 +4166,7 @@
         <v>5.6</v>
       </c>
       <c r="AQ19" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AR19" t="n">
         <v>4.2</v>
@@ -4190,7 +4190,7 @@
         <v>6.4</v>
       </c>
       <c r="AY19" t="n">
-        <v>5</v>
+        <v>3.9</v>
       </c>
       <c r="AZ19" t="n">
         <v>7.2</v>
@@ -4214,11 +4214,11 @@
         <v>7</v>
       </c>
       <c r="BG19" t="n">
-        <v>4.2</v>
+        <v>9</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-24 21:58:49</t>
+          <t>2026-03-25 00:04:12</t>
         </is>
       </c>
     </row>
@@ -4252,7 +4252,7 @@
         <v>3.15</v>
       </c>
       <c r="G20" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="H20" t="n">
         <v>2.7</v>
@@ -4261,7 +4261,7 @@
         <v>2.86</v>
       </c>
       <c r="J20" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="K20" t="n">
         <v>3.15</v>
@@ -4273,10 +4273,10 @@
         <v>1.13</v>
       </c>
       <c r="N20" t="n">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="O20" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="P20" t="n">
         <v>1.53</v>
@@ -4294,25 +4294,25 @@
         <v>2.14</v>
       </c>
       <c r="U20" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="V20" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="W20" t="n">
         <v>1.43</v>
       </c>
       <c r="X20" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="Y20" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z20" t="n">
         <v>18</v>
       </c>
       <c r="AA20" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="AB20" t="n">
         <v>9.199999999999999</v>
@@ -4327,7 +4327,7 @@
         <v>90</v>
       </c>
       <c r="AF20" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AG20" t="n">
         <v>19</v>
@@ -4336,31 +4336,31 @@
         <v>36</v>
       </c>
       <c r="AI20" t="n">
-        <v>170</v>
+        <v>500</v>
       </c>
       <c r="AJ20" t="n">
         <v>900</v>
       </c>
       <c r="AK20" t="n">
-        <v>110</v>
+        <v>500</v>
       </c>
       <c r="AL20" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="AM20" t="n">
-        <v>210</v>
+        <v>500</v>
       </c>
       <c r="AN20" t="n">
-        <v>65</v>
+        <v>500</v>
       </c>
       <c r="AO20" t="n">
-        <v>55</v>
+        <v>500</v>
       </c>
       <c r="AP20" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AQ20" t="n">
         <v>7.4</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>7.2</v>
       </c>
       <c r="AR20" t="n">
         <v>11.5</v>
@@ -4369,13 +4369,13 @@
         <v>24</v>
       </c>
       <c r="AT20" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AU20" t="n">
         <v>6.2</v>
       </c>
       <c r="AV20" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AW20" t="n">
         <v>23</v>
@@ -4384,7 +4384,7 @@
         <v>14</v>
       </c>
       <c r="AY20" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AZ20" t="n">
         <v>20</v>
@@ -4393,13 +4393,13 @@
         <v>34</v>
       </c>
       <c r="BB20" t="n">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="BC20" t="n">
         <v>27</v>
       </c>
       <c r="BD20" t="n">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="BE20" t="n">
         <v>70</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-24 21:58:49</t>
+          <t>2026-03-25 00:04:12</t>
         </is>
       </c>
     </row>
@@ -4443,16 +4443,16 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="G21" t="n">
         <v>2.74</v>
       </c>
       <c r="H21" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="I21" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="J21" t="n">
         <v>2.72</v>
@@ -4461,28 +4461,28 @@
         <v>2.84</v>
       </c>
       <c r="L21" t="n">
-        <v>1.01</v>
+        <v>1.78</v>
       </c>
       <c r="M21" t="n">
         <v>1.2</v>
       </c>
       <c r="N21" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="O21" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="P21" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="R21" t="n">
         <v>1.08</v>
       </c>
       <c r="S21" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="T21" t="n">
         <v>2.78</v>
@@ -4491,16 +4491,16 @@
         <v>1.46</v>
       </c>
       <c r="V21" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W21" t="n">
         <v>1.57</v>
       </c>
       <c r="X21" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="Y21" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="Z21" t="n">
         <v>26</v>
@@ -4509,13 +4509,13 @@
         <v>110</v>
       </c>
       <c r="AB21" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AC21" t="n">
         <v>7.6</v>
       </c>
       <c r="AD21" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AE21" t="n">
         <v>110</v>
@@ -4533,7 +4533,7 @@
         <v>200</v>
       </c>
       <c r="AJ21" t="n">
-        <v>46</v>
+        <v>100</v>
       </c>
       <c r="AK21" t="n">
         <v>65</v>
@@ -4545,52 +4545,52 @@
         <v>540</v>
       </c>
       <c r="AN21" t="n">
-        <v>210</v>
+        <v>90</v>
       </c>
       <c r="AO21" t="n">
         <v>210</v>
       </c>
       <c r="AP21" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AQ21" t="n">
         <v>7.2</v>
       </c>
       <c r="AR21" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AS21" t="n">
         <v>38</v>
       </c>
       <c r="AT21" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AU21" t="n">
         <v>6.6</v>
       </c>
       <c r="AV21" t="n">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="AW21" t="n">
         <v>38</v>
       </c>
       <c r="AX21" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AY21" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AZ21" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BA21" t="n">
         <v>46</v>
       </c>
       <c r="BB21" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BC21" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BD21" t="n">
         <v>44</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-24 21:58:49</t>
+          <t>2026-03-25 00:04:12</t>
         </is>
       </c>
     </row>
@@ -4754,7 +4754,7 @@
         <v>13</v>
       </c>
       <c r="AS22" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AT22" t="n">
         <v>6.6</v>
@@ -4766,7 +4766,7 @@
         <v>13.5</v>
       </c>
       <c r="AW22" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="AX22" t="n">
         <v>8.6</v>
@@ -4787,7 +4787,7 @@
         <v>20</v>
       </c>
       <c r="BD22" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="BE22" t="n">
         <v>5.5</v>
@@ -4796,11 +4796,11 @@
         <v>13.5</v>
       </c>
       <c r="BG22" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-24 21:58:49</t>
+          <t>2026-03-25 00:04:12</t>
         </is>
       </c>
     </row>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-24 21:58:49</t>
+          <t>2026-03-25 00:04:12</t>
         </is>
       </c>
     </row>
@@ -5034,7 +5034,7 @@
         <v>7.2</v>
       </c>
       <c r="I24" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J24" t="n">
         <v>3.65</v>
@@ -5073,7 +5073,7 @@
         <v>1.67</v>
       </c>
       <c r="V24" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="W24" t="n">
         <v>2.5</v>
@@ -5133,7 +5133,7 @@
         <v>1000</v>
       </c>
       <c r="AP24" t="n">
-        <v>4</v>
+        <v>5.4</v>
       </c>
       <c r="AQ24" t="n">
         <v>4.2</v>
@@ -5145,7 +5145,7 @@
         <v>4.2</v>
       </c>
       <c r="AT24" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="AU24" t="n">
         <v>4.8</v>
@@ -5163,7 +5163,7 @@
         <v>8</v>
       </c>
       <c r="AZ24" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="BA24" t="n">
         <v>4.2</v>
@@ -5172,10 +5172,10 @@
         <v>3.85</v>
       </c>
       <c r="BC24" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="BD24" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="BE24" t="n">
         <v>2.2</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-24 21:58:49</t>
+          <t>2026-03-25 00:04:12</t>
         </is>
       </c>
     </row>
@@ -5222,7 +5222,7 @@
         <v>1.4</v>
       </c>
       <c r="G25" t="n">
-        <v>2.44</v>
+        <v>4.4</v>
       </c>
       <c r="H25" t="n">
         <v>3.35</v>
@@ -5234,7 +5234,7 @@
         <v>3.4</v>
       </c>
       <c r="K25" t="n">
-        <v>950</v>
+        <v>11.5</v>
       </c>
       <c r="L25" t="n">
         <v>1.01</v>
@@ -5270,7 +5270,7 @@
         <v>1.13</v>
       </c>
       <c r="W25" t="n">
-        <v>1.69</v>
+        <v>1.29</v>
       </c>
       <c r="X25" t="n">
         <v>1000</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-24 21:58:49</t>
+          <t>2026-03-25 00:04:12</t>
         </is>
       </c>
     </row>
@@ -5446,7 +5446,7 @@
         <v>2.08</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="R26" t="n">
         <v>1.4</v>
@@ -5500,7 +5500,7 @@
         <v>21</v>
       </c>
       <c r="AI26" t="n">
-        <v>390</v>
+        <v>700</v>
       </c>
       <c r="AJ26" t="n">
         <v>16.5</v>
@@ -5518,7 +5518,7 @@
         <v>10.5</v>
       </c>
       <c r="AO26" t="n">
-        <v>160</v>
+        <v>700</v>
       </c>
       <c r="AP26" t="n">
         <v>14.5</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-24 21:58:49</t>
+          <t>2026-03-25 00:04:12</t>
         </is>
       </c>
     </row>
@@ -5607,7 +5607,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="G27" t="n">
         <v>2.7</v>
@@ -5616,13 +5616,13 @@
         <v>2.84</v>
       </c>
       <c r="I27" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="J27" t="n">
         <v>3.6</v>
       </c>
       <c r="K27" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="L27" t="n">
         <v>1.29</v>
@@ -5655,7 +5655,7 @@
         <v>2.26</v>
       </c>
       <c r="V27" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="W27" t="n">
         <v>1.58</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-24 21:58:49</t>
+          <t>2026-03-25 00:04:12</t>
         </is>
       </c>
     </row>
@@ -5801,22 +5801,22 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="G28" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="H28" t="n">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="I28" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="J28" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="K28" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="L28" t="n">
         <v>1.47</v>
@@ -5834,22 +5834,22 @@
         <v>1.71</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="R28" t="n">
         <v>1.25</v>
       </c>
       <c r="S28" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="T28" t="n">
         <v>2.18</v>
       </c>
       <c r="U28" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="V28" t="n">
-        <v>2.42</v>
+        <v>2.36</v>
       </c>
       <c r="W28" t="n">
         <v>1.16</v>
@@ -5864,10 +5864,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AA28" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AB28" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AC28" t="n">
         <v>8.800000000000001</v>
@@ -5876,13 +5876,13 @@
         <v>11</v>
       </c>
       <c r="AE28" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AF28" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AG28" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AH28" t="n">
         <v>28</v>
@@ -5906,13 +5906,13 @@
         <v>700</v>
       </c>
       <c r="AO28" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AP28" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AQ28" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AR28" t="n">
         <v>7.6</v>
@@ -5921,28 +5921,28 @@
         <v>14</v>
       </c>
       <c r="AT28" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AU28" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="AV28" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW28" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AX28" t="n">
         <v>26</v>
       </c>
       <c r="AY28" t="n">
-        <v>18.5</v>
+        <v>22</v>
       </c>
       <c r="AZ28" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BA28" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BB28" t="n">
         <v>46</v>
@@ -5960,11 +5960,11 @@
         <v>46</v>
       </c>
       <c r="BG28" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-24 21:58:49</t>
+          <t>2026-03-25 00:04:12</t>
         </is>
       </c>
     </row>
@@ -6043,7 +6043,7 @@
         <v>1.74</v>
       </c>
       <c r="V29" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="W29" t="n">
         <v>2.54</v>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-24 21:58:49</t>
+          <t>2026-03-25 00:04:12</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-25.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-25.xlsx
@@ -757,64 +757,64 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="G2" t="n">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="H2" t="n">
         <v>1.94</v>
       </c>
       <c r="I2" t="n">
-        <v>2.16</v>
+        <v>2.08</v>
       </c>
       <c r="J2" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="K2" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L2" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="M2" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N2" t="n">
-        <v>2.8</v>
+        <v>3.15</v>
       </c>
       <c r="O2" t="n">
         <v>1.39</v>
       </c>
       <c r="P2" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.04</v>
+        <v>2.16</v>
       </c>
       <c r="R2" t="n">
         <v>1.27</v>
       </c>
       <c r="S2" t="n">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="T2" t="n">
         <v>1.92</v>
       </c>
       <c r="U2" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="V2" t="n">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="W2" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="X2" t="n">
         <v>22</v>
       </c>
       <c r="Y2" t="n">
-        <v>15.5</v>
+        <v>27</v>
       </c>
       <c r="Z2" t="n">
         <v>40</v>
@@ -826,10 +826,10 @@
         <v>1000</v>
       </c>
       <c r="AC2" t="n">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="AD2" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AE2" t="n">
         <v>1000</v>
@@ -862,10 +862,10 @@
         <v>1000</v>
       </c>
       <c r="AO2" t="n">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="AP2" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="AQ2" t="n">
         <v>4.9</v>
@@ -874,43 +874,43 @@
         <v>5.8</v>
       </c>
       <c r="AS2" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AT2" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="AU2" t="n">
         <v>4.9</v>
       </c>
       <c r="AV2" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AW2" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX2" t="n">
         <v>7</v>
       </c>
-      <c r="AX2" t="n">
-        <v>2.56</v>
-      </c>
       <c r="AY2" t="n">
-        <v>3.8</v>
+        <v>7.8</v>
       </c>
       <c r="AZ2" t="n">
-        <v>9.6</v>
+        <v>6.8</v>
       </c>
       <c r="BA2" t="n">
-        <v>4.4</v>
+        <v>2.82</v>
       </c>
       <c r="BB2" t="n">
-        <v>2.28</v>
+        <v>2.6</v>
       </c>
       <c r="BC2" t="n">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="BD2" t="n">
-        <v>2.24</v>
+        <v>2.16</v>
       </c>
       <c r="BE2" t="n">
-        <v>3.55</v>
+        <v>2.64</v>
       </c>
       <c r="BF2" t="n">
         <v>2.5</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-25 00:04:12</t>
+          <t>2026-03-25 02:09:31</t>
         </is>
       </c>
     </row>
@@ -954,43 +954,43 @@
         <v>5.7</v>
       </c>
       <c r="G3" t="n">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="H3" t="n">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="I3" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="J3" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K3" t="n">
         <v>3.9</v>
       </c>
       <c r="L3" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="M3" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N3" t="n">
-        <v>2.82</v>
+        <v>2.98</v>
       </c>
       <c r="O3" t="n">
         <v>1.45</v>
       </c>
       <c r="P3" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="R3" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="T3" t="n">
         <v>2.12</v>
@@ -1002,7 +1002,7 @@
         <v>2.16</v>
       </c>
       <c r="W3" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="X3" t="n">
         <v>11</v>
@@ -1029,7 +1029,7 @@
         <v>28</v>
       </c>
       <c r="AF3" t="n">
-        <v>120</v>
+        <v>75</v>
       </c>
       <c r="AG3" t="n">
         <v>30</v>
@@ -1038,7 +1038,7 @@
         <v>32</v>
       </c>
       <c r="AI3" t="n">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="AJ3" t="n">
         <v>900</v>
@@ -1047,74 +1047,74 @@
         <v>480</v>
       </c>
       <c r="AL3" t="n">
-        <v>450</v>
+        <v>700</v>
       </c>
       <c r="AM3" t="n">
         <v>580</v>
       </c>
       <c r="AN3" t="n">
-        <v>230</v>
+        <v>700</v>
       </c>
       <c r="AO3" t="n">
         <v>20</v>
       </c>
       <c r="AP3" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ3" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>16</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>19</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>19</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>21</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>21</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>28</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>28</v>
+      </c>
+      <c r="BF3" t="n">
         <v>5.6</v>
       </c>
-      <c r="AR3" t="n">
-        <v>7</v>
-      </c>
-      <c r="AS3" t="n">
+      <c r="BG3" t="n">
         <v>14</v>
       </c>
-      <c r="AT3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>18</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>5</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>12</v>
-      </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-25 00:04:12</t>
+          <t>2026-03-25 02:09:31</t>
         </is>
       </c>
     </row>
@@ -1148,7 +1148,7 @@
         <v>2.36</v>
       </c>
       <c r="G4" t="n">
-        <v>2.6</v>
+        <v>2.52</v>
       </c>
       <c r="H4" t="n">
         <v>3.1</v>
@@ -1157,37 +1157,37 @@
         <v>3.4</v>
       </c>
       <c r="J4" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K4" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="L4" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="M4" t="n">
         <v>1.07</v>
       </c>
       <c r="N4" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="O4" t="n">
         <v>1.33</v>
       </c>
       <c r="P4" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="R4" t="n">
         <v>1.33</v>
       </c>
       <c r="S4" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="T4" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="U4" t="n">
         <v>2.1</v>
@@ -1196,13 +1196,13 @@
         <v>1.41</v>
       </c>
       <c r="W4" t="n">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="X4" t="n">
         <v>16</v>
       </c>
       <c r="Y4" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="Z4" t="n">
         <v>23</v>
@@ -1211,7 +1211,7 @@
         <v>60</v>
       </c>
       <c r="AB4" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AC4" t="n">
         <v>8.199999999999999</v>
@@ -1223,7 +1223,7 @@
         <v>40</v>
       </c>
       <c r="AF4" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AG4" t="n">
         <v>14</v>
@@ -1235,80 +1235,80 @@
         <v>55</v>
       </c>
       <c r="AJ4" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="AK4" t="n">
         <v>34</v>
       </c>
       <c r="AL4" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AM4" t="n">
         <v>440</v>
       </c>
       <c r="AN4" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="AO4" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AP4" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AQ4" t="n">
         <v>10.5</v>
       </c>
-      <c r="AQ4" t="n">
-        <v>9</v>
-      </c>
       <c r="AR4" t="n">
-        <v>15</v>
+        <v>19.5</v>
       </c>
       <c r="AS4" t="n">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="AT4" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="AU4" t="n">
         <v>6.8</v>
       </c>
       <c r="AV4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AW4" t="n">
-        <v>14.5</v>
+        <v>20</v>
       </c>
       <c r="AX4" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AY4" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ4" t="n">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="BA4" t="n">
-        <v>17.5</v>
+        <v>23</v>
       </c>
       <c r="BB4" t="n">
         <v>16</v>
       </c>
       <c r="BC4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BD4" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="BE4" t="n">
-        <v>5.4</v>
+        <v>28</v>
       </c>
       <c r="BF4" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BG4" t="n">
-        <v>6.2</v>
+        <v>23</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-25 00:04:12</t>
+          <t>2026-03-25 02:09:31</t>
         </is>
       </c>
     </row>
@@ -1339,49 +1339,49 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="G5" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="H5" t="n">
         <v>20</v>
       </c>
       <c r="I5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J5" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="K5" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="L5" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="M5" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N5" t="n">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="O5" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="P5" t="n">
-        <v>2.66</v>
+        <v>2.84</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="R5" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="S5" t="n">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="T5" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="U5" t="n">
         <v>1.66</v>
@@ -1390,10 +1390,10 @@
         <v>1.04</v>
       </c>
       <c r="W5" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="X5" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="Y5" t="n">
         <v>1000</v>
@@ -1405,10 +1405,10 @@
         <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AD5" t="n">
         <v>1000</v>
@@ -1417,22 +1417,22 @@
         <v>1000</v>
       </c>
       <c r="AF5" t="n">
-        <v>8.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG5" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AI5" t="n">
         <v>1000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AK5" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AL5" t="n">
         <v>1000</v>
@@ -1441,68 +1441,68 @@
         <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>3.75</v>
+        <v>3.45</v>
       </c>
       <c r="AO5" t="n">
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="AQ5" t="n">
         <v>6.6</v>
       </c>
       <c r="AR5" t="n">
+        <v>7</v>
+      </c>
+      <c r="AS5" t="n">
         <v>7.2</v>
       </c>
-      <c r="AS5" t="n">
-        <v>7.4</v>
-      </c>
       <c r="AT5" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU5" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AV5" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AW5" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX5" t="n">
         <v>7.2</v>
       </c>
-      <c r="AX5" t="n">
-        <v>6.8</v>
-      </c>
       <c r="AY5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AZ5" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BA5" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB5" t="n">
         <v>7.2</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>7</v>
       </c>
       <c r="BC5" t="n">
         <v>11.5</v>
       </c>
       <c r="BD5" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BE5" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BF5" t="n">
-        <v>3.2</v>
+        <v>2.96</v>
       </c>
       <c r="BG5" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-25 00:04:12</t>
+          <t>2026-03-25 02:09:31</t>
         </is>
       </c>
     </row>
@@ -1533,16 +1533,16 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="G6" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="H6" t="n">
         <v>6.8</v>
       </c>
       <c r="I6" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J6" t="n">
         <v>4.2</v>
@@ -1551,43 +1551,43 @@
         <v>5.3</v>
       </c>
       <c r="L6" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="M6" t="n">
         <v>1.05</v>
       </c>
       <c r="N6" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="O6" t="n">
         <v>1.25</v>
       </c>
       <c r="P6" t="n">
-        <v>2.08</v>
+        <v>2.18</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="R6" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="S6" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="T6" t="n">
         <v>1.87</v>
       </c>
       <c r="U6" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="V6" t="n">
         <v>1.13</v>
       </c>
       <c r="W6" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="X6" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="Y6" t="n">
         <v>27</v>
@@ -1596,22 +1596,22 @@
         <v>270</v>
       </c>
       <c r="AA6" t="n">
-        <v>280</v>
+        <v>260</v>
       </c>
       <c r="AB6" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AC6" t="n">
         <v>11.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="AE6" t="n">
         <v>480</v>
       </c>
       <c r="AF6" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AG6" t="n">
         <v>11</v>
@@ -1641,40 +1641,40 @@
         <v>200</v>
       </c>
       <c r="AP6" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AQ6" t="n">
+        <v>21</v>
+      </c>
+      <c r="AR6" t="n">
         <v>20</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>7.4</v>
       </c>
       <c r="AS6" t="n">
         <v>7.8</v>
       </c>
       <c r="AT6" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AU6" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AV6" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX6" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AY6" t="n">
         <v>8.4</v>
       </c>
       <c r="AZ6" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BA6" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="BB6" t="n">
         <v>11</v>
@@ -1683,20 +1683,20 @@
         <v>13</v>
       </c>
       <c r="BD6" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="BE6" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF6" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BG6" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-25 00:04:12</t>
+          <t>2026-03-25 02:09:31</t>
         </is>
       </c>
     </row>
@@ -1727,170 +1727,170 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="G7" t="n">
-        <v>3.35</v>
+        <v>2.98</v>
       </c>
       <c r="H7" t="n">
-        <v>2.68</v>
+        <v>2.9</v>
       </c>
       <c r="I7" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="J7" t="n">
-        <v>2.84</v>
+        <v>2.96</v>
       </c>
       <c r="K7" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="L7" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="N7" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="P7" t="n">
         <v>1.49</v>
       </c>
-      <c r="M7" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="N7" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="P7" t="n">
-        <v>1.46</v>
-      </c>
       <c r="Q7" t="n">
-        <v>2.14</v>
+        <v>2.78</v>
       </c>
       <c r="R7" t="n">
         <v>1.18</v>
       </c>
       <c r="S7" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="T7" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="U7" t="n">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="V7" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="W7" t="n">
-        <v>1.42</v>
+        <v>1.51</v>
       </c>
       <c r="X7" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="Y7" t="n">
         <v>9</v>
       </c>
-      <c r="Y7" t="n">
-        <v>9.4</v>
-      </c>
       <c r="Z7" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AA7" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AB7" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC7" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AD7" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AE7" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AF7" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AG7" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AH7" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AI7" t="n">
-        <v>85</v>
+        <v>190</v>
       </c>
       <c r="AJ7" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AK7" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AL7" t="n">
-        <v>85</v>
+        <v>230</v>
       </c>
       <c r="AM7" t="n">
         <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AO7" t="n">
         <v>65</v>
       </c>
       <c r="AP7" t="n">
-        <v>4.2</v>
+        <v>7</v>
       </c>
       <c r="AQ7" t="n">
-        <v>3.9</v>
+        <v>7.4</v>
       </c>
       <c r="AR7" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="AS7" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>15</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AY7" t="n">
         <v>6</v>
       </c>
-      <c r="AT7" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>5</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>4.6</v>
-      </c>
       <c r="AZ7" t="n">
-        <v>5.2</v>
+        <v>18.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>6.2</v>
+        <v>7.8</v>
       </c>
       <c r="BB7" t="n">
-        <v>6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC7" t="n">
-        <v>5.9</v>
+        <v>7.8</v>
       </c>
       <c r="BD7" t="n">
-        <v>6.2</v>
+        <v>7.8</v>
       </c>
       <c r="BE7" t="n">
-        <v>6.4</v>
+        <v>8.6</v>
       </c>
       <c r="BF7" t="n">
-        <v>6</v>
+        <v>7.8</v>
       </c>
       <c r="BG7" t="n">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-25 00:04:12</t>
+          <t>2026-03-25 02:09:31</t>
         </is>
       </c>
     </row>
@@ -1921,64 +1921,64 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="G8" t="n">
-        <v>1.68</v>
+        <v>1.8</v>
       </c>
       <c r="H8" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="I8" t="n">
-        <v>8.6</v>
+        <v>6.8</v>
       </c>
       <c r="J8" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K8" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="L8" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="M8" t="n">
         <v>1.08</v>
       </c>
       <c r="N8" t="n">
-        <v>2.84</v>
+        <v>3.2</v>
       </c>
       <c r="O8" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="P8" t="n">
         <v>1.73</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.94</v>
+        <v>2.02</v>
       </c>
       <c r="R8" t="n">
         <v>1.27</v>
       </c>
       <c r="S8" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="T8" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="U8" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="V8" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="W8" t="n">
-        <v>2.46</v>
+        <v>2.24</v>
       </c>
       <c r="X8" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="Y8" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="Z8" t="n">
         <v>1000</v>
@@ -1987,104 +1987,104 @@
         <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AC8" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>75</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF8" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="AD8" t="n">
-        <v>32</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>9</v>
-      </c>
       <c r="AG8" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="AI8" t="n">
         <v>1000</v>
       </c>
       <c r="AJ8" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AK8" t="n">
         <v>21</v>
       </c>
       <c r="AL8" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AM8" t="n">
         <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AO8" t="n">
         <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>4.9</v>
+        <v>9</v>
       </c>
       <c r="AQ8" t="n">
-        <v>5.7</v>
+        <v>14.5</v>
       </c>
       <c r="AR8" t="n">
-        <v>7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS8" t="n">
-        <v>7.6</v>
+        <v>10</v>
       </c>
       <c r="AT8" t="n">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="AU8" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="AV8" t="n">
-        <v>6.2</v>
+        <v>21</v>
       </c>
       <c r="AW8" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ8" t="n">
         <v>7.4</v>
       </c>
-      <c r="AX8" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>6</v>
-      </c>
       <c r="BA8" t="n">
-        <v>7.4</v>
+        <v>9.6</v>
       </c>
       <c r="BB8" t="n">
-        <v>5.2</v>
+        <v>6.6</v>
       </c>
       <c r="BC8" t="n">
-        <v>5.7</v>
+        <v>17</v>
       </c>
       <c r="BD8" t="n">
-        <v>6.8</v>
+        <v>8.4</v>
       </c>
       <c r="BE8" t="n">
-        <v>7.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF8" t="n">
-        <v>4.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG8" t="n">
-        <v>7.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-25 00:04:12</t>
+          <t>2026-03-25 02:09:31</t>
         </is>
       </c>
     </row>
@@ -2115,58 +2115,58 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="G9" t="n">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="H9" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="I9" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="J9" t="n">
         <v>3</v>
       </c>
       <c r="K9" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L9" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="M9" t="n">
         <v>1.1</v>
       </c>
       <c r="N9" t="n">
-        <v>2.82</v>
+        <v>3</v>
       </c>
       <c r="O9" t="n">
         <v>1.42</v>
       </c>
       <c r="P9" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.12</v>
+        <v>2.3</v>
       </c>
       <c r="R9" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="S9" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="T9" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="U9" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="V9" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="W9" t="n">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="X9" t="n">
         <v>21</v>
@@ -2181,7 +2181,7 @@
         <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>9.199999999999999</v>
+        <v>27</v>
       </c>
       <c r="AC9" t="n">
         <v>14</v>
@@ -2193,19 +2193,19 @@
         <v>1000</v>
       </c>
       <c r="AF9" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG9" t="n">
         <v>36</v>
       </c>
       <c r="AH9" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AI9" t="n">
         <v>1000</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK9" t="n">
         <v>1000</v>
@@ -2223,62 +2223,62 @@
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>7.8</v>
+        <v>4.9</v>
       </c>
       <c r="AQ9" t="n">
-        <v>9.4</v>
+        <v>5.7</v>
       </c>
       <c r="AR9" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="AS9" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AT9" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="AU9" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AV9" t="n">
         <v>12</v>
       </c>
       <c r="AW9" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AX9" t="n">
-        <v>10.5</v>
+        <v>5.6</v>
       </c>
       <c r="AY9" t="n">
-        <v>8.4</v>
+        <v>4.9</v>
       </c>
       <c r="AZ9" t="n">
-        <v>5</v>
+        <v>6.4</v>
       </c>
       <c r="BA9" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BB9" t="n">
-        <v>5.3</v>
+        <v>6.8</v>
       </c>
       <c r="BC9" t="n">
-        <v>5.3</v>
+        <v>6.8</v>
       </c>
       <c r="BD9" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="BE9" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BF9" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BG9" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-25 00:04:12</t>
+          <t>2026-03-25 02:09:31</t>
         </is>
       </c>
     </row>
@@ -2309,10 +2309,10 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.82</v>
+        <v>2.94</v>
       </c>
       <c r="G10" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="H10" t="n">
         <v>3.3</v>
@@ -2321,58 +2321,58 @@
         <v>3.5</v>
       </c>
       <c r="J10" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="K10" t="n">
-        <v>2.86</v>
+        <v>2.7</v>
       </c>
       <c r="L10" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="M10" t="n">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="N10" t="n">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="O10" t="n">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="P10" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="R10" t="n">
         <v>1.13</v>
       </c>
       <c r="S10" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="T10" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="U10" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="V10" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W10" t="n">
         <v>1.47</v>
       </c>
       <c r="X10" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="Y10" t="n">
         <v>9.4</v>
       </c>
       <c r="Z10" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AA10" t="n">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AB10" t="n">
         <v>9</v>
@@ -2381,31 +2381,31 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AD10" t="n">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="AE10" t="n">
-        <v>440</v>
+        <v>1000</v>
       </c>
       <c r="AF10" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="AG10" t="n">
-        <v>18.5</v>
+        <v>15.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="AI10" t="n">
         <v>1000</v>
       </c>
       <c r="AJ10" t="n">
-        <v>400</v>
+        <v>1000</v>
       </c>
       <c r="AK10" t="n">
-        <v>290</v>
+        <v>1000</v>
       </c>
       <c r="AL10" t="n">
-        <v>1000</v>
+        <v>540</v>
       </c>
       <c r="AM10" t="n">
         <v>1000</v>
@@ -2423,10 +2423,10 @@
         <v>6.8</v>
       </c>
       <c r="AR10" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AS10" t="n">
-        <v>4.9</v>
+        <v>20</v>
       </c>
       <c r="AT10" t="n">
         <v>6.4</v>
@@ -2435,44 +2435,44 @@
         <v>5.9</v>
       </c>
       <c r="AV10" t="n">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="AW10" t="n">
-        <v>4.8</v>
+        <v>6.6</v>
       </c>
       <c r="AX10" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AY10" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AZ10" t="n">
-        <v>20</v>
+        <v>16.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>4.8</v>
+        <v>6.4</v>
       </c>
       <c r="BB10" t="n">
-        <v>4.8</v>
+        <v>18</v>
       </c>
       <c r="BC10" t="n">
-        <v>4.8</v>
+        <v>6.4</v>
       </c>
       <c r="BD10" t="n">
-        <v>5</v>
+        <v>6.4</v>
       </c>
       <c r="BE10" t="n">
-        <v>5</v>
+        <v>6.8</v>
       </c>
       <c r="BF10" t="n">
-        <v>5.1</v>
+        <v>10</v>
       </c>
       <c r="BG10" t="n">
-        <v>4.9</v>
+        <v>6.4</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-25 00:04:12</t>
+          <t>2026-03-25 02:09:31</t>
         </is>
       </c>
     </row>
@@ -2506,13 +2506,13 @@
         <v>2.64</v>
       </c>
       <c r="G11" t="n">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="H11" t="n">
         <v>3.25</v>
       </c>
       <c r="I11" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="J11" t="n">
         <v>3</v>
@@ -2521,40 +2521,40 @@
         <v>3.15</v>
       </c>
       <c r="L11" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="M11" t="n">
         <v>1.13</v>
       </c>
       <c r="N11" t="n">
-        <v>2.48</v>
+        <v>2.58</v>
       </c>
       <c r="O11" t="n">
         <v>1.57</v>
       </c>
       <c r="P11" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.68</v>
+        <v>2.8</v>
       </c>
       <c r="R11" t="n">
         <v>1.18</v>
       </c>
       <c r="S11" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="T11" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="U11" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="V11" t="n">
         <v>1.4</v>
       </c>
       <c r="W11" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="X11" t="n">
         <v>8.199999999999999</v>
@@ -2566,7 +2566,7 @@
         <v>500</v>
       </c>
       <c r="AA11" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB11" t="n">
         <v>8</v>
@@ -2575,7 +2575,7 @@
         <v>7.2</v>
       </c>
       <c r="AD11" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="AE11" t="n">
         <v>290</v>
@@ -2584,7 +2584,7 @@
         <v>970</v>
       </c>
       <c r="AG11" t="n">
-        <v>14</v>
+        <v>970</v>
       </c>
       <c r="AH11" t="n">
         <v>950</v>
@@ -2596,7 +2596,7 @@
         <v>900</v>
       </c>
       <c r="AK11" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AL11" t="n">
         <v>1000</v>
@@ -2614,13 +2614,13 @@
         <v>7</v>
       </c>
       <c r="AQ11" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AR11" t="n">
         <v>9</v>
       </c>
       <c r="AS11" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AT11" t="n">
         <v>6.8</v>
@@ -2629,44 +2629,44 @@
         <v>6.2</v>
       </c>
       <c r="AV11" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AW11" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AX11" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AY11" t="n">
         <v>11.5</v>
       </c>
       <c r="AZ11" t="n">
-        <v>8.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>5.9</v>
+        <v>11</v>
       </c>
       <c r="BB11" t="n">
-        <v>9</v>
+        <v>16.5</v>
       </c>
       <c r="BC11" t="n">
         <v>10.5</v>
       </c>
       <c r="BD11" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BE11" t="n">
+        <v>12</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>34</v>
+      </c>
+      <c r="BG11" t="n">
         <v>10.5</v>
       </c>
-      <c r="BF11" t="n">
-        <v>9</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>9.6</v>
-      </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-25 00:04:12</t>
+          <t>2026-03-25 02:09:31</t>
         </is>
       </c>
     </row>
@@ -2697,13 +2697,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="G12" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="H12" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="I12" t="n">
         <v>5.8</v>
@@ -2712,34 +2712,34 @@
         <v>3.05</v>
       </c>
       <c r="K12" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L12" t="n">
-        <v>1.48</v>
+        <v>1.6</v>
       </c>
       <c r="M12" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N12" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="O12" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="P12" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.6</v>
+        <v>2.72</v>
       </c>
       <c r="R12" t="n">
         <v>1.18</v>
       </c>
       <c r="S12" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="T12" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="U12" t="n">
         <v>1.66</v>
@@ -2748,10 +2748,10 @@
         <v>1.21</v>
       </c>
       <c r="W12" t="n">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="X12" t="n">
-        <v>16</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y12" t="n">
         <v>1000</v>
@@ -2814,7 +2814,7 @@
         <v>14.5</v>
       </c>
       <c r="AS12" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AT12" t="n">
         <v>4.8</v>
@@ -2823,10 +2823,10 @@
         <v>6.6</v>
       </c>
       <c r="AV12" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AW12" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX12" t="n">
         <v>7.8</v>
@@ -2835,32 +2835,32 @@
         <v>8.4</v>
       </c>
       <c r="AZ12" t="n">
-        <v>19.5</v>
+        <v>7</v>
       </c>
       <c r="BA12" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="BB12" t="n">
         <v>10.5</v>
       </c>
       <c r="BC12" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="BD12" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE12" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF12" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.84</v>
+        <v>4</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-25 00:04:12</t>
+          <t>2026-03-25 02:09:31</t>
         </is>
       </c>
     </row>
@@ -2900,37 +2900,37 @@
         <v>2.26</v>
       </c>
       <c r="I13" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="J13" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K13" t="n">
         <v>3.9</v>
       </c>
       <c r="L13" t="n">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="M13" t="n">
         <v>1.05</v>
       </c>
       <c r="N13" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="O13" t="n">
         <v>1.23</v>
       </c>
       <c r="P13" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="R13" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="S13" t="n">
-        <v>2.74</v>
+        <v>2.84</v>
       </c>
       <c r="T13" t="n">
         <v>1.61</v>
@@ -2942,7 +2942,7 @@
         <v>1.73</v>
       </c>
       <c r="W13" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="X13" t="n">
         <v>38</v>
@@ -2954,7 +2954,7 @@
         <v>970</v>
       </c>
       <c r="AA13" t="n">
-        <v>900</v>
+        <v>120</v>
       </c>
       <c r="AB13" t="n">
         <v>970</v>
@@ -3008,7 +3008,7 @@
         <v>13</v>
       </c>
       <c r="AS13" t="n">
-        <v>21</v>
+        <v>7.2</v>
       </c>
       <c r="AT13" t="n">
         <v>8.4</v>
@@ -3035,16 +3035,16 @@
         <v>7.2</v>
       </c>
       <c r="BB13" t="n">
-        <v>8.800000000000001</v>
+        <v>23</v>
       </c>
       <c r="BC13" t="n">
-        <v>24</v>
+        <v>7.4</v>
       </c>
       <c r="BD13" t="n">
         <v>28</v>
       </c>
       <c r="BE13" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF13" t="n">
         <v>19</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-25 00:04:12</t>
+          <t>2026-03-25 02:09:31</t>
         </is>
       </c>
     </row>
@@ -3085,13 +3085,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="G14" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="H14" t="n">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="I14" t="n">
         <v>2.8</v>
@@ -3100,46 +3100,46 @@
         <v>3.5</v>
       </c>
       <c r="K14" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L14" t="n">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="M14" t="n">
         <v>1.06</v>
       </c>
       <c r="N14" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="O14" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="P14" t="n">
         <v>2.06</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="R14" t="n">
         <v>1.42</v>
       </c>
       <c r="S14" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="T14" t="n">
         <v>1.64</v>
       </c>
       <c r="U14" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="V14" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="W14" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="X14" t="n">
-        <v>970</v>
+        <v>17</v>
       </c>
       <c r="Y14" t="n">
         <v>13</v>
@@ -3157,7 +3157,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AD14" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AE14" t="n">
         <v>60</v>
@@ -3166,22 +3166,22 @@
         <v>20</v>
       </c>
       <c r="AG14" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AH14" t="n">
         <v>25</v>
       </c>
       <c r="AI14" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AJ14" t="n">
         <v>46</v>
       </c>
       <c r="AK14" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AL14" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AM14" t="n">
         <v>200</v>
@@ -3190,7 +3190,7 @@
         <v>1000</v>
       </c>
       <c r="AO14" t="n">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="AP14" t="n">
         <v>13.5</v>
@@ -3199,16 +3199,16 @@
         <v>11</v>
       </c>
       <c r="AR14" t="n">
-        <v>9</v>
+        <v>16.5</v>
       </c>
       <c r="AS14" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AT14" t="n">
         <v>11.5</v>
       </c>
       <c r="AU14" t="n">
-        <v>5.3</v>
+        <v>7</v>
       </c>
       <c r="AV14" t="n">
         <v>11</v>
@@ -3217,19 +3217,19 @@
         <v>13</v>
       </c>
       <c r="AX14" t="n">
-        <v>17</v>
+        <v>10.5</v>
       </c>
       <c r="AY14" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AZ14" t="n">
         <v>9</v>
       </c>
       <c r="BA14" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BB14" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BC14" t="n">
         <v>14.5</v>
@@ -3238,17 +3238,17 @@
         <v>20</v>
       </c>
       <c r="BE14" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF14" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BG14" t="n">
         <v>17.5</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-25 00:04:12</t>
+          <t>2026-03-25 02:09:31</t>
         </is>
       </c>
     </row>
@@ -3282,52 +3282,52 @@
         <v>3.65</v>
       </c>
       <c r="G15" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="H15" t="n">
         <v>2.08</v>
       </c>
       <c r="I15" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="J15" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K15" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L15" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="M15" t="n">
         <v>1.06</v>
       </c>
       <c r="N15" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="O15" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="P15" t="n">
         <v>2.16</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="R15" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="S15" t="n">
         <v>3.1</v>
       </c>
       <c r="T15" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="U15" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="V15" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="W15" t="n">
         <v>1.33</v>
@@ -3336,7 +3336,7 @@
         <v>18.5</v>
       </c>
       <c r="Y15" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="Z15" t="n">
         <v>14.5</v>
@@ -3363,28 +3363,28 @@
         <v>15.5</v>
       </c>
       <c r="AH15" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AI15" t="n">
         <v>34</v>
       </c>
       <c r="AJ15" t="n">
-        <v>900</v>
+        <v>70</v>
       </c>
       <c r="AK15" t="n">
-        <v>100</v>
+        <v>42</v>
       </c>
       <c r="AL15" t="n">
         <v>120</v>
       </c>
       <c r="AM15" t="n">
-        <v>580</v>
+        <v>85</v>
       </c>
       <c r="AN15" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AO15" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AP15" t="n">
         <v>12.5</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-25 00:04:12</t>
+          <t>2026-03-25 02:09:31</t>
         </is>
       </c>
     </row>
@@ -3479,10 +3479,10 @@
         <v>3.8</v>
       </c>
       <c r="H16" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="I16" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="J16" t="n">
         <v>3.7</v>
@@ -3491,34 +3491,34 @@
         <v>3.85</v>
       </c>
       <c r="L16" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="M16" t="n">
         <v>1.04</v>
       </c>
       <c r="N16" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="O16" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="P16" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="R16" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="S16" t="n">
-        <v>2.66</v>
+        <v>2.74</v>
       </c>
       <c r="T16" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="U16" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="V16" t="n">
         <v>1.83</v>
@@ -3527,16 +3527,16 @@
         <v>1.36</v>
       </c>
       <c r="X16" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Y16" t="n">
         <v>13.5</v>
       </c>
       <c r="Z16" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AA16" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AB16" t="n">
         <v>19</v>
@@ -3566,16 +3566,16 @@
         <v>150</v>
       </c>
       <c r="AK16" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AL16" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AM16" t="n">
-        <v>320</v>
+        <v>70</v>
       </c>
       <c r="AN16" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AO16" t="n">
         <v>12</v>
@@ -3596,7 +3596,7 @@
         <v>16</v>
       </c>
       <c r="AU16" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AV16" t="n">
         <v>9.4</v>
@@ -3620,7 +3620,7 @@
         <v>44</v>
       </c>
       <c r="BC16" t="n">
-        <v>9.199999999999999</v>
+        <v>30</v>
       </c>
       <c r="BD16" t="n">
         <v>30</v>
@@ -3629,14 +3629,14 @@
         <v>50</v>
       </c>
       <c r="BF16" t="n">
-        <v>21</v>
+        <v>8.6</v>
       </c>
       <c r="BG16" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-25 00:04:12</t>
+          <t>2026-03-25 02:09:31</t>
         </is>
       </c>
     </row>
@@ -3673,19 +3673,19 @@
         <v>1.71</v>
       </c>
       <c r="H17" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="I17" t="n">
         <v>6</v>
       </c>
       <c r="J17" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K17" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="L17" t="n">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="M17" t="n">
         <v>1.05</v>
@@ -3694,25 +3694,25 @@
         <v>4.1</v>
       </c>
       <c r="O17" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P17" t="n">
         <v>2.08</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="R17" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="S17" t="n">
-        <v>2.98</v>
+        <v>3.1</v>
       </c>
       <c r="T17" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="U17" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="V17" t="n">
         <v>1.2</v>
@@ -3721,10 +3721,10 @@
         <v>2.42</v>
       </c>
       <c r="X17" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Y17" t="n">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="Z17" t="n">
         <v>220</v>
@@ -3739,13 +3739,13 @@
         <v>10</v>
       </c>
       <c r="AD17" t="n">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="AE17" t="n">
         <v>400</v>
       </c>
       <c r="AF17" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AG17" t="n">
         <v>10.5</v>
@@ -3760,7 +3760,7 @@
         <v>17.5</v>
       </c>
       <c r="AK17" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AL17" t="n">
         <v>36</v>
@@ -3769,7 +3769,7 @@
         <v>580</v>
       </c>
       <c r="AN17" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AO17" t="n">
         <v>310</v>
@@ -3781,7 +3781,7 @@
         <v>17.5</v>
       </c>
       <c r="AR17" t="n">
-        <v>36</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS17" t="n">
         <v>9</v>
@@ -3826,11 +3826,11 @@
         <v>8</v>
       </c>
       <c r="BG17" t="n">
-        <v>65</v>
+        <v>13.5</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-25 00:04:12</t>
+          <t>2026-03-25 02:09:31</t>
         </is>
       </c>
     </row>
@@ -3861,85 +3861,85 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="G18" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="H18" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="I18" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="J18" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="K18" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="L18" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="M18" t="n">
         <v>1.07</v>
       </c>
       <c r="N18" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="O18" t="n">
         <v>1.34</v>
       </c>
       <c r="P18" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="Q18" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="R18" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="S18" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="T18" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="U18" t="n">
         <v>2.04</v>
       </c>
       <c r="V18" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W18" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="X18" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="Y18" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Z18" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AA18" t="n">
-        <v>120</v>
+        <v>900</v>
       </c>
       <c r="AB18" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AC18" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AD18" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AE18" t="n">
-        <v>320</v>
+        <v>55</v>
       </c>
       <c r="AF18" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AG18" t="n">
         <v>10.5</v>
@@ -3948,40 +3948,40 @@
         <v>19</v>
       </c>
       <c r="AI18" t="n">
-        <v>150</v>
+        <v>65</v>
       </c>
       <c r="AJ18" t="n">
         <v>23</v>
       </c>
       <c r="AK18" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AL18" t="n">
-        <v>85</v>
+        <v>38</v>
       </c>
       <c r="AM18" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AN18" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AO18" t="n">
-        <v>260</v>
+        <v>65</v>
       </c>
       <c r="AP18" t="n">
         <v>12</v>
       </c>
       <c r="AQ18" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AR18" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AS18" t="n">
-        <v>9.800000000000001</v>
+        <v>14</v>
       </c>
       <c r="AT18" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AU18" t="n">
         <v>7.2</v>
@@ -3990,41 +3990,41 @@
         <v>16</v>
       </c>
       <c r="AW18" t="n">
-        <v>48</v>
+        <v>12.5</v>
       </c>
       <c r="AX18" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AY18" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AZ18" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>21</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>32</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BF18" t="n">
         <v>14</v>
       </c>
-      <c r="BA18" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>20</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>27</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>13</v>
-      </c>
       <c r="BG18" t="n">
-        <v>9.199999999999999</v>
+        <v>50</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-25 00:04:12</t>
+          <t>2026-03-25 02:09:31</t>
         </is>
       </c>
     </row>
@@ -4055,58 +4055,58 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="G19" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="H19" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="I19" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J19" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="K19" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="L19" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="M19" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N19" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="O19" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="P19" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="R19" t="n">
         <v>1.29</v>
       </c>
       <c r="S19" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="T19" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="U19" t="n">
         <v>1.64</v>
       </c>
       <c r="V19" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="W19" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="X19" t="n">
         <v>970</v>
@@ -4115,13 +4115,13 @@
         <v>70</v>
       </c>
       <c r="Z19" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AA19" t="n">
         <v>1000</v>
       </c>
       <c r="AB19" t="n">
-        <v>970</v>
+        <v>12</v>
       </c>
       <c r="AC19" t="n">
         <v>42</v>
@@ -4133,7 +4133,7 @@
         <v>1000</v>
       </c>
       <c r="AF19" t="n">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="AG19" t="n">
         <v>25</v>
@@ -4145,7 +4145,7 @@
         <v>1000</v>
       </c>
       <c r="AJ19" t="n">
-        <v>900</v>
+        <v>180</v>
       </c>
       <c r="AK19" t="n">
         <v>70</v>
@@ -4157,16 +4157,16 @@
         <v>1000</v>
       </c>
       <c r="AN19" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AO19" t="n">
         <v>1000</v>
       </c>
       <c r="AP19" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AQ19" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AR19" t="n">
         <v>4.2</v>
@@ -4175,13 +4175,13 @@
         <v>4.2</v>
       </c>
       <c r="AT19" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="AU19" t="n">
         <v>6.2</v>
       </c>
       <c r="AV19" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AW19" t="n">
         <v>4.2</v>
@@ -4190,35 +4190,35 @@
         <v>6.4</v>
       </c>
       <c r="AY19" t="n">
-        <v>3.9</v>
+        <v>5.2</v>
       </c>
       <c r="AZ19" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BA19" t="n">
         <v>4.2</v>
       </c>
       <c r="BB19" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BG19" t="n">
         <v>9.6</v>
       </c>
-      <c r="BC19" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>3</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>7</v>
-      </c>
-      <c r="BG19" t="n">
-        <v>9</v>
-      </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-25 00:04:12</t>
+          <t>2026-03-25 02:09:31</t>
         </is>
       </c>
     </row>
@@ -4252,28 +4252,28 @@
         <v>3.15</v>
       </c>
       <c r="G20" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="H20" t="n">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="I20" t="n">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="J20" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="K20" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="L20" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="M20" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="N20" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="O20" t="n">
         <v>1.55</v>
@@ -4282,49 +4282,49 @@
         <v>1.53</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.66</v>
+        <v>2.76</v>
       </c>
       <c r="R20" t="n">
         <v>1.18</v>
       </c>
       <c r="S20" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="T20" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="U20" t="n">
         <v>1.79</v>
       </c>
       <c r="V20" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="W20" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="X20" t="n">
         <v>8.4</v>
       </c>
       <c r="Y20" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="Z20" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AA20" t="n">
+        <v>900</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AE20" t="n">
         <v>100</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>17</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>90</v>
       </c>
       <c r="AF20" t="n">
         <v>20</v>
@@ -4357,16 +4357,16 @@
         <v>500</v>
       </c>
       <c r="AP20" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AQ20" t="n">
         <v>7.4</v>
       </c>
       <c r="AR20" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AS20" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AT20" t="n">
         <v>8</v>
@@ -4378,7 +4378,7 @@
         <v>12</v>
       </c>
       <c r="AW20" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AX20" t="n">
         <v>14</v>
@@ -4396,7 +4396,7 @@
         <v>29</v>
       </c>
       <c r="BC20" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BD20" t="n">
         <v>36</v>
@@ -4408,11 +4408,11 @@
         <v>30</v>
       </c>
       <c r="BG20" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-25 00:04:12</t>
+          <t>2026-03-25 02:09:31</t>
         </is>
       </c>
     </row>
@@ -4446,10 +4446,10 @@
         <v>2.64</v>
       </c>
       <c r="G21" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="H21" t="n">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="I21" t="n">
         <v>3.9</v>
@@ -4458,46 +4458,46 @@
         <v>2.72</v>
       </c>
       <c r="K21" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="L21" t="n">
-        <v>1.78</v>
+        <v>1.86</v>
       </c>
       <c r="M21" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="N21" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="O21" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="P21" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.55</v>
+        <v>4.1</v>
       </c>
       <c r="R21" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="S21" t="n">
-        <v>3.85</v>
+        <v>10</v>
       </c>
       <c r="T21" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="U21" t="n">
         <v>1.46</v>
       </c>
       <c r="V21" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="W21" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="X21" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="Y21" t="n">
         <v>8</v>
@@ -4533,25 +4533,25 @@
         <v>200</v>
       </c>
       <c r="AJ21" t="n">
-        <v>100</v>
+        <v>55</v>
       </c>
       <c r="AK21" t="n">
         <v>65</v>
       </c>
       <c r="AL21" t="n">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AM21" t="n">
-        <v>540</v>
+        <v>500</v>
       </c>
       <c r="AN21" t="n">
-        <v>90</v>
+        <v>500</v>
       </c>
       <c r="AO21" t="n">
         <v>210</v>
       </c>
       <c r="AP21" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="AQ21" t="n">
         <v>7.2</v>
@@ -4560,31 +4560,31 @@
         <v>16</v>
       </c>
       <c r="AS21" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AT21" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="AU21" t="n">
         <v>6.6</v>
       </c>
       <c r="AV21" t="n">
-        <v>18.5</v>
+        <v>15.5</v>
       </c>
       <c r="AW21" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AX21" t="n">
         <v>12.5</v>
       </c>
       <c r="AY21" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="AZ21" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BA21" t="n">
-        <v>46</v>
+        <v>90</v>
       </c>
       <c r="BB21" t="n">
         <v>25</v>
@@ -4593,20 +4593,20 @@
         <v>29</v>
       </c>
       <c r="BD21" t="n">
-        <v>44</v>
+        <v>75</v>
       </c>
       <c r="BE21" t="n">
         <v>120</v>
       </c>
       <c r="BF21" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="BG21" t="n">
         <v>46</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-25 00:04:12</t>
+          <t>2026-03-25 02:09:31</t>
         </is>
       </c>
     </row>
@@ -4637,46 +4637,46 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="G22" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="H22" t="n">
         <v>4.3</v>
       </c>
       <c r="I22" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="J22" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="K22" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L22" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="M22" t="n">
         <v>1.09</v>
       </c>
       <c r="N22" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="O22" t="n">
         <v>1.41</v>
       </c>
       <c r="P22" t="n">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.16</v>
+        <v>2.24</v>
       </c>
       <c r="R22" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="S22" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="T22" t="n">
         <v>1.94</v>
@@ -4685,13 +4685,13 @@
         <v>1.87</v>
       </c>
       <c r="V22" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="W22" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="X22" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="Y22" t="n">
         <v>16.5</v>
@@ -4709,28 +4709,28 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AD22" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE22" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AF22" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AG22" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AH22" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI22" t="n">
         <v>85</v>
       </c>
       <c r="AJ22" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AK22" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AL22" t="n">
         <v>48</v>
@@ -4739,10 +4739,10 @@
         <v>1000</v>
       </c>
       <c r="AN22" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AO22" t="n">
-        <v>110</v>
+        <v>290</v>
       </c>
       <c r="AP22" t="n">
         <v>8.4</v>
@@ -4754,7 +4754,7 @@
         <v>13</v>
       </c>
       <c r="AS22" t="n">
-        <v>5.6</v>
+        <v>6.8</v>
       </c>
       <c r="AT22" t="n">
         <v>6.6</v>
@@ -4766,7 +4766,7 @@
         <v>13.5</v>
       </c>
       <c r="AW22" t="n">
-        <v>5.5</v>
+        <v>6.6</v>
       </c>
       <c r="AX22" t="n">
         <v>8.6</v>
@@ -4775,32 +4775,32 @@
         <v>7.8</v>
       </c>
       <c r="AZ22" t="n">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="BA22" t="n">
-        <v>5.4</v>
+        <v>6.6</v>
       </c>
       <c r="BB22" t="n">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="BC22" t="n">
         <v>20</v>
       </c>
       <c r="BD22" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="BE22" t="n">
-        <v>5.5</v>
+        <v>6.8</v>
       </c>
       <c r="BF22" t="n">
         <v>13.5</v>
       </c>
       <c r="BG22" t="n">
-        <v>5.6</v>
+        <v>6.8</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-25 00:04:12</t>
+          <t>2026-03-25 02:09:31</t>
         </is>
       </c>
     </row>
@@ -4831,46 +4831,46 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="G23" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="H23" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="I23" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="J23" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="K23" t="n">
         <v>3.65</v>
       </c>
       <c r="L23" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="M23" t="n">
         <v>1.09</v>
       </c>
       <c r="N23" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="O23" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="P23" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="R23" t="n">
         <v>1.26</v>
       </c>
       <c r="S23" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="T23" t="n">
         <v>2</v>
@@ -4879,13 +4879,13 @@
         <v>1.87</v>
       </c>
       <c r="V23" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="W23" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="X23" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Y23" t="n">
         <v>1000</v>
@@ -4897,10 +4897,10 @@
         <v>1000</v>
       </c>
       <c r="AB23" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AC23" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD23" t="n">
         <v>1000</v>
@@ -4909,10 +4909,10 @@
         <v>1000</v>
       </c>
       <c r="AF23" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AG23" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AH23" t="n">
         <v>1000</v>
@@ -4921,10 +4921,10 @@
         <v>1000</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK23" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AL23" t="n">
         <v>1000</v>
@@ -4933,7 +4933,7 @@
         <v>1000</v>
       </c>
       <c r="AN23" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AO23" t="n">
         <v>1000</v>
@@ -4942,59 +4942,59 @@
         <v>5.8</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.32</v>
+        <v>6.2</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.32</v>
+        <v>4.1</v>
       </c>
       <c r="AS23" t="n">
-        <v>1.33</v>
+        <v>4.5</v>
       </c>
       <c r="AT23" t="n">
-        <v>1.27</v>
+        <v>6.6</v>
       </c>
       <c r="AU23" t="n">
-        <v>1.34</v>
+        <v>7</v>
       </c>
       <c r="AV23" t="n">
-        <v>1.32</v>
+        <v>16</v>
       </c>
       <c r="AW23" t="n">
-        <v>1.33</v>
+        <v>2.62</v>
       </c>
       <c r="AX23" t="n">
-        <v>1.29</v>
+        <v>5.7</v>
       </c>
       <c r="AY23" t="n">
-        <v>1.29</v>
+        <v>5.6</v>
       </c>
       <c r="AZ23" t="n">
-        <v>1.31</v>
+        <v>7.6</v>
       </c>
       <c r="BA23" t="n">
-        <v>1.33</v>
+        <v>10</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.33</v>
+        <v>6.4</v>
       </c>
       <c r="BC23" t="n">
-        <v>1.31</v>
+        <v>7.8</v>
       </c>
       <c r="BD23" t="n">
-        <v>1.33</v>
+        <v>2.56</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.34</v>
+        <v>11</v>
       </c>
       <c r="BF23" t="n">
-        <v>4.4</v>
+        <v>7.2</v>
       </c>
       <c r="BG23" t="n">
-        <v>1.55</v>
+        <v>8</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-25 00:04:12</t>
+          <t>2026-03-25 02:09:31</t>
         </is>
       </c>
     </row>
@@ -5025,58 +5025,58 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="G24" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="H24" t="n">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="I24" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="J24" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="K24" t="n">
         <v>4.4</v>
       </c>
       <c r="L24" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="M24" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N24" t="n">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="O24" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="P24" t="n">
-        <v>1.67</v>
+        <v>1.79</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="R24" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="S24" t="n">
         <v>3.9</v>
       </c>
       <c r="T24" t="n">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="U24" t="n">
-        <v>1.67</v>
+        <v>1.74</v>
       </c>
       <c r="V24" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="W24" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="X24" t="n">
         <v>1000</v>
@@ -5094,7 +5094,7 @@
         <v>27</v>
       </c>
       <c r="AC24" t="n">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="AD24" t="n">
         <v>1000</v>
@@ -5103,7 +5103,7 @@
         <v>1000</v>
       </c>
       <c r="AF24" t="n">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="AG24" t="n">
         <v>1000</v>
@@ -5133,7 +5133,7 @@
         <v>1000</v>
       </c>
       <c r="AP24" t="n">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="AQ24" t="n">
         <v>4.2</v>
@@ -5145,10 +5145,10 @@
         <v>4.2</v>
       </c>
       <c r="AT24" t="n">
-        <v>3.95</v>
+        <v>5.6</v>
       </c>
       <c r="AU24" t="n">
-        <v>4.8</v>
+        <v>7.2</v>
       </c>
       <c r="AV24" t="n">
         <v>4.2</v>
@@ -5160,35 +5160,35 @@
         <v>6.8</v>
       </c>
       <c r="AY24" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AZ24" t="n">
-        <v>2.54</v>
+        <v>7.6</v>
       </c>
       <c r="BA24" t="n">
         <v>4.2</v>
       </c>
       <c r="BB24" t="n">
-        <v>3.85</v>
+        <v>6.2</v>
       </c>
       <c r="BC24" t="n">
-        <v>2.46</v>
+        <v>6.8</v>
       </c>
       <c r="BD24" t="n">
-        <v>2.38</v>
+        <v>3.5</v>
       </c>
       <c r="BE24" t="n">
-        <v>2.2</v>
+        <v>3.75</v>
       </c>
       <c r="BF24" t="n">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="BG24" t="n">
         <v>4.2</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-25 00:04:12</t>
+          <t>2026-03-25 02:09:31</t>
         </is>
       </c>
     </row>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-25 00:04:12</t>
+          <t>2026-03-25 02:09:31</t>
         </is>
       </c>
     </row>
@@ -5413,55 +5413,55 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="G26" t="n">
         <v>1.69</v>
       </c>
       <c r="H26" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="I26" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="J26" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="K26" t="n">
         <v>4.5</v>
       </c>
       <c r="L26" t="n">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="M26" t="n">
         <v>1.06</v>
       </c>
       <c r="N26" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="O26" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="P26" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="R26" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S26" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="T26" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="U26" t="n">
         <v>2.06</v>
       </c>
       <c r="V26" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="W26" t="n">
         <v>2.44</v>
@@ -5515,7 +5515,7 @@
         <v>580</v>
       </c>
       <c r="AN26" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AO26" t="n">
         <v>700</v>
@@ -5527,10 +5527,10 @@
         <v>17.5</v>
       </c>
       <c r="AR26" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AS26" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AT26" t="n">
         <v>8</v>
@@ -5542,7 +5542,7 @@
         <v>17</v>
       </c>
       <c r="AW26" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AX26" t="n">
         <v>9.6</v>
@@ -5554,7 +5554,7 @@
         <v>16.5</v>
       </c>
       <c r="BA26" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BB26" t="n">
         <v>13</v>
@@ -5566,17 +5566,17 @@
         <v>19.5</v>
       </c>
       <c r="BE26" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF26" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BG26" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-25 00:04:12</t>
+          <t>2026-03-25 02:09:31</t>
         </is>
       </c>
     </row>
@@ -5610,58 +5610,58 @@
         <v>2.54</v>
       </c>
       <c r="G27" t="n">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="H27" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="I27" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="J27" t="n">
         <v>3.6</v>
       </c>
       <c r="K27" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L27" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="M27" t="n">
         <v>1.06</v>
       </c>
       <c r="N27" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="O27" t="n">
         <v>1.28</v>
       </c>
       <c r="P27" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="R27" t="n">
         <v>1.4</v>
       </c>
       <c r="S27" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="T27" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="U27" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="V27" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W27" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="X27" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="Y27" t="n">
         <v>14.5</v>
@@ -5673,7 +5673,7 @@
         <v>120</v>
       </c>
       <c r="AB27" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AC27" t="n">
         <v>9.199999999999999</v>
@@ -5682,10 +5682,10 @@
         <v>13.5</v>
       </c>
       <c r="AE27" t="n">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="AF27" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AG27" t="n">
         <v>12</v>
@@ -5724,7 +5724,7 @@
         <v>16.5</v>
       </c>
       <c r="AS27" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AT27" t="n">
         <v>8</v>
@@ -5748,7 +5748,7 @@
         <v>12.5</v>
       </c>
       <c r="BA27" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BB27" t="n">
         <v>18</v>
@@ -5760,17 +5760,17 @@
         <v>18</v>
       </c>
       <c r="BE27" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF27" t="n">
         <v>14</v>
       </c>
       <c r="BG27" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-25 00:04:12</t>
+          <t>2026-03-25 02:09:31</t>
         </is>
       </c>
     </row>
@@ -5801,55 +5801,55 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="G28" t="n">
         <v>7.4</v>
       </c>
       <c r="H28" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="I28" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="J28" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K28" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L28" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="M28" t="n">
         <v>1.09</v>
       </c>
       <c r="N28" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="O28" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="P28" t="n">
         <v>1.71</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="R28" t="n">
         <v>1.25</v>
       </c>
       <c r="S28" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="T28" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="U28" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="V28" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="W28" t="n">
         <v>1.16</v>
@@ -5861,13 +5861,13 @@
         <v>6.8</v>
       </c>
       <c r="Z28" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AA28" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AB28" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AC28" t="n">
         <v>8.800000000000001</v>
@@ -5879,16 +5879,16 @@
         <v>21</v>
       </c>
       <c r="AF28" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AG28" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AH28" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AI28" t="n">
-        <v>55</v>
+        <v>110</v>
       </c>
       <c r="AJ28" t="n">
         <v>900</v>
@@ -5897,7 +5897,7 @@
         <v>700</v>
       </c>
       <c r="AL28" t="n">
-        <v>450</v>
+        <v>700</v>
       </c>
       <c r="AM28" t="n">
         <v>700</v>
@@ -5909,19 +5909,19 @@
         <v>14.5</v>
       </c>
       <c r="AP28" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AQ28" t="n">
         <v>6</v>
       </c>
       <c r="AR28" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AS28" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AT28" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AU28" t="n">
         <v>7.2</v>
@@ -5933,19 +5933,19 @@
         <v>17.5</v>
       </c>
       <c r="AX28" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AY28" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AZ28" t="n">
         <v>18</v>
       </c>
       <c r="BA28" t="n">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="BB28" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BC28" t="n">
         <v>40</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-25 00:04:12</t>
+          <t>2026-03-25 02:09:31</t>
         </is>
       </c>
     </row>
@@ -5995,16 +5995,16 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="G29" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="H29" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="I29" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="J29" t="n">
         <v>3.85</v>
@@ -6013,55 +6013,55 @@
         <v>4.1</v>
       </c>
       <c r="L29" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="M29" t="n">
         <v>1.09</v>
       </c>
       <c r="N29" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="O29" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="P29" t="n">
         <v>1.73</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="R29" t="n">
         <v>1.27</v>
       </c>
       <c r="S29" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="T29" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="U29" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="V29" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="W29" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="X29" t="n">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="Y29" t="n">
         <v>970</v>
       </c>
       <c r="Z29" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AA29" t="n">
         <v>1000</v>
       </c>
       <c r="AB29" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AC29" t="n">
         <v>10</v>
@@ -6085,19 +6085,19 @@
         <v>1000</v>
       </c>
       <c r="AJ29" t="n">
-        <v>970</v>
+        <v>20</v>
       </c>
       <c r="AK29" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AL29" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AM29" t="n">
         <v>1000</v>
       </c>
       <c r="AN29" t="n">
-        <v>12.5</v>
+        <v>16</v>
       </c>
       <c r="AO29" t="n">
         <v>1000</v>
@@ -6106,25 +6106,25 @@
         <v>10.5</v>
       </c>
       <c r="AQ29" t="n">
-        <v>17</v>
+        <v>5.2</v>
       </c>
       <c r="AR29" t="n">
-        <v>8.199999999999999</v>
+        <v>6.4</v>
       </c>
       <c r="AS29" t="n">
-        <v>9.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="AT29" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AU29" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AV29" t="n">
-        <v>7</v>
+        <v>5.7</v>
       </c>
       <c r="AW29" t="n">
-        <v>8.800000000000001</v>
+        <v>6.8</v>
       </c>
       <c r="AX29" t="n">
         <v>7.6</v>
@@ -6133,10 +6133,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ29" t="n">
-        <v>7</v>
+        <v>5.7</v>
       </c>
       <c r="BA29" t="n">
-        <v>8.800000000000001</v>
+        <v>6.8</v>
       </c>
       <c r="BB29" t="n">
         <v>13.5</v>
@@ -6145,20 +6145,20 @@
         <v>17.5</v>
       </c>
       <c r="BD29" t="n">
-        <v>8</v>
+        <v>6.2</v>
       </c>
       <c r="BE29" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BF29" t="n">
-        <v>9.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="BG29" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-25 00:04:12</t>
+          <t>2026-03-25 02:09:31</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-25.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-25.xlsx
@@ -757,22 +757,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="G2" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="H2" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="I2" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="J2" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="K2" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L2" t="n">
         <v>1.46</v>
@@ -781,34 +781,34 @@
         <v>1.08</v>
       </c>
       <c r="N2" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="O2" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="P2" t="n">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.16</v>
+        <v>2.08</v>
       </c>
       <c r="R2" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="S2" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="T2" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="U2" t="n">
         <v>1.92</v>
       </c>
-      <c r="U2" t="n">
-        <v>1.89</v>
-      </c>
       <c r="V2" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="W2" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="X2" t="n">
         <v>22</v>
@@ -829,7 +829,7 @@
         <v>14</v>
       </c>
       <c r="AD2" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AE2" t="n">
         <v>1000</v>
@@ -874,7 +874,7 @@
         <v>5.8</v>
       </c>
       <c r="AS2" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AT2" t="n">
         <v>6</v>
@@ -886,7 +886,7 @@
         <v>5.3</v>
       </c>
       <c r="AW2" t="n">
-        <v>11</v>
+        <v>6.8</v>
       </c>
       <c r="AX2" t="n">
         <v>7</v>
@@ -895,32 +895,32 @@
         <v>7.8</v>
       </c>
       <c r="AZ2" t="n">
-        <v>6.8</v>
+        <v>9.6</v>
       </c>
       <c r="BA2" t="n">
-        <v>2.82</v>
+        <v>3</v>
       </c>
       <c r="BB2" t="n">
-        <v>2.6</v>
+        <v>2.06</v>
       </c>
       <c r="BC2" t="n">
-        <v>2.16</v>
+        <v>1.91</v>
       </c>
       <c r="BD2" t="n">
-        <v>2.16</v>
+        <v>1.87</v>
       </c>
       <c r="BE2" t="n">
-        <v>2.64</v>
+        <v>2.46</v>
       </c>
       <c r="BF2" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="BG2" t="n">
         <v>4</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-25 02:09:31</t>
+          <t>2026-03-25 04:14:47</t>
         </is>
       </c>
     </row>
@@ -951,10 +951,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="G3" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="H3" t="n">
         <v>1.74</v>
@@ -978,13 +978,13 @@
         <v>2.98</v>
       </c>
       <c r="O3" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="P3" t="n">
         <v>1.64</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="R3" t="n">
         <v>1.23</v>
@@ -996,7 +996,7 @@
         <v>2.12</v>
       </c>
       <c r="U3" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="V3" t="n">
         <v>2.16</v>
@@ -1014,7 +1014,7 @@
         <v>11.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>23</v>
+        <v>19.5</v>
       </c>
       <c r="AB3" t="n">
         <v>16.5</v>
@@ -1026,13 +1026,13 @@
         <v>13</v>
       </c>
       <c r="AE3" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AF3" t="n">
         <v>75</v>
       </c>
       <c r="AG3" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="AH3" t="n">
         <v>32</v>
@@ -1056,7 +1056,7 @@
         <v>700</v>
       </c>
       <c r="AO3" t="n">
-        <v>20</v>
+        <v>16.5</v>
       </c>
       <c r="AP3" t="n">
         <v>8.800000000000001</v>
@@ -1071,7 +1071,7 @@
         <v>16</v>
       </c>
       <c r="AT3" t="n">
-        <v>13.5</v>
+        <v>7.6</v>
       </c>
       <c r="AU3" t="n">
         <v>7.2</v>
@@ -1083,10 +1083,10 @@
         <v>19</v>
       </c>
       <c r="AX3" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AY3" t="n">
-        <v>21</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ3" t="n">
         <v>21</v>
@@ -1095,26 +1095,26 @@
         <v>28</v>
       </c>
       <c r="BB3" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BC3" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="BD3" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="BE3" t="n">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="BF3" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BG3" t="n">
         <v>14</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-25 02:09:31</t>
+          <t>2026-03-25 04:14:47</t>
         </is>
       </c>
     </row>
@@ -1145,22 +1145,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.36</v>
+        <v>2.28</v>
       </c>
       <c r="G4" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="H4" t="n">
         <v>3.1</v>
       </c>
       <c r="I4" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="J4" t="n">
         <v>3.35</v>
       </c>
       <c r="K4" t="n">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="L4" t="n">
         <v>1.42</v>
@@ -1190,13 +1190,13 @@
         <v>1.76</v>
       </c>
       <c r="U4" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="V4" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W4" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="X4" t="n">
         <v>16</v>
@@ -1214,7 +1214,7 @@
         <v>10.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AD4" t="n">
         <v>15.5</v>
@@ -1238,7 +1238,7 @@
         <v>34</v>
       </c>
       <c r="AK4" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="AL4" t="n">
         <v>42</v>
@@ -1247,10 +1247,10 @@
         <v>440</v>
       </c>
       <c r="AN4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AO4" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AP4" t="n">
         <v>11.5</v>
@@ -1289,26 +1289,26 @@
         <v>23</v>
       </c>
       <c r="BB4" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="BC4" t="n">
-        <v>22</v>
+        <v>15.5</v>
       </c>
       <c r="BD4" t="n">
         <v>24</v>
       </c>
       <c r="BE4" t="n">
-        <v>28</v>
+        <v>6.8</v>
       </c>
       <c r="BF4" t="n">
         <v>18</v>
       </c>
       <c r="BG4" t="n">
-        <v>23</v>
+        <v>6.8</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-25 02:09:31</t>
+          <t>2026-03-25 04:14:47</t>
         </is>
       </c>
     </row>
@@ -1339,58 +1339,58 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="G5" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="H5" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="I5" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J5" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="K5" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="L5" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="M5" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N5" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="O5" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="P5" t="n">
-        <v>2.84</v>
+        <v>2.96</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="R5" t="n">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="S5" t="n">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="T5" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="U5" t="n">
         <v>1.66</v>
       </c>
       <c r="V5" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="W5" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="X5" t="n">
         <v>38</v>
@@ -1417,13 +1417,13 @@
         <v>1000</v>
       </c>
       <c r="AF5" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AG5" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AH5" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="AI5" t="n">
         <v>1000</v>
@@ -1432,7 +1432,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AK5" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AL5" t="n">
         <v>1000</v>
@@ -1441,7 +1441,7 @@
         <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="AO5" t="n">
         <v>1000</v>
@@ -1450,25 +1450,25 @@
         <v>7</v>
       </c>
       <c r="AQ5" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="AR5" t="n">
-        <v>7</v>
+        <v>8.4</v>
       </c>
       <c r="AS5" t="n">
-        <v>7.2</v>
+        <v>8.6</v>
       </c>
       <c r="AT5" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AU5" t="n">
         <v>17</v>
       </c>
       <c r="AV5" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="AW5" t="n">
-        <v>7</v>
+        <v>8.4</v>
       </c>
       <c r="AX5" t="n">
         <v>7.2</v>
@@ -1477,32 +1477,32 @@
         <v>11</v>
       </c>
       <c r="AZ5" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BA5" t="n">
-        <v>7</v>
+        <v>8.4</v>
       </c>
       <c r="BB5" t="n">
         <v>7.2</v>
       </c>
       <c r="BC5" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BD5" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BE5" t="n">
-        <v>7</v>
+        <v>8.4</v>
       </c>
       <c r="BF5" t="n">
-        <v>2.96</v>
+        <v>2.78</v>
       </c>
       <c r="BG5" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-25 02:09:31</t>
+          <t>2026-03-25 04:14:47</t>
         </is>
       </c>
     </row>
@@ -1536,19 +1536,19 @@
         <v>1.49</v>
       </c>
       <c r="G6" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="H6" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="I6" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="J6" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K6" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="L6" t="n">
         <v>1.35</v>
@@ -1557,19 +1557,19 @@
         <v>1.05</v>
       </c>
       <c r="N6" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="O6" t="n">
         <v>1.25</v>
       </c>
       <c r="P6" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="Q6" t="n">
         <v>1.73</v>
       </c>
       <c r="R6" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="S6" t="n">
         <v>2.86</v>
@@ -1581,13 +1581,13 @@
         <v>1.92</v>
       </c>
       <c r="V6" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="W6" t="n">
         <v>2.72</v>
       </c>
       <c r="X6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Y6" t="n">
         <v>27</v>
@@ -1599,7 +1599,7 @@
         <v>260</v>
       </c>
       <c r="AB6" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AC6" t="n">
         <v>11.5</v>
@@ -1635,7 +1635,7 @@
         <v>390</v>
       </c>
       <c r="AN6" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AO6" t="n">
         <v>200</v>
@@ -1656,13 +1656,13 @@
         <v>7.4</v>
       </c>
       <c r="AU6" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AV6" t="n">
         <v>14.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>8.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="AX6" t="n">
         <v>7.8</v>
@@ -1674,7 +1674,7 @@
         <v>19</v>
       </c>
       <c r="BA6" t="n">
-        <v>8.6</v>
+        <v>7.4</v>
       </c>
       <c r="BB6" t="n">
         <v>11</v>
@@ -1686,17 +1686,17 @@
         <v>21</v>
       </c>
       <c r="BE6" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BF6" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BG6" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-25 02:09:31</t>
+          <t>2026-03-25 04:14:47</t>
         </is>
       </c>
     </row>
@@ -1727,127 +1727,127 @@
         </is>
       </c>
       <c r="F7" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="G7" t="n">
         <v>2.7</v>
       </c>
-      <c r="G7" t="n">
-        <v>2.98</v>
-      </c>
       <c r="H7" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="I7" t="n">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="J7" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="K7" t="n">
         <v>3.25</v>
       </c>
       <c r="L7" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="M7" t="n">
         <v>1.13</v>
       </c>
       <c r="N7" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="O7" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="P7" t="n">
         <v>1.49</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="R7" t="n">
         <v>1.18</v>
       </c>
       <c r="S7" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="T7" t="n">
         <v>2.08</v>
       </c>
       <c r="U7" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="V7" t="n">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="W7" t="n">
-        <v>1.51</v>
+        <v>1.59</v>
       </c>
       <c r="X7" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="Y7" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AA7" t="n">
-        <v>60</v>
+        <v>170</v>
       </c>
       <c r="AB7" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="AC7" t="n">
         <v>7.2</v>
       </c>
       <c r="AD7" t="n">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="AE7" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="AF7" t="n">
-        <v>22</v>
+        <v>16.5</v>
       </c>
       <c r="AG7" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AI7" t="n">
+        <v>500</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>46</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>42</v>
+      </c>
+      <c r="AL7" t="n">
         <v>190</v>
       </c>
-      <c r="AJ7" t="n">
-        <v>60</v>
-      </c>
-      <c r="AK7" t="n">
+      <c r="AM7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN7" t="n">
         <v>48</v>
       </c>
-      <c r="AL7" t="n">
-        <v>230</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>60</v>
-      </c>
       <c r="AO7" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>7</v>
+        <v>4.3</v>
       </c>
       <c r="AQ7" t="n">
-        <v>7.4</v>
+        <v>4.8</v>
       </c>
       <c r="AR7" t="n">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="AS7" t="n">
         <v>8.6</v>
       </c>
       <c r="AT7" t="n">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="AU7" t="n">
         <v>5.8</v>
@@ -1856,41 +1856,41 @@
         <v>12</v>
       </c>
       <c r="AW7" t="n">
-        <v>15</v>
+        <v>8.6</v>
       </c>
       <c r="AX7" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AY7" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="AZ7" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BB7" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BC7" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BD7" t="n">
         <v>7.8</v>
       </c>
       <c r="BE7" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BF7" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BG7" t="n">
         <v>7.8</v>
       </c>
-      <c r="BG7" t="n">
-        <v>7.6</v>
-      </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-25 02:09:31</t>
+          <t>2026-03-25 04:14:47</t>
         </is>
       </c>
     </row>
@@ -1921,25 +1921,25 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="G8" t="n">
-        <v>1.8</v>
+        <v>1.68</v>
       </c>
       <c r="H8" t="n">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="I8" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="J8" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="K8" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="L8" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="M8" t="n">
         <v>1.08</v>
@@ -1948,37 +1948,37 @@
         <v>3.2</v>
       </c>
       <c r="O8" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="P8" t="n">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="R8" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="S8" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="T8" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="U8" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="V8" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="W8" t="n">
-        <v>2.24</v>
+        <v>2.46</v>
       </c>
       <c r="X8" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="Y8" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="Z8" t="n">
         <v>1000</v>
@@ -1987,104 +1987,104 @@
         <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AC8" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF8" t="n">
         <v>9</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>75</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>9.800000000000001</v>
       </c>
       <c r="AG8" t="n">
         <v>10.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="AI8" t="n">
         <v>1000</v>
       </c>
       <c r="AJ8" t="n">
-        <v>18</v>
+        <v>180</v>
       </c>
       <c r="AK8" t="n">
+        <v>65</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>12</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>10</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>11</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AZ8" t="n">
         <v>21</v>
       </c>
-      <c r="AL8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>14</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>9</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>10</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>21</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>5</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>7.4</v>
-      </c>
       <c r="BA8" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="BB8" t="n">
-        <v>6.6</v>
+        <v>13</v>
       </c>
       <c r="BC8" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BD8" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="BE8" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="BF8" t="n">
-        <v>9.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BG8" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-25 02:09:31</t>
+          <t>2026-03-25 04:14:47</t>
         </is>
       </c>
     </row>
@@ -2115,19 +2115,19 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="G9" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="H9" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="I9" t="n">
         <v>5</v>
       </c>
       <c r="J9" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K9" t="n">
         <v>3.6</v>
@@ -2142,13 +2142,13 @@
         <v>3</v>
       </c>
       <c r="O9" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="P9" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="R9" t="n">
         <v>1.25</v>
@@ -2157,22 +2157,22 @@
         <v>4.2</v>
       </c>
       <c r="T9" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="U9" t="n">
         <v>1.86</v>
       </c>
       <c r="V9" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="W9" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="X9" t="n">
         <v>21</v>
       </c>
       <c r="Y9" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z9" t="n">
         <v>1000</v>
@@ -2181,10 +2181,10 @@
         <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>27</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC9" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="AD9" t="n">
         <v>1000</v>
@@ -2193,19 +2193,19 @@
         <v>1000</v>
       </c>
       <c r="AF9" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AG9" t="n">
         <v>36</v>
       </c>
       <c r="AH9" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AI9" t="n">
         <v>1000</v>
       </c>
       <c r="AJ9" t="n">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="AK9" t="n">
         <v>1000</v>
@@ -2223,62 +2223,62 @@
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AQ9" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AR9" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="AS9" t="n">
-        <v>6.6</v>
+        <v>4.8</v>
       </c>
       <c r="AT9" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AU9" t="n">
         <v>6.2</v>
       </c>
       <c r="AV9" t="n">
-        <v>12</v>
+        <v>5.4</v>
       </c>
       <c r="AW9" t="n">
-        <v>6.2</v>
+        <v>4.9</v>
       </c>
       <c r="AX9" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="AY9" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AZ9" t="n">
         <v>6.4</v>
       </c>
       <c r="BA9" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BB9" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD9" t="n">
         <v>6.8</v>
       </c>
-      <c r="BC9" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>6.2</v>
-      </c>
       <c r="BE9" t="n">
-        <v>6.6</v>
+        <v>4.9</v>
       </c>
       <c r="BF9" t="n">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="BG9" t="n">
-        <v>6.4</v>
+        <v>4.8</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-25 02:09:31</t>
+          <t>2026-03-25 04:14:47</t>
         </is>
       </c>
     </row>
@@ -2309,40 +2309,40 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="G10" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="H10" t="n">
         <v>3.1</v>
       </c>
-      <c r="H10" t="n">
-        <v>3.3</v>
-      </c>
       <c r="I10" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="J10" t="n">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="K10" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="L10" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="M10" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="N10" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="O10" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="P10" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="R10" t="n">
         <v>1.13</v>
@@ -2351,25 +2351,25 @@
         <v>7.2</v>
       </c>
       <c r="T10" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="U10" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="V10" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="W10" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="X10" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="Y10" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="Z10" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AA10" t="n">
         <v>1000</v>
@@ -2378,19 +2378,19 @@
         <v>9</v>
       </c>
       <c r="AC10" t="n">
-        <v>8.199999999999999</v>
+        <v>6.8</v>
       </c>
       <c r="AD10" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AE10" t="n">
         <v>1000</v>
       </c>
       <c r="AF10" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="AG10" t="n">
-        <v>15.5</v>
+        <v>18.5</v>
       </c>
       <c r="AH10" t="n">
         <v>75</v>
@@ -2402,10 +2402,10 @@
         <v>1000</v>
       </c>
       <c r="AK10" t="n">
-        <v>1000</v>
+        <v>290</v>
       </c>
       <c r="AL10" t="n">
-        <v>540</v>
+        <v>500</v>
       </c>
       <c r="AM10" t="n">
         <v>1000</v>
@@ -2417,10 +2417,10 @@
         <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="AQ10" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AR10" t="n">
         <v>17</v>
@@ -2429,50 +2429,50 @@
         <v>20</v>
       </c>
       <c r="AT10" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AU10" t="n">
-        <v>5.9</v>
+        <v>5.6</v>
       </c>
       <c r="AV10" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AW10" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>21</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BB10" t="n">
         <v>6.6</v>
       </c>
-      <c r="AX10" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AZ10" t="n">
+      <c r="BC10" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BG10" t="n">
         <v>16.5</v>
       </c>
-      <c r="BA10" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>18</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>10</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>6.4</v>
-      </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-25 02:09:31</t>
+          <t>2026-03-25 04:14:47</t>
         </is>
       </c>
     </row>
@@ -2527,7 +2527,7 @@
         <v>1.13</v>
       </c>
       <c r="N11" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="O11" t="n">
         <v>1.57</v>
@@ -2548,7 +2548,7 @@
         <v>2.14</v>
       </c>
       <c r="U11" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="V11" t="n">
         <v>1.4</v>
@@ -2569,7 +2569,7 @@
         <v>900</v>
       </c>
       <c r="AB11" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="AC11" t="n">
         <v>7.2</v>
@@ -2581,7 +2581,7 @@
         <v>290</v>
       </c>
       <c r="AF11" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AG11" t="n">
         <v>970</v>
@@ -2596,7 +2596,7 @@
         <v>900</v>
       </c>
       <c r="AK11" t="n">
-        <v>140</v>
+        <v>500</v>
       </c>
       <c r="AL11" t="n">
         <v>1000</v>
@@ -2611,19 +2611,19 @@
         <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AQ11" t="n">
         <v>8</v>
       </c>
       <c r="AR11" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS11" t="n">
-        <v>10.5</v>
+        <v>23</v>
       </c>
       <c r="AT11" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AU11" t="n">
         <v>6.2</v>
@@ -2632,7 +2632,7 @@
         <v>9</v>
       </c>
       <c r="AW11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AX11" t="n">
         <v>7.8</v>
@@ -2644,29 +2644,29 @@
         <v>11.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB11" t="n">
-        <v>16.5</v>
+        <v>21</v>
       </c>
       <c r="BC11" t="n">
-        <v>10.5</v>
+        <v>16</v>
       </c>
       <c r="BD11" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BE11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BF11" t="n">
         <v>34</v>
       </c>
       <c r="BG11" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-25 02:09:31</t>
+          <t>2026-03-25 04:14:47</t>
         </is>
       </c>
     </row>
@@ -2697,22 +2697,22 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="G12" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="H12" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="I12" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="J12" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K12" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="L12" t="n">
         <v>1.6</v>
@@ -2721,7 +2721,7 @@
         <v>1.13</v>
       </c>
       <c r="N12" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="O12" t="n">
         <v>1.55</v>
@@ -2736,10 +2736,10 @@
         <v>1.18</v>
       </c>
       <c r="S12" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="T12" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="U12" t="n">
         <v>1.66</v>
@@ -2748,7 +2748,7 @@
         <v>1.21</v>
       </c>
       <c r="W12" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="X12" t="n">
         <v>8.800000000000001</v>
@@ -2763,19 +2763,19 @@
         <v>1000</v>
       </c>
       <c r="AB12" t="n">
-        <v>11</v>
+        <v>6.4</v>
       </c>
       <c r="AC12" t="n">
         <v>14</v>
       </c>
       <c r="AD12" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE12" t="n">
         <v>1000</v>
       </c>
       <c r="AF12" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="AG12" t="n">
         <v>27</v>
@@ -2805,62 +2805,62 @@
         <v>1000</v>
       </c>
       <c r="AP12" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="AQ12" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AR12" t="n">
         <v>14.5</v>
       </c>
       <c r="AS12" t="n">
-        <v>5.1</v>
+        <v>10.5</v>
       </c>
       <c r="AT12" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="AU12" t="n">
         <v>6.6</v>
       </c>
       <c r="AV12" t="n">
-        <v>6.6</v>
+        <v>11.5</v>
       </c>
       <c r="AW12" t="n">
-        <v>8.800000000000001</v>
+        <v>5.4</v>
       </c>
       <c r="AX12" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AY12" t="n">
-        <v>8.4</v>
+        <v>7.2</v>
       </c>
       <c r="AZ12" t="n">
-        <v>7</v>
+        <v>14.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>3.25</v>
+        <v>3.9</v>
       </c>
       <c r="BB12" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BC12" t="n">
         <v>13</v>
       </c>
       <c r="BD12" t="n">
+        <v>44</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BF12" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="BE12" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>7</v>
-      </c>
       <c r="BG12" t="n">
-        <v>4</v>
+        <v>9.6</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-25 02:09:31</t>
+          <t>2026-03-25 04:14:47</t>
         </is>
       </c>
     </row>
@@ -2891,19 +2891,19 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="G13" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="H13" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="I13" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="J13" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K13" t="n">
         <v>3.9</v>
@@ -2933,19 +2933,19 @@
         <v>2.84</v>
       </c>
       <c r="T13" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="U13" t="n">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="V13" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="W13" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="X13" t="n">
-        <v>38</v>
+        <v>90</v>
       </c>
       <c r="Y13" t="n">
         <v>970</v>
@@ -2957,7 +2957,7 @@
         <v>120</v>
       </c>
       <c r="AB13" t="n">
-        <v>970</v>
+        <v>29</v>
       </c>
       <c r="AC13" t="n">
         <v>12</v>
@@ -2996,65 +2996,65 @@
         <v>500</v>
       </c>
       <c r="AO13" t="n">
-        <v>55</v>
+        <v>15.5</v>
       </c>
       <c r="AP13" t="n">
-        <v>14</v>
+        <v>10.5</v>
       </c>
       <c r="AQ13" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AR13" t="n">
         <v>13</v>
       </c>
       <c r="AS13" t="n">
-        <v>7.2</v>
+        <v>14.5</v>
       </c>
       <c r="AT13" t="n">
         <v>8.4</v>
       </c>
       <c r="AU13" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AV13" t="n">
         <v>6.2</v>
       </c>
       <c r="AW13" t="n">
-        <v>16.5</v>
+        <v>10.5</v>
       </c>
       <c r="AX13" t="n">
-        <v>17.5</v>
+        <v>11.5</v>
       </c>
       <c r="AY13" t="n">
-        <v>10.5</v>
+        <v>7.6</v>
       </c>
       <c r="AZ13" t="n">
         <v>8.4</v>
       </c>
       <c r="BA13" t="n">
-        <v>7.2</v>
+        <v>26</v>
       </c>
       <c r="BB13" t="n">
-        <v>23</v>
+        <v>8.4</v>
       </c>
       <c r="BC13" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BF13" t="n">
         <v>7.4</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>28</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>19</v>
       </c>
       <c r="BG13" t="n">
         <v>11.5</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-25 02:09:31</t>
+          <t>2026-03-25 04:14:47</t>
         </is>
       </c>
     </row>
@@ -3085,19 +3085,19 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="G14" t="n">
         <v>2.86</v>
       </c>
       <c r="H14" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="I14" t="n">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="J14" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K14" t="n">
         <v>3.65</v>
@@ -3127,13 +3127,13 @@
         <v>3.2</v>
       </c>
       <c r="T14" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="U14" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="V14" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="W14" t="n">
         <v>1.53</v>
@@ -3142,7 +3142,7 @@
         <v>17</v>
       </c>
       <c r="Y14" t="n">
-        <v>13</v>
+        <v>970</v>
       </c>
       <c r="Z14" t="n">
         <v>38</v>
@@ -3151,7 +3151,7 @@
         <v>130</v>
       </c>
       <c r="AB14" t="n">
-        <v>970</v>
+        <v>20</v>
       </c>
       <c r="AC14" t="n">
         <v>8.199999999999999</v>
@@ -3190,10 +3190,10 @@
         <v>1000</v>
       </c>
       <c r="AO14" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="AP14" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AQ14" t="n">
         <v>11</v>
@@ -3202,7 +3202,7 @@
         <v>16.5</v>
       </c>
       <c r="AS14" t="n">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="AT14" t="n">
         <v>11.5</v>
@@ -3214,7 +3214,7 @@
         <v>11</v>
       </c>
       <c r="AW14" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="AX14" t="n">
         <v>10.5</v>
@@ -3226,29 +3226,29 @@
         <v>9</v>
       </c>
       <c r="BA14" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="BB14" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="BC14" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BD14" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="BE14" t="n">
-        <v>9.800000000000001</v>
+        <v>13</v>
       </c>
       <c r="BF14" t="n">
-        <v>7.4</v>
+        <v>9</v>
       </c>
       <c r="BG14" t="n">
         <v>17.5</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-25 02:09:31</t>
+          <t>2026-03-25 04:14:47</t>
         </is>
       </c>
     </row>
@@ -3282,19 +3282,19 @@
         <v>3.65</v>
       </c>
       <c r="G15" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="H15" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="I15" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="J15" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="K15" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="L15" t="n">
         <v>1.37</v>
@@ -3309,34 +3309,34 @@
         <v>1.27</v>
       </c>
       <c r="P15" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="R15" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S15" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="T15" t="n">
-        <v>1.74</v>
+        <v>1.69</v>
       </c>
       <c r="U15" t="n">
-        <v>2.24</v>
+        <v>2.38</v>
       </c>
       <c r="V15" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="W15" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="X15" t="n">
         <v>18.5</v>
       </c>
       <c r="Y15" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Z15" t="n">
         <v>14.5</v>
@@ -3360,7 +3360,7 @@
         <v>28</v>
       </c>
       <c r="AG15" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AH15" t="n">
         <v>17</v>
@@ -3369,7 +3369,7 @@
         <v>34</v>
       </c>
       <c r="AJ15" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AK15" t="n">
         <v>42</v>
@@ -3378,16 +3378,16 @@
         <v>120</v>
       </c>
       <c r="AM15" t="n">
-        <v>85</v>
+        <v>320</v>
       </c>
       <c r="AN15" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AO15" t="n">
+        <v>15</v>
+      </c>
+      <c r="AP15" t="n">
         <v>14.5</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>12.5</v>
       </c>
       <c r="AQ15" t="n">
         <v>9.199999999999999</v>
@@ -3396,10 +3396,10 @@
         <v>12.5</v>
       </c>
       <c r="AS15" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AT15" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AU15" t="n">
         <v>7.4</v>
@@ -3411,16 +3411,16 @@
         <v>18</v>
       </c>
       <c r="AX15" t="n">
+        <v>16</v>
+      </c>
+      <c r="AY15" t="n">
         <v>13</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>11.5</v>
       </c>
       <c r="AZ15" t="n">
         <v>14</v>
       </c>
       <c r="BA15" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BB15" t="n">
         <v>50</v>
@@ -3432,17 +3432,17 @@
         <v>36</v>
       </c>
       <c r="BE15" t="n">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="BF15" t="n">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="BG15" t="n">
         <v>11</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-25 02:09:31</t>
+          <t>2026-03-25 04:14:47</t>
         </is>
       </c>
     </row>
@@ -3473,7 +3473,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="G16" t="n">
         <v>3.8</v>
@@ -3482,13 +3482,13 @@
         <v>2.12</v>
       </c>
       <c r="I16" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="J16" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="K16" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L16" t="n">
         <v>1.33</v>
@@ -3518,22 +3518,22 @@
         <v>1.58</v>
       </c>
       <c r="U16" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="V16" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="W16" t="n">
         <v>1.36</v>
       </c>
       <c r="X16" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Y16" t="n">
         <v>13.5</v>
       </c>
       <c r="Z16" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AA16" t="n">
         <v>27</v>
@@ -3542,7 +3542,7 @@
         <v>19</v>
       </c>
       <c r="AC16" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD16" t="n">
         <v>11.5</v>
@@ -3557,10 +3557,10 @@
         <v>16</v>
       </c>
       <c r="AH16" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AI16" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AJ16" t="n">
         <v>150</v>
@@ -3575,19 +3575,19 @@
         <v>70</v>
       </c>
       <c r="AN16" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AO16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AP16" t="n">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="AQ16" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="AR16" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AS16" t="n">
         <v>21</v>
@@ -3596,47 +3596,47 @@
         <v>16</v>
       </c>
       <c r="AU16" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AV16" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW16" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AX16" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AY16" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AZ16" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BA16" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="BB16" t="n">
-        <v>44</v>
+        <v>9.6</v>
       </c>
       <c r="BC16" t="n">
         <v>30</v>
       </c>
       <c r="BD16" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="BE16" t="n">
         <v>50</v>
       </c>
       <c r="BF16" t="n">
-        <v>8.6</v>
+        <v>24</v>
       </c>
       <c r="BG16" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-25 02:09:31</t>
+          <t>2026-03-25 04:14:47</t>
         </is>
       </c>
     </row>
@@ -3667,7 +3667,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="G17" t="n">
         <v>1.71</v>
@@ -3691,16 +3691,16 @@
         <v>1.05</v>
       </c>
       <c r="N17" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="O17" t="n">
         <v>1.27</v>
       </c>
       <c r="P17" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="R17" t="n">
         <v>1.42</v>
@@ -3709,7 +3709,7 @@
         <v>3.1</v>
       </c>
       <c r="T17" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="U17" t="n">
         <v>2.02</v>
@@ -3721,10 +3721,10 @@
         <v>2.42</v>
       </c>
       <c r="X17" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Y17" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Z17" t="n">
         <v>220</v>
@@ -3736,10 +3736,10 @@
         <v>9.6</v>
       </c>
       <c r="AC17" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AD17" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AE17" t="n">
         <v>400</v>
@@ -3748,16 +3748,16 @@
         <v>11</v>
       </c>
       <c r="AG17" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH17" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AI17" t="n">
         <v>320</v>
       </c>
       <c r="AJ17" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AK17" t="n">
         <v>17.5</v>
@@ -3769,7 +3769,7 @@
         <v>580</v>
       </c>
       <c r="AN17" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AO17" t="n">
         <v>310</v>
@@ -3781,10 +3781,10 @@
         <v>17.5</v>
       </c>
       <c r="AR17" t="n">
-        <v>8.199999999999999</v>
+        <v>20</v>
       </c>
       <c r="AS17" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AT17" t="n">
         <v>8</v>
@@ -3820,17 +3820,17 @@
         <v>25</v>
       </c>
       <c r="BE17" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BF17" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BG17" t="n">
         <v>13.5</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-25 02:09:31</t>
+          <t>2026-03-25 04:14:47</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="G18" t="n">
         <v>2.06</v>
@@ -3870,13 +3870,13 @@
         <v>4.1</v>
       </c>
       <c r="I18" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="J18" t="n">
         <v>3.55</v>
       </c>
       <c r="K18" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L18" t="n">
         <v>1.44</v>
@@ -3885,22 +3885,22 @@
         <v>1.07</v>
       </c>
       <c r="N18" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="O18" t="n">
         <v>1.34</v>
       </c>
       <c r="P18" t="n">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="R18" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="S18" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="T18" t="n">
         <v>1.85</v>
@@ -3909,7 +3909,7 @@
         <v>2.04</v>
       </c>
       <c r="V18" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W18" t="n">
         <v>1.95</v>
@@ -3918,19 +3918,19 @@
         <v>15</v>
       </c>
       <c r="Y18" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Z18" t="n">
         <v>32</v>
       </c>
       <c r="AA18" t="n">
-        <v>900</v>
+        <v>95</v>
       </c>
       <c r="AB18" t="n">
         <v>9.6</v>
       </c>
       <c r="AC18" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD18" t="n">
         <v>17.5</v>
@@ -3939,7 +3939,7 @@
         <v>55</v>
       </c>
       <c r="AF18" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AG18" t="n">
         <v>10.5</v>
@@ -3951,16 +3951,16 @@
         <v>65</v>
       </c>
       <c r="AJ18" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AK18" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL18" t="n">
         <v>38</v>
       </c>
       <c r="AM18" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AN18" t="n">
         <v>16.5</v>
@@ -3972,25 +3972,25 @@
         <v>12</v>
       </c>
       <c r="AQ18" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AR18" t="n">
         <v>27</v>
       </c>
       <c r="AS18" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="AT18" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU18" t="n">
         <v>7.2</v>
       </c>
       <c r="AV18" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AW18" t="n">
-        <v>12.5</v>
+        <v>44</v>
       </c>
       <c r="AX18" t="n">
         <v>10.5</v>
@@ -4002,7 +4002,7 @@
         <v>17</v>
       </c>
       <c r="BA18" t="n">
-        <v>11.5</v>
+        <v>28</v>
       </c>
       <c r="BB18" t="n">
         <v>21</v>
@@ -4014,17 +4014,17 @@
         <v>32</v>
       </c>
       <c r="BE18" t="n">
-        <v>11.5</v>
+        <v>14.5</v>
       </c>
       <c r="BF18" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BG18" t="n">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-25 02:09:31</t>
+          <t>2026-03-25 04:14:47</t>
         </is>
       </c>
     </row>
@@ -4073,40 +4073,40 @@
         <v>4.5</v>
       </c>
       <c r="L19" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="M19" t="n">
         <v>1.08</v>
       </c>
       <c r="N19" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="O19" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="P19" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="R19" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="S19" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="T19" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="U19" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="V19" t="n">
         <v>1.11</v>
       </c>
       <c r="W19" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="X19" t="n">
         <v>970</v>
@@ -4157,7 +4157,7 @@
         <v>1000</v>
       </c>
       <c r="AN19" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="AO19" t="n">
         <v>1000</v>
@@ -4166,7 +4166,7 @@
         <v>5.7</v>
       </c>
       <c r="AQ19" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AR19" t="n">
         <v>4.2</v>
@@ -4175,13 +4175,13 @@
         <v>4.2</v>
       </c>
       <c r="AT19" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AU19" t="n">
         <v>6.2</v>
       </c>
       <c r="AV19" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AW19" t="n">
         <v>4.2</v>
@@ -4190,35 +4190,35 @@
         <v>6.4</v>
       </c>
       <c r="AY19" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AZ19" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BA19" t="n">
         <v>4.2</v>
       </c>
       <c r="BB19" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BC19" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BD19" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="BE19" t="n">
         <v>2.96</v>
       </c>
       <c r="BF19" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BG19" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-25 02:09:31</t>
+          <t>2026-03-25 04:14:47</t>
         </is>
       </c>
     </row>
@@ -4252,16 +4252,16 @@
         <v>3.15</v>
       </c>
       <c r="G20" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="H20" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="I20" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="J20" t="n">
         <v>2.9</v>
-      </c>
-      <c r="J20" t="n">
-        <v>2.92</v>
       </c>
       <c r="K20" t="n">
         <v>3.1</v>
@@ -4276,7 +4276,7 @@
         <v>2.66</v>
       </c>
       <c r="O20" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="P20" t="n">
         <v>1.53</v>
@@ -4300,7 +4300,7 @@
         <v>1.53</v>
       </c>
       <c r="W20" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="X20" t="n">
         <v>8.4</v>
@@ -4324,7 +4324,7 @@
         <v>17.5</v>
       </c>
       <c r="AE20" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AF20" t="n">
         <v>20</v>
@@ -4333,7 +4333,7 @@
         <v>19</v>
       </c>
       <c r="AH20" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AI20" t="n">
         <v>500</v>
@@ -4342,7 +4342,7 @@
         <v>900</v>
       </c>
       <c r="AK20" t="n">
-        <v>500</v>
+        <v>120</v>
       </c>
       <c r="AL20" t="n">
         <v>500</v>
@@ -4366,7 +4366,7 @@
         <v>12</v>
       </c>
       <c r="AS20" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="AT20" t="n">
         <v>8</v>
@@ -4387,7 +4387,7 @@
         <v>13</v>
       </c>
       <c r="AZ20" t="n">
-        <v>20</v>
+        <v>16.5</v>
       </c>
       <c r="BA20" t="n">
         <v>34</v>
@@ -4396,7 +4396,7 @@
         <v>29</v>
       </c>
       <c r="BC20" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BD20" t="n">
         <v>36</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-25 02:09:31</t>
+          <t>2026-03-25 04:14:47</t>
         </is>
       </c>
     </row>
@@ -4443,10 +4443,10 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="G21" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="H21" t="n">
         <v>3.75</v>
@@ -4455,91 +4455,91 @@
         <v>3.9</v>
       </c>
       <c r="J21" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="K21" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="L21" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="M21" t="n">
         <v>1.22</v>
       </c>
       <c r="N21" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="O21" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="P21" t="n">
         <v>1.3</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="R21" t="n">
         <v>1.09</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="T21" t="n">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="U21" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="V21" t="n">
         <v>1.34</v>
       </c>
       <c r="W21" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="X21" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="Y21" t="n">
         <v>8</v>
       </c>
       <c r="Z21" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AA21" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AB21" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="AC21" t="n">
         <v>7.6</v>
       </c>
       <c r="AD21" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE21" t="n">
         <v>110</v>
       </c>
       <c r="AF21" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AG21" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AH21" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AI21" t="n">
         <v>200</v>
       </c>
       <c r="AJ21" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AK21" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AL21" t="n">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="AM21" t="n">
         <v>500</v>
@@ -4551,7 +4551,7 @@
         <v>210</v>
       </c>
       <c r="AP21" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AQ21" t="n">
         <v>7.2</v>
@@ -4563,7 +4563,7 @@
         <v>44</v>
       </c>
       <c r="AT21" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="AU21" t="n">
         <v>6.6</v>
@@ -4584,16 +4584,16 @@
         <v>24</v>
       </c>
       <c r="BA21" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="BB21" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BC21" t="n">
         <v>29</v>
       </c>
       <c r="BD21" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="BE21" t="n">
         <v>120</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-25 02:09:31</t>
+          <t>2026-03-25 04:14:47</t>
         </is>
       </c>
     </row>
@@ -4652,37 +4652,37 @@
         <v>3.35</v>
       </c>
       <c r="K22" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="L22" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="M22" t="n">
         <v>1.09</v>
       </c>
       <c r="N22" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="O22" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="P22" t="n">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="R22" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="S22" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="T22" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="U22" t="n">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="V22" t="n">
         <v>1.25</v>
@@ -4691,116 +4691,116 @@
         <v>1.94</v>
       </c>
       <c r="X22" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="Y22" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="Z22" t="n">
         <v>36</v>
       </c>
       <c r="AA22" t="n">
-        <v>130</v>
+        <v>900</v>
       </c>
       <c r="AB22" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC22" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AD22" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AE22" t="n">
-        <v>75</v>
+        <v>170</v>
       </c>
       <c r="AF22" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AG22" t="n">
         <v>11</v>
       </c>
       <c r="AH22" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>90</v>
+      </c>
+      <c r="AJ22" t="n">
         <v>25</v>
       </c>
-      <c r="AI22" t="n">
-        <v>85</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>29</v>
-      </c>
       <c r="AK22" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AL22" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AM22" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN22" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AO22" t="n">
-        <v>290</v>
+        <v>95</v>
       </c>
       <c r="AP22" t="n">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="AQ22" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AR22" t="n">
         <v>13</v>
       </c>
       <c r="AS22" t="n">
+        <v>9</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU22" t="n">
         <v>6.8</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>6.6</v>
       </c>
       <c r="AV22" t="n">
         <v>13.5</v>
       </c>
       <c r="AW22" t="n">
-        <v>6.6</v>
+        <v>8.6</v>
       </c>
       <c r="AX22" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA22" t="n">
         <v>8.6</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>6.6</v>
       </c>
       <c r="BB22" t="n">
         <v>20</v>
       </c>
       <c r="BC22" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BD22" t="n">
-        <v>6.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE22" t="n">
-        <v>6.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF22" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BG22" t="n">
-        <v>6.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-25 02:09:31</t>
+          <t>2026-03-25 04:14:47</t>
         </is>
       </c>
     </row>
@@ -4827,7 +4827,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Club 2 de Mayo</t>
+          <t>Club 2 de Mayo de Pedro Juan Cab</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -4837,16 +4837,16 @@
         <v>2.06</v>
       </c>
       <c r="H23" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="I23" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J23" t="n">
         <v>3.5</v>
       </c>
       <c r="K23" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="L23" t="n">
         <v>1.5</v>
@@ -4873,7 +4873,7 @@
         <v>4.4</v>
       </c>
       <c r="T23" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="U23" t="n">
         <v>1.87</v>
@@ -4897,7 +4897,7 @@
         <v>1000</v>
       </c>
       <c r="AB23" t="n">
-        <v>18.5</v>
+        <v>7.8</v>
       </c>
       <c r="AC23" t="n">
         <v>9.199999999999999</v>
@@ -4942,13 +4942,13 @@
         <v>5.8</v>
       </c>
       <c r="AQ23" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AR23" t="n">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="AS23" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="AT23" t="n">
         <v>6.6</v>
@@ -4960,41 +4960,41 @@
         <v>16</v>
       </c>
       <c r="AW23" t="n">
-        <v>2.62</v>
+        <v>3.15</v>
       </c>
       <c r="AX23" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="AY23" t="n">
-        <v>5.6</v>
+        <v>9.4</v>
       </c>
       <c r="AZ23" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BC23" t="n">
         <v>7.6</v>
       </c>
-      <c r="BA23" t="n">
+      <c r="BD23" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BE23" t="n">
         <v>10</v>
       </c>
-      <c r="BB23" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BC23" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BD23" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="BE23" t="n">
-        <v>11</v>
-      </c>
       <c r="BF23" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BG23" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-25 02:09:31</t>
+          <t>2026-03-25 04:14:47</t>
         </is>
       </c>
     </row>
@@ -5025,13 +5025,13 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="G24" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="H24" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="I24" t="n">
         <v>9</v>
@@ -5055,7 +5055,7 @@
         <v>1.37</v>
       </c>
       <c r="P24" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="Q24" t="n">
         <v>2.14</v>
@@ -5076,7 +5076,7 @@
         <v>1.13</v>
       </c>
       <c r="W24" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="X24" t="n">
         <v>1000</v>
@@ -5133,7 +5133,7 @@
         <v>1000</v>
       </c>
       <c r="AP24" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AQ24" t="n">
         <v>4.2</v>
@@ -5163,22 +5163,22 @@
         <v>7.8</v>
       </c>
       <c r="AZ24" t="n">
-        <v>7.6</v>
+        <v>2.12</v>
       </c>
       <c r="BA24" t="n">
         <v>4.2</v>
       </c>
       <c r="BB24" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BC24" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BD24" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="BE24" t="n">
-        <v>3.75</v>
+        <v>3.2</v>
       </c>
       <c r="BF24" t="n">
         <v>8.4</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-25 02:09:31</t>
+          <t>2026-03-25 04:14:47</t>
         </is>
       </c>
     </row>
@@ -5243,19 +5243,19 @@
         <v>1.01</v>
       </c>
       <c r="N25" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="O25" t="n">
         <v>1.23</v>
       </c>
       <c r="P25" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="Q25" t="n">
         <v>1.23</v>
       </c>
       <c r="R25" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="S25" t="n">
         <v>1.66</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-25 02:09:31</t>
+          <t>2026-03-25 04:14:47</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="G26" t="n">
         <v>1.69</v>
@@ -5422,13 +5422,13 @@
         <v>5.5</v>
       </c>
       <c r="I26" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="J26" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="K26" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L26" t="n">
         <v>1.38</v>
@@ -5437,22 +5437,22 @@
         <v>1.06</v>
       </c>
       <c r="N26" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O26" t="n">
         <v>1.28</v>
       </c>
       <c r="P26" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="R26" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="S26" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="T26" t="n">
         <v>1.79</v>
@@ -5503,10 +5503,10 @@
         <v>700</v>
       </c>
       <c r="AJ26" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AK26" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="AL26" t="n">
         <v>150</v>
@@ -5515,7 +5515,7 @@
         <v>580</v>
       </c>
       <c r="AN26" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AO26" t="n">
         <v>700</v>
@@ -5527,7 +5527,7 @@
         <v>17.5</v>
       </c>
       <c r="AR26" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AS26" t="n">
         <v>8.4</v>
@@ -5536,7 +5536,7 @@
         <v>8</v>
       </c>
       <c r="AU26" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV26" t="n">
         <v>17</v>
@@ -5572,11 +5572,11 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BG26" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-25 02:09:31</t>
+          <t>2026-03-25 04:14:47</t>
         </is>
       </c>
     </row>
@@ -5607,16 +5607,16 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="G27" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="H27" t="n">
-        <v>2.86</v>
+        <v>2.78</v>
       </c>
       <c r="I27" t="n">
-        <v>2.98</v>
+        <v>2.92</v>
       </c>
       <c r="J27" t="n">
         <v>3.6</v>
@@ -5631,7 +5631,7 @@
         <v>1.06</v>
       </c>
       <c r="N27" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O27" t="n">
         <v>1.28</v>
@@ -5640,7 +5640,7 @@
         <v>2.1</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="R27" t="n">
         <v>1.4</v>
@@ -5649,37 +5649,37 @@
         <v>3.2</v>
       </c>
       <c r="T27" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="U27" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="V27" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="W27" t="n">
         <v>1.6</v>
       </c>
       <c r="X27" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="Y27" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="Z27" t="n">
         <v>38</v>
       </c>
       <c r="AA27" t="n">
-        <v>120</v>
+        <v>900</v>
       </c>
       <c r="AB27" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AC27" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AD27" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AE27" t="n">
         <v>85</v>
@@ -5691,16 +5691,16 @@
         <v>12</v>
       </c>
       <c r="AH27" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AI27" t="n">
         <v>120</v>
       </c>
       <c r="AJ27" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AK27" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AL27" t="n">
         <v>95</v>
@@ -5709,43 +5709,43 @@
         <v>580</v>
       </c>
       <c r="AN27" t="n">
-        <v>19.5</v>
+        <v>44</v>
       </c>
       <c r="AO27" t="n">
         <v>42</v>
       </c>
       <c r="AP27" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="AQ27" t="n">
         <v>10.5</v>
       </c>
       <c r="AR27" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AS27" t="n">
         <v>7.8</v>
       </c>
       <c r="AT27" t="n">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="AU27" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AV27" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AW27" t="n">
         <v>13</v>
       </c>
       <c r="AX27" t="n">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="AY27" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="AZ27" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BA27" t="n">
         <v>7.6</v>
@@ -5754,23 +5754,23 @@
         <v>18</v>
       </c>
       <c r="BC27" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="BD27" t="n">
-        <v>18</v>
+        <v>7.4</v>
       </c>
       <c r="BE27" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BF27" t="n">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="BG27" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-25 02:09:31</t>
+          <t>2026-03-25 04:14:47</t>
         </is>
       </c>
     </row>
@@ -5807,16 +5807,16 @@
         <v>7.4</v>
       </c>
       <c r="H28" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="I28" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="J28" t="n">
         <v>3.7</v>
       </c>
       <c r="K28" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L28" t="n">
         <v>1.5</v>
@@ -5831,7 +5831,7 @@
         <v>1.43</v>
       </c>
       <c r="P28" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="Q28" t="n">
         <v>2.3</v>
@@ -5864,7 +5864,7 @@
         <v>8.4</v>
       </c>
       <c r="AA28" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AB28" t="n">
         <v>19</v>
@@ -5930,7 +5930,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AW28" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AX28" t="n">
         <v>27</v>
@@ -5939,7 +5939,7 @@
         <v>19</v>
       </c>
       <c r="AZ28" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BA28" t="n">
         <v>28</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-25 02:09:31</t>
+          <t>2026-03-25 04:14:47</t>
         </is>
       </c>
     </row>
@@ -6025,7 +6025,7 @@
         <v>1.42</v>
       </c>
       <c r="P29" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="Q29" t="n">
         <v>2.28</v>
@@ -6085,7 +6085,7 @@
         <v>1000</v>
       </c>
       <c r="AJ29" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AK29" t="n">
         <v>20</v>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-25 02:09:31</t>
+          <t>2026-03-25 04:14:47</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-25.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-25.xlsx
@@ -757,52 +757,52 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="G2" t="n">
         <v>4.5</v>
       </c>
       <c r="H2" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="I2" t="n">
         <v>2.06</v>
       </c>
       <c r="J2" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K2" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="L2" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="M2" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N2" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="O2" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="P2" t="n">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="R2" t="n">
         <v>1.31</v>
       </c>
       <c r="S2" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="T2" t="n">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="U2" t="n">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="V2" t="n">
         <v>1.94</v>
@@ -811,116 +811,116 @@
         <v>1.3</v>
       </c>
       <c r="X2" t="n">
-        <v>22</v>
+        <v>13.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>27</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z2" t="n">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="AA2" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AB2" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AC2" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>90</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>26</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>38</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>500</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>500</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>55</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>9</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>10</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>11</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>11</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY2" t="n">
         <v>14</v>
       </c>
-      <c r="AD2" t="n">
-        <v>36</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>85</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AQ2" t="n">
+      <c r="AZ2" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BC2" t="n">
         <v>4.9</v>
       </c>
-      <c r="AR2" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>6</v>
-      </c>
-      <c r="AU2" t="n">
+      <c r="BD2" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BE2" t="n">
         <v>4.9</v>
       </c>
-      <c r="AV2" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>7</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>3</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>2.46</v>
-      </c>
       <c r="BF2" t="n">
-        <v>2.46</v>
+        <v>4.7</v>
       </c>
       <c r="BG2" t="n">
         <v>4</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-25 04:14:47</t>
+          <t>2026-03-25 06:20:07</t>
         </is>
       </c>
     </row>
@@ -957,7 +957,7 @@
         <v>6.8</v>
       </c>
       <c r="H3" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="I3" t="n">
         <v>1.85</v>
@@ -978,13 +978,13 @@
         <v>2.98</v>
       </c>
       <c r="O3" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="P3" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="R3" t="n">
         <v>1.23</v>
@@ -993,10 +993,10 @@
         <v>4.5</v>
       </c>
       <c r="T3" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="U3" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="V3" t="n">
         <v>2.16</v>
@@ -1023,19 +1023,19 @@
         <v>10</v>
       </c>
       <c r="AD3" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AE3" t="n">
         <v>24</v>
       </c>
       <c r="AF3" t="n">
-        <v>75</v>
+        <v>130</v>
       </c>
       <c r="AG3" t="n">
         <v>26</v>
       </c>
       <c r="AH3" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="AI3" t="n">
         <v>150</v>
@@ -1056,34 +1056,34 @@
         <v>700</v>
       </c>
       <c r="AO3" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AP3" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AQ3" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="AR3" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AS3" t="n">
         <v>16</v>
       </c>
       <c r="AT3" t="n">
-        <v>7.6</v>
+        <v>13</v>
       </c>
       <c r="AU3" t="n">
         <v>7.2</v>
       </c>
       <c r="AV3" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW3" t="n">
         <v>19</v>
       </c>
       <c r="AX3" t="n">
-        <v>16</v>
+        <v>6.2</v>
       </c>
       <c r="AY3" t="n">
         <v>9.800000000000001</v>
@@ -1095,26 +1095,26 @@
         <v>28</v>
       </c>
       <c r="BB3" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="BC3" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BE3" t="n">
         <v>6.6</v>
       </c>
-      <c r="BD3" t="n">
-        <v>6</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>6</v>
-      </c>
       <c r="BF3" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BG3" t="n">
         <v>14</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-25 04:14:47</t>
+          <t>2026-03-25 06:20:07</t>
         </is>
       </c>
     </row>
@@ -1145,22 +1145,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="G4" t="n">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="H4" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="I4" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="J4" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K4" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="L4" t="n">
         <v>1.42</v>
@@ -1172,143 +1172,143 @@
         <v>3.5</v>
       </c>
       <c r="O4" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="P4" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="R4" t="n">
         <v>1.33</v>
       </c>
       <c r="S4" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="T4" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="U4" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="V4" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="W4" t="n">
-        <v>1.67</v>
+        <v>1.74</v>
       </c>
       <c r="X4" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Z4" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AA4" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="AB4" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC4" t="n">
         <v>8.4</v>
       </c>
       <c r="AD4" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AE4" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="AF4" t="n">
-        <v>18.5</v>
+        <v>15</v>
       </c>
       <c r="AG4" t="n">
-        <v>14</v>
+        <v>11.5</v>
       </c>
       <c r="AH4" t="n">
         <v>21</v>
       </c>
       <c r="AI4" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AJ4" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AK4" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AL4" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AM4" t="n">
-        <v>440</v>
+        <v>580</v>
       </c>
       <c r="AN4" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AO4" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="AP4" t="n">
         <v>11.5</v>
       </c>
       <c r="AQ4" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AR4" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AS4" t="n">
         <v>18.5</v>
       </c>
       <c r="AT4" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU4" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV4" t="n">
+        <v>13</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AX4" t="n">
         <v>12</v>
       </c>
-      <c r="AW4" t="n">
+      <c r="AY4" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>27</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>22</v>
+      </c>
+      <c r="BC4" t="n">
         <v>20</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>13</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>15</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>23</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>19</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>15.5</v>
       </c>
       <c r="BD4" t="n">
         <v>24</v>
       </c>
       <c r="BE4" t="n">
-        <v>6.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF4" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="BG4" t="n">
-        <v>6.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-25 04:14:47</t>
+          <t>2026-03-25 06:20:07</t>
         </is>
       </c>
     </row>
@@ -1345,13 +1345,13 @@
         <v>1.2</v>
       </c>
       <c r="H5" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="I5" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J5" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="K5" t="n">
         <v>10.5</v>
@@ -1375,19 +1375,19 @@
         <v>1.46</v>
       </c>
       <c r="R5" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="S5" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="T5" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="U5" t="n">
         <v>1.66</v>
       </c>
       <c r="V5" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W5" t="n">
         <v>6</v>
@@ -1459,7 +1459,7 @@
         <v>8.6</v>
       </c>
       <c r="AT5" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU5" t="n">
         <v>17</v>
@@ -1477,32 +1477,32 @@
         <v>11</v>
       </c>
       <c r="AZ5" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BA5" t="n">
         <v>8.4</v>
       </c>
       <c r="BB5" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BC5" t="n">
         <v>12</v>
       </c>
       <c r="BD5" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="BE5" t="n">
         <v>8.4</v>
       </c>
       <c r="BF5" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="BG5" t="n">
         <v>10</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-25 04:14:47</t>
+          <t>2026-03-25 06:20:07</t>
         </is>
       </c>
     </row>
@@ -1533,16 +1533,16 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="G6" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="H6" t="n">
         <v>7</v>
       </c>
       <c r="I6" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J6" t="n">
         <v>4.3</v>
@@ -1560,19 +1560,19 @@
         <v>4.4</v>
       </c>
       <c r="O6" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="P6" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="R6" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="S6" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="T6" t="n">
         <v>1.87</v>
@@ -1581,10 +1581,10 @@
         <v>1.92</v>
       </c>
       <c r="V6" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="W6" t="n">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="X6" t="n">
         <v>21</v>
@@ -1602,7 +1602,7 @@
         <v>9.6</v>
       </c>
       <c r="AC6" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AD6" t="n">
         <v>46</v>
@@ -1647,10 +1647,10 @@
         <v>21</v>
       </c>
       <c r="AR6" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="AS6" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AT6" t="n">
         <v>7.4</v>
@@ -1659,10 +1659,10 @@
         <v>9</v>
       </c>
       <c r="AV6" t="n">
-        <v>14.5</v>
+        <v>17.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="AX6" t="n">
         <v>7.8</v>
@@ -1674,7 +1674,7 @@
         <v>19</v>
       </c>
       <c r="BA6" t="n">
-        <v>7.4</v>
+        <v>16.5</v>
       </c>
       <c r="BB6" t="n">
         <v>11</v>
@@ -1686,17 +1686,17 @@
         <v>21</v>
       </c>
       <c r="BE6" t="n">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="BF6" t="n">
         <v>6</v>
       </c>
       <c r="BG6" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-25 04:14:47</t>
+          <t>2026-03-25 06:20:07</t>
         </is>
       </c>
     </row>
@@ -1727,170 +1727,170 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.46</v>
+        <v>2.12</v>
       </c>
       <c r="G7" t="n">
-        <v>2.7</v>
+        <v>2.28</v>
       </c>
       <c r="H7" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="I7" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J7" t="n">
         <v>3.2</v>
       </c>
-      <c r="I7" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="J7" t="n">
-        <v>2.92</v>
-      </c>
       <c r="K7" t="n">
-        <v>3.25</v>
+        <v>3.8</v>
       </c>
       <c r="L7" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="M7" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="N7" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="O7" t="n">
         <v>1.62</v>
       </c>
       <c r="P7" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.74</v>
+        <v>2.68</v>
       </c>
       <c r="R7" t="n">
         <v>1.18</v>
       </c>
       <c r="S7" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="X7" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>30</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>110</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>80</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>29</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>130</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>32</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>32</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>150</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>22</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>55</v>
+      </c>
+      <c r="AT7" t="n">
         <v>5.7</v>
       </c>
-      <c r="T7" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="X7" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="Z7" t="n">
+      <c r="AU7" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>38</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>22</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>60</v>
+      </c>
+      <c r="BB7" t="n">
         <v>24</v>
       </c>
-      <c r="AA7" t="n">
-        <v>170</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>8</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>65</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>500</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>46</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>42</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>190</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>48</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>12</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>8</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>8</v>
-      </c>
       <c r="BC7" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="BD7" t="n">
-        <v>7.8</v>
+        <v>44</v>
       </c>
       <c r="BE7" t="n">
-        <v>8.4</v>
+        <v>28</v>
       </c>
       <c r="BF7" t="n">
-        <v>7.4</v>
+        <v>24</v>
       </c>
       <c r="BG7" t="n">
-        <v>7.8</v>
+        <v>9.6</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-25 04:14:47</t>
+          <t>2026-03-25 06:20:07</t>
         </is>
       </c>
     </row>
@@ -1921,64 +1921,64 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.56</v>
+        <v>1.68</v>
       </c>
       <c r="G8" t="n">
-        <v>1.68</v>
+        <v>1.76</v>
       </c>
       <c r="H8" t="n">
-        <v>6.8</v>
+        <v>5.9</v>
       </c>
       <c r="I8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J8" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="K8" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="L8" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="M8" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N8" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="O8" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="P8" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.06</v>
+        <v>2.16</v>
       </c>
       <c r="R8" t="n">
         <v>1.29</v>
       </c>
       <c r="S8" t="n">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="T8" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="U8" t="n">
         <v>1.78</v>
       </c>
       <c r="V8" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="W8" t="n">
-        <v>2.46</v>
+        <v>2.28</v>
       </c>
       <c r="X8" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Y8" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="Z8" t="n">
         <v>1000</v>
@@ -1990,31 +1990,31 @@
         <v>7</v>
       </c>
       <c r="AC8" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD8" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AE8" t="n">
         <v>1000</v>
       </c>
       <c r="AF8" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG8" t="n">
         <v>10.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>60</v>
+        <v>26</v>
       </c>
       <c r="AI8" t="n">
         <v>1000</v>
       </c>
       <c r="AJ8" t="n">
-        <v>180</v>
+        <v>19</v>
       </c>
       <c r="AK8" t="n">
-        <v>65</v>
+        <v>22</v>
       </c>
       <c r="AL8" t="n">
         <v>1000</v>
@@ -2023,68 +2023,68 @@
         <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AO8" t="n">
         <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AQ8" t="n">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="AR8" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AS8" t="n">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT8" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AU8" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AV8" t="n">
+        <v>16</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AX8" t="n">
         <v>8.199999999999999</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>11</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>7.6</v>
       </c>
       <c r="AY8" t="n">
         <v>8.6</v>
       </c>
       <c r="AZ8" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BA8" t="n">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="BB8" t="n">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="BC8" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="BD8" t="n">
         <v>9.4</v>
       </c>
       <c r="BE8" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BF8" t="n">
-        <v>8.6</v>
+        <v>12</v>
       </c>
       <c r="BG8" t="n">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-25 04:14:47</t>
+          <t>2026-03-25 06:20:07</t>
         </is>
       </c>
     </row>
@@ -2115,64 +2115,64 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.02</v>
+        <v>2.12</v>
       </c>
       <c r="G9" t="n">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="H9" t="n">
         <v>4.1</v>
       </c>
       <c r="I9" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="J9" t="n">
         <v>3.05</v>
       </c>
       <c r="K9" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="L9" t="n">
         <v>1.5</v>
       </c>
       <c r="M9" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N9" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="O9" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="P9" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="R9" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="S9" t="n">
         <v>4.2</v>
       </c>
       <c r="T9" t="n">
-        <v>1.9</v>
+        <v>1.79</v>
       </c>
       <c r="U9" t="n">
-        <v>1.86</v>
+        <v>1.98</v>
       </c>
       <c r="V9" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="W9" t="n">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="X9" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="Y9" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="Z9" t="n">
         <v>1000</v>
@@ -2181,10 +2181,10 @@
         <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AC9" t="n">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="AD9" t="n">
         <v>1000</v>
@@ -2196,7 +2196,7 @@
         <v>1000</v>
       </c>
       <c r="AG9" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AH9" t="n">
         <v>1000</v>
@@ -2205,7 +2205,7 @@
         <v>1000</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK9" t="n">
         <v>1000</v>
@@ -2223,62 +2223,62 @@
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="AQ9" t="n">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="AR9" t="n">
-        <v>6.2</v>
+        <v>1.99</v>
       </c>
       <c r="AS9" t="n">
-        <v>4.8</v>
+        <v>2.06</v>
       </c>
       <c r="AT9" t="n">
-        <v>6.4</v>
+        <v>3.4</v>
       </c>
       <c r="AU9" t="n">
-        <v>6.2</v>
+        <v>3.6</v>
       </c>
       <c r="AV9" t="n">
-        <v>5.4</v>
+        <v>7.6</v>
       </c>
       <c r="AW9" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AY9" t="n">
         <v>4.9</v>
       </c>
-      <c r="AX9" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>5.1</v>
-      </c>
       <c r="AZ9" t="n">
-        <v>6.4</v>
+        <v>1.97</v>
       </c>
       <c r="BA9" t="n">
-        <v>7</v>
+        <v>2.06</v>
       </c>
       <c r="BB9" t="n">
-        <v>6</v>
+        <v>1.99</v>
       </c>
       <c r="BC9" t="n">
-        <v>6</v>
+        <v>1.98</v>
       </c>
       <c r="BD9" t="n">
-        <v>6.8</v>
+        <v>2.02</v>
       </c>
       <c r="BE9" t="n">
-        <v>4.9</v>
+        <v>2.06</v>
       </c>
       <c r="BF9" t="n">
-        <v>5.9</v>
+        <v>2.06</v>
       </c>
       <c r="BG9" t="n">
-        <v>4.8</v>
+        <v>2.06</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-25 04:14:47</t>
+          <t>2026-03-25 06:20:07</t>
         </is>
       </c>
     </row>
@@ -2312,10 +2312,10 @@
         <v>2.98</v>
       </c>
       <c r="G10" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="H10" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="I10" t="n">
         <v>3.4</v>
@@ -2324,7 +2324,7 @@
         <v>2.58</v>
       </c>
       <c r="K10" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="L10" t="n">
         <v>1.72</v>
@@ -2333,7 +2333,7 @@
         <v>1.18</v>
       </c>
       <c r="N10" t="n">
-        <v>2.24</v>
+        <v>2.32</v>
       </c>
       <c r="O10" t="n">
         <v>1.72</v>
@@ -2342,7 +2342,7 @@
         <v>1.41</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="R10" t="n">
         <v>1.13</v>
@@ -2366,13 +2366,13 @@
         <v>6.6</v>
       </c>
       <c r="Y10" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z10" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AA10" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AB10" t="n">
         <v>9</v>
@@ -2381,37 +2381,37 @@
         <v>6.8</v>
       </c>
       <c r="AD10" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AE10" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AF10" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AG10" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AH10" t="n">
-        <v>75</v>
+        <v>48</v>
       </c>
       <c r="AI10" t="n">
-        <v>1000</v>
+        <v>540</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AK10" t="n">
-        <v>290</v>
+        <v>160</v>
       </c>
       <c r="AL10" t="n">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="AM10" t="n">
         <v>1000</v>
       </c>
       <c r="AN10" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AO10" t="n">
         <v>1000</v>
@@ -2423,7 +2423,7 @@
         <v>7.4</v>
       </c>
       <c r="AR10" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AS10" t="n">
         <v>20</v>
@@ -2438,7 +2438,7 @@
         <v>14.5</v>
       </c>
       <c r="AW10" t="n">
-        <v>7.8</v>
+        <v>24</v>
       </c>
       <c r="AX10" t="n">
         <v>15.5</v>
@@ -2447,32 +2447,32 @@
         <v>13</v>
       </c>
       <c r="AZ10" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BA10" t="n">
-        <v>5.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB10" t="n">
-        <v>6.6</v>
+        <v>18</v>
       </c>
       <c r="BC10" t="n">
-        <v>7.2</v>
+        <v>24</v>
       </c>
       <c r="BD10" t="n">
-        <v>5.5</v>
+        <v>8.6</v>
       </c>
       <c r="BE10" t="n">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="BF10" t="n">
-        <v>7.4</v>
+        <v>10</v>
       </c>
       <c r="BG10" t="n">
-        <v>16.5</v>
+        <v>7.8</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-25 04:14:47</t>
+          <t>2026-03-25 06:20:07</t>
         </is>
       </c>
     </row>
@@ -2503,22 +2503,22 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="G11" t="n">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="H11" t="n">
         <v>3.25</v>
       </c>
       <c r="I11" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="J11" t="n">
         <v>3</v>
       </c>
       <c r="K11" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="L11" t="n">
         <v>1.61</v>
@@ -2527,40 +2527,40 @@
         <v>1.13</v>
       </c>
       <c r="N11" t="n">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="O11" t="n">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="P11" t="n">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.8</v>
+        <v>2.66</v>
       </c>
       <c r="R11" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S11" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="T11" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="U11" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="V11" t="n">
         <v>1.4</v>
       </c>
       <c r="W11" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="X11" t="n">
-        <v>8.199999999999999</v>
+        <v>13.5</v>
       </c>
       <c r="Y11" t="n">
-        <v>9.199999999999999</v>
+        <v>13</v>
       </c>
       <c r="Z11" t="n">
         <v>500</v>
@@ -2569,7 +2569,7 @@
         <v>900</v>
       </c>
       <c r="AB11" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AC11" t="n">
         <v>7.2</v>
@@ -2578,34 +2578,34 @@
         <v>34</v>
       </c>
       <c r="AE11" t="n">
-        <v>290</v>
+        <v>120</v>
       </c>
       <c r="AF11" t="n">
+        <v>46</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>32</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>70</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>220</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>140</v>
+      </c>
+      <c r="AL11" t="n">
         <v>500</v>
       </c>
-      <c r="AG11" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>950</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>900</v>
-      </c>
-      <c r="AK11" t="n">
+      <c r="AM11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN11" t="n">
         <v>500</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>1000</v>
       </c>
       <c r="AO11" t="n">
         <v>1000</v>
@@ -2614,10 +2614,10 @@
         <v>7.2</v>
       </c>
       <c r="AQ11" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR11" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS11" t="n">
         <v>23</v>
@@ -2626,16 +2626,16 @@
         <v>7</v>
       </c>
       <c r="AU11" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV11" t="n">
         <v>9</v>
       </c>
       <c r="AW11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AX11" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AY11" t="n">
         <v>11.5</v>
@@ -2644,7 +2644,7 @@
         <v>11.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>9.800000000000001</v>
+        <v>6.4</v>
       </c>
       <c r="BB11" t="n">
         <v>21</v>
@@ -2653,20 +2653,20 @@
         <v>16</v>
       </c>
       <c r="BD11" t="n">
-        <v>11.5</v>
+        <v>30</v>
       </c>
       <c r="BE11" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="BF11" t="n">
         <v>34</v>
       </c>
       <c r="BG11" t="n">
-        <v>9.800000000000001</v>
+        <v>13</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-25 04:14:47</t>
+          <t>2026-03-25 06:20:07</t>
         </is>
       </c>
     </row>
@@ -2697,85 +2697,85 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.92</v>
+        <v>2.02</v>
       </c>
       <c r="G12" t="n">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="H12" t="n">
-        <v>5.1</v>
+        <v>4.5</v>
       </c>
       <c r="I12" t="n">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="J12" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="K12" t="n">
         <v>3.35</v>
       </c>
       <c r="L12" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="M12" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="N12" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="O12" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="P12" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="R12" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="S12" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="T12" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="U12" t="n">
         <v>1.66</v>
       </c>
       <c r="V12" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="W12" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="X12" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y12" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Z12" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA12" t="n">
         <v>1000</v>
       </c>
       <c r="AB12" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AC12" t="n">
-        <v>14</v>
+        <v>7.8</v>
       </c>
       <c r="AD12" t="n">
-        <v>950</v>
+        <v>70</v>
       </c>
       <c r="AE12" t="n">
         <v>1000</v>
       </c>
       <c r="AF12" t="n">
-        <v>28</v>
+        <v>11.5</v>
       </c>
       <c r="AG12" t="n">
         <v>27</v>
@@ -2790,10 +2790,10 @@
         <v>120</v>
       </c>
       <c r="AK12" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="AL12" t="n">
-        <v>1000</v>
+        <v>460</v>
       </c>
       <c r="AM12" t="n">
         <v>1000</v>
@@ -2805,46 +2805,46 @@
         <v>1000</v>
       </c>
       <c r="AP12" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AQ12" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AR12" t="n">
         <v>14.5</v>
       </c>
       <c r="AS12" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AT12" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="AU12" t="n">
         <v>6.6</v>
       </c>
       <c r="AV12" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AW12" t="n">
-        <v>5.4</v>
+        <v>7.4</v>
       </c>
       <c r="AX12" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY12" t="n">
         <v>7.2</v>
       </c>
       <c r="AZ12" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BA12" t="n">
-        <v>3.9</v>
+        <v>10</v>
       </c>
       <c r="BB12" t="n">
         <v>11</v>
       </c>
       <c r="BC12" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BD12" t="n">
         <v>44</v>
@@ -2853,14 +2853,14 @@
         <v>9.6</v>
       </c>
       <c r="BF12" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BG12" t="n">
-        <v>9.6</v>
+        <v>6</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-25 04:14:47</t>
+          <t>2026-03-25 06:20:07</t>
         </is>
       </c>
     </row>
@@ -2894,19 +2894,19 @@
         <v>3.2</v>
       </c>
       <c r="G13" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="H13" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="I13" t="n">
         <v>2.38</v>
       </c>
       <c r="J13" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="K13" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="L13" t="n">
         <v>1.34</v>
@@ -2918,31 +2918,31 @@
         <v>4.7</v>
       </c>
       <c r="O13" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P13" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="R13" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="S13" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="T13" t="n">
         <v>1.62</v>
       </c>
       <c r="U13" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="V13" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="W13" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="X13" t="n">
         <v>90</v>
@@ -2951,16 +2951,16 @@
         <v>970</v>
       </c>
       <c r="Z13" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AA13" t="n">
-        <v>120</v>
+        <v>34</v>
       </c>
       <c r="AB13" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="AC13" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AD13" t="n">
         <v>20</v>
@@ -2969,13 +2969,13 @@
         <v>65</v>
       </c>
       <c r="AF13" t="n">
-        <v>65</v>
+        <v>25</v>
       </c>
       <c r="AG13" t="n">
-        <v>970</v>
+        <v>15</v>
       </c>
       <c r="AH13" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="AI13" t="n">
         <v>75</v>
@@ -2990,10 +2990,10 @@
         <v>500</v>
       </c>
       <c r="AM13" t="n">
-        <v>580</v>
+        <v>320</v>
       </c>
       <c r="AN13" t="n">
-        <v>500</v>
+        <v>29</v>
       </c>
       <c r="AO13" t="n">
         <v>15.5</v>
@@ -3002,7 +3002,7 @@
         <v>10.5</v>
       </c>
       <c r="AQ13" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AR13" t="n">
         <v>13</v>
@@ -3014,47 +3014,47 @@
         <v>8.4</v>
       </c>
       <c r="AU13" t="n">
-        <v>5.1</v>
+        <v>7.2</v>
       </c>
       <c r="AV13" t="n">
         <v>6.2</v>
       </c>
       <c r="AW13" t="n">
-        <v>10.5</v>
+        <v>17</v>
       </c>
       <c r="AX13" t="n">
         <v>11.5</v>
       </c>
       <c r="AY13" t="n">
-        <v>7.6</v>
+        <v>11.5</v>
       </c>
       <c r="AZ13" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BA13" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="BB13" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BC13" t="n">
-        <v>7.8</v>
+        <v>14.5</v>
       </c>
       <c r="BD13" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="BE13" t="n">
-        <v>4.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF13" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="BG13" t="n">
         <v>11.5</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-25 04:14:47</t>
+          <t>2026-03-25 06:20:07</t>
         </is>
       </c>
     </row>
@@ -3085,13 +3085,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="G14" t="n">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="H14" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="I14" t="n">
         <v>2.76</v>
@@ -3100,7 +3100,7 @@
         <v>3.55</v>
       </c>
       <c r="K14" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="L14" t="n">
         <v>1.39</v>
@@ -3121,37 +3121,37 @@
         <v>1.88</v>
       </c>
       <c r="R14" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="S14" t="n">
         <v>3.2</v>
       </c>
       <c r="T14" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="U14" t="n">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="V14" t="n">
         <v>1.57</v>
       </c>
       <c r="W14" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="X14" t="n">
         <v>17</v>
       </c>
       <c r="Y14" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="Z14" t="n">
         <v>38</v>
       </c>
       <c r="AA14" t="n">
-        <v>130</v>
+        <v>95</v>
       </c>
       <c r="AB14" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="AC14" t="n">
         <v>8.199999999999999</v>
@@ -3160,10 +3160,10 @@
         <v>13</v>
       </c>
       <c r="AE14" t="n">
-        <v>60</v>
+        <v>28</v>
       </c>
       <c r="AF14" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AG14" t="n">
         <v>12.5</v>
@@ -3172,28 +3172,28 @@
         <v>25</v>
       </c>
       <c r="AI14" t="n">
-        <v>95</v>
+        <v>38</v>
       </c>
       <c r="AJ14" t="n">
         <v>46</v>
       </c>
       <c r="AK14" t="n">
-        <v>29</v>
+        <v>75</v>
       </c>
       <c r="AL14" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AM14" t="n">
         <v>200</v>
       </c>
       <c r="AN14" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AO14" t="n">
-        <v>55</v>
+        <v>22</v>
       </c>
       <c r="AP14" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AQ14" t="n">
         <v>11</v>
@@ -3202,7 +3202,7 @@
         <v>16.5</v>
       </c>
       <c r="AS14" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="AT14" t="n">
         <v>11.5</v>
@@ -3220,7 +3220,7 @@
         <v>10.5</v>
       </c>
       <c r="AY14" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AZ14" t="n">
         <v>9</v>
@@ -3235,20 +3235,20 @@
         <v>15</v>
       </c>
       <c r="BD14" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="BE14" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="BF14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BG14" t="n">
         <v>17.5</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-25 04:14:47</t>
+          <t>2026-03-25 06:20:07</t>
         </is>
       </c>
     </row>
@@ -3279,170 +3279,170 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="G15" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="H15" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="I15" t="n">
         <v>2.16</v>
       </c>
       <c r="J15" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="K15" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L15" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="M15" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N15" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="O15" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="P15" t="n">
-        <v>2.12</v>
+        <v>2.26</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="R15" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="S15" t="n">
-        <v>3.05</v>
+        <v>2.92</v>
       </c>
       <c r="T15" t="n">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="U15" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="V15" t="n">
         <v>1.86</v>
       </c>
       <c r="W15" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="X15" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="Y15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Z15" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AA15" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AB15" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AC15" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD15" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AE15" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AF15" t="n">
         <v>28</v>
       </c>
       <c r="AG15" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AH15" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AI15" t="n">
+        <v>32</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>65</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>75</v>
+      </c>
+      <c r="AN15" t="n">
         <v>34</v>
       </c>
-      <c r="AJ15" t="n">
-        <v>75</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>42</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>120</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>320</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>40</v>
-      </c>
       <c r="AO15" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AP15" t="n">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="AQ15" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AR15" t="n">
         <v>12.5</v>
       </c>
       <c r="AS15" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AT15" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AU15" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AV15" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AW15" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AX15" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="AY15" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AZ15" t="n">
         <v>14</v>
       </c>
       <c r="BA15" t="n">
-        <v>16.5</v>
+        <v>27</v>
       </c>
       <c r="BB15" t="n">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="BC15" t="n">
-        <v>9.199999999999999</v>
+        <v>32</v>
       </c>
       <c r="BD15" t="n">
         <v>36</v>
       </c>
       <c r="BE15" t="n">
-        <v>29</v>
+        <v>13.5</v>
       </c>
       <c r="BF15" t="n">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="BG15" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-25 04:14:47</t>
+          <t>2026-03-25 06:20:07</t>
         </is>
       </c>
     </row>
@@ -3473,19 +3473,19 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="G16" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="H16" t="n">
         <v>2.12</v>
       </c>
       <c r="I16" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="J16" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="K16" t="n">
         <v>3.9</v>
@@ -3497,16 +3497,16 @@
         <v>1.04</v>
       </c>
       <c r="N16" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="O16" t="n">
         <v>1.22</v>
       </c>
       <c r="P16" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="R16" t="n">
         <v>1.52</v>
@@ -3515,28 +3515,28 @@
         <v>2.74</v>
       </c>
       <c r="T16" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="U16" t="n">
         <v>2.48</v>
       </c>
       <c r="V16" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="W16" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="X16" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="Y16" t="n">
         <v>13.5</v>
       </c>
       <c r="Z16" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AA16" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AB16" t="n">
         <v>19</v>
@@ -3575,7 +3575,7 @@
         <v>70</v>
       </c>
       <c r="AN16" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AO16" t="n">
         <v>13</v>
@@ -3596,7 +3596,7 @@
         <v>16</v>
       </c>
       <c r="AU16" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV16" t="n">
         <v>9.199999999999999</v>
@@ -3605,7 +3605,7 @@
         <v>16.5</v>
       </c>
       <c r="AX16" t="n">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="AY16" t="n">
         <v>13</v>
@@ -3617,7 +3617,7 @@
         <v>15</v>
       </c>
       <c r="BB16" t="n">
-        <v>9.6</v>
+        <v>50</v>
       </c>
       <c r="BC16" t="n">
         <v>30</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-25 04:14:47</t>
+          <t>2026-03-25 06:20:07</t>
         </is>
       </c>
     </row>
@@ -3667,16 +3667,16 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="G17" t="n">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="H17" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="I17" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="J17" t="n">
         <v>4.1</v>
@@ -3688,7 +3688,7 @@
         <v>1.37</v>
       </c>
       <c r="M17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N17" t="n">
         <v>4.3</v>
@@ -3703,64 +3703,64 @@
         <v>1.81</v>
       </c>
       <c r="R17" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S17" t="n">
         <v>3.1</v>
       </c>
       <c r="T17" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="U17" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="V17" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W17" t="n">
-        <v>2.42</v>
+        <v>2.34</v>
       </c>
       <c r="X17" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="Y17" t="n">
         <v>21</v>
       </c>
       <c r="Z17" t="n">
-        <v>220</v>
+        <v>110</v>
       </c>
       <c r="AA17" t="n">
         <v>900</v>
       </c>
       <c r="AB17" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC17" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD17" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE17" t="n">
-        <v>400</v>
+        <v>75</v>
       </c>
       <c r="AF17" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AG17" t="n">
         <v>10</v>
       </c>
       <c r="AH17" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AI17" t="n">
-        <v>320</v>
+        <v>75</v>
       </c>
       <c r="AJ17" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AK17" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AL17" t="n">
         <v>36</v>
@@ -3769,34 +3769,34 @@
         <v>580</v>
       </c>
       <c r="AN17" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AO17" t="n">
-        <v>310</v>
+        <v>600</v>
       </c>
       <c r="AP17" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AQ17" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AR17" t="n">
         <v>20</v>
       </c>
       <c r="AS17" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AT17" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU17" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AV17" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AW17" t="n">
-        <v>55</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX17" t="n">
         <v>9</v>
@@ -3808,7 +3808,7 @@
         <v>16.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>55</v>
+        <v>9</v>
       </c>
       <c r="BB17" t="n">
         <v>14</v>
@@ -3820,17 +3820,17 @@
         <v>25</v>
       </c>
       <c r="BE17" t="n">
-        <v>38</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF17" t="n">
         <v>7.6</v>
       </c>
       <c r="BG17" t="n">
-        <v>13.5</v>
+        <v>23</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-25 04:14:47</t>
+          <t>2026-03-25 06:20:07</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="G18" t="n">
         <v>2.06</v>
@@ -3903,22 +3903,22 @@
         <v>3.6</v>
       </c>
       <c r="T18" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="U18" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="V18" t="n">
         <v>1.29</v>
       </c>
       <c r="W18" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="X18" t="n">
         <v>15</v>
       </c>
       <c r="Y18" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="Z18" t="n">
         <v>32</v>
@@ -3963,7 +3963,7 @@
         <v>130</v>
       </c>
       <c r="AN18" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AO18" t="n">
         <v>65</v>
@@ -3978,7 +3978,7 @@
         <v>27</v>
       </c>
       <c r="AS18" t="n">
-        <v>28</v>
+        <v>75</v>
       </c>
       <c r="AT18" t="n">
         <v>8.199999999999999</v>
@@ -3990,7 +3990,7 @@
         <v>15.5</v>
       </c>
       <c r="AW18" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AX18" t="n">
         <v>10.5</v>
@@ -4014,17 +4014,17 @@
         <v>32</v>
       </c>
       <c r="BE18" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BF18" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BG18" t="n">
         <v>27</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-25 04:14:47</t>
+          <t>2026-03-25 06:20:07</t>
         </is>
       </c>
     </row>
@@ -4055,58 +4055,58 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.48</v>
+        <v>1.56</v>
       </c>
       <c r="G19" t="n">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="H19" t="n">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="I19" t="n">
-        <v>11</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J19" t="n">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="K19" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="L19" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="M19" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N19" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="O19" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="P19" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="Q19" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S19" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T19" t="n">
         <v>2.18</v>
       </c>
-      <c r="R19" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S19" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.28</v>
-      </c>
       <c r="U19" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="V19" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="W19" t="n">
-        <v>2.86</v>
+        <v>2.6</v>
       </c>
       <c r="X19" t="n">
         <v>970</v>
@@ -4115,13 +4115,13 @@
         <v>70</v>
       </c>
       <c r="Z19" t="n">
-        <v>95</v>
+        <v>170</v>
       </c>
       <c r="AA19" t="n">
         <v>1000</v>
       </c>
       <c r="AB19" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AC19" t="n">
         <v>42</v>
@@ -4133,22 +4133,22 @@
         <v>1000</v>
       </c>
       <c r="AF19" t="n">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="AG19" t="n">
-        <v>25</v>
+        <v>970</v>
       </c>
       <c r="AH19" t="n">
-        <v>150</v>
+        <v>65</v>
       </c>
       <c r="AI19" t="n">
         <v>1000</v>
       </c>
       <c r="AJ19" t="n">
-        <v>180</v>
+        <v>900</v>
       </c>
       <c r="AK19" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AL19" t="n">
         <v>500</v>
@@ -4163,10 +4163,10 @@
         <v>1000</v>
       </c>
       <c r="AP19" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="AQ19" t="n">
-        <v>7.2</v>
+        <v>15.5</v>
       </c>
       <c r="AR19" t="n">
         <v>4.2</v>
@@ -4175,50 +4175,50 @@
         <v>4.2</v>
       </c>
       <c r="AT19" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="AU19" t="n">
         <v>6.2</v>
       </c>
       <c r="AV19" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW19" t="n">
         <v>4.2</v>
       </c>
       <c r="AX19" t="n">
-        <v>6.4</v>
+        <v>4.5</v>
       </c>
       <c r="AY19" t="n">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="AZ19" t="n">
-        <v>7.8</v>
+        <v>6.8</v>
       </c>
       <c r="BA19" t="n">
         <v>4.2</v>
       </c>
       <c r="BB19" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BC19" t="n">
-        <v>6.6</v>
+        <v>11.5</v>
       </c>
       <c r="BD19" t="n">
-        <v>6.2</v>
+        <v>34</v>
       </c>
       <c r="BE19" t="n">
-        <v>2.96</v>
+        <v>9.4</v>
       </c>
       <c r="BF19" t="n">
         <v>9.6</v>
       </c>
       <c r="BG19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-25 04:14:47</t>
+          <t>2026-03-25 06:20:07</t>
         </is>
       </c>
     </row>
@@ -4252,16 +4252,16 @@
         <v>3.15</v>
       </c>
       <c r="G20" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="H20" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="I20" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="J20" t="n">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="K20" t="n">
         <v>3.1</v>
@@ -4270,70 +4270,70 @@
         <v>1.6</v>
       </c>
       <c r="M20" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="N20" t="n">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="O20" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="P20" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="R20" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S20" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="T20" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="U20" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="V20" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="W20" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="X20" t="n">
         <v>8.4</v>
       </c>
       <c r="Y20" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="Z20" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AA20" t="n">
         <v>900</v>
       </c>
       <c r="AB20" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="AC20" t="n">
         <v>7</v>
       </c>
       <c r="AD20" t="n">
-        <v>17.5</v>
+        <v>14.5</v>
       </c>
       <c r="AE20" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AF20" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="AG20" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AH20" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AI20" t="n">
         <v>500</v>
@@ -4342,7 +4342,7 @@
         <v>900</v>
       </c>
       <c r="AK20" t="n">
-        <v>120</v>
+        <v>500</v>
       </c>
       <c r="AL20" t="n">
         <v>500</v>
@@ -4351,10 +4351,10 @@
         <v>500</v>
       </c>
       <c r="AN20" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AO20" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP20" t="n">
         <v>7.4</v>
@@ -4363,43 +4363,43 @@
         <v>7.4</v>
       </c>
       <c r="AR20" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AS20" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="AT20" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU20" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AV20" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AW20" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AX20" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AY20" t="n">
         <v>13</v>
       </c>
       <c r="AZ20" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BA20" t="n">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="BB20" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="BC20" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BD20" t="n">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="BE20" t="n">
         <v>70</v>
@@ -4408,11 +4408,11 @@
         <v>30</v>
       </c>
       <c r="BG20" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-25 04:14:47</t>
+          <t>2026-03-25 06:20:07</t>
         </is>
       </c>
     </row>
@@ -4443,22 +4443,22 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="G21" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="H21" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="I21" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="J21" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="K21" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="L21" t="n">
         <v>1.85</v>
@@ -4482,37 +4482,37 @@
         <v>1.09</v>
       </c>
       <c r="S21" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="T21" t="n">
-        <v>2.74</v>
+        <v>2.82</v>
       </c>
       <c r="U21" t="n">
         <v>1.47</v>
       </c>
       <c r="V21" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W21" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="X21" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="Y21" t="n">
         <v>8</v>
       </c>
       <c r="Z21" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AA21" t="n">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="AB21" t="n">
         <v>6.4</v>
       </c>
       <c r="AC21" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD21" t="n">
         <v>21</v>
@@ -4521,7 +4521,7 @@
         <v>110</v>
       </c>
       <c r="AF21" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AG21" t="n">
         <v>16.5</v>
@@ -4545,7 +4545,7 @@
         <v>500</v>
       </c>
       <c r="AN21" t="n">
-        <v>500</v>
+        <v>85</v>
       </c>
       <c r="AO21" t="n">
         <v>210</v>
@@ -4557,22 +4557,22 @@
         <v>7.2</v>
       </c>
       <c r="AR21" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AS21" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AT21" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="AU21" t="n">
         <v>6.6</v>
       </c>
       <c r="AV21" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AW21" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AX21" t="n">
         <v>12.5</v>
@@ -4581,32 +4581,32 @@
         <v>14.5</v>
       </c>
       <c r="AZ21" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BA21" t="n">
-        <v>85</v>
+        <v>48</v>
       </c>
       <c r="BB21" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BC21" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="BD21" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="BE21" t="n">
         <v>120</v>
       </c>
       <c r="BF21" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="BG21" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-25 04:14:47</t>
+          <t>2026-03-25 06:20:07</t>
         </is>
       </c>
     </row>
@@ -4646,13 +4646,13 @@
         <v>4.3</v>
       </c>
       <c r="I22" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="J22" t="n">
         <v>3.35</v>
       </c>
       <c r="K22" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L22" t="n">
         <v>1.47</v>
@@ -4661,28 +4661,28 @@
         <v>1.09</v>
       </c>
       <c r="N22" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="O22" t="n">
         <v>1.39</v>
       </c>
       <c r="P22" t="n">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="R22" t="n">
         <v>1.28</v>
       </c>
       <c r="S22" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="T22" t="n">
         <v>1.91</v>
       </c>
       <c r="U22" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="V22" t="n">
         <v>1.25</v>
@@ -4691,10 +4691,10 @@
         <v>1.94</v>
       </c>
       <c r="X22" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Y22" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Z22" t="n">
         <v>36</v>
@@ -4733,13 +4733,13 @@
         <v>24</v>
       </c>
       <c r="AL22" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AM22" t="n">
         <v>580</v>
       </c>
       <c r="AN22" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AO22" t="n">
         <v>95</v>
@@ -4754,10 +4754,10 @@
         <v>13</v>
       </c>
       <c r="AS22" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="AT22" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="AU22" t="n">
         <v>6.8</v>
@@ -4766,7 +4766,7 @@
         <v>13.5</v>
       </c>
       <c r="AW22" t="n">
-        <v>8.6</v>
+        <v>23</v>
       </c>
       <c r="AX22" t="n">
         <v>10</v>
@@ -4778,7 +4778,7 @@
         <v>17</v>
       </c>
       <c r="BA22" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB22" t="n">
         <v>20</v>
@@ -4787,20 +4787,20 @@
         <v>19</v>
       </c>
       <c r="BD22" t="n">
-        <v>8.199999999999999</v>
+        <v>23</v>
       </c>
       <c r="BE22" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BF22" t="n">
         <v>14.5</v>
       </c>
       <c r="BG22" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-25 04:14:47</t>
+          <t>2026-03-25 06:20:07</t>
         </is>
       </c>
     </row>
@@ -4846,7 +4846,7 @@
         <v>3.5</v>
       </c>
       <c r="K23" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="L23" t="n">
         <v>1.5</v>
@@ -4918,7 +4918,7 @@
         <v>1000</v>
       </c>
       <c r="AI23" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ23" t="n">
         <v>900</v>
@@ -4942,10 +4942,10 @@
         <v>5.8</v>
       </c>
       <c r="AQ23" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AR23" t="n">
-        <v>3.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS23" t="n">
         <v>4</v>
@@ -4960,16 +4960,16 @@
         <v>16</v>
       </c>
       <c r="AW23" t="n">
-        <v>3.15</v>
+        <v>7.4</v>
       </c>
       <c r="AX23" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AY23" t="n">
-        <v>9.4</v>
+        <v>5.5</v>
       </c>
       <c r="AZ23" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BA23" t="n">
         <v>9.6</v>
@@ -4981,7 +4981,7 @@
         <v>7.6</v>
       </c>
       <c r="BD23" t="n">
-        <v>3.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE23" t="n">
         <v>10</v>
@@ -4990,11 +4990,11 @@
         <v>7</v>
       </c>
       <c r="BG23" t="n">
-        <v>7.6</v>
+        <v>10</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-25 04:14:47</t>
+          <t>2026-03-25 06:20:07</t>
         </is>
       </c>
     </row>
@@ -5025,10 +5025,10 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="G24" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="H24" t="n">
         <v>6.8</v>
@@ -5076,7 +5076,7 @@
         <v>1.13</v>
       </c>
       <c r="W24" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="X24" t="n">
         <v>1000</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-25 04:14:47</t>
+          <t>2026-03-25 06:20:07</t>
         </is>
       </c>
     </row>
@@ -5219,46 +5219,46 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.4</v>
+        <v>1.72</v>
       </c>
       <c r="G25" t="n">
-        <v>4.4</v>
+        <v>1.79</v>
       </c>
       <c r="H25" t="n">
-        <v>3.35</v>
+        <v>4.5</v>
       </c>
       <c r="I25" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="J25" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="K25" t="n">
-        <v>11.5</v>
+        <v>4.5</v>
       </c>
       <c r="L25" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="M25" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N25" t="n">
-        <v>1.28</v>
+        <v>1.39</v>
       </c>
       <c r="O25" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P25" t="n">
-        <v>1.28</v>
+        <v>1.39</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="R25" t="n">
-        <v>1.22</v>
+        <v>1.42</v>
       </c>
       <c r="S25" t="n">
-        <v>1.66</v>
+        <v>2.7</v>
       </c>
       <c r="T25" t="n">
         <v>1.01</v>
@@ -5267,13 +5267,13 @@
         <v>1.01</v>
       </c>
       <c r="V25" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="W25" t="n">
-        <v>1.29</v>
+        <v>2.26</v>
       </c>
       <c r="X25" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="Y25" t="n">
         <v>1000</v>
@@ -5288,7 +5288,7 @@
         <v>1000</v>
       </c>
       <c r="AC25" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AD25" t="n">
         <v>1000</v>
@@ -5300,10 +5300,10 @@
         <v>1000</v>
       </c>
       <c r="AG25" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AH25" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AI25" t="n">
         <v>1000</v>
@@ -5321,68 +5321,68 @@
         <v>1000</v>
       </c>
       <c r="AN25" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AO25" t="n">
         <v>1000</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.22</v>
+        <v>6.4</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.21</v>
+        <v>6.6</v>
       </c>
       <c r="AR25" t="n">
-        <v>1.23</v>
+        <v>2</v>
       </c>
       <c r="AS25" t="n">
-        <v>1.24</v>
+        <v>2</v>
       </c>
       <c r="AT25" t="n">
-        <v>1.19</v>
+        <v>4.8</v>
       </c>
       <c r="AU25" t="n">
-        <v>1.21</v>
+        <v>4.8</v>
       </c>
       <c r="AV25" t="n">
-        <v>1.21</v>
+        <v>3.85</v>
       </c>
       <c r="AW25" t="n">
-        <v>1.24</v>
+        <v>2.22</v>
       </c>
       <c r="AX25" t="n">
-        <v>1.24</v>
+        <v>2.96</v>
       </c>
       <c r="AY25" t="n">
-        <v>1.2</v>
+        <v>3.1</v>
       </c>
       <c r="AZ25" t="n">
-        <v>1.24</v>
+        <v>2.32</v>
       </c>
       <c r="BA25" t="n">
-        <v>1.24</v>
+        <v>1.97</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.24</v>
+        <v>6.2</v>
       </c>
       <c r="BC25" t="n">
-        <v>1.22</v>
+        <v>2.48</v>
       </c>
       <c r="BD25" t="n">
-        <v>1.24</v>
+        <v>1.93</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.24</v>
+        <v>1.99</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.21</v>
+        <v>3.8</v>
       </c>
       <c r="BG25" t="n">
-        <v>1.55</v>
+        <v>2.02</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-25 04:14:47</t>
+          <t>2026-03-25 06:20:07</t>
         </is>
       </c>
     </row>
@@ -5419,7 +5419,7 @@
         <v>1.69</v>
       </c>
       <c r="H26" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="I26" t="n">
         <v>6.2</v>
@@ -5428,7 +5428,7 @@
         <v>4.1</v>
       </c>
       <c r="K26" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="L26" t="n">
         <v>1.38</v>
@@ -5455,7 +5455,7 @@
         <v>3.15</v>
       </c>
       <c r="T26" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="U26" t="n">
         <v>2.06</v>
@@ -5479,13 +5479,13 @@
         <v>900</v>
       </c>
       <c r="AB26" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC26" t="n">
         <v>10.5</v>
       </c>
       <c r="AD26" t="n">
-        <v>55</v>
+        <v>22</v>
       </c>
       <c r="AE26" t="n">
         <v>400</v>
@@ -5503,7 +5503,7 @@
         <v>700</v>
       </c>
       <c r="AJ26" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AK26" t="n">
         <v>30</v>
@@ -5527,10 +5527,10 @@
         <v>17.5</v>
       </c>
       <c r="AR26" t="n">
+        <v>7</v>
+      </c>
+      <c r="AS26" t="n">
         <v>7.6</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>8.4</v>
       </c>
       <c r="AT26" t="n">
         <v>8</v>
@@ -5542,7 +5542,7 @@
         <v>17</v>
       </c>
       <c r="AW26" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="AX26" t="n">
         <v>9.6</v>
@@ -5554,7 +5554,7 @@
         <v>16.5</v>
       </c>
       <c r="BA26" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="BB26" t="n">
         <v>13</v>
@@ -5566,17 +5566,17 @@
         <v>19.5</v>
       </c>
       <c r="BE26" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="BF26" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BG26" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-25 04:14:47</t>
+          <t>2026-03-25 06:20:07</t>
         </is>
       </c>
     </row>
@@ -5607,22 +5607,22 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.58</v>
+        <v>2.7</v>
       </c>
       <c r="G27" t="n">
-        <v>2.68</v>
+        <v>2.9</v>
       </c>
       <c r="H27" t="n">
-        <v>2.78</v>
+        <v>2.62</v>
       </c>
       <c r="I27" t="n">
-        <v>2.92</v>
+        <v>2.82</v>
       </c>
       <c r="J27" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="K27" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L27" t="n">
         <v>1.38</v>
@@ -5631,40 +5631,40 @@
         <v>1.06</v>
       </c>
       <c r="N27" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="O27" t="n">
         <v>1.28</v>
       </c>
       <c r="P27" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="R27" t="n">
         <v>1.4</v>
       </c>
       <c r="S27" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="T27" t="n">
         <v>1.66</v>
       </c>
       <c r="U27" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="V27" t="n">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="W27" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="X27" t="n">
-        <v>18.5</v>
+        <v>26</v>
       </c>
       <c r="Y27" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Z27" t="n">
         <v>38</v>
@@ -5676,31 +5676,31 @@
         <v>13.5</v>
       </c>
       <c r="AC27" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AD27" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AE27" t="n">
         <v>85</v>
       </c>
       <c r="AF27" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AG27" t="n">
         <v>12</v>
       </c>
       <c r="AH27" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AI27" t="n">
         <v>120</v>
       </c>
       <c r="AJ27" t="n">
-        <v>36</v>
+        <v>900</v>
       </c>
       <c r="AK27" t="n">
-        <v>26</v>
+        <v>75</v>
       </c>
       <c r="AL27" t="n">
         <v>95</v>
@@ -5721,16 +5721,16 @@
         <v>10.5</v>
       </c>
       <c r="AR27" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AS27" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="AT27" t="n">
-        <v>9.4</v>
+        <v>11.5</v>
       </c>
       <c r="AU27" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="AV27" t="n">
         <v>10</v>
@@ -5748,7 +5748,7 @@
         <v>13.5</v>
       </c>
       <c r="BA27" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BB27" t="n">
         <v>18</v>
@@ -5757,20 +5757,20 @@
         <v>20</v>
       </c>
       <c r="BD27" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE27" t="n">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BF27" t="n">
         <v>16.5</v>
       </c>
       <c r="BG27" t="n">
-        <v>6.8</v>
+        <v>20</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-25 04:14:47</t>
+          <t>2026-03-25 06:20:07</t>
         </is>
       </c>
     </row>
@@ -5810,13 +5810,13 @@
         <v>1.66</v>
       </c>
       <c r="I28" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="J28" t="n">
         <v>3.7</v>
       </c>
       <c r="K28" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="L28" t="n">
         <v>1.5</v>
@@ -5825,7 +5825,7 @@
         <v>1.09</v>
       </c>
       <c r="N28" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="O28" t="n">
         <v>1.43</v>
@@ -5834,7 +5834,7 @@
         <v>1.69</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="R28" t="n">
         <v>1.25</v>
@@ -5855,40 +5855,40 @@
         <v>1.16</v>
       </c>
       <c r="X28" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="Y28" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="Z28" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AA28" t="n">
-        <v>16.5</v>
+        <v>21</v>
       </c>
       <c r="AB28" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="AC28" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AD28" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AE28" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="AF28" t="n">
-        <v>60</v>
+        <v>270</v>
       </c>
       <c r="AG28" t="n">
-        <v>29</v>
+        <v>950</v>
       </c>
       <c r="AH28" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="AI28" t="n">
-        <v>110</v>
+        <v>290</v>
       </c>
       <c r="AJ28" t="n">
         <v>900</v>
@@ -5909,10 +5909,10 @@
         <v>14.5</v>
       </c>
       <c r="AP28" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ28" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AR28" t="n">
         <v>7.4</v>
@@ -5921,7 +5921,7 @@
         <v>13.5</v>
       </c>
       <c r="AT28" t="n">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="AU28" t="n">
         <v>7.2</v>
@@ -5930,13 +5930,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AW28" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AX28" t="n">
         <v>27</v>
       </c>
       <c r="AY28" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="AZ28" t="n">
         <v>18.5</v>
@@ -5957,14 +5957,14 @@
         <v>70</v>
       </c>
       <c r="BF28" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BG28" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-25 04:14:47</t>
+          <t>2026-03-25 06:20:07</t>
         </is>
       </c>
     </row>
@@ -5995,58 +5995,58 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="G29" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="H29" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="I29" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="J29" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K29" t="n">
         <v>4.1</v>
       </c>
       <c r="L29" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="M29" t="n">
         <v>1.09</v>
       </c>
       <c r="N29" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="O29" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="P29" t="n">
         <v>1.72</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="R29" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="S29" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="T29" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="U29" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="V29" t="n">
         <v>1.15</v>
       </c>
       <c r="W29" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="X29" t="n">
         <v>14</v>
@@ -6055,19 +6055,19 @@
         <v>970</v>
       </c>
       <c r="Z29" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AA29" t="n">
         <v>1000</v>
       </c>
       <c r="AB29" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AC29" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AD29" t="n">
-        <v>28</v>
+        <v>950</v>
       </c>
       <c r="AE29" t="n">
         <v>1000</v>
@@ -6088,7 +6088,7 @@
         <v>19</v>
       </c>
       <c r="AK29" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AL29" t="n">
         <v>50</v>
@@ -6106,16 +6106,16 @@
         <v>10.5</v>
       </c>
       <c r="AQ29" t="n">
-        <v>5.2</v>
+        <v>16.5</v>
       </c>
       <c r="AR29" t="n">
-        <v>6.4</v>
+        <v>50</v>
       </c>
       <c r="AS29" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AT29" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="AU29" t="n">
         <v>7.8</v>
@@ -6127,10 +6127,10 @@
         <v>6.8</v>
       </c>
       <c r="AX29" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AY29" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ29" t="n">
         <v>5.7</v>
@@ -6139,7 +6139,7 @@
         <v>6.8</v>
       </c>
       <c r="BB29" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BC29" t="n">
         <v>17.5</v>
@@ -6148,17 +6148,17 @@
         <v>6.2</v>
       </c>
       <c r="BE29" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BF29" t="n">
         <v>11.5</v>
       </c>
       <c r="BG29" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-25 04:14:47</t>
+          <t>2026-03-25 06:20:07</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-25.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-25.xlsx
@@ -757,170 +757,170 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3.95</v>
+        <v>4.7</v>
       </c>
       <c r="G2" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="H2" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="I2" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="J2" t="n">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="K2" t="n">
-        <v>4.3</v>
+        <v>3.55</v>
       </c>
       <c r="L2" t="n">
-        <v>1.45</v>
+        <v>2.08</v>
       </c>
       <c r="M2" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="N2" t="n">
-        <v>3.5</v>
+        <v>2.58</v>
       </c>
       <c r="O2" t="n">
-        <v>1.35</v>
+        <v>1.61</v>
       </c>
       <c r="P2" t="n">
-        <v>1.81</v>
+        <v>1.48</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.06</v>
+        <v>2.94</v>
       </c>
       <c r="R2" t="n">
-        <v>1.31</v>
+        <v>1.17</v>
       </c>
       <c r="S2" t="n">
-        <v>3.85</v>
+        <v>6.2</v>
       </c>
       <c r="T2" t="n">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="U2" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="V2" t="n">
         <v>1.96</v>
       </c>
-      <c r="V2" t="n">
-        <v>1.94</v>
-      </c>
       <c r="W2" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="X2" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>27</v>
+      </c>
+      <c r="AB2" t="n">
         <v>13.5</v>
       </c>
-      <c r="Y2" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>14</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>500</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>15.5</v>
-      </c>
       <c r="AC2" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD2" t="n">
         <v>12</v>
       </c>
       <c r="AE2" t="n">
-        <v>65</v>
+        <v>34</v>
       </c>
       <c r="AF2" t="n">
-        <v>90</v>
+        <v>44</v>
       </c>
       <c r="AG2" t="n">
         <v>26</v>
       </c>
       <c r="AH2" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AI2" t="n">
-        <v>500</v>
+        <v>85</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AK2" t="n">
-        <v>500</v>
+        <v>120</v>
       </c>
       <c r="AL2" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AM2" t="n">
-        <v>1000</v>
+        <v>340</v>
       </c>
       <c r="AN2" t="n">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AO2" t="n">
+        <v>34</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>17</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>21</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>28</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>17</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>24</v>
+      </c>
+      <c r="BA2" t="n">
         <v>55</v>
       </c>
-      <c r="AP2" t="n">
-        <v>9</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>10</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>11</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>11</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>9</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>13</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>14</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>12.5</v>
-      </c>
       <c r="BB2" t="n">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC2" t="n">
-        <v>4.9</v>
+        <v>7.8</v>
       </c>
       <c r="BD2" t="n">
-        <v>4.8</v>
+        <v>8</v>
       </c>
       <c r="BE2" t="n">
-        <v>4.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF2" t="n">
-        <v>4.7</v>
+        <v>8</v>
       </c>
       <c r="BG2" t="n">
-        <v>4</v>
+        <v>7.2</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-25 06:20:07</t>
+          <t>2026-03-25 08:25:18</t>
         </is>
       </c>
     </row>
@@ -960,22 +960,22 @@
         <v>1.75</v>
       </c>
       <c r="I3" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="J3" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K3" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L3" t="n">
         <v>1.51</v>
       </c>
       <c r="M3" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N3" t="n">
-        <v>2.98</v>
+        <v>2.92</v>
       </c>
       <c r="O3" t="n">
         <v>1.45</v>
@@ -984,58 +984,58 @@
         <v>1.63</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="R3" t="n">
         <v>1.23</v>
       </c>
       <c r="S3" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="T3" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="U3" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="V3" t="n">
         <v>2.16</v>
       </c>
       <c r="W3" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="X3" t="n">
         <v>11</v>
       </c>
       <c r="Y3" t="n">
-        <v>7.8</v>
+        <v>6.8</v>
       </c>
       <c r="Z3" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>20</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>16</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD3" t="n">
         <v>11.5</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>11</v>
       </c>
       <c r="AE3" t="n">
         <v>24</v>
       </c>
       <c r="AF3" t="n">
-        <v>130</v>
+        <v>85</v>
       </c>
       <c r="AG3" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AH3" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="AI3" t="n">
         <v>150</v>
@@ -1065,7 +1065,7 @@
         <v>5.6</v>
       </c>
       <c r="AR3" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS3" t="n">
         <v>16</v>
@@ -1083,38 +1083,38 @@
         <v>19</v>
       </c>
       <c r="AX3" t="n">
-        <v>6.2</v>
+        <v>19</v>
       </c>
       <c r="AY3" t="n">
+        <v>21</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>22</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>36</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BE3" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="AZ3" t="n">
-        <v>21</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>28</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>7</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>6.6</v>
-      </c>
       <c r="BF3" t="n">
-        <v>6.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG3" t="n">
         <v>14</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-25 06:20:07</t>
+          <t>2026-03-25 08:25:18</t>
         </is>
       </c>
     </row>
@@ -1151,16 +1151,16 @@
         <v>2.36</v>
       </c>
       <c r="H4" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="I4" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="J4" t="n">
         <v>3.4</v>
       </c>
       <c r="K4" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L4" t="n">
         <v>1.42</v>
@@ -1175,28 +1175,28 @@
         <v>1.34</v>
       </c>
       <c r="P4" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="Q4" t="n">
         <v>2.02</v>
       </c>
       <c r="R4" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="S4" t="n">
         <v>3.65</v>
       </c>
       <c r="T4" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="U4" t="n">
         <v>2.06</v>
       </c>
       <c r="V4" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="W4" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="X4" t="n">
         <v>14.5</v>
@@ -1205,10 +1205,10 @@
         <v>14</v>
       </c>
       <c r="Z4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AA4" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AB4" t="n">
         <v>9.800000000000001</v>
@@ -1220,7 +1220,7 @@
         <v>16</v>
       </c>
       <c r="AE4" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AF4" t="n">
         <v>15</v>
@@ -1229,7 +1229,7 @@
         <v>11.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AI4" t="n">
         <v>60</v>
@@ -1241,10 +1241,10 @@
         <v>26</v>
       </c>
       <c r="AL4" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AM4" t="n">
-        <v>580</v>
+        <v>1000</v>
       </c>
       <c r="AN4" t="n">
         <v>20</v>
@@ -1256,13 +1256,13 @@
         <v>11.5</v>
       </c>
       <c r="AQ4" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AR4" t="n">
         <v>21</v>
       </c>
       <c r="AS4" t="n">
-        <v>18.5</v>
+        <v>38</v>
       </c>
       <c r="AT4" t="n">
         <v>8.199999999999999</v>
@@ -1274,31 +1274,31 @@
         <v>13</v>
       </c>
       <c r="AW4" t="n">
-        <v>14.5</v>
+        <v>25</v>
       </c>
       <c r="AX4" t="n">
         <v>12</v>
       </c>
       <c r="AY4" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AZ4" t="n">
         <v>15.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="BB4" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BC4" t="n">
         <v>20</v>
       </c>
       <c r="BD4" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="BE4" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BF4" t="n">
         <v>16.5</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-25 06:20:07</t>
+          <t>2026-03-25 08:25:18</t>
         </is>
       </c>
     </row>
@@ -1342,46 +1342,46 @@
         <v>1.17</v>
       </c>
       <c r="G5" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="H5" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="I5" t="n">
         <v>27</v>
       </c>
       <c r="J5" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="K5" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="L5" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="M5" t="n">
         <v>1.02</v>
       </c>
       <c r="N5" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="O5" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="P5" t="n">
-        <v>2.96</v>
+        <v>3.2</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="R5" t="n">
-        <v>1.79</v>
+        <v>1.91</v>
       </c>
       <c r="S5" t="n">
-        <v>2.12</v>
+        <v>2.02</v>
       </c>
       <c r="T5" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="U5" t="n">
         <v>1.66</v>
@@ -1390,10 +1390,10 @@
         <v>1.04</v>
       </c>
       <c r="W5" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="X5" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="Y5" t="n">
         <v>1000</v>
@@ -1405,7 +1405,7 @@
         <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="AC5" t="n">
         <v>24</v>
@@ -1417,10 +1417,10 @@
         <v>1000</v>
       </c>
       <c r="AF5" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="AG5" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AH5" t="n">
         <v>55</v>
@@ -1429,80 +1429,80 @@
         <v>1000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AK5" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="AL5" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM5" t="n">
         <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>3.25</v>
+        <v>2.94</v>
       </c>
       <c r="AO5" t="n">
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>7</v>
+        <v>13.5</v>
       </c>
       <c r="AQ5" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>10</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX5" t="n">
         <v>7.8</v>
       </c>
-      <c r="AR5" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>17</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>7.2</v>
-      </c>
       <c r="AY5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AZ5" t="n">
-        <v>8.4</v>
+        <v>24</v>
       </c>
       <c r="BA5" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB5" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BC5" t="n">
         <v>12</v>
       </c>
       <c r="BD5" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE5" t="n">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="BF5" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="BG5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-25 06:20:07</t>
+          <t>2026-03-25 08:25:18</t>
         </is>
       </c>
     </row>
@@ -1533,13 +1533,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="G6" t="n">
         <v>1.55</v>
       </c>
       <c r="H6" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="I6" t="n">
         <v>8.800000000000001</v>
@@ -1548,7 +1548,7 @@
         <v>4.3</v>
       </c>
       <c r="K6" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="L6" t="n">
         <v>1.35</v>
@@ -1557,88 +1557,88 @@
         <v>1.05</v>
       </c>
       <c r="N6" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="O6" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P6" t="n">
-        <v>2.24</v>
+        <v>2.18</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="R6" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="S6" t="n">
-        <v>2.84</v>
+        <v>2.92</v>
       </c>
       <c r="T6" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="U6" t="n">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="V6" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="W6" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="X6" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="Z6" t="n">
+        <v>160</v>
+      </c>
+      <c r="AA6" t="n">
         <v>270</v>
       </c>
-      <c r="AA6" t="n">
-        <v>260</v>
-      </c>
       <c r="AB6" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC6" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="AE6" t="n">
         <v>480</v>
       </c>
       <c r="AF6" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AG6" t="n">
         <v>11</v>
       </c>
       <c r="AH6" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="AI6" t="n">
         <v>390</v>
       </c>
       <c r="AJ6" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AK6" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AL6" t="n">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="AM6" t="n">
-        <v>390</v>
+        <v>550</v>
       </c>
       <c r="AN6" t="n">
         <v>7.6</v>
       </c>
       <c r="AO6" t="n">
-        <v>200</v>
+        <v>230</v>
       </c>
       <c r="AP6" t="n">
         <v>15.5</v>
@@ -1647,31 +1647,31 @@
         <v>21</v>
       </c>
       <c r="AR6" t="n">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="AS6" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT6" t="n">
         <v>7.4</v>
       </c>
       <c r="AU6" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AV6" t="n">
-        <v>17.5</v>
+        <v>22</v>
       </c>
       <c r="AW6" t="n">
-        <v>8.6</v>
+        <v>16.5</v>
       </c>
       <c r="AX6" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AY6" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ6" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BA6" t="n">
         <v>16.5</v>
@@ -1683,20 +1683,20 @@
         <v>13</v>
       </c>
       <c r="BD6" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="BE6" t="n">
         <v>28</v>
       </c>
       <c r="BF6" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BG6" t="n">
-        <v>8.800000000000001</v>
+        <v>13.5</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-25 06:20:07</t>
+          <t>2026-03-25 08:25:18</t>
         </is>
       </c>
     </row>
@@ -1727,170 +1727,170 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.12</v>
+        <v>2.78</v>
       </c>
       <c r="G7" t="n">
-        <v>2.28</v>
+        <v>3.15</v>
       </c>
       <c r="H7" t="n">
-        <v>3.6</v>
+        <v>2.86</v>
       </c>
       <c r="I7" t="n">
-        <v>4.3</v>
+        <v>3.2</v>
       </c>
       <c r="J7" t="n">
-        <v>3.2</v>
+        <v>2.94</v>
       </c>
       <c r="K7" t="n">
-        <v>3.8</v>
+        <v>3.15</v>
       </c>
       <c r="L7" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="M7" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N7" t="n">
-        <v>2.52</v>
+        <v>2.38</v>
       </c>
       <c r="O7" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="P7" t="n">
-        <v>1.51</v>
+        <v>1.46</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.68</v>
+        <v>2.82</v>
       </c>
       <c r="R7" t="n">
         <v>1.18</v>
       </c>
       <c r="S7" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="T7" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="U7" t="n">
         <v>1.67</v>
       </c>
       <c r="V7" t="n">
-        <v>1.31</v>
+        <v>1.45</v>
       </c>
       <c r="W7" t="n">
-        <v>1.78</v>
+        <v>1.48</v>
       </c>
       <c r="X7" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y7" t="n">
-        <v>11</v>
+        <v>8.6</v>
       </c>
       <c r="Z7" t="n">
-        <v>30</v>
+        <v>18.5</v>
       </c>
       <c r="AA7" t="n">
-        <v>110</v>
+        <v>60</v>
       </c>
       <c r="AB7" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>50</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>32</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>50</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>48</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>80</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>230</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>60</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>70</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AQ7" t="n">
         <v>7.6</v>
       </c>
-      <c r="AC7" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>80</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH7" t="n">
+      <c r="AR7" t="n">
+        <v>16</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>23</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>13</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>36</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>28</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>34</v>
+      </c>
+      <c r="BD7" t="n">
         <v>29</v>
       </c>
-      <c r="AI7" t="n">
-        <v>130</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>32</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>34</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>65</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>32</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>150</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AR7" t="n">
+      <c r="BE7" t="n">
+        <v>55</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>20</v>
+      </c>
+      <c r="BG7" t="n">
         <v>22</v>
       </c>
-      <c r="AS7" t="n">
-        <v>55</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>14</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>38</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>10</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>22</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>60</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>24</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>24</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>44</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>28</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>24</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>9.6</v>
-      </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-25 06:20:07</t>
+          <t>2026-03-25 08:25:18</t>
         </is>
       </c>
     </row>
@@ -1921,16 +1921,16 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="G8" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="H8" t="n">
         <v>5.9</v>
       </c>
       <c r="I8" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="J8" t="n">
         <v>3.65</v>
@@ -1939,7 +1939,7 @@
         <v>4.1</v>
       </c>
       <c r="L8" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="M8" t="n">
         <v>1.09</v>
@@ -1948,10 +1948,10 @@
         <v>3.3</v>
       </c>
       <c r="O8" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="P8" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="Q8" t="n">
         <v>2.16</v>
@@ -1969,7 +1969,7 @@
         <v>1.78</v>
       </c>
       <c r="V8" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="W8" t="n">
         <v>2.28</v>
@@ -1978,22 +1978,22 @@
         <v>12</v>
       </c>
       <c r="Y8" t="n">
-        <v>18.5</v>
+        <v>29</v>
       </c>
       <c r="Z8" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AA8" t="n">
         <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AC8" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AD8" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="AE8" t="n">
         <v>1000</v>
@@ -2017,7 +2017,7 @@
         <v>22</v>
       </c>
       <c r="AL8" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AM8" t="n">
         <v>1000</v>
@@ -2035,10 +2035,10 @@
         <v>15</v>
       </c>
       <c r="AR8" t="n">
+        <v>23</v>
+      </c>
+      <c r="AS8" t="n">
         <v>9.6</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>9.800000000000001</v>
       </c>
       <c r="AT8" t="n">
         <v>5.9</v>
@@ -2047,10 +2047,10 @@
         <v>7.4</v>
       </c>
       <c r="AV8" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX8" t="n">
         <v>8.199999999999999</v>
@@ -2062,7 +2062,7 @@
         <v>20</v>
       </c>
       <c r="BA8" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB8" t="n">
         <v>15.5</v>
@@ -2071,20 +2071,20 @@
         <v>18</v>
       </c>
       <c r="BD8" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE8" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BF8" t="n">
         <v>12</v>
       </c>
       <c r="BG8" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-25 06:20:07</t>
+          <t>2026-03-25 08:25:18</t>
         </is>
       </c>
     </row>
@@ -2115,28 +2115,28 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="G9" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="H9" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="I9" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="J9" t="n">
         <v>3.05</v>
       </c>
       <c r="K9" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="L9" t="n">
         <v>1.5</v>
       </c>
       <c r="M9" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="N9" t="n">
         <v>3.1</v>
@@ -2145,70 +2145,70 @@
         <v>1.4</v>
       </c>
       <c r="P9" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="R9" t="n">
         <v>1.26</v>
       </c>
       <c r="S9" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="T9" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="U9" t="n">
-        <v>1.98</v>
+        <v>1.9</v>
       </c>
       <c r="V9" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="W9" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="X9" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="Y9" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="Z9" t="n">
         <v>1000</v>
       </c>
       <c r="AA9" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB9" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AC9" t="n">
-        <v>42</v>
+        <v>7.8</v>
       </c>
       <c r="AD9" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AE9" t="n">
         <v>1000</v>
       </c>
       <c r="AF9" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AG9" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AH9" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AI9" t="n">
         <v>1000</v>
       </c>
       <c r="AJ9" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AK9" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AL9" t="n">
         <v>1000</v>
@@ -2217,68 +2217,68 @@
         <v>1000</v>
       </c>
       <c r="AN9" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AO9" t="n">
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>5.6</v>
+        <v>8</v>
       </c>
       <c r="AQ9" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.99</v>
+        <v>6.8</v>
       </c>
       <c r="AS9" t="n">
-        <v>2.06</v>
+        <v>6.8</v>
       </c>
       <c r="AT9" t="n">
-        <v>3.4</v>
+        <v>7.4</v>
       </c>
       <c r="AU9" t="n">
-        <v>3.6</v>
+        <v>5.8</v>
       </c>
       <c r="AV9" t="n">
         <v>7.6</v>
       </c>
       <c r="AW9" t="n">
-        <v>2.04</v>
+        <v>7.6</v>
       </c>
       <c r="AX9" t="n">
-        <v>2.06</v>
+        <v>9.4</v>
       </c>
       <c r="AY9" t="n">
-        <v>4.9</v>
+        <v>8</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.97</v>
+        <v>15</v>
       </c>
       <c r="BA9" t="n">
-        <v>2.06</v>
+        <v>6.4</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.99</v>
+        <v>11.5</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.98</v>
+        <v>12</v>
       </c>
       <c r="BD9" t="n">
-        <v>2.02</v>
+        <v>7.2</v>
       </c>
       <c r="BE9" t="n">
-        <v>2.06</v>
+        <v>6.8</v>
       </c>
       <c r="BF9" t="n">
-        <v>2.06</v>
+        <v>6</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.06</v>
+        <v>6.6</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-25 06:20:07</t>
+          <t>2026-03-25 08:25:18</t>
         </is>
       </c>
     </row>
@@ -2309,19 +2309,19 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.98</v>
+        <v>2.82</v>
       </c>
       <c r="G10" t="n">
-        <v>3.25</v>
+        <v>2.96</v>
       </c>
       <c r="H10" t="n">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="I10" t="n">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="J10" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="K10" t="n">
         <v>2.82</v>
@@ -2333,64 +2333,64 @@
         <v>1.18</v>
       </c>
       <c r="N10" t="n">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="O10" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="P10" t="n">
         <v>1.41</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="R10" t="n">
         <v>1.13</v>
       </c>
       <c r="S10" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="T10" t="n">
         <v>2.26</v>
       </c>
       <c r="U10" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="V10" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="W10" t="n">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="X10" t="n">
         <v>6.6</v>
       </c>
       <c r="Y10" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="Z10" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AA10" t="n">
-        <v>170</v>
+        <v>420</v>
       </c>
       <c r="AB10" t="n">
-        <v>9</v>
+        <v>7.4</v>
       </c>
       <c r="AC10" t="n">
         <v>6.8</v>
       </c>
       <c r="AD10" t="n">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="AE10" t="n">
         <v>160</v>
       </c>
       <c r="AF10" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AG10" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="AH10" t="n">
         <v>48</v>
@@ -2399,10 +2399,10 @@
         <v>540</v>
       </c>
       <c r="AJ10" t="n">
-        <v>160</v>
+        <v>210</v>
       </c>
       <c r="AK10" t="n">
-        <v>160</v>
+        <v>290</v>
       </c>
       <c r="AL10" t="n">
         <v>300</v>
@@ -2411,7 +2411,7 @@
         <v>1000</v>
       </c>
       <c r="AN10" t="n">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="AO10" t="n">
         <v>1000</v>
@@ -2420,59 +2420,59 @@
         <v>5.5</v>
       </c>
       <c r="AQ10" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AR10" t="n">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="AS10" t="n">
-        <v>20</v>
+        <v>9.4</v>
       </c>
       <c r="AT10" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="AU10" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AV10" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AW10" t="n">
-        <v>24</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX10" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AY10" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ10" t="n">
         <v>22</v>
       </c>
       <c r="BA10" t="n">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BB10" t="n">
         <v>18</v>
       </c>
       <c r="BC10" t="n">
-        <v>24</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BD10" t="n">
-        <v>8.6</v>
+        <v>29</v>
       </c>
       <c r="BE10" t="n">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="BF10" t="n">
         <v>10</v>
       </c>
       <c r="BG10" t="n">
-        <v>7.8</v>
+        <v>9.6</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-25 06:20:07</t>
+          <t>2026-03-25 08:25:18</t>
         </is>
       </c>
     </row>
@@ -2503,7 +2503,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="G11" t="n">
         <v>2.72</v>
@@ -2527,13 +2527,13 @@
         <v>1.13</v>
       </c>
       <c r="N11" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="O11" t="n">
         <v>1.54</v>
       </c>
       <c r="P11" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="Q11" t="n">
         <v>2.66</v>
@@ -2545,10 +2545,10 @@
         <v>5.4</v>
       </c>
       <c r="T11" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="U11" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="V11" t="n">
         <v>1.4</v>
@@ -2557,7 +2557,7 @@
         <v>1.58</v>
       </c>
       <c r="X11" t="n">
-        <v>13.5</v>
+        <v>8.6</v>
       </c>
       <c r="Y11" t="n">
         <v>13</v>
@@ -2569,13 +2569,13 @@
         <v>900</v>
       </c>
       <c r="AB11" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AC11" t="n">
         <v>7.2</v>
       </c>
       <c r="AD11" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="AE11" t="n">
         <v>120</v>
@@ -2584,37 +2584,37 @@
         <v>46</v>
       </c>
       <c r="AG11" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="AH11" t="n">
         <v>70</v>
       </c>
       <c r="AI11" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ11" t="n">
-        <v>220</v>
+        <v>100</v>
       </c>
       <c r="AK11" t="n">
         <v>140</v>
       </c>
       <c r="AL11" t="n">
-        <v>500</v>
+        <v>460</v>
       </c>
       <c r="AM11" t="n">
         <v>1000</v>
       </c>
       <c r="AN11" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AO11" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AP11" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AQ11" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AR11" t="n">
         <v>9.800000000000001</v>
@@ -2629,44 +2629,44 @@
         <v>6.4</v>
       </c>
       <c r="AV11" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AW11" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="AX11" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY11" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AZ11" t="n">
         <v>11.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>6.4</v>
+        <v>12</v>
       </c>
       <c r="BB11" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="BC11" t="n">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="BD11" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="BE11" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="BF11" t="n">
-        <v>34</v>
+        <v>10.5</v>
       </c>
       <c r="BG11" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-25 06:20:07</t>
+          <t>2026-03-25 08:25:18</t>
         </is>
       </c>
     </row>
@@ -2697,10 +2697,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="G12" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="H12" t="n">
         <v>4.5</v>
@@ -2709,31 +2709,31 @@
         <v>5.2</v>
       </c>
       <c r="J12" t="n">
-        <v>3.05</v>
+        <v>2.94</v>
       </c>
       <c r="K12" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="L12" t="n">
         <v>1.61</v>
       </c>
       <c r="M12" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="N12" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="O12" t="n">
         <v>1.57</v>
       </c>
       <c r="P12" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="R12" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="S12" t="n">
         <v>5.7</v>
@@ -2742,22 +2742,22 @@
         <v>2.2</v>
       </c>
       <c r="U12" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="V12" t="n">
         <v>1.25</v>
       </c>
       <c r="W12" t="n">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="X12" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="Y12" t="n">
         <v>12.5</v>
       </c>
       <c r="Z12" t="n">
-        <v>500</v>
+        <v>120</v>
       </c>
       <c r="AA12" t="n">
         <v>1000</v>
@@ -2769,31 +2769,31 @@
         <v>7.8</v>
       </c>
       <c r="AD12" t="n">
-        <v>70</v>
+        <v>38</v>
       </c>
       <c r="AE12" t="n">
         <v>1000</v>
       </c>
       <c r="AF12" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AG12" t="n">
-        <v>27</v>
+        <v>12.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AI12" t="n">
         <v>1000</v>
       </c>
       <c r="AJ12" t="n">
-        <v>120</v>
+        <v>65</v>
       </c>
       <c r="AK12" t="n">
         <v>75</v>
       </c>
       <c r="AL12" t="n">
-        <v>460</v>
+        <v>180</v>
       </c>
       <c r="AM12" t="n">
         <v>1000</v>
@@ -2814,53 +2814,53 @@
         <v>14.5</v>
       </c>
       <c r="AS12" t="n">
-        <v>12</v>
+        <v>8.6</v>
       </c>
       <c r="AT12" t="n">
         <v>5.6</v>
       </c>
       <c r="AU12" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AV12" t="n">
         <v>12</v>
       </c>
       <c r="AW12" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="AX12" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AY12" t="n">
-        <v>7.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ12" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>10</v>
+        <v>8.6</v>
       </c>
       <c r="BB12" t="n">
         <v>11</v>
       </c>
       <c r="BC12" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BD12" t="n">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="BE12" t="n">
-        <v>9.6</v>
+        <v>28</v>
       </c>
       <c r="BF12" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="BG12" t="n">
-        <v>6</v>
+        <v>8.6</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-25 06:20:07</t>
+          <t>2026-03-25 08:25:18</t>
         </is>
       </c>
     </row>
@@ -2891,22 +2891,22 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="G13" t="n">
-        <v>3.4</v>
+        <v>3.05</v>
       </c>
       <c r="H13" t="n">
-        <v>2.28</v>
+        <v>2.46</v>
       </c>
       <c r="I13" t="n">
-        <v>2.38</v>
+        <v>2.64</v>
       </c>
       <c r="J13" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="K13" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L13" t="n">
         <v>1.34</v>
@@ -2921,140 +2921,140 @@
         <v>1.24</v>
       </c>
       <c r="P13" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="R13" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="S13" t="n">
         <v>2.88</v>
       </c>
       <c r="T13" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="U13" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="V13" t="n">
-        <v>1.73</v>
+        <v>1.61</v>
       </c>
       <c r="W13" t="n">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="X13" t="n">
-        <v>90</v>
+        <v>18.5</v>
       </c>
       <c r="Y13" t="n">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="Z13" t="n">
+        <v>34</v>
+      </c>
+      <c r="AA13" t="n">
         <v>500</v>
       </c>
-      <c r="AA13" t="n">
+      <c r="AB13" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>25</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI13" t="n">
         <v>34</v>
       </c>
-      <c r="AB13" t="n">
-        <v>17</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>20</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>65</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>25</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>15</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>16</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>75</v>
-      </c>
       <c r="AJ13" t="n">
-        <v>900</v>
+        <v>50</v>
       </c>
       <c r="AK13" t="n">
-        <v>500</v>
+        <v>80</v>
       </c>
       <c r="AL13" t="n">
-        <v>500</v>
+        <v>95</v>
       </c>
       <c r="AM13" t="n">
-        <v>320</v>
+        <v>70</v>
       </c>
       <c r="AN13" t="n">
-        <v>29</v>
+        <v>600</v>
       </c>
       <c r="AO13" t="n">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="AP13" t="n">
         <v>10.5</v>
       </c>
       <c r="AQ13" t="n">
-        <v>7</v>
+        <v>11.5</v>
       </c>
       <c r="AR13" t="n">
-        <v>13</v>
+        <v>8.4</v>
       </c>
       <c r="AS13" t="n">
         <v>14.5</v>
       </c>
       <c r="AT13" t="n">
-        <v>8.4</v>
+        <v>13.5</v>
       </c>
       <c r="AU13" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV13" t="n">
-        <v>6.2</v>
+        <v>7.8</v>
       </c>
       <c r="AW13" t="n">
-        <v>17</v>
+        <v>10.5</v>
       </c>
       <c r="AX13" t="n">
-        <v>11.5</v>
+        <v>19</v>
       </c>
       <c r="AY13" t="n">
         <v>11.5</v>
       </c>
       <c r="AZ13" t="n">
-        <v>8.6</v>
+        <v>12.5</v>
       </c>
       <c r="BA13" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>23</v>
+      </c>
+      <c r="BC13" t="n">
         <v>15</v>
       </c>
-      <c r="BB13" t="n">
-        <v>8</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>14.5</v>
-      </c>
       <c r="BD13" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="BE13" t="n">
-        <v>8.199999999999999</v>
+        <v>12.5</v>
       </c>
       <c r="BF13" t="n">
-        <v>6.8</v>
+        <v>18</v>
       </c>
       <c r="BG13" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-25 06:20:07</t>
+          <t>2026-03-25 08:25:18</t>
         </is>
       </c>
     </row>
@@ -3085,19 +3085,19 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.76</v>
+        <v>2.84</v>
       </c>
       <c r="G14" t="n">
         <v>2.9</v>
       </c>
       <c r="H14" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="I14" t="n">
-        <v>2.76</v>
+        <v>2.7</v>
       </c>
       <c r="J14" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K14" t="n">
         <v>3.7</v>
@@ -3115,7 +3115,7 @@
         <v>1.28</v>
       </c>
       <c r="P14" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="Q14" t="n">
         <v>1.88</v>
@@ -3130,28 +3130,28 @@
         <v>1.7</v>
       </c>
       <c r="U14" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="V14" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="W14" t="n">
         <v>1.52</v>
       </c>
       <c r="X14" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="Y14" t="n">
-        <v>500</v>
+        <v>19.5</v>
       </c>
       <c r="Z14" t="n">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="AA14" t="n">
-        <v>95</v>
+        <v>900</v>
       </c>
       <c r="AB14" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="AC14" t="n">
         <v>8.199999999999999</v>
@@ -3172,83 +3172,83 @@
         <v>25</v>
       </c>
       <c r="AI14" t="n">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="AJ14" t="n">
-        <v>46</v>
+        <v>100</v>
       </c>
       <c r="AK14" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AL14" t="n">
-        <v>40</v>
+        <v>150</v>
       </c>
       <c r="AM14" t="n">
         <v>200</v>
       </c>
       <c r="AN14" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AO14" t="n">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="AP14" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AQ14" t="n">
         <v>11</v>
       </c>
       <c r="AR14" t="n">
-        <v>16.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS14" t="n">
         <v>16</v>
       </c>
       <c r="AT14" t="n">
-        <v>11.5</v>
+        <v>7.8</v>
       </c>
       <c r="AU14" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AV14" t="n">
         <v>11</v>
       </c>
       <c r="AW14" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AX14" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AY14" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="AZ14" t="n">
         <v>9</v>
       </c>
       <c r="BA14" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="BB14" t="n">
         <v>20</v>
       </c>
       <c r="BC14" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="BD14" t="n">
         <v>20</v>
       </c>
       <c r="BE14" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BF14" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BG14" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-25 06:20:07</t>
+          <t>2026-03-25 08:25:18</t>
         </is>
       </c>
     </row>
@@ -3279,13 +3279,13 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="G15" t="n">
         <v>3.8</v>
       </c>
       <c r="H15" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="I15" t="n">
         <v>2.16</v>
@@ -3303,28 +3303,28 @@
         <v>1.05</v>
       </c>
       <c r="N15" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="O15" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P15" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="R15" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="S15" t="n">
-        <v>2.92</v>
+        <v>2.84</v>
       </c>
       <c r="T15" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="U15" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="V15" t="n">
         <v>1.86</v>
@@ -3333,19 +3333,19 @@
         <v>1.35</v>
       </c>
       <c r="X15" t="n">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="Y15" t="n">
         <v>12</v>
       </c>
       <c r="Z15" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AA15" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AB15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AC15" t="n">
         <v>9.199999999999999</v>
@@ -3357,16 +3357,16 @@
         <v>21</v>
       </c>
       <c r="AF15" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AG15" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AH15" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AI15" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AJ15" t="n">
         <v>65</v>
@@ -3381,28 +3381,28 @@
         <v>75</v>
       </c>
       <c r="AN15" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AO15" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AP15" t="n">
         <v>16.5</v>
       </c>
       <c r="AQ15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AR15" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AS15" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AT15" t="n">
         <v>15</v>
       </c>
       <c r="AU15" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AV15" t="n">
         <v>9.4</v>
@@ -3411,7 +3411,7 @@
         <v>17.5</v>
       </c>
       <c r="AX15" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AY15" t="n">
         <v>13.5</v>
@@ -3420,10 +3420,10 @@
         <v>14</v>
       </c>
       <c r="BA15" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BB15" t="n">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="BC15" t="n">
         <v>32</v>
@@ -3432,17 +3432,17 @@
         <v>36</v>
       </c>
       <c r="BE15" t="n">
-        <v>13.5</v>
+        <v>34</v>
       </c>
       <c r="BF15" t="n">
         <v>27</v>
       </c>
       <c r="BG15" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-25 06:20:07</t>
+          <t>2026-03-25 08:25:18</t>
         </is>
       </c>
     </row>
@@ -3473,22 +3473,22 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="G16" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="H16" t="n">
         <v>2.12</v>
       </c>
       <c r="I16" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="J16" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="K16" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L16" t="n">
         <v>1.33</v>
@@ -3497,64 +3497,64 @@
         <v>1.04</v>
       </c>
       <c r="N16" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="O16" t="n">
         <v>1.22</v>
       </c>
       <c r="P16" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="R16" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="S16" t="n">
         <v>2.74</v>
       </c>
       <c r="T16" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="U16" t="n">
         <v>2.48</v>
       </c>
       <c r="V16" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="W16" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="X16" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="Y16" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Z16" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AB16" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AC16" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AD16" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AE16" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AF16" t="n">
         <v>28</v>
       </c>
       <c r="AG16" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AH16" t="n">
         <v>15.5</v>
@@ -3563,7 +3563,7 @@
         <v>30</v>
       </c>
       <c r="AJ16" t="n">
-        <v>150</v>
+        <v>65</v>
       </c>
       <c r="AK16" t="n">
         <v>38</v>
@@ -3578,65 +3578,65 @@
         <v>30</v>
       </c>
       <c r="AO16" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AP16" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AQ16" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AR16" t="n">
+        <v>14</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>22</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>24</v>
+      </c>
+      <c r="AY16" t="n">
         <v>13.5</v>
       </c>
-      <c r="AS16" t="n">
-        <v>21</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>16</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>22</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>13</v>
-      </c>
       <c r="AZ16" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="BA16" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="BB16" t="n">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="BC16" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BD16" t="n">
         <v>21</v>
       </c>
       <c r="BE16" t="n">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="BF16" t="n">
         <v>24</v>
       </c>
       <c r="BG16" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-25 06:20:07</t>
+          <t>2026-03-25 08:25:18</t>
         </is>
       </c>
     </row>
@@ -3673,31 +3673,31 @@
         <v>1.74</v>
       </c>
       <c r="H17" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="I17" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="J17" t="n">
         <v>4.1</v>
       </c>
       <c r="K17" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="L17" t="n">
         <v>1.37</v>
       </c>
       <c r="M17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N17" t="n">
         <v>4.3</v>
       </c>
       <c r="O17" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="P17" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="Q17" t="n">
         <v>1.81</v>
@@ -3706,28 +3706,28 @@
         <v>1.43</v>
       </c>
       <c r="S17" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="T17" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="U17" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="V17" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="W17" t="n">
         <v>2.34</v>
       </c>
       <c r="X17" t="n">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="Y17" t="n">
         <v>21</v>
       </c>
       <c r="Z17" t="n">
-        <v>110</v>
+        <v>46</v>
       </c>
       <c r="AA17" t="n">
         <v>900</v>
@@ -3736,7 +3736,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AC17" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AD17" t="n">
         <v>21</v>
@@ -3745,7 +3745,7 @@
         <v>75</v>
       </c>
       <c r="AF17" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AG17" t="n">
         <v>10</v>
@@ -3754,83 +3754,83 @@
         <v>20</v>
       </c>
       <c r="AI17" t="n">
-        <v>75</v>
+        <v>320</v>
       </c>
       <c r="AJ17" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AK17" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AL17" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AM17" t="n">
-        <v>580</v>
+        <v>110</v>
       </c>
       <c r="AN17" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AO17" t="n">
-        <v>600</v>
+        <v>310</v>
       </c>
       <c r="AP17" t="n">
         <v>15.5</v>
       </c>
       <c r="AQ17" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AR17" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AS17" t="n">
-        <v>9.6</v>
+        <v>14.5</v>
       </c>
       <c r="AT17" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AU17" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AV17" t="n">
+        <v>18</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>32</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ17" t="n">
         <v>17.5</v>
       </c>
-      <c r="AW17" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>9</v>
-      </c>
-      <c r="AY17" t="n">
+      <c r="BA17" t="n">
+        <v>30</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>28</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>36</v>
+      </c>
+      <c r="BF17" t="n">
         <v>8.4</v>
       </c>
-      <c r="AZ17" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>9</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>14</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>25</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>7.6</v>
-      </c>
       <c r="BG17" t="n">
-        <v>23</v>
+        <v>13.5</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-25 06:20:07</t>
+          <t>2026-03-25 08:25:18</t>
         </is>
       </c>
     </row>
@@ -3861,10 +3861,10 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="G18" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="H18" t="n">
         <v>4.1</v>
@@ -3873,158 +3873,158 @@
         <v>4.5</v>
       </c>
       <c r="J18" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="K18" t="n">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="L18" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="M18" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N18" t="n">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="O18" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="P18" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.02</v>
+        <v>1.93</v>
       </c>
       <c r="R18" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="S18" t="n">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="T18" t="n">
-        <v>1.86</v>
+        <v>1.76</v>
       </c>
       <c r="U18" t="n">
-        <v>2.06</v>
+        <v>2.16</v>
       </c>
       <c r="V18" t="n">
         <v>1.29</v>
       </c>
       <c r="W18" t="n">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="X18" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Y18" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Z18" t="n">
         <v>32</v>
       </c>
       <c r="AA18" t="n">
-        <v>95</v>
+        <v>900</v>
       </c>
       <c r="AB18" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC18" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="AD18" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AE18" t="n">
         <v>55</v>
       </c>
       <c r="AF18" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AG18" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH18" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AI18" t="n">
-        <v>65</v>
+        <v>320</v>
       </c>
       <c r="AJ18" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AK18" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL18" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AM18" t="n">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="AN18" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AO18" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AP18" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AQ18" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AR18" t="n">
         <v>27</v>
       </c>
       <c r="AS18" t="n">
-        <v>75</v>
+        <v>16</v>
       </c>
       <c r="AT18" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AU18" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AV18" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AW18" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AX18" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AY18" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="AZ18" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="BB18" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="BC18" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="BD18" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BE18" t="n">
+        <v>60</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>12</v>
+      </c>
+      <c r="BG18" t="n">
         <v>14</v>
       </c>
-      <c r="BF18" t="n">
-        <v>14</v>
-      </c>
-      <c r="BG18" t="n">
-        <v>27</v>
-      </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-25 06:20:07</t>
+          <t>2026-03-25 08:25:18</t>
         </is>
       </c>
     </row>
@@ -4055,40 +4055,40 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="G19" t="n">
         <v>1.62</v>
       </c>
       <c r="H19" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="I19" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J19" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="K19" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="L19" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="M19" t="n">
         <v>1.09</v>
       </c>
       <c r="N19" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="O19" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="P19" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="R19" t="n">
         <v>1.26</v>
@@ -4097,16 +4097,16 @@
         <v>4.2</v>
       </c>
       <c r="T19" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="U19" t="n">
         <v>1.68</v>
       </c>
       <c r="V19" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="W19" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="X19" t="n">
         <v>970</v>
@@ -4136,19 +4136,19 @@
         <v>40</v>
       </c>
       <c r="AG19" t="n">
+        <v>36</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>500</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>500</v>
+      </c>
+      <c r="AK19" t="n">
         <v>970</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>65</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>900</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>65</v>
       </c>
       <c r="AL19" t="n">
         <v>500</v>
@@ -4166,59 +4166,59 @@
         <v>5.6</v>
       </c>
       <c r="AQ19" t="n">
-        <v>15.5</v>
+        <v>9.6</v>
       </c>
       <c r="AR19" t="n">
-        <v>4.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS19" t="n">
-        <v>4.2</v>
+        <v>5.8</v>
       </c>
       <c r="AT19" t="n">
-        <v>3.95</v>
+        <v>5.5</v>
       </c>
       <c r="AU19" t="n">
         <v>6.2</v>
       </c>
       <c r="AV19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AW19" t="n">
-        <v>4.2</v>
+        <v>5.7</v>
       </c>
       <c r="AX19" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AY19" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="AZ19" t="n">
-        <v>6.8</v>
+        <v>13</v>
       </c>
       <c r="BA19" t="n">
-        <v>4.2</v>
+        <v>5.7</v>
       </c>
       <c r="BB19" t="n">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="BC19" t="n">
-        <v>11.5</v>
+        <v>9</v>
       </c>
       <c r="BD19" t="n">
-        <v>34</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE19" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BF19" t="n">
         <v>9.6</v>
       </c>
       <c r="BG19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-25 06:20:07</t>
+          <t>2026-03-25 08:25:18</t>
         </is>
       </c>
     </row>
@@ -4249,46 +4249,46 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="G20" t="n">
         <v>3.3</v>
       </c>
       <c r="H20" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="I20" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="J20" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="K20" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="L20" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="M20" t="n">
         <v>1.13</v>
       </c>
       <c r="N20" t="n">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="O20" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="P20" t="n">
         <v>1.54</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.74</v>
+        <v>2.68</v>
       </c>
       <c r="R20" t="n">
         <v>1.19</v>
       </c>
       <c r="S20" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="T20" t="n">
         <v>2.1</v>
@@ -4303,43 +4303,43 @@
         <v>1.44</v>
       </c>
       <c r="X20" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="Y20" t="n">
         <v>8.4</v>
       </c>
-      <c r="Y20" t="n">
-        <v>9</v>
-      </c>
       <c r="Z20" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AA20" t="n">
         <v>900</v>
       </c>
       <c r="AB20" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC20" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AD20" t="n">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="AE20" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AF20" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="AG20" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AH20" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AI20" t="n">
         <v>500</v>
       </c>
       <c r="AJ20" t="n">
-        <v>900</v>
+        <v>220</v>
       </c>
       <c r="AK20" t="n">
         <v>500</v>
@@ -4351,49 +4351,49 @@
         <v>500</v>
       </c>
       <c r="AN20" t="n">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="AO20" t="n">
         <v>600</v>
       </c>
       <c r="AP20" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AQ20" t="n">
         <v>7.4</v>
       </c>
       <c r="AR20" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AS20" t="n">
         <v>24</v>
       </c>
       <c r="AT20" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AU20" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AV20" t="n">
         <v>11.5</v>
       </c>
       <c r="AW20" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AX20" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AY20" t="n">
         <v>13</v>
       </c>
       <c r="AZ20" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BA20" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="BB20" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="BC20" t="n">
         <v>26</v>
@@ -4402,17 +4402,17 @@
         <v>48</v>
       </c>
       <c r="BE20" t="n">
-        <v>70</v>
+        <v>95</v>
       </c>
       <c r="BF20" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BG20" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-25 06:20:07</t>
+          <t>2026-03-25 08:25:18</t>
         </is>
       </c>
     </row>
@@ -4443,22 +4443,22 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="G21" t="n">
         <v>2.7</v>
       </c>
       <c r="H21" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="I21" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="J21" t="n">
-        <v>2.78</v>
+        <v>2.72</v>
       </c>
       <c r="K21" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="L21" t="n">
         <v>1.85</v>
@@ -4467,16 +4467,16 @@
         <v>1.22</v>
       </c>
       <c r="N21" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="O21" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="P21" t="n">
         <v>1.3</v>
       </c>
       <c r="Q21" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="R21" t="n">
         <v>1.09</v>
@@ -4491,28 +4491,28 @@
         <v>1.47</v>
       </c>
       <c r="V21" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="W21" t="n">
         <v>1.58</v>
       </c>
       <c r="X21" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="Y21" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="Z21" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AA21" t="n">
         <v>500</v>
       </c>
       <c r="AB21" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AC21" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AD21" t="n">
         <v>21</v>
@@ -4521,19 +4521,19 @@
         <v>110</v>
       </c>
       <c r="AF21" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AG21" t="n">
         <v>16.5</v>
       </c>
       <c r="AH21" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AI21" t="n">
         <v>200</v>
       </c>
       <c r="AJ21" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AK21" t="n">
         <v>60</v>
@@ -4554,13 +4554,13 @@
         <v>5.1</v>
       </c>
       <c r="AQ21" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AR21" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AS21" t="n">
-        <v>48</v>
+        <v>80</v>
       </c>
       <c r="AT21" t="n">
         <v>5.6</v>
@@ -4569,10 +4569,10 @@
         <v>6.6</v>
       </c>
       <c r="AV21" t="n">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="AW21" t="n">
-        <v>48</v>
+        <v>75</v>
       </c>
       <c r="AX21" t="n">
         <v>12.5</v>
@@ -4581,32 +4581,32 @@
         <v>14.5</v>
       </c>
       <c r="AZ21" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="BA21" t="n">
-        <v>48</v>
+        <v>70</v>
       </c>
       <c r="BB21" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="BC21" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="BD21" t="n">
-        <v>70</v>
+        <v>44</v>
       </c>
       <c r="BE21" t="n">
         <v>120</v>
       </c>
       <c r="BF21" t="n">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="BG21" t="n">
         <v>50</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-25 06:20:07</t>
+          <t>2026-03-25 08:25:18</t>
         </is>
       </c>
     </row>
@@ -4637,19 +4637,19 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="G22" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="H22" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="I22" t="n">
         <v>4.9</v>
       </c>
       <c r="J22" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="K22" t="n">
         <v>3.7</v>
@@ -4661,7 +4661,7 @@
         <v>1.09</v>
       </c>
       <c r="N22" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="O22" t="n">
         <v>1.39</v>
@@ -4670,25 +4670,25 @@
         <v>1.81</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="R22" t="n">
         <v>1.28</v>
       </c>
       <c r="S22" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="T22" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="U22" t="n">
         <v>2</v>
       </c>
       <c r="V22" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="W22" t="n">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="X22" t="n">
         <v>12</v>
@@ -4697,7 +4697,7 @@
         <v>14.5</v>
       </c>
       <c r="Z22" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AA22" t="n">
         <v>900</v>
@@ -4709,7 +4709,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AD22" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AE22" t="n">
         <v>170</v>
@@ -4721,19 +4721,19 @@
         <v>11</v>
       </c>
       <c r="AH22" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AI22" t="n">
-        <v>90</v>
+        <v>370</v>
       </c>
       <c r="AJ22" t="n">
         <v>25</v>
       </c>
       <c r="AK22" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AL22" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AM22" t="n">
         <v>580</v>
@@ -4742,65 +4742,65 @@
         <v>19.5</v>
       </c>
       <c r="AO22" t="n">
-        <v>95</v>
+        <v>290</v>
       </c>
       <c r="AP22" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ22" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AR22" t="n">
         <v>13</v>
       </c>
       <c r="AS22" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AT22" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AU22" t="n">
         <v>6.8</v>
       </c>
       <c r="AV22" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="AW22" t="n">
-        <v>23</v>
+        <v>9.6</v>
       </c>
       <c r="AX22" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY22" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ22" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BA22" t="n">
-        <v>9.199999999999999</v>
+        <v>28</v>
       </c>
       <c r="BB22" t="n">
         <v>20</v>
       </c>
       <c r="BC22" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BD22" t="n">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="BE22" t="n">
         <v>9.6</v>
       </c>
       <c r="BF22" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BG22" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-25 06:20:07</t>
+          <t>2026-03-25 08:25:18</t>
         </is>
       </c>
     </row>
@@ -4834,7 +4834,7 @@
         <v>1.96</v>
       </c>
       <c r="G23" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="H23" t="n">
         <v>4.4</v>
@@ -4849,7 +4849,7 @@
         <v>3.7</v>
       </c>
       <c r="L23" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="M23" t="n">
         <v>1.09</v>
@@ -4858,7 +4858,7 @@
         <v>3.15</v>
       </c>
       <c r="O23" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="P23" t="n">
         <v>1.71</v>
@@ -4873,16 +4873,16 @@
         <v>4.4</v>
       </c>
       <c r="T23" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="U23" t="n">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="V23" t="n">
         <v>1.27</v>
       </c>
       <c r="W23" t="n">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="X23" t="n">
         <v>22</v>
@@ -4897,13 +4897,13 @@
         <v>1000</v>
       </c>
       <c r="AB23" t="n">
-        <v>7.8</v>
+        <v>17</v>
       </c>
       <c r="AC23" t="n">
-        <v>9.199999999999999</v>
+        <v>14</v>
       </c>
       <c r="AD23" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AE23" t="n">
         <v>1000</v>
@@ -4939,16 +4939,16 @@
         <v>1000</v>
       </c>
       <c r="AP23" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="AQ23" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AR23" t="n">
-        <v>8.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AS23" t="n">
-        <v>4</v>
+        <v>2.24</v>
       </c>
       <c r="AT23" t="n">
         <v>6.6</v>
@@ -4957,44 +4957,44 @@
         <v>7</v>
       </c>
       <c r="AV23" t="n">
-        <v>16</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AW23" t="n">
-        <v>7.4</v>
+        <v>3.05</v>
       </c>
       <c r="AX23" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="AY23" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="AZ23" t="n">
-        <v>7.4</v>
+        <v>3.8</v>
       </c>
       <c r="BA23" t="n">
-        <v>9.6</v>
+        <v>3.05</v>
       </c>
       <c r="BB23" t="n">
-        <v>7.4</v>
+        <v>9</v>
       </c>
       <c r="BC23" t="n">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="BD23" t="n">
-        <v>8.800000000000001</v>
+        <v>4.4</v>
       </c>
       <c r="BE23" t="n">
-        <v>10</v>
+        <v>2.26</v>
       </c>
       <c r="BF23" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG23" t="n">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-25 06:20:07</t>
+          <t>2026-03-25 08:25:18</t>
         </is>
       </c>
     </row>
@@ -5031,10 +5031,10 @@
         <v>1.65</v>
       </c>
       <c r="H24" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="I24" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="J24" t="n">
         <v>3.75</v>
@@ -5067,7 +5067,7 @@
         <v>3.9</v>
       </c>
       <c r="T24" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="U24" t="n">
         <v>1.74</v>
@@ -5076,10 +5076,10 @@
         <v>1.13</v>
       </c>
       <c r="W24" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="X24" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Y24" t="n">
         <v>1000</v>
@@ -5091,10 +5091,10 @@
         <v>1000</v>
       </c>
       <c r="AB24" t="n">
-        <v>27</v>
+        <v>7.2</v>
       </c>
       <c r="AC24" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AD24" t="n">
         <v>1000</v>
@@ -5121,7 +5121,7 @@
         <v>1000</v>
       </c>
       <c r="AL24" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AM24" t="n">
         <v>1000</v>
@@ -5133,7 +5133,7 @@
         <v>1000</v>
       </c>
       <c r="AP24" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="AQ24" t="n">
         <v>4.2</v>
@@ -5145,10 +5145,10 @@
         <v>4.2</v>
       </c>
       <c r="AT24" t="n">
-        <v>5.6</v>
+        <v>4.3</v>
       </c>
       <c r="AU24" t="n">
-        <v>7.2</v>
+        <v>5</v>
       </c>
       <c r="AV24" t="n">
         <v>4.2</v>
@@ -5157,38 +5157,38 @@
         <v>4.2</v>
       </c>
       <c r="AX24" t="n">
-        <v>6.8</v>
+        <v>4.7</v>
       </c>
       <c r="AY24" t="n">
-        <v>7.8</v>
+        <v>5.1</v>
       </c>
       <c r="AZ24" t="n">
-        <v>2.12</v>
+        <v>3.6</v>
       </c>
       <c r="BA24" t="n">
         <v>4.2</v>
       </c>
       <c r="BB24" t="n">
-        <v>6.4</v>
+        <v>3.55</v>
       </c>
       <c r="BC24" t="n">
-        <v>7</v>
+        <v>3.45</v>
       </c>
       <c r="BD24" t="n">
-        <v>3.55</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE24" t="n">
-        <v>3.2</v>
+        <v>3.75</v>
       </c>
       <c r="BF24" t="n">
-        <v>8.4</v>
+        <v>5.3</v>
       </c>
       <c r="BG24" t="n">
         <v>4.2</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-25 06:20:07</t>
+          <t>2026-03-25 08:25:18</t>
         </is>
       </c>
     </row>
@@ -5228,43 +5228,43 @@
         <v>4.5</v>
       </c>
       <c r="I25" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="J25" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K25" t="n">
         <v>4.5</v>
       </c>
       <c r="L25" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="M25" t="n">
         <v>1.06</v>
       </c>
       <c r="N25" t="n">
-        <v>1.39</v>
+        <v>4.1</v>
       </c>
       <c r="O25" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="P25" t="n">
-        <v>1.39</v>
+        <v>2.1</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.26</v>
+        <v>1.76</v>
       </c>
       <c r="R25" t="n">
         <v>1.42</v>
       </c>
       <c r="S25" t="n">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="T25" t="n">
-        <v>1.01</v>
+        <v>1.78</v>
       </c>
       <c r="U25" t="n">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="V25" t="n">
         <v>1.2</v>
@@ -5273,7 +5273,7 @@
         <v>2.26</v>
       </c>
       <c r="X25" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="Y25" t="n">
         <v>1000</v>
@@ -5288,7 +5288,7 @@
         <v>1000</v>
       </c>
       <c r="AC25" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AD25" t="n">
         <v>1000</v>
@@ -5300,10 +5300,10 @@
         <v>1000</v>
       </c>
       <c r="AG25" t="n">
-        <v>500</v>
+        <v>36</v>
       </c>
       <c r="AH25" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AI25" t="n">
         <v>1000</v>
@@ -5327,62 +5327,62 @@
         <v>1000</v>
       </c>
       <c r="AP25" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="AQ25" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="AR25" t="n">
-        <v>2</v>
+        <v>2.36</v>
       </c>
       <c r="AS25" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="AT25" t="n">
-        <v>4.8</v>
+        <v>7</v>
       </c>
       <c r="AU25" t="n">
-        <v>4.8</v>
+        <v>7</v>
       </c>
       <c r="AV25" t="n">
-        <v>3.85</v>
+        <v>3.05</v>
       </c>
       <c r="AW25" t="n">
-        <v>2.22</v>
+        <v>2.92</v>
       </c>
       <c r="AX25" t="n">
-        <v>2.96</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY25" t="n">
-        <v>3.1</v>
+        <v>7.4</v>
       </c>
       <c r="AZ25" t="n">
-        <v>2.32</v>
+        <v>2.92</v>
       </c>
       <c r="BA25" t="n">
-        <v>1.97</v>
+        <v>2.34</v>
       </c>
       <c r="BB25" t="n">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="BC25" t="n">
-        <v>2.48</v>
+        <v>3.8</v>
       </c>
       <c r="BD25" t="n">
-        <v>1.93</v>
+        <v>2.78</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.99</v>
+        <v>2.36</v>
       </c>
       <c r="BF25" t="n">
-        <v>3.8</v>
+        <v>7.2</v>
       </c>
       <c r="BG25" t="n">
-        <v>2.02</v>
+        <v>2.34</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-25 06:20:07</t>
+          <t>2026-03-25 08:25:18</t>
         </is>
       </c>
     </row>
@@ -5413,61 +5413,61 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="G26" t="n">
-        <v>1.69</v>
+        <v>1.82</v>
       </c>
       <c r="H26" t="n">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="I26" t="n">
-        <v>6.2</v>
+        <v>5.3</v>
       </c>
       <c r="J26" t="n">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="K26" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="L26" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="M26" t="n">
         <v>1.06</v>
       </c>
       <c r="N26" t="n">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="O26" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="P26" t="n">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="R26" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="S26" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="T26" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="U26" t="n">
         <v>2.06</v>
       </c>
       <c r="V26" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="W26" t="n">
-        <v>2.44</v>
+        <v>2.2</v>
       </c>
       <c r="X26" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="Y26" t="n">
         <v>40</v>
@@ -5482,101 +5482,101 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AC26" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AD26" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AE26" t="n">
         <v>400</v>
       </c>
       <c r="AF26" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AG26" t="n">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="AH26" t="n">
-        <v>21</v>
+        <v>60</v>
       </c>
       <c r="AI26" t="n">
         <v>700</v>
       </c>
       <c r="AJ26" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AK26" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="AL26" t="n">
-        <v>150</v>
+        <v>80</v>
       </c>
       <c r="AM26" t="n">
         <v>580</v>
       </c>
       <c r="AN26" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AO26" t="n">
-        <v>700</v>
+        <v>160</v>
       </c>
       <c r="AP26" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AQ26" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AR26" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="AS26" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>16</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>28</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>29</v>
+      </c>
+      <c r="BB26" t="n">
         <v>7.6</v>
       </c>
-      <c r="AT26" t="n">
-        <v>8</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>17</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AX26" t="n">
+      <c r="BC26" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>21</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BF26" t="n">
         <v>9.6</v>
       </c>
-      <c r="AY26" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AZ26" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BA26" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BB26" t="n">
-        <v>13</v>
-      </c>
-      <c r="BC26" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BD26" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BE26" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BF26" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="BG26" t="n">
-        <v>7.4</v>
+        <v>9.4</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-25 06:20:07</t>
+          <t>2026-03-25 08:25:18</t>
         </is>
       </c>
     </row>
@@ -5607,22 +5607,22 @@
         </is>
       </c>
       <c r="F27" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="G27" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="H27" t="n">
         <v>2.7</v>
       </c>
-      <c r="G27" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="H27" t="n">
-        <v>2.62</v>
-      </c>
       <c r="I27" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="J27" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="K27" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="L27" t="n">
         <v>1.38</v>
@@ -5634,7 +5634,7 @@
         <v>4.1</v>
       </c>
       <c r="O27" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="P27" t="n">
         <v>2.06</v>
@@ -5643,134 +5643,134 @@
         <v>1.86</v>
       </c>
       <c r="R27" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S27" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="T27" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="U27" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="V27" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="W27" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="X27" t="n">
-        <v>26</v>
+        <v>16.5</v>
       </c>
       <c r="Y27" t="n">
         <v>13</v>
       </c>
       <c r="Z27" t="n">
-        <v>38</v>
+        <v>19.5</v>
       </c>
       <c r="AA27" t="n">
-        <v>900</v>
+        <v>44</v>
       </c>
       <c r="AB27" t="n">
         <v>13.5</v>
       </c>
       <c r="AC27" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD27" t="n">
         <v>12</v>
       </c>
       <c r="AE27" t="n">
+        <v>29</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>20</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>40</v>
+      </c>
+      <c r="AJ27" t="n">
         <v>85</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>21</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>16</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>120</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>900</v>
       </c>
       <c r="AK27" t="n">
         <v>75</v>
       </c>
       <c r="AL27" t="n">
-        <v>95</v>
+        <v>40</v>
       </c>
       <c r="AM27" t="n">
-        <v>580</v>
+        <v>80</v>
       </c>
       <c r="AN27" t="n">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="AO27" t="n">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="AP27" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AQ27" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>36</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>12</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV27" t="n">
         <v>10.5</v>
       </c>
-      <c r="AR27" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>10</v>
-      </c>
       <c r="AW27" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="AX27" t="n">
-        <v>14.5</v>
+        <v>9.6</v>
       </c>
       <c r="AY27" t="n">
-        <v>8.6</v>
+        <v>10.5</v>
       </c>
       <c r="AZ27" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BA27" t="n">
-        <v>8.4</v>
+        <v>23</v>
       </c>
       <c r="BB27" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="BC27" t="n">
+        <v>26</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>32</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BF27" t="n">
         <v>20</v>
-      </c>
-      <c r="BD27" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BE27" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BF27" t="n">
-        <v>16.5</v>
       </c>
       <c r="BG27" t="n">
         <v>20</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-25 06:20:07</t>
+          <t>2026-03-25 08:25:18</t>
         </is>
       </c>
     </row>
@@ -5804,16 +5804,16 @@
         <v>6.6</v>
       </c>
       <c r="G28" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="H28" t="n">
         <v>1.66</v>
       </c>
       <c r="I28" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="J28" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="K28" t="n">
         <v>4</v>
@@ -5843,52 +5843,52 @@
         <v>4.5</v>
       </c>
       <c r="T28" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="U28" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="V28" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="W28" t="n">
         <v>1.16</v>
       </c>
       <c r="X28" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="Y28" t="n">
         <v>6.6</v>
       </c>
       <c r="Z28" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AA28" t="n">
-        <v>21</v>
+        <v>16.5</v>
       </c>
       <c r="AB28" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AC28" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AD28" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AE28" t="n">
+        <v>22</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>120</v>
+      </c>
+      <c r="AG28" t="n">
         <v>29</v>
       </c>
-      <c r="AF28" t="n">
-        <v>270</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>950</v>
-      </c>
       <c r="AH28" t="n">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="AI28" t="n">
-        <v>290</v>
+        <v>55</v>
       </c>
       <c r="AJ28" t="n">
         <v>900</v>
@@ -5909,7 +5909,7 @@
         <v>14.5</v>
       </c>
       <c r="AP28" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AQ28" t="n">
         <v>5.9</v>
@@ -5921,37 +5921,37 @@
         <v>13.5</v>
       </c>
       <c r="AT28" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="AU28" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AV28" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AW28" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AX28" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AY28" t="n">
         <v>24</v>
       </c>
       <c r="AZ28" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="BA28" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="BB28" t="n">
         <v>48</v>
       </c>
       <c r="BC28" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BD28" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BE28" t="n">
         <v>70</v>
@@ -5960,11 +5960,11 @@
         <v>48</v>
       </c>
       <c r="BG28" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-25 06:20:07</t>
+          <t>2026-03-25 08:25:18</t>
         </is>
       </c>
     </row>
@@ -5995,46 +5995,46 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="G29" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="H29" t="n">
         <v>7.2</v>
       </c>
       <c r="I29" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="J29" t="n">
         <v>3.9</v>
       </c>
       <c r="K29" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L29" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="M29" t="n">
         <v>1.09</v>
       </c>
       <c r="N29" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="O29" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="P29" t="n">
         <v>1.72</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="R29" t="n">
         <v>1.26</v>
       </c>
       <c r="S29" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="T29" t="n">
         <v>2.2</v>
@@ -6043,13 +6043,13 @@
         <v>1.73</v>
       </c>
       <c r="V29" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="W29" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="X29" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="Y29" t="n">
         <v>970</v>
@@ -6064,7 +6064,7 @@
         <v>7.4</v>
       </c>
       <c r="AC29" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="AD29" t="n">
         <v>950</v>
@@ -6073,7 +6073,7 @@
         <v>1000</v>
       </c>
       <c r="AF29" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AG29" t="n">
         <v>10.5</v>
@@ -6085,10 +6085,10 @@
         <v>1000</v>
       </c>
       <c r="AJ29" t="n">
-        <v>19</v>
+        <v>970</v>
       </c>
       <c r="AK29" t="n">
-        <v>19.5</v>
+        <v>970</v>
       </c>
       <c r="AL29" t="n">
         <v>50</v>
@@ -6097,7 +6097,7 @@
         <v>1000</v>
       </c>
       <c r="AN29" t="n">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="AO29" t="n">
         <v>1000</v>
@@ -6106,25 +6106,25 @@
         <v>10.5</v>
       </c>
       <c r="AQ29" t="n">
-        <v>16.5</v>
+        <v>6.6</v>
       </c>
       <c r="AR29" t="n">
-        <v>50</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS29" t="n">
-        <v>6.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT29" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AU29" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AV29" t="n">
-        <v>5.7</v>
+        <v>7.4</v>
       </c>
       <c r="AW29" t="n">
-        <v>6.8</v>
+        <v>9.6</v>
       </c>
       <c r="AX29" t="n">
         <v>7.4</v>
@@ -6133,32 +6133,32 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ29" t="n">
-        <v>5.7</v>
+        <v>7.4</v>
       </c>
       <c r="BA29" t="n">
-        <v>6.8</v>
+        <v>9.6</v>
       </c>
       <c r="BB29" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="BC29" t="n">
-        <v>17.5</v>
+        <v>6.6</v>
       </c>
       <c r="BD29" t="n">
-        <v>6.2</v>
+        <v>42</v>
       </c>
       <c r="BE29" t="n">
-        <v>6.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF29" t="n">
         <v>11.5</v>
       </c>
       <c r="BG29" t="n">
-        <v>6.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-25 06:20:07</t>
+          <t>2026-03-25 08:25:18</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-25.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH29"/>
+  <dimension ref="A1:BH28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -743,184 +743,184 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>08:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Menemen Belediyespor</t>
+          <t>Beyoglu Yeni Carsi</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Mardin Buyuksehir Belediye</t>
+          <t>Muglaspor</t>
         </is>
       </c>
       <c r="F2" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="H2" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="I2" t="n">
+        <v>11</v>
+      </c>
+      <c r="J2" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K2" t="n">
         <v>4.7</v>
       </c>
-      <c r="G2" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="H2" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="I2" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="J2" t="n">
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="P2" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S2" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="W2" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>9</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>990</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>18</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>21</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>22</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>50</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>29</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BF2" t="n">
         <v>3.25</v>
       </c>
-      <c r="K2" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="L2" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="N2" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="S2" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="T2" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="X2" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>27</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>12</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>34</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>44</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>26</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>36</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>85</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>160</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>120</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>150</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>340</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>220</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>34</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>5</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>17</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>10</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>21</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>28</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>17</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>24</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>55</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>8</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>8</v>
-      </c>
       <c r="BG2" t="n">
-        <v>7.2</v>
+        <v>3.65</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-25 08:25:18</t>
+          <t>2026-03-25 10:30:55</t>
         </is>
       </c>
     </row>
@@ -942,179 +942,179 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Beyoglu Yeni Carsi</t>
+          <t>Altinordu</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Muglaspor</t>
+          <t>Kastamonuspor</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>5.6</v>
+        <v>1.85</v>
       </c>
       <c r="G3" t="n">
-        <v>6.8</v>
+        <v>1.93</v>
       </c>
       <c r="H3" t="n">
-        <v>1.75</v>
+        <v>5.7</v>
       </c>
       <c r="I3" t="n">
-        <v>1.86</v>
+        <v>6.2</v>
       </c>
       <c r="J3" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="K3" t="n">
-        <v>3.85</v>
+        <v>3.45</v>
       </c>
       <c r="L3" t="n">
-        <v>1.51</v>
+        <v>2.4</v>
       </c>
       <c r="M3" t="n">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="N3" t="n">
-        <v>2.92</v>
+        <v>2.36</v>
       </c>
       <c r="O3" t="n">
-        <v>1.45</v>
+        <v>1.71</v>
       </c>
       <c r="P3" t="n">
-        <v>1.63</v>
+        <v>1.42</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.38</v>
+        <v>3.2</v>
       </c>
       <c r="R3" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="S3" t="n">
-        <v>4.6</v>
+        <v>7.6</v>
       </c>
       <c r="T3" t="n">
-        <v>2.16</v>
+        <v>2.62</v>
       </c>
       <c r="U3" t="n">
-        <v>1.7</v>
+        <v>1.53</v>
       </c>
       <c r="V3" t="n">
-        <v>2.16</v>
+        <v>1.19</v>
       </c>
       <c r="W3" t="n">
-        <v>1.18</v>
+        <v>2.08</v>
       </c>
       <c r="X3" t="n">
-        <v>11</v>
+        <v>7.4</v>
       </c>
       <c r="Y3" t="n">
-        <v>6.8</v>
+        <v>240</v>
       </c>
       <c r="Z3" t="n">
-        <v>9.800000000000001</v>
+        <v>55</v>
       </c>
       <c r="AA3" t="n">
+        <v>250</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>34</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>150</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>42</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>220</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>22</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>40</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>100</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>550</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>36</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>390</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>32</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>130</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>23</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>29</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>130</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>24</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>65</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF3" t="n">
         <v>20</v>
       </c>
-      <c r="AB3" t="n">
-        <v>16</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>24</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>85</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>28</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>28</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>150</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>900</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>480</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>700</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>580</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>700</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>16</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>13</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>19</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>19</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>21</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>22</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>36</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>9.800000000000001</v>
-      </c>
       <c r="BG3" t="n">
-        <v>14</v>
+        <v>90</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-25 08:25:18</t>
+          <t>2026-03-25 10:30:55</t>
         </is>
       </c>
     </row>
@@ -1136,179 +1136,179 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Altinordu</t>
+          <t>Karacabey Belediyespor AS</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kastamonuspor</t>
+          <t>Karaman Belediyespor</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.24</v>
+        <v>1.07</v>
       </c>
       <c r="G4" t="n">
-        <v>2.36</v>
+        <v>1.08</v>
       </c>
       <c r="H4" t="n">
-        <v>3.4</v>
+        <v>50</v>
       </c>
       <c r="I4" t="n">
-        <v>3.8</v>
+        <v>85</v>
       </c>
       <c r="J4" t="n">
-        <v>3.4</v>
+        <v>17.5</v>
       </c>
       <c r="K4" t="n">
-        <v>3.85</v>
+        <v>21</v>
       </c>
       <c r="L4" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>3.5</v>
+        <v>14</v>
       </c>
       <c r="O4" t="n">
-        <v>1.34</v>
+        <v>1.06</v>
       </c>
       <c r="P4" t="n">
-        <v>1.85</v>
+        <v>4.2</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.02</v>
+        <v>1.28</v>
       </c>
       <c r="R4" t="n">
-        <v>1.32</v>
+        <v>2.08</v>
       </c>
       <c r="S4" t="n">
-        <v>3.65</v>
+        <v>1.84</v>
       </c>
       <c r="T4" t="n">
-        <v>1.8</v>
+        <v>2.52</v>
       </c>
       <c r="U4" t="n">
-        <v>2.06</v>
+        <v>1.55</v>
       </c>
       <c r="V4" t="n">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="W4" t="n">
-        <v>1.73</v>
+        <v>13.5</v>
       </c>
       <c r="X4" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="Y4" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="Z4" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AA4" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>9.800000000000001</v>
+        <v>23</v>
       </c>
       <c r="AC4" t="n">
+        <v>42</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>880</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>70</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>400</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>370</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA4" t="n">
         <v>8.4</v>
       </c>
-      <c r="AD4" t="n">
-        <v>16</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>60</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>15</v>
-      </c>
-      <c r="AG4" t="n">
+      <c r="BB4" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BC4" t="n">
         <v>11.5</v>
       </c>
-      <c r="AH4" t="n">
-        <v>19</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>60</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>30</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>26</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>42</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>20</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>48</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>11</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>21</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>38</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>13</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>25</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>12</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>34</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>24</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>20</v>
-      </c>
       <c r="BD4" t="n">
-        <v>27</v>
+        <v>7.4</v>
       </c>
       <c r="BE4" t="n">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="BF4" t="n">
-        <v>16.5</v>
+        <v>2.34</v>
       </c>
       <c r="BG4" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-25 08:25:18</t>
+          <t>2026-03-25 10:30:55</t>
         </is>
       </c>
     </row>
@@ -1330,70 +1330,70 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Karacabey Belediyespor AS</t>
+          <t>Batman Petrolspor</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Karaman Belediyespor</t>
+          <t>Sanliurfaspor</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="G5" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="H5" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="I5" t="n">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="J5" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="K5" t="n">
         <v>11</v>
       </c>
       <c r="L5" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>7.2</v>
+        <v>9.6</v>
       </c>
       <c r="O5" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="P5" t="n">
         <v>3.2</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="R5" t="n">
-        <v>1.91</v>
+        <v>1.69</v>
       </c>
       <c r="S5" t="n">
-        <v>2.02</v>
+        <v>2.32</v>
       </c>
       <c r="T5" t="n">
-        <v>2.26</v>
+        <v>1.03</v>
       </c>
       <c r="U5" t="n">
-        <v>1.66</v>
+        <v>1.01</v>
       </c>
       <c r="V5" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="W5" t="n">
-        <v>6.4</v>
+        <v>5.9</v>
       </c>
       <c r="X5" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="Y5" t="n">
         <v>1000</v>
@@ -1405,111 +1405,111 @@
         <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="AC5" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AD5" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AE5" t="n">
-        <v>1000</v>
+        <v>370</v>
       </c>
       <c r="AF5" t="n">
-        <v>10.5</v>
+        <v>6.8</v>
       </c>
       <c r="AG5" t="n">
-        <v>15.5</v>
+        <v>10</v>
       </c>
       <c r="AH5" t="n">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="AI5" t="n">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AJ5" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="AK5" t="n">
         <v>14.5</v>
       </c>
       <c r="AL5" t="n">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="AM5" t="n">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AN5" t="n">
-        <v>2.94</v>
+        <v>4.6</v>
       </c>
       <c r="AO5" t="n">
-        <v>1000</v>
+        <v>570</v>
       </c>
       <c r="AP5" t="n">
-        <v>13.5</v>
+        <v>6.8</v>
       </c>
       <c r="AQ5" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>50</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>22</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>25</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>22</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BC5" t="n">
         <v>10</v>
       </c>
-      <c r="AR5" t="n">
-        <v>10</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>10</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>12</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>24</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>12</v>
-      </c>
       <c r="BD5" t="n">
-        <v>9.199999999999999</v>
+        <v>5.8</v>
       </c>
       <c r="BE5" t="n">
-        <v>10</v>
+        <v>6.6</v>
       </c>
       <c r="BF5" t="n">
-        <v>2.6</v>
+        <v>3.8</v>
       </c>
       <c r="BG5" t="n">
-        <v>11</v>
+        <v>6.6</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-25 08:25:18</t>
+          <t>2026-03-25 10:30:55</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Turkish 2 Lig</t>
+          <t>Italian Serie D</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1519,184 +1519,184 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>10:30:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Batman Petrolspor</t>
+          <t>Lentigione Calcio</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sanliurfaspor</t>
+          <t>Pistoiese</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.48</v>
+        <v>3.05</v>
       </c>
       <c r="G6" t="n">
-        <v>1.55</v>
+        <v>3.2</v>
       </c>
       <c r="H6" t="n">
-        <v>7.2</v>
+        <v>2.6</v>
       </c>
       <c r="I6" t="n">
-        <v>8.800000000000001</v>
+        <v>2.68</v>
       </c>
       <c r="J6" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K6" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N6" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S6" t="n">
         <v>4.3</v>
       </c>
-      <c r="K6" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N6" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="P6" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="R6" t="n">
+      <c r="T6" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="W6" t="n">
         <v>1.45</v>
       </c>
-      <c r="S6" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="T6" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="W6" t="n">
-        <v>2.8</v>
-      </c>
       <c r="X6" t="n">
-        <v>19.5</v>
+        <v>12</v>
       </c>
       <c r="Y6" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>17</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>40</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE6" t="n">
         <v>32</v>
       </c>
-      <c r="Z6" t="n">
-        <v>160</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>270</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>36</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>480</v>
-      </c>
       <c r="AF6" t="n">
-        <v>9.6</v>
+        <v>20</v>
       </c>
       <c r="AG6" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>50</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>55</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>38</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>42</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>30</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>32</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV6" t="n">
         <v>11</v>
       </c>
-      <c r="AH6" t="n">
-        <v>30</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>390</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>14</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>16</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>50</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>550</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>230</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>21</v>
-      </c>
-      <c r="AR6" t="n">
+      <c r="AW6" t="n">
+        <v>28</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA6" t="n">
         <v>38</v>
       </c>
-      <c r="AS6" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>22</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>16.5</v>
-      </c>
       <c r="BB6" t="n">
-        <v>11</v>
+        <v>46</v>
       </c>
       <c r="BC6" t="n">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="BD6" t="n">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="BE6" t="n">
-        <v>28</v>
+        <v>110</v>
       </c>
       <c r="BF6" t="n">
-        <v>6.2</v>
+        <v>34</v>
       </c>
       <c r="BG6" t="n">
-        <v>13.5</v>
+        <v>25</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-25 08:25:18</t>
+          <t>2026-03-25 10:30:55</t>
         </is>
       </c>
     </row>
@@ -1713,191 +1713,191 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>10:30:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Lentigione Calcio</t>
+          <t>Ghivizzano Borgo A Mozz</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Pistoiese</t>
+          <t>Vivi Altotevere Sansepo</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.78</v>
+        <v>1.89</v>
       </c>
       <c r="G7" t="n">
-        <v>3.15</v>
+        <v>1.94</v>
       </c>
       <c r="H7" t="n">
-        <v>2.86</v>
+        <v>4.6</v>
       </c>
       <c r="I7" t="n">
-        <v>3.2</v>
+        <v>5.1</v>
       </c>
       <c r="J7" t="n">
-        <v>2.94</v>
+        <v>3.5</v>
       </c>
       <c r="K7" t="n">
-        <v>3.15</v>
+        <v>3.75</v>
       </c>
       <c r="L7" t="n">
-        <v>1.61</v>
+        <v>1.47</v>
       </c>
       <c r="M7" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="N7" t="n">
-        <v>2.38</v>
+        <v>3.25</v>
       </c>
       <c r="O7" t="n">
-        <v>1.61</v>
+        <v>1.39</v>
       </c>
       <c r="P7" t="n">
-        <v>1.46</v>
+        <v>1.77</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.82</v>
+        <v>2.22</v>
       </c>
       <c r="R7" t="n">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="S7" t="n">
-        <v>5.8</v>
+        <v>4.2</v>
       </c>
       <c r="T7" t="n">
-        <v>2.08</v>
+        <v>1.96</v>
       </c>
       <c r="U7" t="n">
-        <v>1.67</v>
+        <v>1.9</v>
       </c>
       <c r="V7" t="n">
-        <v>1.45</v>
+        <v>1.25</v>
       </c>
       <c r="W7" t="n">
-        <v>1.48</v>
+        <v>2.06</v>
       </c>
       <c r="X7" t="n">
-        <v>9.199999999999999</v>
+        <v>12</v>
       </c>
       <c r="Y7" t="n">
-        <v>8.6</v>
+        <v>16.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>18.5</v>
+        <v>44</v>
       </c>
       <c r="AA7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>32</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH7" t="n">
         <v>60</v>
       </c>
-      <c r="AB7" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>15</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>50</v>
-      </c>
-      <c r="AF7" t="n">
+      <c r="AI7" t="n">
+        <v>260</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>29</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN7" t="n">
         <v>18</v>
       </c>
-      <c r="AG7" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>32</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>80</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>50</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>48</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>80</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>230</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>60</v>
-      </c>
       <c r="AO7" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>6.8</v>
+        <v>10</v>
       </c>
       <c r="AQ7" t="n">
-        <v>7.6</v>
+        <v>13</v>
       </c>
       <c r="AR7" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="AS7" t="n">
-        <v>23</v>
+        <v>10.5</v>
       </c>
       <c r="AT7" t="n">
-        <v>7.2</v>
+        <v>6.2</v>
       </c>
       <c r="AU7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AV7" t="n">
-        <v>13</v>
+        <v>16.5</v>
       </c>
       <c r="AW7" t="n">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="AX7" t="n">
-        <v>14.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY7" t="n">
-        <v>11.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ7" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="BA7" t="n">
         <v>10</v>
       </c>
       <c r="BB7" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="BC7" t="n">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="BD7" t="n">
-        <v>29</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE7" t="n">
-        <v>55</v>
+        <v>110</v>
       </c>
       <c r="BF7" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="BG7" t="n">
-        <v>22</v>
+        <v>10.5</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-25 08:25:18</t>
+          <t>2026-03-25 10:30:55</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Italian Serie D</t>
+          <t>Turkish 2 Lig</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1907,191 +1907,191 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>11:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Ghivizzano Borgo A Mozz</t>
+          <t>Ankaragucu</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Vivi Altotevere Sansepo</t>
+          <t>Ankaraspor</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.67</v>
+        <v>1.97</v>
       </c>
       <c r="G8" t="n">
-        <v>1.77</v>
+        <v>2.12</v>
       </c>
       <c r="H8" t="n">
-        <v>5.9</v>
+        <v>4.7</v>
       </c>
       <c r="I8" t="n">
-        <v>6.8</v>
+        <v>5.5</v>
       </c>
       <c r="J8" t="n">
-        <v>3.65</v>
+        <v>3.2</v>
       </c>
       <c r="K8" t="n">
-        <v>4.1</v>
+        <v>3.55</v>
       </c>
       <c r="L8" t="n">
         <v>1.46</v>
       </c>
       <c r="M8" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N8" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="O8" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="P8" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="R8" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="S8" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="T8" t="n">
-        <v>2.04</v>
+        <v>1.76</v>
       </c>
       <c r="U8" t="n">
-        <v>1.78</v>
+        <v>2</v>
       </c>
       <c r="V8" t="n">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="W8" t="n">
-        <v>2.28</v>
+        <v>1.9</v>
       </c>
       <c r="X8" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB8" t="n">
         <v>12</v>
       </c>
-      <c r="Y8" t="n">
-        <v>29</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>170</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB8" t="n">
+      <c r="AC8" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>100</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>900</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>65</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>65</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA8" t="n">
         <v>7.2</v>
       </c>
-      <c r="AC8" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>38</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>26</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>19</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>22</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>110</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>15</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>10</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>15</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>23</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV8" t="n">
+      <c r="BB8" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BC8" t="n">
         <v>16.5</v>
       </c>
-      <c r="AW8" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>20</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>18</v>
-      </c>
       <c r="BD8" t="n">
-        <v>8.800000000000001</v>
+        <v>7</v>
       </c>
       <c r="BE8" t="n">
-        <v>10</v>
+        <v>6.4</v>
       </c>
       <c r="BF8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BG8" t="n">
-        <v>9.4</v>
+        <v>7.2</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-25 08:25:18</t>
+          <t>2026-03-25 10:30:55</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Turkish 2 Lig</t>
+          <t>Algerian Ligue 1</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2101,191 +2101,191 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>13:45:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Ankaragucu</t>
+          <t>Belouizdad</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ankaraspor</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.08</v>
+        <v>2.94</v>
       </c>
       <c r="G9" t="n">
-        <v>2.2</v>
+        <v>3.15</v>
       </c>
       <c r="H9" t="n">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="I9" t="n">
-        <v>5</v>
+        <v>3.4</v>
       </c>
       <c r="J9" t="n">
-        <v>3.05</v>
+        <v>2.66</v>
       </c>
       <c r="K9" t="n">
-        <v>3.45</v>
+        <v>2.86</v>
       </c>
       <c r="L9" t="n">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="M9" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="N9" t="n">
-        <v>3.1</v>
+        <v>2.34</v>
       </c>
       <c r="O9" t="n">
-        <v>1.4</v>
+        <v>1.69</v>
       </c>
       <c r="P9" t="n">
-        <v>1.7</v>
+        <v>1.41</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.22</v>
+        <v>3.2</v>
       </c>
       <c r="R9" t="n">
-        <v>1.26</v>
+        <v>1.13</v>
       </c>
       <c r="S9" t="n">
-        <v>4.1</v>
+        <v>7</v>
       </c>
       <c r="T9" t="n">
-        <v>1.81</v>
+        <v>2.3</v>
       </c>
       <c r="U9" t="n">
-        <v>1.9</v>
+        <v>1.64</v>
       </c>
       <c r="V9" t="n">
-        <v>1.26</v>
+        <v>1.42</v>
       </c>
       <c r="W9" t="n">
-        <v>1.83</v>
+        <v>1.46</v>
       </c>
       <c r="X9" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>22</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>170</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>160</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>48</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>540</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>210</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>160</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>300</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>7</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AS9" t="n">
         <v>20</v>
       </c>
-      <c r="Y9" t="n">
-        <v>24</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>900</v>
-      </c>
-      <c r="AB9" t="n">
+      <c r="AT9" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AW9" t="n">
         <v>10</v>
       </c>
-      <c r="AC9" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>100</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>14</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>20</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>38</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>500</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>75</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>55</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>8</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>7.6</v>
-      </c>
       <c r="AX9" t="n">
+        <v>15</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>22</v>
+      </c>
+      <c r="BA9" t="n">
         <v>9.4</v>
       </c>
-      <c r="AY9" t="n">
-        <v>8</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>15</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>6.4</v>
-      </c>
       <c r="BB9" t="n">
-        <v>11.5</v>
+        <v>18</v>
       </c>
       <c r="BC9" t="n">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="BD9" t="n">
-        <v>7.2</v>
+        <v>29</v>
       </c>
       <c r="BE9" t="n">
-        <v>6.8</v>
+        <v>28</v>
       </c>
       <c r="BF9" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="BG9" t="n">
-        <v>6.6</v>
+        <v>9.4</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-25 08:25:18</t>
+          <t>2026-03-25 10:30:55</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Algerian Ligue 1</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2295,191 +2295,191 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>13:45:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Belouizdad</t>
+          <t>Albion FC</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Wanderers (Uru)</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.82</v>
+        <v>2.62</v>
       </c>
       <c r="G10" t="n">
-        <v>2.96</v>
+        <v>2.72</v>
       </c>
       <c r="H10" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="I10" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="J10" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="K10" t="n">
-        <v>2.82</v>
+        <v>3.2</v>
       </c>
       <c r="L10" t="n">
-        <v>1.72</v>
+        <v>1.6</v>
       </c>
       <c r="M10" t="n">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="N10" t="n">
-        <v>2.38</v>
+        <v>2.72</v>
       </c>
       <c r="O10" t="n">
-        <v>1.7</v>
+        <v>1.53</v>
       </c>
       <c r="P10" t="n">
-        <v>1.41</v>
+        <v>1.56</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.25</v>
+        <v>2.66</v>
       </c>
       <c r="R10" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="S10" t="n">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="T10" t="n">
-        <v>2.26</v>
+        <v>2.06</v>
       </c>
       <c r="U10" t="n">
-        <v>1.63</v>
+        <v>1.81</v>
       </c>
       <c r="V10" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W10" t="n">
-        <v>1.51</v>
+        <v>1.58</v>
       </c>
       <c r="X10" t="n">
-        <v>6.6</v>
+        <v>9</v>
       </c>
       <c r="Y10" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z10" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AA10" t="n">
-        <v>420</v>
+        <v>900</v>
       </c>
       <c r="AB10" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC10" t="n">
         <v>7.4</v>
       </c>
-      <c r="AC10" t="n">
-        <v>6.8</v>
-      </c>
       <c r="AD10" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="AE10" t="n">
-        <v>160</v>
+        <v>500</v>
       </c>
       <c r="AF10" t="n">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="AG10" t="n">
-        <v>15</v>
+        <v>18.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>48</v>
+        <v>70</v>
       </c>
       <c r="AI10" t="n">
-        <v>540</v>
+        <v>500</v>
       </c>
       <c r="AJ10" t="n">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="AK10" t="n">
-        <v>290</v>
+        <v>500</v>
       </c>
       <c r="AL10" t="n">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="AM10" t="n">
         <v>1000</v>
       </c>
       <c r="AN10" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AO10" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP10" t="n">
-        <v>5.5</v>
+        <v>7.6</v>
       </c>
       <c r="AQ10" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AR10" t="n">
         <v>18.5</v>
       </c>
       <c r="AS10" t="n">
-        <v>9.4</v>
+        <v>27</v>
       </c>
       <c r="AT10" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AU10" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="AV10" t="n">
-        <v>15.5</v>
+        <v>10.5</v>
       </c>
       <c r="AW10" t="n">
-        <v>9.199999999999999</v>
+        <v>25</v>
       </c>
       <c r="AX10" t="n">
-        <v>14</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY10" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ10" t="n">
-        <v>22</v>
+        <v>11.5</v>
       </c>
       <c r="BA10" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>19</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>28</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>46</v>
+      </c>
+      <c r="BF10" t="n">
         <v>9.6</v>
       </c>
-      <c r="BB10" t="n">
-        <v>18</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>29</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>10</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>10</v>
-      </c>
       <c r="BG10" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-25 08:25:18</t>
+          <t>2026-03-25 10:30:55</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Algerian Ligue 1</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2489,33 +2489,33 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Albion FC</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Wanderers (Uru)</t>
+          <t>Kabylie</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.62</v>
+        <v>2.08</v>
       </c>
       <c r="G11" t="n">
-        <v>2.72</v>
+        <v>2.18</v>
       </c>
       <c r="H11" t="n">
-        <v>3.25</v>
+        <v>4.5</v>
       </c>
       <c r="I11" t="n">
-        <v>3.55</v>
+        <v>5.2</v>
       </c>
       <c r="J11" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="K11" t="n">
         <v>3.2</v>
@@ -2527,79 +2527,79 @@
         <v>1.13</v>
       </c>
       <c r="N11" t="n">
-        <v>2.72</v>
+        <v>2.58</v>
       </c>
       <c r="O11" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="P11" t="n">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.66</v>
+        <v>2.74</v>
       </c>
       <c r="R11" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="S11" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="T11" t="n">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="U11" t="n">
-        <v>1.79</v>
+        <v>1.69</v>
       </c>
       <c r="V11" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="W11" t="n">
-        <v>1.58</v>
+        <v>1.84</v>
       </c>
       <c r="X11" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="Y11" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>500</v>
+        <v>120</v>
       </c>
       <c r="AA11" t="n">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="AB11" t="n">
-        <v>8</v>
+        <v>6.8</v>
       </c>
       <c r="AC11" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AD11" t="n">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="AE11" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AF11" t="n">
-        <v>46</v>
+        <v>12</v>
       </c>
       <c r="AG11" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="AH11" t="n">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="AI11" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AJ11" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="AK11" t="n">
-        <v>140</v>
+        <v>75</v>
       </c>
       <c r="AL11" t="n">
-        <v>460</v>
+        <v>180</v>
       </c>
       <c r="AM11" t="n">
         <v>1000</v>
@@ -2608,72 +2608,72 @@
         <v>600</v>
       </c>
       <c r="AO11" t="n">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AQ11" t="n">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="AR11" t="n">
-        <v>9.800000000000001</v>
+        <v>17.5</v>
       </c>
       <c r="AS11" t="n">
-        <v>23</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT11" t="n">
-        <v>7</v>
+        <v>5.6</v>
       </c>
       <c r="AU11" t="n">
         <v>6.4</v>
       </c>
       <c r="AV11" t="n">
-        <v>9.4</v>
+        <v>12</v>
       </c>
       <c r="AW11" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="AX11" t="n">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AY11" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BB11" t="n">
         <v>11</v>
       </c>
-      <c r="AZ11" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>12</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>18.5</v>
-      </c>
       <c r="BC11" t="n">
-        <v>18.5</v>
+        <v>13.5</v>
       </c>
       <c r="BD11" t="n">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="BE11" t="n">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="BF11" t="n">
-        <v>10.5</v>
+        <v>8.4</v>
       </c>
       <c r="BG11" t="n">
-        <v>11.5</v>
+        <v>9</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-25 08:25:18</t>
+          <t>2026-03-25 10:30:55</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Algerian Ligue 1</t>
+          <t>English National League</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2683,108 +2683,108 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>16:45:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Morecambe</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kabylie</t>
+          <t>Hartlepool</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.08</v>
+        <v>2.84</v>
       </c>
       <c r="G12" t="n">
-        <v>2.2</v>
+        <v>2.96</v>
       </c>
       <c r="H12" t="n">
-        <v>4.5</v>
+        <v>2.56</v>
       </c>
       <c r="I12" t="n">
-        <v>5.2</v>
+        <v>2.6</v>
       </c>
       <c r="J12" t="n">
-        <v>2.94</v>
+        <v>3.65</v>
       </c>
       <c r="K12" t="n">
-        <v>3.2</v>
+        <v>3.85</v>
       </c>
       <c r="L12" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N12" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="T12" t="n">
         <v>1.61</v>
       </c>
-      <c r="M12" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="N12" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="O12" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="P12" t="n">
+      <c r="U12" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="W12" t="n">
         <v>1.51</v>
       </c>
-      <c r="Q12" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S12" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.83</v>
-      </c>
       <c r="X12" t="n">
-        <v>8.4</v>
+        <v>18.5</v>
       </c>
       <c r="Y12" t="n">
-        <v>12.5</v>
+        <v>17</v>
       </c>
       <c r="Z12" t="n">
-        <v>120</v>
+        <v>18.5</v>
       </c>
       <c r="AA12" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AB12" t="n">
-        <v>6.8</v>
+        <v>15.5</v>
       </c>
       <c r="AC12" t="n">
-        <v>7.8</v>
+        <v>11.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="AE12" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AF12" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="AG12" t="n">
         <v>12.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>85</v>
+        <v>22</v>
       </c>
       <c r="AI12" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AJ12" t="n">
         <v>65</v>
@@ -2793,74 +2793,74 @@
         <v>75</v>
       </c>
       <c r="AL12" t="n">
-        <v>180</v>
+        <v>36</v>
       </c>
       <c r="AM12" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AN12" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AO12" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AP12" t="n">
-        <v>6.8</v>
+        <v>16</v>
       </c>
       <c r="AQ12" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>30</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV12" t="n">
         <v>10</v>
       </c>
-      <c r="AR12" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>12</v>
-      </c>
       <c r="AW12" t="n">
-        <v>8.4</v>
+        <v>21</v>
       </c>
       <c r="AX12" t="n">
-        <v>9.6</v>
+        <v>14</v>
       </c>
       <c r="AY12" t="n">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="AZ12" t="n">
-        <v>14.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BA12" t="n">
-        <v>8.6</v>
+        <v>16.5</v>
       </c>
       <c r="BB12" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="BC12" t="n">
-        <v>13.5</v>
+        <v>25</v>
       </c>
       <c r="BD12" t="n">
-        <v>24</v>
+        <v>18.5</v>
       </c>
       <c r="BE12" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="BF12" t="n">
-        <v>7.2</v>
+        <v>17.5</v>
       </c>
       <c r="BG12" t="n">
-        <v>8.6</v>
+        <v>10.5</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-25 08:25:18</t>
+          <t>2026-03-25 10:30:55</t>
         </is>
       </c>
     </row>
@@ -2882,179 +2882,179 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Morecambe</t>
+          <t>Truro City</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Hartlepool</t>
+          <t>Solihull Moors</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="G13" t="n">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="H13" t="n">
-        <v>2.46</v>
+        <v>2.68</v>
       </c>
       <c r="I13" t="n">
-        <v>2.64</v>
+        <v>2.74</v>
       </c>
       <c r="J13" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K13" t="n">
         <v>3.65</v>
       </c>
-      <c r="K13" t="n">
-        <v>3.85</v>
-      </c>
       <c r="L13" t="n">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="M13" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N13" t="n">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="O13" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="P13" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="U13" t="n">
         <v>2.24</v>
       </c>
-      <c r="Q13" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="U13" t="n">
-        <v>2.4</v>
-      </c>
       <c r="V13" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="W13" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="X13" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>19</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>38</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>40</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>28</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>16</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>40</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>46</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>65</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>85</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>85</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>25</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>22</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>16</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>32</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW13" t="n">
         <v>18.5</v>
       </c>
-      <c r="Y13" t="n">
-        <v>14</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>34</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>500</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>12</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>25</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>22</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>34</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>50</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>80</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>95</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>70</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>600</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>18</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>10.5</v>
-      </c>
       <c r="AX13" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="AY13" t="n">
         <v>11.5</v>
       </c>
       <c r="AZ13" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="BA13" t="n">
-        <v>14.5</v>
+        <v>32</v>
       </c>
       <c r="BB13" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="BC13" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="BD13" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BE13" t="n">
-        <v>12.5</v>
+        <v>18.5</v>
       </c>
       <c r="BF13" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="BG13" t="n">
-        <v>13</v>
+        <v>18.5</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-25 08:25:18</t>
+          <t>2026-03-25 10:30:55</t>
         </is>
       </c>
     </row>
@@ -3076,179 +3076,179 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Truro City</t>
+          <t>Scunthorpe</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Solihull Moors</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.84</v>
+        <v>3.55</v>
       </c>
       <c r="G14" t="n">
-        <v>2.9</v>
+        <v>3.8</v>
       </c>
       <c r="H14" t="n">
-        <v>2.62</v>
+        <v>2.14</v>
       </c>
       <c r="I14" t="n">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
       <c r="J14" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="K14" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="L14" t="n">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="M14" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N14" t="n">
-        <v>4.1</v>
+        <v>4.9</v>
       </c>
       <c r="O14" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="P14" t="n">
-        <v>2.04</v>
+        <v>2.34</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.88</v>
+        <v>1.69</v>
       </c>
       <c r="R14" t="n">
-        <v>1.41</v>
+        <v>1.53</v>
       </c>
       <c r="S14" t="n">
-        <v>3.2</v>
+        <v>2.72</v>
       </c>
       <c r="T14" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="U14" t="n">
-        <v>2.26</v>
+        <v>2.42</v>
       </c>
       <c r="V14" t="n">
-        <v>1.59</v>
+        <v>1.83</v>
       </c>
       <c r="W14" t="n">
-        <v>1.52</v>
+        <v>1.36</v>
       </c>
       <c r="X14" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Z14" t="n">
         <v>15.5</v>
       </c>
-      <c r="Y14" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="Z14" t="n">
+      <c r="AA14" t="n">
+        <v>27</v>
+      </c>
+      <c r="AB14" t="n">
         <v>18</v>
       </c>
-      <c r="AA14" t="n">
-        <v>900</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>20</v>
-      </c>
       <c r="AC14" t="n">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AD14" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AE14" t="n">
+        <v>21</v>
+      </c>
+      <c r="AF14" t="n">
         <v>28</v>
       </c>
-      <c r="AF14" t="n">
-        <v>19.5</v>
-      </c>
       <c r="AG14" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>29</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>65</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>36</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>70</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>29</v>
+      </c>
+      <c r="AO14" t="n">
         <v>12.5</v>
       </c>
-      <c r="AH14" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>85</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>100</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>65</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>150</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>200</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>25</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>42</v>
-      </c>
       <c r="AP14" t="n">
-        <v>13.5</v>
+        <v>17.5</v>
       </c>
       <c r="AQ14" t="n">
         <v>11</v>
       </c>
       <c r="AR14" t="n">
-        <v>9.199999999999999</v>
+        <v>13.5</v>
       </c>
       <c r="AS14" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="AT14" t="n">
-        <v>7.8</v>
+        <v>15</v>
       </c>
       <c r="AU14" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV14" t="n">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW14" t="n">
-        <v>23</v>
+        <v>17.5</v>
       </c>
       <c r="AX14" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="AY14" t="n">
-        <v>8.6</v>
+        <v>13.5</v>
       </c>
       <c r="AZ14" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="BA14" t="n">
+        <v>26</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>50</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>30</v>
+      </c>
+      <c r="BD14" t="n">
         <v>32</v>
       </c>
-      <c r="BB14" t="n">
-        <v>20</v>
-      </c>
-      <c r="BC14" t="n">
+      <c r="BE14" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BF14" t="n">
         <v>25</v>
       </c>
-      <c r="BD14" t="n">
-        <v>20</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>15</v>
-      </c>
-      <c r="BF14" t="n">
+      <c r="BG14" t="n">
         <v>10.5</v>
       </c>
-      <c r="BG14" t="n">
-        <v>18.5</v>
-      </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-25 08:25:18</t>
+          <t>2026-03-25 10:30:55</t>
         </is>
       </c>
     </row>
@@ -3270,179 +3270,179 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Scunthorpe</t>
+          <t>Southend</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>Woking</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.65</v>
+        <v>1.7</v>
       </c>
       <c r="G15" t="n">
-        <v>3.8</v>
+        <v>1.74</v>
       </c>
       <c r="H15" t="n">
-        <v>2.1</v>
+        <v>5.4</v>
       </c>
       <c r="I15" t="n">
-        <v>2.16</v>
+        <v>5.9</v>
       </c>
       <c r="J15" t="n">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="K15" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="L15" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="M15" t="n">
         <v>1.05</v>
       </c>
       <c r="N15" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="O15" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="P15" t="n">
-        <v>2.28</v>
+        <v>2.14</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.74</v>
+        <v>1.81</v>
       </c>
       <c r="R15" t="n">
-        <v>1.49</v>
+        <v>1.43</v>
       </c>
       <c r="S15" t="n">
-        <v>2.84</v>
+        <v>3.1</v>
       </c>
       <c r="T15" t="n">
-        <v>1.63</v>
+        <v>1.79</v>
       </c>
       <c r="U15" t="n">
-        <v>2.42</v>
+        <v>2.12</v>
       </c>
       <c r="V15" t="n">
-        <v>1.86</v>
+        <v>1.2</v>
       </c>
       <c r="W15" t="n">
-        <v>1.35</v>
+        <v>2.34</v>
       </c>
       <c r="X15" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="Y15" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="Z15" t="n">
-        <v>14.5</v>
+        <v>44</v>
       </c>
       <c r="AA15" t="n">
-        <v>27</v>
+        <v>140</v>
       </c>
       <c r="AB15" t="n">
-        <v>18</v>
+        <v>9.6</v>
       </c>
       <c r="AC15" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AD15" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>75</v>
+      </c>
+      <c r="AF15" t="n">
         <v>10.5</v>
       </c>
-      <c r="AE15" t="n">
+      <c r="AG15" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>160</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>32</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>75</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AR15" t="n">
         <v>21</v>
       </c>
-      <c r="AF15" t="n">
+      <c r="AS15" t="n">
+        <v>29</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>55</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA15" t="n">
         <v>30</v>
       </c>
-      <c r="AG15" t="n">
-        <v>16</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>16</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>30</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>65</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>40</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>44</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>75</v>
-      </c>
-      <c r="AN15" t="n">
+      <c r="BB15" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>28</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>36</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BG15" t="n">
         <v>32</v>
       </c>
-      <c r="AO15" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>11</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>13</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>23</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>15</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>25</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>14</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>26</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>50</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>32</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>36</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>34</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>27</v>
-      </c>
-      <c r="BG15" t="n">
-        <v>11</v>
-      </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-25 08:25:18</t>
+          <t>2026-03-25 10:30:55</t>
         </is>
       </c>
     </row>
@@ -3464,25 +3464,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Tamworth FC</t>
+          <t>Wealdstone</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Forest Green</t>
+          <t>Yeovil</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>3.6</v>
+        <v>1.94</v>
       </c>
       <c r="G16" t="n">
-        <v>3.7</v>
+        <v>2</v>
       </c>
       <c r="H16" t="n">
-        <v>2.12</v>
+        <v>4</v>
       </c>
       <c r="I16" t="n">
-        <v>2.18</v>
+        <v>4.4</v>
       </c>
       <c r="J16" t="n">
         <v>3.8</v>
@@ -3491,152 +3491,152 @@
         <v>3.95</v>
       </c>
       <c r="L16" t="n">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="M16" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="N16" t="n">
-        <v>5</v>
+        <v>3.9</v>
       </c>
       <c r="O16" t="n">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="P16" t="n">
-        <v>2.34</v>
+        <v>2.04</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.69</v>
+        <v>1.92</v>
       </c>
       <c r="R16" t="n">
-        <v>1.53</v>
+        <v>1.38</v>
       </c>
       <c r="S16" t="n">
-        <v>2.74</v>
+        <v>3.4</v>
       </c>
       <c r="T16" t="n">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="U16" t="n">
-        <v>2.48</v>
+        <v>2.1</v>
       </c>
       <c r="V16" t="n">
-        <v>1.84</v>
+        <v>1.29</v>
       </c>
       <c r="W16" t="n">
-        <v>1.37</v>
+        <v>2</v>
       </c>
       <c r="X16" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>900</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>23</v>
+      </c>
+      <c r="AK16" t="n">
         <v>20</v>
       </c>
-      <c r="Y16" t="n">
-        <v>13</v>
-      </c>
-      <c r="Z16" t="n">
+      <c r="AL16" t="n">
+        <v>34</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>14</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>60</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>14</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>27</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>28</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>15</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>44</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ16" t="n">
         <v>16.5</v>
       </c>
-      <c r="AA16" t="n">
-        <v>26</v>
-      </c>
-      <c r="AB16" t="n">
+      <c r="BA16" t="n">
+        <v>28</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BC16" t="n">
         <v>18.5</v>
       </c>
-      <c r="AC16" t="n">
-        <v>9</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>11</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>20</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>28</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AI16" t="n">
+      <c r="BD16" t="n">
         <v>30</v>
       </c>
-      <c r="AJ16" t="n">
-        <v>65</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>38</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>42</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>70</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>30</v>
-      </c>
-      <c r="AO16" t="n">
+      <c r="BE16" t="n">
+        <v>60</v>
+      </c>
+      <c r="BF16" t="n">
         <v>12.5</v>
       </c>
-      <c r="AP16" t="n">
-        <v>19</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>14</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>22</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>24</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>14</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>25</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>27</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>32</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>21</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>29</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>24</v>
-      </c>
       <c r="BG16" t="n">
-        <v>10.5</v>
+        <v>23</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-25 08:25:18</t>
+          <t>2026-03-25 10:30:55</t>
         </is>
       </c>
     </row>
@@ -3658,186 +3658,186 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Southend</t>
+          <t>Tamworth FC</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Woking</t>
+          <t>Forest Green</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.69</v>
+        <v>3.6</v>
       </c>
       <c r="G17" t="n">
-        <v>1.74</v>
+        <v>3.7</v>
       </c>
       <c r="H17" t="n">
-        <v>5.4</v>
+        <v>2.12</v>
       </c>
       <c r="I17" t="n">
-        <v>5.9</v>
+        <v>2.18</v>
       </c>
       <c r="J17" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="K17" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="L17" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N17" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="W17" t="n">
         <v>1.37</v>
       </c>
-      <c r="M17" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N17" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="O17" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="P17" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="S17" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="T17" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="U17" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="W17" t="n">
-        <v>2.34</v>
-      </c>
       <c r="X17" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="Y17" t="n">
-        <v>21</v>
+        <v>13.5</v>
       </c>
       <c r="Z17" t="n">
-        <v>46</v>
+        <v>15.5</v>
       </c>
       <c r="AA17" t="n">
-        <v>900</v>
+        <v>26</v>
       </c>
       <c r="AB17" t="n">
-        <v>9.800000000000001</v>
+        <v>19</v>
       </c>
       <c r="AC17" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD17" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="AE17" t="n">
-        <v>75</v>
+        <v>19.5</v>
       </c>
       <c r="AF17" t="n">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="AG17" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AH17" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="AI17" t="n">
-        <v>320</v>
+        <v>28</v>
       </c>
       <c r="AJ17" t="n">
-        <v>17.5</v>
+        <v>65</v>
       </c>
       <c r="AK17" t="n">
-        <v>17.5</v>
+        <v>36</v>
       </c>
       <c r="AL17" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="AM17" t="n">
-        <v>110</v>
+        <v>65</v>
       </c>
       <c r="AN17" t="n">
-        <v>9.800000000000001</v>
+        <v>27</v>
       </c>
       <c r="AO17" t="n">
-        <v>310</v>
+        <v>11.5</v>
       </c>
       <c r="AP17" t="n">
-        <v>15.5</v>
+        <v>19.5</v>
       </c>
       <c r="AQ17" t="n">
-        <v>17.5</v>
+        <v>12</v>
       </c>
       <c r="AR17" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="AS17" t="n">
-        <v>14.5</v>
+        <v>22</v>
       </c>
       <c r="AT17" t="n">
-        <v>8.199999999999999</v>
+        <v>16.5</v>
       </c>
       <c r="AU17" t="n">
         <v>8.4</v>
       </c>
       <c r="AV17" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="AW17" t="n">
-        <v>32</v>
+        <v>17.5</v>
       </c>
       <c r="AX17" t="n">
-        <v>9.4</v>
+        <v>25</v>
       </c>
       <c r="AY17" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AZ17" t="n">
-        <v>17.5</v>
+        <v>13</v>
       </c>
       <c r="BA17" t="n">
+        <v>25</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>50</v>
+      </c>
+      <c r="BC17" t="n">
         <v>30</v>
       </c>
-      <c r="BB17" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>15</v>
-      </c>
       <c r="BD17" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="BE17" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="BF17" t="n">
-        <v>8.4</v>
+        <v>23</v>
       </c>
       <c r="BG17" t="n">
-        <v>13.5</v>
+        <v>10</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-25 08:25:18</t>
+          <t>2026-03-25 10:30:55</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>English National League</t>
+          <t>Colombian Primera B</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3847,191 +3847,191 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>16:45:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Wealdstone</t>
+          <t>Envigado</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Yeovil</t>
+          <t>Bogota</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.94</v>
+        <v>1.59</v>
       </c>
       <c r="G18" t="n">
-        <v>2.02</v>
+        <v>1.64</v>
       </c>
       <c r="H18" t="n">
-        <v>4.1</v>
+        <v>7.4</v>
       </c>
       <c r="I18" t="n">
-        <v>4.5</v>
+        <v>9</v>
       </c>
       <c r="J18" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="K18" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="L18" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N18" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="O18" t="n">
         <v>1.42</v>
       </c>
-      <c r="M18" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N18" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="O18" t="n">
-        <v>1.32</v>
-      </c>
       <c r="P18" t="n">
-        <v>2</v>
+        <v>1.72</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.93</v>
+        <v>2.26</v>
       </c>
       <c r="R18" t="n">
-        <v>1.38</v>
+        <v>1.26</v>
       </c>
       <c r="S18" t="n">
-        <v>3.35</v>
+        <v>4.3</v>
       </c>
       <c r="T18" t="n">
-        <v>1.76</v>
+        <v>2.2</v>
       </c>
       <c r="U18" t="n">
-        <v>2.16</v>
+        <v>1.67</v>
       </c>
       <c r="V18" t="n">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="W18" t="n">
-        <v>1.98</v>
+        <v>2.56</v>
       </c>
       <c r="X18" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="Y18" t="n">
-        <v>16</v>
+        <v>70</v>
       </c>
       <c r="Z18" t="n">
-        <v>32</v>
+        <v>170</v>
       </c>
       <c r="AA18" t="n">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="AB18" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AC18" t="n">
+        <v>42</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>180</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>40</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>36</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>500</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>500</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>65</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>500</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>29</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR18" t="n">
         <v>8.6</v>
       </c>
-      <c r="AD18" t="n">
-        <v>17</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>55</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>10</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>18</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>320</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>23</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>21</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>36</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>110</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>14</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>55</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>14</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>14</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>27</v>
-      </c>
       <c r="AS18" t="n">
-        <v>16</v>
+        <v>7.2</v>
       </c>
       <c r="AT18" t="n">
-        <v>8.6</v>
+        <v>5.5</v>
       </c>
       <c r="AU18" t="n">
-        <v>7.8</v>
+        <v>6.2</v>
       </c>
       <c r="AV18" t="n">
-        <v>14.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW18" t="n">
-        <v>42</v>
+        <v>7</v>
       </c>
       <c r="AX18" t="n">
-        <v>11.5</v>
+        <v>4.9</v>
       </c>
       <c r="AY18" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BC18" t="n">
         <v>9</v>
       </c>
-      <c r="AZ18" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>30</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>18.5</v>
-      </c>
       <c r="BD18" t="n">
-        <v>30</v>
+        <v>8.4</v>
       </c>
       <c r="BE18" t="n">
-        <v>60</v>
+        <v>28</v>
       </c>
       <c r="BF18" t="n">
-        <v>12</v>
+        <v>5.7</v>
       </c>
       <c r="BG18" t="n">
-        <v>14</v>
+        <v>9.6</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-25 08:25:18</t>
+          <t>2026-03-25 10:30:55</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Colombian Primera B</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4046,186 +4046,186 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Envigado</t>
+          <t>Cerro</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Bogota</t>
+          <t>Juventud De Las Piedras</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.58</v>
+        <v>3.1</v>
       </c>
       <c r="G19" t="n">
-        <v>1.62</v>
+        <v>3.3</v>
       </c>
       <c r="H19" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="I19" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="J19" t="n">
+        <v>3</v>
+      </c>
+      <c r="K19" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="N19" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X19" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>19</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>900</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC19" t="n">
         <v>7.2</v>
       </c>
-      <c r="I19" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="J19" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="K19" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="L19" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="M19" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="N19" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="O19" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="P19" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="S19" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="W19" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="X19" t="n">
-        <v>970</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>70</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>170</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>11</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>42</v>
-      </c>
       <c r="AD19" t="n">
-        <v>180</v>
+        <v>16</v>
       </c>
       <c r="AE19" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AF19" t="n">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="AG19" t="n">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="AH19" t="n">
+        <v>28</v>
+      </c>
+      <c r="AI19" t="n">
         <v>500</v>
       </c>
-      <c r="AI19" t="n">
-        <v>1000</v>
-      </c>
       <c r="AJ19" t="n">
-        <v>500</v>
+        <v>150</v>
       </c>
       <c r="AK19" t="n">
-        <v>970</v>
+        <v>120</v>
       </c>
       <c r="AL19" t="n">
         <v>500</v>
       </c>
       <c r="AM19" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN19" t="n">
-        <v>29</v>
+        <v>600</v>
       </c>
       <c r="AO19" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AP19" t="n">
-        <v>5.6</v>
+        <v>7.4</v>
       </c>
       <c r="AQ19" t="n">
-        <v>9.6</v>
+        <v>7.4</v>
       </c>
       <c r="AR19" t="n">
-        <v>9.199999999999999</v>
+        <v>12.5</v>
       </c>
       <c r="AS19" t="n">
-        <v>5.8</v>
+        <v>24</v>
       </c>
       <c r="AT19" t="n">
-        <v>5.5</v>
+        <v>8</v>
       </c>
       <c r="AU19" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV19" t="n">
-        <v>8</v>
+        <v>11.5</v>
       </c>
       <c r="AW19" t="n">
-        <v>5.7</v>
+        <v>26</v>
       </c>
       <c r="AX19" t="n">
-        <v>4.6</v>
+        <v>16.5</v>
       </c>
       <c r="AY19" t="n">
-        <v>5.4</v>
+        <v>13</v>
       </c>
       <c r="AZ19" t="n">
-        <v>13</v>
+        <v>16.5</v>
       </c>
       <c r="BA19" t="n">
-        <v>5.7</v>
+        <v>50</v>
       </c>
       <c r="BB19" t="n">
-        <v>6.6</v>
+        <v>28</v>
       </c>
       <c r="BC19" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="BD19" t="n">
-        <v>8.800000000000001</v>
+        <v>46</v>
       </c>
       <c r="BE19" t="n">
-        <v>10</v>
+        <v>70</v>
       </c>
       <c r="BF19" t="n">
-        <v>9.6</v>
+        <v>30</v>
       </c>
       <c r="BG19" t="n">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-25 08:25:18</t>
+          <t>2026-03-25 10:30:55</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Argentinian Primera Division</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4235,191 +4235,191 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Cerro</t>
+          <t>Deportivo Riestra</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Juventud De Las Piedras</t>
+          <t>San Lorenzo</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>3.1</v>
+        <v>2.48</v>
       </c>
       <c r="G20" t="n">
-        <v>3.3</v>
+        <v>2.54</v>
       </c>
       <c r="H20" t="n">
-        <v>2.68</v>
+        <v>4</v>
       </c>
       <c r="I20" t="n">
-        <v>2.82</v>
+        <v>4.3</v>
       </c>
       <c r="J20" t="n">
-        <v>3</v>
+        <v>2.74</v>
       </c>
       <c r="K20" t="n">
-        <v>3.15</v>
+        <v>2.78</v>
       </c>
       <c r="L20" t="n">
-        <v>1.59</v>
+        <v>1.85</v>
       </c>
       <c r="M20" t="n">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="N20" t="n">
-        <v>2.66</v>
+        <v>2.04</v>
       </c>
       <c r="O20" t="n">
-        <v>1.56</v>
+        <v>1.92</v>
       </c>
       <c r="P20" t="n">
-        <v>1.54</v>
+        <v>1.3</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.68</v>
+        <v>4.1</v>
       </c>
       <c r="R20" t="n">
-        <v>1.19</v>
+        <v>1.1</v>
       </c>
       <c r="S20" t="n">
-        <v>5.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="T20" t="n">
-        <v>2.1</v>
+        <v>2.76</v>
       </c>
       <c r="U20" t="n">
-        <v>1.81</v>
+        <v>1.49</v>
       </c>
       <c r="V20" t="n">
-        <v>1.54</v>
+        <v>1.29</v>
       </c>
       <c r="W20" t="n">
-        <v>1.44</v>
+        <v>1.67</v>
       </c>
       <c r="X20" t="n">
-        <v>8.6</v>
+        <v>5.6</v>
       </c>
       <c r="Y20" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="Z20" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="AA20" t="n">
-        <v>900</v>
+        <v>130</v>
       </c>
       <c r="AB20" t="n">
-        <v>9.199999999999999</v>
+        <v>5.9</v>
       </c>
       <c r="AC20" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AD20" t="n">
-        <v>16.5</v>
+        <v>24</v>
       </c>
       <c r="AE20" t="n">
-        <v>95</v>
+        <v>130</v>
       </c>
       <c r="AF20" t="n">
-        <v>20</v>
+        <v>13.5</v>
       </c>
       <c r="AG20" t="n">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="AH20" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="AI20" t="n">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="AJ20" t="n">
-        <v>220</v>
+        <v>46</v>
       </c>
       <c r="AK20" t="n">
-        <v>500</v>
+        <v>55</v>
       </c>
       <c r="AL20" t="n">
-        <v>500</v>
+        <v>540</v>
       </c>
       <c r="AM20" t="n">
         <v>500</v>
       </c>
       <c r="AN20" t="n">
-        <v>500</v>
+        <v>75</v>
       </c>
       <c r="AO20" t="n">
         <v>600</v>
       </c>
       <c r="AP20" t="n">
-        <v>7.6</v>
+        <v>5</v>
       </c>
       <c r="AQ20" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AR20" t="n">
-        <v>13.5</v>
+        <v>21</v>
       </c>
       <c r="AS20" t="n">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="AT20" t="n">
-        <v>8</v>
+        <v>5.4</v>
       </c>
       <c r="AU20" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV20" t="n">
-        <v>11.5</v>
+        <v>20</v>
       </c>
       <c r="AW20" t="n">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="AX20" t="n">
-        <v>16.5</v>
+        <v>11</v>
       </c>
       <c r="AY20" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AZ20" t="n">
-        <v>16.5</v>
+        <v>34</v>
       </c>
       <c r="BA20" t="n">
-        <v>50</v>
+        <v>85</v>
       </c>
       <c r="BB20" t="n">
+        <v>30</v>
+      </c>
+      <c r="BC20" t="n">
         <v>28</v>
       </c>
-      <c r="BC20" t="n">
-        <v>26</v>
-      </c>
       <c r="BD20" t="n">
+        <v>46</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>130</v>
+      </c>
+      <c r="BF20" t="n">
         <v>48</v>
       </c>
-      <c r="BE20" t="n">
-        <v>95</v>
-      </c>
-      <c r="BF20" t="n">
-        <v>29</v>
-      </c>
       <c r="BG20" t="n">
-        <v>32</v>
+        <v>80</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-25 08:25:18</t>
+          <t>2026-03-25 10:30:55</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Colombian Primera B</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4434,186 +4434,186 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Deportivo Riestra</t>
+          <t>Barranquilla</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>San Lorenzo</t>
+          <t>Leones FC</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.62</v>
+        <v>1.97</v>
       </c>
       <c r="G21" t="n">
-        <v>2.7</v>
+        <v>2.12</v>
       </c>
       <c r="H21" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="I21" t="n">
-        <v>3.95</v>
+        <v>4.9</v>
       </c>
       <c r="J21" t="n">
-        <v>2.72</v>
+        <v>3.3</v>
       </c>
       <c r="K21" t="n">
-        <v>2.8</v>
+        <v>3.7</v>
       </c>
       <c r="L21" t="n">
-        <v>1.85</v>
+        <v>1.47</v>
       </c>
       <c r="M21" t="n">
-        <v>1.22</v>
+        <v>1.09</v>
       </c>
       <c r="N21" t="n">
-        <v>2.02</v>
+        <v>3.3</v>
       </c>
       <c r="O21" t="n">
-        <v>1.94</v>
+        <v>1.39</v>
       </c>
       <c r="P21" t="n">
-        <v>1.3</v>
+        <v>1.81</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.1</v>
+        <v>2.16</v>
       </c>
       <c r="R21" t="n">
-        <v>1.09</v>
+        <v>1.28</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T21" t="n">
-        <v>2.82</v>
+        <v>1.9</v>
       </c>
       <c r="U21" t="n">
-        <v>1.47</v>
+        <v>2</v>
       </c>
       <c r="V21" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="W21" t="n">
-        <v>1.58</v>
+        <v>1.89</v>
       </c>
       <c r="X21" t="n">
-        <v>5.7</v>
+        <v>12</v>
       </c>
       <c r="Y21" t="n">
-        <v>8.6</v>
+        <v>14.5</v>
       </c>
       <c r="Z21" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="AA21" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AB21" t="n">
-        <v>6.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC21" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD21" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AE21" t="n">
-        <v>110</v>
+        <v>170</v>
       </c>
       <c r="AF21" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AG21" t="n">
-        <v>16.5</v>
+        <v>11</v>
       </c>
       <c r="AH21" t="n">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="AI21" t="n">
-        <v>200</v>
+        <v>370</v>
       </c>
       <c r="AJ21" t="n">
+        <v>25</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>25</v>
+      </c>
+      <c r="AL21" t="n">
         <v>46</v>
       </c>
-      <c r="AK21" t="n">
-        <v>60</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>140</v>
-      </c>
       <c r="AM21" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN21" t="n">
-        <v>85</v>
+        <v>19</v>
       </c>
       <c r="AO21" t="n">
-        <v>210</v>
+        <v>290</v>
       </c>
       <c r="AP21" t="n">
-        <v>5.1</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ21" t="n">
-        <v>7.4</v>
+        <v>11.5</v>
       </c>
       <c r="AR21" t="n">
+        <v>13</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>28</v>
+      </c>
+      <c r="BB21" t="n">
         <v>20</v>
       </c>
-      <c r="AS21" t="n">
-        <v>80</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>19</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>75</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>32</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>70</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>24</v>
-      </c>
       <c r="BC21" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="BD21" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="BE21" t="n">
-        <v>120</v>
+        <v>9.6</v>
       </c>
       <c r="BF21" t="n">
-        <v>32</v>
+        <v>15.5</v>
       </c>
       <c r="BG21" t="n">
-        <v>50</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-25 08:25:18</t>
+          <t>2026-03-25 10:30:55</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Colombian Primera B</t>
+          <t>Paraguayan Primera Division</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4623,191 +4623,191 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>19:30:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Barranquilla</t>
+          <t>Guarani (Par)</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Leones FC</t>
+          <t>Club 2 de Mayo de Pedro Juan Cab</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="G22" t="n">
-        <v>2.12</v>
+        <v>2.04</v>
       </c>
       <c r="H22" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="I22" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="J22" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="K22" t="n">
         <v>3.7</v>
       </c>
       <c r="L22" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="M22" t="n">
         <v>1.09</v>
       </c>
       <c r="N22" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="O22" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="P22" t="n">
-        <v>1.81</v>
+        <v>1.72</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.16</v>
+        <v>2.28</v>
       </c>
       <c r="R22" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="S22" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="T22" t="n">
-        <v>1.89</v>
+        <v>1.98</v>
       </c>
       <c r="U22" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="V22" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="W22" t="n">
-        <v>1.89</v>
+        <v>1.96</v>
       </c>
       <c r="X22" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>14</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>40</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>36</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>500</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>900</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>150</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>55</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>10</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>6</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA22" t="n">
         <v>12</v>
       </c>
-      <c r="Y22" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>34</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>900</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>19</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>170</v>
-      </c>
-      <c r="AF22" t="n">
+      <c r="BB22" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>8</v>
+      </c>
+      <c r="BG22" t="n">
         <v>12.5</v>
       </c>
-      <c r="AG22" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>370</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>25</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>25</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>46</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>580</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>290</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>13</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>28</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>20</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>20</v>
-      </c>
-      <c r="BD22" t="n">
-        <v>36</v>
-      </c>
-      <c r="BE22" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BF22" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BG22" t="n">
-        <v>9.800000000000001</v>
-      </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-25 08:25:18</t>
+          <t>2026-03-25 10:30:55</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Paraguayan Primera Division</t>
+          <t>Colombian Primera B</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4817,75 +4817,75 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>19:30:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Guarani (Par)</t>
+          <t>Real Soacha Cundinamarca FC</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Club 2 de Mayo de Pedro Juan Cab</t>
+          <t>Atletico FC Cali</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.96</v>
+        <v>1.6</v>
       </c>
       <c r="G23" t="n">
-        <v>2.02</v>
+        <v>1.66</v>
       </c>
       <c r="H23" t="n">
-        <v>4.4</v>
+        <v>6.8</v>
       </c>
       <c r="I23" t="n">
-        <v>4.7</v>
+        <v>8.6</v>
       </c>
       <c r="J23" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="K23" t="n">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="L23" t="n">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="M23" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N23" t="n">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="O23" t="n">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="P23" t="n">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.28</v>
+        <v>2.16</v>
       </c>
       <c r="R23" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="S23" t="n">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="T23" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="U23" t="n">
-        <v>1.92</v>
+        <v>1.74</v>
       </c>
       <c r="V23" t="n">
-        <v>1.27</v>
+        <v>1.13</v>
       </c>
       <c r="W23" t="n">
-        <v>1.98</v>
+        <v>2.52</v>
       </c>
       <c r="X23" t="n">
-        <v>22</v>
+        <v>500</v>
       </c>
       <c r="Y23" t="n">
         <v>1000</v>
@@ -4897,13 +4897,13 @@
         <v>1000</v>
       </c>
       <c r="AB23" t="n">
-        <v>17</v>
+        <v>7.2</v>
       </c>
       <c r="AC23" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AD23" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AE23" t="n">
         <v>1000</v>
@@ -4912,22 +4912,22 @@
         <v>40</v>
       </c>
       <c r="AG23" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AH23" t="n">
         <v>1000</v>
       </c>
       <c r="AI23" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AJ23" t="n">
         <v>900</v>
       </c>
       <c r="AK23" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AL23" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AM23" t="n">
         <v>1000</v>
@@ -4939,69 +4939,69 @@
         <v>1000</v>
       </c>
       <c r="AP23" t="n">
-        <v>6.4</v>
+        <v>5.8</v>
       </c>
       <c r="AQ23" t="n">
-        <v>7</v>
+        <v>4.2</v>
       </c>
       <c r="AR23" t="n">
-        <v>10</v>
+        <v>4.2</v>
       </c>
       <c r="AS23" t="n">
-        <v>2.24</v>
+        <v>4.2</v>
       </c>
       <c r="AT23" t="n">
-        <v>6.6</v>
+        <v>4.3</v>
       </c>
       <c r="AU23" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AV23" t="n">
-        <v>8.199999999999999</v>
+        <v>4.2</v>
       </c>
       <c r="AW23" t="n">
-        <v>3.05</v>
+        <v>4.2</v>
       </c>
       <c r="AX23" t="n">
-        <v>6.4</v>
+        <v>4.8</v>
       </c>
       <c r="AY23" t="n">
-        <v>6.2</v>
+        <v>5.2</v>
       </c>
       <c r="AZ23" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="BA23" t="n">
-        <v>3.05</v>
+        <v>4.2</v>
       </c>
       <c r="BB23" t="n">
-        <v>9</v>
+        <v>6.8</v>
       </c>
       <c r="BC23" t="n">
-        <v>9</v>
+        <v>6.8</v>
       </c>
       <c r="BD23" t="n">
-        <v>4.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE23" t="n">
-        <v>2.26</v>
+        <v>3.85</v>
       </c>
       <c r="BF23" t="n">
-        <v>8.199999999999999</v>
+        <v>5.5</v>
       </c>
       <c r="BG23" t="n">
-        <v>12.5</v>
+        <v>4.2</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-25 08:25:18</t>
+          <t>2026-03-25 10:30:55</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Colombian Primera B</t>
+          <t>US USL League One</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5016,67 +5016,67 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Real Soacha Cundinamarca FC</t>
+          <t>Greenville Triumph SC</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Atletico FC Cali</t>
+          <t>New York Cosmos</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.58</v>
+        <v>1.72</v>
       </c>
       <c r="G24" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="H24" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="I24" t="n">
-        <v>8.6</v>
+        <v>6</v>
       </c>
       <c r="J24" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K24" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="L24" t="n">
-        <v>1.46</v>
+        <v>1.32</v>
       </c>
       <c r="M24" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="N24" t="n">
-        <v>3.35</v>
+        <v>4.1</v>
       </c>
       <c r="O24" t="n">
-        <v>1.37</v>
+        <v>1.24</v>
       </c>
       <c r="P24" t="n">
-        <v>1.78</v>
+        <v>2.1</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.14</v>
+        <v>1.68</v>
       </c>
       <c r="R24" t="n">
-        <v>1.29</v>
+        <v>1.49</v>
       </c>
       <c r="S24" t="n">
-        <v>3.9</v>
+        <v>2.62</v>
       </c>
       <c r="T24" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="U24" t="n">
-        <v>1.74</v>
+        <v>2.16</v>
       </c>
       <c r="V24" t="n">
-        <v>1.13</v>
+        <v>1.21</v>
       </c>
       <c r="W24" t="n">
-        <v>2.52</v>
+        <v>2.32</v>
       </c>
       <c r="X24" t="n">
         <v>500</v>
@@ -5091,10 +5091,10 @@
         <v>1000</v>
       </c>
       <c r="AB24" t="n">
-        <v>7.2</v>
+        <v>500</v>
       </c>
       <c r="AC24" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AD24" t="n">
         <v>1000</v>
@@ -5106,7 +5106,7 @@
         <v>40</v>
       </c>
       <c r="AG24" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AH24" t="n">
         <v>1000</v>
@@ -5121,81 +5121,81 @@
         <v>1000</v>
       </c>
       <c r="AL24" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AM24" t="n">
         <v>1000</v>
       </c>
       <c r="AN24" t="n">
-        <v>55</v>
+        <v>29</v>
       </c>
       <c r="AO24" t="n">
         <v>1000</v>
       </c>
       <c r="AP24" t="n">
-        <v>5.6</v>
+        <v>8.4</v>
       </c>
       <c r="AQ24" t="n">
+        <v>9</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BC24" t="n">
         <v>4.2</v>
       </c>
-      <c r="AR24" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>5</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="BC24" t="n">
-        <v>3.45</v>
-      </c>
       <c r="BD24" t="n">
-        <v>8.199999999999999</v>
+        <v>3.95</v>
       </c>
       <c r="BE24" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="BF24" t="n">
-        <v>5.3</v>
+        <v>7.2</v>
       </c>
       <c r="BG24" t="n">
-        <v>4.2</v>
+        <v>3.85</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-25 08:25:18</t>
+          <t>2026-03-25 10:30:55</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>US USL League One</t>
+          <t>US United Soccer League</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5210,186 +5210,186 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Greenville Triumph SC</t>
+          <t>Lexington SC</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>New York Cosmos</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="G25" t="n">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="H25" t="n">
-        <v>4.5</v>
+        <v>5.3</v>
       </c>
       <c r="I25" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="J25" t="n">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="K25" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L25" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="M25" t="n">
         <v>1.06</v>
       </c>
       <c r="N25" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O25" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="P25" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.76</v>
+        <v>1.85</v>
       </c>
       <c r="R25" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="S25" t="n">
-        <v>2.66</v>
+        <v>3.15</v>
       </c>
       <c r="T25" t="n">
-        <v>1.78</v>
+        <v>1.84</v>
       </c>
       <c r="U25" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="V25" t="n">
         <v>1.2</v>
       </c>
       <c r="W25" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="X25" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="Y25" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="Z25" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA25" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB25" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AC25" t="n">
-        <v>14</v>
+        <v>9.6</v>
       </c>
       <c r="AD25" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AE25" t="n">
-        <v>1000</v>
+        <v>400</v>
       </c>
       <c r="AF25" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AG25" t="n">
-        <v>36</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH25" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AI25" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AK25" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AL25" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM25" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN25" t="n">
+        <v>11</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>160</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>20</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BA25" t="n">
         <v>29</v>
       </c>
-      <c r="AO25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>7</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="BA25" t="n">
-        <v>2.34</v>
-      </c>
       <c r="BB25" t="n">
-        <v>7.4</v>
+        <v>14.5</v>
       </c>
       <c r="BC25" t="n">
-        <v>3.8</v>
+        <v>15</v>
       </c>
       <c r="BD25" t="n">
-        <v>2.78</v>
+        <v>21</v>
       </c>
       <c r="BE25" t="n">
-        <v>2.36</v>
+        <v>28</v>
       </c>
       <c r="BF25" t="n">
-        <v>7.2</v>
+        <v>5.9</v>
       </c>
       <c r="BG25" t="n">
-        <v>2.34</v>
+        <v>12.5</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-25 08:25:18</t>
+          <t>2026-03-25 10:30:55</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>US United Soccer League</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5399,184 +5399,184 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Lexington SC</t>
+          <t>Boston River</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Penarol</t>
         </is>
       </c>
       <c r="F26" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="G26" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J26" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K26" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M26" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N26" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="O26" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="P26" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S26" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="U26" t="n">
         <v>1.75</v>
       </c>
-      <c r="G26" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="H26" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="I26" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="J26" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="K26" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="L26" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="M26" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N26" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="O26" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="P26" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S26" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T26" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="U26" t="n">
-        <v>2.06</v>
-      </c>
       <c r="V26" t="n">
-        <v>1.23</v>
+        <v>2.42</v>
       </c>
       <c r="W26" t="n">
-        <v>2.2</v>
+        <v>1.16</v>
       </c>
       <c r="X26" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="Y26" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>19</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>21</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>120</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>29</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>29</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>900</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>700</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>700</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>700</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>700</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>14</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>6</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>34</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>23</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>23</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>34</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>48</v>
+      </c>
+      <c r="BC26" t="n">
         <v>40</v>
       </c>
-      <c r="Z26" t="n">
-        <v>220</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>900</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>400</v>
-      </c>
-      <c r="AF26" t="n">
+      <c r="BD26" t="n">
+        <v>46</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>70</v>
+      </c>
+      <c r="BF26" t="n">
+        <v>46</v>
+      </c>
+      <c r="BG26" t="n">
         <v>12</v>
       </c>
-      <c r="AG26" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>60</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>700</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>19</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>19</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>80</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>580</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>160</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>16</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>21</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>16</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>28</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>10</v>
-      </c>
-      <c r="AY26" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AZ26" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BA26" t="n">
-        <v>29</v>
-      </c>
-      <c r="BB26" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BC26" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BD26" t="n">
-        <v>21</v>
-      </c>
-      <c r="BE26" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BF26" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BG26" t="n">
-        <v>9.4</v>
-      </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-25 08:25:18</t>
+          <t>2026-03-25 10:30:55</t>
         </is>
       </c>
     </row>
@@ -5607,7 +5607,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="G27" t="n">
         <v>2.94</v>
@@ -5616,7 +5616,7 @@
         <v>2.7</v>
       </c>
       <c r="I27" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="J27" t="n">
         <v>3.35</v>
@@ -5634,7 +5634,7 @@
         <v>4.1</v>
       </c>
       <c r="O27" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="P27" t="n">
         <v>2.06</v>
@@ -5646,7 +5646,7 @@
         <v>1.41</v>
       </c>
       <c r="S27" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="T27" t="n">
         <v>1.64</v>
@@ -5667,7 +5667,7 @@
         <v>13</v>
       </c>
       <c r="Z27" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AA27" t="n">
         <v>44</v>
@@ -5682,7 +5682,7 @@
         <v>12</v>
       </c>
       <c r="AE27" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AF27" t="n">
         <v>20</v>
@@ -5697,7 +5697,7 @@
         <v>40</v>
       </c>
       <c r="AJ27" t="n">
-        <v>85</v>
+        <v>44</v>
       </c>
       <c r="AK27" t="n">
         <v>75</v>
@@ -5721,16 +5721,16 @@
         <v>11</v>
       </c>
       <c r="AR27" t="n">
-        <v>11.5</v>
+        <v>16.5</v>
       </c>
       <c r="AS27" t="n">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="AT27" t="n">
         <v>12</v>
       </c>
       <c r="AU27" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV27" t="n">
         <v>10.5</v>
@@ -5751,7 +5751,7 @@
         <v>23</v>
       </c>
       <c r="BB27" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="BC27" t="n">
         <v>26</v>
@@ -5763,21 +5763,21 @@
         <v>12.5</v>
       </c>
       <c r="BF27" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="BG27" t="n">
-        <v>20</v>
+        <v>15.5</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-25 08:25:18</t>
+          <t>2026-03-25 10:30:55</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5787,378 +5787,184 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>22:00:00</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Boston River</t>
+          <t>America de Cali S.A</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Penarol</t>
+          <t>Llaneros FC</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>6.6</v>
+        <v>1.59</v>
       </c>
       <c r="G28" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="H28" t="n">
         <v>7.6</v>
       </c>
-      <c r="H28" t="n">
-        <v>1.66</v>
-      </c>
       <c r="I28" t="n">
-        <v>1.71</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J28" t="n">
-        <v>3.65</v>
+        <v>3.95</v>
       </c>
       <c r="K28" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="L28" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="M28" t="n">
         <v>1.09</v>
       </c>
       <c r="N28" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="O28" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="P28" t="n">
-        <v>1.69</v>
+        <v>1.74</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.32</v>
+        <v>2.26</v>
       </c>
       <c r="R28" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="S28" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="T28" t="n">
         <v>2.2</v>
       </c>
       <c r="U28" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="V28" t="n">
-        <v>2.4</v>
+        <v>1.14</v>
       </c>
       <c r="W28" t="n">
-        <v>1.16</v>
+        <v>2.6</v>
       </c>
       <c r="X28" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>65</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>950</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>950</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>15</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>970</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>17</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>10</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV28" t="n">
         <v>11.5</v>
       </c>
-      <c r="Y28" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>19</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD28" t="n">
+      <c r="AW28" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>13</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BF28" t="n">
         <v>10.5</v>
       </c>
-      <c r="AE28" t="n">
-        <v>22</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>120</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>29</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>29</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>55</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>900</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>700</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>700</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>700</v>
-      </c>
-      <c r="AN28" t="n">
-        <v>700</v>
-      </c>
-      <c r="AO28" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AP28" t="n">
-        <v>10</v>
-      </c>
-      <c r="AQ28" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AR28" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>18</v>
-      </c>
-      <c r="AX28" t="n">
-        <v>28</v>
-      </c>
-      <c r="AY28" t="n">
-        <v>24</v>
-      </c>
-      <c r="AZ28" t="n">
-        <v>21</v>
-      </c>
-      <c r="BA28" t="n">
-        <v>34</v>
-      </c>
-      <c r="BB28" t="n">
-        <v>48</v>
-      </c>
-      <c r="BC28" t="n">
-        <v>42</v>
-      </c>
-      <c r="BD28" t="n">
-        <v>44</v>
-      </c>
-      <c r="BE28" t="n">
-        <v>70</v>
-      </c>
-      <c r="BF28" t="n">
-        <v>48</v>
-      </c>
       <c r="BG28" t="n">
-        <v>12</v>
+        <v>9.6</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-25 08:25:18</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Colombian Primera A</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>22:00:00</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>America de Cali S.A</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Llaneros FC</t>
-        </is>
-      </c>
-      <c r="F29" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="G29" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="H29" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="I29" t="n">
-        <v>8</v>
-      </c>
-      <c r="J29" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="K29" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="L29" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="M29" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="N29" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="O29" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="P29" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="S29" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="T29" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="V29" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="W29" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="X29" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>970</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>65</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>9</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>950</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>950</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>970</v>
-      </c>
-      <c r="AK29" t="n">
-        <v>970</v>
-      </c>
-      <c r="AL29" t="n">
-        <v>50</v>
-      </c>
-      <c r="AM29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN29" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AO29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP29" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AQ29" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AR29" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AS29" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AT29" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AU29" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV29" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AW29" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AX29" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AY29" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ29" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BA29" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BB29" t="n">
-        <v>6</v>
-      </c>
-      <c r="BC29" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BD29" t="n">
-        <v>42</v>
-      </c>
-      <c r="BE29" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BF29" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BG29" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BH29" t="inlineStr">
-        <is>
-          <t>2026-03-25 08:25:18</t>
+          <t>2026-03-25 10:30:55</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-25.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH12"/>
+  <dimension ref="A1:BH10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -733,7 +733,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Colombian Primera B</t>
+          <t>Argentinian Primera Division</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -743,36 +743,36 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Envigado</t>
+          <t>Deportivo Riestra</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Bogota</t>
+          <t>San Lorenzo</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>75</v>
+        <v>18.5</v>
       </c>
       <c r="G2" t="n">
-        <v>350</v>
+        <v>34</v>
       </c>
       <c r="H2" t="n">
-        <v>1.09</v>
+        <v>28</v>
       </c>
       <c r="I2" t="n">
-        <v>1.12</v>
+        <v>270</v>
       </c>
       <c r="J2" t="n">
-        <v>8.4</v>
+        <v>1.07</v>
       </c>
       <c r="K2" t="n">
-        <v>13.5</v>
+        <v>1.08</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -787,16 +787,16 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="R2" t="n">
-        <v>1.26</v>
+        <v>1.01</v>
       </c>
       <c r="S2" t="n">
-        <v>4.2</v>
+        <v>280</v>
       </c>
       <c r="T2" t="n">
         <v>0</v>
@@ -805,10 +805,10 @@
         <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>9.199999999999999</v>
+        <v>1.02</v>
       </c>
       <c r="W2" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X2" t="n">
         <v>1000</v>
@@ -826,10 +826,10 @@
         <v>1000</v>
       </c>
       <c r="AC2" t="n">
-        <v>1000</v>
+        <v>1.08</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.32</v>
+        <v>1000</v>
       </c>
       <c r="AE2" t="n">
         <v>1000</v>
@@ -844,7 +844,7 @@
         <v>1000</v>
       </c>
       <c r="AI2" t="n">
-        <v>960</v>
+        <v>1000</v>
       </c>
       <c r="AJ2" t="n">
         <v>1000</v>
@@ -862,72 +862,72 @@
         <v>1000</v>
       </c>
       <c r="AO2" t="n">
-        <v>980</v>
+        <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>220</v>
+        <v>1000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>220</v>
+        <v>1000</v>
       </c>
       <c r="AR2" t="n">
-        <v>220</v>
+        <v>1000</v>
       </c>
       <c r="AS2" t="n">
-        <v>220</v>
+        <v>1000</v>
       </c>
       <c r="AT2" t="n">
-        <v>220</v>
+        <v>19.5</v>
       </c>
       <c r="AU2" t="n">
-        <v>5.9</v>
+        <v>1.03</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.19</v>
+        <v>16.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>5.9</v>
+        <v>27</v>
       </c>
       <c r="AX2" t="n">
-        <v>220</v>
+        <v>19.5</v>
       </c>
       <c r="AY2" t="n">
-        <v>5.9</v>
+        <v>17</v>
       </c>
       <c r="AZ2" t="n">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>5.8</v>
+        <v>46</v>
       </c>
       <c r="BB2" t="n">
-        <v>220</v>
+        <v>19.5</v>
       </c>
       <c r="BC2" t="n">
-        <v>5.9</v>
+        <v>38</v>
       </c>
       <c r="BD2" t="n">
-        <v>5.6</v>
+        <v>48</v>
       </c>
       <c r="BE2" t="n">
-        <v>5.9</v>
+        <v>42</v>
       </c>
       <c r="BF2" t="n">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="BG2" t="n">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-25 18:52:04</t>
+          <t>2026-03-25 20:57:51</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Colombian Primera B</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -937,36 +937,36 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cerro</t>
+          <t>Barranquilla</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Juventud De Las Piedras</t>
+          <t>Leones FC</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="G3" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="H3" t="n">
-        <v>1.01</v>
+        <v>100</v>
       </c>
       <c r="I3" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="J3" t="n">
-        <v>11.5</v>
+        <v>100</v>
       </c>
       <c r="K3" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -975,34 +975,34 @@
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="Q3" t="n">
-        <v>100</v>
+        <v>6.8</v>
       </c>
       <c r="R3" t="n">
         <v>1.01</v>
       </c>
       <c r="S3" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="T3" t="n">
         <v>1.39</v>
       </c>
       <c r="U3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="V3" t="n">
         <v>1.01</v>
       </c>
       <c r="W3" t="n">
-        <v>11</v>
+        <v>100</v>
       </c>
       <c r="X3" t="n">
         <v>1000</v>
@@ -1017,7 +1017,7 @@
         <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.22</v>
+        <v>1000</v>
       </c>
       <c r="AC3" t="n">
         <v>1000</v>
@@ -1029,7 +1029,7 @@
         <v>1000</v>
       </c>
       <c r="AF3" t="n">
-        <v>1000</v>
+        <v>1.2</v>
       </c>
       <c r="AG3" t="n">
         <v>1000</v>
@@ -1059,69 +1059,69 @@
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>5.6</v>
+        <v>110</v>
       </c>
       <c r="AQ3" t="n">
-        <v>5.6</v>
+        <v>110</v>
       </c>
       <c r="AR3" t="n">
-        <v>5.6</v>
+        <v>110</v>
       </c>
       <c r="AS3" t="n">
-        <v>5.6</v>
+        <v>110</v>
       </c>
       <c r="AT3" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AX3" t="n">
         <v>1.08</v>
       </c>
-      <c r="AU3" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>5.3</v>
-      </c>
       <c r="AY3" t="n">
-        <v>5.6</v>
+        <v>6.8</v>
       </c>
       <c r="AZ3" t="n">
-        <v>5.6</v>
+        <v>40</v>
       </c>
       <c r="BA3" t="n">
-        <v>5.8</v>
+        <v>3.45</v>
       </c>
       <c r="BB3" t="n">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="BC3" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="BD3" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="BE3" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="BF3" t="n">
-        <v>5.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG3" t="n">
-        <v>5.6</v>
+        <v>3.45</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-25 18:52:04</t>
+          <t>2026-03-25 20:57:51</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Paraguayan Primera Division</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1131,184 +1131,184 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>19:30:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Deportivo Riestra</t>
+          <t>Guarani (Par)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>San Lorenzo</t>
+          <t>Club 2 de Mayo de Pedro Juan Cab</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.54</v>
+        <v>1.21</v>
       </c>
       <c r="G4" t="n">
-        <v>2.58</v>
+        <v>1.23</v>
       </c>
       <c r="H4" t="n">
-        <v>4</v>
+        <v>42</v>
       </c>
       <c r="I4" t="n">
-        <v>4.1</v>
+        <v>65</v>
       </c>
       <c r="J4" t="n">
-        <v>2.72</v>
+        <v>6</v>
       </c>
       <c r="K4" t="n">
-        <v>2.76</v>
+        <v>7</v>
       </c>
       <c r="L4" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="O4" t="n">
-        <v>1.89</v>
+        <v>1.81</v>
       </c>
       <c r="P4" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.85</v>
+        <v>5.4</v>
       </c>
       <c r="R4" t="n">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="S4" t="n">
-        <v>9.6</v>
+        <v>23</v>
       </c>
       <c r="T4" t="n">
-        <v>2.78</v>
+        <v>3.4</v>
       </c>
       <c r="U4" t="n">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="V4" t="n">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="W4" t="n">
-        <v>1.63</v>
+        <v>5.4</v>
       </c>
       <c r="X4" t="n">
-        <v>5.3</v>
+        <v>1000</v>
       </c>
       <c r="Y4" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="Z4" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AA4" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>6.2</v>
+        <v>2.24</v>
       </c>
       <c r="AC4" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AD4" t="n">
-        <v>23</v>
+        <v>55</v>
       </c>
       <c r="AE4" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AF4" t="n">
-        <v>13</v>
+        <v>4.8</v>
       </c>
       <c r="AG4" t="n">
         <v>15</v>
       </c>
       <c r="AH4" t="n">
-        <v>38</v>
+        <v>90</v>
       </c>
       <c r="AI4" t="n">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="AK4" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AL4" t="n">
-        <v>120</v>
+        <v>550</v>
       </c>
       <c r="AM4" t="n">
         <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>85</v>
+        <v>110</v>
       </c>
       <c r="AO4" t="n">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>5.2</v>
+        <v>1000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AR4" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AS4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>44</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>280</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>70</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>320</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>55</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>260</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>30</v>
+      </c>
+      <c r="BF4" t="n">
         <v>80</v>
       </c>
-      <c r="AT4" t="n">
-        <v>6</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>75</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>12</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>14</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>30</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>80</v>
-      </c>
-      <c r="BB4" t="n">
+      <c r="BG4" t="n">
         <v>34</v>
       </c>
-      <c r="BC4" t="n">
-        <v>42</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>90</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>240</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>55</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>85</v>
-      </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-25 18:52:04</t>
+          <t>2026-03-25 20:57:51</t>
         </is>
       </c>
     </row>
@@ -1325,17 +1325,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Barranquilla</t>
+          <t>Real Soacha Cundinamarca FC</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Leones FC</t>
+          <t>Atletico FC Cali</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1345,171 +1345,171 @@
         <v>1.83</v>
       </c>
       <c r="H5" t="n">
-        <v>5.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>5.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J5" t="n">
-        <v>3.7</v>
+        <v>2.92</v>
       </c>
       <c r="K5" t="n">
-        <v>3.75</v>
+        <v>3</v>
       </c>
       <c r="L5" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.83</v>
+        <v>4.2</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.12</v>
+        <v>1.3</v>
       </c>
       <c r="R5" t="n">
-        <v>1.31</v>
+        <v>1.72</v>
       </c>
       <c r="S5" t="n">
-        <v>4.1</v>
+        <v>2.32</v>
       </c>
       <c r="T5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>1.22</v>
+        <v>1.12</v>
       </c>
       <c r="W5" t="n">
         <v>2.2</v>
       </c>
       <c r="X5" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="Y5" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="Z5" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AA5" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="AC5" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>320</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>80</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>75</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK5" t="n">
         <v>8.4</v>
       </c>
-      <c r="AD5" t="n">
-        <v>21</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>90</v>
-      </c>
-      <c r="AF5" t="n">
+      <c r="AL5" t="n">
+        <v>22</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>230</v>
+      </c>
+      <c r="AP5" t="n">
         <v>10.5</v>
       </c>
-      <c r="AG5" t="n">
+      <c r="AQ5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BG5" t="n">
         <v>10</v>
       </c>
-      <c r="AH5" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>90</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>21</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>42</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>150</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>14</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>130</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>11</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>15</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>36</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>23</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>7</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>70</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>9</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>20</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>65</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>34</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>70</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>65</v>
-      </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-25 18:52:04</t>
+          <t>2026-03-25 20:57:51</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Paraguayan Primera Division</t>
+          <t>US USL League One</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1519,191 +1519,191 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>19:30:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Guarani (Par)</t>
+          <t>Greenville Triumph SC</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Club 2 de Mayo de Pedro Juan Cab</t>
+          <t>New York Cosmos</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.92</v>
+        <v>2.24</v>
       </c>
       <c r="G6" t="n">
-        <v>1.97</v>
+        <v>2.44</v>
       </c>
       <c r="H6" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="I6" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="J6" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="K6" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC6" t="n">
         <v>4.7</v>
       </c>
-      <c r="J6" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="K6" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="N6" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="P6" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="S6" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="W6" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="X6" t="n">
-        <v>11</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>34</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>120</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AC6" t="n">
+      <c r="AD6" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>42</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AH6" t="n">
         <v>8</v>
       </c>
-      <c r="AD6" t="n">
-        <v>32</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>310</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>11</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>10</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>60</v>
-      </c>
       <c r="AI6" t="n">
-        <v>230</v>
+        <v>40</v>
       </c>
       <c r="AJ6" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AK6" t="n">
-        <v>23</v>
+        <v>11.5</v>
       </c>
       <c r="AL6" t="n">
-        <v>110</v>
+        <v>19</v>
       </c>
       <c r="AM6" t="n">
-        <v>150</v>
+        <v>95</v>
       </c>
       <c r="AN6" t="n">
-        <v>18.5</v>
+        <v>24</v>
       </c>
       <c r="AO6" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AP6" t="n">
         <v>10</v>
       </c>
       <c r="AQ6" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AR6" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="AS6" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="AT6" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AU6" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AV6" t="n">
         <v>7.4</v>
       </c>
-      <c r="AV6" t="n">
-        <v>17</v>
-      </c>
       <c r="AW6" t="n">
-        <v>44</v>
+        <v>9.6</v>
       </c>
       <c r="AX6" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC6" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="AY6" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>20</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>34</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>20</v>
-      </c>
       <c r="BD6" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="BE6" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="BF6" t="n">
-        <v>17.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG6" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-25 18:52:04</t>
+          <t>2026-03-25 20:57:51</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Colombian Primera B</t>
+          <t>US United Soccer League</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1718,186 +1718,186 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Real Soacha Cundinamarca FC</t>
+          <t>Lexington SC</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Atletico FC Cali</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.58</v>
+        <v>2.04</v>
       </c>
       <c r="G7" t="n">
-        <v>1.63</v>
+        <v>2.16</v>
       </c>
       <c r="H7" t="n">
-        <v>7.4</v>
+        <v>5.6</v>
       </c>
       <c r="I7" t="n">
-        <v>8.6</v>
+        <v>6.2</v>
       </c>
       <c r="J7" t="n">
-        <v>3.8</v>
+        <v>2.78</v>
       </c>
       <c r="K7" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="O7" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="S7" t="n">
+        <v>15</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="X7" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>44</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>320</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>48</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>340</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>19</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>95</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>38</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>80</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>330</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>90</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>10</v>
+      </c>
+      <c r="AT7" t="n">
         <v>4.1</v>
       </c>
-      <c r="L7" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N7" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="P7" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S7" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="W7" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="X7" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>22</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>65</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>290</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AC7" t="n">
+      <c r="AU7" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC7" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AD7" t="n">
-        <v>30</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>160</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>28</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>150</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>15</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>500</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>210</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>11</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>210</v>
-      </c>
-      <c r="AP7" t="n">
+      <c r="BD7" t="n">
+        <v>10</v>
+      </c>
+      <c r="BE7" t="n">
         <v>10.5</v>
       </c>
-      <c r="AQ7" t="n">
-        <v>19</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>40</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>13</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>25</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AY7" t="n">
+      <c r="BF7" t="n">
         <v>9.4</v>
       </c>
-      <c r="AZ7" t="n">
-        <v>24</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>13</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>12</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>16</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>9.800000000000001</v>
-      </c>
       <c r="BG7" t="n">
-        <v>36</v>
+        <v>10.5</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-25 18:52:04</t>
+          <t>2026-03-25 20:57:51</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>US USL League One</t>
+          <t>US United Soccer League</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1907,191 +1907,191 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Greenville Triumph SC</t>
+          <t>Sporting Club Jacksonville</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>New York Cosmos</t>
+          <t>Miami FC</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.72</v>
+        <v>2.24</v>
       </c>
       <c r="G8" t="n">
-        <v>1.75</v>
+        <v>2.32</v>
       </c>
       <c r="H8" t="n">
-        <v>4.7</v>
+        <v>3.55</v>
       </c>
       <c r="I8" t="n">
-        <v>5.8</v>
+        <v>3.7</v>
       </c>
       <c r="J8" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="K8" t="n">
-        <v>4.5</v>
+        <v>3.55</v>
       </c>
       <c r="L8" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.14</v>
+        <v>11</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.72</v>
+        <v>1.09</v>
       </c>
       <c r="R8" t="n">
-        <v>1.49</v>
+        <v>3.25</v>
       </c>
       <c r="S8" t="n">
-        <v>2.8</v>
+        <v>1.4</v>
       </c>
       <c r="T8" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.21</v>
+        <v>1.35</v>
       </c>
       <c r="W8" t="n">
-        <v>2.32</v>
+        <v>1.76</v>
       </c>
       <c r="X8" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="Y8" t="n">
         <v>1000</v>
       </c>
       <c r="Z8" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AA8" t="n">
         <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AC8" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AD8" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AE8" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AF8" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AG8" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>16</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>11</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>21</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>11</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>11</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>11</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AV8" t="n">
         <v>10.5</v>
       </c>
-      <c r="AH8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>900</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>29</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP8" t="n">
+      <c r="AW8" t="n">
         <v>8.4</v>
       </c>
-      <c r="AQ8" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>6</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>7</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>7.6</v>
-      </c>
       <c r="AX8" t="n">
-        <v>8.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="AY8" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AZ8" t="n">
-        <v>8.199999999999999</v>
+        <v>6.8</v>
       </c>
       <c r="BA8" t="n">
-        <v>6.6</v>
+        <v>13.5</v>
       </c>
       <c r="BB8" t="n">
-        <v>7.8</v>
+        <v>11</v>
       </c>
       <c r="BC8" t="n">
-        <v>7.6</v>
+        <v>12</v>
       </c>
       <c r="BD8" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BE8" t="n">
-        <v>6.4</v>
+        <v>17.5</v>
       </c>
       <c r="BF8" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="BG8" t="n">
-        <v>4.9</v>
+        <v>12.5</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-25 18:52:04</t>
+          <t>2026-03-25 20:57:51</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>US United Soccer League</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2101,191 +2101,191 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Lexington SC</t>
+          <t>Boston River</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Penarol</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.84</v>
+        <v>38</v>
       </c>
       <c r="G9" t="n">
-        <v>1.87</v>
+        <v>46</v>
       </c>
       <c r="H9" t="n">
-        <v>4.7</v>
+        <v>1.15</v>
       </c>
       <c r="I9" t="n">
-        <v>5</v>
+        <v>1.16</v>
       </c>
       <c r="J9" t="n">
-        <v>3.95</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>4</v>
+        <v>9.6</v>
       </c>
       <c r="L9" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>4.4</v>
+        <v>6.4</v>
       </c>
       <c r="O9" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="P9" t="n">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="R9" t="n">
-        <v>1.46</v>
+        <v>1.39</v>
       </c>
       <c r="S9" t="n">
-        <v>3</v>
+        <v>3.45</v>
       </c>
       <c r="T9" t="n">
-        <v>1.78</v>
+        <v>2.32</v>
       </c>
       <c r="U9" t="n">
-        <v>2.14</v>
+        <v>1.64</v>
       </c>
       <c r="V9" t="n">
-        <v>1.25</v>
+        <v>7.2</v>
       </c>
       <c r="W9" t="n">
-        <v>2.14</v>
+        <v>1.02</v>
       </c>
       <c r="X9" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="Y9" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="Z9" t="n">
-        <v>120</v>
+        <v>4.8</v>
       </c>
       <c r="AA9" t="n">
-        <v>900</v>
+        <v>7.2</v>
       </c>
       <c r="AB9" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AC9" t="n">
-        <v>9.4</v>
+        <v>13.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>55</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AE9" t="n">
-        <v>170</v>
+        <v>14.5</v>
       </c>
       <c r="AF9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>70</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>44</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>70</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>600</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>320</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>400</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>7</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>17</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>17</v>
+      </c>
+      <c r="AU9" t="n">
         <v>12</v>
       </c>
-      <c r="AG9" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>390</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>120</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>65</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>580</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>11</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>310</v>
-      </c>
-      <c r="AP9" t="n">
+      <c r="AV9" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AW9" t="n">
         <v>13</v>
       </c>
-      <c r="AQ9" t="n">
-        <v>15</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>28</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>30</v>
-      </c>
       <c r="AX9" t="n">
-        <v>9.800000000000001</v>
+        <v>17</v>
       </c>
       <c r="AY9" t="n">
-        <v>9.199999999999999</v>
+        <v>50</v>
       </c>
       <c r="AZ9" t="n">
-        <v>12.5</v>
+        <v>32</v>
       </c>
       <c r="BA9" t="n">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="BB9" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="BC9" t="n">
-        <v>15.5</v>
+        <v>24</v>
       </c>
       <c r="BD9" t="n">
-        <v>21</v>
+        <v>200</v>
       </c>
       <c r="BE9" t="n">
-        <v>10.5</v>
+        <v>250</v>
       </c>
       <c r="BF9" t="n">
-        <v>9</v>
+        <v>44</v>
       </c>
       <c r="BG9" t="n">
-        <v>10.5</v>
+        <v>6.2</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-25 18:52:04</t>
+          <t>2026-03-25 20:57:51</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>US United Soccer League</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2295,572 +2295,184 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>22:00:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Sporting Club Jacksonville</t>
+          <t>America de Cali S.A</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Miami FC</t>
+          <t>Llaneros FC</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.66</v>
+        <v>1.51</v>
       </c>
       <c r="G10" t="n">
-        <v>2.72</v>
+        <v>1.52</v>
       </c>
       <c r="H10" t="n">
-        <v>2.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>2.88</v>
+        <v>9.6</v>
       </c>
       <c r="J10" t="n">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="K10" t="n">
-        <v>3.7</v>
+        <v>4.4</v>
       </c>
       <c r="L10" t="n">
-        <v>1.37</v>
+        <v>1.46</v>
       </c>
       <c r="M10" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="N10" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="O10" t="n">
-        <v>1.27</v>
+        <v>1.39</v>
       </c>
       <c r="P10" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q10" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q10" t="n">
-        <v>1.8</v>
-      </c>
       <c r="R10" t="n">
-        <v>1.47</v>
+        <v>1.29</v>
       </c>
       <c r="S10" t="n">
-        <v>3</v>
+        <v>4.2</v>
       </c>
       <c r="T10" t="n">
-        <v>1.67</v>
+        <v>2.3</v>
       </c>
       <c r="U10" t="n">
-        <v>2.34</v>
+        <v>1.7</v>
       </c>
       <c r="V10" t="n">
-        <v>1.53</v>
+        <v>1.11</v>
       </c>
       <c r="W10" t="n">
-        <v>1.58</v>
+        <v>2.92</v>
       </c>
       <c r="X10" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>24</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>75</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>370</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>36</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>180</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>40</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>18</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>250</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>320</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>21</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>60</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>14</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>30</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>14</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>27</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>14</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BC10" t="n">
         <v>17</v>
       </c>
-      <c r="Y10" t="n">
+      <c r="BD10" t="n">
+        <v>34</v>
+      </c>
+      <c r="BE10" t="n">
         <v>13.5</v>
       </c>
-      <c r="Z10" t="n">
-        <v>21</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>46</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>28</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>19</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>15</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>36</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>38</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>27</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>36</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>70</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>19</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>21</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>15</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>18</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>40</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>24</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>17</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>13</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>32</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>30</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>24</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>30</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>44</v>
-      </c>
       <c r="BF10" t="n">
-        <v>17</v>
+        <v>9.4</v>
       </c>
       <c r="BG10" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-25 18:52:04</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Uruguayan Primera Division</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>20:30:00</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Boston River</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Penarol</t>
-        </is>
-      </c>
-      <c r="F11" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="G11" t="n">
-        <v>7</v>
-      </c>
-      <c r="H11" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="I11" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="J11" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="K11" t="n">
-        <v>4</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="N11" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="O11" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="P11" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="S11" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="V11" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="X11" t="n">
-        <v>12</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>16</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>20</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>55</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>27</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>28</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>48</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>230</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>130</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>450</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>220</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>190</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>16</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>18</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>38</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>23</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>23</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>40</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>60</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>40</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>75</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>70</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>85</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>12</v>
-      </c>
-      <c r="BH11" t="inlineStr">
-        <is>
-          <t>2026-03-25 18:52:04</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Colombian Primera A</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>22:00:00</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>America de Cali S.A</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Llaneros FC</t>
-        </is>
-      </c>
-      <c r="F12" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="G12" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="H12" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="I12" t="n">
-        <v>9</v>
-      </c>
-      <c r="J12" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="K12" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="M12" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N12" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="O12" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="P12" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S12" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="W12" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="X12" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>22</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>75</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>370</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>34</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>190</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>40</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>180</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>11</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>290</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>11</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>19</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>60</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>6</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>9</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>29</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>12</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>7</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>28</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>12</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>12</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>17</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>21</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>11</v>
-      </c>
-      <c r="BH12" t="inlineStr">
-        <is>
-          <t>2026-03-25 18:52:04</t>
+          <t>2026-03-25 20:57:51</t>
         </is>
       </c>
     </row>
